--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -850,7 +850,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>LionDriver as installed on a 2020 Toyota Corolla LE (US) with comma 3X and integrated panda, software BL-004 (structure and failure analysis written at BL-001, risk analysis at BL-004), while the vehicle is driven on public roads by a licensed driver. Functions F1-F7 per fmea-plan.md section 3.1, plus F8 (stock vehicle safety functions are preserved), added because the harness intercepts the stock ADAS camera.</t>
+          <t>LionDriver as installed on the reference configuration CFG-001 (Corolla E210 · ZRE212 · US, US sedan MY2020-2022) with comma 3X and integrated panda, software BL-004 (structure and failure analysis written at BL-001, risk analysis at BL-004), while the vehicle is driven on public roads by a licensed driver. Functions F1-F7 per fmea-plan.md section 3.1, plus F8 (stock vehicle safety functions are preserved), added because the harness intercepts the stock ADAS camera.</t>
         </is>
       </c>
     </row>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$82</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Worksheet'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Structure'!$A$1:$E$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -802,7 +802,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.6 · draft</t>
+          <t>0.7 · draft</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>RT-1</t>
+          <t>RT-2</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>10 (9)</t>
+          <t>14 (13)</t>
         </is>
       </c>
     </row>
@@ -15666,7 +15666,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.6 · BL-004&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.7 · BL-004&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -15681,7 +15681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16155,8 +16155,116 @@
         </is>
       </c>
     </row>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="59" t="inlineStr">
+        <is>
+          <t>SFM-ACT-012</t>
+        </is>
+      </c>
+      <c r="B12" s="59" t="inlineStr">
+        <is>
+          <t>monitoring</t>
+        </is>
+      </c>
+      <c r="C12" s="59" t="inlineStr">
+        <is>
+          <t>Measure on the HIL bench and the reference car (WP-V-05) how the panda reacts to over-limit and not-engaged torque frames, and what the EPS does when frames are refused; re-rate the MSR rows from code-derived to measured timing</t>
+        </is>
+      </c>
+      <c r="D12" s="59" t="inlineStr"/>
+      <c r="E12" s="59" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F12" s="59" t="inlineStr"/>
+      <c r="G12" s="59" t="inlineStr"/>
+      <c r="H12" s="59" t="inlineStr"/>
+      <c r="I12" s="59" t="inlineStr"/>
+    </row>
+    <row r="13" ht="46.5" customHeight="1">
+      <c r="A13" s="59" t="inlineStr">
+        <is>
+          <t>SFM-ACT-013</t>
+        </is>
+      </c>
+      <c r="B13" s="59" t="inlineStr">
+        <is>
+          <t>monitoring</t>
+        </is>
+      </c>
+      <c r="C13" s="59" t="inlineStr">
+        <is>
+          <t>Check on the host, within the SG-01 FTTI, that the panda reports controls_allowed false while the item is disengaged (the reverse of the BL-004 controlsMismatch counter), with a disable and an alert</t>
+        </is>
+      </c>
+      <c r="D13" s="59" t="inlineStr"/>
+      <c r="E13" s="59" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F13" s="59" t="inlineStr"/>
+      <c r="G13" s="59" t="inlineStr"/>
+      <c r="H13" s="59" t="inlineStr"/>
+      <c r="I13" s="59" t="inlineStr"/>
+    </row>
+    <row r="14" ht="46.5" customHeight="1">
+      <c r="A14" s="59" t="inlineStr">
+        <is>
+          <t>SFM-ACT-014</t>
+        </is>
+      </c>
+      <c r="B14" s="59" t="inlineStr">
+        <is>
+          <t>monitoring</t>
+        </is>
+      </c>
+      <c r="C14" s="59" t="inlineStr">
+        <is>
+          <t>Specify in the TSC a steering-direction plausibility monitor (commanded torque sign against measured yaw rate and lane-relative lateral motion), or justify its absence against HZ-003</t>
+        </is>
+      </c>
+      <c r="D14" s="59" t="inlineStr"/>
+      <c r="E14" s="59" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F14" s="59" t="inlineStr"/>
+      <c r="G14" s="59" t="inlineStr"/>
+      <c r="H14" s="59" t="inlineStr"/>
+      <c r="I14" s="59" t="inlineStr"/>
+    </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="59" t="inlineStr">
+        <is>
+          <t>SFM-ACT-015</t>
+        </is>
+      </c>
+      <c r="B15" s="59" t="inlineStr">
+        <is>
+          <t>monitoring</t>
+        </is>
+      </c>
+      <c r="C15" s="59" t="inlineStr">
+        <is>
+          <t>Detect stale commands and inputs within the SG-01 FTTI: command-frame freshness in the MCU with an active zero frame (TSR-408, TSR-109) and frozen-content and age checks on model outputs in controlsd (TSR-602, AIR-17)</t>
+        </is>
+      </c>
+      <c r="D15" s="59" t="inlineStr"/>
+      <c r="E15" s="59" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F15" s="59" t="inlineStr"/>
+      <c r="G15" s="59" t="inlineStr"/>
+      <c r="H15" s="59" t="inlineStr"/>
+      <c r="I15" s="59" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I11"/>
+  <autoFilter ref="A1:I15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$82</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Worksheet'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Structure'!$A$1:$E$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -802,7 +802,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.7 · draft</t>
+          <t>0.8 · draft</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>14 (13)</t>
+          <t>17 (16)</t>
         </is>
       </c>
     </row>
@@ -15666,7 +15666,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.7 · BL-004&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.8 · BL-004&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -15681,7 +15681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16155,7 +16155,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
+    <row r="12" ht="73.5" customHeight="1">
       <c r="A12" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-012</t>
@@ -16168,7 +16168,7 @@
       </c>
       <c r="C12" s="59" t="inlineStr">
         <is>
-          <t>Measure on the HIL bench and the reference car (WP-V-05) how the panda reacts to over-limit and not-engaged torque frames, and what the EPS does when frames are refused; re-rate the MSR rows from code-derived to measured timing</t>
+          <t>Measure on the HIL bench and the reference car (WP-V-05) how the panda reacts to over-limit and not-engaged steering and acceleration frames and to driver brake, gas and cancel inputs, and what the EPS and PCM do when frames are refused; re-rate the MSR rows from code-derived to measured timing</t>
         </is>
       </c>
       <c r="D12" s="59" t="inlineStr"/>
@@ -16263,8 +16263,89 @@
       <c r="H15" s="59" t="inlineStr"/>
       <c r="I15" s="59" t="inlineStr"/>
     </row>
+    <row r="16" ht="46.5" customHeight="1">
+      <c r="A16" s="59" t="inlineStr">
+        <is>
+          <t>SFM-ACT-016</t>
+        </is>
+      </c>
+      <c r="B16" s="59" t="inlineStr">
+        <is>
+          <t>monitoring</t>
+        </is>
+      </c>
+      <c r="C16" s="59" t="inlineStr">
+        <is>
+          <t>Supervise driver override in the panda: driver steering torque above the override threshold limits or revokes lateral authority within the SG-05 0.2 s budget (TSR-304)</t>
+        </is>
+      </c>
+      <c r="D16" s="59" t="inlineStr"/>
+      <c r="E16" s="59" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F16" s="59" t="inlineStr"/>
+      <c r="G16" s="59" t="inlineStr"/>
+      <c r="H16" s="59" t="inlineStr"/>
+      <c r="I16" s="59" t="inlineStr"/>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="59" t="inlineStr">
+        <is>
+          <t>SFM-ACT-017</t>
+        </is>
+      </c>
+      <c r="B17" s="59" t="inlineStr">
+        <is>
+          <t>monitoring</t>
+        </is>
+      </c>
+      <c r="C17" s="59" t="inlineStr">
+        <is>
+          <t>Add WP-S-04 FTTI rows for the warning paths without one (insufficient lateral control, late or insufficient braking warnings, SG-008 unintended engagement, driver monitoring), so these mechanisms can be compared with a time budget</t>
+        </is>
+      </c>
+      <c r="D17" s="59" t="inlineStr"/>
+      <c r="E17" s="59" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F17" s="59" t="inlineStr"/>
+      <c r="G17" s="59" t="inlineStr"/>
+      <c r="H17" s="59" t="inlineStr"/>
+      <c r="I17" s="59" t="inlineStr"/>
+    </row>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="59" t="inlineStr">
+        <is>
+          <t>SFM-ACT-018</t>
+        </is>
+      </c>
+      <c r="B18" s="59" t="inlineStr">
+        <is>
+          <t>monitoring</t>
+        </is>
+      </c>
+      <c r="C18" s="59" t="inlineStr">
+        <is>
+          <t>Detect silent loss of the actuation path: report forwarded and refused TX frames from the panda, and compare EPS and PCM acceptance (LKA_STATE, ACC status) with the commands, warning within the SG-02/06 1 s budget</t>
+        </is>
+      </c>
+      <c r="D18" s="59" t="inlineStr"/>
+      <c r="E18" s="59" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F18" s="59" t="inlineStr"/>
+      <c r="G18" s="59" t="inlineStr"/>
+      <c r="H18" s="59" t="inlineStr"/>
+      <c r="I18" s="59" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I15"/>
+  <autoFilter ref="A1:I18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -802,7 +802,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.8 · draft</t>
+          <t>0.9 · draft</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>BL-004</t>
+          <t>BL-005</t>
         </is>
       </c>
     </row>
@@ -838,11 +838,11 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="90" customHeight="1">
+    <row r="10" ht="105" customHeight="1">
       <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Scope</t>
@@ -850,7 +850,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>LionDriver as installed on the reference configuration CFG-001 (Corolla E210 · ZRE212 · US, US sedan MY2020-2022) with comma 3X and integrated panda, software BL-004 (structure and failure analysis written at BL-001, risk analysis at BL-004), while the vehicle is driven on public roads by a licensed driver. Functions F1-F7 per fmea-plan.md section 3.1, plus F8 (stock vehicle safety functions are preserved), added because the harness intercepts the stock ADAS camera.</t>
+          <t>LionDriver as installed on the reference configuration CFG-001 (Corolla E210 · ZRE212 · US, US sedan MY2020-2022) with comma 3X and integrated panda, software BL-005 (structure and failure analysis written at BL-001, risk analysis at BL-004, MSR re-rated at BL-005), while the vehicle is driven on public roads by a licensed driver. Functions F1-F7 per fmea-plan.md section 3.1, plus F8 (stock vehicle safety functions are preserved), added because the harness intercepts the stock ADAS camera.</t>
         </is>
       </c>
     </row>
@@ -8272,7 +8272,7 @@
       <c r="R44" s="37" t="inlineStr"/>
       <c r="S44" s="37" t="inlineStr"/>
     </row>
-    <row r="45" ht="195" customHeight="1">
+    <row r="45" ht="222" customHeight="1">
       <c r="A45" s="38" t="n"/>
       <c r="B45" s="38" t="n"/>
       <c r="C45" s="38" t="n"/>
@@ -8330,7 +8330,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• selfdrived raises controlsMismatch (IMMEDIATE_DISABLE) when the panda reports controls not allowed while engaged, but only after 200 frames (2 s at 100 Hz)</t>
+            <t>• selfdrived raises controlsMismatch (IMMEDIATE_DISABLE) when the panda reports controls not allowed while engaged, after 2 consecutive pandaStates samples and at most 0.5 s (BL-005, TSR-621; 200 cumulative frames, about 2 s, at BL-004)</t>
           </r>
           <r>
             <rPr>
@@ -8339,7 +8339,7 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   openpilot/selfdrive/selfdrived/selfdrived.py:338</t>
+   openpilot/selfdrive/selfdrived/supervision.py</t>
           </r>
         </is>
       </c>
@@ -8351,15 +8351,24 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• No pre-release test targets this cause</t>
-          </r>
-        </is>
-      </c>
-      <c r="L45" s="46" t="n">
-        <v>10</v>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• BL-005: test_supervision.py checks the 2-sample and 0.5 s bounds and the 0.3 s engagement grace of controlsMismatch (tests.yaml unit_tests on every push and PR); targeted, not proven by mutation (RT-1 D 8). At BL-004 no test targeted this cause</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/selfdrived/tests/test_supervision.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L45" s="35" t="n">
+        <v>8</v>
       </c>
       <c r="M45" s="36" t="inlineStr">
         <is>
@@ -14689,9 +14698,9 @@
           </r>
         </is>
       </c>
-      <c r="O78" s="48" t="inlineStr">
-        <is>
-          <t>open</t>
+      <c r="O78" s="50" t="inlineStr">
+        <is>
+          <t>in progress</t>
         </is>
       </c>
       <c r="P78" s="40" t="inlineStr"/>
@@ -15666,7 +15675,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.8 · BL-004&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.9 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -15997,7 +16006,7 @@
       <c r="H7" s="59" t="inlineStr"/>
       <c r="I7" s="59" t="inlineStr"/>
     </row>
-    <row r="8" ht="46.5" customHeight="1">
+    <row r="8" ht="73.5" customHeight="1">
       <c r="A8" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-008</t>
@@ -16020,7 +16029,7 @@
       </c>
       <c r="E8" s="59" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>in progress</t>
         </is>
       </c>
       <c r="F8" s="59" t="inlineStr">
@@ -16030,7 +16039,11 @@
       </c>
       <c r="G8" s="59" t="inlineStr"/>
       <c r="H8" s="59" t="inlineStr"/>
-      <c r="I8" s="59" t="inlineStr"/>
+      <c r="I8" s="59" t="inlineStr">
+        <is>
+          <t>BL-005: the reference build is the default (LionDriver #36), the panda accepts only TOYOTA parameter 73 (reference_lock.h) and pandad configures a car mode only on a reference panda (#41). Fuzzy fingerprint matches are still accepted on the host (SFM-032.C1)</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="100.5" customHeight="1">
       <c r="A9" s="59" t="inlineStr">
@@ -16073,7 +16086,7 @@
       <c r="H9" s="59" t="inlineStr"/>
       <c r="I9" s="59" t="inlineStr"/>
     </row>
-    <row r="10" ht="60" customHeight="1">
+    <row r="10" ht="73.5" customHeight="1">
       <c r="A10" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-010</t>
@@ -16111,7 +16124,7 @@
       <c r="H10" s="59" t="inlineStr"/>
       <c r="I10" s="59" t="inlineStr">
         <is>
-          <t>controlsMismatch debounce cut from 200 cumulative samples (~2 s) to 2 consecutive samples, at most 0.5 s (change-2026-10-13-host-supervision.md); FTTI justification of SOFT_DISABLE reactions open</t>
+          <t>controlsMismatch debounce cut from 200 cumulative samples (~2 s) to 2 consecutive samples, at most 0.5 s (change-2026-10-13-host-supervision.md); credited at BL-005 (SFM-015.C2 M 6). FTTI justification of SOFT_DISABLE reactions open</t>
         </is>
       </c>
     </row>
@@ -16182,7 +16195,7 @@
       <c r="H12" s="59" t="inlineStr"/>
       <c r="I12" s="59" t="inlineStr"/>
     </row>
-    <row r="13" ht="46.5" customHeight="1">
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-013</t>
@@ -16195,7 +16208,7 @@
       </c>
       <c r="C13" s="59" t="inlineStr">
         <is>
-          <t>Check on the host, within the SG-01 FTTI, that the panda reports controls_allowed false while the item is disengaged (the reverse of the BL-004 controlsMismatch counter), with a disable and an alert</t>
+          <t>Check on the host, within the SG-01 FTTI, that the panda reports controls_allowed false while the item is disengaged (the reverse of the controlsMismatch check, which at BL-005 still covers only engaged with authority withdrawn), with a disable and an alert</t>
         </is>
       </c>
       <c r="D13" s="59" t="inlineStr"/>
@@ -16236,7 +16249,7 @@
       <c r="H14" s="59" t="inlineStr"/>
       <c r="I14" s="59" t="inlineStr"/>
     </row>
-    <row r="15" ht="60" customHeight="1">
+    <row r="15" ht="87" customHeight="1">
       <c r="A15" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-015</t>
@@ -16255,13 +16268,17 @@
       <c r="D15" s="59" t="inlineStr"/>
       <c r="E15" s="59" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>in progress</t>
         </is>
       </c>
       <c r="F15" s="59" t="inlineStr"/>
       <c r="G15" s="59" t="inlineStr"/>
       <c r="H15" s="59" t="inlineStr"/>
-      <c r="I15" s="59" t="inlineStr"/>
+      <c r="I15" s="59" t="inlineStr">
+        <is>
+          <t>BL-005: command-frame arrival in the MCU (TSR-408, 50 ms STEERING_LKA, reference build by default) and input age checks in controlsd (TSR-602) are in. Open: the active zero frame (TSR-109), a frozen-content check on model outputs, and stale data with fresh timestamps (SFM-006.C1 to C3)</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="46.5" customHeight="1">
       <c r="A16" s="59" t="inlineStr">
@@ -16317,7 +16334,7 @@
       <c r="H17" s="59" t="inlineStr"/>
       <c r="I17" s="59" t="inlineStr"/>
     </row>
-    <row r="18" ht="60" customHeight="1">
+    <row r="18" ht="73.5" customHeight="1">
       <c r="A18" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-018</t>
@@ -16336,13 +16353,17 @@
       <c r="D18" s="59" t="inlineStr"/>
       <c r="E18" s="59" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>in progress</t>
         </is>
       </c>
       <c r="F18" s="59" t="inlineStr"/>
       <c r="G18" s="59" t="inlineStr"/>
       <c r="H18" s="59" t="inlineStr"/>
-      <c r="I18" s="59" t="inlineStr"/>
+      <c r="I18" s="59" t="inlineStr">
+        <is>
+          <t>BL-005: frames that stop reaching the panda are detected (TSR-408) and alerted within 0.5 s (TSR-621), credited on SFM-005.C2 and SFM-011.C2. Open: frames that reach the panda but are not accepted by the EPS or PCM (SFM-005.C1, SFM-011.C1; TSR-626)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I18"/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$82</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Worksheet'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Structure'!$A$1:$E$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -802,7 +802,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.9 · draft</t>
+          <t>0.10 · draft</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>17 (16)</t>
+          <t>18 (17)</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1687,7 @@
       <c r="R5" s="45" t="inlineStr"/>
       <c r="S5" s="45" t="inlineStr"/>
     </row>
-    <row r="6" ht="100.5" customHeight="1">
+    <row r="6" ht="195" customHeight="1">
       <c r="A6" s="30" t="inlineStr">
         <is>
           <r>
@@ -1926,11 +1926,39 @@
             </rPr>
             <t>Derive steering and acceleration envelopes from measurements on the reference vehicle and set the panda limits from them, independently of the SoC limits (same as SWF-ACT-003, FSC FOI-001)</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-ACT-019 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Revoke lateral authority in the panda when it rejects a steering frame while authority is granted, and keep it revoked until a new valid engagement (TSR-108; lead decision DQ-060, option A). At BL-005 the frame is dropped and only the host disengages (pandaTxBlocked)</t>
+          </r>
         </is>
       </c>
       <c r="O6" s="47" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>open
+open</t>
         </is>
       </c>
       <c r="P6" s="33" t="inlineStr"/>
@@ -1938,7 +1966,7 @@
       <c r="R6" s="37" t="inlineStr"/>
       <c r="S6" s="37" t="inlineStr"/>
     </row>
-    <row r="7" ht="168" customHeight="1">
+    <row r="7" ht="276" customHeight="1">
       <c r="A7" s="38" t="n"/>
       <c r="B7" s="38" t="n"/>
       <c r="C7" s="38" t="n"/>
@@ -2053,11 +2081,39 @@
             </rPr>
             <t>Produce SOTIF / ISO PAS 8800 evidence for the neural-network elements (driving model, lead detection, driver monitoring model) per WP-V-02..04, including fault-induced inputs (corrupted or stale frames)</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-ACT-019 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Revoke lateral authority in the panda when it rejects a steering frame while authority is granted, and keep it revoked until a new valid engagement (TSR-108; lead decision DQ-060, option A). At BL-005 the frame is dropped and only the host disengages (pandaTxBlocked)</t>
+          </r>
         </is>
       </c>
       <c r="O7" s="47" t="inlineStr">
         <is>
           <t>open
+open
 open</t>
         </is>
       </c>
@@ -2210,7 +2266,7 @@
       <c r="R8" s="37" t="inlineStr"/>
       <c r="S8" s="37" t="inlineStr"/>
     </row>
-    <row r="9" ht="195" customHeight="1">
+    <row r="9" ht="289.5" customHeight="1">
       <c r="A9" s="39" t="n"/>
       <c r="B9" s="39" t="n"/>
       <c r="C9" s="39" t="n"/>
@@ -2360,11 +2416,39 @@
             </rPr>
             <t>Requirements-based tests for the host safety-relevant functions (selfdrived, controlsd, pandad, car interface, locationd bounds, monitoring policy), proven by mutation or fault injection and run as a CI gate (see SWF host actions)</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-ACT-019 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Revoke lateral authority in the panda when it rejects a steering frame while authority is granted, and keep it revoked until a new valid engagement (TSR-108; lead decision DQ-060, option A). At BL-005 the frame is dropped and only the host disengages (pandaTxBlocked)</t>
+          </r>
         </is>
       </c>
       <c r="O9" s="48" t="inlineStr">
         <is>
           <t>open
+open
 open</t>
         </is>
       </c>
@@ -11563,7 +11647,7 @@
       <c r="R62" s="45" t="inlineStr"/>
       <c r="S62" s="45" t="inlineStr"/>
     </row>
-    <row r="63" ht="100.5" customHeight="1">
+    <row r="63" ht="114" customHeight="1">
       <c r="A63" s="51" t="inlineStr">
         <is>
           <r>
@@ -11800,7 +11884,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Decide in the FSC how the item reacts when driver awareness reaches zero (driverUnresponsive3 / driverDistracted3 have no disable reaction at BL-004) and implement the decision</t>
+            <t>Decide in the FSC how the item reacts when driver awareness reaches zero (driverUnresponsive3 / driverDistracted3 have no disable reaction at BL-004 or BL-005) and implement the decision. DQ-205 (answered) makes this the safe state of SG-010 (ASIL A); the reaction itself is still to be decided</t>
           </r>
         </is>
       </c>
@@ -15675,7 +15759,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.9 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.10 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -15690,7 +15774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15895,7 +15979,7 @@
       <c r="H4" s="59" t="inlineStr"/>
       <c r="I4" s="59" t="inlineStr"/>
     </row>
-    <row r="5" ht="46.5" customHeight="1">
+    <row r="5" ht="73.5" customHeight="1">
       <c r="A5" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-005</t>
@@ -15908,7 +15992,7 @@
       </c>
       <c r="C5" s="59" t="inlineStr">
         <is>
-          <t>Decide in the FSC how the item reacts when driver awareness reaches zero (driverUnresponsive3 / driverDistracted3 have no disable reaction at BL-004) and implement the decision</t>
+          <t>Decide in the FSC how the item reacts when driver awareness reaches zero (driverUnresponsive3 / driverDistracted3 have no disable reaction at BL-004 or BL-005) and implement the decision. DQ-205 (answered) makes this the safe state of SG-010 (ASIL A); the reaction itself is still to be decided</t>
         </is>
       </c>
       <c r="D5" s="59" t="inlineStr">
@@ -16280,7 +16364,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="46.5" customHeight="1">
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-016</t>
@@ -16293,7 +16377,7 @@
       </c>
       <c r="C16" s="59" t="inlineStr">
         <is>
-          <t>Supervise driver override in the panda: driver steering torque above the override threshold limits or revokes lateral authority within the SG-05 0.2 s budget (TSR-304)</t>
+          <t>Supervise driver override in the panda: driver steering torque above the override threshold limits or revokes lateral authority within the SG-05 0.2 s budget (TSR-304). Behaviour decided by the lead (DQ-053, option A): back off on override and show a cue</t>
         </is>
       </c>
       <c r="D16" s="59" t="inlineStr"/>
@@ -16365,8 +16449,41 @@
         </is>
       </c>
     </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="59" t="inlineStr">
+        <is>
+          <t>SFM-ACT-019</t>
+        </is>
+      </c>
+      <c r="B19" s="59" t="inlineStr">
+        <is>
+          <t>design change</t>
+        </is>
+      </c>
+      <c r="C19" s="59" t="inlineStr">
+        <is>
+          <t>Revoke lateral authority in the panda when it rejects a steering frame while authority is granted, and keep it revoked until a new valid engagement (TSR-108; lead decision DQ-060, option A). At BL-005 the frame is dropped and only the host disengages (pandaTxBlocked)</t>
+        </is>
+      </c>
+      <c r="D19" s="59" t="inlineStr"/>
+      <c r="E19" s="59" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F19" s="59" t="inlineStr">
+        <is>
+          <t>SFM-002.C1
+SFM-002.C2
+SFM-002.C4</t>
+        </is>
+      </c>
+      <c r="G19" s="59" t="inlineStr"/>
+      <c r="H19" s="59" t="inlineStr"/>
+      <c r="I19" s="59" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I18"/>
+  <autoFilter ref="A1:I19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -11,12 +11,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Worksheet" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Structure" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MSR" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$82</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Worksheet'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Structure'!$A$1:$E$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'MSR'!$A$2:$P$66</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'MSR'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -126,6 +129,12 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="001B2430"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="005B6676"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -252,7 +261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -398,6 +407,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -765,7 +780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C33"/>
+  <dimension ref="B2:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -935,104 +950,112 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>FMEA-MSR (msr: complete)</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>60 rated, 4 exempt; MSR AP H 60, M 0, L 0 (provisional table)</t>
+        </is>
+      </c>
+    </row>
     <row r="21">
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Monitoring M</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>1–4: 0 · 5–6: 15 · 7–8: 16 · 9–10: 29 (see sheet MSR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="12" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>High: an action or a rationale is required</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="14" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C25" s="13" t="inlineStr">
         <is>
           <t>Medium: an action or a rationale is recommended</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="15" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="16" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>Aa</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>Amber text: no test targets the cause (detection 9 or 10)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="17" t="inlineStr"/>
-      <c r="C26" s="13" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="17" t="inlineStr"/>
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>Yellow cells on the Worksheet: reviewer input (decision from the list, comment)</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="6" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Review sign-off</t>
         </is>
       </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>Reviewer</t>
-        </is>
-      </c>
-      <c r="C29" s="19" t="inlineStr"/>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t>Independence level</t>
-        </is>
-      </c>
-      <c r="C30" s="19" t="inlineStr"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="18" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Reviewer</t>
         </is>
       </c>
       <c r="C31" s="19" t="inlineStr"/>
     </row>
-    <row r="32" ht="30" customHeight="1">
+    <row r="32" ht="18" customHeight="1">
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>Result (accepted / accepted with findings / rejected)</t>
+          <t>Independence level</t>
         </is>
       </c>
       <c r="C32" s="19" t="inlineStr"/>
@@ -1040,10 +1063,26 @@
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="18" t="inlineStr">
         <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C33" s="19" t="inlineStr"/>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>Result (accepted / accepted with findings / rejected)</t>
+        </is>
+      </c>
+      <c r="C34" s="19" t="inlineStr"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="B35" s="18" t="inlineStr">
+        <is>
           <t>Findings reference</t>
         </is>
       </c>
-      <c r="C33" s="19" t="inlineStr"/>
+      <c r="C35" s="19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16842,4 +16881,4118 @@
   <autoFilter ref="A1:E20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:P66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="61" t="inlineStr">
+        <is>
+          <t>FMEA-MSR (monitoring and system response, msr-plan.md): S, F, M and MSR AP per rating-tables.md §7 (RT-2). The MSR AP table is provisional until the handbook table is transcribed (decision register DQ-207). Exempt causes are rated in the FMEA named in the reason.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Failure mode</t>
+        </is>
+      </c>
+      <c r="B2" s="29" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C2" s="29" t="inlineStr">
+        <is>
+          <t>Cause</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>Failure cause</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>Diagnostic</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>System response</t>
+        </is>
+      </c>
+      <c r="G2" s="28" t="inlineStr">
+        <is>
+          <t>Effect after the response</t>
+        </is>
+      </c>
+      <c r="H2" s="29" t="inlineStr">
+        <is>
+          <t>S after</t>
+        </is>
+      </c>
+      <c r="I2" s="29" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J2" s="29" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K2" s="29" t="inlineStr">
+        <is>
+          <t>MSR AP</t>
+        </is>
+      </c>
+      <c r="L2" s="28" t="inlineStr">
+        <is>
+          <t>Timing (FTTI · FDTI + FRTI)</t>
+        </is>
+      </c>
+      <c r="M2" s="29" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="N2" s="28" t="inlineStr">
+        <is>
+          <t>Monitoring actions</t>
+        </is>
+      </c>
+      <c r="O2" s="28" t="inlineStr">
+        <is>
+          <t>Reviewer decision</t>
+        </is>
+      </c>
+      <c r="P2" s="28" t="inlineStr">
+        <is>
+          <t>Reviewer comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="87" customHeight="1">
+      <c r="A3" s="34" t="inlineStr">
+        <is>
+          <t>SFM-001 · Steering torque applied when not engaged</t>
+        </is>
+      </c>
+      <c r="B3" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" s="33" t="inlineStr">
+        <is>
+          <t>SFM-001.C1</t>
+        </is>
+      </c>
+      <c r="D3" s="34" t="inlineStr">
+        <is>
+          <t>State machine reports active while disabled</t>
+        </is>
+      </c>
+      <c r="E3" s="34" t="inlineStr">
+        <is>
+          <t>Panda Toyota safety model checks every STEERING_LKA frame: a torque request while controls_allowed is false is refused. controls_allowed needs PCM cruise engaged on the car bus and the heartbeat engaged state, so a wrong host state alone does not grant it</t>
+        </is>
+      </c>
+      <c r="F3" s="34" t="inlineStr">
+        <is>
+          <t>Frame not sent; no torque request reaches the EPS</t>
+        </is>
+      </c>
+      <c r="G3" s="34" t="inlineStr">
+        <is>
+          <t>No assist torque while not engaged; manual steering unaffected. Whether refused frames set an EPS LKA fault indication is to be confirmed on the reference car (SFM-ACT-012)</t>
+        </is>
+      </c>
+      <c r="H3" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J3" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L3" s="34" t="inlineStr">
+        <is>
+          <t>SG-01 continuous limits · per frame
+0 + 10 ms</t>
+        </is>
+      </c>
+      <c r="M3" s="33" t="inlineStr">
+        <is>
+          <t>code derived</t>
+        </is>
+      </c>
+      <c r="N3" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-012 · open</t>
+        </is>
+      </c>
+      <c r="O3" s="37" t="inlineStr"/>
+      <c r="P3" s="37" t="inlineStr"/>
+    </row>
+    <row r="4" ht="73.5" customHeight="1">
+      <c r="A4" s="34" t="inlineStr">
+        <is>
+          <t>SFM-001 · Steering torque applied when not engaged</t>
+        </is>
+      </c>
+      <c r="B4" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" s="33" t="inlineStr">
+        <is>
+          <t>SFM-001.C2</t>
+        </is>
+      </c>
+      <c r="D4" s="34" t="inlineStr">
+        <is>
+          <t>Panda allows steering TX without valid engagement (controls_allowed set incorrectly)</t>
+        </is>
+      </c>
+      <c r="E4" s="34" t="inlineStr">
+        <is>
+          <t>None for this cause. controlsd sends torque only while latActive, so the host channel masks the panda fault but nothing detects it; the TSR-621 mismatch check (BL-005) still covers only the opposite direction (enabled, panda not allowed)</t>
+        </is>
+      </c>
+      <c r="F4" s="34" t="inlineStr">
+        <is>
+          <t>None; the fault stays latent until the host also commands torque</t>
+        </is>
+      </c>
+      <c r="G4" s="34" t="inlineStr">
+        <is>
+          <t>Unchanged: torque while not engaged once the host also fails (dual-point, DFA/FTA)</t>
+        </is>
+      </c>
+      <c r="H4" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K4" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L4" s="34" t="inlineStr"/>
+      <c r="M4" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N4" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-013 · open</t>
+        </is>
+      </c>
+      <c r="O4" s="37" t="inlineStr"/>
+      <c r="P4" s="37" t="inlineStr"/>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>SFM-001 · Steering torque applied when not engaged</t>
+        </is>
+      </c>
+      <c r="B5" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" s="33" t="inlineStr">
+        <is>
+          <t>SFM-001.C3</t>
+        </is>
+      </c>
+      <c r="D5" s="34" t="inlineStr">
+        <is>
+          <t>Steering message packed with non-zero torque/request bit while latActive is false</t>
+        </is>
+      </c>
+      <c r="E5" s="34" t="inlineStr">
+        <is>
+          <t>Panda refuses a STEERING_LKA frame carrying torque or the request bit while controls_allowed is false (checked on every frame)</t>
+        </is>
+      </c>
+      <c r="F5" s="34" t="inlineStr">
+        <is>
+          <t>Frame not sent; no torque request reaches the EPS</t>
+        </is>
+      </c>
+      <c r="G5" s="34" t="inlineStr">
+        <is>
+          <t>No assist torque while not engaged; manual steering unaffected (EPS reaction to refused frames to confirm, SFM-ACT-012)</t>
+        </is>
+      </c>
+      <c r="H5" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L5" s="34" t="inlineStr">
+        <is>
+          <t>SG-01 continuous limits · per frame
+0 + 10 ms</t>
+        </is>
+      </c>
+      <c r="M5" s="33" t="inlineStr">
+        <is>
+          <t>code derived</t>
+        </is>
+      </c>
+      <c r="N5" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-012 · open</t>
+        </is>
+      </c>
+      <c r="O5" s="37" t="inlineStr"/>
+      <c r="P5" s="37" t="inlineStr"/>
+    </row>
+    <row r="6" ht="141" customHeight="1">
+      <c r="A6" s="34" t="inlineStr">
+        <is>
+          <t>SFM-002 · Steering torque or torque rate above limits</t>
+        </is>
+      </c>
+      <c r="B6" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" s="33" t="inlineStr">
+        <is>
+          <t>SFM-002.C1</t>
+        </is>
+      </c>
+      <c r="D6" s="34" t="inlineStr">
+        <is>
+          <t>Lateral controller output too high (gain, torque model, saturation logic)</t>
+        </is>
+      </c>
+      <c r="E6" s="34" t="inlineStr">
+        <is>
+          <t>Panda checks torque magnitude and rate of every STEERING_LKA frame against the Toyota limits</t>
+        </is>
+      </c>
+      <c r="F6" s="34" t="inlineStr">
+        <is>
+          <t>Over-limit frame refused; torque stays inside the envelope. BL-005, while engaged, the refusal also gives pandaTxBlocked, an immediate disable with a take-over alert at the next pandaStates sample (TSR-615)</t>
+        </is>
+      </c>
+      <c r="G6" s="34" t="inlineStr">
+        <is>
+          <t>Torque bounded by the panda envelope. Repeated refusals interrupt LKA frames and assist may drop without a LionDriver alert at BL-004; since BL-005 the first refusal while engaged disengages with an alert (pandaTxBlocked). The envelope itself is not yet derived from vehicle measurements (SFM-ACT-001), so S after the response stays 10</t>
+        </is>
+      </c>
+      <c r="H6" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L6" s="34" t="inlineStr">
+        <is>
+          <t>SG-01 continuous limits · per frame
+0 + 10 ms</t>
+        </is>
+      </c>
+      <c r="M6" s="33" t="inlineStr">
+        <is>
+          <t>code derived</t>
+        </is>
+      </c>
+      <c r="N6" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-012 · open</t>
+        </is>
+      </c>
+      <c r="O6" s="37" t="inlineStr"/>
+      <c r="P6" s="37" t="inlineStr"/>
+    </row>
+    <row r="7" ht="100.5" customHeight="1">
+      <c r="A7" s="34" t="inlineStr">
+        <is>
+          <t>SFM-002 · Steering torque or torque rate above limits</t>
+        </is>
+      </c>
+      <c r="B7" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="33" t="inlineStr">
+        <is>
+          <t>SFM-002.C2</t>
+        </is>
+      </c>
+      <c r="D7" s="34" t="inlineStr">
+        <is>
+          <t>Model outputs excessive desired curvature</t>
+        </is>
+      </c>
+      <c r="E7" s="34" t="inlineStr">
+        <is>
+          <t>Panda checks torque magnitude and rate of every STEERING_LKA frame; an excessive curvature request is bounded where it becomes torque</t>
+        </is>
+      </c>
+      <c r="F7" s="34" t="inlineStr">
+        <is>
+          <t>Over-limit frame refused; torque stays inside the envelope. BL-005, while engaged, the refusal also gives pandaTxBlocked, an immediate disable with a take-over alert at the next pandaStates sample (TSR-615)</t>
+        </is>
+      </c>
+      <c r="G7" s="34" t="inlineStr">
+        <is>
+          <t>Torque bounded by the panda envelope; an in-envelope wrong curvature still steers (SOTIF, SFM-ACT-009)</t>
+        </is>
+      </c>
+      <c r="H7" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I7" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="J7" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K7" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L7" s="34" t="inlineStr">
+        <is>
+          <t>SG-01 continuous limits · per frame
+0 + 10 ms</t>
+        </is>
+      </c>
+      <c r="M7" s="33" t="inlineStr">
+        <is>
+          <t>code derived</t>
+        </is>
+      </c>
+      <c r="N7" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-012 · open</t>
+        </is>
+      </c>
+      <c r="O7" s="37" t="inlineStr"/>
+      <c r="P7" s="37" t="inlineStr"/>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="34" t="inlineStr">
+        <is>
+          <t>SFM-002 · Steering torque or torque rate above limits</t>
+        </is>
+      </c>
+      <c r="B8" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C8" s="33" t="inlineStr">
+        <is>
+          <t>SFM-002.C3</t>
+        </is>
+      </c>
+      <c r="D8" s="34" t="inlineStr">
+        <is>
+          <t>Safety model torque/rate limits wrong for this vehicle or not enforced</t>
+        </is>
+      </c>
+      <c r="E8" s="34" t="inlineStr">
+        <is>
+          <t>With the panda limits themselves wrong, only the host excessive-actuation check remains: lateral acceleration above 2x the ISO 11270 limit for 0.25 s (WP-S-04 T-21)</t>
+        </is>
+      </c>
+      <c r="F8" s="34" t="inlineStr">
+        <is>
+          <t>SOFT_DISABLE: actuation continues for up to 3 s while the alert counts down (T-16); 3.25 s exceeds the 0.5 s SG-01 FTTI</t>
+        </is>
+      </c>
+      <c r="G8" s="34" t="inlineStr">
+        <is>
+          <t>Excessive torque continues for up to 3.25 s before disengagement</t>
+        </is>
+      </c>
+      <c r="H8" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J8" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="K8" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L8" s="34" t="inlineStr">
+        <is>
+          <t>250 + 3000 ms</t>
+        </is>
+      </c>
+      <c r="M8" s="33" t="inlineStr">
+        <is>
+          <t>code derived</t>
+        </is>
+      </c>
+      <c r="N8" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-010 · in progress</t>
+        </is>
+      </c>
+      <c r="O8" s="37" t="inlineStr"/>
+      <c r="P8" s="37" t="inlineStr"/>
+    </row>
+    <row r="9" ht="100.5" customHeight="1">
+      <c r="A9" s="34" t="inlineStr">
+        <is>
+          <t>SFM-002 · Steering torque or torque rate above limits</t>
+        </is>
+      </c>
+      <c r="B9" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C9" s="33" t="inlineStr">
+        <is>
+          <t>SFM-002.C4</t>
+        </is>
+      </c>
+      <c r="D9" s="34" t="inlineStr">
+        <is>
+          <t>Wrong vehicle parameters (steer ratio, lateral accel factor, torque offsets) from online learners</t>
+        </is>
+      </c>
+      <c r="E9" s="34" t="inlineStr">
+        <is>
+          <t>Panda torque magnitude and rate limits are opendbc constants, independent of the learned vehicle parameters, and are checked on every frame</t>
+        </is>
+      </c>
+      <c r="F9" s="34" t="inlineStr">
+        <is>
+          <t>Over-limit frame refused; torque stays inside the envelope. BL-005, while engaged, the refusal also gives pandaTxBlocked, an immediate disable with a take-over alert at the next pandaStates sample (TSR-615)</t>
+        </is>
+      </c>
+      <c r="G9" s="34" t="inlineStr">
+        <is>
+          <t>Torque bounded by the panda envelope; in-envelope tracking error remains (SFM-004)</t>
+        </is>
+      </c>
+      <c r="H9" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L9" s="34" t="inlineStr">
+        <is>
+          <t>SG-01 continuous limits · per frame
+0 + 10 ms</t>
+        </is>
+      </c>
+      <c r="M9" s="33" t="inlineStr">
+        <is>
+          <t>code derived</t>
+        </is>
+      </c>
+      <c r="N9" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-012 · open</t>
+        </is>
+      </c>
+      <c r="O9" s="37" t="inlineStr"/>
+      <c r="P9" s="37" t="inlineStr"/>
+    </row>
+    <row r="10" ht="46.5" customHeight="1">
+      <c r="A10" s="34" t="inlineStr">
+        <is>
+          <t>SFM-003 · Steering in the wrong direction (away from lane center)</t>
+        </is>
+      </c>
+      <c r="B10" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C10" s="33" t="inlineStr">
+        <is>
+          <t>SFM-003.C1</t>
+        </is>
+      </c>
+      <c r="D10" s="34" t="inlineStr">
+        <is>
+          <t>Calibration (camera extrinsics) wrong or not converged</t>
+        </is>
+      </c>
+      <c r="E10" s="34" t="inlineStr">
+        <is>
+          <t>None detects the direction: the panda rate limit bounds how fast the deviation grows, and only the driver notices it</t>
+        </is>
+      </c>
+      <c r="F10" s="34" t="inlineStr">
+        <is>
+          <t>None automatic; steerOverride hands lateral control to the driver once the driver steers</t>
+        </is>
+      </c>
+      <c r="G10" s="34" t="inlineStr">
+        <is>
+          <t>Unchanged: deviation away from the lane centre at the limited rate until the driver overrides</t>
+        </is>
+      </c>
+      <c r="H10" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I10" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J10" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K10" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L10" s="34" t="inlineStr"/>
+      <c r="M10" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N10" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-014 · open</t>
+        </is>
+      </c>
+      <c r="O10" s="37" t="inlineStr"/>
+      <c r="P10" s="37" t="inlineStr"/>
+    </row>
+    <row r="11" ht="46.5" customHeight="1">
+      <c r="A11" s="34" t="inlineStr">
+        <is>
+          <t>SFM-003 · Steering in the wrong direction (away from lane center)</t>
+        </is>
+      </c>
+      <c r="B11" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>SFM-003.C2</t>
+        </is>
+      </c>
+      <c r="D11" s="34" t="inlineStr">
+        <is>
+          <t>Sign convention error in steering signal parse or pack for this car</t>
+        </is>
+      </c>
+      <c r="E11" s="34" t="inlineStr">
+        <is>
+          <t>None detects the direction: the panda rate limit bounds how fast the deviation grows, and only the driver notices it</t>
+        </is>
+      </c>
+      <c r="F11" s="34" t="inlineStr">
+        <is>
+          <t>None automatic; steerOverride hands lateral control to the driver once the driver steers</t>
+        </is>
+      </c>
+      <c r="G11" s="34" t="inlineStr">
+        <is>
+          <t>Unchanged: deviation away from the lane centre at the limited rate until the driver overrides</t>
+        </is>
+      </c>
+      <c r="H11" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J11" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K11" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L11" s="34" t="inlineStr"/>
+      <c r="M11" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N11" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-014 · open</t>
+        </is>
+      </c>
+      <c r="O11" s="37" t="inlineStr"/>
+      <c r="P11" s="37" t="inlineStr"/>
+    </row>
+    <row r="12" ht="46.5" customHeight="1">
+      <c r="A12" s="34" t="inlineStr">
+        <is>
+          <t>SFM-003 · Steering in the wrong direction (away from lane center)</t>
+        </is>
+      </c>
+      <c r="B12" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" s="33" t="inlineStr">
+        <is>
+          <t>SFM-003.C3</t>
+        </is>
+      </c>
+      <c r="D12" s="34" t="inlineStr">
+        <is>
+          <t>Model desired curvature has wrong sign (corrupted frame, wrong camera stream)</t>
+        </is>
+      </c>
+      <c r="E12" s="34" t="inlineStr">
+        <is>
+          <t>None detects the direction: the panda rate limit bounds how fast the deviation grows, and only the driver notices it</t>
+        </is>
+      </c>
+      <c r="F12" s="34" t="inlineStr">
+        <is>
+          <t>None automatic; steerOverride hands lateral control to the driver once the driver steers</t>
+        </is>
+      </c>
+      <c r="G12" s="34" t="inlineStr">
+        <is>
+          <t>Unchanged: deviation away from the lane centre at the limited rate until the driver overrides</t>
+        </is>
+      </c>
+      <c r="H12" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I12" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J12" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K12" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L12" s="34" t="inlineStr"/>
+      <c r="M12" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N12" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-014 · open</t>
+        </is>
+      </c>
+      <c r="O12" s="37" t="inlineStr"/>
+      <c r="P12" s="37" t="inlineStr"/>
+    </row>
+    <row r="13" ht="46.5" customHeight="1">
+      <c r="A13" s="34" t="inlineStr">
+        <is>
+          <t>SFM-003 · Steering in the wrong direction (away from lane center)</t>
+        </is>
+      </c>
+      <c r="B13" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>SFM-003.C4</t>
+        </is>
+      </c>
+      <c r="D13" s="34" t="inlineStr">
+        <is>
+          <t>Device mount moved after calibration</t>
+        </is>
+      </c>
+      <c r="E13" s="34" t="inlineStr">
+        <is>
+          <t>None detects the direction: the panda rate limit bounds how fast the deviation grows, and only the driver notices it</t>
+        </is>
+      </c>
+      <c r="F13" s="34" t="inlineStr">
+        <is>
+          <t>None automatic; steerOverride hands lateral control to the driver once the driver steers</t>
+        </is>
+      </c>
+      <c r="G13" s="34" t="inlineStr">
+        <is>
+          <t>Unchanged: deviation away from the lane centre at the limited rate until the driver overrides</t>
+        </is>
+      </c>
+      <c r="H13" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I13" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K13" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L13" s="34" t="inlineStr"/>
+      <c r="M13" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N13" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-014 · open</t>
+        </is>
+      </c>
+      <c r="O13" s="37" t="inlineStr"/>
+      <c r="P13" s="37" t="inlineStr"/>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="34" t="inlineStr">
+        <is>
+          <t>SFM-004 · Insufficient lateral control (undershoot in curves, drift toward lane edge)</t>
+        </is>
+      </c>
+      <c r="B14" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" s="33" t="inlineStr">
+        <is>
+          <t>SFM-004.C1</t>
+        </is>
+      </c>
+      <c r="D14" s="34" t="inlineStr">
+        <is>
+          <t>Safety model torque limit below what the curve requires (by design)</t>
+        </is>
+      </c>
+      <c r="E14" s="34" t="inlineStr">
+        <is>
+          <t>steerSaturated warns when the controller is saturated and undershoots the curve by more than 1.2x; the lane departure warning fires as the car nears the line</t>
+        </is>
+      </c>
+      <c r="F14" s="34" t="inlineStr">
+        <is>
+          <t>Audible and visual warning; lateral control stays active, the driver steers</t>
+        </is>
+      </c>
+      <c r="G14" s="34" t="inlineStr">
+        <is>
+          <t>Driver warned and takes over; no FTTI defined for the warning path</t>
+        </is>
+      </c>
+      <c r="H14" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I14" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J14" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="K14" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L14" s="34" t="inlineStr"/>
+      <c r="M14" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N14" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-017 · open</t>
+        </is>
+      </c>
+      <c r="O14" s="37" t="inlineStr"/>
+      <c r="P14" s="37" t="inlineStr"/>
+    </row>
+    <row r="15" ht="73.5" customHeight="1">
+      <c r="A15" s="34" t="inlineStr">
+        <is>
+          <t>SFM-004 · Insufficient lateral control (undershoot in curves, drift toward lane edge)</t>
+        </is>
+      </c>
+      <c r="B15" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C15" s="33" t="inlineStr">
+        <is>
+          <t>SFM-004.C2</t>
+        </is>
+      </c>
+      <c r="D15" s="34" t="inlineStr">
+        <is>
+          <t>EPS limits or rejects torque request (EPS fault, torque limit, lockout)</t>
+        </is>
+      </c>
+      <c r="E15" s="34" t="inlineStr">
+        <is>
+          <t>steerSaturated warns when the controller is saturated and undershoots the curve by more than 1.2x; the lane departure warning fires as the car nears the line; an EPS fault signal also raises steerUnavailable</t>
+        </is>
+      </c>
+      <c r="F15" s="34" t="inlineStr">
+        <is>
+          <t>Audible and visual warning; lateral control stays active, the driver steers</t>
+        </is>
+      </c>
+      <c r="G15" s="34" t="inlineStr">
+        <is>
+          <t>Driver warned and takes over; no FTTI defined for the warning path</t>
+        </is>
+      </c>
+      <c r="H15" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I15" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="K15" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L15" s="34" t="inlineStr"/>
+      <c r="M15" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N15" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-017 · open</t>
+        </is>
+      </c>
+      <c r="O15" s="37" t="inlineStr"/>
+      <c r="P15" s="37" t="inlineStr"/>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="34" t="inlineStr">
+        <is>
+          <t>SFM-004 · Insufficient lateral control (undershoot in curves, drift toward lane edge)</t>
+        </is>
+      </c>
+      <c r="B16" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C16" s="33" t="inlineStr">
+        <is>
+          <t>SFM-004.C3</t>
+        </is>
+      </c>
+      <c r="D16" s="34" t="inlineStr">
+        <is>
+          <t>Controller tuning or torque model too weak for vehicle state</t>
+        </is>
+      </c>
+      <c r="E16" s="34" t="inlineStr">
+        <is>
+          <t>steerSaturated warns when the controller is saturated and undershoots the curve by more than 1.2x; the lane departure warning fires as the car nears the line</t>
+        </is>
+      </c>
+      <c r="F16" s="34" t="inlineStr">
+        <is>
+          <t>Audible and visual warning; lateral control stays active, the driver steers</t>
+        </is>
+      </c>
+      <c r="G16" s="34" t="inlineStr">
+        <is>
+          <t>Driver warned and takes over; no FTTI defined for the warning path</t>
+        </is>
+      </c>
+      <c r="H16" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I16" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J16" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="K16" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L16" s="34" t="inlineStr"/>
+      <c r="M16" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N16" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-017 · open</t>
+        </is>
+      </c>
+      <c r="O16" s="37" t="inlineStr"/>
+      <c r="P16" s="37" t="inlineStr"/>
+    </row>
+    <row r="17" ht="33" customHeight="1">
+      <c r="A17" s="34" t="inlineStr">
+        <is>
+          <t>SFM-005 · Loss of lateral control without driver alert</t>
+        </is>
+      </c>
+      <c r="B17" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" s="33" t="inlineStr">
+        <is>
+          <t>SFM-005.C1</t>
+        </is>
+      </c>
+      <c r="D17" s="34" t="inlineStr">
+        <is>
+          <t>EPS stops accepting requests without a fault signal on CAN</t>
+        </is>
+      </c>
+      <c r="E17" s="34" t="inlineStr">
+        <is>
+          <t>None: steerUnavailable needs an EPS fault signal, which this cause does not produce</t>
+        </is>
+      </c>
+      <c r="F17" s="34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G17" s="34" t="inlineStr">
+        <is>
+          <t>Unchanged: assist lost silently; only the driver notices</t>
+        </is>
+      </c>
+      <c r="H17" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I17" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K17" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L17" s="34" t="inlineStr"/>
+      <c r="M17" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N17" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-018 · in progress</t>
+        </is>
+      </c>
+      <c r="O17" s="37" t="inlineStr"/>
+      <c r="P17" s="37" t="inlineStr"/>
+    </row>
+    <row r="18" ht="141" customHeight="1">
+      <c r="A18" s="34" t="inlineStr">
+        <is>
+          <t>SFM-005 · Loss of lateral control without driver alert</t>
+        </is>
+      </c>
+      <c r="B18" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" s="33" t="inlineStr">
+        <is>
+          <t>SFM-005.C2</t>
+        </is>
+      </c>
+      <c r="D18" s="34" t="inlineStr">
+        <is>
+          <t>pandad stops forwarding TX without the state being reported</t>
+        </is>
+      </c>
+      <c r="E18" s="34" t="inlineStr">
+        <is>
+          <t>BL-005: when no STEERING_LKA frame reaches the panda for 50 ms while authority is granted, the 100 Hz safety task clears controls_allowed (tx_arrival_ok, safety.h; TSR-408). pandad keeps publishing pandaStates, so selfdrived sees controlsAllowed false on the next sample and raises controlsMismatch after 2 consecutive samples, at most 0.5 s after the first mismatched frame (TSR-621). At BL-004 only the EPS drop-out path existed (about 3.5 s)</t>
+        </is>
+      </c>
+      <c r="F18" s="34" t="inlineStr">
+        <is>
+          <t>controlsMismatch IMMEDIATE_DISABLE with a take-over alert; the EPS drops LKA once frames stop</t>
+        </is>
+      </c>
+      <c r="G18" s="34" t="inlineStr">
+        <is>
+          <t>Lateral control lost with a take-over alert within about 0.56 s of the last frame; controlled handback</t>
+        </is>
+      </c>
+      <c r="H18" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="I18" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="K18" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L18" s="34" t="inlineStr">
+        <is>
+          <t>SG-02/06 loss without warning · 1000 ms
+60 + 500 ms</t>
+        </is>
+      </c>
+      <c r="M18" s="33" t="inlineStr">
+        <is>
+          <t>code derived</t>
+        </is>
+      </c>
+      <c r="N18" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-012 · open
+SFM-ACT-018 · in progress</t>
+        </is>
+      </c>
+      <c r="O18" s="37" t="inlineStr"/>
+      <c r="P18" s="37" t="inlineStr"/>
+    </row>
+    <row r="19" ht="33" customHeight="1">
+      <c r="A19" s="34" t="inlineStr">
+        <is>
+          <t>SFM-005 · Loss of lateral control without driver alert</t>
+        </is>
+      </c>
+      <c r="B19" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C19" s="33" t="inlineStr">
+        <is>
+          <t>SFM-005.C3</t>
+        </is>
+      </c>
+      <c r="D19" s="34" t="inlineStr">
+        <is>
+          <t>Process crash or hang not detected by liveness checks</t>
+        </is>
+      </c>
+      <c r="E19" s="34" t="inlineStr">
+        <is>
+          <t>None: by definition the hang escapes the liveness and frequency checks</t>
+        </is>
+      </c>
+      <c r="F19" s="34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G19" s="34" t="inlineStr">
+        <is>
+          <t>Unchanged: assist frozen or lost without an alert</t>
+        </is>
+      </c>
+      <c r="H19" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I19" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J19" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K19" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L19" s="34" t="inlineStr"/>
+      <c r="M19" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N19" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-018 · in progress</t>
+        </is>
+      </c>
+      <c r="O19" s="37" t="inlineStr"/>
+      <c r="P19" s="37" t="inlineStr"/>
+    </row>
+    <row r="20" ht="100.5" customHeight="1">
+      <c r="A20" s="34" t="inlineStr">
+        <is>
+          <t>SFM-006 · Lateral command frozen at last value</t>
+        </is>
+      </c>
+      <c r="B20" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C20" s="33" t="inlineStr">
+        <is>
+          <t>SFM-006.C1</t>
+        </is>
+      </c>
+      <c r="D20" s="34" t="inlineStr">
+        <is>
+          <t>controlsd hangs while card keeps sending the last carControl</t>
+        </is>
+      </c>
+      <c r="E20" s="34" t="inlineStr">
+        <is>
+          <t>selfdrived liveness check on controlsState (10 missed periods at 100 Hz, T-14); card stops sending once carControl is 0.1 s old (T-13). BL-005: 50 ms after the last STEERING_LKA frame the panda clears controls_allowed (TSR-408), and selfdrived raises controlsMismatch within 0.5 s (TSR-621)</t>
+        </is>
+      </c>
+      <c r="F20" s="34" t="inlineStr">
+        <is>
+          <t>controlsMismatch IMMEDIATE_DISABLE with alert (and commIssue SOFT_DISABLE); no frame is sent after the stall, so the torque ends only when the EPS drops LKA, about 2 s later (T-23); there is no active zero frame (TSR-109)</t>
+        </is>
+      </c>
+      <c r="G20" s="34" t="inlineStr">
+        <is>
+          <t>Last torque command held about 0.1 s, then LKA frames stop and assist decays over about 2 s. The driver is now warned within about 0.66 s, but the actuation reaction is still beyond the 0.5 s FTTI</t>
+        </is>
+      </c>
+      <c r="H20" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I20" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J20" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="K20" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L20" s="34" t="inlineStr">
+        <is>
+          <t>SG-01 SoC command stall · 500 ms
+160 + 2000 ms</t>
+        </is>
+      </c>
+      <c r="M20" s="33" t="inlineStr">
+        <is>
+          <t>code derived</t>
+        </is>
+      </c>
+      <c r="N20" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-015 · in progress</t>
+        </is>
+      </c>
+      <c r="O20" s="37" t="inlineStr"/>
+      <c r="P20" s="37" t="inlineStr"/>
+    </row>
+    <row r="21" ht="100.5" customHeight="1">
+      <c r="A21" s="34" t="inlineStr">
+        <is>
+          <t>SFM-006 · Lateral command frozen at last value</t>
+        </is>
+      </c>
+      <c r="B21" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C21" s="33" t="inlineStr">
+        <is>
+          <t>SFM-006.C2</t>
+        </is>
+      </c>
+      <c r="D21" s="34" t="inlineStr">
+        <is>
+          <t>modeld output frozen (stale frame) but still published as valid</t>
+        </is>
+      </c>
+      <c r="E21" s="34" t="inlineStr">
+        <is>
+          <t>Liveness and frequency checks pass: the frozen model output is still published on time and marked valid. No frozen-content or age check on model outputs. BL-005: controlsd drops lateral control when modelV2 is more than 0.5 s older than selfdriveState (TSR-602), which a frozen output published on time passes</t>
+        </is>
+      </c>
+      <c r="F21" s="34" t="inlineStr">
+        <is>
+          <t>None until another check trips</t>
+        </is>
+      </c>
+      <c r="G21" s="34" t="inlineStr">
+        <is>
+          <t>Unchanged: steering follows a frozen path</t>
+        </is>
+      </c>
+      <c r="H21" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I21" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J21" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="K21" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L21" s="34" t="inlineStr"/>
+      <c r="M21" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N21" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-015 · in progress</t>
+        </is>
+      </c>
+      <c r="O21" s="37" t="inlineStr"/>
+      <c r="P21" s="37" t="inlineStr"/>
+    </row>
+    <row r="22" ht="33" customHeight="1">
+      <c r="A22" s="34" t="inlineStr">
+        <is>
+          <t>SFM-006 · Lateral command frozen at last value</t>
+        </is>
+      </c>
+      <c r="B22" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C22" s="33" t="inlineStr">
+        <is>
+          <t>SFM-006.C3</t>
+        </is>
+      </c>
+      <c r="D22" s="34" t="inlineStr">
+        <is>
+          <t>Messaging delivers stale data with fresh timestamps</t>
+        </is>
+      </c>
+      <c r="E22" s="34" t="inlineStr">
+        <is>
+          <t>Liveness checks use arrival and timestamps, so stale data with fresh timestamps passes them</t>
+        </is>
+      </c>
+      <c r="F22" s="34" t="inlineStr">
+        <is>
+          <t>None until another check trips</t>
+        </is>
+      </c>
+      <c r="G22" s="34" t="inlineStr">
+        <is>
+          <t>Unchanged: control acts on stale data</t>
+        </is>
+      </c>
+      <c r="H22" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I22" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="J22" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="K22" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L22" s="34" t="inlineStr"/>
+      <c r="M22" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N22" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-015 · in progress</t>
+        </is>
+      </c>
+      <c r="O22" s="37" t="inlineStr"/>
+      <c r="P22" s="37" t="inlineStr"/>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="34" t="inlineStr">
+        <is>
+          <t>SFM-008 · Unintended acceleration</t>
+        </is>
+      </c>
+      <c r="B23" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C23" s="33" t="inlineStr">
+        <is>
+          <t>SFM-008.C1</t>
+        </is>
+      </c>
+      <c r="D23" s="34" t="inlineStr">
+        <is>
+          <t>Planner targets higher speed (missed lead, wrong set speed)</t>
+        </is>
+      </c>
+      <c r="E23" s="34" t="inlineStr">
+        <is>
+          <t>The panda bounds the acceleration request to the Toyota maximum but cannot tell a wrong target inside it; the driver's brake press revokes control</t>
+        </is>
+      </c>
+      <c r="F23" s="34" t="inlineStr">
+        <is>
+          <t>Panda revokes control on a brake press</t>
+        </is>
+      </c>
+      <c r="G23" s="34" t="inlineStr">
+        <is>
+          <t>Unchanged until the driver brakes</t>
+        </is>
+      </c>
+      <c r="H23" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I23" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J23" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="K23" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L23" s="34" t="inlineStr"/>
+      <c r="M23" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N23" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-001 · open
+SFM-ACT-002 · open</t>
+        </is>
+      </c>
+      <c r="O23" s="37" t="inlineStr"/>
+      <c r="P23" s="37" t="inlineStr"/>
+    </row>
+    <row r="24" ht="87" customHeight="1">
+      <c r="A24" s="34" t="inlineStr">
+        <is>
+          <t>SFM-008 · Unintended acceleration</t>
+        </is>
+      </c>
+      <c r="B24" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C24" s="33" t="inlineStr">
+        <is>
+          <t>SFM-008.C2</t>
+        </is>
+      </c>
+      <c r="D24" s="34" t="inlineStr">
+        <is>
+          <t>Longitudinal controller output too high</t>
+        </is>
+      </c>
+      <c r="E24" s="34" t="inlineStr">
+        <is>
+          <t>Panda checks every ACC_CONTROL frame against the acceleration limits and blocks it unless control is allowed and the gas is not pressed</t>
+        </is>
+      </c>
+      <c r="F24" s="34" t="inlineStr">
+        <is>
+          <t>Over-limit frame refused. BL-005, while engaged, the refusal also gives pandaTxBlocked, an immediate disable with a take-over alert at the next pandaStates sample (TSR-615)</t>
+        </is>
+      </c>
+      <c r="G24" s="34" t="inlineStr">
+        <is>
+          <t>Acceleration bounded by the panda limit; an in-limit overshoot remains</t>
+        </is>
+      </c>
+      <c r="H24" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I24" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="J24" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K24" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L24" s="34" t="inlineStr">
+        <is>
+          <t>SG-03/04 · 1000 ms
+0 + 10 ms</t>
+        </is>
+      </c>
+      <c r="M24" s="33" t="inlineStr">
+        <is>
+          <t>code derived</t>
+        </is>
+      </c>
+      <c r="N24" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-012 · open</t>
+        </is>
+      </c>
+      <c r="O24" s="37" t="inlineStr"/>
+      <c r="P24" s="37" t="inlineStr"/>
+    </row>
+    <row r="25" ht="87" customHeight="1">
+      <c r="A25" s="34" t="inlineStr">
+        <is>
+          <t>SFM-008 · Unintended acceleration</t>
+        </is>
+      </c>
+      <c r="B25" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C25" s="33" t="inlineStr">
+        <is>
+          <t>SFM-008.C3</t>
+        </is>
+      </c>
+      <c r="D25" s="34" t="inlineStr">
+        <is>
+          <t>Wrong scaling of acceleration request for this car</t>
+        </is>
+      </c>
+      <c r="E25" s="34" t="inlineStr">
+        <is>
+          <t>Panda decodes the packed acceleration request with its own scaling and checks it against the limits on every frame, independently of the host packing</t>
+        </is>
+      </c>
+      <c r="F25" s="34" t="inlineStr">
+        <is>
+          <t>Over-limit frame refused. BL-005, while engaged, the refusal also gives pandaTxBlocked, an immediate disable with a take-over alert at the next pandaStates sample (TSR-615)</t>
+        </is>
+      </c>
+      <c r="G25" s="34" t="inlineStr">
+        <is>
+          <t>Acceleration bounded by the panda limit</t>
+        </is>
+      </c>
+      <c r="H25" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I25" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J25" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K25" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L25" s="34" t="inlineStr">
+        <is>
+          <t>SG-03/04 · 1000 ms
+0 + 10 ms</t>
+        </is>
+      </c>
+      <c r="M25" s="33" t="inlineStr">
+        <is>
+          <t>code derived</t>
+        </is>
+      </c>
+      <c r="N25" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-012 · open</t>
+        </is>
+      </c>
+      <c r="O25" s="37" t="inlineStr"/>
+      <c r="P25" s="37" t="inlineStr"/>
+    </row>
+    <row r="26" ht="46.5" customHeight="1">
+      <c r="A26" s="34" t="inlineStr">
+        <is>
+          <t>SFM-008 · Unintended acceleration</t>
+        </is>
+      </c>
+      <c r="B26" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C26" s="33" t="inlineStr">
+        <is>
+          <t>SFM-008.C4</t>
+        </is>
+      </c>
+      <c r="D26" s="34" t="inlineStr">
+        <is>
+          <t>Powertrain applies more acceleration than requested</t>
+        </is>
+      </c>
+      <c r="E26" s="34" t="inlineStr">
+        <is>
+          <t>Excessive longitudinal acceleration check on measured acceleration (&gt; 2x ACCEL_MAX for 0.25 s, T-21)</t>
+        </is>
+      </c>
+      <c r="F26" s="34" t="inlineStr">
+        <is>
+          <t>SOFT_DISABLE: actuation continues for up to 3 s (T-16); 3.25 s exceeds the 1 s FTTI</t>
+        </is>
+      </c>
+      <c r="G26" s="34" t="inlineStr">
+        <is>
+          <t>Excess acceleration for up to 3.25 s</t>
+        </is>
+      </c>
+      <c r="H26" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I26" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="K26" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L26" s="34" t="inlineStr">
+        <is>
+          <t>SG-03/04 · 1000 ms
+250 + 3000 ms</t>
+        </is>
+      </c>
+      <c r="M26" s="33" t="inlineStr">
+        <is>
+          <t>code derived</t>
+        </is>
+      </c>
+      <c r="N26" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-003 · open</t>
+        </is>
+      </c>
+      <c r="O26" s="37" t="inlineStr"/>
+      <c r="P26" s="37" t="inlineStr"/>
+    </row>
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" s="34" t="inlineStr">
+        <is>
+          <t>SFM-009 · Unintended or excessive deceleration (phantom braking)</t>
+        </is>
+      </c>
+      <c r="B27" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C27" s="33" t="inlineStr">
+        <is>
+          <t>SFM-009.C1</t>
+        </is>
+      </c>
+      <c r="D27" s="34" t="inlineStr">
+        <is>
+          <t>False lead (radar ghost, model false positive) or FCW false trigger</t>
+        </is>
+      </c>
+      <c r="E27" s="34" t="inlineStr">
+        <is>
+          <t>The panda bounds deceleration to the Toyota minimum but cannot tell a false lead; the panda blocks acceleration requests while the driver presses the gas</t>
+        </is>
+      </c>
+      <c r="F27" s="34" t="inlineStr">
+        <is>
+          <t>Driver overrides with the gas</t>
+        </is>
+      </c>
+      <c r="G27" s="34" t="inlineStr">
+        <is>
+          <t>Unchanged until the driver presses the gas</t>
+        </is>
+      </c>
+      <c r="H27" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I27" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="J27" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="K27" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L27" s="34" t="inlineStr"/>
+      <c r="M27" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N27" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-009 · open</t>
+        </is>
+      </c>
+      <c r="O27" s="37" t="inlineStr"/>
+      <c r="P27" s="37" t="inlineStr"/>
+    </row>
+    <row r="28" ht="87" customHeight="1">
+      <c r="A28" s="34" t="inlineStr">
+        <is>
+          <t>SFM-009 · Unintended or excessive deceleration (phantom braking)</t>
+        </is>
+      </c>
+      <c r="B28" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C28" s="33" t="inlineStr">
+        <is>
+          <t>SFM-009.C2</t>
+        </is>
+      </c>
+      <c r="D28" s="34" t="inlineStr">
+        <is>
+          <t>Longitudinal controller overshoot</t>
+        </is>
+      </c>
+      <c r="E28" s="34" t="inlineStr">
+        <is>
+          <t>Panda checks every ACC_CONTROL frame against the minimum acceleration limit</t>
+        </is>
+      </c>
+      <c r="F28" s="34" t="inlineStr">
+        <is>
+          <t>Over-limit frame refused. BL-005, while engaged, the refusal also gives pandaTxBlocked, an immediate disable with a take-over alert at the next pandaStates sample (TSR-615)</t>
+        </is>
+      </c>
+      <c r="G28" s="34" t="inlineStr">
+        <is>
+          <t>Deceleration bounded by the panda limit; in-limit overshoot remains</t>
+        </is>
+      </c>
+      <c r="H28" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I28" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="J28" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K28" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L28" s="34" t="inlineStr">
+        <is>
+          <t>SG-03/04 · 1000 ms
+0 + 10 ms</t>
+        </is>
+      </c>
+      <c r="M28" s="33" t="inlineStr">
+        <is>
+          <t>code derived</t>
+        </is>
+      </c>
+      <c r="N28" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-012 · open</t>
+        </is>
+      </c>
+      <c r="O28" s="37" t="inlineStr"/>
+      <c r="P28" s="37" t="inlineStr"/>
+    </row>
+    <row r="29" ht="46.5" customHeight="1">
+      <c r="A29" s="34" t="inlineStr">
+        <is>
+          <t>SFM-009 · Unintended or excessive deceleration (phantom braking)</t>
+        </is>
+      </c>
+      <c r="B29" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C29" s="33" t="inlineStr">
+        <is>
+          <t>SFM-009.C3</t>
+        </is>
+      </c>
+      <c r="D29" s="34" t="inlineStr">
+        <is>
+          <t>Wrong vEgo/aEgo from CAN parse</t>
+        </is>
+      </c>
+      <c r="E29" s="34" t="inlineStr">
+        <is>
+          <t>Limits bound the request but cannot tell wrong vehicle speed or acceleration inputs</t>
+        </is>
+      </c>
+      <c r="F29" s="34" t="inlineStr">
+        <is>
+          <t>Driver overrides with the gas</t>
+        </is>
+      </c>
+      <c r="G29" s="34" t="inlineStr">
+        <is>
+          <t>Unchanged until the driver presses the gas</t>
+        </is>
+      </c>
+      <c r="H29" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I29" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J29" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="K29" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L29" s="34" t="inlineStr"/>
+      <c r="M29" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N29" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-003 · open</t>
+        </is>
+      </c>
+      <c r="O29" s="37" t="inlineStr"/>
+      <c r="P29" s="37" t="inlineStr"/>
+    </row>
+    <row r="30" ht="46.5" customHeight="1">
+      <c r="A30" s="34" t="inlineStr">
+        <is>
+          <t>SFM-010 · Insufficient deceleration for lead vehicle or stop</t>
+        </is>
+      </c>
+      <c r="B30" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C30" s="33" t="inlineStr">
+        <is>
+          <t>SFM-010.C1</t>
+        </is>
+      </c>
+      <c r="D30" s="34" t="inlineStr">
+        <is>
+          <t>Lead missed due to radar/vision fusion fault</t>
+        </is>
+      </c>
+      <c r="E30" s="34" t="inlineStr">
+        <is>
+          <t>FCW comes from the same planner and model that missed the lead, so it is not designed to catch this cause</t>
+        </is>
+      </c>
+      <c r="F30" s="34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G30" s="34" t="inlineStr">
+        <is>
+          <t>Unchanged: stock PCS/AEB is the remaining measure (SFM-ACT-006)</t>
+        </is>
+      </c>
+      <c r="H30" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I30" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="J30" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="K30" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L30" s="34" t="inlineStr"/>
+      <c r="M30" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N30" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-009 · open</t>
+        </is>
+      </c>
+      <c r="O30" s="37" t="inlineStr"/>
+      <c r="P30" s="37" t="inlineStr"/>
+    </row>
+    <row r="31" ht="46.5" customHeight="1">
+      <c r="A31" s="34" t="inlineStr">
+        <is>
+          <t>SFM-010 · Insufficient deceleration for lead vehicle or stop</t>
+        </is>
+      </c>
+      <c r="B31" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C31" s="33" t="inlineStr">
+        <is>
+          <t>SFM-010.C2</t>
+        </is>
+      </c>
+      <c r="D31" s="34" t="inlineStr">
+        <is>
+          <t>Safety model minimum accel limit prevents required braking (by design)</t>
+        </is>
+      </c>
+      <c r="E31" s="34" t="inlineStr">
+        <is>
+          <t>FCW warns when the planner sees that the lead needs more deceleration than the limit allows</t>
+        </is>
+      </c>
+      <c r="F31" s="34" t="inlineStr">
+        <is>
+          <t>Audible forward-collision warning; the driver brakes</t>
+        </is>
+      </c>
+      <c r="G31" s="34" t="inlineStr">
+        <is>
+          <t>Driver warned; no FTTI compared</t>
+        </is>
+      </c>
+      <c r="H31" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I31" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J31" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="K31" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L31" s="34" t="inlineStr"/>
+      <c r="M31" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N31" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-006 · open
+SFM-ACT-017 · open</t>
+        </is>
+      </c>
+      <c r="O31" s="37" t="inlineStr"/>
+      <c r="P31" s="37" t="inlineStr"/>
+    </row>
+    <row r="32" ht="46.5" customHeight="1">
+      <c r="A32" s="34" t="inlineStr">
+        <is>
+          <t>SFM-010 · Insufficient deceleration for lead vehicle or stop</t>
+        </is>
+      </c>
+      <c r="B32" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C32" s="33" t="inlineStr">
+        <is>
+          <t>SFM-010.C3</t>
+        </is>
+      </c>
+      <c r="D32" s="34" t="inlineStr">
+        <is>
+          <t>Brake system does not achieve requested deceleration</t>
+        </is>
+      </c>
+      <c r="E32" s="34" t="inlineStr">
+        <is>
+          <t>FCW warns as the gap closes faster than planned</t>
+        </is>
+      </c>
+      <c r="F32" s="34" t="inlineStr">
+        <is>
+          <t>Audible forward-collision warning; the driver brakes</t>
+        </is>
+      </c>
+      <c r="G32" s="34" t="inlineStr">
+        <is>
+          <t>Driver warned; no FTTI compared</t>
+        </is>
+      </c>
+      <c r="H32" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I32" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="K32" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L32" s="34" t="inlineStr"/>
+      <c r="M32" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N32" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-003 · open
+SFM-ACT-017 · open</t>
+        </is>
+      </c>
+      <c r="O32" s="37" t="inlineStr"/>
+      <c r="P32" s="37" t="inlineStr"/>
+    </row>
+    <row r="33" ht="46.5" customHeight="1">
+      <c r="A33" s="34" t="inlineStr">
+        <is>
+          <t>SFM-011 · Loss of longitudinal control without driver alert</t>
+        </is>
+      </c>
+      <c r="B33" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C33" s="33" t="inlineStr">
+        <is>
+          <t>SFM-011.C1</t>
+        </is>
+      </c>
+      <c r="D33" s="34" t="inlineStr">
+        <is>
+          <t>Powertrain ignores requests without fault signal</t>
+        </is>
+      </c>
+      <c r="E33" s="34" t="inlineStr">
+        <is>
+          <t>None: accFaulted needs a PCM fault signal, which this cause does not produce</t>
+        </is>
+      </c>
+      <c r="F33" s="34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G33" s="34" t="inlineStr">
+        <is>
+          <t>Unchanged: longitudinal control lost silently</t>
+        </is>
+      </c>
+      <c r="H33" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I33" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K33" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L33" s="34" t="inlineStr"/>
+      <c r="M33" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N33" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-018 · in progress</t>
+        </is>
+      </c>
+      <c r="O33" s="37" t="inlineStr"/>
+      <c r="P33" s="37" t="inlineStr"/>
+    </row>
+    <row r="34" ht="114" customHeight="1">
+      <c r="A34" s="34" t="inlineStr">
+        <is>
+          <t>SFM-011 · Loss of longitudinal control without driver alert</t>
+        </is>
+      </c>
+      <c r="B34" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C34" s="33" t="inlineStr">
+        <is>
+          <t>SFM-011.C2</t>
+        </is>
+      </c>
+      <c r="D34" s="34" t="inlineStr">
+        <is>
+          <t>TX path to vehicle lost silently</t>
+        </is>
+      </c>
+      <c r="E34" s="34" t="inlineStr">
+        <is>
+          <t>BL-005: when the TX path is lost, STEERING_LKA stops too; 50 ms later the 100 Hz panda safety task clears controls_allowed (TSR-408; ACC_CONTROL alone after 100 ms). pandaStates still arrive, so selfdrived raises controlsMismatch after 2 consecutive samples, at most 0.5 s after the first mismatched frame (TSR-621). At BL-004 only the PCM fault path existed, with unknown timing</t>
+        </is>
+      </c>
+      <c r="F34" s="34" t="inlineStr">
+        <is>
+          <t>controlsMismatch IMMEDIATE_DISABLE with a take-over alert; accFaulted follows if the PCM faults ACC</t>
+        </is>
+      </c>
+      <c r="G34" s="34" t="inlineStr">
+        <is>
+          <t>Longitudinal control lost with a take-over alert within about 0.6 s; what the PCM does with the last request until it faults ACC is not characterised (SFM-ACT-003)</t>
+        </is>
+      </c>
+      <c r="H34" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="I34" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="J34" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="K34" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L34" s="34" t="inlineStr">
+        <is>
+          <t>SG-02/06 loss without warning · 1000 ms
+110 + 500 ms</t>
+        </is>
+      </c>
+      <c r="M34" s="33" t="inlineStr">
+        <is>
+          <t>code derived</t>
+        </is>
+      </c>
+      <c r="N34" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-012 · open
+SFM-ACT-018 · in progress</t>
+        </is>
+      </c>
+      <c r="O34" s="37" t="inlineStr"/>
+      <c r="P34" s="37" t="inlineStr"/>
+    </row>
+    <row r="35" ht="46.5" customHeight="1">
+      <c r="A35" s="34" t="inlineStr">
+        <is>
+          <t>SFM-012 · Late reaction to lead vehicle braking</t>
+        </is>
+      </c>
+      <c r="B35" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C35" s="33" t="inlineStr">
+        <is>
+          <t>SFM-012.C1</t>
+        </is>
+      </c>
+      <c r="D35" s="34" t="inlineStr">
+        <is>
+          <t>Pipeline latency (CPU overload, thermal throttle, messaging delay)</t>
+        </is>
+      </c>
+      <c r="E35" s="34" t="inlineStr">
+        <is>
+          <t>selfdrivedLagging and modeldLagging after about 1 s of averaging (T-20), commIssueAvgFreq over 1-10 s (T-15)</t>
+        </is>
+      </c>
+      <c r="F35" s="34" t="inlineStr">
+        <is>
+          <t>SOFT_DISABLE (3 s)</t>
+        </is>
+      </c>
+      <c r="G35" s="34" t="inlineStr">
+        <is>
+          <t>Driver warned; no FTTI compared for late reaction</t>
+        </is>
+      </c>
+      <c r="H35" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I35" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J35" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="K35" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L35" s="34" t="inlineStr">
+        <is>
+          <t>1000 + 3000 ms</t>
+        </is>
+      </c>
+      <c r="M35" s="33" t="inlineStr">
+        <is>
+          <t>code derived</t>
+        </is>
+      </c>
+      <c r="N35" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-017 · open</t>
+        </is>
+      </c>
+      <c r="O35" s="37" t="inlineStr"/>
+      <c r="P35" s="37" t="inlineStr"/>
+    </row>
+    <row r="36" ht="33" customHeight="1">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t>SFM-012 · Late reaction to lead vehicle braking</t>
+        </is>
+      </c>
+      <c r="B36" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C36" s="33" t="inlineStr">
+        <is>
+          <t>SFM-012.C2</t>
+        </is>
+      </c>
+      <c r="D36" s="34" t="inlineStr">
+        <is>
+          <t>Lead state filtered too slowly (radard)</t>
+        </is>
+      </c>
+      <c r="E36" s="34" t="inlineStr">
+        <is>
+          <t>None: slow filtering in radard keeps message rates normal</t>
+        </is>
+      </c>
+      <c r="F36" s="34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G36" s="34" t="inlineStr">
+        <is>
+          <t>Unchanged: late braking until FCW or the driver acts</t>
+        </is>
+      </c>
+      <c r="H36" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I36" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J36" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K36" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L36" s="34" t="inlineStr"/>
+      <c r="M36" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N36" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-009 · open</t>
+        </is>
+      </c>
+      <c r="O36" s="37" t="inlineStr"/>
+      <c r="P36" s="37" t="inlineStr"/>
+    </row>
+    <row r="37" ht="73.5" customHeight="1">
+      <c r="A37" s="34" t="inlineStr">
+        <is>
+          <t>SFM-013 · Engagement without driver request or with entry conditions not met</t>
+        </is>
+      </c>
+      <c r="B37" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C37" s="33" t="inlineStr">
+        <is>
+          <t>SFM-013.C1</t>
+        </is>
+      </c>
+      <c r="D37" s="34" t="inlineStr">
+        <is>
+          <t>State machine transition error</t>
+        </is>
+      </c>
+      <c r="E37" s="34" t="inlineStr">
+        <is>
+          <t>Panda grants control only on the PCM cruise engage edge read from the car bus, so a wrong host state alone does not grant actuation; frames are refused on every cycle. WP-S-04 has no FTTI row for SG-008, so the timing is not compared</t>
+        </is>
+      </c>
+      <c r="F37" s="34" t="inlineStr">
+        <is>
+          <t>Frames refused; no actuation</t>
+        </is>
+      </c>
+      <c r="G37" s="34" t="inlineStr">
+        <is>
+          <t>No actuation without PCM cruise</t>
+        </is>
+      </c>
+      <c r="H37" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="I37" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J37" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="K37" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L37" s="34" t="inlineStr">
+        <is>
+          <t>0 + 10 ms</t>
+        </is>
+      </c>
+      <c r="M37" s="33" t="inlineStr">
+        <is>
+          <t>code derived</t>
+        </is>
+      </c>
+      <c r="N37" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-017 · open</t>
+        </is>
+      </c>
+      <c r="O37" s="37" t="inlineStr"/>
+      <c r="P37" s="37" t="inlineStr"/>
+    </row>
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" s="34" t="inlineStr">
+        <is>
+          <t>SFM-013 · Engagement without driver request or with entry conditions not met</t>
+        </is>
+      </c>
+      <c r="B38" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C38" s="33" t="inlineStr">
+        <is>
+          <t>SFM-013.C2</t>
+        </is>
+      </c>
+      <c r="D38" s="34" t="inlineStr">
+        <is>
+          <t>Cruise state or button parsed incorrectly (spurious enable)</t>
+        </is>
+      </c>
+      <c r="E38" s="34" t="inlineStr">
+        <is>
+          <t>Panda parses the PCM cruise state itself and grants control only on its engage edge; a host parsing error does not grant actuation. No SG-008 FTTI row in WP-S-04</t>
+        </is>
+      </c>
+      <c r="F38" s="34" t="inlineStr">
+        <is>
+          <t>Frames refused; no actuation</t>
+        </is>
+      </c>
+      <c r="G38" s="34" t="inlineStr">
+        <is>
+          <t>No actuation without PCM cruise</t>
+        </is>
+      </c>
+      <c r="H38" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="I38" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J38" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="K38" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L38" s="34" t="inlineStr">
+        <is>
+          <t>0 + 10 ms</t>
+        </is>
+      </c>
+      <c r="M38" s="33" t="inlineStr">
+        <is>
+          <t>code derived</t>
+        </is>
+      </c>
+      <c r="N38" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-017 · open</t>
+        </is>
+      </c>
+      <c r="O38" s="37" t="inlineStr"/>
+      <c r="P38" s="37" t="inlineStr"/>
+    </row>
+    <row r="39" ht="33" customHeight="1">
+      <c r="A39" s="34" t="inlineStr">
+        <is>
+          <t>SFM-014 · Fails to disengage when a fault requires it</t>
+        </is>
+      </c>
+      <c r="B39" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C39" s="33" t="inlineStr">
+        <is>
+          <t>SFM-014.C1</t>
+        </is>
+      </c>
+      <c r="D39" s="34" t="inlineStr">
+        <is>
+          <t>Event missing for the fault (no detection)</t>
+        </is>
+      </c>
+      <c r="E39" s="34" t="inlineStr">
+        <is>
+          <t>None: with no event for the fault, the heartbeat still reports engaged</t>
+        </is>
+      </c>
+      <c r="F39" s="34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G39" s="34" t="inlineStr">
+        <is>
+          <t>Unchanged: control continues on the faulted input</t>
+        </is>
+      </c>
+      <c r="H39" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I39" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="J39" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K39" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L39" s="34" t="inlineStr"/>
+      <c r="M39" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N39" s="34" t="inlineStr"/>
+      <c r="O39" s="37" t="inlineStr"/>
+      <c r="P39" s="37" t="inlineStr"/>
+    </row>
+    <row r="40" ht="46.5" customHeight="1">
+      <c r="A40" s="34" t="inlineStr">
+        <is>
+          <t>SFM-014 · Fails to disengage when a fault requires it</t>
+        </is>
+      </c>
+      <c r="B40" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C40" s="33" t="inlineStr">
+        <is>
+          <t>SFM-014.C2</t>
+        </is>
+      </c>
+      <c r="D40" s="34" t="inlineStr">
+        <is>
+          <t>Event mapped to wrong reaction type in events.py</t>
+        </is>
+      </c>
+      <c r="E40" s="34" t="inlineStr">
+        <is>
+          <t>None: the wrong reaction type is the monitor that has failed</t>
+        </is>
+      </c>
+      <c r="F40" s="34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G40" s="34" t="inlineStr">
+        <is>
+          <t>Unchanged: a fault that needs IMMEDIATE_DISABLE gets a weaker reaction</t>
+        </is>
+      </c>
+      <c r="H40" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I40" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="J40" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K40" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L40" s="34" t="inlineStr"/>
+      <c r="M40" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N40" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-010 · in progress</t>
+        </is>
+      </c>
+      <c r="O40" s="37" t="inlineStr"/>
+      <c r="P40" s="37" t="inlineStr"/>
+    </row>
+    <row r="41" ht="46.5" customHeight="1">
+      <c r="A41" s="34" t="inlineStr">
+        <is>
+          <t>SFM-014 · Fails to disengage when a fault requires it</t>
+        </is>
+      </c>
+      <c r="B41" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C41" s="33" t="inlineStr">
+        <is>
+          <t>SFM-014.C3</t>
+        </is>
+      </c>
+      <c r="D41" s="34" t="inlineStr">
+        <is>
+          <t>Catch-all commIssue suppressed by the no_system_errors logic while another event is active</t>
+        </is>
+      </c>
+      <c r="E41" s="34" t="inlineStr">
+        <is>
+          <t>None: the catch-all is itself suppressed</t>
+        </is>
+      </c>
+      <c r="F41" s="34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G41" s="34" t="inlineStr">
+        <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="H41" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I41" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="J41" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K41" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L41" s="34" t="inlineStr"/>
+      <c r="M41" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N41" s="34" t="inlineStr"/>
+      <c r="O41" s="37" t="inlineStr"/>
+      <c r="P41" s="37" t="inlineStr"/>
+    </row>
+    <row r="42" ht="33" customHeight="1">
+      <c r="A42" s="34" t="inlineStr">
+        <is>
+          <t>SFM-015 · Abrupt disengagement without alert</t>
+        </is>
+      </c>
+      <c r="B42" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C42" s="33" t="inlineStr">
+        <is>
+          <t>SFM-015.C1</t>
+        </is>
+      </c>
+      <c r="D42" s="34" t="inlineStr">
+        <is>
+          <t>Alert generated but not rendered or played (see SFM-026)</t>
+        </is>
+      </c>
+      <c r="E42" s="34" t="inlineStr">
+        <is>
+          <t>None at BL-004: the alert is appended but nothing checks that it was shown or played</t>
+        </is>
+      </c>
+      <c r="F42" s="34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G42" s="34" t="inlineStr">
+        <is>
+          <t>Unchanged: disengagement without a perceived alert</t>
+        </is>
+      </c>
+      <c r="H42" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I42" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J42" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K42" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L42" s="34" t="inlineStr"/>
+      <c r="M42" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N42" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-007 · open</t>
+        </is>
+      </c>
+      <c r="O42" s="37" t="inlineStr"/>
+      <c r="P42" s="37" t="inlineStr"/>
+    </row>
+    <row r="43" ht="127.5" customHeight="1">
+      <c r="A43" s="34" t="inlineStr">
+        <is>
+          <t>SFM-015 · Abrupt disengagement without alert</t>
+        </is>
+      </c>
+      <c r="B43" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C43" s="33" t="inlineStr">
+        <is>
+          <t>SFM-015.C2</t>
+        </is>
+      </c>
+      <c r="D43" s="34" t="inlineStr">
+        <is>
+          <t>Panda drops controls_allowed on its own (e.g. safety violation) and selfdrived reacts late</t>
+        </is>
+      </c>
+      <c r="E43" s="34" t="inlineStr">
+        <is>
+          <t>BL-005: selfdrived counts consecutive pandaStates samples with controlsAllowed false while engaged and raises controlsMismatch at the second, or 0.5 s after the first mismatched frame if the samples are stale (ControlsMismatch, supervision.py; TSR-621). A TX-rate or heartbeat revocation is named at once (pandaTxRateExceeded, pandaHeartbeatLost; TSR-615). At BL-004: 200 cumulative cycles, about 2 s (T-17)</t>
+        </is>
+      </c>
+      <c r="F43" s="34" t="inlineStr">
+        <is>
+          <t>controlsMismatch (or the named panda event) IMMEDIATE_DISABLE with a take-over alert, within 0.5 s of the first mismatched frame</t>
+        </is>
+      </c>
+      <c r="G43" s="34" t="inlineStr">
+        <is>
+          <t>Handback with a take-over alert within the 1 s budget; controlled handback</t>
+        </is>
+      </c>
+      <c r="H43" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="I43" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J43" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="K43" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L43" s="34" t="inlineStr">
+        <is>
+          <t>SG-02/06 loss without warning · 1000 ms
+500 + 10 ms</t>
+        </is>
+      </c>
+      <c r="M43" s="33" t="inlineStr">
+        <is>
+          <t>code derived</t>
+        </is>
+      </c>
+      <c r="N43" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-010 · in progress
+SFM-ACT-012 · open</t>
+        </is>
+      </c>
+      <c r="O43" s="37" t="inlineStr"/>
+      <c r="P43" s="37" t="inlineStr"/>
+    </row>
+    <row r="44" ht="33" customHeight="1">
+      <c r="A44" s="34" t="inlineStr">
+        <is>
+          <t>SFM-015 · Abrupt disengagement without alert</t>
+        </is>
+      </c>
+      <c r="B44" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C44" s="33" t="inlineStr">
+        <is>
+          <t>SFM-015.C3</t>
+        </is>
+      </c>
+      <c r="D44" s="34" t="inlineStr">
+        <is>
+          <t>Device power loss (12 V interruption, harness connector)</t>
+        </is>
+      </c>
+      <c r="E44" s="62" t="inlineStr">
+        <is>
+          <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-012.C1)</t>
+        </is>
+      </c>
+      <c r="F44" s="34" t="inlineStr"/>
+      <c r="G44" s="34" t="inlineStr"/>
+      <c r="H44" s="35" t="inlineStr"/>
+      <c r="I44" s="35" t="inlineStr"/>
+      <c r="J44" s="35" t="inlineStr"/>
+      <c r="K44" s="33" t="inlineStr"/>
+      <c r="L44" s="34" t="inlineStr"/>
+      <c r="M44" s="33" t="inlineStr"/>
+      <c r="N44" s="34" t="inlineStr"/>
+      <c r="O44" s="37" t="inlineStr"/>
+      <c r="P44" s="37" t="inlineStr"/>
+    </row>
+    <row r="45" ht="46.5" customHeight="1">
+      <c r="A45" s="34" t="inlineStr">
+        <is>
+          <t>SFM-017 · Brake press does not disengage</t>
+        </is>
+      </c>
+      <c r="B45" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C45" s="33" t="inlineStr">
+        <is>
+          <t>SFM-017.C1</t>
+        </is>
+      </c>
+      <c r="D45" s="34" t="inlineStr">
+        <is>
+          <t>brakePressed parsed wrong or CAN signal missing</t>
+        </is>
+      </c>
+      <c r="E45" s="34" t="inlineStr">
+        <is>
+          <t>Panda parses the brake signal itself and revokes control on the brake press (T-04, 25 ms), independently of the host parse</t>
+        </is>
+      </c>
+      <c r="F45" s="34" t="inlineStr">
+        <is>
+          <t>Steering and acceleration frames refused from the next cycle</t>
+        </is>
+      </c>
+      <c r="G45" s="34" t="inlineStr">
+        <is>
+          <t>Control released within about 35 ms; the host alert follows later</t>
+        </is>
+      </c>
+      <c r="H45" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="I45" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J45" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K45" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L45" s="34" t="inlineStr">
+        <is>
+          <t>SG-05 brake/cancel · 200 ms
+25 + 10 ms</t>
+        </is>
+      </c>
+      <c r="M45" s="33" t="inlineStr">
+        <is>
+          <t>code derived</t>
+        </is>
+      </c>
+      <c r="N45" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-012 · open</t>
+        </is>
+      </c>
+      <c r="O45" s="37" t="inlineStr"/>
+      <c r="P45" s="37" t="inlineStr"/>
+    </row>
+    <row r="46" ht="46.5" customHeight="1">
+      <c r="A46" s="34" t="inlineStr">
+        <is>
+          <t>SFM-017 · Brake press does not disengage</t>
+        </is>
+      </c>
+      <c r="B46" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C46" s="33" t="inlineStr">
+        <is>
+          <t>SFM-017.C2</t>
+        </is>
+      </c>
+      <c r="D46" s="34" t="inlineStr">
+        <is>
+          <t>Car events ignored when canValid is false</t>
+        </is>
+      </c>
+      <c r="E46" s="34" t="inlineStr">
+        <is>
+          <t>Panda revokes control on the brake press from its own CAN parse, whatever the host does with canValid</t>
+        </is>
+      </c>
+      <c r="F46" s="34" t="inlineStr">
+        <is>
+          <t>Steering and acceleration frames refused from the next cycle</t>
+        </is>
+      </c>
+      <c r="G46" s="34" t="inlineStr">
+        <is>
+          <t>Control released within about 35 ms</t>
+        </is>
+      </c>
+      <c r="H46" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="I46" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="J46" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K46" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L46" s="34" t="inlineStr">
+        <is>
+          <t>SG-05 brake/cancel · 200 ms
+25 + 10 ms</t>
+        </is>
+      </c>
+      <c r="M46" s="33" t="inlineStr">
+        <is>
+          <t>code derived</t>
+        </is>
+      </c>
+      <c r="N46" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-012 · open</t>
+        </is>
+      </c>
+      <c r="O46" s="37" t="inlineStr"/>
+      <c r="P46" s="37" t="inlineStr"/>
+    </row>
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" s="34" t="inlineStr">
+        <is>
+          <t>SFM-018 · Item resists driver steering input</t>
+        </is>
+      </c>
+      <c r="B47" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C47" s="33" t="inlineStr">
+        <is>
+          <t>SFM-018.C1</t>
+        </is>
+      </c>
+      <c r="D47" s="34" t="inlineStr">
+        <is>
+          <t>Driver torque threshold too high or signal parsed wrong</t>
+        </is>
+      </c>
+      <c r="E47" s="34" t="inlineStr">
+        <is>
+          <t>None at BL-004: the panda does not supervise driver override (WP-S-04 §5, TSR-304); the EPS torque limit lets the driver overpower the request but detects nothing</t>
+        </is>
+      </c>
+      <c r="F47" s="34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G47" s="34" t="inlineStr">
+        <is>
+          <t>Unchanged: driver steers against the bounded torque</t>
+        </is>
+      </c>
+      <c r="H47" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I47" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J47" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K47" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L47" s="34" t="inlineStr"/>
+      <c r="M47" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N47" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-016 · open</t>
+        </is>
+      </c>
+      <c r="O47" s="37" t="inlineStr"/>
+      <c r="P47" s="37" t="inlineStr"/>
+    </row>
+    <row r="48" ht="33" customHeight="1">
+      <c r="A48" s="34" t="inlineStr">
+        <is>
+          <t>SFM-018 · Item resists driver steering input</t>
+        </is>
+      </c>
+      <c r="B48" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C48" s="33" t="inlineStr">
+        <is>
+          <t>SFM-018.C2</t>
+        </is>
+      </c>
+      <c r="D48" s="34" t="inlineStr">
+        <is>
+          <t>Controller keeps commanding torque during override</t>
+        </is>
+      </c>
+      <c r="E48" s="34" t="inlineStr">
+        <is>
+          <t>None at BL-004: no override supervision in the panda (TSR-304)</t>
+        </is>
+      </c>
+      <c r="F48" s="34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G48" s="34" t="inlineStr">
+        <is>
+          <t>Unchanged: driver steers against the bounded torque</t>
+        </is>
+      </c>
+      <c r="H48" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I48" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="J48" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K48" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L48" s="34" t="inlineStr"/>
+      <c r="M48" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N48" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-016 · open</t>
+        </is>
+      </c>
+      <c r="O48" s="37" t="inlineStr"/>
+      <c r="P48" s="37" t="inlineStr"/>
+    </row>
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" s="34" t="inlineStr">
+        <is>
+          <t>SFM-019 · Cancel button does not disengage</t>
+        </is>
+      </c>
+      <c r="B49" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C49" s="33" t="inlineStr">
+        <is>
+          <t>SFM-019.C1</t>
+        </is>
+      </c>
+      <c r="D49" s="34" t="inlineStr">
+        <is>
+          <t>Button message parsed wrong or missing</t>
+        </is>
+      </c>
+      <c r="E49" s="34" t="inlineStr">
+        <is>
+          <t>Cancel turns PCM cruise off; the panda reads PCM cruise from the car bus and revokes control (T-04, 30 ms), independently of the host button parse</t>
+        </is>
+      </c>
+      <c r="F49" s="34" t="inlineStr">
+        <is>
+          <t>Frames refused from the next cycle</t>
+        </is>
+      </c>
+      <c r="G49" s="34" t="inlineStr">
+        <is>
+          <t>Control released within about 40 ms</t>
+        </is>
+      </c>
+      <c r="H49" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="I49" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J49" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K49" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L49" s="34" t="inlineStr">
+        <is>
+          <t>SG-05 brake/cancel · 200 ms
+30 + 10 ms</t>
+        </is>
+      </c>
+      <c r="M49" s="33" t="inlineStr">
+        <is>
+          <t>code derived</t>
+        </is>
+      </c>
+      <c r="N49" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-012 · open</t>
+        </is>
+      </c>
+      <c r="O49" s="37" t="inlineStr"/>
+      <c r="P49" s="37" t="inlineStr"/>
+    </row>
+    <row r="50" ht="46.5" customHeight="1">
+      <c r="A50" s="34" t="inlineStr">
+        <is>
+          <t>SFM-020 · Accelerator override not honored</t>
+        </is>
+      </c>
+      <c r="B50" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C50" s="33" t="inlineStr">
+        <is>
+          <t>SFM-020.C1</t>
+        </is>
+      </c>
+      <c r="D50" s="34" t="inlineStr">
+        <is>
+          <t>gasPressed parsed wrong or missing</t>
+        </is>
+      </c>
+      <c r="E50" s="34" t="inlineStr">
+        <is>
+          <t>Panda parses the gas pedal itself and refuses acceleration requests while it is pressed (longitudinal allowed only without gas)</t>
+        </is>
+      </c>
+      <c r="F50" s="34" t="inlineStr">
+        <is>
+          <t>ACC_CONTROL frames with a request refused</t>
+        </is>
+      </c>
+      <c r="G50" s="34" t="inlineStr">
+        <is>
+          <t>No item deceleration while the driver presses the gas</t>
+        </is>
+      </c>
+      <c r="H50" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="I50" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J50" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K50" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L50" s="34" t="inlineStr">
+        <is>
+          <t>SG-03/04 · 1000 ms
+33 + 10 ms</t>
+        </is>
+      </c>
+      <c r="M50" s="33" t="inlineStr">
+        <is>
+          <t>code derived</t>
+        </is>
+      </c>
+      <c r="N50" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-012 · open</t>
+        </is>
+      </c>
+      <c r="O50" s="37" t="inlineStr"/>
+      <c r="P50" s="37" t="inlineStr"/>
+    </row>
+    <row r="51" ht="87" customHeight="1">
+      <c r="A51" s="34" t="inlineStr">
+        <is>
+          <t>SFM-021 · Stock cruise stays engaged after LionDriver disengages</t>
+        </is>
+      </c>
+      <c r="B51" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C51" s="33" t="inlineStr">
+        <is>
+          <t>SFM-021.C1</t>
+        </is>
+      </c>
+      <c r="D51" s="34" t="inlineStr">
+        <is>
+          <t>Cancel message not packed/sent for this car</t>
+        </is>
+      </c>
+      <c r="E51" s="34" t="inlineStr">
+        <is>
+          <t>BL-005: selfdrived raises cruiseMismatch after 1 s of PCM cruise engaged while the item is not (CRUISE_MISMATCH_TIME, selfdrived.py; TSR-308). At BL-004 it was raised after 6 s with no reaction (T-19)</t>
+        </is>
+      </c>
+      <c r="F51" s="34" t="inlineStr">
+        <is>
+          <t>Repeating audible prompt to press Cancel or brake; controlsd keeps requesting the cancel</t>
+        </is>
+      </c>
+      <c r="G51" s="34" t="inlineStr">
+        <is>
+          <t>Stock cruise keeps controlling speed until the driver acts on the prompt; the mode confusion is now announced. The driver must act, so S after the response stays 10 (msr-plan.md §4.8)</t>
+        </is>
+      </c>
+      <c r="H51" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I51" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J51" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="K51" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L51" s="34" t="inlineStr">
+        <is>
+          <t>1000 + 10 ms</t>
+        </is>
+      </c>
+      <c r="M51" s="33" t="inlineStr">
+        <is>
+          <t>code derived</t>
+        </is>
+      </c>
+      <c r="N51" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-011 · completed</t>
+        </is>
+      </c>
+      <c r="O51" s="37" t="inlineStr"/>
+      <c r="P51" s="37" t="inlineStr"/>
+    </row>
+    <row r="52" ht="87" customHeight="1">
+      <c r="A52" s="34" t="inlineStr">
+        <is>
+          <t>SFM-021 · Stock cruise stays engaged after LionDriver disengages</t>
+        </is>
+      </c>
+      <c r="B52" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C52" s="33" t="inlineStr">
+        <is>
+          <t>SFM-021.C2</t>
+        </is>
+      </c>
+      <c r="D52" s="34" t="inlineStr">
+        <is>
+          <t>PCM ignores cancel request</t>
+        </is>
+      </c>
+      <c r="E52" s="34" t="inlineStr">
+        <is>
+          <t>BL-005: selfdrived raises cruiseMismatch after 1 s of PCM cruise engaged while the item is not (CRUISE_MISMATCH_TIME, selfdrived.py; TSR-308). At BL-004 it was raised after 6 s with no reaction (T-19)</t>
+        </is>
+      </c>
+      <c r="F52" s="34" t="inlineStr">
+        <is>
+          <t>Repeating audible prompt to press Cancel or brake; controlsd keeps requesting the cancel</t>
+        </is>
+      </c>
+      <c r="G52" s="34" t="inlineStr">
+        <is>
+          <t>Stock cruise keeps controlling speed until the driver acts on the prompt; the mode confusion is now announced. The driver must act, so S after the response stays 10 (msr-plan.md §4.8)</t>
+        </is>
+      </c>
+      <c r="H52" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I52" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="J52" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="K52" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L52" s="34" t="inlineStr">
+        <is>
+          <t>1000 + 10 ms</t>
+        </is>
+      </c>
+      <c r="M52" s="33" t="inlineStr">
+        <is>
+          <t>code derived</t>
+        </is>
+      </c>
+      <c r="N52" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-011 · completed</t>
+        </is>
+      </c>
+      <c r="O52" s="37" t="inlineStr"/>
+      <c r="P52" s="37" t="inlineStr"/>
+    </row>
+    <row r="53" ht="46.5" customHeight="1">
+      <c r="A53" s="34" t="inlineStr">
+        <is>
+          <t>SFM-022 · Inattentive driver not detected</t>
+        </is>
+      </c>
+      <c r="B53" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C53" s="33" t="inlineStr">
+        <is>
+          <t>SFM-022.C1</t>
+        </is>
+      </c>
+      <c r="D53" s="34" t="inlineStr">
+        <is>
+          <t>DM model false negative (eyes off road classified attentive)</t>
+        </is>
+      </c>
+      <c r="E53" s="34" t="inlineStr">
+        <is>
+          <t>Fallback to the wheel-touch policy only when the model is uncertain; a confident false negative is not caught</t>
+        </is>
+      </c>
+      <c r="F53" s="34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G53" s="34" t="inlineStr">
+        <is>
+          <t>Unchanged: escalation does not start</t>
+        </is>
+      </c>
+      <c r="H53" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I53" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="J53" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="K53" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L53" s="34" t="inlineStr"/>
+      <c r="M53" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N53" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-009 · open</t>
+        </is>
+      </c>
+      <c r="O53" s="37" t="inlineStr"/>
+      <c r="P53" s="37" t="inlineStr"/>
+    </row>
+    <row r="54" ht="46.5" customHeight="1">
+      <c r="A54" s="34" t="inlineStr">
+        <is>
+          <t>SFM-022 · Inattentive driver not detected</t>
+        </is>
+      </c>
+      <c r="B54" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C54" s="33" t="inlineStr">
+        <is>
+          <t>SFM-022.C2</t>
+        </is>
+      </c>
+      <c r="D54" s="34" t="inlineStr">
+        <is>
+          <t>Pose thresholds/calibration wrong for driver or mount</t>
+        </is>
+      </c>
+      <c r="E54" s="34" t="inlineStr">
+        <is>
+          <t>Fallback to the wheel-touch policy only when the model is uncertain; wrong thresholds give confident outputs</t>
+        </is>
+      </c>
+      <c r="F54" s="34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G54" s="34" t="inlineStr">
+        <is>
+          <t>Unchanged: escalation does not start</t>
+        </is>
+      </c>
+      <c r="H54" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I54" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J54" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="K54" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L54" s="34" t="inlineStr"/>
+      <c r="M54" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N54" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-009 · open</t>
+        </is>
+      </c>
+      <c r="O54" s="37" t="inlineStr"/>
+      <c r="P54" s="37" t="inlineStr"/>
+    </row>
+    <row r="55" ht="46.5" customHeight="1">
+      <c r="A55" s="34" t="inlineStr">
+        <is>
+          <t>SFM-022 · Inattentive driver not detected</t>
+        </is>
+      </c>
+      <c r="B55" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C55" s="33" t="inlineStr">
+        <is>
+          <t>SFM-022.C3</t>
+        </is>
+      </c>
+      <c r="D55" s="34" t="inlineStr">
+        <is>
+          <t>Driver camera or IR illumination degraded</t>
+        </is>
+      </c>
+      <c r="E55" s="34" t="inlineStr">
+        <is>
+          <t>A dead camera raises cameraMalfunction; a degraded image makes the model uncertain and falls back to the wheel-touch policy after 10 s</t>
+        </is>
+      </c>
+      <c r="F55" s="34" t="inlineStr">
+        <is>
+          <t>SOFT_DISABLE, or wheel-touch escalation</t>
+        </is>
+      </c>
+      <c r="G55" s="34" t="inlineStr">
+        <is>
+          <t>Driver monitored by wheel touch; no FTTI defined for DM</t>
+        </is>
+      </c>
+      <c r="H55" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I55" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="J55" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="K55" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L55" s="34" t="inlineStr"/>
+      <c r="M55" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N55" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-017 · open</t>
+        </is>
+      </c>
+      <c r="O55" s="37" t="inlineStr"/>
+      <c r="P55" s="37" t="inlineStr"/>
+    </row>
+    <row r="56" ht="46.5" customHeight="1">
+      <c r="A56" s="34" t="inlineStr">
+        <is>
+          <t>SFM-025 · Terminal driver-unresponsive state does not bring the item to a safe state</t>
+        </is>
+      </c>
+      <c r="B56" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C56" s="33" t="inlineStr">
+        <is>
+          <t>SFM-025.C1</t>
+        </is>
+      </c>
+      <c r="D56" s="34" t="inlineStr">
+        <is>
+          <t>driverDistracted3 / driverUnresponsive3 mapped only to ET.PERMANENT (no disable reaction)</t>
+        </is>
+      </c>
+      <c r="E56" s="34" t="inlineStr">
+        <is>
+          <t>None: the lockout acts only after disengagement; the terminal alert has no disable reaction</t>
+        </is>
+      </c>
+      <c r="F56" s="34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G56" s="34" t="inlineStr">
+        <is>
+          <t>Unchanged: control continues with an unresponsive driver</t>
+        </is>
+      </c>
+      <c r="H56" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I56" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="J56" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K56" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L56" s="34" t="inlineStr"/>
+      <c r="M56" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N56" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-005 · decision pending</t>
+        </is>
+      </c>
+      <c r="O56" s="37" t="inlineStr"/>
+      <c r="P56" s="37" t="inlineStr"/>
+    </row>
+    <row r="57" ht="33" customHeight="1">
+      <c r="A57" s="34" t="inlineStr">
+        <is>
+          <t>SFM-026 · Takeover or disengagement alert not presented</t>
+        </is>
+      </c>
+      <c r="B57" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C57" s="33" t="inlineStr">
+        <is>
+          <t>SFM-026.C1</t>
+        </is>
+      </c>
+      <c r="D57" s="34" t="inlineStr">
+        <is>
+          <t>UI process hung or display off</t>
+        </is>
+      </c>
+      <c r="E57" s="34" t="inlineStr">
+        <is>
+          <t>None at BL-004: the audio channel masks a hung UI but nothing detects it</t>
+        </is>
+      </c>
+      <c r="F57" s="34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G57" s="34" t="inlineStr">
+        <is>
+          <t>Alert audible only</t>
+        </is>
+      </c>
+      <c r="H57" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I57" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J57" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K57" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L57" s="34" t="inlineStr"/>
+      <c r="M57" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N57" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-007 · open</t>
+        </is>
+      </c>
+      <c r="O57" s="37" t="inlineStr"/>
+      <c r="P57" s="37" t="inlineStr"/>
+    </row>
+    <row r="58" ht="33" customHeight="1">
+      <c r="A58" s="34" t="inlineStr">
+        <is>
+          <t>SFM-026 · Takeover or disengagement alert not presented</t>
+        </is>
+      </c>
+      <c r="B58" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C58" s="33" t="inlineStr">
+        <is>
+          <t>SFM-026.C2</t>
+        </is>
+      </c>
+      <c r="D58" s="34" t="inlineStr">
+        <is>
+          <t>soundd failure or volume too low for cabin noise</t>
+        </is>
+      </c>
+      <c r="E58" s="34" t="inlineStr">
+        <is>
+          <t>None at BL-004: the screen masks a soundd failure but nothing detects it</t>
+        </is>
+      </c>
+      <c r="F58" s="34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G58" s="34" t="inlineStr">
+        <is>
+          <t>Alert visual only</t>
+        </is>
+      </c>
+      <c r="H58" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I58" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J58" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K58" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L58" s="34" t="inlineStr"/>
+      <c r="M58" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N58" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-007 · open</t>
+        </is>
+      </c>
+      <c r="O58" s="37" t="inlineStr"/>
+      <c r="P58" s="37" t="inlineStr"/>
+    </row>
+    <row r="59" ht="33" customHeight="1">
+      <c r="A59" s="34" t="inlineStr">
+        <is>
+          <t>SFM-026 · Takeover or disengagement alert not presented</t>
+        </is>
+      </c>
+      <c r="B59" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C59" s="33" t="inlineStr">
+        <is>
+          <t>SFM-026.C3</t>
+        </is>
+      </c>
+      <c r="D59" s="34" t="inlineStr">
+        <is>
+          <t>Speaker or display hardware failure</t>
+        </is>
+      </c>
+      <c r="E59" s="34" t="inlineStr">
+        <is>
+          <t>None: no self-test of speaker or display</t>
+        </is>
+      </c>
+      <c r="F59" s="34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G59" s="34" t="inlineStr">
+        <is>
+          <t>Alert on one channel or none</t>
+        </is>
+      </c>
+      <c r="H59" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I59" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="J59" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K59" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L59" s="34" t="inlineStr"/>
+      <c r="M59" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N59" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-007 · open</t>
+        </is>
+      </c>
+      <c r="O59" s="37" t="inlineStr"/>
+      <c r="P59" s="37" t="inlineStr"/>
+    </row>
+    <row r="60" ht="127.5" customHeight="1">
+      <c r="A60" s="34" t="inlineStr">
+        <is>
+          <t>SFM-029 · Actuator command limits not enforced</t>
+        </is>
+      </c>
+      <c r="B60" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C60" s="33" t="inlineStr">
+        <is>
+          <t>SFM-029.C1</t>
+        </is>
+      </c>
+      <c r="D60" s="34" t="inlineStr">
+        <is>
+          <t>Wrong safety model or parameter set for this car</t>
+        </is>
+      </c>
+      <c r="E60" s="34" t="inlineStr">
+        <is>
+          <t>controlsMismatch compares the panda safety model and parameter with CarParams, only from 10 s after start (T-18). BL-005: the panda refuses any car mode other than TOYOTA parameter 73, so a wrong request leaves it out of the car mode and the mismatch blocks engagement; a non-reference panda is named (pandaNotReferenceBuild). Not compared with an FTTI: the fault is present from power-up</t>
+        </is>
+      </c>
+      <c r="F60" s="34" t="inlineStr">
+        <is>
+          <t>IMMEDIATE_DISABLE with alert; engagement refused while the mismatch persists</t>
+        </is>
+      </c>
+      <c r="G60" s="34" t="inlineStr">
+        <is>
+          <t>Item disengaged with an alert</t>
+        </is>
+      </c>
+      <c r="H60" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="I60" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="J60" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="K60" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L60" s="34" t="inlineStr">
+        <is>
+          <t>10000 + 10 ms</t>
+        </is>
+      </c>
+      <c r="M60" s="33" t="inlineStr">
+        <is>
+          <t>code derived</t>
+        </is>
+      </c>
+      <c r="N60" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-008 · in progress</t>
+        </is>
+      </c>
+      <c r="O60" s="37" t="inlineStr"/>
+      <c r="P60" s="37" t="inlineStr"/>
+    </row>
+    <row r="61" ht="46.5" customHeight="1">
+      <c r="A61" s="34" t="inlineStr">
+        <is>
+          <t>SFM-029 · Actuator command limits not enforced</t>
+        </is>
+      </c>
+      <c r="B61" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C61" s="33" t="inlineStr">
+        <is>
+          <t>SFM-029.C2</t>
+        </is>
+      </c>
+      <c r="D61" s="34" t="inlineStr">
+        <is>
+          <t>Safety model limit defect in firmware</t>
+        </is>
+      </c>
+      <c r="E61" s="34" t="inlineStr">
+        <is>
+          <t>None: controlsMismatch checks which safety model is active, not its limit values; the limit code is itself the monitor that has failed</t>
+        </is>
+      </c>
+      <c r="F61" s="34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G61" s="34" t="inlineStr">
+        <is>
+          <t>Unchanged: commands beyond the intended envelope reach the EPS</t>
+        </is>
+      </c>
+      <c r="H61" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I61" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J61" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K61" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L61" s="34" t="inlineStr"/>
+      <c r="M61" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N61" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-001 · open</t>
+        </is>
+      </c>
+      <c r="O61" s="37" t="inlineStr"/>
+      <c r="P61" s="37" t="inlineStr"/>
+    </row>
+    <row r="62" ht="33" customHeight="1">
+      <c r="A62" s="34" t="inlineStr">
+        <is>
+          <t>SFM-029 · Actuator command limits not enforced</t>
+        </is>
+      </c>
+      <c r="B62" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C62" s="33" t="inlineStr">
+        <is>
+          <t>SFM-029.C3</t>
+        </is>
+      </c>
+      <c r="D62" s="34" t="inlineStr">
+        <is>
+          <t>Panda MCU hardware fault (see DFMEA/FMEDA)</t>
+        </is>
+      </c>
+      <c r="E62" s="62" t="inlineStr">
+        <is>
+          <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-001.C1)</t>
+        </is>
+      </c>
+      <c r="F62" s="34" t="inlineStr"/>
+      <c r="G62" s="34" t="inlineStr"/>
+      <c r="H62" s="35" t="inlineStr"/>
+      <c r="I62" s="35" t="inlineStr"/>
+      <c r="J62" s="35" t="inlineStr"/>
+      <c r="K62" s="33" t="inlineStr"/>
+      <c r="L62" s="34" t="inlineStr"/>
+      <c r="M62" s="33" t="inlineStr"/>
+      <c r="N62" s="34" t="inlineStr"/>
+      <c r="O62" s="37" t="inlineStr"/>
+      <c r="P62" s="37" t="inlineStr"/>
+    </row>
+    <row r="63" ht="46.5" customHeight="1">
+      <c r="A63" s="34" t="inlineStr">
+        <is>
+          <t>SFM-029 · Actuator command limits not enforced</t>
+        </is>
+      </c>
+      <c r="B63" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C63" s="33" t="inlineStr">
+        <is>
+          <t>SFM-029.C4</t>
+        </is>
+      </c>
+      <c r="D63" s="34" t="inlineStr">
+        <is>
+          <t>Harness allows the device to reach a bus without passing the panda filter</t>
+        </is>
+      </c>
+      <c r="E63" s="34" t="inlineStr">
+        <is>
+          <t>None: controlsMismatch cannot see a path that bypasses the panda</t>
+        </is>
+      </c>
+      <c r="F63" s="34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G63" s="34" t="inlineStr">
+        <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="H63" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I63" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="J63" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K63" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L63" s="34" t="inlineStr"/>
+      <c r="M63" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N63" s="34" t="inlineStr"/>
+      <c r="O63" s="37" t="inlineStr"/>
+      <c r="P63" s="37" t="inlineStr"/>
+    </row>
+    <row r="64" ht="114" customHeight="1">
+      <c r="A64" s="34" t="inlineStr">
+        <is>
+          <t>SFM-032 · Wrong vehicle configuration active (fingerprint or car port)</t>
+        </is>
+      </c>
+      <c r="B64" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C64" s="33" t="inlineStr">
+        <is>
+          <t>SFM-032.C1</t>
+        </is>
+      </c>
+      <c r="D64" s="34" t="inlineStr">
+        <is>
+          <t>Fuzzy fingerprint matches a similar platform</t>
+        </is>
+      </c>
+      <c r="E64" s="34" t="inlineStr">
+        <is>
+          <t>BL-005: if the matched platform needs a Toyota safety parameter other than 73, the panda refuses the car mode, so controlsMismatch (from 10 s after start) blocks engagement. A similar platform with parameter 73 is not detected: controlsMismatch compares the panda with CarParams, which share the same wrong platform, and carUnrecognized does not fire on a fuzzy match</t>
+        </is>
+      </c>
+      <c r="F64" s="34" t="inlineStr">
+        <is>
+          <t>For a platform with another safety parameter, no engagement (NO_ENTRY) and an alert; otherwise none</t>
+        </is>
+      </c>
+      <c r="G64" s="34" t="inlineStr">
+        <is>
+          <t>Partly mitigated: the panda envelope is that of the reference parameter, but host tuning, scaling and DBC of a similar platform with parameter 73 apply unseen</t>
+        </is>
+      </c>
+      <c r="H64" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I64" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="J64" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="K64" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L64" s="34" t="inlineStr">
+        <is>
+          <t>10000 + 10 ms</t>
+        </is>
+      </c>
+      <c r="M64" s="33" t="inlineStr">
+        <is>
+          <t>code derived</t>
+        </is>
+      </c>
+      <c r="N64" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-008 · in progress</t>
+        </is>
+      </c>
+      <c r="O64" s="37" t="inlineStr"/>
+      <c r="P64" s="37" t="inlineStr"/>
+    </row>
+    <row r="65" ht="33" customHeight="1">
+      <c r="A65" s="34" t="inlineStr">
+        <is>
+          <t>SFM-034 · Harness relay fault</t>
+        </is>
+      </c>
+      <c r="B65" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C65" s="33" t="inlineStr">
+        <is>
+          <t>SFM-034.C1</t>
+        </is>
+      </c>
+      <c r="D65" s="34" t="inlineStr">
+        <is>
+          <t>Relay contact wear or connector fault</t>
+        </is>
+      </c>
+      <c r="E65" s="62" t="inlineStr">
+        <is>
+          <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-010.C1)</t>
+        </is>
+      </c>
+      <c r="F65" s="34" t="inlineStr"/>
+      <c r="G65" s="34" t="inlineStr"/>
+      <c r="H65" s="35" t="inlineStr"/>
+      <c r="I65" s="35" t="inlineStr"/>
+      <c r="J65" s="35" t="inlineStr"/>
+      <c r="K65" s="33" t="inlineStr"/>
+      <c r="L65" s="34" t="inlineStr"/>
+      <c r="M65" s="33" t="inlineStr"/>
+      <c r="N65" s="34" t="inlineStr"/>
+      <c r="O65" s="37" t="inlineStr"/>
+      <c r="P65" s="37" t="inlineStr"/>
+    </row>
+    <row r="66" ht="33" customHeight="1">
+      <c r="A66" s="34" t="inlineStr">
+        <is>
+          <t>SFM-034 · Harness relay fault</t>
+        </is>
+      </c>
+      <c r="B66" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C66" s="33" t="inlineStr">
+        <is>
+          <t>SFM-034.C2</t>
+        </is>
+      </c>
+      <c r="D66" s="34" t="inlineStr">
+        <is>
+          <t>Relay drive output fault on panda</t>
+        </is>
+      </c>
+      <c r="E66" s="62" t="inlineStr">
+        <is>
+          <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-011.C1)</t>
+        </is>
+      </c>
+      <c r="F66" s="34" t="inlineStr"/>
+      <c r="G66" s="34" t="inlineStr"/>
+      <c r="H66" s="35" t="inlineStr"/>
+      <c r="I66" s="35" t="inlineStr"/>
+      <c r="J66" s="35" t="inlineStr"/>
+      <c r="K66" s="33" t="inlineStr"/>
+      <c r="L66" s="34" t="inlineStr"/>
+      <c r="M66" s="33" t="inlineStr"/>
+      <c r="N66" s="34" t="inlineStr"/>
+      <c r="O66" s="37" t="inlineStr"/>
+      <c r="P66" s="37" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P66"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:P1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="O3 O4 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 O34 O35 O36 O37 O38 O39 O40 O41 O42 O43 O44 O45 O46 O47 O48 O49 O50 O51 O52 O53 O54 O55 O56 O57 O58 O59 O60 O61 O62 O63 O64 O65 O66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this MSR row" type="list">
+      <formula1>"Agree,Re-rate,Reject,Question"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.9 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -802,7 +802,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.10 · draft</t>
+          <t>0.11 · draft</t>
         </is>
       </c>
     </row>
@@ -15759,7 +15759,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.10 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.11 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Structure" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$83</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Worksheet'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Structure'!$A$1:$E$20</definedName>
@@ -802,7 +802,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.11 · draft</t>
+          <t>0.12 · draft</t>
         </is>
       </c>
     </row>
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17">
@@ -1057,7 +1057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S82"/>
+  <dimension ref="A1:S83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2720,7 +2720,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -2829,7 +2829,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -3081,7 +3081,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -3414,7 +3414,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -3550,7 +3550,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -3784,7 +3784,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -4862,7 +4862,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -5420,7 +5420,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -5511,7 +5511,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -6015,7 +6015,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -6483,7 +6483,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -6716,7 +6716,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -7079,7 +7079,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -7552,7 +7552,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -8595,7 +8595,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -9242,7 +9242,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -9606,7 +9606,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -9970,7 +9970,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -10221,7 +10221,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -11040,7 +11040,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -12315,7 +12315,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -12658,7 +12658,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -13122,7 +13122,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -14447,7 +14447,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -14906,7 +14906,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Stock ADAS camera messages blocked or replaced by the harness relay</t>
+            <t>Stock ADAS camera messages blocked or replaced by the harness-box intercept</t>
           </r>
         </is>
       </c>
@@ -14954,7 +14954,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Relay intercepts stock camera messages the vehicle needs for AEB</t>
+            <t>The intercept routes the stock camera messages the vehicle needs for AEB through the panda</t>
           </r>
         </is>
       </c>
@@ -14966,7 +14966,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Forwarding keeps stock pre-collision messages (0x283, 0x344) passing the relay (SWF-011); which TSS2 functions remain with openpilot longitudinal is not established</t>
+            <t>• Forwarding keeps stock pre-collision messages (0x283, 0x344) passing the intercept (SWF-011); which TSS2 functions remain with openpilot longitudinal is not established</t>
           </r>
           <r>
             <rPr>
@@ -15035,18 +15035,18 @@
       <c r="S79" s="37" t="inlineStr"/>
     </row>
     <row r="80" ht="100.5" customHeight="1">
-      <c r="A80" s="39" t="n"/>
-      <c r="B80" s="39" t="n"/>
-      <c r="C80" s="39" t="n"/>
-      <c r="D80" s="39" t="n"/>
-      <c r="E80" s="39" t="n"/>
-      <c r="F80" s="39" t="n"/>
-      <c r="G80" s="40" t="inlineStr">
+      <c r="A80" s="38" t="n"/>
+      <c r="B80" s="38" t="n"/>
+      <c r="C80" s="38" t="n"/>
+      <c r="D80" s="38" t="n"/>
+      <c r="E80" s="38" t="n"/>
+      <c r="F80" s="38" t="n"/>
+      <c r="G80" s="33" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="H80" s="41" t="inlineStr">
+      <c r="H80" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15067,7 +15067,7 @@
           </r>
         </is>
       </c>
-      <c r="I80" s="41" t="inlineStr">
+      <c r="I80" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15088,10 +15088,10 @@
           </r>
         </is>
       </c>
-      <c r="J80" s="42" t="n">
+      <c r="J80" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="K80" s="41" t="inlineStr">
+      <c r="K80" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15112,15 +15112,15 @@
           </r>
         </is>
       </c>
-      <c r="L80" s="42" t="n">
+      <c r="L80" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="M80" s="44" t="inlineStr">
+      <c r="M80" s="36" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N80" s="41" t="inlineStr">
+      <c r="N80" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15142,18 +15142,103 @@
           </r>
         </is>
       </c>
-      <c r="O80" s="48" t="inlineStr">
+      <c r="O80" s="47" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P80" s="40" t="inlineStr"/>
-      <c r="Q80" s="40" t="inlineStr"/>
-      <c r="R80" s="45" t="inlineStr"/>
-      <c r="S80" s="45" t="inlineStr"/>
+      <c r="P80" s="33" t="inlineStr"/>
+      <c r="Q80" s="33" t="inlineStr"/>
+      <c r="R80" s="37" t="inlineStr"/>
+      <c r="S80" s="37" t="inlineStr"/>
     </row>
-    <row r="81" ht="87" customHeight="1">
-      <c r="A81" s="30" t="inlineStr">
+    <row r="81" ht="141" customHeight="1">
+      <c r="A81" s="39" t="n"/>
+      <c r="B81" s="39" t="n"/>
+      <c r="C81" s="39" t="n"/>
+      <c r="D81" s="39" t="n"/>
+      <c r="E81" s="39" t="n"/>
+      <c r="F81" s="39" t="n"/>
+      <c r="G81" s="40" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="H81" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The harness box loses its supply (ignition branch or D1 open without comma power, VIN shorted), or a switch channel opens, so the stock camera path through the unpowered or open DG419LE switches is cut (RR-2026-010)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: DFM-020</t>
+          </r>
+        </is>
+      </c>
+      <c r="I81" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Consumer-grade harness box without automotive qualification data available to LionDriver; rated in the DFMEA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/08-analyses/fmea/analyses/dfmea.yaml</t>
+          </r>
+        </is>
+      </c>
+      <c r="J81" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="K81" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• As rated in the DFMEA: no pre-release test of this hardware fault</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/08-analyses/fmea/analyses/dfmea.yaml</t>
+          </r>
+        </is>
+      </c>
+      <c r="L81" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="M81" s="44" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N81" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15162,6 +15247,39 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
+            <t xml:space="preserve">SFM-ACT-003 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+          </r>
+        </is>
+      </c>
+      <c r="O81" s="48" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P81" s="40" t="inlineStr"/>
+      <c r="Q81" s="40" t="inlineStr"/>
+      <c r="R81" s="45" t="inlineStr"/>
+      <c r="S81" s="45" t="inlineStr"/>
+    </row>
+    <row r="82" ht="87" customHeight="1">
+      <c r="A82" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
             <t xml:space="preserve">SFM-SE-001
 </t>
           </r>
@@ -15175,7 +15293,7 @@
           </r>
         </is>
       </c>
-      <c r="B81" s="30" t="inlineStr">
+      <c r="B82" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15197,7 +15315,7 @@
           </r>
         </is>
       </c>
-      <c r="C81" s="30" t="inlineStr">
+      <c r="C82" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15318,21 +15436,21 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Relay stuck or intermittent; stock camera and item both on bus, or neither</t>
-          </r>
-        </is>
-      </c>
-      <c r="D81" s="31" t="inlineStr">
+            <t>Intercept switch stuck or intermittent: in intercept when released (camera cut off from the car), or in pass-through when driven (stock camera and item both on the bus)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D82" s="31" t="inlineStr">
         <is>
           <t>HZ-011
 HZ-002
 HZ-006</t>
         </is>
       </c>
-      <c r="E81" s="32" t="n">
+      <c r="E82" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="F81" s="30" t="inlineStr">
+      <c r="F82" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15351,24 +15469,24 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Harness relay fault</t>
-          </r>
-        </is>
-      </c>
-      <c r="G81" s="33" t="inlineStr">
+            <t>Harness-box intercept switch stuck or in the wrong position</t>
+          </r>
+        </is>
+      </c>
+      <c r="G82" s="33" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H81" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Relay contact wear or connector fault</t>
+      <c r="H82" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Switch U1 or U2 stuck in intercept, its IN input damaged high or driven high, its pull-down R2/R3 open, or the switches damaged by box supply transients (DG419LE, RR-2026-010)</t>
           </r>
           <r>
             <rPr>
@@ -15381,7 +15499,7 @@
           </r>
         </is>
       </c>
-      <c r="I81" s="34" t="inlineStr">
+      <c r="I82" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15402,10 +15520,10 @@
           </r>
         </is>
       </c>
-      <c r="J81" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="K81" s="34" t="inlineStr">
+      <c r="J82" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="K82" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15426,15 +15544,15 @@
           </r>
         </is>
       </c>
-      <c r="L81" s="46" t="n">
+      <c r="L82" s="46" t="n">
         <v>10</v>
       </c>
-      <c r="M81" s="36" t="inlineStr">
+      <c r="M82" s="36" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N81" s="34" t="inlineStr">
+      <c r="N82" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15451,37 +15569,37 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Hardware fault rated in the DFMEA (DFM-010 O3 D10, DFM-011 O3 D9); this row inherits that rating; relayMalfunction (SWF-012) is the in-field mechanism</t>
-          </r>
-        </is>
-      </c>
-      <c r="O81" s="34" t="inlineStr"/>
-      <c r="P81" s="33" t="inlineStr"/>
-      <c r="Q81" s="33" t="inlineStr"/>
-      <c r="R81" s="37" t="inlineStr"/>
-      <c r="S81" s="37" t="inlineStr"/>
+            <t>Hardware fault rated in the DFMEA (DFM-010.C1-C3 O3 D10, DFM-010.C4 O4 D10); this row inherits the worst. relayMalfunction (SWF-012) is the in-field mechanism; there is no switch-state feedback (RR-2026-010)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O82" s="34" t="inlineStr"/>
+      <c r="P82" s="33" t="inlineStr"/>
+      <c r="Q82" s="33" t="inlineStr"/>
+      <c r="R82" s="37" t="inlineStr"/>
+      <c r="S82" s="37" t="inlineStr"/>
     </row>
-    <row r="82" ht="87" customHeight="1">
-      <c r="A82" s="39" t="n"/>
-      <c r="B82" s="39" t="n"/>
-      <c r="C82" s="39" t="n"/>
-      <c r="D82" s="39" t="n"/>
-      <c r="E82" s="39" t="n"/>
-      <c r="F82" s="39" t="n"/>
-      <c r="G82" s="40" t="inlineStr">
+    <row r="83" ht="102" customHeight="1">
+      <c r="A83" s="39" t="n"/>
+      <c r="B83" s="39" t="n"/>
+      <c r="C83" s="39" t="n"/>
+      <c r="D83" s="39" t="n"/>
+      <c r="E83" s="39" t="n"/>
+      <c r="F83" s="39" t="n"/>
+      <c r="G83" s="40" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="H82" s="41" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Relay drive output fault on panda</t>
+      <c r="H83" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Switch stuck in pass-through, or the SBU1 drive lost, held low or too low to change the switch over (5 V drive against VL = VIN)</t>
           </r>
           <r>
             <rPr>
@@ -15494,7 +15612,7 @@
           </r>
         </is>
       </c>
-      <c r="I82" s="41" t="inlineStr">
+      <c r="I83" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15515,10 +15633,10 @@
           </r>
         </is>
       </c>
-      <c r="J82" s="42" t="n">
+      <c r="J83" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="K82" s="41" t="inlineStr">
+      <c r="K83" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15539,15 +15657,15 @@
           </r>
         </is>
       </c>
-      <c r="L82" s="43" t="n">
-        <v>10</v>
-      </c>
-      <c r="M82" s="44" t="inlineStr">
+      <c r="L83" s="43" t="n">
+        <v>9</v>
+      </c>
+      <c r="M83" s="44" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N82" s="41" t="inlineStr">
+      <c r="N83" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15564,24 +15682,22 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Hardware fault rated in the DFMEA (DFM-011, DFM-010); this row inherits that rating</t>
-          </r>
-        </is>
-      </c>
-      <c r="O82" s="41" t="inlineStr"/>
-      <c r="P82" s="40" t="inlineStr"/>
-      <c r="Q82" s="40" t="inlineStr"/>
-      <c r="R82" s="45" t="inlineStr"/>
-      <c r="S82" s="45" t="inlineStr"/>
+            <t>Hardware fault rated in the DFMEA (DFM-011.C1 O3 D9, DFM-011.C2 O2 D9); this row inherits the worst</t>
+          </r>
+        </is>
+      </c>
+      <c r="O83" s="41" t="inlineStr"/>
+      <c r="P83" s="40" t="inlineStr"/>
+      <c r="Q83" s="40" t="inlineStr"/>
+      <c r="R83" s="45" t="inlineStr"/>
+      <c r="S83" s="45" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S82"/>
+  <autoFilter ref="A2:S83"/>
   <mergeCells count="172">
     <mergeCell ref="F17:F19"/>
     <mergeCell ref="E39:E40"/>
-    <mergeCell ref="C79:C80"/>
     <mergeCell ref="A57:A59"/>
-    <mergeCell ref="E79:E80"/>
     <mergeCell ref="A20:A22"/>
     <mergeCell ref="F25:F28"/>
     <mergeCell ref="A51:A52"/>
@@ -15591,7 +15707,6 @@
     <mergeCell ref="C32:C34"/>
     <mergeCell ref="E32:E34"/>
     <mergeCell ref="B23:B24"/>
-    <mergeCell ref="F79:F80"/>
     <mergeCell ref="B20:B22"/>
     <mergeCell ref="D20:D22"/>
     <mergeCell ref="E3:E5"/>
@@ -15600,7 +15715,6 @@
     <mergeCell ref="F29:F31"/>
     <mergeCell ref="F47:F48"/>
     <mergeCell ref="E49:E50"/>
-    <mergeCell ref="F81:F82"/>
     <mergeCell ref="A71:A74"/>
     <mergeCell ref="B37:B38"/>
     <mergeCell ref="C71:C74"/>
@@ -15616,6 +15730,7 @@
     <mergeCell ref="E44:E46"/>
     <mergeCell ref="B57:B59"/>
     <mergeCell ref="C69:C70"/>
+    <mergeCell ref="F79:F81"/>
     <mergeCell ref="D57:D59"/>
     <mergeCell ref="N1:Q1"/>
     <mergeCell ref="D41:D43"/>
@@ -15624,7 +15739,6 @@
     <mergeCell ref="B35:B36"/>
     <mergeCell ref="F10:F13"/>
     <mergeCell ref="D49:D50"/>
-    <mergeCell ref="A79:A80"/>
     <mergeCell ref="E55:E56"/>
     <mergeCell ref="A32:A34"/>
     <mergeCell ref="A14:A16"/>
@@ -15648,37 +15762,38 @@
     <mergeCell ref="D37:D38"/>
     <mergeCell ref="A23:A24"/>
     <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C82:C83"/>
     <mergeCell ref="D55:D56"/>
+    <mergeCell ref="C79:C81"/>
     <mergeCell ref="I1:M1"/>
+    <mergeCell ref="E79:E81"/>
     <mergeCell ref="D39:D40"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="D79:D80"/>
-    <mergeCell ref="E81:E82"/>
     <mergeCell ref="A39:A40"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="B14:B16"/>
     <mergeCell ref="D23:D24"/>
     <mergeCell ref="B29:B31"/>
     <mergeCell ref="A49:A50"/>
-    <mergeCell ref="B81:B82"/>
     <mergeCell ref="D32:D34"/>
     <mergeCell ref="C49:C50"/>
-    <mergeCell ref="D81:D82"/>
     <mergeCell ref="F32:F34"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="E67:E68"/>
     <mergeCell ref="A17:A19"/>
     <mergeCell ref="E51:E52"/>
     <mergeCell ref="C17:C19"/>
+    <mergeCell ref="E82:E83"/>
     <mergeCell ref="E60:E61"/>
     <mergeCell ref="E69:E70"/>
     <mergeCell ref="A25:A28"/>
     <mergeCell ref="B71:B74"/>
+    <mergeCell ref="B82:B83"/>
     <mergeCell ref="A44:A46"/>
     <mergeCell ref="F51:F52"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A64:A66"/>
+    <mergeCell ref="A79:A81"/>
     <mergeCell ref="B41:B43"/>
     <mergeCell ref="F23:F24"/>
     <mergeCell ref="B10:B13"/>
@@ -15725,20 +15840,22 @@
     <mergeCell ref="C25:C28"/>
     <mergeCell ref="A55:A56"/>
     <mergeCell ref="C55:C56"/>
+    <mergeCell ref="B79:B81"/>
     <mergeCell ref="B32:B34"/>
+    <mergeCell ref="D79:D81"/>
     <mergeCell ref="C67:C68"/>
     <mergeCell ref="E17:E19"/>
     <mergeCell ref="D71:D74"/>
     <mergeCell ref="E75:E76"/>
     <mergeCell ref="A47:A48"/>
-    <mergeCell ref="A81:A82"/>
     <mergeCell ref="D17:D19"/>
-    <mergeCell ref="C81:C82"/>
+    <mergeCell ref="F82:F83"/>
     <mergeCell ref="D67:D68"/>
     <mergeCell ref="F67:F68"/>
     <mergeCell ref="B51:B52"/>
     <mergeCell ref="E47:E48"/>
     <mergeCell ref="D51:D52"/>
+    <mergeCell ref="D82:D83"/>
     <mergeCell ref="D60:D61"/>
     <mergeCell ref="F60:F61"/>
     <mergeCell ref="C37:C38"/>
@@ -15747,11 +15864,12 @@
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="F69:F70"/>
     <mergeCell ref="B25:B28"/>
+    <mergeCell ref="A82:A83"/>
     <mergeCell ref="D35:D36"/>
     <mergeCell ref="C6:C9"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
+    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
       <formula1>"Agree,Re-rate,Reject,Question"</formula1>
     </dataValidation>
   </dataValidations>
@@ -15759,7 +15877,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.11 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.12 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -15921,7 +16039,7 @@
       <c r="H3" s="59" t="inlineStr"/>
       <c r="I3" s="59" t="inlineStr"/>
     </row>
-    <row r="4" ht="330" customHeight="1">
+    <row r="4" ht="343.5" customHeight="1">
       <c r="A4" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-003</t>
@@ -15934,7 +16052,7 @@
       </c>
       <c r="C4" s="59" t="inlineStr">
         <is>
-          <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+          <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
         </is>
       </c>
       <c r="D4" s="59" t="inlineStr">
@@ -15972,7 +16090,8 @@
 SFM-026.C2
 SFM-027.C1
 SFM-028.C2
-SFM-031.C1</t>
+SFM-031.C1
+SFM-033.C3</t>
         </is>
       </c>
       <c r="G4" s="59" t="inlineStr"/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Structure" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$85</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Worksheet'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Structure'!$A$1:$E$20</definedName>
@@ -802,7 +802,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.12 · draft</t>
+          <t>0.13 · draft</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17">
@@ -1057,7 +1057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S83"/>
+  <dimension ref="A1:S85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -15692,9 +15692,387 @@
       <c r="R83" s="45" t="inlineStr"/>
       <c r="S83" s="45" t="inlineStr"/>
     </row>
+    <row r="84" ht="100.5" customHeight="1">
+      <c r="A84" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-SE-001
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>LionDriver item (L2 ACC + ALC + driver monitoring)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B84" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-FN-008
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>F8 Stock function preservation: keep stock vehicle safety functions not replaced by the item available</t>
+          </r>
+        </is>
+      </c>
+      <c r="C84" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Stock AEB/FCW degraded while the driver relies on it</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-006: PCS braking triggered by a frame from the item</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Stock PCS warning or braking suppressed, altered or triggered by the item</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>A PCS-relevant frame from the SoC (0x344 PRE_COLLISION_2, 0x411 PCS_HUD, a DSU-only ID, or 0x283 PRE_COLLISION with a non-zero payload) reaches the car bus</t>
+          </r>
+        </is>
+      </c>
+      <c r="D84" s="31" t="inlineStr">
+        <is>
+          <t>HZ-011
+HZ-006</t>
+        </is>
+      </c>
+      <c r="E84" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F84" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-035 · unintended
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Item sends a frame that alters the stock pre-collision function</t>
+          </r>
+        </is>
+      </c>
+      <c r="G84" s="33" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H84" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Host code (car interface, pandad) emits a PCS-relevant ID or a non-zero PRE_COLLISION payload (QM fault)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I84" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream opendbc Toyota port; no carcontroller path builds 0x344, 0x411 or the DSU IDs for the reference car, and 0x283 is sent with a zero payload only; no LionDriver requirements, no field-exposure credit</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   opendbc_repo/opendbc/car/toyota</t>
+          </r>
+        </is>
+      </c>
+      <c r="J84" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="K84" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• process_replay over the CI route corpus compares sendcan with the reference commit; a regression check, not designed or proven for this cause</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/test/process_replay/test_processes.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L84" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="M84" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N84" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Rationale  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The panda refuses these frames on every frame (SFM-035.C3 is the case where that check fails); no separate action. A compromised SoC sending them on purpose is a TARA topic, out of scope here</t>
+          </r>
+        </is>
+      </c>
+      <c r="O84" s="34" t="inlineStr"/>
+      <c r="P84" s="33" t="inlineStr"/>
+      <c r="Q84" s="33" t="inlineStr"/>
+      <c r="R84" s="37" t="inlineStr"/>
+      <c r="S84" s="37" t="inlineStr"/>
+    </row>
+    <row r="85" ht="100.5" customHeight="1">
+      <c r="A85" s="39" t="n"/>
+      <c r="B85" s="39" t="n"/>
+      <c r="C85" s="39" t="n"/>
+      <c r="D85" s="39" t="n"/>
+      <c r="E85" s="39" t="n"/>
+      <c r="F85" s="39" t="n"/>
+      <c r="G85" s="40" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="H85" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The TX whitelist or the PRE_COLLISION content check lets a PCS-relevant frame through (table change, or a build that is not the reference build, where 0x411 is allowed by design)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I85" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Panda safety code: MISRA C:2012, 100% line coverage, review; reduced whitelist (TSR-705); reference build the default since BL-005 (pandad requires it, TSR-514/619)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   opendbc_repo/opendbc/safety/modes/toyota.h</t>
+          </r>
+        </is>
+      </c>
+      <c r="J85" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="K85" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• opendbc safety suite with 100% line coverage and mutation tests in both variants, run by CI on every change (proven, early, test-to-fail)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   opendbc_repo/opendbc/safety/tests/test_toyota.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L85" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="M85" s="44" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N85" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Rationale  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The whitelist is a static table pinned by mutation-proven tests in both variants; the non-reference variant keeps 0x411 by design and cannot configure a car mode with pandad at BL-005. No SW FMEA mode covers the table yet (FTA BE-7.07, for the SW FMEA)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O85" s="41" t="inlineStr"/>
+      <c r="P85" s="40" t="inlineStr"/>
+      <c r="Q85" s="40" t="inlineStr"/>
+      <c r="R85" s="45" t="inlineStr"/>
+      <c r="S85" s="45" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:S83"/>
-  <mergeCells count="172">
+  <autoFilter ref="A2:S85"/>
+  <mergeCells count="178">
+    <mergeCell ref="F84:F85"/>
     <mergeCell ref="F17:F19"/>
     <mergeCell ref="E39:E40"/>
     <mergeCell ref="A57:A59"/>
@@ -15754,6 +16132,7 @@
     <mergeCell ref="E6:E9"/>
     <mergeCell ref="B69:B70"/>
     <mergeCell ref="B3:B5"/>
+    <mergeCell ref="B84:B85"/>
     <mergeCell ref="C51:C52"/>
     <mergeCell ref="C60:C61"/>
     <mergeCell ref="C64:C66"/>
@@ -15779,6 +16158,7 @@
     <mergeCell ref="F32:F34"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="E67:E68"/>
+    <mergeCell ref="A84:A85"/>
     <mergeCell ref="A17:A19"/>
     <mergeCell ref="E51:E52"/>
     <mergeCell ref="C17:C19"/>
@@ -15788,6 +16168,8 @@
     <mergeCell ref="A25:A28"/>
     <mergeCell ref="B71:B74"/>
     <mergeCell ref="B82:B83"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="E84:E85"/>
     <mergeCell ref="A44:A46"/>
     <mergeCell ref="F51:F52"/>
     <mergeCell ref="C3:C5"/>
@@ -15867,9 +16249,10 @@
     <mergeCell ref="A82:A83"/>
     <mergeCell ref="D35:D36"/>
     <mergeCell ref="C6:C9"/>
+    <mergeCell ref="D84:D85"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
+    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83 R84 R85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
       <formula1>"Agree,Re-rate,Reject,Question"</formula1>
     </dataValidation>
   </dataValidations>
@@ -15877,7 +16260,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.12 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.13 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Structure" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$87</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Worksheet'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Structure'!$A$1:$E$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -252,7 +252,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -389,6 +389,9 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -880,7 +883,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -890,7 +893,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16">
@@ -900,7 +903,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17">
@@ -931,7 +934,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>18 (17)</t>
+          <t>19 (18)</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S85"/>
+  <dimension ref="A1:S87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -16069,9 +16072,342 @@
       <c r="R85" s="45" t="inlineStr"/>
       <c r="S85" s="45" t="inlineStr"/>
     </row>
+    <row r="86" ht="127.5" customHeight="1">
+      <c r="A86" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-SE-001
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>LionDriver item (L2 ACC + ALC + driver monitoring)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B86" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-FN-008
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>F8 Stock function preservation: keep stock vehicle safety functions not replaced by the item available</t>
+          </r>
+        </is>
+      </c>
+      <c r="C86" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Stock AEB deceleration reduced or delayed if the PCM arbitrates otherwise</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>PCS braking depends on the PCM giving it priority over the item's request (AOU-04R, unverified)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>ACC_CONTROL keeps carrying the planner's acceleration request while the stock camera reports a PCS braking event</t>
+          </r>
+        </is>
+      </c>
+      <c r="D86" s="31" t="inlineStr">
+        <is>
+          <t>HZ-011</t>
+        </is>
+      </c>
+      <c r="E86" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F86" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-036 · unintended
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Item keeps requesting acceleration while stock PCS brakes</t>
+          </r>
+        </is>
+      </c>
+      <c r="G86" s="33" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H86" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The item has no reaction to a stock PCS event on its longitudinal command; controlsd keeps requesting the planner's acceleration (design gap, FTA BE-7.13)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I86" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• None in the item: FSR-07.04 places PCS priority in the PCM as an external measure (AOU-04R)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/02-concept/WP-C-04-functional-safety-concept.md</t>
+          </r>
+        </is>
+      </c>
+      <c r="J86" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="K86" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No pre-release test targets this cause</t>
+          </r>
+        </is>
+      </c>
+      <c r="L86" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="M86" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N86" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-ACT-020 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>React to a stock PCS event on the longitudinal command (for example a neutral or zero acceleration request, or a longitudinal disable, while stockAeb is set), so stock AEB does not depend on PCM arbitration alone (AOU-04R); or keep today's behaviour and rely on the AOU-04R vehicle test. Lead decision DQ-300</t>
+          </r>
+        </is>
+      </c>
+      <c r="O86" s="58" t="inlineStr">
+        <is>
+          <t>decision pending</t>
+        </is>
+      </c>
+      <c r="P86" s="33" t="inlineStr"/>
+      <c r="Q86" s="33" t="inlineStr"/>
+      <c r="R86" s="37" t="inlineStr"/>
+      <c r="S86" s="37" t="inlineStr"/>
+    </row>
+    <row r="87" ht="100.5" customHeight="1">
+      <c r="A87" s="39" t="n"/>
+      <c r="B87" s="39" t="n"/>
+      <c r="C87" s="39" t="n"/>
+      <c r="D87" s="39" t="n"/>
+      <c r="E87" s="39" t="n"/>
+      <c r="F87" s="39" t="n"/>
+      <c r="G87" s="40" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H87" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The PCM does not give stock PCS braking priority over the item's ACC_CONTROL request (AOU-04R not met)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I87" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Series-production Toyota ECU; PCS priority over 0x343 assumed (AOU-04R), not verified by LionDriver</t>
+          </r>
+        </is>
+      </c>
+      <c r="J87" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="K87" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No pre-release test targets this cause; AOU-04R needs a message review and a PCS target test (WP-C-04)</t>
+          </r>
+        </is>
+      </c>
+      <c r="L87" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="M87" s="44" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N87" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-ACT-006 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Establish on the reference car which stock TSS2 functions (PCS/AEB, FCW) remain available with LionDriver installed and longitudinal control enabled, and verify the stock pre-collision path after installation (PFMEA PFM-014)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O87" s="48" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P87" s="40" t="inlineStr"/>
+      <c r="Q87" s="40" t="inlineStr"/>
+      <c r="R87" s="45" t="inlineStr"/>
+      <c r="S87" s="45" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:S85"/>
-  <mergeCells count="178">
+  <autoFilter ref="A2:S87"/>
+  <mergeCells count="184">
     <mergeCell ref="F84:F85"/>
     <mergeCell ref="F17:F19"/>
     <mergeCell ref="E39:E40"/>
@@ -16079,9 +16415,12 @@
     <mergeCell ref="A20:A22"/>
     <mergeCell ref="F25:F28"/>
     <mergeCell ref="A51:A52"/>
+    <mergeCell ref="B86:B87"/>
     <mergeCell ref="A29:A31"/>
+    <mergeCell ref="D86:D87"/>
     <mergeCell ref="E23:E24"/>
     <mergeCell ref="F55:F56"/>
+    <mergeCell ref="F86:F87"/>
     <mergeCell ref="C32:C34"/>
     <mergeCell ref="E32:E34"/>
     <mergeCell ref="B23:B24"/>
@@ -16103,6 +16442,7 @@
     <mergeCell ref="C41:C43"/>
     <mergeCell ref="F71:F74"/>
     <mergeCell ref="A10:A13"/>
+    <mergeCell ref="C86:C87"/>
     <mergeCell ref="C44:C46"/>
     <mergeCell ref="A35:A36"/>
     <mergeCell ref="E44:E46"/>
@@ -16176,6 +16516,7 @@
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A64:A66"/>
     <mergeCell ref="A79:A81"/>
+    <mergeCell ref="E86:E87"/>
     <mergeCell ref="B41:B43"/>
     <mergeCell ref="F23:F24"/>
     <mergeCell ref="B10:B13"/>
@@ -16221,6 +16562,7 @@
     <mergeCell ref="B64:B66"/>
     <mergeCell ref="C25:C28"/>
     <mergeCell ref="A55:A56"/>
+    <mergeCell ref="A86:A87"/>
     <mergeCell ref="C55:C56"/>
     <mergeCell ref="B79:B81"/>
     <mergeCell ref="B32:B34"/>
@@ -16252,7 +16594,7 @@
     <mergeCell ref="D84:D85"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83 R84 R85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
+    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83 R84 R85 R86 R87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
       <formula1>"Agree,Re-rate,Reject,Question"</formula1>
     </dataValidation>
   </dataValidations>
@@ -16275,7 +16617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16290,79 +16632,79 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="58" t="inlineStr">
+      <c r="A1" s="59" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B1" s="58" t="inlineStr">
+      <c r="B1" s="59" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="C1" s="58" t="inlineStr">
+      <c r="C1" s="59" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" s="58" t="inlineStr">
+      <c r="D1" s="59" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E1" s="58" t="inlineStr">
+      <c r="E1" s="59" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="58" t="inlineStr">
+      <c r="F1" s="59" t="inlineStr">
         <is>
           <t>Causes</t>
         </is>
       </c>
-      <c r="G1" s="58" t="inlineStr">
+      <c r="G1" s="59" t="inlineStr">
         <is>
           <t>Revised S/O/D</t>
         </is>
       </c>
-      <c r="H1" s="58" t="inlineStr">
+      <c r="H1" s="59" t="inlineStr">
         <is>
           <t>Revised AP</t>
         </is>
       </c>
-      <c r="I1" s="58" t="inlineStr">
+      <c r="I1" s="59" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
     </row>
     <row r="2" ht="127.5" customHeight="1">
-      <c r="A2" s="59" t="inlineStr">
+      <c r="A2" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-001</t>
         </is>
       </c>
-      <c r="B2" s="59" t="inlineStr">
+      <c r="B2" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C2" s="59" t="inlineStr">
+      <c r="C2" s="60" t="inlineStr">
         <is>
           <t>Derive steering and acceleration envelopes from measurements on the reference vehicle and set the panda limits from them, independently of the SoC limits (same as SWF-ACT-003, FSC FOI-001)</t>
         </is>
       </c>
-      <c r="D2" s="59" t="inlineStr">
+      <c r="D2" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E2" s="59" t="inlineStr">
+      <c r="E2" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F2" s="59" t="inlineStr">
+      <c r="F2" s="60" t="inlineStr">
         <is>
           <t>SFM-002.C1
 SFM-002.C2
@@ -16375,37 +16717,37 @@
 SFM-029.C2</t>
         </is>
       </c>
-      <c r="G2" s="59" t="inlineStr"/>
-      <c r="H2" s="59" t="inlineStr"/>
-      <c r="I2" s="59" t="inlineStr"/>
+      <c r="G2" s="60" t="inlineStr"/>
+      <c r="H2" s="60" t="inlineStr"/>
+      <c r="I2" s="60" t="inlineStr"/>
     </row>
     <row r="3" ht="127.5" customHeight="1">
-      <c r="A3" s="59" t="inlineStr">
+      <c r="A3" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-002</t>
         </is>
       </c>
-      <c r="B3" s="59" t="inlineStr">
+      <c r="B3" s="60" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C3" s="59" t="inlineStr">
+      <c r="C3" s="60" t="inlineStr">
         <is>
           <t>Requirements-based tests for the host safety-relevant functions (selfdrived, controlsd, pandad, car interface, locationd bounds, monitoring policy), proven by mutation or fault injection and run as a CI gate (see SWF host actions)</t>
         </is>
       </c>
-      <c r="D3" s="59" t="inlineStr">
+      <c r="D3" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E3" s="59" t="inlineStr">
+      <c r="E3" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F3" s="59" t="inlineStr">
+      <c r="F3" s="60" t="inlineStr">
         <is>
           <t>SFM-002.C4
 SFM-004.C3
@@ -16418,37 +16760,37 @@
 SFM-030.C1</t>
         </is>
       </c>
-      <c r="G3" s="59" t="inlineStr"/>
-      <c r="H3" s="59" t="inlineStr"/>
-      <c r="I3" s="59" t="inlineStr"/>
+      <c r="G3" s="60" t="inlineStr"/>
+      <c r="H3" s="60" t="inlineStr"/>
+      <c r="I3" s="60" t="inlineStr"/>
     </row>
     <row r="4" ht="343.5" customHeight="1">
-      <c r="A4" s="59" t="inlineStr">
+      <c r="A4" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-003</t>
         </is>
       </c>
-      <c r="B4" s="59" t="inlineStr">
+      <c r="B4" s="60" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C4" s="59" t="inlineStr">
+      <c r="C4" s="60" t="inlineStr">
         <is>
           <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
         </is>
       </c>
-      <c r="D4" s="59" t="inlineStr">
+      <c r="D4" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E4" s="59" t="inlineStr">
+      <c r="E4" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F4" s="59" t="inlineStr">
+      <c r="F4" s="60" t="inlineStr">
         <is>
           <t>SFM-003.C1
 SFM-003.C2
@@ -16477,109 +16819,110 @@
 SFM-033.C3</t>
         </is>
       </c>
-      <c r="G4" s="59" t="inlineStr"/>
-      <c r="H4" s="59" t="inlineStr"/>
-      <c r="I4" s="59" t="inlineStr"/>
+      <c r="G4" s="60" t="inlineStr"/>
+      <c r="H4" s="60" t="inlineStr"/>
+      <c r="I4" s="60" t="inlineStr"/>
     </row>
     <row r="5" ht="73.5" customHeight="1">
-      <c r="A5" s="59" t="inlineStr">
+      <c r="A5" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-005</t>
         </is>
       </c>
-      <c r="B5" s="59" t="inlineStr">
+      <c r="B5" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C5" s="59" t="inlineStr">
+      <c r="C5" s="60" t="inlineStr">
         <is>
           <t>Decide in the FSC how the item reacts when driver awareness reaches zero (driverUnresponsive3 / driverDistracted3 have no disable reaction at BL-004 or BL-005) and implement the decision. DQ-205 (answered) makes this the safe state of SG-010 (ASIL A); the reaction itself is still to be decided</t>
         </is>
       </c>
-      <c r="D5" s="59" t="inlineStr">
+      <c r="D5" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E5" s="59" t="inlineStr">
+      <c r="E5" s="60" t="inlineStr">
         <is>
           <t>decision pending</t>
         </is>
       </c>
-      <c r="F5" s="59" t="inlineStr">
+      <c r="F5" s="60" t="inlineStr">
         <is>
           <t>SFM-025.C1</t>
         </is>
       </c>
-      <c r="G5" s="59" t="inlineStr"/>
-      <c r="H5" s="59" t="inlineStr"/>
-      <c r="I5" s="59" t="inlineStr"/>
+      <c r="G5" s="60" t="inlineStr"/>
+      <c r="H5" s="60" t="inlineStr"/>
+      <c r="I5" s="60" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="59" t="inlineStr">
+      <c r="A6" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-006</t>
         </is>
       </c>
-      <c r="B6" s="59" t="inlineStr">
+      <c r="B6" s="60" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C6" s="59" t="inlineStr">
+      <c r="C6" s="60" t="inlineStr">
         <is>
           <t>Establish on the reference car which stock TSS2 functions (PCS/AEB, FCW) remain available with LionDriver installed and longitudinal control enabled, and verify the stock pre-collision path after installation (PFMEA PFM-014)</t>
         </is>
       </c>
-      <c r="D6" s="59" t="inlineStr">
+      <c r="D6" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E6" s="59" t="inlineStr">
+      <c r="E6" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F6" s="59" t="inlineStr">
+      <c r="F6" s="60" t="inlineStr">
         <is>
           <t>SFM-010.C2
 SFM-033.C1
-SFM-033.C2</t>
-        </is>
-      </c>
-      <c r="G6" s="59" t="inlineStr"/>
-      <c r="H6" s="59" t="inlineStr"/>
-      <c r="I6" s="59" t="inlineStr"/>
+SFM-033.C2
+SFM-036.C2</t>
+        </is>
+      </c>
+      <c r="G6" s="60" t="inlineStr"/>
+      <c r="H6" s="60" t="inlineStr"/>
+      <c r="I6" s="60" t="inlineStr"/>
     </row>
     <row r="7" ht="73.5" customHeight="1">
-      <c r="A7" s="59" t="inlineStr">
+      <c r="A7" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-007</t>
         </is>
       </c>
-      <c r="B7" s="59" t="inlineStr">
+      <c r="B7" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C7" s="59" t="inlineStr">
+      <c r="C7" s="60" t="inlineStr">
         <is>
           <t>Supervise the alert channels: treat loss of ui or soundd liveness, or a stale displayed state, as a fault that escalates (audible fallback, disengagement) instead of continuing silently</t>
         </is>
       </c>
-      <c r="D7" s="59" t="inlineStr">
+      <c r="D7" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E7" s="59" t="inlineStr">
+      <c r="E7" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F7" s="59" t="inlineStr">
+      <c r="F7" s="60" t="inlineStr">
         <is>
           <t>SFM-015.C1
 SFM-026.C1
@@ -16588,76 +16931,76 @@
 SFM-028.C1</t>
         </is>
       </c>
-      <c r="G7" s="59" t="inlineStr"/>
-      <c r="H7" s="59" t="inlineStr"/>
-      <c r="I7" s="59" t="inlineStr"/>
+      <c r="G7" s="60" t="inlineStr"/>
+      <c r="H7" s="60" t="inlineStr"/>
+      <c r="I7" s="60" t="inlineStr"/>
     </row>
     <row r="8" ht="73.5" customHeight="1">
-      <c r="A8" s="59" t="inlineStr">
+      <c r="A8" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-008</t>
         </is>
       </c>
-      <c r="B8" s="59" t="inlineStr">
+      <c r="B8" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C8" s="59" t="inlineStr">
+      <c r="C8" s="60" t="inlineStr">
         <is>
           <t>Allow engagement only when the fingerprint, CarParams and panda safety parameter match the reference configuration AC-001 (refuse fuzzy matches in the reference build); see PFMEA PFM-013</t>
         </is>
       </c>
-      <c r="D8" s="59" t="inlineStr">
+      <c r="D8" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E8" s="59" t="inlineStr">
+      <c r="E8" s="60" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F8" s="59" t="inlineStr">
+      <c r="F8" s="60" t="inlineStr">
         <is>
           <t>SFM-032.C1</t>
         </is>
       </c>
-      <c r="G8" s="59" t="inlineStr"/>
-      <c r="H8" s="59" t="inlineStr"/>
-      <c r="I8" s="59" t="inlineStr">
+      <c r="G8" s="60" t="inlineStr"/>
+      <c r="H8" s="60" t="inlineStr"/>
+      <c r="I8" s="60" t="inlineStr">
         <is>
           <t>BL-005: the reference build is the default (LionDriver #36), the panda accepts only TOYOTA parameter 73 (reference_lock.h) and pandad configures a car mode only on a reference panda (#41). Fuzzy fingerprint matches are still accepted on the host (SFM-032.C1)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="100.5" customHeight="1">
-      <c r="A9" s="59" t="inlineStr">
+      <c r="A9" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-009</t>
         </is>
       </c>
-      <c r="B9" s="59" t="inlineStr">
+      <c r="B9" s="60" t="inlineStr">
         <is>
           <t>prevention</t>
         </is>
       </c>
-      <c r="C9" s="59" t="inlineStr">
+      <c r="C9" s="60" t="inlineStr">
         <is>
           <t>Produce SOTIF / ISO PAS 8800 evidence for the neural-network elements (driving model, lead detection, driver monitoring model) per WP-V-02..04, including fault-induced inputs (corrupted or stale frames)</t>
         </is>
       </c>
-      <c r="D9" s="59" t="inlineStr">
+      <c r="D9" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E9" s="59" t="inlineStr">
+      <c r="E9" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F9" s="59" t="inlineStr">
+      <c r="F9" s="60" t="inlineStr">
         <is>
           <t>SFM-002.C2
 SFM-003.C3
@@ -16668,37 +17011,37 @@
 SFM-022.C2</t>
         </is>
       </c>
-      <c r="G9" s="59" t="inlineStr"/>
-      <c r="H9" s="59" t="inlineStr"/>
-      <c r="I9" s="59" t="inlineStr"/>
+      <c r="G9" s="60" t="inlineStr"/>
+      <c r="H9" s="60" t="inlineStr"/>
+      <c r="I9" s="60" t="inlineStr"/>
     </row>
     <row r="10" ht="73.5" customHeight="1">
-      <c r="A10" s="59" t="inlineStr">
+      <c r="A10" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-010</t>
         </is>
       </c>
-      <c r="B10" s="59" t="inlineStr">
+      <c r="B10" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C10" s="59" t="inlineStr">
+      <c r="C10" s="60" t="inlineStr">
         <is>
           <t>Justify every SOFT_DISABLE reaction and debounce against the FTTI (WP-S-04) and alert at once when the panda withdraws authority while engaged (controlsMismatch debounce)</t>
         </is>
       </c>
-      <c r="D10" s="59" t="inlineStr">
+      <c r="D10" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E10" s="59" t="inlineStr">
+      <c r="E10" s="60" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F10" s="59" t="inlineStr">
+      <c r="F10" s="60" t="inlineStr">
         <is>
           <t>SFM-014.C2
 SFM-015.C2
@@ -16706,286 +17049,317 @@
 SFM-016.C2</t>
         </is>
       </c>
-      <c r="G10" s="59" t="inlineStr"/>
-      <c r="H10" s="59" t="inlineStr"/>
-      <c r="I10" s="59" t="inlineStr">
+      <c r="G10" s="60" t="inlineStr"/>
+      <c r="H10" s="60" t="inlineStr"/>
+      <c r="I10" s="60" t="inlineStr">
         <is>
           <t>controlsMismatch debounce cut from 200 cumulative samples (~2 s) to 2 consecutive samples, at most 0.5 s (change-2026-10-13-host-supervision.md); credited at BL-005 (SFM-015.C2 M 6). FTTI justification of SOFT_DISABLE reactions open</t>
         </is>
       </c>
     </row>
     <row r="11" ht="33" customHeight="1">
-      <c r="A11" s="59" t="inlineStr">
+      <c r="A11" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-011</t>
         </is>
       </c>
-      <c r="B11" s="59" t="inlineStr">
+      <c r="B11" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C11" s="59" t="inlineStr">
+      <c r="C11" s="60" t="inlineStr">
         <is>
           <t>Alert the driver when stock cruise stays engaged while the item is disengaged (cruiseMismatch has no alert at BL-004)</t>
         </is>
       </c>
-      <c r="D11" s="59" t="inlineStr">
+      <c r="D11" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E11" s="60" t="inlineStr">
+      <c r="E11" s="61" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F11" s="59" t="inlineStr">
+      <c r="F11" s="60" t="inlineStr">
         <is>
           <t>SFM-021.C1
 SFM-021.C2</t>
         </is>
       </c>
-      <c r="G11" s="59" t="inlineStr"/>
-      <c r="H11" s="59" t="inlineStr"/>
-      <c r="I11" s="59" t="inlineStr">
+      <c r="G11" s="60" t="inlineStr"/>
+      <c r="H11" s="60" t="inlineStr"/>
+      <c r="I11" s="60" t="inlineStr">
         <is>
           <t>cruiseMismatch now alerts after 1 s (change-2026-10-13-host-supervision.md); see SWF-ACT-034</t>
         </is>
       </c>
     </row>
     <row r="12" ht="73.5" customHeight="1">
-      <c r="A12" s="59" t="inlineStr">
+      <c r="A12" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-012</t>
         </is>
       </c>
-      <c r="B12" s="59" t="inlineStr">
+      <c r="B12" s="60" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C12" s="59" t="inlineStr">
+      <c r="C12" s="60" t="inlineStr">
         <is>
           <t>Measure on the HIL bench and the reference car (WP-V-05) how the panda reacts to over-limit and not-engaged steering and acceleration frames and to driver brake, gas and cancel inputs, and what the EPS and PCM do when frames are refused; re-rate the MSR rows from code-derived to measured timing</t>
         </is>
       </c>
-      <c r="D12" s="59" t="inlineStr"/>
-      <c r="E12" s="59" t="inlineStr">
+      <c r="D12" s="60" t="inlineStr"/>
+      <c r="E12" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F12" s="59" t="inlineStr"/>
-      <c r="G12" s="59" t="inlineStr"/>
-      <c r="H12" s="59" t="inlineStr"/>
-      <c r="I12" s="59" t="inlineStr"/>
+      <c r="F12" s="60" t="inlineStr"/>
+      <c r="G12" s="60" t="inlineStr"/>
+      <c r="H12" s="60" t="inlineStr"/>
+      <c r="I12" s="60" t="inlineStr"/>
     </row>
     <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="59" t="inlineStr">
+      <c r="A13" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-013</t>
         </is>
       </c>
-      <c r="B13" s="59" t="inlineStr">
+      <c r="B13" s="60" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C13" s="59" t="inlineStr">
+      <c r="C13" s="60" t="inlineStr">
         <is>
           <t>Check on the host, within the SG-01 FTTI, that the panda reports controls_allowed false while the item is disengaged (the reverse of the controlsMismatch check, which at BL-005 still covers only engaged with authority withdrawn), with a disable and an alert</t>
         </is>
       </c>
-      <c r="D13" s="59" t="inlineStr"/>
-      <c r="E13" s="59" t="inlineStr">
+      <c r="D13" s="60" t="inlineStr"/>
+      <c r="E13" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F13" s="59" t="inlineStr"/>
-      <c r="G13" s="59" t="inlineStr"/>
-      <c r="H13" s="59" t="inlineStr"/>
-      <c r="I13" s="59" t="inlineStr"/>
+      <c r="F13" s="60" t="inlineStr"/>
+      <c r="G13" s="60" t="inlineStr"/>
+      <c r="H13" s="60" t="inlineStr"/>
+      <c r="I13" s="60" t="inlineStr"/>
     </row>
     <row r="14" ht="46.5" customHeight="1">
-      <c r="A14" s="59" t="inlineStr">
+      <c r="A14" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-014</t>
         </is>
       </c>
-      <c r="B14" s="59" t="inlineStr">
+      <c r="B14" s="60" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C14" s="59" t="inlineStr">
+      <c r="C14" s="60" t="inlineStr">
         <is>
           <t>Specify in the TSC a steering-direction plausibility monitor (commanded torque sign against measured yaw rate and lane-relative lateral motion), or justify its absence against HZ-003</t>
         </is>
       </c>
-      <c r="D14" s="59" t="inlineStr"/>
-      <c r="E14" s="59" t="inlineStr">
+      <c r="D14" s="60" t="inlineStr"/>
+      <c r="E14" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F14" s="59" t="inlineStr"/>
-      <c r="G14" s="59" t="inlineStr"/>
-      <c r="H14" s="59" t="inlineStr"/>
-      <c r="I14" s="59" t="inlineStr"/>
+      <c r="F14" s="60" t="inlineStr"/>
+      <c r="G14" s="60" t="inlineStr"/>
+      <c r="H14" s="60" t="inlineStr"/>
+      <c r="I14" s="60" t="inlineStr"/>
     </row>
     <row r="15" ht="87" customHeight="1">
-      <c r="A15" s="59" t="inlineStr">
+      <c r="A15" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-015</t>
         </is>
       </c>
-      <c r="B15" s="59" t="inlineStr">
+      <c r="B15" s="60" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C15" s="59" t="inlineStr">
+      <c r="C15" s="60" t="inlineStr">
         <is>
           <t>Detect stale commands and inputs within the SG-01 FTTI: command-frame freshness in the MCU with an active zero frame (TSR-408, TSR-109) and frozen-content and age checks on model outputs in controlsd (TSR-602, AIR-17)</t>
         </is>
       </c>
-      <c r="D15" s="59" t="inlineStr"/>
-      <c r="E15" s="59" t="inlineStr">
+      <c r="D15" s="60" t="inlineStr"/>
+      <c r="E15" s="60" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F15" s="59" t="inlineStr"/>
-      <c r="G15" s="59" t="inlineStr"/>
-      <c r="H15" s="59" t="inlineStr"/>
-      <c r="I15" s="59" t="inlineStr">
+      <c r="F15" s="60" t="inlineStr"/>
+      <c r="G15" s="60" t="inlineStr"/>
+      <c r="H15" s="60" t="inlineStr"/>
+      <c r="I15" s="60" t="inlineStr">
         <is>
           <t>BL-005: command-frame arrival in the MCU (TSR-408, 50 ms STEERING_LKA, reference build by default) and input age checks in controlsd (TSR-602) are in. Open: the active zero frame (TSR-109), a frozen-content check on model outputs, and stale data with fresh timestamps (SFM-006.C1 to C3)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="60" customHeight="1">
-      <c r="A16" s="59" t="inlineStr">
+      <c r="A16" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-016</t>
         </is>
       </c>
-      <c r="B16" s="59" t="inlineStr">
+      <c r="B16" s="60" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C16" s="59" t="inlineStr">
+      <c r="C16" s="60" t="inlineStr">
         <is>
           <t>Supervise driver override in the panda: driver steering torque above the override threshold limits or revokes lateral authority within the SG-05 0.2 s budget (TSR-304). Behaviour decided by the lead (DQ-053, option A): back off on override and show a cue</t>
         </is>
       </c>
-      <c r="D16" s="59" t="inlineStr"/>
-      <c r="E16" s="59" t="inlineStr">
+      <c r="D16" s="60" t="inlineStr"/>
+      <c r="E16" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F16" s="59" t="inlineStr"/>
-      <c r="G16" s="59" t="inlineStr"/>
-      <c r="H16" s="59" t="inlineStr"/>
-      <c r="I16" s="59" t="inlineStr"/>
+      <c r="F16" s="60" t="inlineStr"/>
+      <c r="G16" s="60" t="inlineStr"/>
+      <c r="H16" s="60" t="inlineStr"/>
+      <c r="I16" s="60" t="inlineStr"/>
     </row>
     <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="59" t="inlineStr">
+      <c r="A17" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-017</t>
         </is>
       </c>
-      <c r="B17" s="59" t="inlineStr">
+      <c r="B17" s="60" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C17" s="59" t="inlineStr">
+      <c r="C17" s="60" t="inlineStr">
         <is>
           <t>Add WP-S-04 FTTI rows for the warning paths without one (insufficient lateral control, late or insufficient braking warnings, SG-008 unintended engagement, driver monitoring), so these mechanisms can be compared with a time budget</t>
         </is>
       </c>
-      <c r="D17" s="59" t="inlineStr"/>
-      <c r="E17" s="59" t="inlineStr">
+      <c r="D17" s="60" t="inlineStr"/>
+      <c r="E17" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F17" s="59" t="inlineStr"/>
-      <c r="G17" s="59" t="inlineStr"/>
-      <c r="H17" s="59" t="inlineStr"/>
-      <c r="I17" s="59" t="inlineStr"/>
+      <c r="F17" s="60" t="inlineStr"/>
+      <c r="G17" s="60" t="inlineStr"/>
+      <c r="H17" s="60" t="inlineStr"/>
+      <c r="I17" s="60" t="inlineStr"/>
     </row>
     <row r="18" ht="73.5" customHeight="1">
-      <c r="A18" s="59" t="inlineStr">
+      <c r="A18" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-018</t>
         </is>
       </c>
-      <c r="B18" s="59" t="inlineStr">
+      <c r="B18" s="60" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C18" s="59" t="inlineStr">
+      <c r="C18" s="60" t="inlineStr">
         <is>
           <t>Detect silent loss of the actuation path: report forwarded and refused TX frames from the panda, and compare EPS and PCM acceptance (LKA_STATE, ACC status) with the commands, warning within the SG-02/06 1 s budget</t>
         </is>
       </c>
-      <c r="D18" s="59" t="inlineStr"/>
-      <c r="E18" s="59" t="inlineStr">
+      <c r="D18" s="60" t="inlineStr"/>
+      <c r="E18" s="60" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F18" s="59" t="inlineStr"/>
-      <c r="G18" s="59" t="inlineStr"/>
-      <c r="H18" s="59" t="inlineStr"/>
-      <c r="I18" s="59" t="inlineStr">
+      <c r="F18" s="60" t="inlineStr"/>
+      <c r="G18" s="60" t="inlineStr"/>
+      <c r="H18" s="60" t="inlineStr"/>
+      <c r="I18" s="60" t="inlineStr">
         <is>
           <t>BL-005: frames that stop reaching the panda are detected (TSR-408) and alerted within 0.5 s (TSR-621), credited on SFM-005.C2 and SFM-011.C2. Open: frames that reach the panda but are not accepted by the EPS or PCM (SFM-005.C1, SFM-011.C1; TSR-626)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="59" t="inlineStr">
+      <c r="A19" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-019</t>
         </is>
       </c>
-      <c r="B19" s="59" t="inlineStr">
+      <c r="B19" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C19" s="59" t="inlineStr">
+      <c r="C19" s="60" t="inlineStr">
         <is>
           <t>Revoke lateral authority in the panda when it rejects a steering frame while authority is granted, and keep it revoked until a new valid engagement (TSR-108; lead decision DQ-060, option A). At BL-005 the frame is dropped and only the host disengages (pandaTxBlocked)</t>
         </is>
       </c>
-      <c r="D19" s="59" t="inlineStr"/>
-      <c r="E19" s="59" t="inlineStr">
+      <c r="D19" s="60" t="inlineStr"/>
+      <c r="E19" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F19" s="59" t="inlineStr">
+      <c r="F19" s="60" t="inlineStr">
         <is>
           <t>SFM-002.C1
 SFM-002.C2
 SFM-002.C4</t>
         </is>
       </c>
-      <c r="G19" s="59" t="inlineStr"/>
-      <c r="H19" s="59" t="inlineStr"/>
-      <c r="I19" s="59" t="inlineStr"/>
+      <c r="G19" s="60" t="inlineStr"/>
+      <c r="H19" s="60" t="inlineStr"/>
+      <c r="I19" s="60" t="inlineStr"/>
+    </row>
+    <row r="20" ht="73.5" customHeight="1">
+      <c r="A20" s="60" t="inlineStr">
+        <is>
+          <t>SFM-ACT-020</t>
+        </is>
+      </c>
+      <c r="B20" s="60" t="inlineStr">
+        <is>
+          <t>design change</t>
+        </is>
+      </c>
+      <c r="C20" s="60" t="inlineStr">
+        <is>
+          <t>React to a stock PCS event on the longitudinal command (for example a neutral or zero acceleration request, or a longitudinal disable, while stockAeb is set), so stock AEB does not depend on PCM arbitration alone (AOU-04R); or keep today's behaviour and rely on the AOU-04R vehicle test. Lead decision DQ-300</t>
+        </is>
+      </c>
+      <c r="D20" s="60" t="inlineStr"/>
+      <c r="E20" s="60" t="inlineStr">
+        <is>
+          <t>decision pending</t>
+        </is>
+      </c>
+      <c r="F20" s="60" t="inlineStr">
+        <is>
+          <t>SFM-036.C1</t>
+        </is>
+      </c>
+      <c r="G20" s="60" t="inlineStr"/>
+      <c r="H20" s="60" t="inlineStr"/>
+      <c r="I20" s="60" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I19"/>
+  <autoFilter ref="A1:I20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17007,50 +17381,50 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="58" t="inlineStr">
+      <c r="A1" s="59" t="inlineStr">
         <is>
           <t>Element</t>
         </is>
       </c>
-      <c r="B1" s="58" t="inlineStr">
+      <c r="B1" s="59" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="58" t="inlineStr">
+      <c r="C1" s="59" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="D1" s="58" t="inlineStr">
+      <c r="D1" s="59" t="inlineStr">
         <is>
           <t>Parent</t>
         </is>
       </c>
-      <c r="E1" s="58" t="inlineStr">
+      <c r="E1" s="59" t="inlineStr">
         <is>
           <t>Functions</t>
         </is>
       </c>
     </row>
     <row r="2" ht="222" customHeight="1">
-      <c r="A2" s="59" t="inlineStr">
+      <c r="A2" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-001</t>
         </is>
       </c>
-      <c r="B2" s="59" t="inlineStr">
+      <c r="B2" s="60" t="inlineStr">
         <is>
           <t>LionDriver item (L2 ACC + ALC + driver monitoring)</t>
         </is>
       </c>
-      <c r="C2" s="59" t="inlineStr">
+      <c r="C2" s="60" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="D2" s="59" t="inlineStr"/>
-      <c r="E2" s="59" t="inlineStr">
+      <c r="D2" s="60" t="inlineStr"/>
+      <c r="E2" s="60" t="inlineStr">
         <is>
           <t>SFM-FN-001: F1 Lateral control: request steering torque from the EPS to keep the vehicle in its lane while engaged
 SFM-FN-002: F2 Longitudinal control: request acceleration/deceleration to hold set speed and follow leads while engaged
@@ -17064,398 +17438,398 @@
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="59" t="inlineStr">
+      <c r="A3" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="B3" s="59" t="inlineStr">
+      <c r="B3" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    comma 3X device</t>
         </is>
       </c>
-      <c r="C3" s="59" t="inlineStr">
+      <c r="C3" s="60" t="inlineStr">
         <is>
           <t>system</t>
         </is>
       </c>
-      <c r="D3" s="59" t="inlineStr">
+      <c r="D3" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-001</t>
         </is>
       </c>
-      <c r="E3" s="59" t="inlineStr"/>
+      <c r="E3" s="60" t="inlineStr"/>
     </row>
     <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="59" t="inlineStr">
+      <c r="A4" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-003</t>
         </is>
       </c>
-      <c r="B4" s="59" t="inlineStr">
+      <c r="B4" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Integrated panda (CAN interface and safety model)</t>
         </is>
       </c>
-      <c r="C4" s="59" t="inlineStr">
+      <c r="C4" s="60" t="inlineStr">
         <is>
           <t>subsystem</t>
         </is>
       </c>
-      <c r="D4" s="59" t="inlineStr">
+      <c r="D4" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E4" s="59" t="inlineStr"/>
+      <c r="E4" s="60" t="inlineStr"/>
     </row>
     <row r="5" ht="19.5" customHeight="1">
-      <c r="A5" s="59" t="inlineStr">
+      <c r="A5" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-004</t>
         </is>
       </c>
-      <c r="B5" s="59" t="inlineStr">
+      <c r="B5" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Harness (Toyota A connector, harness box, comma power v3)</t>
         </is>
       </c>
-      <c r="C5" s="59" t="inlineStr">
+      <c r="C5" s="60" t="inlineStr">
         <is>
           <t>component</t>
         </is>
       </c>
-      <c r="D5" s="59" t="inlineStr">
+      <c r="D5" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-001</t>
         </is>
       </c>
-      <c r="E5" s="59" t="inlineStr"/>
+      <c r="E5" s="60" t="inlineStr"/>
     </row>
     <row r="6" ht="19.5" customHeight="1">
-      <c r="A6" s="59" t="inlineStr">
+      <c r="A6" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-010</t>
         </is>
       </c>
-      <c r="B6" s="59" t="inlineStr">
+      <c r="B6" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Perception (camerad, modeld)</t>
         </is>
       </c>
-      <c r="C6" s="59" t="inlineStr">
+      <c r="C6" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D6" s="59" t="inlineStr">
+      <c r="D6" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E6" s="59" t="inlineStr"/>
+      <c r="E6" s="60" t="inlineStr"/>
     </row>
     <row r="7" ht="19.5" customHeight="1">
-      <c r="A7" s="59" t="inlineStr">
+      <c r="A7" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-011</t>
         </is>
       </c>
-      <c r="B7" s="59" t="inlineStr">
+      <c r="B7" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Localization and calibration (locationd, calibrationd, paramsd, torqued)</t>
         </is>
       </c>
-      <c r="C7" s="59" t="inlineStr">
+      <c r="C7" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D7" s="59" t="inlineStr">
+      <c r="D7" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E7" s="59" t="inlineStr"/>
+      <c r="E7" s="60" t="inlineStr"/>
     </row>
     <row r="8" ht="19.5" customHeight="1">
-      <c r="A8" s="59" t="inlineStr">
+      <c r="A8" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-012</t>
         </is>
       </c>
-      <c r="B8" s="59" t="inlineStr">
+      <c r="B8" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Planning (plannerd, radard)</t>
         </is>
       </c>
-      <c r="C8" s="59" t="inlineStr">
+      <c r="C8" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D8" s="59" t="inlineStr">
+      <c r="D8" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E8" s="59" t="inlineStr"/>
+      <c r="E8" s="60" t="inlineStr"/>
     </row>
     <row r="9" ht="19.5" customHeight="1">
-      <c r="A9" s="59" t="inlineStr">
+      <c r="A9" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-013</t>
         </is>
       </c>
-      <c r="B9" s="59" t="inlineStr">
+      <c r="B9" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Control (controlsd, lateral/longitudinal controllers)</t>
         </is>
       </c>
-      <c r="C9" s="59" t="inlineStr">
+      <c r="C9" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D9" s="59" t="inlineStr">
+      <c r="D9" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E9" s="59" t="inlineStr"/>
+      <c r="E9" s="60" t="inlineStr"/>
     </row>
     <row r="10" ht="19.5" customHeight="1">
-      <c r="A10" s="59" t="inlineStr">
+      <c r="A10" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-014</t>
         </is>
       </c>
-      <c r="B10" s="59" t="inlineStr">
+      <c r="B10" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Supervision (selfdrived state machine, events, alert manager)</t>
         </is>
       </c>
-      <c r="C10" s="59" t="inlineStr">
+      <c r="C10" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D10" s="59" t="inlineStr">
+      <c r="D10" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E10" s="59" t="inlineStr"/>
+      <c r="E10" s="60" t="inlineStr"/>
     </row>
     <row r="11" ht="19.5" customHeight="1">
-      <c r="A11" s="59" t="inlineStr">
+      <c r="A11" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-015</t>
         </is>
       </c>
-      <c r="B11" s="59" t="inlineStr">
+      <c r="B11" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Driver monitoring (dmonitoringmodeld, dmonitoringd)</t>
         </is>
       </c>
-      <c r="C11" s="59" t="inlineStr">
+      <c r="C11" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D11" s="59" t="inlineStr">
+      <c r="D11" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E11" s="59" t="inlineStr"/>
+      <c r="E11" s="60" t="inlineStr"/>
     </row>
     <row r="12" ht="19.5" customHeight="1">
-      <c r="A12" s="59" t="inlineStr">
+      <c r="A12" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-016</t>
         </is>
       </c>
-      <c r="B12" s="59" t="inlineStr">
+      <c r="B12" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Car interface (card, car_events, opendbc Toyota port)</t>
         </is>
       </c>
-      <c r="C12" s="59" t="inlineStr">
+      <c r="C12" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D12" s="59" t="inlineStr">
+      <c r="D12" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E12" s="59" t="inlineStr"/>
+      <c r="E12" s="60" t="inlineStr"/>
     </row>
     <row r="13" ht="19.5" customHeight="1">
-      <c r="A13" s="59" t="inlineStr">
+      <c r="A13" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-017</t>
         </is>
       </c>
-      <c r="B13" s="59" t="inlineStr">
+      <c r="B13" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Panda daemon (pandad)</t>
         </is>
       </c>
-      <c r="C13" s="59" t="inlineStr">
+      <c r="C13" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D13" s="59" t="inlineStr">
+      <c r="D13" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E13" s="59" t="inlineStr"/>
+      <c r="E13" s="60" t="inlineStr"/>
     </row>
     <row r="14" ht="19.5" customHeight="1">
-      <c r="A14" s="59" t="inlineStr">
+      <c r="A14" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-018</t>
         </is>
       </c>
-      <c r="B14" s="59" t="inlineStr">
+      <c r="B14" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        HMI (ui, soundd)</t>
         </is>
       </c>
-      <c r="C14" s="59" t="inlineStr">
+      <c r="C14" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D14" s="59" t="inlineStr">
+      <c r="D14" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E14" s="59" t="inlineStr"/>
+      <c r="E14" s="60" t="inlineStr"/>
     </row>
     <row r="15" ht="19.5" customHeight="1">
-      <c r="A15" s="59" t="inlineStr">
+      <c r="A15" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-019</t>
         </is>
       </c>
-      <c r="B15" s="59" t="inlineStr">
+      <c r="B15" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Platform (manager, messaging, hardwared, OS)</t>
         </is>
       </c>
-      <c r="C15" s="59" t="inlineStr">
+      <c r="C15" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D15" s="59" t="inlineStr">
+      <c r="D15" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E15" s="59" t="inlineStr"/>
+      <c r="E15" s="60" t="inlineStr"/>
     </row>
     <row r="16" ht="19.5" customHeight="1">
-      <c r="A16" s="59" t="inlineStr">
+      <c r="A16" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-030</t>
         </is>
       </c>
-      <c r="B16" s="59" t="inlineStr">
+      <c r="B16" s="60" t="inlineStr">
         <is>
           <t>Toyota EPS</t>
         </is>
       </c>
-      <c r="C16" s="59" t="inlineStr">
+      <c r="C16" s="60" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D16" s="59" t="inlineStr"/>
-      <c r="E16" s="59" t="inlineStr"/>
+      <c r="D16" s="60" t="inlineStr"/>
+      <c r="E16" s="60" t="inlineStr"/>
     </row>
     <row r="17" ht="19.5" customHeight="1">
-      <c r="A17" s="59" t="inlineStr">
+      <c r="A17" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-031</t>
         </is>
       </c>
-      <c r="B17" s="59" t="inlineStr">
+      <c r="B17" s="60" t="inlineStr">
         <is>
           <t>Toyota powertrain and brake control (receives ACC acceleration requests)</t>
         </is>
       </c>
-      <c r="C17" s="59" t="inlineStr">
+      <c r="C17" s="60" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D17" s="59" t="inlineStr"/>
-      <c r="E17" s="59" t="inlineStr"/>
+      <c r="D17" s="60" t="inlineStr"/>
+      <c r="E17" s="60" t="inlineStr"/>
     </row>
     <row r="18" ht="19.5" customHeight="1">
-      <c r="A18" s="59" t="inlineStr">
+      <c r="A18" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-032</t>
         </is>
       </c>
-      <c r="B18" s="59" t="inlineStr">
+      <c r="B18" s="60" t="inlineStr">
         <is>
           <t>Toyota stock ADAS camera (TSS2)</t>
         </is>
       </c>
-      <c r="C18" s="59" t="inlineStr">
+      <c r="C18" s="60" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D18" s="59" t="inlineStr"/>
-      <c r="E18" s="59" t="inlineStr"/>
+      <c r="D18" s="60" t="inlineStr"/>
+      <c r="E18" s="60" t="inlineStr"/>
     </row>
     <row r="19" ht="19.5" customHeight="1">
-      <c r="A19" s="59" t="inlineStr">
+      <c r="A19" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-033</t>
         </is>
       </c>
-      <c r="B19" s="59" t="inlineStr">
+      <c r="B19" s="60" t="inlineStr">
         <is>
           <t>Vehicle CAN buses and 12 V supply</t>
         </is>
       </c>
-      <c r="C19" s="59" t="inlineStr">
+      <c r="C19" s="60" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D19" s="59" t="inlineStr"/>
-      <c r="E19" s="59" t="inlineStr"/>
+      <c r="D19" s="60" t="inlineStr"/>
+      <c r="E19" s="60" t="inlineStr"/>
     </row>
     <row r="20" ht="19.5" customHeight="1">
-      <c r="A20" s="59" t="inlineStr">
+      <c r="A20" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-034</t>
         </is>
       </c>
-      <c r="B20" s="59" t="inlineStr">
+      <c r="B20" s="60" t="inlineStr">
         <is>
           <t>Driver</t>
         </is>
       </c>
-      <c r="C20" s="59" t="inlineStr">
+      <c r="C20" s="60" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D20" s="59" t="inlineStr"/>
-      <c r="E20" s="59" t="inlineStr"/>
+      <c r="D20" s="60" t="inlineStr"/>
+      <c r="E20" s="60" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E20"/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MSR" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$83</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Worksheet'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Structure'!$A$1:$E$20</definedName>
@@ -817,7 +817,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.11 · draft</t>
+          <t>0.12 · draft</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17">
@@ -1096,7 +1096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S82"/>
+  <dimension ref="A1:S83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2759,7 +2759,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -2868,7 +2868,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -3120,7 +3120,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -3453,7 +3453,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -3589,7 +3589,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -3823,7 +3823,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -4901,7 +4901,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -5459,7 +5459,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -5550,7 +5550,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -6054,7 +6054,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -6522,7 +6522,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -6755,7 +6755,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -7118,7 +7118,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -7591,7 +7591,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -8634,7 +8634,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -9281,7 +9281,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -9645,7 +9645,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -10009,7 +10009,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -10260,7 +10260,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -11079,7 +11079,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -12354,7 +12354,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -12697,7 +12697,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -13161,7 +13161,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -14486,7 +14486,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
           </r>
         </is>
       </c>
@@ -14945,7 +14945,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Stock ADAS camera messages blocked or replaced by the harness relay</t>
+            <t>Stock ADAS camera messages blocked or replaced by the harness-box intercept</t>
           </r>
         </is>
       </c>
@@ -14993,7 +14993,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Relay intercepts stock camera messages the vehicle needs for AEB</t>
+            <t>The intercept routes the stock camera messages the vehicle needs for AEB through the panda</t>
           </r>
         </is>
       </c>
@@ -15005,7 +15005,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Forwarding keeps stock pre-collision messages (0x283, 0x344) passing the relay (SWF-011); which TSS2 functions remain with openpilot longitudinal is not established</t>
+            <t>• Forwarding keeps stock pre-collision messages (0x283, 0x344) passing the intercept (SWF-011); which TSS2 functions remain with openpilot longitudinal is not established</t>
           </r>
           <r>
             <rPr>
@@ -15074,18 +15074,18 @@
       <c r="S79" s="37" t="inlineStr"/>
     </row>
     <row r="80" ht="100.5" customHeight="1">
-      <c r="A80" s="39" t="n"/>
-      <c r="B80" s="39" t="n"/>
-      <c r="C80" s="39" t="n"/>
-      <c r="D80" s="39" t="n"/>
-      <c r="E80" s="39" t="n"/>
-      <c r="F80" s="39" t="n"/>
-      <c r="G80" s="40" t="inlineStr">
+      <c r="A80" s="38" t="n"/>
+      <c r="B80" s="38" t="n"/>
+      <c r="C80" s="38" t="n"/>
+      <c r="D80" s="38" t="n"/>
+      <c r="E80" s="38" t="n"/>
+      <c r="F80" s="38" t="n"/>
+      <c r="G80" s="33" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="H80" s="41" t="inlineStr">
+      <c r="H80" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15106,7 +15106,7 @@
           </r>
         </is>
       </c>
-      <c r="I80" s="41" t="inlineStr">
+      <c r="I80" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15127,10 +15127,10 @@
           </r>
         </is>
       </c>
-      <c r="J80" s="42" t="n">
+      <c r="J80" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="K80" s="41" t="inlineStr">
+      <c r="K80" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15151,15 +15151,15 @@
           </r>
         </is>
       </c>
-      <c r="L80" s="42" t="n">
+      <c r="L80" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="M80" s="44" t="inlineStr">
+      <c r="M80" s="36" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N80" s="41" t="inlineStr">
+      <c r="N80" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15181,18 +15181,103 @@
           </r>
         </is>
       </c>
-      <c r="O80" s="48" t="inlineStr">
+      <c r="O80" s="47" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P80" s="40" t="inlineStr"/>
-      <c r="Q80" s="40" t="inlineStr"/>
-      <c r="R80" s="45" t="inlineStr"/>
-      <c r="S80" s="45" t="inlineStr"/>
-    </row>
-    <row r="81" ht="87" customHeight="1">
-      <c r="A81" s="30" t="inlineStr">
+      <c r="P80" s="33" t="inlineStr"/>
+      <c r="Q80" s="33" t="inlineStr"/>
+      <c r="R80" s="37" t="inlineStr"/>
+      <c r="S80" s="37" t="inlineStr"/>
+    </row>
+    <row r="81" ht="141" customHeight="1">
+      <c r="A81" s="39" t="n"/>
+      <c r="B81" s="39" t="n"/>
+      <c r="C81" s="39" t="n"/>
+      <c r="D81" s="39" t="n"/>
+      <c r="E81" s="39" t="n"/>
+      <c r="F81" s="39" t="n"/>
+      <c r="G81" s="40" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="H81" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The harness box loses its supply (ignition branch or D1 open without comma power, VIN shorted), or a switch channel opens, so the stock camera path through the unpowered or open DG419LE switches is cut (RR-2026-010)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: DFM-020</t>
+          </r>
+        </is>
+      </c>
+      <c r="I81" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Consumer-grade harness box without automotive qualification data available to LionDriver; rated in the DFMEA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/08-analyses/fmea/analyses/dfmea.yaml</t>
+          </r>
+        </is>
+      </c>
+      <c r="J81" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="K81" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• As rated in the DFMEA: no pre-release test of this hardware fault</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/08-analyses/fmea/analyses/dfmea.yaml</t>
+          </r>
+        </is>
+      </c>
+      <c r="L81" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="M81" s="44" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N81" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15201,6 +15286,39 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
+            <t xml:space="preserve">SFM-ACT-003 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+          </r>
+        </is>
+      </c>
+      <c r="O81" s="48" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P81" s="40" t="inlineStr"/>
+      <c r="Q81" s="40" t="inlineStr"/>
+      <c r="R81" s="45" t="inlineStr"/>
+      <c r="S81" s="45" t="inlineStr"/>
+    </row>
+    <row r="82" ht="87" customHeight="1">
+      <c r="A82" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
             <t xml:space="preserve">SFM-SE-001
 </t>
           </r>
@@ -15214,7 +15332,7 @@
           </r>
         </is>
       </c>
-      <c r="B81" s="30" t="inlineStr">
+      <c r="B82" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15236,7 +15354,7 @@
           </r>
         </is>
       </c>
-      <c r="C81" s="30" t="inlineStr">
+      <c r="C82" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15357,21 +15475,21 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Relay stuck or intermittent; stock camera and item both on bus, or neither</t>
-          </r>
-        </is>
-      </c>
-      <c r="D81" s="31" t="inlineStr">
+            <t>Intercept switch stuck or intermittent: in intercept when released (camera cut off from the car), or in pass-through when driven (stock camera and item both on the bus)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D82" s="31" t="inlineStr">
         <is>
           <t>HZ-011
 HZ-002
 HZ-006</t>
         </is>
       </c>
-      <c r="E81" s="32" t="n">
+      <c r="E82" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="F81" s="30" t="inlineStr">
+      <c r="F82" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15390,24 +15508,24 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Harness relay fault</t>
-          </r>
-        </is>
-      </c>
-      <c r="G81" s="33" t="inlineStr">
+            <t>Harness-box intercept switch stuck or in the wrong position</t>
+          </r>
+        </is>
+      </c>
+      <c r="G82" s="33" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H81" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Relay contact wear or connector fault</t>
+      <c r="H82" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Switch U1 or U2 stuck in intercept, its IN input damaged high or driven high, its pull-down R2/R3 open, or the switches damaged by box supply transients (DG419LE, RR-2026-010)</t>
           </r>
           <r>
             <rPr>
@@ -15420,7 +15538,7 @@
           </r>
         </is>
       </c>
-      <c r="I81" s="34" t="inlineStr">
+      <c r="I82" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15441,10 +15559,10 @@
           </r>
         </is>
       </c>
-      <c r="J81" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="K81" s="34" t="inlineStr">
+      <c r="J82" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="K82" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15465,15 +15583,15 @@
           </r>
         </is>
       </c>
-      <c r="L81" s="46" t="n">
+      <c r="L82" s="46" t="n">
         <v>10</v>
       </c>
-      <c r="M81" s="36" t="inlineStr">
+      <c r="M82" s="36" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N81" s="34" t="inlineStr">
+      <c r="N82" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15490,37 +15608,37 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Hardware fault rated in the DFMEA (DFM-010 O3 D10, DFM-011 O3 D9); this row inherits that rating; relayMalfunction (SWF-012) is the in-field mechanism</t>
-          </r>
-        </is>
-      </c>
-      <c r="O81" s="34" t="inlineStr"/>
-      <c r="P81" s="33" t="inlineStr"/>
-      <c r="Q81" s="33" t="inlineStr"/>
-      <c r="R81" s="37" t="inlineStr"/>
-      <c r="S81" s="37" t="inlineStr"/>
-    </row>
-    <row r="82" ht="87" customHeight="1">
-      <c r="A82" s="39" t="n"/>
-      <c r="B82" s="39" t="n"/>
-      <c r="C82" s="39" t="n"/>
-      <c r="D82" s="39" t="n"/>
-      <c r="E82" s="39" t="n"/>
-      <c r="F82" s="39" t="n"/>
-      <c r="G82" s="40" t="inlineStr">
+            <t>Hardware fault rated in the DFMEA (DFM-010.C1-C3 O3 D10, DFM-010.C4 O4 D10); this row inherits the worst. relayMalfunction (SWF-012) is the in-field mechanism; there is no switch-state feedback (RR-2026-010)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O82" s="34" t="inlineStr"/>
+      <c r="P82" s="33" t="inlineStr"/>
+      <c r="Q82" s="33" t="inlineStr"/>
+      <c r="R82" s="37" t="inlineStr"/>
+      <c r="S82" s="37" t="inlineStr"/>
+    </row>
+    <row r="83" ht="102" customHeight="1">
+      <c r="A83" s="39" t="n"/>
+      <c r="B83" s="39" t="n"/>
+      <c r="C83" s="39" t="n"/>
+      <c r="D83" s="39" t="n"/>
+      <c r="E83" s="39" t="n"/>
+      <c r="F83" s="39" t="n"/>
+      <c r="G83" s="40" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="H82" s="41" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Relay drive output fault on panda</t>
+      <c r="H83" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Switch stuck in pass-through, or the SBU1 drive lost, held low or too low to change the switch over (5 V drive against VL = VIN)</t>
           </r>
           <r>
             <rPr>
@@ -15533,7 +15651,7 @@
           </r>
         </is>
       </c>
-      <c r="I82" s="41" t="inlineStr">
+      <c r="I83" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15554,10 +15672,10 @@
           </r>
         </is>
       </c>
-      <c r="J82" s="42" t="n">
+      <c r="J83" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="K82" s="41" t="inlineStr">
+      <c r="K83" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15578,15 +15696,15 @@
           </r>
         </is>
       </c>
-      <c r="L82" s="43" t="n">
-        <v>10</v>
-      </c>
-      <c r="M82" s="44" t="inlineStr">
+      <c r="L83" s="43" t="n">
+        <v>9</v>
+      </c>
+      <c r="M83" s="44" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N82" s="41" t="inlineStr">
+      <c r="N83" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15603,24 +15721,22 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Hardware fault rated in the DFMEA (DFM-011, DFM-010); this row inherits that rating</t>
-          </r>
-        </is>
-      </c>
-      <c r="O82" s="41" t="inlineStr"/>
-      <c r="P82" s="40" t="inlineStr"/>
-      <c r="Q82" s="40" t="inlineStr"/>
-      <c r="R82" s="45" t="inlineStr"/>
-      <c r="S82" s="45" t="inlineStr"/>
+            <t>Hardware fault rated in the DFMEA (DFM-011.C1 O3 D9, DFM-011.C2 O2 D9); this row inherits the worst</t>
+          </r>
+        </is>
+      </c>
+      <c r="O83" s="41" t="inlineStr"/>
+      <c r="P83" s="40" t="inlineStr"/>
+      <c r="Q83" s="40" t="inlineStr"/>
+      <c r="R83" s="45" t="inlineStr"/>
+      <c r="S83" s="45" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S82"/>
+  <autoFilter ref="A2:S83"/>
   <mergeCells count="172">
     <mergeCell ref="F17:F19"/>
     <mergeCell ref="E39:E40"/>
-    <mergeCell ref="C79:C80"/>
     <mergeCell ref="A57:A59"/>
-    <mergeCell ref="E79:E80"/>
     <mergeCell ref="A20:A22"/>
     <mergeCell ref="F25:F28"/>
     <mergeCell ref="A51:A52"/>
@@ -15630,7 +15746,6 @@
     <mergeCell ref="C32:C34"/>
     <mergeCell ref="E32:E34"/>
     <mergeCell ref="B23:B24"/>
-    <mergeCell ref="F79:F80"/>
     <mergeCell ref="B20:B22"/>
     <mergeCell ref="D20:D22"/>
     <mergeCell ref="E3:E5"/>
@@ -15639,7 +15754,6 @@
     <mergeCell ref="F29:F31"/>
     <mergeCell ref="F47:F48"/>
     <mergeCell ref="E49:E50"/>
-    <mergeCell ref="F81:F82"/>
     <mergeCell ref="A71:A74"/>
     <mergeCell ref="B37:B38"/>
     <mergeCell ref="C71:C74"/>
@@ -15655,6 +15769,7 @@
     <mergeCell ref="E44:E46"/>
     <mergeCell ref="B57:B59"/>
     <mergeCell ref="C69:C70"/>
+    <mergeCell ref="F79:F81"/>
     <mergeCell ref="D57:D59"/>
     <mergeCell ref="N1:Q1"/>
     <mergeCell ref="D41:D43"/>
@@ -15663,7 +15778,6 @@
     <mergeCell ref="B35:B36"/>
     <mergeCell ref="F10:F13"/>
     <mergeCell ref="D49:D50"/>
-    <mergeCell ref="A79:A80"/>
     <mergeCell ref="E55:E56"/>
     <mergeCell ref="A32:A34"/>
     <mergeCell ref="A14:A16"/>
@@ -15687,37 +15801,38 @@
     <mergeCell ref="D37:D38"/>
     <mergeCell ref="A23:A24"/>
     <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C82:C83"/>
     <mergeCell ref="D55:D56"/>
+    <mergeCell ref="C79:C81"/>
     <mergeCell ref="I1:M1"/>
+    <mergeCell ref="E79:E81"/>
     <mergeCell ref="D39:D40"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="D79:D80"/>
-    <mergeCell ref="E81:E82"/>
     <mergeCell ref="A39:A40"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="B14:B16"/>
     <mergeCell ref="D23:D24"/>
     <mergeCell ref="B29:B31"/>
     <mergeCell ref="A49:A50"/>
-    <mergeCell ref="B81:B82"/>
     <mergeCell ref="D32:D34"/>
     <mergeCell ref="C49:C50"/>
-    <mergeCell ref="D81:D82"/>
     <mergeCell ref="F32:F34"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="E67:E68"/>
     <mergeCell ref="A17:A19"/>
     <mergeCell ref="E51:E52"/>
     <mergeCell ref="C17:C19"/>
+    <mergeCell ref="E82:E83"/>
     <mergeCell ref="E60:E61"/>
     <mergeCell ref="E69:E70"/>
     <mergeCell ref="A25:A28"/>
     <mergeCell ref="B71:B74"/>
+    <mergeCell ref="B82:B83"/>
     <mergeCell ref="A44:A46"/>
     <mergeCell ref="F51:F52"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A64:A66"/>
+    <mergeCell ref="A79:A81"/>
     <mergeCell ref="B41:B43"/>
     <mergeCell ref="F23:F24"/>
     <mergeCell ref="B10:B13"/>
@@ -15764,20 +15879,22 @@
     <mergeCell ref="C25:C28"/>
     <mergeCell ref="A55:A56"/>
     <mergeCell ref="C55:C56"/>
+    <mergeCell ref="B79:B81"/>
     <mergeCell ref="B32:B34"/>
+    <mergeCell ref="D79:D81"/>
     <mergeCell ref="C67:C68"/>
     <mergeCell ref="E17:E19"/>
     <mergeCell ref="D71:D74"/>
     <mergeCell ref="E75:E76"/>
     <mergeCell ref="A47:A48"/>
-    <mergeCell ref="A81:A82"/>
     <mergeCell ref="D17:D19"/>
-    <mergeCell ref="C81:C82"/>
+    <mergeCell ref="F82:F83"/>
     <mergeCell ref="D67:D68"/>
     <mergeCell ref="F67:F68"/>
     <mergeCell ref="B51:B52"/>
     <mergeCell ref="E47:E48"/>
     <mergeCell ref="D51:D52"/>
+    <mergeCell ref="D82:D83"/>
     <mergeCell ref="D60:D61"/>
     <mergeCell ref="F60:F61"/>
     <mergeCell ref="C37:C38"/>
@@ -15786,11 +15903,12 @@
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="F69:F70"/>
     <mergeCell ref="B25:B28"/>
+    <mergeCell ref="A82:A83"/>
     <mergeCell ref="D35:D36"/>
     <mergeCell ref="C6:C9"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
+    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
       <formula1>"Agree,Re-rate,Reject,Question"</formula1>
     </dataValidation>
   </dataValidations>
@@ -15798,7 +15916,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.11 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.12 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -15960,7 +16078,7 @@
       <c r="H3" s="59" t="inlineStr"/>
       <c r="I3" s="59" t="inlineStr"/>
     </row>
-    <row r="4" ht="330" customHeight="1">
+    <row r="4" ht="343.5" customHeight="1">
       <c r="A4" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-003</t>
@@ -15973,7 +16091,7 @@
       </c>
       <c r="C4" s="59" t="inlineStr">
         <is>
-          <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, relay and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+          <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
         </is>
       </c>
       <c r="D4" s="59" t="inlineStr">
@@ -16011,7 +16129,8 @@
 SFM-026.C2
 SFM-027.C1
 SFM-028.C2
-SFM-031.C1</t>
+SFM-031.C1
+SFM-033.C3</t>
         </is>
       </c>
       <c r="G4" s="59" t="inlineStr"/>
@@ -21019,10 +21138,10 @@
       <c r="O64" s="37" t="inlineStr"/>
       <c r="P64" s="37" t="inlineStr"/>
     </row>
-    <row r="65" ht="33" customHeight="1">
+    <row r="65" ht="73.5" customHeight="1">
       <c r="A65" s="34" t="inlineStr">
         <is>
-          <t>SFM-034 · Harness relay fault</t>
+          <t>SFM-034 · Harness-box intercept switch stuck or in the wrong position</t>
         </is>
       </c>
       <c r="B65" s="35" t="n">
@@ -21035,7 +21154,7 @@
       </c>
       <c r="D65" s="34" t="inlineStr">
         <is>
-          <t>Relay contact wear or connector fault</t>
+          <t>Switch U1 or U2 stuck in intercept, its IN input damaged high or driven high, its pull-down R2/R3 open, or the switches damaged by box supply transients (DG419LE, RR-2026-010)</t>
         </is>
       </c>
       <c r="E65" s="62" t="inlineStr">
@@ -21055,10 +21174,10 @@
       <c r="O65" s="37" t="inlineStr"/>
       <c r="P65" s="37" t="inlineStr"/>
     </row>
-    <row r="66" ht="33" customHeight="1">
+    <row r="66" ht="60" customHeight="1">
       <c r="A66" s="34" t="inlineStr">
         <is>
-          <t>SFM-034 · Harness relay fault</t>
+          <t>SFM-034 · Harness-box intercept switch stuck or in the wrong position</t>
         </is>
       </c>
       <c r="B66" s="35" t="n">
@@ -21071,7 +21190,7 @@
       </c>
       <c r="D66" s="34" t="inlineStr">
         <is>
-          <t>Relay drive output fault on panda</t>
+          <t>Switch stuck in pass-through, or the SBU1 drive lost, held low or too low to change the switch over (5 V drive against VL = VIN)</t>
         </is>
       </c>
       <c r="E66" s="62" t="inlineStr">
@@ -21105,7 +21224,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.11 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.12 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MSR" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$87</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Worksheet'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Structure'!$A$1:$E$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'MSR'!$A$2:$P$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'MSR'!$A$2:$P$70</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'MSR'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -261,7 +261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -398,6 +398,9 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -817,7 +820,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.12 · draft</t>
+          <t>0.13 · draft</t>
         </is>
       </c>
     </row>
@@ -895,7 +898,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -905,7 +908,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16">
@@ -915,7 +918,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17">
@@ -946,7 +949,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>18 (17)</t>
+          <t>19 (18)</t>
         </is>
       </c>
     </row>
@@ -958,7 +961,7 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>60 rated, 4 exempt; MSR AP H 60, M 0, L 0 (provisional table)</t>
+          <t>64 rated, 4 exempt; MSR AP H 64, M 0, L 0 (provisional table)</t>
         </is>
       </c>
     </row>
@@ -970,7 +973,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>1–4: 0 · 5–6: 15 · 7–8: 16 · 9–10: 29 (see sheet MSR)</t>
+          <t>1–4: 0 · 5–6: 16 · 7–8: 17 · 9–10: 31 (see sheet MSR)</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S83"/>
+  <dimension ref="A1:S87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -15731,18 +15734,732 @@
       <c r="R83" s="45" t="inlineStr"/>
       <c r="S83" s="45" t="inlineStr"/>
     </row>
+    <row r="84" ht="100.5" customHeight="1">
+      <c r="A84" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-SE-001
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>LionDriver item (L2 ACC + ALC + driver monitoring)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B84" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-FN-008
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>F8 Stock function preservation: keep stock vehicle safety functions not replaced by the item available</t>
+          </r>
+        </is>
+      </c>
+      <c r="C84" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Stock AEB/FCW degraded while the driver relies on it</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-006: PCS braking triggered by a frame from the item</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Stock PCS warning or braking suppressed, altered or triggered by the item</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>A PCS-relevant frame from the SoC (0x344 PRE_COLLISION_2, 0x411 PCS_HUD, a DSU-only ID, or 0x283 PRE_COLLISION with a non-zero payload) reaches the car bus</t>
+          </r>
+        </is>
+      </c>
+      <c r="D84" s="31" t="inlineStr">
+        <is>
+          <t>HZ-011
+HZ-006</t>
+        </is>
+      </c>
+      <c r="E84" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F84" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-035 · unintended
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Item sends a frame that alters the stock pre-collision function</t>
+          </r>
+        </is>
+      </c>
+      <c r="G84" s="33" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H84" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Host code (car interface, pandad) emits a PCS-relevant ID or a non-zero PRE_COLLISION payload (QM fault)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I84" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream opendbc Toyota port; no carcontroller path builds 0x344, 0x411 or the DSU IDs for the reference car, and 0x283 is sent with a zero payload only; no LionDriver requirements, no field-exposure credit</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   opendbc_repo/opendbc/car/toyota</t>
+          </r>
+        </is>
+      </c>
+      <c r="J84" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="K84" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• process_replay over the CI route corpus compares sendcan with the reference commit; a regression check, not designed or proven for this cause</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/test/process_replay/test_processes.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L84" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="M84" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N84" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Rationale  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The panda refuses these frames on every frame (SFM-035.C3 is the case where that check fails); no separate action. A compromised SoC sending them on purpose is a TARA topic, out of scope here</t>
+          </r>
+        </is>
+      </c>
+      <c r="O84" s="34" t="inlineStr"/>
+      <c r="P84" s="33" t="inlineStr"/>
+      <c r="Q84" s="33" t="inlineStr"/>
+      <c r="R84" s="37" t="inlineStr"/>
+      <c r="S84" s="37" t="inlineStr"/>
+    </row>
+    <row r="85" ht="100.5" customHeight="1">
+      <c r="A85" s="39" t="n"/>
+      <c r="B85" s="39" t="n"/>
+      <c r="C85" s="39" t="n"/>
+      <c r="D85" s="39" t="n"/>
+      <c r="E85" s="39" t="n"/>
+      <c r="F85" s="39" t="n"/>
+      <c r="G85" s="40" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="H85" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The TX whitelist or the PRE_COLLISION content check lets a PCS-relevant frame through (table change, or a build that is not the reference build, where 0x411 is allowed by design)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I85" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Panda safety code: MISRA C:2012, 100% line coverage, review; reduced whitelist (TSR-705); reference build the default since BL-005 (pandad requires it, TSR-514/619)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   opendbc_repo/opendbc/safety/modes/toyota.h</t>
+          </r>
+        </is>
+      </c>
+      <c r="J85" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="K85" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• opendbc safety suite with 100% line coverage and mutation tests in both variants, run by CI on every change (proven, early, test-to-fail)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   opendbc_repo/opendbc/safety/tests/test_toyota.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L85" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="M85" s="44" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N85" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Rationale  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The whitelist is a static table pinned by mutation-proven tests in both variants; the non-reference variant keeps 0x411 by design and cannot configure a car mode with pandad at BL-005. No SW FMEA mode covers the table yet (FTA BE-7.07, for the SW FMEA)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O85" s="41" t="inlineStr"/>
+      <c r="P85" s="40" t="inlineStr"/>
+      <c r="Q85" s="40" t="inlineStr"/>
+      <c r="R85" s="45" t="inlineStr"/>
+      <c r="S85" s="45" t="inlineStr"/>
+    </row>
+    <row r="86" ht="127.5" customHeight="1">
+      <c r="A86" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-SE-001
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>LionDriver item (L2 ACC + ALC + driver monitoring)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B86" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-FN-008
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>F8 Stock function preservation: keep stock vehicle safety functions not replaced by the item available</t>
+          </r>
+        </is>
+      </c>
+      <c r="C86" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Stock AEB deceleration reduced or delayed if the PCM arbitrates otherwise</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>PCS braking depends on the PCM giving it priority over the item's request (AOU-04R, unverified)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>ACC_CONTROL keeps carrying the planner's acceleration request while the stock camera reports a PCS braking event</t>
+          </r>
+        </is>
+      </c>
+      <c r="D86" s="31" t="inlineStr">
+        <is>
+          <t>HZ-011</t>
+        </is>
+      </c>
+      <c r="E86" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F86" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-036 · unintended
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Item keeps requesting acceleration while stock PCS brakes</t>
+          </r>
+        </is>
+      </c>
+      <c r="G86" s="33" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H86" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The item has no reaction to a stock PCS event on its longitudinal command; controlsd keeps requesting the planner's acceleration (design gap, FTA BE-7.13)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I86" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• None in the item: FSR-07.04 places PCS priority in the PCM as an external measure (AOU-04R)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/02-concept/WP-C-04-functional-safety-concept.md</t>
+          </r>
+        </is>
+      </c>
+      <c r="J86" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="K86" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No pre-release test targets this cause</t>
+          </r>
+        </is>
+      </c>
+      <c r="L86" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="M86" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N86" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-ACT-020 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>React to a stock PCS event on the longitudinal command (for example a neutral or zero acceleration request, or a longitudinal disable, while stockAeb is set), so stock AEB does not depend on PCM arbitration alone (AOU-04R); or keep today's behaviour and rely on the AOU-04R vehicle test. Lead decision DQ-300</t>
+          </r>
+        </is>
+      </c>
+      <c r="O86" s="58" t="inlineStr">
+        <is>
+          <t>decision pending</t>
+        </is>
+      </c>
+      <c r="P86" s="33" t="inlineStr"/>
+      <c r="Q86" s="33" t="inlineStr"/>
+      <c r="R86" s="37" t="inlineStr"/>
+      <c r="S86" s="37" t="inlineStr"/>
+    </row>
+    <row r="87" ht="100.5" customHeight="1">
+      <c r="A87" s="39" t="n"/>
+      <c r="B87" s="39" t="n"/>
+      <c r="C87" s="39" t="n"/>
+      <c r="D87" s="39" t="n"/>
+      <c r="E87" s="39" t="n"/>
+      <c r="F87" s="39" t="n"/>
+      <c r="G87" s="40" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H87" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The PCM does not give stock PCS braking priority over the item's ACC_CONTROL request (AOU-04R not met)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I87" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Series-production Toyota ECU; PCS priority over 0x343 assumed (AOU-04R), not verified by LionDriver</t>
+          </r>
+        </is>
+      </c>
+      <c r="J87" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="K87" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No pre-release test targets this cause; AOU-04R needs a message review and a PCS target test (WP-C-04)</t>
+          </r>
+        </is>
+      </c>
+      <c r="L87" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="M87" s="44" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N87" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-ACT-006 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Establish on the reference car which stock TSS2 functions (PCS/AEB, FCW) remain available with LionDriver installed and longitudinal control enabled, and verify the stock pre-collision path after installation (PFMEA PFM-014)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O87" s="48" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P87" s="40" t="inlineStr"/>
+      <c r="Q87" s="40" t="inlineStr"/>
+      <c r="R87" s="45" t="inlineStr"/>
+      <c r="S87" s="45" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:S83"/>
-  <mergeCells count="172">
+  <autoFilter ref="A2:S87"/>
+  <mergeCells count="184">
+    <mergeCell ref="F84:F85"/>
     <mergeCell ref="F17:F19"/>
     <mergeCell ref="E39:E40"/>
     <mergeCell ref="A57:A59"/>
     <mergeCell ref="A20:A22"/>
     <mergeCell ref="F25:F28"/>
     <mergeCell ref="A51:A52"/>
+    <mergeCell ref="B86:B87"/>
     <mergeCell ref="A29:A31"/>
+    <mergeCell ref="D86:D87"/>
     <mergeCell ref="E23:E24"/>
     <mergeCell ref="F55:F56"/>
+    <mergeCell ref="F86:F87"/>
     <mergeCell ref="C32:C34"/>
     <mergeCell ref="E32:E34"/>
     <mergeCell ref="B23:B24"/>
@@ -15764,6 +16481,7 @@
     <mergeCell ref="C41:C43"/>
     <mergeCell ref="F71:F74"/>
     <mergeCell ref="A10:A13"/>
+    <mergeCell ref="C86:C87"/>
     <mergeCell ref="C44:C46"/>
     <mergeCell ref="A35:A36"/>
     <mergeCell ref="E44:E46"/>
@@ -15793,6 +16511,7 @@
     <mergeCell ref="E6:E9"/>
     <mergeCell ref="B69:B70"/>
     <mergeCell ref="B3:B5"/>
+    <mergeCell ref="B84:B85"/>
     <mergeCell ref="C51:C52"/>
     <mergeCell ref="C60:C61"/>
     <mergeCell ref="C64:C66"/>
@@ -15818,6 +16537,7 @@
     <mergeCell ref="F32:F34"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="E67:E68"/>
+    <mergeCell ref="A84:A85"/>
     <mergeCell ref="A17:A19"/>
     <mergeCell ref="E51:E52"/>
     <mergeCell ref="C17:C19"/>
@@ -15827,12 +16547,15 @@
     <mergeCell ref="A25:A28"/>
     <mergeCell ref="B71:B74"/>
     <mergeCell ref="B82:B83"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="E84:E85"/>
     <mergeCell ref="A44:A46"/>
     <mergeCell ref="F51:F52"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A64:A66"/>
     <mergeCell ref="A79:A81"/>
+    <mergeCell ref="E86:E87"/>
     <mergeCell ref="B41:B43"/>
     <mergeCell ref="F23:F24"/>
     <mergeCell ref="B10:B13"/>
@@ -15878,6 +16601,7 @@
     <mergeCell ref="B64:B66"/>
     <mergeCell ref="C25:C28"/>
     <mergeCell ref="A55:A56"/>
+    <mergeCell ref="A86:A87"/>
     <mergeCell ref="C55:C56"/>
     <mergeCell ref="B79:B81"/>
     <mergeCell ref="B32:B34"/>
@@ -15906,9 +16630,10 @@
     <mergeCell ref="A82:A83"/>
     <mergeCell ref="D35:D36"/>
     <mergeCell ref="C6:C9"/>
+    <mergeCell ref="D84:D85"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
+    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83 R84 R85 R86 R87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
       <formula1>"Agree,Re-rate,Reject,Question"</formula1>
     </dataValidation>
   </dataValidations>
@@ -15916,7 +16641,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.12 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.13 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -15931,7 +16656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15946,79 +16671,79 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="58" t="inlineStr">
+      <c r="A1" s="59" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B1" s="58" t="inlineStr">
+      <c r="B1" s="59" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="C1" s="58" t="inlineStr">
+      <c r="C1" s="59" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" s="58" t="inlineStr">
+      <c r="D1" s="59" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E1" s="58" t="inlineStr">
+      <c r="E1" s="59" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="58" t="inlineStr">
+      <c r="F1" s="59" t="inlineStr">
         <is>
           <t>Causes</t>
         </is>
       </c>
-      <c r="G1" s="58" t="inlineStr">
+      <c r="G1" s="59" t="inlineStr">
         <is>
           <t>Revised S/O/D</t>
         </is>
       </c>
-      <c r="H1" s="58" t="inlineStr">
+      <c r="H1" s="59" t="inlineStr">
         <is>
           <t>Revised AP</t>
         </is>
       </c>
-      <c r="I1" s="58" t="inlineStr">
+      <c r="I1" s="59" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
     </row>
     <row r="2" ht="127.5" customHeight="1">
-      <c r="A2" s="59" t="inlineStr">
+      <c r="A2" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-001</t>
         </is>
       </c>
-      <c r="B2" s="59" t="inlineStr">
+      <c r="B2" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C2" s="59" t="inlineStr">
+      <c r="C2" s="60" t="inlineStr">
         <is>
           <t>Derive steering and acceleration envelopes from measurements on the reference vehicle and set the panda limits from them, independently of the SoC limits (same as SWF-ACT-003, FSC FOI-001)</t>
         </is>
       </c>
-      <c r="D2" s="59" t="inlineStr">
+      <c r="D2" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E2" s="59" t="inlineStr">
+      <c r="E2" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F2" s="59" t="inlineStr">
+      <c r="F2" s="60" t="inlineStr">
         <is>
           <t>SFM-002.C1
 SFM-002.C2
@@ -16031,37 +16756,37 @@
 SFM-029.C2</t>
         </is>
       </c>
-      <c r="G2" s="59" t="inlineStr"/>
-      <c r="H2" s="59" t="inlineStr"/>
-      <c r="I2" s="59" t="inlineStr"/>
+      <c r="G2" s="60" t="inlineStr"/>
+      <c r="H2" s="60" t="inlineStr"/>
+      <c r="I2" s="60" t="inlineStr"/>
     </row>
     <row r="3" ht="127.5" customHeight="1">
-      <c r="A3" s="59" t="inlineStr">
+      <c r="A3" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-002</t>
         </is>
       </c>
-      <c r="B3" s="59" t="inlineStr">
+      <c r="B3" s="60" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C3" s="59" t="inlineStr">
+      <c r="C3" s="60" t="inlineStr">
         <is>
           <t>Requirements-based tests for the host safety-relevant functions (selfdrived, controlsd, pandad, car interface, locationd bounds, monitoring policy), proven by mutation or fault injection and run as a CI gate (see SWF host actions)</t>
         </is>
       </c>
-      <c r="D3" s="59" t="inlineStr">
+      <c r="D3" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E3" s="59" t="inlineStr">
+      <c r="E3" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F3" s="59" t="inlineStr">
+      <c r="F3" s="60" t="inlineStr">
         <is>
           <t>SFM-002.C4
 SFM-004.C3
@@ -16074,37 +16799,37 @@
 SFM-030.C1</t>
         </is>
       </c>
-      <c r="G3" s="59" t="inlineStr"/>
-      <c r="H3" s="59" t="inlineStr"/>
-      <c r="I3" s="59" t="inlineStr"/>
+      <c r="G3" s="60" t="inlineStr"/>
+      <c r="H3" s="60" t="inlineStr"/>
+      <c r="I3" s="60" t="inlineStr"/>
     </row>
     <row r="4" ht="343.5" customHeight="1">
-      <c r="A4" s="59" t="inlineStr">
+      <c r="A4" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-003</t>
         </is>
       </c>
-      <c r="B4" s="59" t="inlineStr">
+      <c r="B4" s="60" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C4" s="59" t="inlineStr">
+      <c r="C4" s="60" t="inlineStr">
         <is>
           <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
         </is>
       </c>
-      <c r="D4" s="59" t="inlineStr">
+      <c r="D4" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E4" s="59" t="inlineStr">
+      <c r="E4" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F4" s="59" t="inlineStr">
+      <c r="F4" s="60" t="inlineStr">
         <is>
           <t>SFM-003.C1
 SFM-003.C2
@@ -16133,109 +16858,110 @@
 SFM-033.C3</t>
         </is>
       </c>
-      <c r="G4" s="59" t="inlineStr"/>
-      <c r="H4" s="59" t="inlineStr"/>
-      <c r="I4" s="59" t="inlineStr"/>
+      <c r="G4" s="60" t="inlineStr"/>
+      <c r="H4" s="60" t="inlineStr"/>
+      <c r="I4" s="60" t="inlineStr"/>
     </row>
     <row r="5" ht="73.5" customHeight="1">
-      <c r="A5" s="59" t="inlineStr">
+      <c r="A5" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-005</t>
         </is>
       </c>
-      <c r="B5" s="59" t="inlineStr">
+      <c r="B5" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C5" s="59" t="inlineStr">
+      <c r="C5" s="60" t="inlineStr">
         <is>
           <t>Decide in the FSC how the item reacts when driver awareness reaches zero (driverUnresponsive3 / driverDistracted3 have no disable reaction at BL-004 or BL-005) and implement the decision. DQ-205 (answered) makes this the safe state of SG-010 (ASIL A); the reaction itself is still to be decided</t>
         </is>
       </c>
-      <c r="D5" s="59" t="inlineStr">
+      <c r="D5" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E5" s="59" t="inlineStr">
+      <c r="E5" s="60" t="inlineStr">
         <is>
           <t>decision pending</t>
         </is>
       </c>
-      <c r="F5" s="59" t="inlineStr">
+      <c r="F5" s="60" t="inlineStr">
         <is>
           <t>SFM-025.C1</t>
         </is>
       </c>
-      <c r="G5" s="59" t="inlineStr"/>
-      <c r="H5" s="59" t="inlineStr"/>
-      <c r="I5" s="59" t="inlineStr"/>
+      <c r="G5" s="60" t="inlineStr"/>
+      <c r="H5" s="60" t="inlineStr"/>
+      <c r="I5" s="60" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="59" t="inlineStr">
+      <c r="A6" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-006</t>
         </is>
       </c>
-      <c r="B6" s="59" t="inlineStr">
+      <c r="B6" s="60" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C6" s="59" t="inlineStr">
+      <c r="C6" s="60" t="inlineStr">
         <is>
           <t>Establish on the reference car which stock TSS2 functions (PCS/AEB, FCW) remain available with LionDriver installed and longitudinal control enabled, and verify the stock pre-collision path after installation (PFMEA PFM-014)</t>
         </is>
       </c>
-      <c r="D6" s="59" t="inlineStr">
+      <c r="D6" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E6" s="59" t="inlineStr">
+      <c r="E6" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F6" s="59" t="inlineStr">
+      <c r="F6" s="60" t="inlineStr">
         <is>
           <t>SFM-010.C2
 SFM-033.C1
-SFM-033.C2</t>
-        </is>
-      </c>
-      <c r="G6" s="59" t="inlineStr"/>
-      <c r="H6" s="59" t="inlineStr"/>
-      <c r="I6" s="59" t="inlineStr"/>
+SFM-033.C2
+SFM-036.C2</t>
+        </is>
+      </c>
+      <c r="G6" s="60" t="inlineStr"/>
+      <c r="H6" s="60" t="inlineStr"/>
+      <c r="I6" s="60" t="inlineStr"/>
     </row>
     <row r="7" ht="73.5" customHeight="1">
-      <c r="A7" s="59" t="inlineStr">
+      <c r="A7" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-007</t>
         </is>
       </c>
-      <c r="B7" s="59" t="inlineStr">
+      <c r="B7" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C7" s="59" t="inlineStr">
+      <c r="C7" s="60" t="inlineStr">
         <is>
           <t>Supervise the alert channels: treat loss of ui or soundd liveness, or a stale displayed state, as a fault that escalates (audible fallback, disengagement) instead of continuing silently</t>
         </is>
       </c>
-      <c r="D7" s="59" t="inlineStr">
+      <c r="D7" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E7" s="59" t="inlineStr">
+      <c r="E7" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F7" s="59" t="inlineStr">
+      <c r="F7" s="60" t="inlineStr">
         <is>
           <t>SFM-015.C1
 SFM-026.C1
@@ -16244,76 +16970,76 @@
 SFM-028.C1</t>
         </is>
       </c>
-      <c r="G7" s="59" t="inlineStr"/>
-      <c r="H7" s="59" t="inlineStr"/>
-      <c r="I7" s="59" t="inlineStr"/>
+      <c r="G7" s="60" t="inlineStr"/>
+      <c r="H7" s="60" t="inlineStr"/>
+      <c r="I7" s="60" t="inlineStr"/>
     </row>
     <row r="8" ht="73.5" customHeight="1">
-      <c r="A8" s="59" t="inlineStr">
+      <c r="A8" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-008</t>
         </is>
       </c>
-      <c r="B8" s="59" t="inlineStr">
+      <c r="B8" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C8" s="59" t="inlineStr">
+      <c r="C8" s="60" t="inlineStr">
         <is>
           <t>Allow engagement only when the fingerprint, CarParams and panda safety parameter match the reference configuration AC-001 (refuse fuzzy matches in the reference build); see PFMEA PFM-013</t>
         </is>
       </c>
-      <c r="D8" s="59" t="inlineStr">
+      <c r="D8" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E8" s="59" t="inlineStr">
+      <c r="E8" s="60" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F8" s="59" t="inlineStr">
+      <c r="F8" s="60" t="inlineStr">
         <is>
           <t>SFM-032.C1</t>
         </is>
       </c>
-      <c r="G8" s="59" t="inlineStr"/>
-      <c r="H8" s="59" t="inlineStr"/>
-      <c r="I8" s="59" t="inlineStr">
+      <c r="G8" s="60" t="inlineStr"/>
+      <c r="H8" s="60" t="inlineStr"/>
+      <c r="I8" s="60" t="inlineStr">
         <is>
           <t>BL-005: the reference build is the default (LionDriver #36), the panda accepts only TOYOTA parameter 73 (reference_lock.h) and pandad configures a car mode only on a reference panda (#41). Fuzzy fingerprint matches are still accepted on the host (SFM-032.C1)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="100.5" customHeight="1">
-      <c r="A9" s="59" t="inlineStr">
+      <c r="A9" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-009</t>
         </is>
       </c>
-      <c r="B9" s="59" t="inlineStr">
+      <c r="B9" s="60" t="inlineStr">
         <is>
           <t>prevention</t>
         </is>
       </c>
-      <c r="C9" s="59" t="inlineStr">
+      <c r="C9" s="60" t="inlineStr">
         <is>
           <t>Produce SOTIF / ISO PAS 8800 evidence for the neural-network elements (driving model, lead detection, driver monitoring model) per WP-V-02..04, including fault-induced inputs (corrupted or stale frames)</t>
         </is>
       </c>
-      <c r="D9" s="59" t="inlineStr">
+      <c r="D9" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E9" s="59" t="inlineStr">
+      <c r="E9" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F9" s="59" t="inlineStr">
+      <c r="F9" s="60" t="inlineStr">
         <is>
           <t>SFM-002.C2
 SFM-003.C3
@@ -16324,37 +17050,37 @@
 SFM-022.C2</t>
         </is>
       </c>
-      <c r="G9" s="59" t="inlineStr"/>
-      <c r="H9" s="59" t="inlineStr"/>
-      <c r="I9" s="59" t="inlineStr"/>
+      <c r="G9" s="60" t="inlineStr"/>
+      <c r="H9" s="60" t="inlineStr"/>
+      <c r="I9" s="60" t="inlineStr"/>
     </row>
     <row r="10" ht="73.5" customHeight="1">
-      <c r="A10" s="59" t="inlineStr">
+      <c r="A10" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-010</t>
         </is>
       </c>
-      <c r="B10" s="59" t="inlineStr">
+      <c r="B10" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C10" s="59" t="inlineStr">
+      <c r="C10" s="60" t="inlineStr">
         <is>
           <t>Justify every SOFT_DISABLE reaction and debounce against the FTTI (WP-S-04) and alert at once when the panda withdraws authority while engaged (controlsMismatch debounce)</t>
         </is>
       </c>
-      <c r="D10" s="59" t="inlineStr">
+      <c r="D10" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E10" s="59" t="inlineStr">
+      <c r="E10" s="60" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F10" s="59" t="inlineStr">
+      <c r="F10" s="60" t="inlineStr">
         <is>
           <t>SFM-014.C2
 SFM-015.C2
@@ -16362,286 +17088,317 @@
 SFM-016.C2</t>
         </is>
       </c>
-      <c r="G10" s="59" t="inlineStr"/>
-      <c r="H10" s="59" t="inlineStr"/>
-      <c r="I10" s="59" t="inlineStr">
+      <c r="G10" s="60" t="inlineStr"/>
+      <c r="H10" s="60" t="inlineStr"/>
+      <c r="I10" s="60" t="inlineStr">
         <is>
           <t>controlsMismatch debounce cut from 200 cumulative samples (~2 s) to 2 consecutive samples, at most 0.5 s (change-2026-10-13-host-supervision.md); credited at BL-005 (SFM-015.C2 M 6). FTTI justification of SOFT_DISABLE reactions open</t>
         </is>
       </c>
     </row>
     <row r="11" ht="33" customHeight="1">
-      <c r="A11" s="59" t="inlineStr">
+      <c r="A11" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-011</t>
         </is>
       </c>
-      <c r="B11" s="59" t="inlineStr">
+      <c r="B11" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C11" s="59" t="inlineStr">
+      <c r="C11" s="60" t="inlineStr">
         <is>
           <t>Alert the driver when stock cruise stays engaged while the item is disengaged (cruiseMismatch has no alert at BL-004)</t>
         </is>
       </c>
-      <c r="D11" s="59" t="inlineStr">
+      <c r="D11" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E11" s="60" t="inlineStr">
+      <c r="E11" s="61" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F11" s="59" t="inlineStr">
+      <c r="F11" s="60" t="inlineStr">
         <is>
           <t>SFM-021.C1
 SFM-021.C2</t>
         </is>
       </c>
-      <c r="G11" s="59" t="inlineStr"/>
-      <c r="H11" s="59" t="inlineStr"/>
-      <c r="I11" s="59" t="inlineStr">
+      <c r="G11" s="60" t="inlineStr"/>
+      <c r="H11" s="60" t="inlineStr"/>
+      <c r="I11" s="60" t="inlineStr">
         <is>
           <t>cruiseMismatch now alerts after 1 s (change-2026-10-13-host-supervision.md); see SWF-ACT-034</t>
         </is>
       </c>
     </row>
     <row r="12" ht="73.5" customHeight="1">
-      <c r="A12" s="59" t="inlineStr">
+      <c r="A12" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-012</t>
         </is>
       </c>
-      <c r="B12" s="59" t="inlineStr">
+      <c r="B12" s="60" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C12" s="59" t="inlineStr">
+      <c r="C12" s="60" t="inlineStr">
         <is>
           <t>Measure on the HIL bench and the reference car (WP-V-05) how the panda reacts to over-limit and not-engaged steering and acceleration frames and to driver brake, gas and cancel inputs, and what the EPS and PCM do when frames are refused; re-rate the MSR rows from code-derived to measured timing</t>
         </is>
       </c>
-      <c r="D12" s="59" t="inlineStr"/>
-      <c r="E12" s="59" t="inlineStr">
+      <c r="D12" s="60" t="inlineStr"/>
+      <c r="E12" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F12" s="59" t="inlineStr"/>
-      <c r="G12" s="59" t="inlineStr"/>
-      <c r="H12" s="59" t="inlineStr"/>
-      <c r="I12" s="59" t="inlineStr"/>
+      <c r="F12" s="60" t="inlineStr"/>
+      <c r="G12" s="60" t="inlineStr"/>
+      <c r="H12" s="60" t="inlineStr"/>
+      <c r="I12" s="60" t="inlineStr"/>
     </row>
     <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="59" t="inlineStr">
+      <c r="A13" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-013</t>
         </is>
       </c>
-      <c r="B13" s="59" t="inlineStr">
+      <c r="B13" s="60" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C13" s="59" t="inlineStr">
+      <c r="C13" s="60" t="inlineStr">
         <is>
           <t>Check on the host, within the SG-01 FTTI, that the panda reports controls_allowed false while the item is disengaged (the reverse of the controlsMismatch check, which at BL-005 still covers only engaged with authority withdrawn), with a disable and an alert</t>
         </is>
       </c>
-      <c r="D13" s="59" t="inlineStr"/>
-      <c r="E13" s="59" t="inlineStr">
+      <c r="D13" s="60" t="inlineStr"/>
+      <c r="E13" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F13" s="59" t="inlineStr"/>
-      <c r="G13" s="59" t="inlineStr"/>
-      <c r="H13" s="59" t="inlineStr"/>
-      <c r="I13" s="59" t="inlineStr"/>
+      <c r="F13" s="60" t="inlineStr"/>
+      <c r="G13" s="60" t="inlineStr"/>
+      <c r="H13" s="60" t="inlineStr"/>
+      <c r="I13" s="60" t="inlineStr"/>
     </row>
     <row r="14" ht="46.5" customHeight="1">
-      <c r="A14" s="59" t="inlineStr">
+      <c r="A14" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-014</t>
         </is>
       </c>
-      <c r="B14" s="59" t="inlineStr">
+      <c r="B14" s="60" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C14" s="59" t="inlineStr">
+      <c r="C14" s="60" t="inlineStr">
         <is>
           <t>Specify in the TSC a steering-direction plausibility monitor (commanded torque sign against measured yaw rate and lane-relative lateral motion), or justify its absence against HZ-003</t>
         </is>
       </c>
-      <c r="D14" s="59" t="inlineStr"/>
-      <c r="E14" s="59" t="inlineStr">
+      <c r="D14" s="60" t="inlineStr"/>
+      <c r="E14" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F14" s="59" t="inlineStr"/>
-      <c r="G14" s="59" t="inlineStr"/>
-      <c r="H14" s="59" t="inlineStr"/>
-      <c r="I14" s="59" t="inlineStr"/>
+      <c r="F14" s="60" t="inlineStr"/>
+      <c r="G14" s="60" t="inlineStr"/>
+      <c r="H14" s="60" t="inlineStr"/>
+      <c r="I14" s="60" t="inlineStr"/>
     </row>
     <row r="15" ht="87" customHeight="1">
-      <c r="A15" s="59" t="inlineStr">
+      <c r="A15" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-015</t>
         </is>
       </c>
-      <c r="B15" s="59" t="inlineStr">
+      <c r="B15" s="60" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C15" s="59" t="inlineStr">
+      <c r="C15" s="60" t="inlineStr">
         <is>
           <t>Detect stale commands and inputs within the SG-01 FTTI: command-frame freshness in the MCU with an active zero frame (TSR-408, TSR-109) and frozen-content and age checks on model outputs in controlsd (TSR-602, AIR-17)</t>
         </is>
       </c>
-      <c r="D15" s="59" t="inlineStr"/>
-      <c r="E15" s="59" t="inlineStr">
+      <c r="D15" s="60" t="inlineStr"/>
+      <c r="E15" s="60" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F15" s="59" t="inlineStr"/>
-      <c r="G15" s="59" t="inlineStr"/>
-      <c r="H15" s="59" t="inlineStr"/>
-      <c r="I15" s="59" t="inlineStr">
+      <c r="F15" s="60" t="inlineStr"/>
+      <c r="G15" s="60" t="inlineStr"/>
+      <c r="H15" s="60" t="inlineStr"/>
+      <c r="I15" s="60" t="inlineStr">
         <is>
           <t>BL-005: command-frame arrival in the MCU (TSR-408, 50 ms STEERING_LKA, reference build by default) and input age checks in controlsd (TSR-602) are in. Open: the active zero frame (TSR-109), a frozen-content check on model outputs, and stale data with fresh timestamps (SFM-006.C1 to C3)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="60" customHeight="1">
-      <c r="A16" s="59" t="inlineStr">
+      <c r="A16" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-016</t>
         </is>
       </c>
-      <c r="B16" s="59" t="inlineStr">
+      <c r="B16" s="60" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C16" s="59" t="inlineStr">
+      <c r="C16" s="60" t="inlineStr">
         <is>
           <t>Supervise driver override in the panda: driver steering torque above the override threshold limits or revokes lateral authority within the SG-05 0.2 s budget (TSR-304). Behaviour decided by the lead (DQ-053, option A): back off on override and show a cue</t>
         </is>
       </c>
-      <c r="D16" s="59" t="inlineStr"/>
-      <c r="E16" s="59" t="inlineStr">
+      <c r="D16" s="60" t="inlineStr"/>
+      <c r="E16" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F16" s="59" t="inlineStr"/>
-      <c r="G16" s="59" t="inlineStr"/>
-      <c r="H16" s="59" t="inlineStr"/>
-      <c r="I16" s="59" t="inlineStr"/>
+      <c r="F16" s="60" t="inlineStr"/>
+      <c r="G16" s="60" t="inlineStr"/>
+      <c r="H16" s="60" t="inlineStr"/>
+      <c r="I16" s="60" t="inlineStr"/>
     </row>
     <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="59" t="inlineStr">
+      <c r="A17" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-017</t>
         </is>
       </c>
-      <c r="B17" s="59" t="inlineStr">
+      <c r="B17" s="60" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C17" s="59" t="inlineStr">
+      <c r="C17" s="60" t="inlineStr">
         <is>
           <t>Add WP-S-04 FTTI rows for the warning paths without one (insufficient lateral control, late or insufficient braking warnings, SG-008 unintended engagement, driver monitoring), so these mechanisms can be compared with a time budget</t>
         </is>
       </c>
-      <c r="D17" s="59" t="inlineStr"/>
-      <c r="E17" s="59" t="inlineStr">
+      <c r="D17" s="60" t="inlineStr"/>
+      <c r="E17" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F17" s="59" t="inlineStr"/>
-      <c r="G17" s="59" t="inlineStr"/>
-      <c r="H17" s="59" t="inlineStr"/>
-      <c r="I17" s="59" t="inlineStr"/>
+      <c r="F17" s="60" t="inlineStr"/>
+      <c r="G17" s="60" t="inlineStr"/>
+      <c r="H17" s="60" t="inlineStr"/>
+      <c r="I17" s="60" t="inlineStr"/>
     </row>
     <row r="18" ht="73.5" customHeight="1">
-      <c r="A18" s="59" t="inlineStr">
+      <c r="A18" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-018</t>
         </is>
       </c>
-      <c r="B18" s="59" t="inlineStr">
+      <c r="B18" s="60" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C18" s="59" t="inlineStr">
+      <c r="C18" s="60" t="inlineStr">
         <is>
           <t>Detect silent loss of the actuation path: report forwarded and refused TX frames from the panda, and compare EPS and PCM acceptance (LKA_STATE, ACC status) with the commands, warning within the SG-02/06 1 s budget</t>
         </is>
       </c>
-      <c r="D18" s="59" t="inlineStr"/>
-      <c r="E18" s="59" t="inlineStr">
+      <c r="D18" s="60" t="inlineStr"/>
+      <c r="E18" s="60" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F18" s="59" t="inlineStr"/>
-      <c r="G18" s="59" t="inlineStr"/>
-      <c r="H18" s="59" t="inlineStr"/>
-      <c r="I18" s="59" t="inlineStr">
+      <c r="F18" s="60" t="inlineStr"/>
+      <c r="G18" s="60" t="inlineStr"/>
+      <c r="H18" s="60" t="inlineStr"/>
+      <c r="I18" s="60" t="inlineStr">
         <is>
           <t>BL-005: frames that stop reaching the panda are detected (TSR-408) and alerted within 0.5 s (TSR-621), credited on SFM-005.C2 and SFM-011.C2. Open: frames that reach the panda but are not accepted by the EPS or PCM (SFM-005.C1, SFM-011.C1; TSR-626)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="59" t="inlineStr">
+      <c r="A19" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-019</t>
         </is>
       </c>
-      <c r="B19" s="59" t="inlineStr">
+      <c r="B19" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C19" s="59" t="inlineStr">
+      <c r="C19" s="60" t="inlineStr">
         <is>
           <t>Revoke lateral authority in the panda when it rejects a steering frame while authority is granted, and keep it revoked until a new valid engagement (TSR-108; lead decision DQ-060, option A). At BL-005 the frame is dropped and only the host disengages (pandaTxBlocked)</t>
         </is>
       </c>
-      <c r="D19" s="59" t="inlineStr"/>
-      <c r="E19" s="59" t="inlineStr">
+      <c r="D19" s="60" t="inlineStr"/>
+      <c r="E19" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F19" s="59" t="inlineStr">
+      <c r="F19" s="60" t="inlineStr">
         <is>
           <t>SFM-002.C1
 SFM-002.C2
 SFM-002.C4</t>
         </is>
       </c>
-      <c r="G19" s="59" t="inlineStr"/>
-      <c r="H19" s="59" t="inlineStr"/>
-      <c r="I19" s="59" t="inlineStr"/>
+      <c r="G19" s="60" t="inlineStr"/>
+      <c r="H19" s="60" t="inlineStr"/>
+      <c r="I19" s="60" t="inlineStr"/>
+    </row>
+    <row r="20" ht="73.5" customHeight="1">
+      <c r="A20" s="60" t="inlineStr">
+        <is>
+          <t>SFM-ACT-020</t>
+        </is>
+      </c>
+      <c r="B20" s="60" t="inlineStr">
+        <is>
+          <t>design change</t>
+        </is>
+      </c>
+      <c r="C20" s="60" t="inlineStr">
+        <is>
+          <t>React to a stock PCS event on the longitudinal command (for example a neutral or zero acceleration request, or a longitudinal disable, while stockAeb is set), so stock AEB does not depend on PCM arbitration alone (AOU-04R); or keep today's behaviour and rely on the AOU-04R vehicle test. Lead decision DQ-300</t>
+        </is>
+      </c>
+      <c r="D20" s="60" t="inlineStr"/>
+      <c r="E20" s="60" t="inlineStr">
+        <is>
+          <t>decision pending</t>
+        </is>
+      </c>
+      <c r="F20" s="60" t="inlineStr">
+        <is>
+          <t>SFM-036.C1</t>
+        </is>
+      </c>
+      <c r="G20" s="60" t="inlineStr"/>
+      <c r="H20" s="60" t="inlineStr"/>
+      <c r="I20" s="60" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I19"/>
+  <autoFilter ref="A1:I20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16663,50 +17420,50 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="58" t="inlineStr">
+      <c r="A1" s="59" t="inlineStr">
         <is>
           <t>Element</t>
         </is>
       </c>
-      <c r="B1" s="58" t="inlineStr">
+      <c r="B1" s="59" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="58" t="inlineStr">
+      <c r="C1" s="59" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="D1" s="58" t="inlineStr">
+      <c r="D1" s="59" t="inlineStr">
         <is>
           <t>Parent</t>
         </is>
       </c>
-      <c r="E1" s="58" t="inlineStr">
+      <c r="E1" s="59" t="inlineStr">
         <is>
           <t>Functions</t>
         </is>
       </c>
     </row>
     <row r="2" ht="222" customHeight="1">
-      <c r="A2" s="59" t="inlineStr">
+      <c r="A2" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-001</t>
         </is>
       </c>
-      <c r="B2" s="59" t="inlineStr">
+      <c r="B2" s="60" t="inlineStr">
         <is>
           <t>LionDriver item (L2 ACC + ALC + driver monitoring)</t>
         </is>
       </c>
-      <c r="C2" s="59" t="inlineStr">
+      <c r="C2" s="60" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="D2" s="59" t="inlineStr"/>
-      <c r="E2" s="59" t="inlineStr">
+      <c r="D2" s="60" t="inlineStr"/>
+      <c r="E2" s="60" t="inlineStr">
         <is>
           <t>SFM-FN-001: F1 Lateral control: request steering torque from the EPS to keep the vehicle in its lane while engaged
 SFM-FN-002: F2 Longitudinal control: request acceleration/deceleration to hold set speed and follow leads while engaged
@@ -16720,398 +17477,398 @@
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="59" t="inlineStr">
+      <c r="A3" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="B3" s="59" t="inlineStr">
+      <c r="B3" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    comma 3X device</t>
         </is>
       </c>
-      <c r="C3" s="59" t="inlineStr">
+      <c r="C3" s="60" t="inlineStr">
         <is>
           <t>system</t>
         </is>
       </c>
-      <c r="D3" s="59" t="inlineStr">
+      <c r="D3" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-001</t>
         </is>
       </c>
-      <c r="E3" s="59" t="inlineStr"/>
+      <c r="E3" s="60" t="inlineStr"/>
     </row>
     <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="59" t="inlineStr">
+      <c r="A4" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-003</t>
         </is>
       </c>
-      <c r="B4" s="59" t="inlineStr">
+      <c r="B4" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Integrated panda (CAN interface and safety model)</t>
         </is>
       </c>
-      <c r="C4" s="59" t="inlineStr">
+      <c r="C4" s="60" t="inlineStr">
         <is>
           <t>subsystem</t>
         </is>
       </c>
-      <c r="D4" s="59" t="inlineStr">
+      <c r="D4" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E4" s="59" t="inlineStr"/>
+      <c r="E4" s="60" t="inlineStr"/>
     </row>
     <row r="5" ht="19.5" customHeight="1">
-      <c r="A5" s="59" t="inlineStr">
+      <c r="A5" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-004</t>
         </is>
       </c>
-      <c r="B5" s="59" t="inlineStr">
+      <c r="B5" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Harness (Toyota A connector, harness box, comma power v3)</t>
         </is>
       </c>
-      <c r="C5" s="59" t="inlineStr">
+      <c r="C5" s="60" t="inlineStr">
         <is>
           <t>component</t>
         </is>
       </c>
-      <c r="D5" s="59" t="inlineStr">
+      <c r="D5" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-001</t>
         </is>
       </c>
-      <c r="E5" s="59" t="inlineStr"/>
+      <c r="E5" s="60" t="inlineStr"/>
     </row>
     <row r="6" ht="19.5" customHeight="1">
-      <c r="A6" s="59" t="inlineStr">
+      <c r="A6" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-010</t>
         </is>
       </c>
-      <c r="B6" s="59" t="inlineStr">
+      <c r="B6" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Perception (camerad, modeld)</t>
         </is>
       </c>
-      <c r="C6" s="59" t="inlineStr">
+      <c r="C6" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D6" s="59" t="inlineStr">
+      <c r="D6" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E6" s="59" t="inlineStr"/>
+      <c r="E6" s="60" t="inlineStr"/>
     </row>
     <row r="7" ht="19.5" customHeight="1">
-      <c r="A7" s="59" t="inlineStr">
+      <c r="A7" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-011</t>
         </is>
       </c>
-      <c r="B7" s="59" t="inlineStr">
+      <c r="B7" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Localization and calibration (locationd, calibrationd, paramsd, torqued)</t>
         </is>
       </c>
-      <c r="C7" s="59" t="inlineStr">
+      <c r="C7" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D7" s="59" t="inlineStr">
+      <c r="D7" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E7" s="59" t="inlineStr"/>
+      <c r="E7" s="60" t="inlineStr"/>
     </row>
     <row r="8" ht="19.5" customHeight="1">
-      <c r="A8" s="59" t="inlineStr">
+      <c r="A8" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-012</t>
         </is>
       </c>
-      <c r="B8" s="59" t="inlineStr">
+      <c r="B8" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Planning (plannerd, radard)</t>
         </is>
       </c>
-      <c r="C8" s="59" t="inlineStr">
+      <c r="C8" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D8" s="59" t="inlineStr">
+      <c r="D8" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E8" s="59" t="inlineStr"/>
+      <c r="E8" s="60" t="inlineStr"/>
     </row>
     <row r="9" ht="19.5" customHeight="1">
-      <c r="A9" s="59" t="inlineStr">
+      <c r="A9" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-013</t>
         </is>
       </c>
-      <c r="B9" s="59" t="inlineStr">
+      <c r="B9" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Control (controlsd, lateral/longitudinal controllers)</t>
         </is>
       </c>
-      <c r="C9" s="59" t="inlineStr">
+      <c r="C9" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D9" s="59" t="inlineStr">
+      <c r="D9" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E9" s="59" t="inlineStr"/>
+      <c r="E9" s="60" t="inlineStr"/>
     </row>
     <row r="10" ht="19.5" customHeight="1">
-      <c r="A10" s="59" t="inlineStr">
+      <c r="A10" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-014</t>
         </is>
       </c>
-      <c r="B10" s="59" t="inlineStr">
+      <c r="B10" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Supervision (selfdrived state machine, events, alert manager)</t>
         </is>
       </c>
-      <c r="C10" s="59" t="inlineStr">
+      <c r="C10" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D10" s="59" t="inlineStr">
+      <c r="D10" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E10" s="59" t="inlineStr"/>
+      <c r="E10" s="60" t="inlineStr"/>
     </row>
     <row r="11" ht="19.5" customHeight="1">
-      <c r="A11" s="59" t="inlineStr">
+      <c r="A11" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-015</t>
         </is>
       </c>
-      <c r="B11" s="59" t="inlineStr">
+      <c r="B11" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Driver monitoring (dmonitoringmodeld, dmonitoringd)</t>
         </is>
       </c>
-      <c r="C11" s="59" t="inlineStr">
+      <c r="C11" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D11" s="59" t="inlineStr">
+      <c r="D11" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E11" s="59" t="inlineStr"/>
+      <c r="E11" s="60" t="inlineStr"/>
     </row>
     <row r="12" ht="19.5" customHeight="1">
-      <c r="A12" s="59" t="inlineStr">
+      <c r="A12" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-016</t>
         </is>
       </c>
-      <c r="B12" s="59" t="inlineStr">
+      <c r="B12" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Car interface (card, car_events, opendbc Toyota port)</t>
         </is>
       </c>
-      <c r="C12" s="59" t="inlineStr">
+      <c r="C12" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D12" s="59" t="inlineStr">
+      <c r="D12" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E12" s="59" t="inlineStr"/>
+      <c r="E12" s="60" t="inlineStr"/>
     </row>
     <row r="13" ht="19.5" customHeight="1">
-      <c r="A13" s="59" t="inlineStr">
+      <c r="A13" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-017</t>
         </is>
       </c>
-      <c r="B13" s="59" t="inlineStr">
+      <c r="B13" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Panda daemon (pandad)</t>
         </is>
       </c>
-      <c r="C13" s="59" t="inlineStr">
+      <c r="C13" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D13" s="59" t="inlineStr">
+      <c r="D13" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E13" s="59" t="inlineStr"/>
+      <c r="E13" s="60" t="inlineStr"/>
     </row>
     <row r="14" ht="19.5" customHeight="1">
-      <c r="A14" s="59" t="inlineStr">
+      <c r="A14" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-018</t>
         </is>
       </c>
-      <c r="B14" s="59" t="inlineStr">
+      <c r="B14" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        HMI (ui, soundd)</t>
         </is>
       </c>
-      <c r="C14" s="59" t="inlineStr">
+      <c r="C14" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D14" s="59" t="inlineStr">
+      <c r="D14" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E14" s="59" t="inlineStr"/>
+      <c r="E14" s="60" t="inlineStr"/>
     </row>
     <row r="15" ht="19.5" customHeight="1">
-      <c r="A15" s="59" t="inlineStr">
+      <c r="A15" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-019</t>
         </is>
       </c>
-      <c r="B15" s="59" t="inlineStr">
+      <c r="B15" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Platform (manager, messaging, hardwared, OS)</t>
         </is>
       </c>
-      <c r="C15" s="59" t="inlineStr">
+      <c r="C15" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D15" s="59" t="inlineStr">
+      <c r="D15" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E15" s="59" t="inlineStr"/>
+      <c r="E15" s="60" t="inlineStr"/>
     </row>
     <row r="16" ht="19.5" customHeight="1">
-      <c r="A16" s="59" t="inlineStr">
+      <c r="A16" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-030</t>
         </is>
       </c>
-      <c r="B16" s="59" t="inlineStr">
+      <c r="B16" s="60" t="inlineStr">
         <is>
           <t>Toyota EPS</t>
         </is>
       </c>
-      <c r="C16" s="59" t="inlineStr">
+      <c r="C16" s="60" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D16" s="59" t="inlineStr"/>
-      <c r="E16" s="59" t="inlineStr"/>
+      <c r="D16" s="60" t="inlineStr"/>
+      <c r="E16" s="60" t="inlineStr"/>
     </row>
     <row r="17" ht="19.5" customHeight="1">
-      <c r="A17" s="59" t="inlineStr">
+      <c r="A17" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-031</t>
         </is>
       </c>
-      <c r="B17" s="59" t="inlineStr">
+      <c r="B17" s="60" t="inlineStr">
         <is>
           <t>Toyota powertrain and brake control (receives ACC acceleration requests)</t>
         </is>
       </c>
-      <c r="C17" s="59" t="inlineStr">
+      <c r="C17" s="60" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D17" s="59" t="inlineStr"/>
-      <c r="E17" s="59" t="inlineStr"/>
+      <c r="D17" s="60" t="inlineStr"/>
+      <c r="E17" s="60" t="inlineStr"/>
     </row>
     <row r="18" ht="19.5" customHeight="1">
-      <c r="A18" s="59" t="inlineStr">
+      <c r="A18" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-032</t>
         </is>
       </c>
-      <c r="B18" s="59" t="inlineStr">
+      <c r="B18" s="60" t="inlineStr">
         <is>
           <t>Toyota stock ADAS camera (TSS2)</t>
         </is>
       </c>
-      <c r="C18" s="59" t="inlineStr">
+      <c r="C18" s="60" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D18" s="59" t="inlineStr"/>
-      <c r="E18" s="59" t="inlineStr"/>
+      <c r="D18" s="60" t="inlineStr"/>
+      <c r="E18" s="60" t="inlineStr"/>
     </row>
     <row r="19" ht="19.5" customHeight="1">
-      <c r="A19" s="59" t="inlineStr">
+      <c r="A19" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-033</t>
         </is>
       </c>
-      <c r="B19" s="59" t="inlineStr">
+      <c r="B19" s="60" t="inlineStr">
         <is>
           <t>Vehicle CAN buses and 12 V supply</t>
         </is>
       </c>
-      <c r="C19" s="59" t="inlineStr">
+      <c r="C19" s="60" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D19" s="59" t="inlineStr"/>
-      <c r="E19" s="59" t="inlineStr"/>
+      <c r="D19" s="60" t="inlineStr"/>
+      <c r="E19" s="60" t="inlineStr"/>
     </row>
     <row r="20" ht="19.5" customHeight="1">
-      <c r="A20" s="59" t="inlineStr">
+      <c r="A20" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-034</t>
         </is>
       </c>
-      <c r="B20" s="59" t="inlineStr">
+      <c r="B20" s="60" t="inlineStr">
         <is>
           <t>Driver</t>
         </is>
       </c>
-      <c r="C20" s="59" t="inlineStr">
+      <c r="C20" s="60" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D20" s="59" t="inlineStr"/>
-      <c r="E20" s="59" t="inlineStr"/>
+      <c r="D20" s="60" t="inlineStr"/>
+      <c r="E20" s="60" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E20"/>
@@ -17125,7 +17882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P66"/>
+  <dimension ref="A1:P70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -17147,7 +17904,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="61" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>FMEA-MSR (monitoring and system response, msr-plan.md): S, F, M and MSR AP per rating-tables.md §7 (RT-2). The MSR AP table is provisional until the handbook table is transcribed (decision register DQ-207). Exempt causes are rated in the FMEA named in the reason.</t>
         </is>
@@ -19875,7 +20632,7 @@
           <t>Device power loss (12 V interruption, harness connector)</t>
         </is>
       </c>
-      <c r="E44" s="62" t="inlineStr">
+      <c r="E44" s="63" t="inlineStr">
         <is>
           <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-012.C1)</t>
         </is>
@@ -20997,7 +21754,7 @@
           <t>Panda MCU hardware fault (see DFMEA/FMEDA)</t>
         </is>
       </c>
-      <c r="E62" s="62" t="inlineStr">
+      <c r="E62" s="63" t="inlineStr">
         <is>
           <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-001.C1)</t>
         </is>
@@ -21157,7 +21914,7 @@
           <t>Switch U1 or U2 stuck in intercept, its IN input damaged high or driven high, its pull-down R2/R3 open, or the switches damaged by box supply transients (DG419LE, RR-2026-010)</t>
         </is>
       </c>
-      <c r="E65" s="62" t="inlineStr">
+      <c r="E65" s="63" t="inlineStr">
         <is>
           <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-010.C1)</t>
         </is>
@@ -21193,7 +21950,7 @@
           <t>Switch stuck in pass-through, or the SBU1 drive lost, held low or too low to change the switch over (5 V drive against VL = VIN)</t>
         </is>
       </c>
-      <c r="E66" s="62" t="inlineStr">
+      <c r="E66" s="63" t="inlineStr">
         <is>
           <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-011.C1)</t>
         </is>
@@ -21210,13 +21967,258 @@
       <c r="O66" s="37" t="inlineStr"/>
       <c r="P66" s="37" t="inlineStr"/>
     </row>
+    <row r="67" ht="73.5" customHeight="1">
+      <c r="A67" s="34" t="inlineStr">
+        <is>
+          <t>SFM-035 · Item sends a frame that alters the stock pre-collision function</t>
+        </is>
+      </c>
+      <c r="B67" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C67" s="33" t="inlineStr">
+        <is>
+          <t>SFM-035.C1</t>
+        </is>
+      </c>
+      <c r="D67" s="34" t="inlineStr">
+        <is>
+          <t>Host code (car interface, pandad) emits a PCS-relevant ID or a non-zero PRE_COLLISION payload (QM fault)</t>
+        </is>
+      </c>
+      <c r="E67" s="34" t="inlineStr">
+        <is>
+          <t>The panda checks every frame from the SoC against the TX whitelist and the 0x283 zero-payload rule before it is sent</t>
+        </is>
+      </c>
+      <c r="F67" s="34" t="inlineStr">
+        <is>
+          <t>Frame refused, the stock PCS path is untouched; while engaged the refusal also gives pandaTxBlocked, an immediate disable with a take-over alert</t>
+        </is>
+      </c>
+      <c r="G67" s="34" t="inlineStr">
+        <is>
+          <t>Stock PCS unaffected. While engaged the item disengages with an alert (controlled handback, S 8), the worst effect left after the response</t>
+        </is>
+      </c>
+      <c r="H67" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="I67" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J67" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K67" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L67" s="34" t="inlineStr">
+        <is>
+          <t>SG-07 content (TX gate, block list) · per frame
+0 + 10 ms</t>
+        </is>
+      </c>
+      <c r="M67" s="33" t="inlineStr">
+        <is>
+          <t>code derived</t>
+        </is>
+      </c>
+      <c r="N67" s="34" t="inlineStr"/>
+      <c r="O67" s="37" t="inlineStr"/>
+      <c r="P67" s="37" t="inlineStr"/>
+    </row>
+    <row r="68" ht="73.5" customHeight="1">
+      <c r="A68" s="34" t="inlineStr">
+        <is>
+          <t>SFM-035 · Item sends a frame that alters the stock pre-collision function</t>
+        </is>
+      </c>
+      <c r="B68" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C68" s="33" t="inlineStr">
+        <is>
+          <t>SFM-035.C3</t>
+        </is>
+      </c>
+      <c r="D68" s="34" t="inlineStr">
+        <is>
+          <t>The TX whitelist or the PRE_COLLISION content check lets a PCS-relevant frame through (table change, or a build that is not the reference build, where 0x411 is allowed by design)</t>
+        </is>
+      </c>
+      <c r="E68" s="34" t="inlineStr">
+        <is>
+          <t>None: the gate is itself the monitor that has failed; pandaTxBlocked counts only refused frames</t>
+        </is>
+      </c>
+      <c r="F68" s="34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G68" s="34" t="inlineStr">
+        <is>
+          <t>Unchanged: the frame reaches the car while the SoC sends it</t>
+        </is>
+      </c>
+      <c r="H68" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I68" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="J68" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K68" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L68" s="34" t="inlineStr"/>
+      <c r="M68" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N68" s="34" t="inlineStr"/>
+      <c r="O68" s="37" t="inlineStr"/>
+      <c r="P68" s="37" t="inlineStr"/>
+    </row>
+    <row r="69" ht="73.5" customHeight="1">
+      <c r="A69" s="34" t="inlineStr">
+        <is>
+          <t>SFM-036 · Item keeps requesting acceleration while stock PCS brakes</t>
+        </is>
+      </c>
+      <c r="B69" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C69" s="33" t="inlineStr">
+        <is>
+          <t>SFM-036.C1</t>
+        </is>
+      </c>
+      <c r="D69" s="34" t="inlineStr">
+        <is>
+          <t>The item has no reaction to a stock PCS event on its longitudinal command; controlsd keeps requesting the planner's acceleration (design gap, FTA BE-7.13)</t>
+        </is>
+      </c>
+      <c r="E69" s="34" t="inlineStr">
+        <is>
+          <t>stockAeb detects the PCS event from the stock camera's PRE_COLLISION frame and raises an alert</t>
+        </is>
+      </c>
+      <c r="F69" s="34" t="inlineStr">
+        <is>
+          <t>Alert only; the longitudinal request continues until the driver brakes (panda revokes on the brake press)</t>
+        </is>
+      </c>
+      <c r="G69" s="34" t="inlineStr">
+        <is>
+          <t>Unchanged unless the PCM gives PCS priority (AOU-04R): the item may still oppose stock braking</t>
+        </is>
+      </c>
+      <c r="H69" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I69" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="J69" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="K69" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L69" s="34" t="inlineStr"/>
+      <c r="M69" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N69" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-020 · decision pending</t>
+        </is>
+      </c>
+      <c r="O69" s="37" t="inlineStr"/>
+      <c r="P69" s="37" t="inlineStr"/>
+    </row>
+    <row r="70" ht="46.5" customHeight="1">
+      <c r="A70" s="34" t="inlineStr">
+        <is>
+          <t>SFM-036 · Item keeps requesting acceleration while stock PCS brakes</t>
+        </is>
+      </c>
+      <c r="B70" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C70" s="33" t="inlineStr">
+        <is>
+          <t>SFM-036.C2</t>
+        </is>
+      </c>
+      <c r="D70" s="34" t="inlineStr">
+        <is>
+          <t>The PCM does not give stock PCS braking priority over the item's ACC_CONTROL request (AOU-04R not met)</t>
+        </is>
+      </c>
+      <c r="E70" s="34" t="inlineStr">
+        <is>
+          <t>None: the item cannot see how the PCM arbitrates</t>
+        </is>
+      </c>
+      <c r="F70" s="34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G70" s="34" t="inlineStr">
+        <is>
+          <t>Unchanged: stock braking reduced while the item requests acceleration</t>
+        </is>
+      </c>
+      <c r="H70" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I70" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="J70" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K70" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L70" s="34" t="inlineStr"/>
+      <c r="M70" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N70" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-020 · decision pending</t>
+        </is>
+      </c>
+      <c r="O70" s="37" t="inlineStr"/>
+      <c r="P70" s="37" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:P66"/>
+  <autoFilter ref="A2:P70"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="O3 O4 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 O34 O35 O36 O37 O38 O39 O40 O41 O42 O43 O44 O45 O46 O47 O48 O49 O50 O51 O52 O53 O54 O55 O56 O57 O58 O59 O60 O61 O62 O63 O64 O65 O66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this MSR row" type="list">
+    <dataValidation sqref="O3 O4 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 O34 O35 O36 O37 O38 O39 O40 O41 O42 O43 O44 O45 O46 O47 O48 O49 O50 O51 O52 O53 O54 O55 O56 O57 O58 O59 O60 O61 O62 O63 O64 O65 O66 O67 O68 O69 O70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this MSR row" type="list">
       <formula1>"Agree,Re-rate,Reject,Question"</formula1>
     </dataValidation>
   </dataValidations>
@@ -21224,7 +22226,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.12 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.13 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -820,7 +820,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.13 · draft</t>
+          <t>0.14 · draft</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="105" customHeight="1">
+    <row r="10" ht="120" customHeight="1">
       <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Scope</t>
@@ -868,7 +868,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>LionDriver as installed on the reference configuration CFG-001 (Corolla E210 · ZRE212 · US, US sedan MY2020-2022) with comma 3X and integrated panda, software BL-005 (structure and failure analysis written at BL-001, risk analysis at BL-004, MSR re-rated at BL-005), while the vehicle is driven on public roads by a licensed driver. Functions F1-F7 per fmea-plan.md section 3.1, plus F8 (stock vehicle safety functions are preserved), added because the harness intercepts the stock ADAS camera.</t>
+          <t>LionDriver as installed on the reference configuration CFG-001 (Corolla E210 · ZRE212 · US, US sedan MY2020-2022) with comma 3X and integrated panda, software BL-005 (structure and failure analysis written at BL-001, risk analysis at BL-004, MSR re-rated at BL-005), while the vehicle is driven by a licensed driver inside the ODD: limited-access highways only since WP-C-02 / WP-C-03 v0.4 (DQ-023). Functions F1-F7 per fmea-plan.md section 3.1, plus F8 (stock vehicle safety functions are preserved), added because the harness intercepts the stock ADAS camera.</t>
         </is>
       </c>
     </row>
@@ -11689,7 +11689,7 @@
       <c r="R62" s="45" t="inlineStr"/>
       <c r="S62" s="45" t="inlineStr"/>
     </row>
-    <row r="63" ht="114" customHeight="1">
+    <row r="63" ht="127.5" customHeight="1">
       <c r="A63" s="51" t="inlineStr">
         <is>
           <r>
@@ -11926,7 +11926,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Decide in the FSC how the item reacts when driver awareness reaches zero (driverUnresponsive3 / driverDistracted3 have no disable reaction at BL-004 or BL-005) and implement the decision. DQ-205 (answered) makes this the safe state of SG-010 (ASIL A); the reaction itself is still to be decided</t>
+            <t>Decide in the FSC how the item reacts when driver awareness reaches zero (driverUnresponsive3 / driverDistracted3 have no disable reaction at BL-004 or BL-005) and implement the decision. DQ-205 (answered) makes this the safe state of SG-010 (WP-C-03 SG-08, ASIL A); the reaction itself is still to be decided</t>
           </r>
         </is>
       </c>
@@ -16641,7 +16641,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.13 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.14 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -16875,7 +16875,7 @@
       </c>
       <c r="C5" s="60" t="inlineStr">
         <is>
-          <t>Decide in the FSC how the item reacts when driver awareness reaches zero (driverUnresponsive3 / driverDistracted3 have no disable reaction at BL-004 or BL-005) and implement the decision. DQ-205 (answered) makes this the safe state of SG-010 (ASIL A); the reaction itself is still to be decided</t>
+          <t>Decide in the FSC how the item reacts when driver awareness reaches zero (driverUnresponsive3 / driverDistracted3 have no disable reaction at BL-004 or BL-005) and implement the decision. DQ-205 (answered) makes this the safe state of SG-010 (WP-C-03 SG-08, ASIL A); the reaction itself is still to be decided</t>
         </is>
       </c>
       <c r="D5" s="60" t="inlineStr">
@@ -22226,7 +22226,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.13 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.14 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$87</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Worksheet'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Structure'!$A$1:$E$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'MSR'!$A$2:$P$70</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'MSR'!$1:$2</definedName>
@@ -820,7 +820,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.14 · draft</t>
+          <t>0.15 · draft</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>19 (18)</t>
+          <t>21 (19)</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>1–4: 0 · 5–6: 16 · 7–8: 17 · 9–10: 31 (see sheet MSR)</t>
+          <t>1–4: 0 · 5–6: 18 · 7–8: 15 · 9–10: 31 (see sheet MSR)</t>
         </is>
       </c>
     </row>
@@ -11689,7 +11689,7 @@
       <c r="R62" s="45" t="inlineStr"/>
       <c r="S62" s="45" t="inlineStr"/>
     </row>
-    <row r="63" ht="127.5" customHeight="1">
+    <row r="63" ht="195" customHeight="1">
       <c r="A63" s="51" t="inlineStr">
         <is>
           <r>
@@ -11926,7 +11926,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Decide in the FSC how the item reacts when driver awareness reaches zero (driverUnresponsive3 / driverDistracted3 have no disable reaction at BL-004 or BL-005) and implement the decision. DQ-205 (answered) makes this the safe state of SG-010 (WP-C-03 SG-08, ASIL A); the reaction itself is still to be decided</t>
+            <t>Decide in the FSC how the item reacts when driver awareness reaches zero (driverUnresponsive3 / driverDistracted3 have no disable reaction at BL-004 or BL-005) and implement the decision. DQ-205 (answered) makes this the safe state of SG-010 (WP-C-03 SG-08, ASIL A); the reaction itself is still to be decided. The requirement is TSR-633 (terminal reaction, ASIL A proposed) with TSR-611 (WP-S-02 §12.3a); the reaction is lead decision DQ-340. The H-09 FTTI is not yet set, so the timing rows of WP-S-04 §3.8.4 cannot be compared</t>
           </r>
         </is>
       </c>
@@ -16641,7 +16641,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.14 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.15 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -16656,7 +16656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16862,7 +16862,7 @@
       <c r="H4" s="60" t="inlineStr"/>
       <c r="I4" s="60" t="inlineStr"/>
     </row>
-    <row r="5" ht="73.5" customHeight="1">
+    <row r="5" ht="114" customHeight="1">
       <c r="A5" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-005</t>
@@ -16875,7 +16875,7 @@
       </c>
       <c r="C5" s="60" t="inlineStr">
         <is>
-          <t>Decide in the FSC how the item reacts when driver awareness reaches zero (driverUnresponsive3 / driverDistracted3 have no disable reaction at BL-004 or BL-005) and implement the decision. DQ-205 (answered) makes this the safe state of SG-010 (WP-C-03 SG-08, ASIL A); the reaction itself is still to be decided</t>
+          <t>Decide in the FSC how the item reacts when driver awareness reaches zero (driverUnresponsive3 / driverDistracted3 have no disable reaction at BL-004 or BL-005) and implement the decision. DQ-205 (answered) makes this the safe state of SG-010 (WP-C-03 SG-08, ASIL A); the reaction itself is still to be decided. The requirement is TSR-633 (terminal reaction, ASIL A proposed) with TSR-611 (WP-S-02 §12.3a); the reaction is lead decision DQ-340. The H-09 FTTI is not yet set, so the timing rows of WP-S-04 §3.8.4 cannot be compared</t>
         </is>
       </c>
       <c r="D5" s="60" t="inlineStr">
@@ -17163,7 +17163,7 @@
       <c r="H12" s="60" t="inlineStr"/>
       <c r="I12" s="60" t="inlineStr"/>
     </row>
-    <row r="13" ht="60" customHeight="1">
+    <row r="13" ht="87" customHeight="1">
       <c r="A13" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-013</t>
@@ -17176,7 +17176,7 @@
       </c>
       <c r="C13" s="60" t="inlineStr">
         <is>
-          <t>Check on the host, within the SG-01 FTTI, that the panda reports controls_allowed false while the item is disengaged (the reverse of the controlsMismatch check, which at BL-005 still covers only engaged with authority withdrawn), with a disable and an alert</t>
+          <t>Check on the host, within the SG-01 FTTI, that the panda reports controls_allowed false while the item is disengaged (the reverse of the controlsMismatch check, which at BL-005 still covers only engaged with authority withdrawn), with a disable and an alert. The requirement is TSR-630, within 0.3 s (WP-S-02 §12.3a; WP-S-04 T-32, not implemented)</t>
         </is>
       </c>
       <c r="D13" s="60" t="inlineStr"/>
@@ -17217,7 +17217,7 @@
       <c r="H14" s="60" t="inlineStr"/>
       <c r="I14" s="60" t="inlineStr"/>
     </row>
-    <row r="15" ht="87" customHeight="1">
+    <row r="15" ht="100.5" customHeight="1">
       <c r="A15" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-015</t>
@@ -17230,7 +17230,7 @@
       </c>
       <c r="C15" s="60" t="inlineStr">
         <is>
-          <t>Detect stale commands and inputs within the SG-01 FTTI: command-frame freshness in the MCU with an active zero frame (TSR-408, TSR-109) and frozen-content and age checks on model outputs in controlsd (TSR-602, AIR-17)</t>
+          <t>Detect stale commands and inputs within the SG-01 FTTI: command-frame freshness in the MCU with an active zero frame (TSR-408, TSR-109) and frozen-content and age checks on model outputs in controlsd (TSR-602, TSR-631, AIR-17)</t>
         </is>
       </c>
       <c r="D15" s="60" t="inlineStr"/>
@@ -17244,11 +17244,11 @@
       <c r="H15" s="60" t="inlineStr"/>
       <c r="I15" s="60" t="inlineStr">
         <is>
-          <t>BL-005: command-frame arrival in the MCU (TSR-408, 50 ms STEERING_LKA, reference build by default) and input age checks in controlsd (TSR-602) are in. Open: the active zero frame (TSR-109), a frozen-content check on model outputs, and stale data with fresh timestamps (SFM-006.C1 to C3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="60" customHeight="1">
+          <t>BL-005: command-frame arrival in the MCU (TSR-408, 50 ms STEERING_LKA, reference build by default) and input age checks in controlsd (TSR-602) are in. Open: the active zero frame (TSR-109), a frozen-content check on model outputs, and stale data with fresh timestamps (SFM-006.C1 to C3). The frozen-content check is TSR-631, with the age taken from the source timestamp (WP-S-02 §12.3a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="73.5" customHeight="1">
       <c r="A16" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-016</t>
@@ -17261,7 +17261,7 @@
       </c>
       <c r="C16" s="60" t="inlineStr">
         <is>
-          <t>Supervise driver override in the panda: driver steering torque above the override threshold limits or revokes lateral authority within the SG-05 0.2 s budget (TSR-304). Behaviour decided by the lead (DQ-053, option A): back off on override and show a cue</t>
+          <t>Supervise driver override in the panda: driver steering torque above the override threshold limits or revokes lateral authority within the SG-05 0.2 s budget (TSR-304). Behaviour decided by the lead (DQ-053, option A): back off on override and show a cue. Requirements: TSR-304 (timing tied to the SG-05 budget) and TSR-628 (WP-S-02 §12.3a)</t>
         </is>
       </c>
       <c r="D16" s="60" t="inlineStr"/>
@@ -17275,7 +17275,7 @@
       <c r="H16" s="60" t="inlineStr"/>
       <c r="I16" s="60" t="inlineStr"/>
     </row>
-    <row r="17" ht="60" customHeight="1">
+    <row r="17" ht="87" customHeight="1">
       <c r="A17" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-017</t>
@@ -17292,17 +17292,21 @@
         </is>
       </c>
       <c r="D17" s="60" t="inlineStr"/>
-      <c r="E17" s="60" t="inlineStr">
-        <is>
-          <t>open</t>
+      <c r="E17" s="61" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="F17" s="60" t="inlineStr"/>
       <c r="G17" s="60" t="inlineStr"/>
       <c r="H17" s="60" t="inlineStr"/>
-      <c r="I17" s="60" t="inlineStr"/>
-    </row>
-    <row r="18" ht="73.5" customHeight="1">
+      <c r="I17" s="60" t="inlineStr">
+        <is>
+          <t>WP-S-04 v0.7 §3.7 (four rows) and §3.8, with T-30 to T-33. Rev 0.15 compares SFM-004, SFM-010.C2/C3, SFM-012.C1 and SFM-013.C1/C2 with them. Driver monitoring (SFM-022.C3, SFM-025.C1) waits for the H-09 FTTI (§3.8.4); follow-up is SFM-ACT-005. Late warnings found: SFM-ACT-021 (lateral) and SFM-ACT-022 (braking)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="100.5" customHeight="1">
       <c r="A18" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-018</t>
@@ -17329,7 +17333,7 @@
       <c r="H18" s="60" t="inlineStr"/>
       <c r="I18" s="60" t="inlineStr">
         <is>
-          <t>BL-005: frames that stop reaching the panda are detected (TSR-408) and alerted within 0.5 s (TSR-621), credited on SFM-005.C2 and SFM-011.C2. Open: frames that reach the panda but are not accepted by the EPS or PCM (SFM-005.C1, SFM-011.C1; TSR-626)</t>
+          <t>BL-005: frames that stop reaching the panda are detected (TSR-408) and alerted within 0.5 s (TSR-621), credited on SFM-005.C2 and SFM-011.C2. Open: frames that reach the panda but are not accepted by the EPS or PCM (SFM-005.C1, SFM-011.C1). Requirements: TSR-632 (per-ID transmitted and refused counts), TSR-626(d)/(e) (EPS and PCM acceptance status) and TSR-615, warning within 1 s (WP-S-02 §12.3a)</t>
         </is>
       </c>
     </row>
@@ -17397,8 +17401,62 @@
       <c r="H20" s="60" t="inlineStr"/>
       <c r="I20" s="60" t="inlineStr"/>
     </row>
+    <row r="21" ht="73.5" customHeight="1">
+      <c r="A21" s="60" t="inlineStr">
+        <is>
+          <t>SFM-ACT-021</t>
+        </is>
+      </c>
+      <c r="B21" s="60" t="inlineStr">
+        <is>
+          <t>monitoring</t>
+        </is>
+      </c>
+      <c r="C21" s="60" t="inlineStr">
+        <is>
+          <t>Make the insufficient-lateral-control warning timely (WP-S-04 §3.8.1): warn before the deficit has lasted 0.4 s, for example from the planned curvature against the envelope, or keep the deficit at or below about 0.5 m/s² through the steering limits and the ODD curve bound (WP-S-04 OI-2). A change to the ODD bound is a lead decision</t>
+        </is>
+      </c>
+      <c r="D21" s="60" t="inlineStr"/>
+      <c r="E21" s="60" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F21" s="60" t="inlineStr"/>
+      <c r="G21" s="60" t="inlineStr"/>
+      <c r="H21" s="60" t="inlineStr"/>
+      <c r="I21" s="60" t="inlineStr"/>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="60" t="inlineStr">
+        <is>
+          <t>SFM-ACT-022</t>
+        </is>
+      </c>
+      <c r="B22" s="60" t="inlineStr">
+        <is>
+          <t>monitoring</t>
+        </is>
+      </c>
+      <c r="C22" s="60" t="inlineStr">
+        <is>
+          <t>Measure the FCW onset after a lead brakes hard (WP-S-04 T-31, M-12) and compare it with the §3.8.2 budget (about 0.6 s at a 1.0 s gap). For pipeline lag (SFM-012.C1), detect it within that budget or show that the FCW path does not depend on the lagging process</t>
+        </is>
+      </c>
+      <c r="D22" s="60" t="inlineStr"/>
+      <c r="E22" s="60" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F22" s="60" t="inlineStr"/>
+      <c r="G22" s="60" t="inlineStr"/>
+      <c r="H22" s="60" t="inlineStr"/>
+      <c r="I22" s="60" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I20"/>
+  <autoFilter ref="A1:I22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18734,7 +18792,7 @@
       </c>
       <c r="G14" s="34" t="inlineStr">
         <is>
-          <t>Driver warned and takes over; no FTTI defined for the warning path</t>
+          <t>Driver warned and takes over; in time only for a deficit of about 0.5 m/s² or less (WP-S-04 §3.8.1)</t>
         </is>
       </c>
       <c r="H14" s="35" t="n">
@@ -18744,22 +18802,28 @@
         <v>6</v>
       </c>
       <c r="J14" s="35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K14" s="36" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="L14" s="34" t="inlineStr"/>
+      <c r="L14" s="34" t="inlineStr">
+        <is>
+          <t>SG-02 insufficient lateral control (warning path, §3.8.1) · 1100 ms
+400 + 100 ms</t>
+        </is>
+      </c>
       <c r="M14" s="33" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>code derived</t>
         </is>
       </c>
       <c r="N14" s="34" t="inlineStr">
         <is>
-          <t>SFM-ACT-017 · open</t>
+          <t>SFM-ACT-017 · completed
+SFM-ACT-021 · open</t>
         </is>
       </c>
       <c r="O14" s="37" t="inlineStr"/>
@@ -18796,7 +18860,7 @@
       </c>
       <c r="G15" s="34" t="inlineStr">
         <is>
-          <t>Driver warned and takes over; no FTTI defined for the warning path</t>
+          <t>Driver warned and takes over; in time only for a deficit of about 0.5 m/s² or less (WP-S-04 §3.8.1)</t>
         </is>
       </c>
       <c r="H15" s="35" t="n">
@@ -18806,22 +18870,28 @@
         <v>5</v>
       </c>
       <c r="J15" s="35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="L15" s="34" t="inlineStr"/>
+      <c r="L15" s="34" t="inlineStr">
+        <is>
+          <t>SG-02 insufficient lateral control (warning path, §3.8.1) · 1100 ms
+400 + 100 ms</t>
+        </is>
+      </c>
       <c r="M15" s="33" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>code derived</t>
         </is>
       </c>
       <c r="N15" s="34" t="inlineStr">
         <is>
-          <t>SFM-ACT-017 · open</t>
+          <t>SFM-ACT-017 · completed
+SFM-ACT-021 · open</t>
         </is>
       </c>
       <c r="O15" s="37" t="inlineStr"/>
@@ -18858,7 +18928,7 @@
       </c>
       <c r="G16" s="34" t="inlineStr">
         <is>
-          <t>Driver warned and takes over; no FTTI defined for the warning path</t>
+          <t>Driver warned and takes over; in time only for a deficit of about 0.5 m/s² or less (WP-S-04 §3.8.1)</t>
         </is>
       </c>
       <c r="H16" s="35" t="n">
@@ -18868,22 +18938,28 @@
         <v>6</v>
       </c>
       <c r="J16" s="35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="L16" s="34" t="inlineStr"/>
+      <c r="L16" s="34" t="inlineStr">
+        <is>
+          <t>SG-02 insufficient lateral control (warning path, §3.8.1) · 1100 ms
+400 + 100 ms</t>
+        </is>
+      </c>
       <c r="M16" s="33" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>code derived</t>
         </is>
       </c>
       <c r="N16" s="34" t="inlineStr">
         <is>
-          <t>SFM-ACT-017 · open</t>
+          <t>SFM-ACT-017 · completed
+SFM-ACT-021 · open</t>
         </is>
       </c>
       <c r="O16" s="37" t="inlineStr"/>
@@ -19789,7 +19865,7 @@
       <c r="O30" s="37" t="inlineStr"/>
       <c r="P30" s="37" t="inlineStr"/>
     </row>
-    <row r="31" ht="46.5" customHeight="1">
+    <row r="31" ht="73.5" customHeight="1">
       <c r="A31" s="34" t="inlineStr">
         <is>
           <t>SFM-010 · Insufficient deceleration for lead vehicle or stop</t>
@@ -19820,7 +19896,7 @@
       </c>
       <c r="G31" s="34" t="inlineStr">
         <is>
-          <t>Driver warned; no FTTI compared</t>
+          <t>Driver warned; FCW must sound within about 0.6 s of the lead braking at a 1.0 s gap (WP-S-04 §3.8.2), its onset is not derived (T-31, to be measured as M-12)</t>
         </is>
       </c>
       <c r="H31" s="35" t="n">
@@ -19837,7 +19913,11 @@
           <t>H</t>
         </is>
       </c>
-      <c r="L31" s="34" t="inlineStr"/>
+      <c r="L31" s="34" t="inlineStr">
+        <is>
+          <t>SG-06 late or insufficient braking warning (FCW, §3.8.2) · 1600 ms</t>
+        </is>
+      </c>
       <c r="M31" s="33" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -19846,13 +19926,13 @@
       <c r="N31" s="34" t="inlineStr">
         <is>
           <t>SFM-ACT-006 · open
-SFM-ACT-017 · open</t>
+SFM-ACT-022 · open</t>
         </is>
       </c>
       <c r="O31" s="37" t="inlineStr"/>
       <c r="P31" s="37" t="inlineStr"/>
     </row>
-    <row r="32" ht="46.5" customHeight="1">
+    <row r="32" ht="73.5" customHeight="1">
       <c r="A32" s="34" t="inlineStr">
         <is>
           <t>SFM-010 · Insufficient deceleration for lead vehicle or stop</t>
@@ -19883,7 +19963,7 @@
       </c>
       <c r="G32" s="34" t="inlineStr">
         <is>
-          <t>Driver warned; no FTTI compared</t>
+          <t>Driver warned; FCW must sound within about 0.6 s of the lead braking at a 1.0 s gap (WP-S-04 §3.8.2), its onset is not derived (T-31, to be measured as M-12)</t>
         </is>
       </c>
       <c r="H32" s="35" t="n">
@@ -19900,7 +19980,11 @@
           <t>H</t>
         </is>
       </c>
-      <c r="L32" s="34" t="inlineStr"/>
+      <c r="L32" s="34" t="inlineStr">
+        <is>
+          <t>SG-06 late or insufficient braking warning (FCW, §3.8.2) · 1600 ms</t>
+        </is>
+      </c>
       <c r="M32" s="33" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -19909,7 +19993,7 @@
       <c r="N32" s="34" t="inlineStr">
         <is>
           <t>SFM-ACT-003 · open
-SFM-ACT-017 · open</t>
+SFM-ACT-022 · open</t>
         </is>
       </c>
       <c r="O32" s="37" t="inlineStr"/>
@@ -20045,7 +20129,7 @@
       <c r="O34" s="37" t="inlineStr"/>
       <c r="P34" s="37" t="inlineStr"/>
     </row>
-    <row r="35" ht="46.5" customHeight="1">
+    <row r="35" ht="60" customHeight="1">
       <c r="A35" s="34" t="inlineStr">
         <is>
           <t>SFM-012 · Late reaction to lead vehicle braking</t>
@@ -20076,7 +20160,7 @@
       </c>
       <c r="G35" s="34" t="inlineStr">
         <is>
-          <t>Driver warned; no FTTI compared for late reaction</t>
+          <t>Driver warned only after the lag is averaged (about 1 s) and the 3 s soft disable; FCW is the remaining warning</t>
         </is>
       </c>
       <c r="H35" s="35" t="n">
@@ -20086,7 +20170,7 @@
         <v>6</v>
       </c>
       <c r="J35" s="35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K35" s="36" t="inlineStr">
         <is>
@@ -20095,7 +20179,8 @@
       </c>
       <c r="L35" s="34" t="inlineStr">
         <is>
-          <t>1000 + 3000 ms</t>
+          <t>SG-06 late or insufficient braking warning (FCW, §3.8.2) · 1600 ms
+1000 + 3000 ms</t>
         </is>
       </c>
       <c r="M35" s="33" t="inlineStr">
@@ -20105,7 +20190,7 @@
       </c>
       <c r="N35" s="34" t="inlineStr">
         <is>
-          <t>SFM-ACT-017 · open</t>
+          <t>SFM-ACT-022 · open</t>
         </is>
       </c>
       <c r="O35" s="37" t="inlineStr"/>
@@ -20194,7 +20279,7 @@
       </c>
       <c r="E37" s="34" t="inlineStr">
         <is>
-          <t>Panda grants control only on the PCM cruise engage edge read from the car bus, so a wrong host state alone does not grant actuation; frames are refused on every cycle. WP-S-04 has no FTTI row for SG-008, so the timing is not compared</t>
+          <t>Panda grants control only on the PCM cruise engage edge read from the car bus, so a wrong host state alone does not grant actuation; frames are refused on every cycle; within the 0.5 s unintended-engagement budget (WP-S-04 §3.8.3)</t>
         </is>
       </c>
       <c r="F37" s="34" t="inlineStr">
@@ -20214,7 +20299,7 @@
         <v>6</v>
       </c>
       <c r="J37" s="35" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K37" s="36" t="inlineStr">
         <is>
@@ -20223,7 +20308,8 @@
       </c>
       <c r="L37" s="34" t="inlineStr">
         <is>
-          <t>0 + 10 ms</t>
+          <t>SG-01 / SG-03 unintended engagement (System FMEA SG-008, §3.8.3) · 500 ms
+0 + 10 ms</t>
         </is>
       </c>
       <c r="M37" s="33" t="inlineStr">
@@ -20233,13 +20319,13 @@
       </c>
       <c r="N37" s="34" t="inlineStr">
         <is>
-          <t>SFM-ACT-017 · open</t>
+          <t>SFM-ACT-013 · open</t>
         </is>
       </c>
       <c r="O37" s="37" t="inlineStr"/>
       <c r="P37" s="37" t="inlineStr"/>
     </row>
-    <row r="38" ht="60" customHeight="1">
+    <row r="38" ht="73.5" customHeight="1">
       <c r="A38" s="34" t="inlineStr">
         <is>
           <t>SFM-013 · Engagement without driver request or with entry conditions not met</t>
@@ -20260,7 +20346,7 @@
       </c>
       <c r="E38" s="34" t="inlineStr">
         <is>
-          <t>Panda parses the PCM cruise state itself and grants control only on its engage edge; a host parsing error does not grant actuation. No SG-008 FTTI row in WP-S-04</t>
+          <t>Panda parses the PCM cruise state itself and grants control only on its engage edge; a host parsing error does not grant actuation; within the 0.5 s unintended-engagement budget (WP-S-04 §3.8.3)</t>
         </is>
       </c>
       <c r="F38" s="34" t="inlineStr">
@@ -20280,7 +20366,7 @@
         <v>6</v>
       </c>
       <c r="J38" s="35" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K38" s="36" t="inlineStr">
         <is>
@@ -20289,7 +20375,8 @@
       </c>
       <c r="L38" s="34" t="inlineStr">
         <is>
-          <t>0 + 10 ms</t>
+          <t>SG-01 / SG-03 unintended engagement (System FMEA SG-008, §3.8.3) · 500 ms
+0 + 10 ms</t>
         </is>
       </c>
       <c r="M38" s="33" t="inlineStr">
@@ -20299,7 +20386,7 @@
       </c>
       <c r="N38" s="34" t="inlineStr">
         <is>
-          <t>SFM-ACT-017 · open</t>
+          <t>SFM-ACT-013 · open</t>
         </is>
       </c>
       <c r="O38" s="37" t="inlineStr"/>
@@ -21328,7 +21415,7 @@
       </c>
       <c r="G55" s="34" t="inlineStr">
         <is>
-          <t>Driver monitored by wheel touch; no FTTI defined for DM</t>
+          <t>Driver monitored by wheel touch; no FTTI until the H-09 goal has one (WP-S-04 §3.8.4)</t>
         </is>
       </c>
       <c r="H55" s="35" t="n">
@@ -21353,7 +21440,7 @@
       </c>
       <c r="N55" s="34" t="inlineStr">
         <is>
-          <t>SFM-ACT-017 · open</t>
+          <t>SFM-ACT-005 · decision pending</t>
         </is>
       </c>
       <c r="O55" s="37" t="inlineStr"/>
@@ -22226,7 +22313,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.14 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.15 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -261,7 +261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -399,6 +399,9 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -820,7 +823,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.15 · draft</t>
+          <t>0.16 · draft</t>
         </is>
       </c>
     </row>
@@ -868,7 +871,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>LionDriver as installed on the reference configuration CFG-001 (Corolla E210 · ZRE212 · US, US sedan MY2020-2022) with comma 3X and integrated panda, software BL-005 (structure and failure analysis written at BL-001, risk analysis at BL-004, MSR re-rated at BL-005), while the vehicle is driven by a licensed driver inside the ODD: limited-access highways only since WP-C-02 / WP-C-03 v0.4 (DQ-023). Functions F1-F7 per fmea-plan.md section 3.1, plus F8 (stock vehicle safety functions are preserved), added because the harness intercepts the stock ADAS camera.</t>
+          <t>LionDriver as installed on the reference configuration CFG-001 (Corolla E210 · ZRE212 · US, US sedan MY2020-2022) with comma 3X and integrated panda, software BL-005 (structure and failure analysis written at BL-001, risk analysis at BL-004, MSR re-rated at BL-005), while the vehicle is driven by a licensed driver inside the ODD: limited-access highways only since WP-C-02 / WP-C-03 v0.4 (DQ-023), up to 110 km/h (DQ-260). Functions F1-F7 per fmea-plan.md section 3.1, plus F8 (stock vehicle safety functions are preserved), added because the harness intercepts the stock ADAS camera.</t>
         </is>
       </c>
     </row>
@@ -918,7 +921,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17">
@@ -938,7 +941,7 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -8938,7 +8941,7 @@
       <c r="R47" s="37" t="inlineStr"/>
       <c r="S47" s="37" t="inlineStr"/>
     </row>
-    <row r="48" ht="73.5" customHeight="1">
+    <row r="48" ht="100.5" customHeight="1">
       <c r="A48" s="39" t="n"/>
       <c r="B48" s="39" t="n"/>
       <c r="C48" s="39" t="n"/>
@@ -8958,7 +8961,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Debounce/counters too long (e.g. excessive actuation 0.25 s, mismatch counter 200 frames)</t>
+            <t>Debounce or counters too long (e.g. excessive actuation 0.25 s); at BL-005 a defect in the controlsMismatch supervision (2 consecutive samples, at most 0.5 s, TSR-621), which replaced the upstream 200-frame counter</t>
           </r>
           <r>
             <rPr>
@@ -8979,7 +8982,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Upstream threshold; TSR-621 records it as partial</t>
+            <t>• New LionDriver supervision code (#51, TSR-621); rated in the SW FMEA</t>
           </r>
           <r>
             <rPr>
@@ -8988,27 +8991,36 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   openpilot/selfdrive/selfdrived/selfdrived.py:504-514</t>
+   openpilot/selfdrive/selfdrived/supervision.py</t>
           </r>
         </is>
       </c>
       <c r="J48" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="K48" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_supervision.py targets the cause (consecutive samples, 0.5 s bound, engagement grace); not run in CI at BL-005 and not proven by mutation (SWF-ACT-055)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/selfdrived/tests/test_supervision.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L48" s="42" t="n">
         <v>8</v>
-      </c>
-      <c r="K48" s="41" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• No test targets this cause</t>
-          </r>
-        </is>
-      </c>
-      <c r="L48" s="43" t="n">
-        <v>10</v>
       </c>
       <c r="M48" s="44" t="inlineStr">
         <is>
@@ -13178,7 +13190,7 @@
       <c r="R70" s="45" t="inlineStr"/>
       <c r="S70" s="45" t="inlineStr"/>
     </row>
-    <row r="71" ht="73.5" customHeight="1">
+    <row r="71" ht="114" customHeight="1">
       <c r="A71" s="30" t="inlineStr">
         <is>
           <r>
@@ -13415,7 +13427,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Panda safety code: MISRA C:2012, 100% line coverage, review; rated in the SW FMEA</t>
+            <t>• The openpilot build and the release script select the reference build (LIONDRIVER_REFERENCE=1) by default, and pandad sets a car mode only on a panda that reports it (TSR-619); rated in the SW FMEA</t>
           </r>
           <r>
             <rPr>
@@ -13429,17 +13441,17 @@
         </is>
       </c>
       <c r="J71" s="35" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K71" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• As rated in the SW FMEA: no test covers the build configuration</t>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• CI job panda_reference_release_build checks every firmware compile for -DLIONDRIVER_REFERENCE; host test of the reference-build health flag. Checks the build configuration, not the signed release image (PFMEA PFM-001)</t>
           </r>
           <r>
             <rPr>
@@ -13448,16 +13460,16 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   assurance/08-analyses/fmea/analyses/sw-fmea.yaml</t>
-          </r>
-        </is>
-      </c>
-      <c r="L71" s="46" t="n">
-        <v>9</v>
-      </c>
-      <c r="M71" s="36" t="inlineStr">
-        <is>
-          <t>H</t>
+   .github/workflows/safety.yaml</t>
+          </r>
+        </is>
+      </c>
+      <c r="L71" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="M71" s="58" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="N71" s="34" t="inlineStr">
@@ -13477,7 +13489,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Rated, and actioned where needed, in the SW FMEA (SWF-013.C2 O8 D9, SWF-ACT-009; open LionDriver#36/#41 set and check the reference build); this row inherits that rating</t>
+            <t>Rated, and actioned, in the SW FMEA (SWF-013.C2 O3 D4 at BL-005, SWF-ACT-009 completed); this row inherits that rating</t>
           </r>
         </is>
       </c>
@@ -16343,7 +16355,7 @@
           </r>
         </is>
       </c>
-      <c r="O86" s="58" t="inlineStr">
+      <c r="O86" s="59" t="inlineStr">
         <is>
           <t>decision pending</t>
         </is>
@@ -16641,7 +16653,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.15 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.16 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -16671,79 +16683,79 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="59" t="inlineStr">
+      <c r="A1" s="60" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B1" s="59" t="inlineStr">
+      <c r="B1" s="60" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="C1" s="59" t="inlineStr">
+      <c r="C1" s="60" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" s="59" t="inlineStr">
+      <c r="D1" s="60" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E1" s="59" t="inlineStr">
+      <c r="E1" s="60" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="59" t="inlineStr">
+      <c r="F1" s="60" t="inlineStr">
         <is>
           <t>Causes</t>
         </is>
       </c>
-      <c r="G1" s="59" t="inlineStr">
+      <c r="G1" s="60" t="inlineStr">
         <is>
           <t>Revised S/O/D</t>
         </is>
       </c>
-      <c r="H1" s="59" t="inlineStr">
+      <c r="H1" s="60" t="inlineStr">
         <is>
           <t>Revised AP</t>
         </is>
       </c>
-      <c r="I1" s="59" t="inlineStr">
+      <c r="I1" s="60" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
     </row>
     <row r="2" ht="127.5" customHeight="1">
-      <c r="A2" s="60" t="inlineStr">
+      <c r="A2" s="61" t="inlineStr">
         <is>
           <t>SFM-ACT-001</t>
         </is>
       </c>
-      <c r="B2" s="60" t="inlineStr">
+      <c r="B2" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C2" s="60" t="inlineStr">
+      <c r="C2" s="61" t="inlineStr">
         <is>
           <t>Derive steering and acceleration envelopes from measurements on the reference vehicle and set the panda limits from them, independently of the SoC limits (same as SWF-ACT-003, FSC FOI-001)</t>
         </is>
       </c>
-      <c r="D2" s="60" t="inlineStr">
+      <c r="D2" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E2" s="60" t="inlineStr">
+      <c r="E2" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F2" s="60" t="inlineStr">
+      <c r="F2" s="61" t="inlineStr">
         <is>
           <t>SFM-002.C1
 SFM-002.C2
@@ -16756,37 +16768,37 @@
 SFM-029.C2</t>
         </is>
       </c>
-      <c r="G2" s="60" t="inlineStr"/>
-      <c r="H2" s="60" t="inlineStr"/>
-      <c r="I2" s="60" t="inlineStr"/>
+      <c r="G2" s="61" t="inlineStr"/>
+      <c r="H2" s="61" t="inlineStr"/>
+      <c r="I2" s="61" t="inlineStr"/>
     </row>
     <row r="3" ht="127.5" customHeight="1">
-      <c r="A3" s="60" t="inlineStr">
+      <c r="A3" s="61" t="inlineStr">
         <is>
           <t>SFM-ACT-002</t>
         </is>
       </c>
-      <c r="B3" s="60" t="inlineStr">
+      <c r="B3" s="61" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C3" s="60" t="inlineStr">
+      <c r="C3" s="61" t="inlineStr">
         <is>
           <t>Requirements-based tests for the host safety-relevant functions (selfdrived, controlsd, pandad, car interface, locationd bounds, monitoring policy), proven by mutation or fault injection and run as a CI gate (see SWF host actions)</t>
         </is>
       </c>
-      <c r="D3" s="60" t="inlineStr">
+      <c r="D3" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E3" s="60" t="inlineStr">
+      <c r="E3" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F3" s="60" t="inlineStr">
+      <c r="F3" s="61" t="inlineStr">
         <is>
           <t>SFM-002.C4
 SFM-004.C3
@@ -16799,37 +16811,37 @@
 SFM-030.C1</t>
         </is>
       </c>
-      <c r="G3" s="60" t="inlineStr"/>
-      <c r="H3" s="60" t="inlineStr"/>
-      <c r="I3" s="60" t="inlineStr"/>
+      <c r="G3" s="61" t="inlineStr"/>
+      <c r="H3" s="61" t="inlineStr"/>
+      <c r="I3" s="61" t="inlineStr"/>
     </row>
     <row r="4" ht="343.5" customHeight="1">
-      <c r="A4" s="60" t="inlineStr">
+      <c r="A4" s="61" t="inlineStr">
         <is>
           <t>SFM-ACT-003</t>
         </is>
       </c>
-      <c r="B4" s="60" t="inlineStr">
+      <c r="B4" s="61" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C4" s="60" t="inlineStr">
+      <c r="C4" s="61" t="inlineStr">
         <is>
           <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
         </is>
       </c>
-      <c r="D4" s="60" t="inlineStr">
+      <c r="D4" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E4" s="60" t="inlineStr">
+      <c r="E4" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F4" s="60" t="inlineStr">
+      <c r="F4" s="61" t="inlineStr">
         <is>
           <t>SFM-003.C1
 SFM-003.C2
@@ -16858,72 +16870,72 @@
 SFM-033.C3</t>
         </is>
       </c>
-      <c r="G4" s="60" t="inlineStr"/>
-      <c r="H4" s="60" t="inlineStr"/>
-      <c r="I4" s="60" t="inlineStr"/>
+      <c r="G4" s="61" t="inlineStr"/>
+      <c r="H4" s="61" t="inlineStr"/>
+      <c r="I4" s="61" t="inlineStr"/>
     </row>
     <row r="5" ht="114" customHeight="1">
-      <c r="A5" s="60" t="inlineStr">
+      <c r="A5" s="61" t="inlineStr">
         <is>
           <t>SFM-ACT-005</t>
         </is>
       </c>
-      <c r="B5" s="60" t="inlineStr">
+      <c r="B5" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C5" s="60" t="inlineStr">
+      <c r="C5" s="61" t="inlineStr">
         <is>
           <t>Decide in the FSC how the item reacts when driver awareness reaches zero (driverUnresponsive3 / driverDistracted3 have no disable reaction at BL-004 or BL-005) and implement the decision. DQ-205 (answered) makes this the safe state of SG-010 (WP-C-03 SG-08, ASIL A); the reaction itself is still to be decided. The requirement is TSR-633 (terminal reaction, ASIL A proposed) with TSR-611 (WP-S-02 §12.3a); the reaction is lead decision DQ-340. The H-09 FTTI is not yet set, so the timing rows of WP-S-04 §3.8.4 cannot be compared</t>
         </is>
       </c>
-      <c r="D5" s="60" t="inlineStr">
+      <c r="D5" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E5" s="60" t="inlineStr">
+      <c r="E5" s="61" t="inlineStr">
         <is>
           <t>decision pending</t>
         </is>
       </c>
-      <c r="F5" s="60" t="inlineStr">
+      <c r="F5" s="61" t="inlineStr">
         <is>
           <t>SFM-025.C1</t>
         </is>
       </c>
-      <c r="G5" s="60" t="inlineStr"/>
-      <c r="H5" s="60" t="inlineStr"/>
-      <c r="I5" s="60" t="inlineStr"/>
+      <c r="G5" s="61" t="inlineStr"/>
+      <c r="H5" s="61" t="inlineStr"/>
+      <c r="I5" s="61" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="60" t="inlineStr">
+      <c r="A6" s="61" t="inlineStr">
         <is>
           <t>SFM-ACT-006</t>
         </is>
       </c>
-      <c r="B6" s="60" t="inlineStr">
+      <c r="B6" s="61" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C6" s="60" t="inlineStr">
+      <c r="C6" s="61" t="inlineStr">
         <is>
           <t>Establish on the reference car which stock TSS2 functions (PCS/AEB, FCW) remain available with LionDriver installed and longitudinal control enabled, and verify the stock pre-collision path after installation (PFMEA PFM-014)</t>
         </is>
       </c>
-      <c r="D6" s="60" t="inlineStr">
+      <c r="D6" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E6" s="60" t="inlineStr">
+      <c r="E6" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F6" s="60" t="inlineStr">
+      <c r="F6" s="61" t="inlineStr">
         <is>
           <t>SFM-010.C2
 SFM-033.C1
@@ -16931,37 +16943,37 @@
 SFM-036.C2</t>
         </is>
       </c>
-      <c r="G6" s="60" t="inlineStr"/>
-      <c r="H6" s="60" t="inlineStr"/>
-      <c r="I6" s="60" t="inlineStr"/>
+      <c r="G6" s="61" t="inlineStr"/>
+      <c r="H6" s="61" t="inlineStr"/>
+      <c r="I6" s="61" t="inlineStr"/>
     </row>
     <row r="7" ht="73.5" customHeight="1">
-      <c r="A7" s="60" t="inlineStr">
+      <c r="A7" s="61" t="inlineStr">
         <is>
           <t>SFM-ACT-007</t>
         </is>
       </c>
-      <c r="B7" s="60" t="inlineStr">
+      <c r="B7" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C7" s="60" t="inlineStr">
+      <c r="C7" s="61" t="inlineStr">
         <is>
           <t>Supervise the alert channels: treat loss of ui or soundd liveness, or a stale displayed state, as a fault that escalates (audible fallback, disengagement) instead of continuing silently</t>
         </is>
       </c>
-      <c r="D7" s="60" t="inlineStr">
+      <c r="D7" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E7" s="60" t="inlineStr">
+      <c r="E7" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F7" s="60" t="inlineStr">
+      <c r="F7" s="61" t="inlineStr">
         <is>
           <t>SFM-015.C1
 SFM-026.C1
@@ -16970,76 +16982,76 @@
 SFM-028.C1</t>
         </is>
       </c>
-      <c r="G7" s="60" t="inlineStr"/>
-      <c r="H7" s="60" t="inlineStr"/>
-      <c r="I7" s="60" t="inlineStr"/>
+      <c r="G7" s="61" t="inlineStr"/>
+      <c r="H7" s="61" t="inlineStr"/>
+      <c r="I7" s="61" t="inlineStr"/>
     </row>
     <row r="8" ht="73.5" customHeight="1">
-      <c r="A8" s="60" t="inlineStr">
+      <c r="A8" s="61" t="inlineStr">
         <is>
           <t>SFM-ACT-008</t>
         </is>
       </c>
-      <c r="B8" s="60" t="inlineStr">
+      <c r="B8" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C8" s="60" t="inlineStr">
+      <c r="C8" s="61" t="inlineStr">
         <is>
           <t>Allow engagement only when the fingerprint, CarParams and panda safety parameter match the reference configuration AC-001 (refuse fuzzy matches in the reference build); see PFMEA PFM-013</t>
         </is>
       </c>
-      <c r="D8" s="60" t="inlineStr">
+      <c r="D8" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E8" s="60" t="inlineStr">
+      <c r="E8" s="61" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F8" s="60" t="inlineStr">
+      <c r="F8" s="61" t="inlineStr">
         <is>
           <t>SFM-032.C1</t>
         </is>
       </c>
-      <c r="G8" s="60" t="inlineStr"/>
-      <c r="H8" s="60" t="inlineStr"/>
-      <c r="I8" s="60" t="inlineStr">
+      <c r="G8" s="61" t="inlineStr"/>
+      <c r="H8" s="61" t="inlineStr"/>
+      <c r="I8" s="61" t="inlineStr">
         <is>
           <t>BL-005: the reference build is the default (LionDriver #36), the panda accepts only TOYOTA parameter 73 (reference_lock.h) and pandad configures a car mode only on a reference panda (#41). Fuzzy fingerprint matches are still accepted on the host (SFM-032.C1)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="100.5" customHeight="1">
-      <c r="A9" s="60" t="inlineStr">
+      <c r="A9" s="61" t="inlineStr">
         <is>
           <t>SFM-ACT-009</t>
         </is>
       </c>
-      <c r="B9" s="60" t="inlineStr">
+      <c r="B9" s="61" t="inlineStr">
         <is>
           <t>prevention</t>
         </is>
       </c>
-      <c r="C9" s="60" t="inlineStr">
+      <c r="C9" s="61" t="inlineStr">
         <is>
           <t>Produce SOTIF / ISO PAS 8800 evidence for the neural-network elements (driving model, lead detection, driver monitoring model) per WP-V-02..04, including fault-induced inputs (corrupted or stale frames)</t>
         </is>
       </c>
-      <c r="D9" s="60" t="inlineStr">
+      <c r="D9" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E9" s="60" t="inlineStr">
+      <c r="E9" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F9" s="60" t="inlineStr">
+      <c r="F9" s="61" t="inlineStr">
         <is>
           <t>SFM-002.C2
 SFM-003.C3
@@ -17050,37 +17062,37 @@
 SFM-022.C2</t>
         </is>
       </c>
-      <c r="G9" s="60" t="inlineStr"/>
-      <c r="H9" s="60" t="inlineStr"/>
-      <c r="I9" s="60" t="inlineStr"/>
+      <c r="G9" s="61" t="inlineStr"/>
+      <c r="H9" s="61" t="inlineStr"/>
+      <c r="I9" s="61" t="inlineStr"/>
     </row>
     <row r="10" ht="73.5" customHeight="1">
-      <c r="A10" s="60" t="inlineStr">
+      <c r="A10" s="61" t="inlineStr">
         <is>
           <t>SFM-ACT-010</t>
         </is>
       </c>
-      <c r="B10" s="60" t="inlineStr">
+      <c r="B10" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C10" s="60" t="inlineStr">
+      <c r="C10" s="61" t="inlineStr">
         <is>
           <t>Justify every SOFT_DISABLE reaction and debounce against the FTTI (WP-S-04) and alert at once when the panda withdraws authority while engaged (controlsMismatch debounce)</t>
         </is>
       </c>
-      <c r="D10" s="60" t="inlineStr">
+      <c r="D10" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E10" s="60" t="inlineStr">
+      <c r="E10" s="61" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F10" s="60" t="inlineStr">
+      <c r="F10" s="61" t="inlineStr">
         <is>
           <t>SFM-014.C2
 SFM-015.C2
@@ -17088,372 +17100,372 @@
 SFM-016.C2</t>
         </is>
       </c>
-      <c r="G10" s="60" t="inlineStr"/>
-      <c r="H10" s="60" t="inlineStr"/>
-      <c r="I10" s="60" t="inlineStr">
+      <c r="G10" s="61" t="inlineStr"/>
+      <c r="H10" s="61" t="inlineStr"/>
+      <c r="I10" s="61" t="inlineStr">
         <is>
           <t>controlsMismatch debounce cut from 200 cumulative samples (~2 s) to 2 consecutive samples, at most 0.5 s (change-2026-10-13-host-supervision.md); credited at BL-005 (SFM-015.C2 M 6). FTTI justification of SOFT_DISABLE reactions open</t>
         </is>
       </c>
     </row>
     <row r="11" ht="33" customHeight="1">
-      <c r="A11" s="60" t="inlineStr">
+      <c r="A11" s="61" t="inlineStr">
         <is>
           <t>SFM-ACT-011</t>
         </is>
       </c>
-      <c r="B11" s="60" t="inlineStr">
+      <c r="B11" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C11" s="60" t="inlineStr">
+      <c r="C11" s="61" t="inlineStr">
         <is>
           <t>Alert the driver when stock cruise stays engaged while the item is disengaged (cruiseMismatch has no alert at BL-004)</t>
         </is>
       </c>
-      <c r="D11" s="60" t="inlineStr">
+      <c r="D11" s="61" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E11" s="61" t="inlineStr">
+      <c r="E11" s="62" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F11" s="60" t="inlineStr">
+      <c r="F11" s="61" t="inlineStr">
         <is>
           <t>SFM-021.C1
 SFM-021.C2</t>
         </is>
       </c>
-      <c r="G11" s="60" t="inlineStr"/>
-      <c r="H11" s="60" t="inlineStr"/>
-      <c r="I11" s="60" t="inlineStr">
+      <c r="G11" s="61" t="inlineStr"/>
+      <c r="H11" s="61" t="inlineStr"/>
+      <c r="I11" s="61" t="inlineStr">
         <is>
           <t>cruiseMismatch now alerts after 1 s (change-2026-10-13-host-supervision.md); see SWF-ACT-034</t>
         </is>
       </c>
     </row>
     <row r="12" ht="73.5" customHeight="1">
-      <c r="A12" s="60" t="inlineStr">
+      <c r="A12" s="61" t="inlineStr">
         <is>
           <t>SFM-ACT-012</t>
         </is>
       </c>
-      <c r="B12" s="60" t="inlineStr">
+      <c r="B12" s="61" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C12" s="60" t="inlineStr">
+      <c r="C12" s="61" t="inlineStr">
         <is>
           <t>Measure on the HIL bench and the reference car (WP-V-05) how the panda reacts to over-limit and not-engaged steering and acceleration frames and to driver brake, gas and cancel inputs, and what the EPS and PCM do when frames are refused; re-rate the MSR rows from code-derived to measured timing</t>
         </is>
       </c>
-      <c r="D12" s="60" t="inlineStr"/>
-      <c r="E12" s="60" t="inlineStr">
+      <c r="D12" s="61" t="inlineStr"/>
+      <c r="E12" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F12" s="60" t="inlineStr"/>
-      <c r="G12" s="60" t="inlineStr"/>
-      <c r="H12" s="60" t="inlineStr"/>
-      <c r="I12" s="60" t="inlineStr"/>
+      <c r="F12" s="61" t="inlineStr"/>
+      <c r="G12" s="61" t="inlineStr"/>
+      <c r="H12" s="61" t="inlineStr"/>
+      <c r="I12" s="61" t="inlineStr"/>
     </row>
     <row r="13" ht="87" customHeight="1">
-      <c r="A13" s="60" t="inlineStr">
+      <c r="A13" s="61" t="inlineStr">
         <is>
           <t>SFM-ACT-013</t>
         </is>
       </c>
-      <c r="B13" s="60" t="inlineStr">
+      <c r="B13" s="61" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C13" s="60" t="inlineStr">
+      <c r="C13" s="61" t="inlineStr">
         <is>
           <t>Check on the host, within the SG-01 FTTI, that the panda reports controls_allowed false while the item is disengaged (the reverse of the controlsMismatch check, which at BL-005 still covers only engaged with authority withdrawn), with a disable and an alert. The requirement is TSR-630, within 0.3 s (WP-S-02 §12.3a; WP-S-04 T-32, not implemented)</t>
         </is>
       </c>
-      <c r="D13" s="60" t="inlineStr"/>
-      <c r="E13" s="60" t="inlineStr">
+      <c r="D13" s="61" t="inlineStr"/>
+      <c r="E13" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F13" s="60" t="inlineStr"/>
-      <c r="G13" s="60" t="inlineStr"/>
-      <c r="H13" s="60" t="inlineStr"/>
-      <c r="I13" s="60" t="inlineStr"/>
+      <c r="F13" s="61" t="inlineStr"/>
+      <c r="G13" s="61" t="inlineStr"/>
+      <c r="H13" s="61" t="inlineStr"/>
+      <c r="I13" s="61" t="inlineStr"/>
     </row>
     <row r="14" ht="46.5" customHeight="1">
-      <c r="A14" s="60" t="inlineStr">
+      <c r="A14" s="61" t="inlineStr">
         <is>
           <t>SFM-ACT-014</t>
         </is>
       </c>
-      <c r="B14" s="60" t="inlineStr">
+      <c r="B14" s="61" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C14" s="60" t="inlineStr">
+      <c r="C14" s="61" t="inlineStr">
         <is>
           <t>Specify in the TSC a steering-direction plausibility monitor (commanded torque sign against measured yaw rate and lane-relative lateral motion), or justify its absence against HZ-003</t>
         </is>
       </c>
-      <c r="D14" s="60" t="inlineStr"/>
-      <c r="E14" s="60" t="inlineStr">
+      <c r="D14" s="61" t="inlineStr"/>
+      <c r="E14" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F14" s="60" t="inlineStr"/>
-      <c r="G14" s="60" t="inlineStr"/>
-      <c r="H14" s="60" t="inlineStr"/>
-      <c r="I14" s="60" t="inlineStr"/>
+      <c r="F14" s="61" t="inlineStr"/>
+      <c r="G14" s="61" t="inlineStr"/>
+      <c r="H14" s="61" t="inlineStr"/>
+      <c r="I14" s="61" t="inlineStr"/>
     </row>
     <row r="15" ht="100.5" customHeight="1">
-      <c r="A15" s="60" t="inlineStr">
+      <c r="A15" s="61" t="inlineStr">
         <is>
           <t>SFM-ACT-015</t>
         </is>
       </c>
-      <c r="B15" s="60" t="inlineStr">
+      <c r="B15" s="61" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C15" s="60" t="inlineStr">
+      <c r="C15" s="61" t="inlineStr">
         <is>
           <t>Detect stale commands and inputs within the SG-01 FTTI: command-frame freshness in the MCU with an active zero frame (TSR-408, TSR-109) and frozen-content and age checks on model outputs in controlsd (TSR-602, TSR-631, AIR-17)</t>
         </is>
       </c>
-      <c r="D15" s="60" t="inlineStr"/>
-      <c r="E15" s="60" t="inlineStr">
+      <c r="D15" s="61" t="inlineStr"/>
+      <c r="E15" s="61" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F15" s="60" t="inlineStr"/>
-      <c r="G15" s="60" t="inlineStr"/>
-      <c r="H15" s="60" t="inlineStr"/>
-      <c r="I15" s="60" t="inlineStr">
+      <c r="F15" s="61" t="inlineStr"/>
+      <c r="G15" s="61" t="inlineStr"/>
+      <c r="H15" s="61" t="inlineStr"/>
+      <c r="I15" s="61" t="inlineStr">
         <is>
           <t>BL-005: command-frame arrival in the MCU (TSR-408, 50 ms STEERING_LKA, reference build by default) and input age checks in controlsd (TSR-602) are in. Open: the active zero frame (TSR-109), a frozen-content check on model outputs, and stale data with fresh timestamps (SFM-006.C1 to C3). The frozen-content check is TSR-631, with the age taken from the source timestamp (WP-S-02 §12.3a)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="73.5" customHeight="1">
-      <c r="A16" s="60" t="inlineStr">
+      <c r="A16" s="61" t="inlineStr">
         <is>
           <t>SFM-ACT-016</t>
         </is>
       </c>
-      <c r="B16" s="60" t="inlineStr">
+      <c r="B16" s="61" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C16" s="60" t="inlineStr">
+      <c r="C16" s="61" t="inlineStr">
         <is>
           <t>Supervise driver override in the panda: driver steering torque above the override threshold limits or revokes lateral authority within the SG-05 0.2 s budget (TSR-304). Behaviour decided by the lead (DQ-053, option A): back off on override and show a cue. Requirements: TSR-304 (timing tied to the SG-05 budget) and TSR-628 (WP-S-02 §12.3a)</t>
         </is>
       </c>
-      <c r="D16" s="60" t="inlineStr"/>
-      <c r="E16" s="60" t="inlineStr">
+      <c r="D16" s="61" t="inlineStr"/>
+      <c r="E16" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F16" s="60" t="inlineStr"/>
-      <c r="G16" s="60" t="inlineStr"/>
-      <c r="H16" s="60" t="inlineStr"/>
-      <c r="I16" s="60" t="inlineStr"/>
+      <c r="F16" s="61" t="inlineStr"/>
+      <c r="G16" s="61" t="inlineStr"/>
+      <c r="H16" s="61" t="inlineStr"/>
+      <c r="I16" s="61" t="inlineStr"/>
     </row>
     <row r="17" ht="87" customHeight="1">
-      <c r="A17" s="60" t="inlineStr">
+      <c r="A17" s="61" t="inlineStr">
         <is>
           <t>SFM-ACT-017</t>
         </is>
       </c>
-      <c r="B17" s="60" t="inlineStr">
+      <c r="B17" s="61" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C17" s="60" t="inlineStr">
+      <c r="C17" s="61" t="inlineStr">
         <is>
           <t>Add WP-S-04 FTTI rows for the warning paths without one (insufficient lateral control, late or insufficient braking warnings, SG-008 unintended engagement, driver monitoring), so these mechanisms can be compared with a time budget</t>
         </is>
       </c>
-      <c r="D17" s="60" t="inlineStr"/>
-      <c r="E17" s="61" t="inlineStr">
+      <c r="D17" s="61" t="inlineStr"/>
+      <c r="E17" s="62" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F17" s="60" t="inlineStr"/>
-      <c r="G17" s="60" t="inlineStr"/>
-      <c r="H17" s="60" t="inlineStr"/>
-      <c r="I17" s="60" t="inlineStr">
+      <c r="F17" s="61" t="inlineStr"/>
+      <c r="G17" s="61" t="inlineStr"/>
+      <c r="H17" s="61" t="inlineStr"/>
+      <c r="I17" s="61" t="inlineStr">
         <is>
           <t>WP-S-04 v0.7 §3.7 (four rows) and §3.8, with T-30 to T-33. Rev 0.15 compares SFM-004, SFM-010.C2/C3, SFM-012.C1 and SFM-013.C1/C2 with them. Driver monitoring (SFM-022.C3, SFM-025.C1) waits for the H-09 FTTI (§3.8.4); follow-up is SFM-ACT-005. Late warnings found: SFM-ACT-021 (lateral) and SFM-ACT-022 (braking)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="100.5" customHeight="1">
-      <c r="A18" s="60" t="inlineStr">
+      <c r="A18" s="61" t="inlineStr">
         <is>
           <t>SFM-ACT-018</t>
         </is>
       </c>
-      <c r="B18" s="60" t="inlineStr">
+      <c r="B18" s="61" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C18" s="60" t="inlineStr">
+      <c r="C18" s="61" t="inlineStr">
         <is>
           <t>Detect silent loss of the actuation path: report forwarded and refused TX frames from the panda, and compare EPS and PCM acceptance (LKA_STATE, ACC status) with the commands, warning within the SG-02/06 1 s budget</t>
         </is>
       </c>
-      <c r="D18" s="60" t="inlineStr"/>
-      <c r="E18" s="60" t="inlineStr">
+      <c r="D18" s="61" t="inlineStr"/>
+      <c r="E18" s="61" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F18" s="60" t="inlineStr"/>
-      <c r="G18" s="60" t="inlineStr"/>
-      <c r="H18" s="60" t="inlineStr"/>
-      <c r="I18" s="60" t="inlineStr">
+      <c r="F18" s="61" t="inlineStr"/>
+      <c r="G18" s="61" t="inlineStr"/>
+      <c r="H18" s="61" t="inlineStr"/>
+      <c r="I18" s="61" t="inlineStr">
         <is>
           <t>BL-005: frames that stop reaching the panda are detected (TSR-408) and alerted within 0.5 s (TSR-621), credited on SFM-005.C2 and SFM-011.C2. Open: frames that reach the panda but are not accepted by the EPS or PCM (SFM-005.C1, SFM-011.C1). Requirements: TSR-632 (per-ID transmitted and refused counts), TSR-626(d)/(e) (EPS and PCM acceptance status) and TSR-615, warning within 1 s (WP-S-02 §12.3a)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="60" t="inlineStr">
+      <c r="A19" s="61" t="inlineStr">
         <is>
           <t>SFM-ACT-019</t>
         </is>
       </c>
-      <c r="B19" s="60" t="inlineStr">
+      <c r="B19" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C19" s="60" t="inlineStr">
+      <c r="C19" s="61" t="inlineStr">
         <is>
           <t>Revoke lateral authority in the panda when it rejects a steering frame while authority is granted, and keep it revoked until a new valid engagement (TSR-108; lead decision DQ-060, option A). At BL-005 the frame is dropped and only the host disengages (pandaTxBlocked)</t>
         </is>
       </c>
-      <c r="D19" s="60" t="inlineStr"/>
-      <c r="E19" s="60" t="inlineStr">
+      <c r="D19" s="61" t="inlineStr"/>
+      <c r="E19" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F19" s="60" t="inlineStr">
+      <c r="F19" s="61" t="inlineStr">
         <is>
           <t>SFM-002.C1
 SFM-002.C2
 SFM-002.C4</t>
         </is>
       </c>
-      <c r="G19" s="60" t="inlineStr"/>
-      <c r="H19" s="60" t="inlineStr"/>
-      <c r="I19" s="60" t="inlineStr"/>
+      <c r="G19" s="61" t="inlineStr"/>
+      <c r="H19" s="61" t="inlineStr"/>
+      <c r="I19" s="61" t="inlineStr"/>
     </row>
     <row r="20" ht="73.5" customHeight="1">
-      <c r="A20" s="60" t="inlineStr">
+      <c r="A20" s="61" t="inlineStr">
         <is>
           <t>SFM-ACT-020</t>
         </is>
       </c>
-      <c r="B20" s="60" t="inlineStr">
+      <c r="B20" s="61" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C20" s="60" t="inlineStr">
+      <c r="C20" s="61" t="inlineStr">
         <is>
           <t>React to a stock PCS event on the longitudinal command (for example a neutral or zero acceleration request, or a longitudinal disable, while stockAeb is set), so stock AEB does not depend on PCM arbitration alone (AOU-04R); or keep today's behaviour and rely on the AOU-04R vehicle test. Lead decision DQ-300</t>
         </is>
       </c>
-      <c r="D20" s="60" t="inlineStr"/>
-      <c r="E20" s="60" t="inlineStr">
+      <c r="D20" s="61" t="inlineStr"/>
+      <c r="E20" s="61" t="inlineStr">
         <is>
           <t>decision pending</t>
         </is>
       </c>
-      <c r="F20" s="60" t="inlineStr">
+      <c r="F20" s="61" t="inlineStr">
         <is>
           <t>SFM-036.C1</t>
         </is>
       </c>
-      <c r="G20" s="60" t="inlineStr"/>
-      <c r="H20" s="60" t="inlineStr"/>
-      <c r="I20" s="60" t="inlineStr"/>
+      <c r="G20" s="61" t="inlineStr"/>
+      <c r="H20" s="61" t="inlineStr"/>
+      <c r="I20" s="61" t="inlineStr"/>
     </row>
     <row r="21" ht="73.5" customHeight="1">
-      <c r="A21" s="60" t="inlineStr">
+      <c r="A21" s="61" t="inlineStr">
         <is>
           <t>SFM-ACT-021</t>
         </is>
       </c>
-      <c r="B21" s="60" t="inlineStr">
+      <c r="B21" s="61" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C21" s="60" t="inlineStr">
+      <c r="C21" s="61" t="inlineStr">
         <is>
           <t>Make the insufficient-lateral-control warning timely (WP-S-04 §3.8.1): warn before the deficit has lasted 0.4 s, for example from the planned curvature against the envelope, or keep the deficit at or below about 0.5 m/s² through the steering limits and the ODD curve bound (WP-S-04 OI-2). A change to the ODD bound is a lead decision</t>
         </is>
       </c>
-      <c r="D21" s="60" t="inlineStr"/>
-      <c r="E21" s="60" t="inlineStr">
+      <c r="D21" s="61" t="inlineStr"/>
+      <c r="E21" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F21" s="60" t="inlineStr"/>
-      <c r="G21" s="60" t="inlineStr"/>
-      <c r="H21" s="60" t="inlineStr"/>
-      <c r="I21" s="60" t="inlineStr"/>
+      <c r="F21" s="61" t="inlineStr"/>
+      <c r="G21" s="61" t="inlineStr"/>
+      <c r="H21" s="61" t="inlineStr"/>
+      <c r="I21" s="61" t="inlineStr"/>
     </row>
     <row r="22" ht="60" customHeight="1">
-      <c r="A22" s="60" t="inlineStr">
+      <c r="A22" s="61" t="inlineStr">
         <is>
           <t>SFM-ACT-022</t>
         </is>
       </c>
-      <c r="B22" s="60" t="inlineStr">
+      <c r="B22" s="61" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C22" s="60" t="inlineStr">
+      <c r="C22" s="61" t="inlineStr">
         <is>
           <t>Measure the FCW onset after a lead brakes hard (WP-S-04 T-31, M-12) and compare it with the §3.8.2 budget (about 0.6 s at a 1.0 s gap). For pipeline lag (SFM-012.C1), detect it within that budget or show that the FCW path does not depend on the lagging process</t>
         </is>
       </c>
-      <c r="D22" s="60" t="inlineStr"/>
-      <c r="E22" s="60" t="inlineStr">
+      <c r="D22" s="61" t="inlineStr"/>
+      <c r="E22" s="61" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F22" s="60" t="inlineStr"/>
-      <c r="G22" s="60" t="inlineStr"/>
-      <c r="H22" s="60" t="inlineStr"/>
-      <c r="I22" s="60" t="inlineStr"/>
+      <c r="F22" s="61" t="inlineStr"/>
+      <c r="G22" s="61" t="inlineStr"/>
+      <c r="H22" s="61" t="inlineStr"/>
+      <c r="I22" s="61" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I22"/>
@@ -17478,50 +17490,50 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="59" t="inlineStr">
+      <c r="A1" s="60" t="inlineStr">
         <is>
           <t>Element</t>
         </is>
       </c>
-      <c r="B1" s="59" t="inlineStr">
+      <c r="B1" s="60" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="59" t="inlineStr">
+      <c r="C1" s="60" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="D1" s="59" t="inlineStr">
+      <c r="D1" s="60" t="inlineStr">
         <is>
           <t>Parent</t>
         </is>
       </c>
-      <c r="E1" s="59" t="inlineStr">
+      <c r="E1" s="60" t="inlineStr">
         <is>
           <t>Functions</t>
         </is>
       </c>
     </row>
     <row r="2" ht="222" customHeight="1">
-      <c r="A2" s="60" t="inlineStr">
+      <c r="A2" s="61" t="inlineStr">
         <is>
           <t>SFM-SE-001</t>
         </is>
       </c>
-      <c r="B2" s="60" t="inlineStr">
+      <c r="B2" s="61" t="inlineStr">
         <is>
           <t>LionDriver item (L2 ACC + ALC + driver monitoring)</t>
         </is>
       </c>
-      <c r="C2" s="60" t="inlineStr">
+      <c r="C2" s="61" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="D2" s="60" t="inlineStr"/>
-      <c r="E2" s="60" t="inlineStr">
+      <c r="D2" s="61" t="inlineStr"/>
+      <c r="E2" s="61" t="inlineStr">
         <is>
           <t>SFM-FN-001: F1 Lateral control: request steering torque from the EPS to keep the vehicle in its lane while engaged
 SFM-FN-002: F2 Longitudinal control: request acceleration/deceleration to hold set speed and follow leads while engaged
@@ -17535,398 +17547,398 @@
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="60" t="inlineStr">
+      <c r="A3" s="61" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="B3" s="60" t="inlineStr">
+      <c r="B3" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">    comma 3X device</t>
         </is>
       </c>
-      <c r="C3" s="60" t="inlineStr">
+      <c r="C3" s="61" t="inlineStr">
         <is>
           <t>system</t>
         </is>
       </c>
-      <c r="D3" s="60" t="inlineStr">
+      <c r="D3" s="61" t="inlineStr">
         <is>
           <t>SFM-SE-001</t>
         </is>
       </c>
-      <c r="E3" s="60" t="inlineStr"/>
+      <c r="E3" s="61" t="inlineStr"/>
     </row>
     <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="60" t="inlineStr">
+      <c r="A4" s="61" t="inlineStr">
         <is>
           <t>SFM-SE-003</t>
         </is>
       </c>
-      <c r="B4" s="60" t="inlineStr">
+      <c r="B4" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">        Integrated panda (CAN interface and safety model)</t>
         </is>
       </c>
-      <c r="C4" s="60" t="inlineStr">
+      <c r="C4" s="61" t="inlineStr">
         <is>
           <t>subsystem</t>
         </is>
       </c>
-      <c r="D4" s="60" t="inlineStr">
+      <c r="D4" s="61" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E4" s="60" t="inlineStr"/>
+      <c r="E4" s="61" t="inlineStr"/>
     </row>
     <row r="5" ht="19.5" customHeight="1">
-      <c r="A5" s="60" t="inlineStr">
+      <c r="A5" s="61" t="inlineStr">
         <is>
           <t>SFM-SE-004</t>
         </is>
       </c>
-      <c r="B5" s="60" t="inlineStr">
+      <c r="B5" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">    Harness (Toyota A connector, harness box, comma power v3)</t>
         </is>
       </c>
-      <c r="C5" s="60" t="inlineStr">
+      <c r="C5" s="61" t="inlineStr">
         <is>
           <t>component</t>
         </is>
       </c>
-      <c r="D5" s="60" t="inlineStr">
+      <c r="D5" s="61" t="inlineStr">
         <is>
           <t>SFM-SE-001</t>
         </is>
       </c>
-      <c r="E5" s="60" t="inlineStr"/>
+      <c r="E5" s="61" t="inlineStr"/>
     </row>
     <row r="6" ht="19.5" customHeight="1">
-      <c r="A6" s="60" t="inlineStr">
+      <c r="A6" s="61" t="inlineStr">
         <is>
           <t>SFM-SE-010</t>
         </is>
       </c>
-      <c r="B6" s="60" t="inlineStr">
+      <c r="B6" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">        Perception (camerad, modeld)</t>
         </is>
       </c>
-      <c r="C6" s="60" t="inlineStr">
+      <c r="C6" s="61" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D6" s="60" t="inlineStr">
+      <c r="D6" s="61" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E6" s="60" t="inlineStr"/>
+      <c r="E6" s="61" t="inlineStr"/>
     </row>
     <row r="7" ht="19.5" customHeight="1">
-      <c r="A7" s="60" t="inlineStr">
+      <c r="A7" s="61" t="inlineStr">
         <is>
           <t>SFM-SE-011</t>
         </is>
       </c>
-      <c r="B7" s="60" t="inlineStr">
+      <c r="B7" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">        Localization and calibration (locationd, calibrationd, paramsd, torqued)</t>
         </is>
       </c>
-      <c r="C7" s="60" t="inlineStr">
+      <c r="C7" s="61" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D7" s="60" t="inlineStr">
+      <c r="D7" s="61" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E7" s="60" t="inlineStr"/>
+      <c r="E7" s="61" t="inlineStr"/>
     </row>
     <row r="8" ht="19.5" customHeight="1">
-      <c r="A8" s="60" t="inlineStr">
+      <c r="A8" s="61" t="inlineStr">
         <is>
           <t>SFM-SE-012</t>
         </is>
       </c>
-      <c r="B8" s="60" t="inlineStr">
+      <c r="B8" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">        Planning (plannerd, radard)</t>
         </is>
       </c>
-      <c r="C8" s="60" t="inlineStr">
+      <c r="C8" s="61" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D8" s="60" t="inlineStr">
+      <c r="D8" s="61" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E8" s="60" t="inlineStr"/>
+      <c r="E8" s="61" t="inlineStr"/>
     </row>
     <row r="9" ht="19.5" customHeight="1">
-      <c r="A9" s="60" t="inlineStr">
+      <c r="A9" s="61" t="inlineStr">
         <is>
           <t>SFM-SE-013</t>
         </is>
       </c>
-      <c r="B9" s="60" t="inlineStr">
+      <c r="B9" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">        Control (controlsd, lateral/longitudinal controllers)</t>
         </is>
       </c>
-      <c r="C9" s="60" t="inlineStr">
+      <c r="C9" s="61" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D9" s="60" t="inlineStr">
+      <c r="D9" s="61" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E9" s="60" t="inlineStr"/>
+      <c r="E9" s="61" t="inlineStr"/>
     </row>
     <row r="10" ht="19.5" customHeight="1">
-      <c r="A10" s="60" t="inlineStr">
+      <c r="A10" s="61" t="inlineStr">
         <is>
           <t>SFM-SE-014</t>
         </is>
       </c>
-      <c r="B10" s="60" t="inlineStr">
+      <c r="B10" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">        Supervision (selfdrived state machine, events, alert manager)</t>
         </is>
       </c>
-      <c r="C10" s="60" t="inlineStr">
+      <c r="C10" s="61" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D10" s="60" t="inlineStr">
+      <c r="D10" s="61" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E10" s="60" t="inlineStr"/>
+      <c r="E10" s="61" t="inlineStr"/>
     </row>
     <row r="11" ht="19.5" customHeight="1">
-      <c r="A11" s="60" t="inlineStr">
+      <c r="A11" s="61" t="inlineStr">
         <is>
           <t>SFM-SE-015</t>
         </is>
       </c>
-      <c r="B11" s="60" t="inlineStr">
+      <c r="B11" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">        Driver monitoring (dmonitoringmodeld, dmonitoringd)</t>
         </is>
       </c>
-      <c r="C11" s="60" t="inlineStr">
+      <c r="C11" s="61" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D11" s="60" t="inlineStr">
+      <c r="D11" s="61" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E11" s="60" t="inlineStr"/>
+      <c r="E11" s="61" t="inlineStr"/>
     </row>
     <row r="12" ht="19.5" customHeight="1">
-      <c r="A12" s="60" t="inlineStr">
+      <c r="A12" s="61" t="inlineStr">
         <is>
           <t>SFM-SE-016</t>
         </is>
       </c>
-      <c r="B12" s="60" t="inlineStr">
+      <c r="B12" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">        Car interface (card, car_events, opendbc Toyota port)</t>
         </is>
       </c>
-      <c r="C12" s="60" t="inlineStr">
+      <c r="C12" s="61" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D12" s="60" t="inlineStr">
+      <c r="D12" s="61" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E12" s="60" t="inlineStr"/>
+      <c r="E12" s="61" t="inlineStr"/>
     </row>
     <row r="13" ht="19.5" customHeight="1">
-      <c r="A13" s="60" t="inlineStr">
+      <c r="A13" s="61" t="inlineStr">
         <is>
           <t>SFM-SE-017</t>
         </is>
       </c>
-      <c r="B13" s="60" t="inlineStr">
+      <c r="B13" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">        Panda daemon (pandad)</t>
         </is>
       </c>
-      <c r="C13" s="60" t="inlineStr">
+      <c r="C13" s="61" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D13" s="60" t="inlineStr">
+      <c r="D13" s="61" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E13" s="60" t="inlineStr"/>
+      <c r="E13" s="61" t="inlineStr"/>
     </row>
     <row r="14" ht="19.5" customHeight="1">
-      <c r="A14" s="60" t="inlineStr">
+      <c r="A14" s="61" t="inlineStr">
         <is>
           <t>SFM-SE-018</t>
         </is>
       </c>
-      <c r="B14" s="60" t="inlineStr">
+      <c r="B14" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">        HMI (ui, soundd)</t>
         </is>
       </c>
-      <c r="C14" s="60" t="inlineStr">
+      <c r="C14" s="61" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D14" s="60" t="inlineStr">
+      <c r="D14" s="61" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E14" s="60" t="inlineStr"/>
+      <c r="E14" s="61" t="inlineStr"/>
     </row>
     <row r="15" ht="19.5" customHeight="1">
-      <c r="A15" s="60" t="inlineStr">
+      <c r="A15" s="61" t="inlineStr">
         <is>
           <t>SFM-SE-019</t>
         </is>
       </c>
-      <c r="B15" s="60" t="inlineStr">
+      <c r="B15" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">        Platform (manager, messaging, hardwared, OS)</t>
         </is>
       </c>
-      <c r="C15" s="60" t="inlineStr">
+      <c r="C15" s="61" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D15" s="60" t="inlineStr">
+      <c r="D15" s="61" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E15" s="60" t="inlineStr"/>
+      <c r="E15" s="61" t="inlineStr"/>
     </row>
     <row r="16" ht="19.5" customHeight="1">
-      <c r="A16" s="60" t="inlineStr">
+      <c r="A16" s="61" t="inlineStr">
         <is>
           <t>SFM-SE-030</t>
         </is>
       </c>
-      <c r="B16" s="60" t="inlineStr">
+      <c r="B16" s="61" t="inlineStr">
         <is>
           <t>Toyota EPS</t>
         </is>
       </c>
-      <c r="C16" s="60" t="inlineStr">
+      <c r="C16" s="61" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D16" s="60" t="inlineStr"/>
-      <c r="E16" s="60" t="inlineStr"/>
+      <c r="D16" s="61" t="inlineStr"/>
+      <c r="E16" s="61" t="inlineStr"/>
     </row>
     <row r="17" ht="19.5" customHeight="1">
-      <c r="A17" s="60" t="inlineStr">
+      <c r="A17" s="61" t="inlineStr">
         <is>
           <t>SFM-SE-031</t>
         </is>
       </c>
-      <c r="B17" s="60" t="inlineStr">
+      <c r="B17" s="61" t="inlineStr">
         <is>
           <t>Toyota powertrain and brake control (receives ACC acceleration requests)</t>
         </is>
       </c>
-      <c r="C17" s="60" t="inlineStr">
+      <c r="C17" s="61" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D17" s="60" t="inlineStr"/>
-      <c r="E17" s="60" t="inlineStr"/>
+      <c r="D17" s="61" t="inlineStr"/>
+      <c r="E17" s="61" t="inlineStr"/>
     </row>
     <row r="18" ht="19.5" customHeight="1">
-      <c r="A18" s="60" t="inlineStr">
+      <c r="A18" s="61" t="inlineStr">
         <is>
           <t>SFM-SE-032</t>
         </is>
       </c>
-      <c r="B18" s="60" t="inlineStr">
+      <c r="B18" s="61" t="inlineStr">
         <is>
           <t>Toyota stock ADAS camera (TSS2)</t>
         </is>
       </c>
-      <c r="C18" s="60" t="inlineStr">
+      <c r="C18" s="61" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D18" s="60" t="inlineStr"/>
-      <c r="E18" s="60" t="inlineStr"/>
+      <c r="D18" s="61" t="inlineStr"/>
+      <c r="E18" s="61" t="inlineStr"/>
     </row>
     <row r="19" ht="19.5" customHeight="1">
-      <c r="A19" s="60" t="inlineStr">
+      <c r="A19" s="61" t="inlineStr">
         <is>
           <t>SFM-SE-033</t>
         </is>
       </c>
-      <c r="B19" s="60" t="inlineStr">
+      <c r="B19" s="61" t="inlineStr">
         <is>
           <t>Vehicle CAN buses and 12 V supply</t>
         </is>
       </c>
-      <c r="C19" s="60" t="inlineStr">
+      <c r="C19" s="61" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D19" s="60" t="inlineStr"/>
-      <c r="E19" s="60" t="inlineStr"/>
+      <c r="D19" s="61" t="inlineStr"/>
+      <c r="E19" s="61" t="inlineStr"/>
     </row>
     <row r="20" ht="19.5" customHeight="1">
-      <c r="A20" s="60" t="inlineStr">
+      <c r="A20" s="61" t="inlineStr">
         <is>
           <t>SFM-SE-034</t>
         </is>
       </c>
-      <c r="B20" s="60" t="inlineStr">
+      <c r="B20" s="61" t="inlineStr">
         <is>
           <t>Driver</t>
         </is>
       </c>
-      <c r="C20" s="60" t="inlineStr">
+      <c r="C20" s="61" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D20" s="60" t="inlineStr"/>
-      <c r="E20" s="60" t="inlineStr"/>
+      <c r="D20" s="61" t="inlineStr"/>
+      <c r="E20" s="61" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E20"/>
@@ -17962,7 +17974,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="62" t="inlineStr">
+      <c r="A1" s="63" t="inlineStr">
         <is>
           <t>FMEA-MSR (monitoring and system response, msr-plan.md): S, F, M and MSR AP per rating-tables.md §7 (RT-2). The MSR AP table is provisional until the handbook table is transcribed (decision register DQ-207). Exempt causes are rated in the FMEA named in the reason.</t>
         </is>
@@ -20719,7 +20731,7 @@
           <t>Device power loss (12 V interruption, harness connector)</t>
         </is>
       </c>
-      <c r="E44" s="63" t="inlineStr">
+      <c r="E44" s="64" t="inlineStr">
         <is>
           <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-012.C1)</t>
         </is>
@@ -21732,7 +21744,7 @@
         <v>8</v>
       </c>
       <c r="I60" s="35" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J60" s="35" t="n">
         <v>7</v>
@@ -21841,7 +21853,7 @@
           <t>Panda MCU hardware fault (see DFMEA/FMEDA)</t>
         </is>
       </c>
-      <c r="E62" s="63" t="inlineStr">
+      <c r="E62" s="64" t="inlineStr">
         <is>
           <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-001.C1)</t>
         </is>
@@ -22001,7 +22013,7 @@
           <t>Switch U1 or U2 stuck in intercept, its IN input damaged high or driven high, its pull-down R2/R3 open, or the switches damaged by box supply transients (DG419LE, RR-2026-010)</t>
         </is>
       </c>
-      <c r="E65" s="63" t="inlineStr">
+      <c r="E65" s="64" t="inlineStr">
         <is>
           <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-010.C1)</t>
         </is>
@@ -22037,7 +22049,7 @@
           <t>Switch stuck in pass-through, or the SBU1 drive lost, held low or too low to change the switch over (5 V drive against VL = VIN)</t>
         </is>
       </c>
-      <c r="E66" s="63" t="inlineStr">
+      <c r="E66" s="64" t="inlineStr">
         <is>
           <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-011.C1)</t>
         </is>
@@ -22313,7 +22325,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.15 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.16 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -823,7 +823,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.16 · draft</t>
+          <t>0.17 · draft</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       <c r="R4" s="37" t="inlineStr"/>
       <c r="S4" s="37" t="inlineStr"/>
     </row>
-    <row r="5" ht="100.5" customHeight="1">
+    <row r="5" ht="235.5" customHeight="1">
       <c r="A5" s="39" t="n"/>
       <c r="B5" s="39" t="n"/>
       <c r="C5" s="39" t="n"/>
@@ -1650,6 +1650,15 @@
             </rPr>
             <t>Steering message packed with non-zero torque/request bit while latActive is false</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: SWF-059</t>
+          </r>
         </is>
       </c>
       <c r="I5" s="41" t="inlineStr">
@@ -1674,7 +1683,7 @@
         </is>
       </c>
       <c r="J5" s="42" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K5" s="41" t="inlineStr">
         <is>
@@ -1684,7 +1693,7 @@
               <color rgb="008A5A00"/>
               <sz val="10"/>
             </rPr>
-            <t>• process_replay over the CI route corpus compares outputs with the reference commit (CI 'process replay'); a regression check, not designed or proven for this cause</t>
+            <t>• As rated in the SW FMEA (SWF-059.C1, D 9 at BL-005): process_replay (CI) replays the TOYOTA3 Corolla TSS2 segment and compares with reference logs made from the same code, so it cannot find a defect already present at the baseline; not designed for this cause; it compares sendcan</t>
           </r>
           <r>
             <rPr>
@@ -1695,6 +1704,32 @@
             <t xml:space="preserve">
    openpilot/selfdrive/test/process_replay/test_processes.py</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• process_replay over the CI route corpus compares outputs with the reference commit (CI 'process replay'); a regression check, not designed or proven for this cause</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/test/process_replay/test_processes.py</t>
+          </r>
         </is>
       </c>
       <c r="L5" s="43" t="n">
@@ -1722,7 +1757,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>The panda refuses steering torque while controls are not allowed (SWF-002, D 3), so this cause leads to the end effect only together with SFM-001.C2; no separate action</t>
+            <t>Rated in the SW FMEA (SWF-059.C1, O 4 D 9 at BL-005); this row inherits that rating. The panda refuses steering torque while controls are not allowed (SWF-002, D 3), so this cause leads to the end effect only together with SFM-001.C2; no separate action</t>
           </r>
         </is>
       </c>
@@ -2333,6 +2368,15 @@
             </rPr>
             <t>Wrong vehicle parameters (steer ratio, lateral accel factor, torque offsets) from online learners</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: SWF-076</t>
+          </r>
         </is>
       </c>
       <c r="I9" s="41" t="inlineStr">
@@ -2383,17 +2427,17 @@
         </is>
       </c>
       <c r="J9" s="42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K9" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• paramsd and torqued unit tests (estimate bounds and convergence); targeted, not proven by fault injection</t>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• As rated in the SW FMEA (SWF-076.C1, D 9 at BL-005): test_paramsd.py (CI) checks the saved-parameter handling; not designed for out-of-bound use</t>
           </r>
           <r>
             <rPr>
@@ -2404,10 +2448,36 @@
             <t xml:space="preserve">
    openpilot/selfdrive/locationd/test/test_paramsd.py</t>
           </r>
-        </is>
-      </c>
-      <c r="L9" s="42" t="n">
-        <v>8</v>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• paramsd and torqued unit tests (estimate bounds and convergence); targeted, not proven by fault injection</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/locationd/test/test_paramsd.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L9" s="43" t="n">
+        <v>9</v>
       </c>
       <c r="M9" s="44" t="inlineStr">
         <is>
@@ -2666,6 +2736,15 @@
             </rPr>
             <t>Calibration (camera extrinsics) wrong or not converged</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: SWF-075</t>
+          </r>
         </is>
       </c>
       <c r="I10" s="34" t="inlineStr">
@@ -2716,10 +2795,36 @@
         </is>
       </c>
       <c r="J10" s="35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K10" s="34" t="inlineStr">
         <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• As rated in the SW FMEA (SWF-075.C1, D 8 at BL-005): test_calibrationd.py (CI) checks status transitions on synthetic data; targeted at the thresholds, not proven</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/locationd/test/test_calibrationd.py</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
           <r>
             <rPr>
               <rFont val="Calibri"/>
@@ -2779,7 +2884,7 @@
       <c r="R10" s="37" t="inlineStr"/>
       <c r="S10" s="37" t="inlineStr"/>
     </row>
-    <row r="11" ht="141" customHeight="1">
+    <row r="11" ht="235.5" customHeight="1">
       <c r="A11" s="38" t="n"/>
       <c r="B11" s="38" t="n"/>
       <c r="C11" s="38" t="n"/>
@@ -2801,6 +2906,15 @@
             </rPr>
             <t>Sign convention error in steering signal parse or pack for this car</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: SWF-057</t>
+          </r>
         </is>
       </c>
       <c r="I11" s="34" t="inlineStr">
@@ -2832,7 +2946,33 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• As rated in the SW FMEA (SWF-057.C1, D 9 at BL-005): process_replay (CI) replays the TOYOTA3 Corolla TSS2 segment and compares with reference logs made from the same code, so it cannot find a defect already present at the baseline; not designed for this cause</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/test/process_replay/test_processes.py</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
               <sz val="10"/>
             </rPr>
             <t>• opendbc car tests check carState against the panda safety model on recorded routes (test_models); targeted at parse and pack consistency, not proven by fault injection, and run only where the route corpus is available</t>
@@ -2848,8 +2988,8 @@
           </r>
         </is>
       </c>
-      <c r="L11" s="35" t="n">
-        <v>8</v>
+      <c r="L11" s="46" t="n">
+        <v>9</v>
       </c>
       <c r="M11" s="36" t="inlineStr">
         <is>
@@ -4323,6 +4463,15 @@
             </rPr>
             <t>modeld output frozen (stale frame) but still published as valid</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: SWF-072</t>
+          </r>
         </is>
       </c>
       <c r="I21" s="34" t="inlineStr">
@@ -4373,10 +4522,27 @@
         </is>
       </c>
       <c r="J21" s="35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K21" s="34" t="inlineStr">
         <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• As rated in the SW FMEA (SWF-072.C2, D 10 at BL-005): modeld has no unit tests, is excluded from process replay (EXCLUDED_PROCS) and from test_fuzzy, and model_replay is not run in LionDriver CI; test_onroad timing checks are device-only</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
           <r>
             <rPr>
               <rFont val="Calibri"/>
@@ -4921,7 +5087,7 @@
       <c r="R24" s="45" t="inlineStr"/>
       <c r="S24" s="45" t="inlineStr"/>
     </row>
-    <row r="25" ht="181.5" customHeight="1">
+    <row r="25" ht="195" customHeight="1">
       <c r="A25" s="30" t="inlineStr">
         <is>
           <r>
@@ -5085,6 +5251,15 @@
             </rPr>
             <t>Planner targets higher speed (missed lead, wrong set speed)</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: SWF-065</t>
+          </r>
         </is>
       </c>
       <c r="I25" s="34" t="inlineStr">
@@ -5135,14 +5310,40 @@
         </is>
       </c>
       <c r="J25" s="35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K25" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• As rated in the SW FMEA (SWF-065.C1, D 9 at BL-005): process_replay (CI) replays the TOYOTA3 Corolla TSS2 segment and compares with reference logs made from the same code, so it cannot find a defect already present at the baseline; not designed for this cause</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/test/process_replay/test_processes.py</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
               <sz val="10"/>
             </rPr>
             <t>• Unit test of the longitudinal plan's following distance and set-speed behaviour; targeted, not proven</t>
@@ -5158,8 +5359,8 @@
           </r>
         </is>
       </c>
-      <c r="L25" s="35" t="n">
-        <v>8</v>
+      <c r="L25" s="46" t="n">
+        <v>9</v>
       </c>
       <c r="M25" s="36" t="inlineStr">
         <is>
@@ -5344,7 +5545,7 @@
       <c r="R26" s="37" t="inlineStr"/>
       <c r="S26" s="37" t="inlineStr"/>
     </row>
-    <row r="27" ht="181.5" customHeight="1">
+    <row r="27" ht="249" customHeight="1">
       <c r="A27" s="38" t="n"/>
       <c r="B27" s="38" t="n"/>
       <c r="C27" s="38" t="n"/>
@@ -5366,6 +5567,15 @@
             </rPr>
             <t>Wrong scaling of acceleration request for this car</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: SWF-059</t>
+          </r>
         </is>
       </c>
       <c r="I27" s="34" t="inlineStr">
@@ -5416,14 +5626,40 @@
         </is>
       </c>
       <c r="J27" s="35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K27" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• As rated in the SW FMEA (SWF-059.C1, D 9 at BL-005): process_replay (CI) replays the TOYOTA3 Corolla TSS2 segment and compares with reference logs made from the same code, so it cannot find a defect already present at the baseline; not designed for this cause; it compares sendcan</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/test/process_replay/test_processes.py</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
               <sz val="10"/>
             </rPr>
             <t>• opendbc car tests check carState against the panda safety model on recorded routes (test_models); targeted at parse and pack consistency, not proven by fault injection, and run only where the route corpus is available</t>
@@ -5439,8 +5675,8 @@
           </r>
         </is>
       </c>
-      <c r="L27" s="35" t="n">
-        <v>8</v>
+      <c r="L27" s="46" t="n">
+        <v>9</v>
       </c>
       <c r="M27" s="36" t="inlineStr">
         <is>
@@ -5965,7 +6201,7 @@
       <c r="R30" s="37" t="inlineStr"/>
       <c r="S30" s="37" t="inlineStr"/>
     </row>
-    <row r="31" ht="141" customHeight="1">
+    <row r="31" ht="235.5" customHeight="1">
       <c r="A31" s="39" t="n"/>
       <c r="B31" s="39" t="n"/>
       <c r="C31" s="39" t="n"/>
@@ -5987,6 +6223,15 @@
             </rPr>
             <t>Wrong vEgo/aEgo from CAN parse</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: SWF-057</t>
+          </r>
         </is>
       </c>
       <c r="I31" s="41" t="inlineStr">
@@ -6018,7 +6263,33 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• As rated in the SW FMEA (SWF-057.C1, D 9 at BL-005): process_replay (CI) replays the TOYOTA3 Corolla TSS2 segment and compares with reference logs made from the same code, so it cannot find a defect already present at the baseline; not designed for this cause</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/test/process_replay/test_processes.py</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
               <sz val="10"/>
             </rPr>
             <t>• opendbc car tests check carState against the panda safety model on recorded routes (test_models); targeted at parse and pack consistency, not proven by fault injection, and run only where the route corpus is available</t>
@@ -6034,8 +6305,8 @@
           </r>
         </is>
       </c>
-      <c r="L31" s="42" t="n">
-        <v>8</v>
+      <c r="L31" s="43" t="n">
+        <v>9</v>
       </c>
       <c r="M31" s="44" t="inlineStr">
         <is>
@@ -6238,6 +6509,15 @@
             </rPr>
             <t>Lead missed due to radar/vision fusion fault</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: SWF-070</t>
+          </r>
         </is>
       </c>
       <c r="I32" s="34" t="inlineStr">
@@ -6292,6 +6572,32 @@
       </c>
       <c r="K32" s="34" t="inlineStr">
         <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• As rated in the SW FMEA (SWF-070.C1, D 8 at BL-005): test_stopped_vehicle test_radar_only_stationary_target reproduces the gap and is marked expectedFailure (CI)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/test/stopped_vehicle/test_stopped_vehicle.py</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
           <r>
             <rPr>
               <rFont val="Calibri"/>
@@ -9059,7 +9365,7 @@
       <c r="R48" s="45" t="inlineStr"/>
       <c r="S48" s="45" t="inlineStr"/>
     </row>
-    <row r="49" ht="141" customHeight="1">
+    <row r="49" ht="235.5" customHeight="1">
       <c r="A49" s="30" t="inlineStr">
         <is>
           <r>
@@ -9223,6 +9529,15 @@
             </rPr>
             <t>brakePressed parsed wrong or CAN signal missing</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: SWF-057</t>
+          </r>
         </is>
       </c>
       <c r="I49" s="34" t="inlineStr">
@@ -9254,7 +9569,33 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• As rated in the SW FMEA (SWF-057.C1, D 9 at BL-005): process_replay (CI) replays the TOYOTA3 Corolla TSS2 segment and compares with reference logs made from the same code, so it cannot find a defect already present at the baseline; not designed for this cause</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/test/process_replay/test_processes.py</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
               <sz val="10"/>
             </rPr>
             <t>• opendbc car tests check carState against the panda safety model on recorded routes (test_models); targeted at parse and pack consistency, not proven by fault injection, and run only where the route corpus is available</t>
@@ -9270,8 +9611,8 @@
           </r>
         </is>
       </c>
-      <c r="L49" s="35" t="n">
-        <v>8</v>
+      <c r="L49" s="46" t="n">
+        <v>9</v>
       </c>
       <c r="M49" s="36" t="inlineStr">
         <is>
@@ -9423,7 +9764,7 @@
       <c r="R50" s="45" t="inlineStr"/>
       <c r="S50" s="45" t="inlineStr"/>
     </row>
-    <row r="51" ht="141" customHeight="1">
+    <row r="51" ht="235.5" customHeight="1">
       <c r="A51" s="30" t="inlineStr">
         <is>
           <r>
@@ -9587,6 +9928,15 @@
             </rPr>
             <t>Driver torque threshold too high or signal parsed wrong</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: SWF-057</t>
+          </r>
         </is>
       </c>
       <c r="I51" s="34" t="inlineStr">
@@ -9618,7 +9968,33 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• As rated in the SW FMEA (SWF-057.C1, D 9 at BL-005): process_replay (CI) replays the TOYOTA3 Corolla TSS2 segment and compares with reference logs made from the same code, so it cannot find a defect already present at the baseline; not designed for this cause</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/test/process_replay/test_processes.py</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
               <sz val="10"/>
             </rPr>
             <t>• opendbc car tests check carState against the panda safety model on recorded routes (test_models); targeted at parse and pack consistency, not proven by fault injection, and run only where the route corpus is available</t>
@@ -9634,8 +10010,8 @@
           </r>
         </is>
       </c>
-      <c r="L51" s="35" t="n">
-        <v>8</v>
+      <c r="L51" s="46" t="n">
+        <v>9</v>
       </c>
       <c r="M51" s="36" t="inlineStr">
         <is>
@@ -9787,7 +10163,7 @@
       <c r="R52" s="45" t="inlineStr"/>
       <c r="S52" s="45" t="inlineStr"/>
     </row>
-    <row r="53" ht="141" customHeight="1">
+    <row r="53" ht="235.5" customHeight="1">
       <c r="A53" s="51" t="inlineStr">
         <is>
           <r>
@@ -9951,6 +10327,15 @@
             </rPr>
             <t>Button message parsed wrong or missing</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: SWF-057</t>
+          </r>
         </is>
       </c>
       <c r="I53" s="41" t="inlineStr">
@@ -9982,7 +10367,33 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• As rated in the SW FMEA (SWF-057.C1, D 9 at BL-005): process_replay (CI) replays the TOYOTA3 Corolla TSS2 segment and compares with reference logs made from the same code, so it cannot find a defect already present at the baseline; not designed for this cause</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/test/process_replay/test_processes.py</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
               <sz val="10"/>
             </rPr>
             <t>• opendbc car tests check carState against the panda safety model on recorded routes (test_models); targeted at parse and pack consistency, not proven by fault injection, and run only where the route corpus is available</t>
@@ -9998,8 +10409,8 @@
           </r>
         </is>
       </c>
-      <c r="L53" s="42" t="n">
-        <v>8</v>
+      <c r="L53" s="43" t="n">
+        <v>9</v>
       </c>
       <c r="M53" s="44" t="inlineStr">
         <is>
@@ -10038,7 +10449,7 @@
       <c r="R53" s="45" t="inlineStr"/>
       <c r="S53" s="45" t="inlineStr"/>
     </row>
-    <row r="54" ht="141" customHeight="1">
+    <row r="54" ht="235.5" customHeight="1">
       <c r="A54" s="51" t="inlineStr">
         <is>
           <r>
@@ -10202,6 +10613,15 @@
             </rPr>
             <t>gasPressed parsed wrong or missing</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: SWF-057</t>
+          </r>
         </is>
       </c>
       <c r="I54" s="41" t="inlineStr">
@@ -10233,7 +10653,33 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• As rated in the SW FMEA (SWF-057.C1, D 9 at BL-005): process_replay (CI) replays the TOYOTA3 Corolla TSS2 segment and compares with reference logs made from the same code, so it cannot find a defect already present at the baseline; not designed for this cause</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/test/process_replay/test_processes.py</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
               <sz val="10"/>
             </rPr>
             <t>• opendbc car tests check carState against the panda safety model on recorded routes (test_models); targeted at parse and pack consistency, not proven by fault injection, and run only where the route corpus is available</t>
@@ -10249,8 +10695,8 @@
           </r>
         </is>
       </c>
-      <c r="L54" s="42" t="n">
-        <v>8</v>
+      <c r="L54" s="43" t="n">
+        <v>9</v>
       </c>
       <c r="M54" s="44" t="inlineStr">
         <is>
@@ -10873,7 +11319,7 @@
       <c r="R57" s="37" t="inlineStr"/>
       <c r="S57" s="37" t="inlineStr"/>
     </row>
-    <row r="58" ht="100.5" customHeight="1">
+    <row r="58" ht="195" customHeight="1">
       <c r="A58" s="38" t="n"/>
       <c r="B58" s="38" t="n"/>
       <c r="C58" s="38" t="n"/>
@@ -10895,6 +11341,15 @@
             </rPr>
             <t>Pose thresholds/calibration wrong for driver or mount</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: SWF-061</t>
+          </r>
         </is>
       </c>
       <c r="I58" s="34" t="inlineStr">
@@ -10923,6 +11378,32 @@
       </c>
       <c r="K58" s="34" t="inlineStr">
         <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• As rated in the SW FMEA (SWF-061.C2, D 8 at BL-005): test_monitoring.py scenarios (distracted, invisible, uncertain, last-second responder) in CI; targeted at the policy, not proven by mutation</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/monitoring/test_monitoring.py</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
           <r>
             <rPr>
               <rFont val="Calibri"/>
@@ -11108,7 +11589,7 @@
       <c r="R59" s="45" t="inlineStr"/>
       <c r="S59" s="45" t="inlineStr"/>
     </row>
-    <row r="60" ht="100.5" customHeight="1">
+    <row r="60" ht="195" customHeight="1">
       <c r="A60" s="30" t="inlineStr">
         <is>
           <r>
@@ -11272,6 +11753,15 @@
             </rPr>
             <t>Policy timers or recovery factor misconfigured</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: SWF-061</t>
+          </r>
         </is>
       </c>
       <c r="I60" s="34" t="inlineStr">
@@ -11300,6 +11790,32 @@
       </c>
       <c r="K60" s="34" t="inlineStr">
         <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• As rated in the SW FMEA (SWF-061.C2, D 8 at BL-005): test_monitoring.py scenarios (distracted, invisible, uncertain, last-second responder) in CI; targeted at the policy, not proven by mutation</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/monitoring/test_monitoring.py</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
           <r>
             <rPr>
               <rFont val="Calibri"/>
@@ -11359,7 +11875,7 @@
       <c r="R60" s="37" t="inlineStr"/>
       <c r="S60" s="37" t="inlineStr"/>
     </row>
-    <row r="61" ht="100.5" customHeight="1">
+    <row r="61" ht="181.5" customHeight="1">
       <c r="A61" s="39" t="n"/>
       <c r="B61" s="39" t="n"/>
       <c r="C61" s="39" t="n"/>
@@ -11381,6 +11897,15 @@
             </rPr>
             <t>Low-speed or always-on exemption applied incorrectly</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: SWF-061</t>
+          </r>
         </is>
       </c>
       <c r="I61" s="41" t="inlineStr">
@@ -11412,10 +11937,10 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• Driver-monitoring policy unit tests (alert timing, awareness recovery, exemptions) on synthetic inputs; targeted, not proven by fault injection; the model itself is not tested</t>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• As rated in the SW FMEA (SWF-061.C3, D 9 at BL-005): test_monitoring.py covers the wheel-touch fallback; not designed for this cause</t>
           </r>
           <r>
             <rPr>
@@ -11426,10 +11951,36 @@
             <t xml:space="preserve">
    openpilot/selfdrive/monitoring/test_monitoring.py</t>
           </r>
-        </is>
-      </c>
-      <c r="L61" s="42" t="n">
-        <v>8</v>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Driver-monitoring policy unit tests (alert timing, awareness recovery, exemptions) on synthetic inputs; targeted, not proven by fault injection; the model itself is not tested</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/monitoring/test_monitoring.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L61" s="43" t="n">
+        <v>9</v>
       </c>
       <c r="M61" s="44" t="inlineStr">
         <is>
@@ -14733,6 +15284,15 @@
             </rPr>
             <t>Fuzzy fingerprint matches a similar platform</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: SWF-058</t>
+          </r>
         </is>
       </c>
       <c r="I78" s="41" t="inlineStr">
@@ -14783,14 +15343,31 @@
         </is>
       </c>
       <c r="J78" s="42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K78" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• As rated in the SW FMEA (SWF-058.C1, D 9 at BL-005): opendbc test_fw_fingerprint exists but is not run by LionDriver CI</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
               <sz val="10"/>
             </rPr>
             <t>• Fingerprinting unit tests (FW and CAN fingerprint); targeted, not proven by fault injection</t>
@@ -14806,8 +15383,8 @@
           </r>
         </is>
       </c>
-      <c r="L78" s="42" t="n">
-        <v>8</v>
+      <c r="L78" s="43" t="n">
+        <v>9</v>
       </c>
       <c r="M78" s="44" t="inlineStr">
         <is>
@@ -16653,7 +17230,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.16 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.17 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -18229,7 +18806,7 @@
         <v>4</v>
       </c>
       <c r="I5" s="35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J5" s="35" t="n">
         <v>5</v>
@@ -18496,7 +19073,7 @@
         <v>10</v>
       </c>
       <c r="I9" s="35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J9" s="35" t="n">
         <v>5</v>
@@ -18563,7 +19140,7 @@
         <v>10</v>
       </c>
       <c r="I10" s="35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J10" s="46" t="n">
         <v>10</v>
@@ -19274,7 +19851,7 @@
         <v>10</v>
       </c>
       <c r="I21" s="35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J21" s="46" t="n">
         <v>9</v>
@@ -19398,7 +19975,7 @@
         <v>10</v>
       </c>
       <c r="I23" s="35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J23" s="46" t="n">
         <v>9</v>
@@ -19528,7 +20105,7 @@
         <v>10</v>
       </c>
       <c r="I25" s="35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J25" s="35" t="n">
         <v>5</v>
@@ -21966,7 +22543,7 @@
         <v>10</v>
       </c>
       <c r="I64" s="35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J64" s="35" t="n">
         <v>8</v>
@@ -22325,7 +22902,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.16 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.17 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -823,7 +823,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.17 · draft</t>
+          <t>0.18 · draft</t>
         </is>
       </c>
     </row>
@@ -12416,6 +12416,15 @@
             </rPr>
             <t>driverDistracted3 / driverUnresponsive3 mapped only to ET.PERMANENT (no disable reaction)</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: SWF-062</t>
+          </r>
         </is>
       </c>
       <c r="I63" s="41" t="inlineStr">
@@ -12450,6 +12459,32 @@
               <color rgb="008A5A00"/>
               <sz val="10"/>
             </rPr>
+            <t>• As rated in the SW FMEA (SWF-062.C1, D 9 at BL-005): test_longitudinal runs the force_decel maneuver in CI and test_monitoring checks the alert levels; neither checks that the reaction meets FSR-040</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/test/longitudinal_maneuvers/test_longitudinal.py</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
             <t>• Present by design and known; no test, because no requirement says what the reaction should be</t>
           </r>
           <r>
@@ -12464,7 +12499,7 @@
         </is>
       </c>
       <c r="L63" s="43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M63" s="44" t="inlineStr">
         <is>
@@ -17230,7 +17265,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.17 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.18 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -22902,7 +22937,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.17 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.18 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -823,7 +823,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.18 · draft</t>
+          <t>0.19 · draft</t>
         </is>
       </c>
     </row>
@@ -17265,7 +17265,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.18 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.19 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -22937,7 +22937,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.18 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.19 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -823,7 +823,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.17 · draft</t>
+          <t>0.20 · draft</t>
         </is>
       </c>
     </row>
@@ -12609,6 +12609,32 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-013: driver-monitoring escalation alerts not shown or played, so an inattentive driver is not told; the forced deceleration does not depend on them (as SWF-082)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
             <t xml:space="preserve">Next higher  </t>
           </r>
           <r>
@@ -12650,7 +12676,8 @@
       <c r="D64" s="31" t="inlineStr">
         <is>
           <t>HZ-012
-HZ-006</t>
+HZ-006
+HZ-013</t>
         </is>
       </c>
       <c r="E64" s="32" t="n">
@@ -13115,6 +13142,32 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-013: a driver-monitoring escalation presented late, or hidden behind a higher-priority alert, so the inattentive driver is told late (as SWF-035)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
             <t xml:space="preserve">Next higher  </t>
           </r>
           <r>
@@ -13155,7 +13208,8 @@
       </c>
       <c r="D67" s="31" t="inlineStr">
         <is>
-          <t>HZ-012</t>
+          <t>HZ-012
+HZ-013</t>
         </is>
       </c>
       <c r="E67" s="32" t="n">
@@ -17230,7 +17284,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.17 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.20 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -22902,7 +22956,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.17 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.20 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -823,7 +823,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.20 · draft</t>
+          <t>0.21 · draft</t>
         </is>
       </c>
     </row>
@@ -7633,6 +7633,32 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-005: positive acceleration requested after an engagement the driver did not ask for</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
             <t xml:space="preserve">Next higher  </t>
           </r>
           <r>
@@ -7673,7 +7699,8 @@
       </c>
       <c r="D39" s="31" t="inlineStr">
         <is>
-          <t>HZ-010</t>
+          <t>HZ-010
+HZ-005</t>
         </is>
       </c>
       <c r="E39" s="32" t="n">
@@ -9445,6 +9472,32 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-005: the item keeps requesting acceleration while the driver brakes</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
             <t xml:space="preserve">Next higher  </t>
           </r>
           <r>
@@ -9485,7 +9538,8 @@
       </c>
       <c r="D49" s="31" t="inlineStr">
         <is>
-          <t>HZ-008</t>
+          <t>HZ-008
+HZ-005</t>
         </is>
       </c>
       <c r="E49" s="32" t="n">
@@ -10815,6 +10869,32 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-008: the driver cancels but stock cruise keeps longitudinal control</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
             <t xml:space="preserve">Next higher  </t>
           </r>
           <r>
@@ -10855,7 +10935,8 @@
       </c>
       <c r="D55" s="31" t="inlineStr">
         <is>
-          <t>HZ-012</t>
+          <t>HZ-012
+HZ-008</t>
         </is>
       </c>
       <c r="E55" s="32" t="n">
@@ -13524,6 +13605,32 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-008: the driver believes control was released by the brake or cancel while the item still acts</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
             <t xml:space="preserve">Next higher  </t>
           </r>
           <r>
@@ -13564,7 +13671,8 @@
       </c>
       <c r="D69" s="31" t="inlineStr">
         <is>
-          <t>HZ-012</t>
+          <t>HZ-012
+HZ-008</t>
         </is>
       </c>
       <c r="E69" s="32" t="n">
@@ -16087,6 +16195,32 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-005: stock ACC and item acceleration requests combine on the bus</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
             <t xml:space="preserve">Next higher  </t>
           </r>
           <r>
@@ -16129,7 +16263,8 @@
         <is>
           <t>HZ-011
 HZ-002
-HZ-006</t>
+HZ-006
+HZ-005</t>
         </is>
       </c>
       <c r="E82" s="32" t="n">
@@ -16264,7 +16399,7 @@
       <c r="R82" s="37" t="inlineStr"/>
       <c r="S82" s="37" t="inlineStr"/>
     </row>
-    <row r="83" ht="102" customHeight="1">
+    <row r="83" ht="142.5" customHeight="1">
       <c r="A83" s="39" t="n"/>
       <c r="B83" s="39" t="n"/>
       <c r="C83" s="39" t="n"/>
@@ -17284,7 +17419,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.20 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.21 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -22956,7 +23091,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.20 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.21 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MSR" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$90</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Worksheet'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Structure'!$A$1:$E$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'MSR'!$A$2:$P$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'MSR'!$A$2:$P$73</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'MSR'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -823,7 +823,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.21 · draft</t>
+          <t>0.22 · draft</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17">
@@ -964,7 +964,7 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>64 rated, 4 exempt; MSR AP H 64, M 0, L 0 (provisional table)</t>
+          <t>67 rated, 4 exempt; MSR AP H 67, M 0, L 0 (provisional table)</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>1–4: 0 · 5–6: 18 · 7–8: 15 · 9–10: 31 (see sheet MSR)</t>
+          <t>1–4: 0 · 5–6: 18 · 7–8: 17 · 9–10: 32 (see sheet MSR)</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S87"/>
+  <dimension ref="A1:S90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17222,9 +17222,496 @@
       <c r="R87" s="45" t="inlineStr"/>
       <c r="S87" s="45" t="inlineStr"/>
     </row>
+    <row r="88" ht="100.5" customHeight="1">
+      <c r="A88" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-SE-001
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>LionDriver item (L2 ACC + ALC + driver monitoring)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B88" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-FN-002
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>F2 Longitudinal control: request acceleration/deceleration to hold set speed and follow leads while engaged</t>
+          </r>
+        </is>
+      </c>
+      <c r="C88" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Unintended acceleration when the frozen request is positive</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Insufficient deceleration when the lead brakes and the frozen request is not braking</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Vehicle holds a constant acceleration or deceleration request</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Same acceleration request repeated regardless of lead, set speed or road</t>
+          </r>
+        </is>
+      </c>
+      <c r="D88" s="31" t="inlineStr">
+        <is>
+          <t>HZ-005
+HZ-007</t>
+        </is>
+      </c>
+      <c r="E88" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F88" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-037 · stuck
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Longitudinal command frozen at last value</t>
+          </r>
+        </is>
+      </c>
+      <c r="G88" s="33" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H88" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>controlsd hangs while card keeps sending the last carControl</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: SWF-047</t>
+          </r>
+        </is>
+      </c>
+      <c r="I88" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream review, ruff, ty; rated in the SW FMEA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/08-analyses/fmea/analyses/sw-fmea.yaml</t>
+          </r>
+        </is>
+      </c>
+      <c r="J88" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="K88" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• As rated in the SW FMEA (SWF-047.C1, D 10 at BL-005): no test injects the exception that stops controlsd</t>
+          </r>
+        </is>
+      </c>
+      <c r="L88" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="M88" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N88" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-ACT-002 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Requirements-based tests for the host safety-relevant functions (selfdrived, controlsd, pandad, car interface, locationd bounds, monitoring policy), proven by mutation or fault injection and run as a CI gate (see SWF host actions)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O88" s="47" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P88" s="33" t="inlineStr"/>
+      <c r="Q88" s="33" t="inlineStr"/>
+      <c r="R88" s="37" t="inlineStr"/>
+      <c r="S88" s="37" t="inlineStr"/>
+    </row>
+    <row r="89" ht="100.5" customHeight="1">
+      <c r="A89" s="38" t="n"/>
+      <c r="B89" s="38" t="n"/>
+      <c r="C89" s="38" t="n"/>
+      <c r="D89" s="38" t="n"/>
+      <c r="E89" s="38" t="n"/>
+      <c r="F89" s="38" t="n"/>
+      <c r="G89" s="33" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H89" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>plannerd stops or runs late while engaged, so controlsd keeps using the last longitudinalPlan</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: SWF-068</t>
+          </r>
+        </is>
+      </c>
+      <c r="I89" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream openpilot code with upstream review; rated in the SW FMEA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/08-analyses/fmea/analyses/sw-fmea.yaml</t>
+          </r>
+        </is>
+      </c>
+      <c r="J89" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="K89" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• As rated in the SW FMEA (SWF-068.C1, D 9 at BL-005): no test targets an exception in the planner loop</t>
+          </r>
+        </is>
+      </c>
+      <c r="L89" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="M89" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N89" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-ACT-002 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Requirements-based tests for the host safety-relevant functions (selfdrived, controlsd, pandad, car interface, locationd bounds, monitoring policy), proven by mutation or fault injection and run as a CI gate (see SWF host actions)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O89" s="47" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P89" s="33" t="inlineStr"/>
+      <c r="Q89" s="33" t="inlineStr"/>
+      <c r="R89" s="37" t="inlineStr"/>
+      <c r="S89" s="37" t="inlineStr"/>
+    </row>
+    <row r="90" ht="100.5" customHeight="1">
+      <c r="A90" s="39" t="n"/>
+      <c r="B90" s="39" t="n"/>
+      <c r="C90" s="39" t="n"/>
+      <c r="D90" s="39" t="n"/>
+      <c r="E90" s="39" t="n"/>
+      <c r="F90" s="39" t="n"/>
+      <c r="G90" s="40" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="H90" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Messaging delivers a stale longitudinal plan or command with fresh timestamps</t>
+          </r>
+        </is>
+      </c>
+      <c r="I90" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• msgq/cereal stamp logMonoTime at publication; SubMaster tracks arrival time and frequency</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/cereal/messaging/__init__.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="J90" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="K90" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No pre-release test targets this cause</t>
+          </r>
+        </is>
+      </c>
+      <c r="L90" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="M90" s="44" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N90" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-ACT-002 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Requirements-based tests for the host safety-relevant functions (selfdrived, controlsd, pandad, car interface, locationd bounds, monitoring policy), proven by mutation or fault injection and run as a CI gate (see SWF host actions)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O90" s="48" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P90" s="40" t="inlineStr"/>
+      <c r="Q90" s="40" t="inlineStr"/>
+      <c r="R90" s="45" t="inlineStr"/>
+      <c r="S90" s="45" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:S87"/>
-  <mergeCells count="184">
+  <autoFilter ref="A2:S90"/>
+  <mergeCells count="190">
     <mergeCell ref="F84:F85"/>
     <mergeCell ref="F17:F19"/>
     <mergeCell ref="E39:E40"/>
@@ -17272,6 +17759,7 @@
     <mergeCell ref="F41:F43"/>
     <mergeCell ref="D10:D13"/>
     <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B88:B90"/>
     <mergeCell ref="F10:F13"/>
     <mergeCell ref="D49:D50"/>
     <mergeCell ref="E55:E56"/>
@@ -17291,6 +17779,7 @@
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="B84:B85"/>
     <mergeCell ref="C51:C52"/>
+    <mergeCell ref="A88:A90"/>
     <mergeCell ref="C60:C61"/>
     <mergeCell ref="C64:C66"/>
     <mergeCell ref="D25:D28"/>
@@ -17303,6 +17792,8 @@
     <mergeCell ref="C79:C81"/>
     <mergeCell ref="I1:M1"/>
     <mergeCell ref="E79:E81"/>
+    <mergeCell ref="C88:C90"/>
+    <mergeCell ref="E88:E90"/>
     <mergeCell ref="D39:D40"/>
     <mergeCell ref="A39:A40"/>
     <mergeCell ref="A3:A5"/>
@@ -17384,6 +17875,8 @@
     <mergeCell ref="B79:B81"/>
     <mergeCell ref="B32:B34"/>
     <mergeCell ref="D79:D81"/>
+    <mergeCell ref="D88:D90"/>
+    <mergeCell ref="F88:F90"/>
     <mergeCell ref="C67:C68"/>
     <mergeCell ref="E17:E19"/>
     <mergeCell ref="D71:D74"/>
@@ -17411,7 +17904,7 @@
     <mergeCell ref="D84:D85"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83 R84 R85 R86 R87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
+    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83 R84 R85 R86 R87 R88 R89 R90" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
       <formula1>"Agree,Re-rate,Reject,Question"</formula1>
     </dataValidation>
   </dataValidations>
@@ -17419,7 +17912,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.21 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.22 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -17538,7 +18031,7 @@
       <c r="H2" s="61" t="inlineStr"/>
       <c r="I2" s="61" t="inlineStr"/>
     </row>
-    <row r="3" ht="127.5" customHeight="1">
+    <row r="3" ht="168" customHeight="1">
       <c r="A3" s="61" t="inlineStr">
         <is>
           <t>SFM-ACT-002</t>
@@ -17574,7 +18067,10 @@
 SFM-008.C1
 SFM-023.C1
 SFM-023.C2
-SFM-030.C1</t>
+SFM-030.C1
+SFM-037.C1
+SFM-037.C2
+SFM-037.C3</t>
         </is>
       </c>
       <c r="G3" s="61" t="inlineStr"/>
@@ -18718,7 +19214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P70"/>
+  <dimension ref="A1:P73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -23077,13 +23573,208 @@
       <c r="O70" s="37" t="inlineStr"/>
       <c r="P70" s="37" t="inlineStr"/>
     </row>
+    <row r="71" ht="100.5" customHeight="1">
+      <c r="A71" s="34" t="inlineStr">
+        <is>
+          <t>SFM-037 · Longitudinal command frozen at last value</t>
+        </is>
+      </c>
+      <c r="B71" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C71" s="33" t="inlineStr">
+        <is>
+          <t>SFM-037.C1</t>
+        </is>
+      </c>
+      <c r="D71" s="34" t="inlineStr">
+        <is>
+          <t>controlsd hangs while card keeps sending the last carControl</t>
+        </is>
+      </c>
+      <c r="E71" s="34" t="inlineStr">
+        <is>
+          <t>card stops sending once carControl is 0.1 s old (T-13); the panda then revokes authority within 0.11 s of the last ACC_CONTROL frame (TSR-408, T-34) and selfdrived raises controlsMismatch within 0.5 s (TSR-621)</t>
+        </is>
+      </c>
+      <c r="F71" s="34" t="inlineStr">
+        <is>
+          <t>controlsMismatch IMMEDIATE_DISABLE with alert; no ACC_CONTROL frame follows the stall and there is no active zero request (TSR-109), so what the PCM does with the last request after the frames stop is not known (AOU, not measured)</t>
+        </is>
+      </c>
+      <c r="G71" s="34" t="inlineStr">
+        <is>
+          <t>Last request held about 0.2 s, then frames stop; the PCM reaction to missing ACC_CONTROL is not established</t>
+        </is>
+      </c>
+      <c r="H71" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I71" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J71" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="K71" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L71" s="34" t="inlineStr">
+        <is>
+          <t>SG-03/04 · 1000 ms</t>
+        </is>
+      </c>
+      <c r="M71" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N71" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-015 · in progress</t>
+        </is>
+      </c>
+      <c r="O71" s="37" t="inlineStr"/>
+      <c r="P71" s="37" t="inlineStr"/>
+    </row>
+    <row r="72" ht="46.5" customHeight="1">
+      <c r="A72" s="34" t="inlineStr">
+        <is>
+          <t>SFM-037 · Longitudinal command frozen at last value</t>
+        </is>
+      </c>
+      <c r="B72" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C72" s="33" t="inlineStr">
+        <is>
+          <t>SFM-037.C2</t>
+        </is>
+      </c>
+      <c r="D72" s="34" t="inlineStr">
+        <is>
+          <t>plannerd stops or runs late while engaged, so controlsd keeps using the last longitudinalPlan</t>
+        </is>
+      </c>
+      <c r="E72" s="34" t="inlineStr">
+        <is>
+          <t>selfdrived liveness check on longitudinalPlan (10 missed periods at 20 Hz, 0.5 s, T-14)</t>
+        </is>
+      </c>
+      <c r="F72" s="34" t="inlineStr">
+        <is>
+          <t>commIssue SOFT_DISABLE; actuation continues for the 3 s countdown (T-16) on the last plan</t>
+        </is>
+      </c>
+      <c r="G72" s="34" t="inlineStr">
+        <is>
+          <t>Frozen request held up to about 3.5 s before the item disengages</t>
+        </is>
+      </c>
+      <c r="H72" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I72" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="J72" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="K72" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L72" s="34" t="inlineStr">
+        <is>
+          <t>SG-03/04 · 1000 ms
+500 + 3000 ms</t>
+        </is>
+      </c>
+      <c r="M72" s="33" t="inlineStr">
+        <is>
+          <t>code derived</t>
+        </is>
+      </c>
+      <c r="N72" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-015 · in progress</t>
+        </is>
+      </c>
+      <c r="O72" s="37" t="inlineStr"/>
+      <c r="P72" s="37" t="inlineStr"/>
+    </row>
+    <row r="73" ht="46.5" customHeight="1">
+      <c r="A73" s="34" t="inlineStr">
+        <is>
+          <t>SFM-037 · Longitudinal command frozen at last value</t>
+        </is>
+      </c>
+      <c r="B73" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C73" s="33" t="inlineStr">
+        <is>
+          <t>SFM-037.C3</t>
+        </is>
+      </c>
+      <c r="D73" s="34" t="inlineStr">
+        <is>
+          <t>Messaging delivers a stale longitudinal plan or command with fresh timestamps</t>
+        </is>
+      </c>
+      <c r="E73" s="34" t="inlineStr">
+        <is>
+          <t>Liveness checks use arrival and timestamps, so stale data with fresh timestamps passes them</t>
+        </is>
+      </c>
+      <c r="F73" s="34" t="inlineStr">
+        <is>
+          <t>None until another check trips</t>
+        </is>
+      </c>
+      <c r="G73" s="34" t="inlineStr">
+        <is>
+          <t>Unchanged: longitudinal control acts on stale data</t>
+        </is>
+      </c>
+      <c r="H73" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I73" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="J73" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="K73" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L73" s="34" t="inlineStr"/>
+      <c r="M73" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N73" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-015 · in progress</t>
+        </is>
+      </c>
+      <c r="O73" s="37" t="inlineStr"/>
+      <c r="P73" s="37" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:P70"/>
+  <autoFilter ref="A2:P73"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="O3 O4 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 O34 O35 O36 O37 O38 O39 O40 O41 O42 O43 O44 O45 O46 O47 O48 O49 O50 O51 O52 O53 O54 O55 O56 O57 O58 O59 O60 O61 O62 O63 O64 O65 O66 O67 O68 O69 O70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this MSR row" type="list">
+    <dataValidation sqref="O3 O4 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 O34 O35 O36 O37 O38 O39 O40 O41 O42 O43 O44 O45 O46 O47 O48 O49 O50 O51 O52 O53 O54 O55 O56 O57 O58 O59 O60 O61 O62 O63 O64 O65 O66 O67 O68 O69 O70 O71 O72 O73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this MSR row" type="list">
       <formula1>"Agree,Re-rate,Reject,Question"</formula1>
     </dataValidation>
   </dataValidations>
@@ -23091,7 +23782,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.21 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.22 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MSR" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$93</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Worksheet'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Structure'!$A$1:$E$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'MSR'!$A$2:$P$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'MSR'!$A$2:$P$76</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'MSR'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -823,7 +823,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.22 · draft</t>
+          <t>0.23 · draft</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -952,7 +952,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>21 (19)</t>
+          <t>22 (20)</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>67 rated, 4 exempt; MSR AP H 67, M 0, L 0 (provisional table)</t>
+          <t>67 rated, 7 exempt; MSR AP H 67, M 0, L 0 (provisional table)</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S90"/>
+  <dimension ref="A1:S93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17709,9 +17709,460 @@
       <c r="R90" s="45" t="inlineStr"/>
       <c r="S90" s="45" t="inlineStr"/>
     </row>
+    <row r="91" ht="114" customHeight="1">
+      <c r="A91" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-SE-001
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>LionDriver item (L2 ACC + ALC + driver monitoring)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B91" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-FN-006
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>F6 Alerting: inform the driver of engagement state, takeover requests and faults (visual and audible)</t>
+          </r>
+        </is>
+      </c>
+      <c r="C91" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Driver unaware of the loss or limit; lane departure</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Driver not prompted to take over while lateral control is lost or limited</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>steerTempUnavailable shown silently, steerSaturated raised late or not at all, or the panda's EPS-fault flag not acted on</t>
+          </r>
+        </is>
+      </c>
+      <c r="D91" s="31" t="inlineStr">
+        <is>
+          <t>HZ-004</t>
+        </is>
+      </c>
+      <c r="E91" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F91" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-038 · late
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Warning of a lateral-control fault or limit late, silent or missing</t>
+          </r>
+        </is>
+      </c>
+      <c r="G91" s="33" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H91" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>After any driver steering input in the last 1.5 s, a temporary EPS fault raises only steerTempUnavailableSilent (a small WARNING with no soft disable), and the warning stays silent for as long as the fault lasts (car_events.py:162-177; T-25, GAP-03)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I91" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream openpilot design choice (a softer alert after an override); no LionDriver requirement on it</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/car/car_events.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="J91" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="K91" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No LionDriver test targets this cause</t>
+          </r>
+        </is>
+      </c>
+      <c r="L91" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="M91" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N91" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-ACT-023 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Warn audibly and with a take-over request on every EPS fault while engaged, with no silent variant after a recent override (car_events.py steerTempUnavailableSilent), and act on the panda fields epsFault and requestsRejected on the host (TSR-626(d), TSR-516(b)). SFM-038.C1, C2; FTA BE-2.08</t>
+          </r>
+        </is>
+      </c>
+      <c r="O91" s="47" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P91" s="33" t="inlineStr"/>
+      <c r="Q91" s="33" t="inlineStr"/>
+      <c r="R91" s="37" t="inlineStr"/>
+      <c r="S91" s="37" t="inlineStr"/>
+    </row>
+    <row r="92" ht="114" customHeight="1">
+      <c r="A92" s="38" t="n"/>
+      <c r="B92" s="38" t="n"/>
+      <c r="C92" s="38" t="n"/>
+      <c r="D92" s="38" t="n"/>
+      <c r="E92" s="38" t="n"/>
+      <c r="F92" s="38" t="n"/>
+      <c r="G92" s="33" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H92" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>pandad publishes the panda fields epsFault and requestsRejected (pandad.cc:137-138), but no SoC process reads them (txRateExceeded is read, TSR-615), so a panda-side EPS-fault refusal reaches the driver only through the panda siren and the stock EPS path (SW FMEA SWF-025 notes)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I92" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• None; the fields were added for the panda siren and logging</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/pandad/pandad.cc</t>
+          </r>
+        </is>
+      </c>
+      <c r="J92" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="K92" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No test targets this cause</t>
+          </r>
+        </is>
+      </c>
+      <c r="L92" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="M92" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N92" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-ACT-023 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Warn audibly and with a take-over request on every EPS fault while engaged, with no silent variant after a recent override (car_events.py steerTempUnavailableSilent), and act on the panda fields epsFault and requestsRejected on the host (TSR-626(d), TSR-516(b)). SFM-038.C1, C2; FTA BE-2.08</t>
+          </r>
+        </is>
+      </c>
+      <c r="O92" s="47" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P92" s="33" t="inlineStr"/>
+      <c r="Q92" s="33" t="inlineStr"/>
+      <c r="R92" s="37" t="inlineStr"/>
+      <c r="S92" s="37" t="inlineStr"/>
+    </row>
+    <row r="93" ht="127.5" customHeight="1">
+      <c r="A93" s="39" t="n"/>
+      <c r="B93" s="39" t="n"/>
+      <c r="C93" s="39" t="n"/>
+      <c r="D93" s="39" t="n"/>
+      <c r="E93" s="39" t="n"/>
+      <c r="F93" s="39" t="n"/>
+      <c r="G93" s="40" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="H93" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>steerSaturated needs the controller saturated, a desired lateral acceleration above 1.0 m/s², an undershoot above 1.2x and no steering input for 2 s (selfdrived.py:465-479), and the controller reports saturation only after 0.4 s (latcontrol.py, T-30); a gradual deficit therefore warns late or not at all (WP-S-04 §3.8.1)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I93" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream openpilot code with upstream review; ruff and type checks in CI (static analysis job)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   scripts/lint/lint.sh</t>
+          </r>
+        </is>
+      </c>
+      <c r="J93" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="K93" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Lateral controller unit tests (saturation detection); targeted at nominal behaviour, not proven</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/controls/tests/test_latcontrol.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L93" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="M93" s="44" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N93" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-ACT-021 · monitoring
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Make the insufficient-lateral-control warning timely (WP-S-04 §3.8.1): warn before the deficit has lasted 0.4 s, for example from the planned curvature against the envelope, or keep the deficit at or below about 0.5 m/s² through the steering limits and the ODD curve bound (WP-S-04 OI-2). A change to the ODD bound is a lead decision</t>
+          </r>
+        </is>
+      </c>
+      <c r="O93" s="48" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P93" s="40" t="inlineStr"/>
+      <c r="Q93" s="40" t="inlineStr"/>
+      <c r="R93" s="45" t="inlineStr"/>
+      <c r="S93" s="45" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:S90"/>
-  <mergeCells count="190">
+  <autoFilter ref="A2:S93"/>
+  <mergeCells count="196">
     <mergeCell ref="F84:F85"/>
     <mergeCell ref="F17:F19"/>
     <mergeCell ref="E39:E40"/>
@@ -17830,6 +18281,7 @@
     <mergeCell ref="B10:B13"/>
     <mergeCell ref="C23:C24"/>
     <mergeCell ref="B49:B50"/>
+    <mergeCell ref="B91:B93"/>
     <mergeCell ref="C20:C22"/>
     <mergeCell ref="C14:C16"/>
     <mergeCell ref="E20:E22"/>
@@ -17842,7 +18294,9 @@
     <mergeCell ref="F49:F50"/>
     <mergeCell ref="B17:B19"/>
     <mergeCell ref="B75:B76"/>
+    <mergeCell ref="D91:D93"/>
     <mergeCell ref="F20:F22"/>
+    <mergeCell ref="F91:F93"/>
     <mergeCell ref="B44:B46"/>
     <mergeCell ref="A67:A68"/>
     <mergeCell ref="E71:E74"/>
@@ -17852,7 +18306,9 @@
     <mergeCell ref="E57:E59"/>
     <mergeCell ref="A69:A70"/>
     <mergeCell ref="D6:D9"/>
+    <mergeCell ref="A91:A93"/>
     <mergeCell ref="F6:F9"/>
+    <mergeCell ref="C91:C93"/>
     <mergeCell ref="D64:D66"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="E41:E43"/>
@@ -17866,6 +18322,7 @@
     <mergeCell ref="E35:E36"/>
     <mergeCell ref="A75:A76"/>
     <mergeCell ref="C75:C76"/>
+    <mergeCell ref="E91:E93"/>
     <mergeCell ref="F57:F59"/>
     <mergeCell ref="B64:B66"/>
     <mergeCell ref="C25:C28"/>
@@ -17904,7 +18361,7 @@
     <mergeCell ref="D84:D85"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83 R84 R85 R86 R87 R88 R89 R90" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
+    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83 R84 R85 R86 R87 R88 R89 R90 R91 R92 R93" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
       <formula1>"Agree,Re-rate,Reject,Question"</formula1>
     </dataValidation>
   </dataValidations>
@@ -17912,7 +18369,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.22 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.23 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -17927,7 +18384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18697,7 +19154,11 @@
           <t>open</t>
         </is>
       </c>
-      <c r="F21" s="61" t="inlineStr"/>
+      <c r="F21" s="61" t="inlineStr">
+        <is>
+          <t>SFM-038.C3</t>
+        </is>
+      </c>
       <c r="G21" s="61" t="inlineStr"/>
       <c r="H21" s="61" t="inlineStr"/>
       <c r="I21" s="61" t="inlineStr"/>
@@ -18729,8 +19190,40 @@
       <c r="H22" s="61" t="inlineStr"/>
       <c r="I22" s="61" t="inlineStr"/>
     </row>
+    <row r="23" ht="73.5" customHeight="1">
+      <c r="A23" s="61" t="inlineStr">
+        <is>
+          <t>SFM-ACT-023</t>
+        </is>
+      </c>
+      <c r="B23" s="61" t="inlineStr">
+        <is>
+          <t>design change</t>
+        </is>
+      </c>
+      <c r="C23" s="61" t="inlineStr">
+        <is>
+          <t>Warn audibly and with a take-over request on every EPS fault while engaged, with no silent variant after a recent override (car_events.py steerTempUnavailableSilent), and act on the panda fields epsFault and requestsRejected on the host (TSR-626(d), TSR-516(b)). SFM-038.C1, C2; FTA BE-2.08</t>
+        </is>
+      </c>
+      <c r="D23" s="61" t="inlineStr"/>
+      <c r="E23" s="61" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F23" s="61" t="inlineStr">
+        <is>
+          <t>SFM-038.C1
+SFM-038.C2</t>
+        </is>
+      </c>
+      <c r="G23" s="61" t="inlineStr"/>
+      <c r="H23" s="61" t="inlineStr"/>
+      <c r="I23" s="61" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I22"/>
+  <autoFilter ref="A1:I23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19214,7 +19707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P73"/>
+  <dimension ref="A1:P76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -23768,13 +24261,121 @@
       <c r="O73" s="37" t="inlineStr"/>
       <c r="P73" s="37" t="inlineStr"/>
     </row>
+    <row r="74" ht="100.5" customHeight="1">
+      <c r="A74" s="34" t="inlineStr">
+        <is>
+          <t>SFM-038 · Warning of a lateral-control fault or limit late, silent or missing</t>
+        </is>
+      </c>
+      <c r="B74" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C74" s="33" t="inlineStr">
+        <is>
+          <t>SFM-038.C1</t>
+        </is>
+      </c>
+      <c r="D74" s="34" t="inlineStr">
+        <is>
+          <t>After any driver steering input in the last 1.5 s, a temporary EPS fault raises only steerTempUnavailableSilent (a small WARNING with no soft disable), and the warning stays silent for as long as the fault lasts (car_events.py:162-177; T-25, GAP-03)</t>
+        </is>
+      </c>
+      <c r="E74" s="64" t="inlineStr">
+        <is>
+          <t>Exempt: The cause is a defect of the warning path itself; its effect on detecting the lateral loss is rated in the MSR rows of SFM-004.C2 and SFM-005 (msr-plan §3)</t>
+        </is>
+      </c>
+      <c r="F74" s="34" t="inlineStr"/>
+      <c r="G74" s="34" t="inlineStr"/>
+      <c r="H74" s="35" t="inlineStr"/>
+      <c r="I74" s="35" t="inlineStr"/>
+      <c r="J74" s="35" t="inlineStr"/>
+      <c r="K74" s="33" t="inlineStr"/>
+      <c r="L74" s="34" t="inlineStr"/>
+      <c r="M74" s="33" t="inlineStr"/>
+      <c r="N74" s="34" t="inlineStr"/>
+      <c r="O74" s="37" t="inlineStr"/>
+      <c r="P74" s="37" t="inlineStr"/>
+    </row>
+    <row r="75" ht="114" customHeight="1">
+      <c r="A75" s="34" t="inlineStr">
+        <is>
+          <t>SFM-038 · Warning of a lateral-control fault or limit late, silent or missing</t>
+        </is>
+      </c>
+      <c r="B75" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C75" s="33" t="inlineStr">
+        <is>
+          <t>SFM-038.C2</t>
+        </is>
+      </c>
+      <c r="D75" s="34" t="inlineStr">
+        <is>
+          <t>pandad publishes the panda fields epsFault and requestsRejected (pandad.cc:137-138), but no SoC process reads them (txRateExceeded is read, TSR-615), so a panda-side EPS-fault refusal reaches the driver only through the panda siren and the stock EPS path (SW FMEA SWF-025 notes)</t>
+        </is>
+      </c>
+      <c r="E75" s="64" t="inlineStr">
+        <is>
+          <t>Exempt: The cause is a defect of the warning path itself; the panda siren that remains is rated on SFM-005 and in the DFMEA (msr-plan §3)</t>
+        </is>
+      </c>
+      <c r="F75" s="34" t="inlineStr"/>
+      <c r="G75" s="34" t="inlineStr"/>
+      <c r="H75" s="35" t="inlineStr"/>
+      <c r="I75" s="35" t="inlineStr"/>
+      <c r="J75" s="35" t="inlineStr"/>
+      <c r="K75" s="33" t="inlineStr"/>
+      <c r="L75" s="34" t="inlineStr"/>
+      <c r="M75" s="33" t="inlineStr"/>
+      <c r="N75" s="34" t="inlineStr"/>
+      <c r="O75" s="37" t="inlineStr"/>
+      <c r="P75" s="37" t="inlineStr"/>
+    </row>
+    <row r="76" ht="127.5" customHeight="1">
+      <c r="A76" s="34" t="inlineStr">
+        <is>
+          <t>SFM-038 · Warning of a lateral-control fault or limit late, silent or missing</t>
+        </is>
+      </c>
+      <c r="B76" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C76" s="33" t="inlineStr">
+        <is>
+          <t>SFM-038.C3</t>
+        </is>
+      </c>
+      <c r="D76" s="34" t="inlineStr">
+        <is>
+          <t>steerSaturated needs the controller saturated, a desired lateral acceleration above 1.0 m/s², an undershoot above 1.2x and no steering input for 2 s (selfdrived.py:465-479), and the controller reports saturation only after 0.4 s (latcontrol.py, T-30); a gradual deficit therefore warns late or not at all (WP-S-04 §3.8.1)</t>
+        </is>
+      </c>
+      <c r="E76" s="64" t="inlineStr">
+        <is>
+          <t>Exempt: The cause is the timing of the warning itself; it is rated as M 8 in the MSR rows of SFM-004.C1-C3 (rev 0.15, WP-S-04 §3.8.1)</t>
+        </is>
+      </c>
+      <c r="F76" s="34" t="inlineStr"/>
+      <c r="G76" s="34" t="inlineStr"/>
+      <c r="H76" s="35" t="inlineStr"/>
+      <c r="I76" s="35" t="inlineStr"/>
+      <c r="J76" s="35" t="inlineStr"/>
+      <c r="K76" s="33" t="inlineStr"/>
+      <c r="L76" s="34" t="inlineStr"/>
+      <c r="M76" s="33" t="inlineStr"/>
+      <c r="N76" s="34" t="inlineStr"/>
+      <c r="O76" s="37" t="inlineStr"/>
+      <c r="P76" s="37" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:P73"/>
+  <autoFilter ref="A2:P76"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="O3 O4 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 O34 O35 O36 O37 O38 O39 O40 O41 O42 O43 O44 O45 O46 O47 O48 O49 O50 O51 O52 O53 O54 O55 O56 O57 O58 O59 O60 O61 O62 O63 O64 O65 O66 O67 O68 O69 O70 O71 O72 O73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this MSR row" type="list">
+    <dataValidation sqref="O3 O4 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 O34 O35 O36 O37 O38 O39 O40 O41 O42 O43 O44 O45 O46 O47 O48 O49 O50 O51 O52 O53 O54 O55 O56 O57 O58 O59 O60 O61 O62 O63 O64 O65 O66 O67 O68 O69 O70 O71 O72 O73 O74 O75 O76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this MSR row" type="list">
       <formula1>"Agree,Re-rate,Reject,Question"</formula1>
     </dataValidation>
   </dataValidations>
@@ -23782,7 +24383,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.22 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.23 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -823,7 +823,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.19 · draft</t>
+          <t>0.20 · draft</t>
         </is>
       </c>
     </row>
@@ -12644,6 +12644,32 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-013: driver-monitoring escalation alerts not shown or played, so an inattentive driver is not told; the forced deceleration does not depend on them (as SWF-082)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
             <t xml:space="preserve">Next higher  </t>
           </r>
           <r>
@@ -12685,7 +12711,8 @@
       <c r="D64" s="31" t="inlineStr">
         <is>
           <t>HZ-012
-HZ-006</t>
+HZ-006
+HZ-013</t>
         </is>
       </c>
       <c r="E64" s="32" t="n">
@@ -13150,6 +13177,32 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-013: a driver-monitoring escalation presented late, or hidden behind a higher-priority alert, so the inattentive driver is told late (as SWF-035)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
             <t xml:space="preserve">Next higher  </t>
           </r>
           <r>
@@ -13190,7 +13243,8 @@
       </c>
       <c r="D67" s="31" t="inlineStr">
         <is>
-          <t>HZ-012</t>
+          <t>HZ-012
+HZ-013</t>
         </is>
       </c>
       <c r="E67" s="32" t="n">
@@ -17265,7 +17319,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.19 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.20 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -22937,7 +22991,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.19 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.20 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -823,7 +823,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.20 · draft</t>
+          <t>0.21 · draft</t>
         </is>
       </c>
     </row>
@@ -7633,6 +7633,32 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-005: positive acceleration requested after an engagement the driver did not ask for</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
             <t xml:space="preserve">Next higher  </t>
           </r>
           <r>
@@ -7673,7 +7699,8 @@
       </c>
       <c r="D39" s="31" t="inlineStr">
         <is>
-          <t>HZ-010</t>
+          <t>HZ-010
+HZ-005</t>
         </is>
       </c>
       <c r="E39" s="32" t="n">
@@ -9445,6 +9472,32 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-005: the item keeps requesting acceleration while the driver brakes</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
             <t xml:space="preserve">Next higher  </t>
           </r>
           <r>
@@ -9485,7 +9538,8 @@
       </c>
       <c r="D49" s="31" t="inlineStr">
         <is>
-          <t>HZ-008</t>
+          <t>HZ-008
+HZ-005</t>
         </is>
       </c>
       <c r="E49" s="32" t="n">
@@ -10815,6 +10869,32 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-008: the driver cancels but stock cruise keeps longitudinal control</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
             <t xml:space="preserve">Next higher  </t>
           </r>
           <r>
@@ -10855,7 +10935,8 @@
       </c>
       <c r="D55" s="31" t="inlineStr">
         <is>
-          <t>HZ-012</t>
+          <t>HZ-012
+HZ-008</t>
         </is>
       </c>
       <c r="E55" s="32" t="n">
@@ -13559,6 +13640,32 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-008: the driver believes control was released by the brake or cancel while the item still acts</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
             <t xml:space="preserve">Next higher  </t>
           </r>
           <r>
@@ -13599,7 +13706,8 @@
       </c>
       <c r="D69" s="31" t="inlineStr">
         <is>
-          <t>HZ-012</t>
+          <t>HZ-012
+HZ-008</t>
         </is>
       </c>
       <c r="E69" s="32" t="n">
@@ -16122,6 +16230,32 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-005: stock ACC and item acceleration requests combine on the bus</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
             <t xml:space="preserve">Next higher  </t>
           </r>
           <r>
@@ -16164,7 +16298,8 @@
         <is>
           <t>HZ-011
 HZ-002
-HZ-006</t>
+HZ-006
+HZ-005</t>
         </is>
       </c>
       <c r="E82" s="32" t="n">
@@ -16299,7 +16434,7 @@
       <c r="R82" s="37" t="inlineStr"/>
       <c r="S82" s="37" t="inlineStr"/>
     </row>
-    <row r="83" ht="102" customHeight="1">
+    <row r="83" ht="142.5" customHeight="1">
       <c r="A83" s="39" t="n"/>
       <c r="B83" s="39" t="n"/>
       <c r="C83" s="39" t="n"/>
@@ -17319,7 +17454,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.20 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.21 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -22991,7 +23126,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.20 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.21 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MSR" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$90</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Worksheet'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Structure'!$A$1:$E$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'MSR'!$A$2:$P$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'MSR'!$A$2:$P$73</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'MSR'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -823,7 +823,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.21 · draft</t>
+          <t>0.22 · draft</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17">
@@ -964,7 +964,7 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>64 rated, 4 exempt; MSR AP H 64, M 0, L 0 (provisional table)</t>
+          <t>67 rated, 4 exempt; MSR AP H 67, M 0, L 0 (provisional table)</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>1–4: 0 · 5–6: 18 · 7–8: 15 · 9–10: 31 (see sheet MSR)</t>
+          <t>1–4: 0 · 5–6: 18 · 7–8: 17 · 9–10: 32 (see sheet MSR)</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S87"/>
+  <dimension ref="A1:S90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17257,9 +17257,496 @@
       <c r="R87" s="45" t="inlineStr"/>
       <c r="S87" s="45" t="inlineStr"/>
     </row>
+    <row r="88" ht="100.5" customHeight="1">
+      <c r="A88" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-SE-001
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>LionDriver item (L2 ACC + ALC + driver monitoring)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B88" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-FN-002
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>F2 Longitudinal control: request acceleration/deceleration to hold set speed and follow leads while engaged</t>
+          </r>
+        </is>
+      </c>
+      <c r="C88" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Unintended acceleration when the frozen request is positive</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Insufficient deceleration when the lead brakes and the frozen request is not braking</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Vehicle holds a constant acceleration or deceleration request</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Same acceleration request repeated regardless of lead, set speed or road</t>
+          </r>
+        </is>
+      </c>
+      <c r="D88" s="31" t="inlineStr">
+        <is>
+          <t>HZ-005
+HZ-007</t>
+        </is>
+      </c>
+      <c r="E88" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F88" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-037 · stuck
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Longitudinal command frozen at last value</t>
+          </r>
+        </is>
+      </c>
+      <c r="G88" s="33" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H88" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>controlsd hangs while card keeps sending the last carControl</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: SWF-047</t>
+          </r>
+        </is>
+      </c>
+      <c r="I88" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream review, ruff, ty; rated in the SW FMEA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/08-analyses/fmea/analyses/sw-fmea.yaml</t>
+          </r>
+        </is>
+      </c>
+      <c r="J88" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="K88" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• As rated in the SW FMEA (SWF-047.C1, D 10 at BL-005): no test injects the exception that stops controlsd</t>
+          </r>
+        </is>
+      </c>
+      <c r="L88" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="M88" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N88" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-ACT-002 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Requirements-based tests for the host safety-relevant functions (selfdrived, controlsd, pandad, car interface, locationd bounds, monitoring policy), proven by mutation or fault injection and run as a CI gate (see SWF host actions)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O88" s="47" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P88" s="33" t="inlineStr"/>
+      <c r="Q88" s="33" t="inlineStr"/>
+      <c r="R88" s="37" t="inlineStr"/>
+      <c r="S88" s="37" t="inlineStr"/>
+    </row>
+    <row r="89" ht="100.5" customHeight="1">
+      <c r="A89" s="38" t="n"/>
+      <c r="B89" s="38" t="n"/>
+      <c r="C89" s="38" t="n"/>
+      <c r="D89" s="38" t="n"/>
+      <c r="E89" s="38" t="n"/>
+      <c r="F89" s="38" t="n"/>
+      <c r="G89" s="33" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H89" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>plannerd stops or runs late while engaged, so controlsd keeps using the last longitudinalPlan</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: SWF-068</t>
+          </r>
+        </is>
+      </c>
+      <c r="I89" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream openpilot code with upstream review; rated in the SW FMEA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/08-analyses/fmea/analyses/sw-fmea.yaml</t>
+          </r>
+        </is>
+      </c>
+      <c r="J89" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="K89" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• As rated in the SW FMEA (SWF-068.C1, D 9 at BL-005): no test targets an exception in the planner loop</t>
+          </r>
+        </is>
+      </c>
+      <c r="L89" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="M89" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N89" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-ACT-002 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Requirements-based tests for the host safety-relevant functions (selfdrived, controlsd, pandad, car interface, locationd bounds, monitoring policy), proven by mutation or fault injection and run as a CI gate (see SWF host actions)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O89" s="47" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P89" s="33" t="inlineStr"/>
+      <c r="Q89" s="33" t="inlineStr"/>
+      <c r="R89" s="37" t="inlineStr"/>
+      <c r="S89" s="37" t="inlineStr"/>
+    </row>
+    <row r="90" ht="100.5" customHeight="1">
+      <c r="A90" s="39" t="n"/>
+      <c r="B90" s="39" t="n"/>
+      <c r="C90" s="39" t="n"/>
+      <c r="D90" s="39" t="n"/>
+      <c r="E90" s="39" t="n"/>
+      <c r="F90" s="39" t="n"/>
+      <c r="G90" s="40" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="H90" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Messaging delivers a stale longitudinal plan or command with fresh timestamps</t>
+          </r>
+        </is>
+      </c>
+      <c r="I90" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• msgq/cereal stamp logMonoTime at publication; SubMaster tracks arrival time and frequency</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/cereal/messaging/__init__.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="J90" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="K90" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No pre-release test targets this cause</t>
+          </r>
+        </is>
+      </c>
+      <c r="L90" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="M90" s="44" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N90" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-ACT-002 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Requirements-based tests for the host safety-relevant functions (selfdrived, controlsd, pandad, car interface, locationd bounds, monitoring policy), proven by mutation or fault injection and run as a CI gate (see SWF host actions)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O90" s="48" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P90" s="40" t="inlineStr"/>
+      <c r="Q90" s="40" t="inlineStr"/>
+      <c r="R90" s="45" t="inlineStr"/>
+      <c r="S90" s="45" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:S87"/>
-  <mergeCells count="184">
+  <autoFilter ref="A2:S90"/>
+  <mergeCells count="190">
     <mergeCell ref="F84:F85"/>
     <mergeCell ref="F17:F19"/>
     <mergeCell ref="E39:E40"/>
@@ -17307,6 +17794,7 @@
     <mergeCell ref="F41:F43"/>
     <mergeCell ref="D10:D13"/>
     <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B88:B90"/>
     <mergeCell ref="F10:F13"/>
     <mergeCell ref="D49:D50"/>
     <mergeCell ref="E55:E56"/>
@@ -17326,6 +17814,7 @@
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="B84:B85"/>
     <mergeCell ref="C51:C52"/>
+    <mergeCell ref="A88:A90"/>
     <mergeCell ref="C60:C61"/>
     <mergeCell ref="C64:C66"/>
     <mergeCell ref="D25:D28"/>
@@ -17338,6 +17827,8 @@
     <mergeCell ref="C79:C81"/>
     <mergeCell ref="I1:M1"/>
     <mergeCell ref="E79:E81"/>
+    <mergeCell ref="C88:C90"/>
+    <mergeCell ref="E88:E90"/>
     <mergeCell ref="D39:D40"/>
     <mergeCell ref="A39:A40"/>
     <mergeCell ref="A3:A5"/>
@@ -17419,6 +17910,8 @@
     <mergeCell ref="B79:B81"/>
     <mergeCell ref="B32:B34"/>
     <mergeCell ref="D79:D81"/>
+    <mergeCell ref="D88:D90"/>
+    <mergeCell ref="F88:F90"/>
     <mergeCell ref="C67:C68"/>
     <mergeCell ref="E17:E19"/>
     <mergeCell ref="D71:D74"/>
@@ -17446,7 +17939,7 @@
     <mergeCell ref="D84:D85"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83 R84 R85 R86 R87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
+    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83 R84 R85 R86 R87 R88 R89 R90" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
       <formula1>"Agree,Re-rate,Reject,Question"</formula1>
     </dataValidation>
   </dataValidations>
@@ -17454,7 +17947,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.21 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.22 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -17573,7 +18066,7 @@
       <c r="H2" s="61" t="inlineStr"/>
       <c r="I2" s="61" t="inlineStr"/>
     </row>
-    <row r="3" ht="127.5" customHeight="1">
+    <row r="3" ht="168" customHeight="1">
       <c r="A3" s="61" t="inlineStr">
         <is>
           <t>SFM-ACT-002</t>
@@ -17609,7 +18102,10 @@
 SFM-008.C1
 SFM-023.C1
 SFM-023.C2
-SFM-030.C1</t>
+SFM-030.C1
+SFM-037.C1
+SFM-037.C2
+SFM-037.C3</t>
         </is>
       </c>
       <c r="G3" s="61" t="inlineStr"/>
@@ -18753,7 +19249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P70"/>
+  <dimension ref="A1:P73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -23112,13 +23608,208 @@
       <c r="O70" s="37" t="inlineStr"/>
       <c r="P70" s="37" t="inlineStr"/>
     </row>
+    <row r="71" ht="100.5" customHeight="1">
+      <c r="A71" s="34" t="inlineStr">
+        <is>
+          <t>SFM-037 · Longitudinal command frozen at last value</t>
+        </is>
+      </c>
+      <c r="B71" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C71" s="33" t="inlineStr">
+        <is>
+          <t>SFM-037.C1</t>
+        </is>
+      </c>
+      <c r="D71" s="34" t="inlineStr">
+        <is>
+          <t>controlsd hangs while card keeps sending the last carControl</t>
+        </is>
+      </c>
+      <c r="E71" s="34" t="inlineStr">
+        <is>
+          <t>card stops sending once carControl is 0.1 s old (T-13); the panda then revokes authority within 0.11 s of the last ACC_CONTROL frame (TSR-408, T-34) and selfdrived raises controlsMismatch within 0.5 s (TSR-621)</t>
+        </is>
+      </c>
+      <c r="F71" s="34" t="inlineStr">
+        <is>
+          <t>controlsMismatch IMMEDIATE_DISABLE with alert; no ACC_CONTROL frame follows the stall and there is no active zero request (TSR-109), so what the PCM does with the last request after the frames stop is not known (AOU, not measured)</t>
+        </is>
+      </c>
+      <c r="G71" s="34" t="inlineStr">
+        <is>
+          <t>Last request held about 0.2 s, then frames stop; the PCM reaction to missing ACC_CONTROL is not established</t>
+        </is>
+      </c>
+      <c r="H71" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I71" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J71" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="K71" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L71" s="34" t="inlineStr">
+        <is>
+          <t>SG-03/04 · 1000 ms</t>
+        </is>
+      </c>
+      <c r="M71" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N71" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-015 · in progress</t>
+        </is>
+      </c>
+      <c r="O71" s="37" t="inlineStr"/>
+      <c r="P71" s="37" t="inlineStr"/>
+    </row>
+    <row r="72" ht="46.5" customHeight="1">
+      <c r="A72" s="34" t="inlineStr">
+        <is>
+          <t>SFM-037 · Longitudinal command frozen at last value</t>
+        </is>
+      </c>
+      <c r="B72" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C72" s="33" t="inlineStr">
+        <is>
+          <t>SFM-037.C2</t>
+        </is>
+      </c>
+      <c r="D72" s="34" t="inlineStr">
+        <is>
+          <t>plannerd stops or runs late while engaged, so controlsd keeps using the last longitudinalPlan</t>
+        </is>
+      </c>
+      <c r="E72" s="34" t="inlineStr">
+        <is>
+          <t>selfdrived liveness check on longitudinalPlan (10 missed periods at 20 Hz, 0.5 s, T-14)</t>
+        </is>
+      </c>
+      <c r="F72" s="34" t="inlineStr">
+        <is>
+          <t>commIssue SOFT_DISABLE; actuation continues for the 3 s countdown (T-16) on the last plan</t>
+        </is>
+      </c>
+      <c r="G72" s="34" t="inlineStr">
+        <is>
+          <t>Frozen request held up to about 3.5 s before the item disengages</t>
+        </is>
+      </c>
+      <c r="H72" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I72" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="J72" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="K72" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L72" s="34" t="inlineStr">
+        <is>
+          <t>SG-03/04 · 1000 ms
+500 + 3000 ms</t>
+        </is>
+      </c>
+      <c r="M72" s="33" t="inlineStr">
+        <is>
+          <t>code derived</t>
+        </is>
+      </c>
+      <c r="N72" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-015 · in progress</t>
+        </is>
+      </c>
+      <c r="O72" s="37" t="inlineStr"/>
+      <c r="P72" s="37" t="inlineStr"/>
+    </row>
+    <row r="73" ht="46.5" customHeight="1">
+      <c r="A73" s="34" t="inlineStr">
+        <is>
+          <t>SFM-037 · Longitudinal command frozen at last value</t>
+        </is>
+      </c>
+      <c r="B73" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C73" s="33" t="inlineStr">
+        <is>
+          <t>SFM-037.C3</t>
+        </is>
+      </c>
+      <c r="D73" s="34" t="inlineStr">
+        <is>
+          <t>Messaging delivers a stale longitudinal plan or command with fresh timestamps</t>
+        </is>
+      </c>
+      <c r="E73" s="34" t="inlineStr">
+        <is>
+          <t>Liveness checks use arrival and timestamps, so stale data with fresh timestamps passes them</t>
+        </is>
+      </c>
+      <c r="F73" s="34" t="inlineStr">
+        <is>
+          <t>None until another check trips</t>
+        </is>
+      </c>
+      <c r="G73" s="34" t="inlineStr">
+        <is>
+          <t>Unchanged: longitudinal control acts on stale data</t>
+        </is>
+      </c>
+      <c r="H73" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I73" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="J73" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="K73" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L73" s="34" t="inlineStr"/>
+      <c r="M73" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N73" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-015 · in progress</t>
+        </is>
+      </c>
+      <c r="O73" s="37" t="inlineStr"/>
+      <c r="P73" s="37" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:P70"/>
+  <autoFilter ref="A2:P73"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="O3 O4 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 O34 O35 O36 O37 O38 O39 O40 O41 O42 O43 O44 O45 O46 O47 O48 O49 O50 O51 O52 O53 O54 O55 O56 O57 O58 O59 O60 O61 O62 O63 O64 O65 O66 O67 O68 O69 O70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this MSR row" type="list">
+    <dataValidation sqref="O3 O4 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 O34 O35 O36 O37 O38 O39 O40 O41 O42 O43 O44 O45 O46 O47 O48 O49 O50 O51 O52 O53 O54 O55 O56 O57 O58 O59 O60 O61 O62 O63 O64 O65 O66 O67 O68 O69 O70 O71 O72 O73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this MSR row" type="list">
       <formula1>"Agree,Re-rate,Reject,Question"</formula1>
     </dataValidation>
   </dataValidations>
@@ -23126,7 +23817,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.21 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.22 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MSR" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$93</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Worksheet'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Structure'!$A$1:$E$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'MSR'!$A$2:$P$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'MSR'!$A$2:$P$76</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'MSR'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -823,7 +823,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.22 · draft</t>
+          <t>0.23 · draft</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -952,7 +952,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>21 (19)</t>
+          <t>22 (20)</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>67 rated, 4 exempt; MSR AP H 67, M 0, L 0 (provisional table)</t>
+          <t>67 rated, 7 exempt; MSR AP H 67, M 0, L 0 (provisional table)</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S90"/>
+  <dimension ref="A1:S93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17744,9 +17744,460 @@
       <c r="R90" s="45" t="inlineStr"/>
       <c r="S90" s="45" t="inlineStr"/>
     </row>
+    <row r="91" ht="114" customHeight="1">
+      <c r="A91" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-SE-001
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>LionDriver item (L2 ACC + ALC + driver monitoring)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B91" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-FN-006
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>F6 Alerting: inform the driver of engagement state, takeover requests and faults (visual and audible)</t>
+          </r>
+        </is>
+      </c>
+      <c r="C91" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Driver unaware of the loss or limit; lane departure</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Driver not prompted to take over while lateral control is lost or limited</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>steerTempUnavailable shown silently, steerSaturated raised late or not at all, or the panda's EPS-fault flag not acted on</t>
+          </r>
+        </is>
+      </c>
+      <c r="D91" s="31" t="inlineStr">
+        <is>
+          <t>HZ-004</t>
+        </is>
+      </c>
+      <c r="E91" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F91" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-038 · late
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Warning of a lateral-control fault or limit late, silent or missing</t>
+          </r>
+        </is>
+      </c>
+      <c r="G91" s="33" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H91" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>After any driver steering input in the last 1.5 s, a temporary EPS fault raises only steerTempUnavailableSilent (a small WARNING with no soft disable), and the warning stays silent for as long as the fault lasts (car_events.py:162-177; T-25, GAP-03)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I91" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream openpilot design choice (a softer alert after an override); no LionDriver requirement on it</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/car/car_events.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="J91" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="K91" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No LionDriver test targets this cause</t>
+          </r>
+        </is>
+      </c>
+      <c r="L91" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="M91" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N91" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-ACT-023 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Warn audibly and with a take-over request on every EPS fault while engaged, with no silent variant after a recent override (car_events.py steerTempUnavailableSilent), and act on the panda fields epsFault and requestsRejected on the host (TSR-626(d), TSR-516(b)). SFM-038.C1, C2; FTA BE-2.08</t>
+          </r>
+        </is>
+      </c>
+      <c r="O91" s="47" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P91" s="33" t="inlineStr"/>
+      <c r="Q91" s="33" t="inlineStr"/>
+      <c r="R91" s="37" t="inlineStr"/>
+      <c r="S91" s="37" t="inlineStr"/>
+    </row>
+    <row r="92" ht="114" customHeight="1">
+      <c r="A92" s="38" t="n"/>
+      <c r="B92" s="38" t="n"/>
+      <c r="C92" s="38" t="n"/>
+      <c r="D92" s="38" t="n"/>
+      <c r="E92" s="38" t="n"/>
+      <c r="F92" s="38" t="n"/>
+      <c r="G92" s="33" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H92" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>pandad publishes the panda fields epsFault and requestsRejected (pandad.cc:137-138), but no SoC process reads them (txRateExceeded is read, TSR-615), so a panda-side EPS-fault refusal reaches the driver only through the panda siren and the stock EPS path (SW FMEA SWF-025 notes)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I92" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• None; the fields were added for the panda siren and logging</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/pandad/pandad.cc</t>
+          </r>
+        </is>
+      </c>
+      <c r="J92" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="K92" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No test targets this cause</t>
+          </r>
+        </is>
+      </c>
+      <c r="L92" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="M92" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N92" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-ACT-023 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Warn audibly and with a take-over request on every EPS fault while engaged, with no silent variant after a recent override (car_events.py steerTempUnavailableSilent), and act on the panda fields epsFault and requestsRejected on the host (TSR-626(d), TSR-516(b)). SFM-038.C1, C2; FTA BE-2.08</t>
+          </r>
+        </is>
+      </c>
+      <c r="O92" s="47" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P92" s="33" t="inlineStr"/>
+      <c r="Q92" s="33" t="inlineStr"/>
+      <c r="R92" s="37" t="inlineStr"/>
+      <c r="S92" s="37" t="inlineStr"/>
+    </row>
+    <row r="93" ht="127.5" customHeight="1">
+      <c r="A93" s="39" t="n"/>
+      <c r="B93" s="39" t="n"/>
+      <c r="C93" s="39" t="n"/>
+      <c r="D93" s="39" t="n"/>
+      <c r="E93" s="39" t="n"/>
+      <c r="F93" s="39" t="n"/>
+      <c r="G93" s="40" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="H93" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>steerSaturated needs the controller saturated, a desired lateral acceleration above 1.0 m/s², an undershoot above 1.2x and no steering input for 2 s (selfdrived.py:465-479), and the controller reports saturation only after 0.4 s (latcontrol.py, T-30); a gradual deficit therefore warns late or not at all (WP-S-04 §3.8.1)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I93" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream openpilot code with upstream review; ruff and type checks in CI (static analysis job)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   scripts/lint/lint.sh</t>
+          </r>
+        </is>
+      </c>
+      <c r="J93" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="K93" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Lateral controller unit tests (saturation detection); targeted at nominal behaviour, not proven</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/controls/tests/test_latcontrol.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L93" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="M93" s="44" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N93" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-ACT-021 · monitoring
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Make the insufficient-lateral-control warning timely (WP-S-04 §3.8.1): warn before the deficit has lasted 0.4 s, for example from the planned curvature against the envelope, or keep the deficit at or below about 0.5 m/s² through the steering limits and the ODD curve bound (WP-S-04 OI-2). A change to the ODD bound is a lead decision</t>
+          </r>
+        </is>
+      </c>
+      <c r="O93" s="48" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P93" s="40" t="inlineStr"/>
+      <c r="Q93" s="40" t="inlineStr"/>
+      <c r="R93" s="45" t="inlineStr"/>
+      <c r="S93" s="45" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:S90"/>
-  <mergeCells count="190">
+  <autoFilter ref="A2:S93"/>
+  <mergeCells count="196">
     <mergeCell ref="F84:F85"/>
     <mergeCell ref="F17:F19"/>
     <mergeCell ref="E39:E40"/>
@@ -17865,6 +18316,7 @@
     <mergeCell ref="B10:B13"/>
     <mergeCell ref="C23:C24"/>
     <mergeCell ref="B49:B50"/>
+    <mergeCell ref="B91:B93"/>
     <mergeCell ref="C20:C22"/>
     <mergeCell ref="C14:C16"/>
     <mergeCell ref="E20:E22"/>
@@ -17877,7 +18329,9 @@
     <mergeCell ref="F49:F50"/>
     <mergeCell ref="B17:B19"/>
     <mergeCell ref="B75:B76"/>
+    <mergeCell ref="D91:D93"/>
     <mergeCell ref="F20:F22"/>
+    <mergeCell ref="F91:F93"/>
     <mergeCell ref="B44:B46"/>
     <mergeCell ref="A67:A68"/>
     <mergeCell ref="E71:E74"/>
@@ -17887,7 +18341,9 @@
     <mergeCell ref="E57:E59"/>
     <mergeCell ref="A69:A70"/>
     <mergeCell ref="D6:D9"/>
+    <mergeCell ref="A91:A93"/>
     <mergeCell ref="F6:F9"/>
+    <mergeCell ref="C91:C93"/>
     <mergeCell ref="D64:D66"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="E41:E43"/>
@@ -17901,6 +18357,7 @@
     <mergeCell ref="E35:E36"/>
     <mergeCell ref="A75:A76"/>
     <mergeCell ref="C75:C76"/>
+    <mergeCell ref="E91:E93"/>
     <mergeCell ref="F57:F59"/>
     <mergeCell ref="B64:B66"/>
     <mergeCell ref="C25:C28"/>
@@ -17939,7 +18396,7 @@
     <mergeCell ref="D84:D85"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83 R84 R85 R86 R87 R88 R89 R90" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
+    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83 R84 R85 R86 R87 R88 R89 R90 R91 R92 R93" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
       <formula1>"Agree,Re-rate,Reject,Question"</formula1>
     </dataValidation>
   </dataValidations>
@@ -17947,7 +18404,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.22 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.23 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -17962,7 +18419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18732,7 +19189,11 @@
           <t>open</t>
         </is>
       </c>
-      <c r="F21" s="61" t="inlineStr"/>
+      <c r="F21" s="61" t="inlineStr">
+        <is>
+          <t>SFM-038.C3</t>
+        </is>
+      </c>
       <c r="G21" s="61" t="inlineStr"/>
       <c r="H21" s="61" t="inlineStr"/>
       <c r="I21" s="61" t="inlineStr"/>
@@ -18764,8 +19225,40 @@
       <c r="H22" s="61" t="inlineStr"/>
       <c r="I22" s="61" t="inlineStr"/>
     </row>
+    <row r="23" ht="73.5" customHeight="1">
+      <c r="A23" s="61" t="inlineStr">
+        <is>
+          <t>SFM-ACT-023</t>
+        </is>
+      </c>
+      <c r="B23" s="61" t="inlineStr">
+        <is>
+          <t>design change</t>
+        </is>
+      </c>
+      <c r="C23" s="61" t="inlineStr">
+        <is>
+          <t>Warn audibly and with a take-over request on every EPS fault while engaged, with no silent variant after a recent override (car_events.py steerTempUnavailableSilent), and act on the panda fields epsFault and requestsRejected on the host (TSR-626(d), TSR-516(b)). SFM-038.C1, C2; FTA BE-2.08</t>
+        </is>
+      </c>
+      <c r="D23" s="61" t="inlineStr"/>
+      <c r="E23" s="61" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F23" s="61" t="inlineStr">
+        <is>
+          <t>SFM-038.C1
+SFM-038.C2</t>
+        </is>
+      </c>
+      <c r="G23" s="61" t="inlineStr"/>
+      <c r="H23" s="61" t="inlineStr"/>
+      <c r="I23" s="61" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I22"/>
+  <autoFilter ref="A1:I23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19249,7 +19742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P73"/>
+  <dimension ref="A1:P76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -23803,13 +24296,121 @@
       <c r="O73" s="37" t="inlineStr"/>
       <c r="P73" s="37" t="inlineStr"/>
     </row>
+    <row r="74" ht="100.5" customHeight="1">
+      <c r="A74" s="34" t="inlineStr">
+        <is>
+          <t>SFM-038 · Warning of a lateral-control fault or limit late, silent or missing</t>
+        </is>
+      </c>
+      <c r="B74" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C74" s="33" t="inlineStr">
+        <is>
+          <t>SFM-038.C1</t>
+        </is>
+      </c>
+      <c r="D74" s="34" t="inlineStr">
+        <is>
+          <t>After any driver steering input in the last 1.5 s, a temporary EPS fault raises only steerTempUnavailableSilent (a small WARNING with no soft disable), and the warning stays silent for as long as the fault lasts (car_events.py:162-177; T-25, GAP-03)</t>
+        </is>
+      </c>
+      <c r="E74" s="64" t="inlineStr">
+        <is>
+          <t>Exempt: The cause is a defect of the warning path itself; its effect on detecting the lateral loss is rated in the MSR rows of SFM-004.C2 and SFM-005 (msr-plan §3)</t>
+        </is>
+      </c>
+      <c r="F74" s="34" t="inlineStr"/>
+      <c r="G74" s="34" t="inlineStr"/>
+      <c r="H74" s="35" t="inlineStr"/>
+      <c r="I74" s="35" t="inlineStr"/>
+      <c r="J74" s="35" t="inlineStr"/>
+      <c r="K74" s="33" t="inlineStr"/>
+      <c r="L74" s="34" t="inlineStr"/>
+      <c r="M74" s="33" t="inlineStr"/>
+      <c r="N74" s="34" t="inlineStr"/>
+      <c r="O74" s="37" t="inlineStr"/>
+      <c r="P74" s="37" t="inlineStr"/>
+    </row>
+    <row r="75" ht="114" customHeight="1">
+      <c r="A75" s="34" t="inlineStr">
+        <is>
+          <t>SFM-038 · Warning of a lateral-control fault or limit late, silent or missing</t>
+        </is>
+      </c>
+      <c r="B75" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C75" s="33" t="inlineStr">
+        <is>
+          <t>SFM-038.C2</t>
+        </is>
+      </c>
+      <c r="D75" s="34" t="inlineStr">
+        <is>
+          <t>pandad publishes the panda fields epsFault and requestsRejected (pandad.cc:137-138), but no SoC process reads them (txRateExceeded is read, TSR-615), so a panda-side EPS-fault refusal reaches the driver only through the panda siren and the stock EPS path (SW FMEA SWF-025 notes)</t>
+        </is>
+      </c>
+      <c r="E75" s="64" t="inlineStr">
+        <is>
+          <t>Exempt: The cause is a defect of the warning path itself; the panda siren that remains is rated on SFM-005 and in the DFMEA (msr-plan §3)</t>
+        </is>
+      </c>
+      <c r="F75" s="34" t="inlineStr"/>
+      <c r="G75" s="34" t="inlineStr"/>
+      <c r="H75" s="35" t="inlineStr"/>
+      <c r="I75" s="35" t="inlineStr"/>
+      <c r="J75" s="35" t="inlineStr"/>
+      <c r="K75" s="33" t="inlineStr"/>
+      <c r="L75" s="34" t="inlineStr"/>
+      <c r="M75" s="33" t="inlineStr"/>
+      <c r="N75" s="34" t="inlineStr"/>
+      <c r="O75" s="37" t="inlineStr"/>
+      <c r="P75" s="37" t="inlineStr"/>
+    </row>
+    <row r="76" ht="127.5" customHeight="1">
+      <c r="A76" s="34" t="inlineStr">
+        <is>
+          <t>SFM-038 · Warning of a lateral-control fault or limit late, silent or missing</t>
+        </is>
+      </c>
+      <c r="B76" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C76" s="33" t="inlineStr">
+        <is>
+          <t>SFM-038.C3</t>
+        </is>
+      </c>
+      <c r="D76" s="34" t="inlineStr">
+        <is>
+          <t>steerSaturated needs the controller saturated, a desired lateral acceleration above 1.0 m/s², an undershoot above 1.2x and no steering input for 2 s (selfdrived.py:465-479), and the controller reports saturation only after 0.4 s (latcontrol.py, T-30); a gradual deficit therefore warns late or not at all (WP-S-04 §3.8.1)</t>
+        </is>
+      </c>
+      <c r="E76" s="64" t="inlineStr">
+        <is>
+          <t>Exempt: The cause is the timing of the warning itself; it is rated as M 8 in the MSR rows of SFM-004.C1-C3 (rev 0.15, WP-S-04 §3.8.1)</t>
+        </is>
+      </c>
+      <c r="F76" s="34" t="inlineStr"/>
+      <c r="G76" s="34" t="inlineStr"/>
+      <c r="H76" s="35" t="inlineStr"/>
+      <c r="I76" s="35" t="inlineStr"/>
+      <c r="J76" s="35" t="inlineStr"/>
+      <c r="K76" s="33" t="inlineStr"/>
+      <c r="L76" s="34" t="inlineStr"/>
+      <c r="M76" s="33" t="inlineStr"/>
+      <c r="N76" s="34" t="inlineStr"/>
+      <c r="O76" s="37" t="inlineStr"/>
+      <c r="P76" s="37" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:P73"/>
+  <autoFilter ref="A2:P76"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="O3 O4 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 O34 O35 O36 O37 O38 O39 O40 O41 O42 O43 O44 O45 O46 O47 O48 O49 O50 O51 O52 O53 O54 O55 O56 O57 O58 O59 O60 O61 O62 O63 O64 O65 O66 O67 O68 O69 O70 O71 O72 O73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this MSR row" type="list">
+    <dataValidation sqref="O3 O4 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 O34 O35 O36 O37 O38 O39 O40 O41 O42 O43 O44 O45 O46 O47 O48 O49 O50 O51 O52 O53 O54 O55 O56 O57 O58 O59 O60 O61 O62 O63 O64 O65 O66 O67 O68 O69 O70 O71 O72 O73 O74 O75 O76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this MSR row" type="list">
       <formula1>"Agree,Re-rate,Reject,Question"</formula1>
     </dataValidation>
   </dataValidations>
@@ -23817,7 +24418,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.22 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.23 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -17744,7 +17744,7 @@
       <c r="R90" s="45" t="inlineStr"/>
       <c r="S90" s="45" t="inlineStr"/>
     </row>
-    <row r="91" ht="114" customHeight="1">
+    <row r="91" ht="168" customHeight="1">
       <c r="A91" s="30" t="inlineStr">
         <is>
           <r>
@@ -17858,7 +17858,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>steerTempUnavailable shown silently, steerSaturated raised late or not at all, or the panda's EPS-fault flag not acted on</t>
+            <t>steerTempUnavailable not escalated to a take-over request, steerSaturated raised late or not at all, or the panda's EPS-fault flag not acted on</t>
           </r>
         </is>
       </c>
@@ -17889,7 +17889,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Warning of a lateral-control fault or limit late, silent or missing</t>
+            <t>Warning of a lateral-control fault or limit late, not escalated or missing</t>
           </r>
         </is>
       </c>
@@ -17906,7 +17906,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>After any driver steering input in the last 1.5 s, a temporary EPS fault raises only steerTempUnavailableSilent (a small WARNING with no soft disable), and the warning stays silent for as long as the fault lasts (car_events.py:162-177; T-25, GAP-03)</t>
+            <t>After any driver steering input in the last 1.5 s, or at standstill, a temporary EPS fault raises only steerTempUnavailableSilent (a LOW-priority WARNING with a prompt chime and no soft disable, events.py:516-521), and it stays latched while the fault lasts, so a long fault never escalates to the take-over request (car_events.py:162-177; T-25, GAP-03)</t>
           </r>
         </is>
       </c>
@@ -17972,7 +17972,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Warn audibly and with a take-over request on every EPS fault while engaged, with no silent variant after a recent override (car_events.py steerTempUnavailableSilent), and act on the panda fields epsFault and requestsRejected on the host (TSR-626(d), TSR-516(b)). SFM-038.C1, C2; FTA BE-2.08</t>
+            <t>Escalate every EPS fault that lasts while engaged to the take-over request (steerTempUnavailable, SOFT_DISABLE), instead of keeping the low-priority steerTempUnavailableSilent prompt latched after a recent override or at standstill (car_events.py:162-177; behaviour change queued for the lead by the FSC session as DQ-342), and act on the panda fields epsFault and requestsRejected on the host (TSR-626(d), TSR-516(b)). SFM-038.C1, C2; FTA BE-2.08</t>
           </r>
         </is>
       </c>
@@ -17986,7 +17986,7 @@
       <c r="R91" s="37" t="inlineStr"/>
       <c r="S91" s="37" t="inlineStr"/>
     </row>
-    <row r="92" ht="114" customHeight="1">
+    <row r="92" ht="168" customHeight="1">
       <c r="A92" s="38" t="n"/>
       <c r="B92" s="38" t="n"/>
       <c r="C92" s="38" t="n"/>
@@ -18072,7 +18072,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Warn audibly and with a take-over request on every EPS fault while engaged, with no silent variant after a recent override (car_events.py steerTempUnavailableSilent), and act on the panda fields epsFault and requestsRejected on the host (TSR-626(d), TSR-516(b)). SFM-038.C1, C2; FTA BE-2.08</t>
+            <t>Escalate every EPS fault that lasts while engaged to the take-over request (steerTempUnavailable, SOFT_DISABLE), instead of keeping the low-priority steerTempUnavailableSilent prompt latched after a recent override or at standstill (car_events.py:162-177; behaviour change queued for the lead by the FSC session as DQ-342), and act on the panda fields epsFault and requestsRejected on the host (TSR-626(d), TSR-516(b)). SFM-038.C1, C2; FTA BE-2.08</t>
           </r>
         </is>
       </c>
@@ -19225,7 +19225,7 @@
       <c r="H22" s="61" t="inlineStr"/>
       <c r="I22" s="61" t="inlineStr"/>
     </row>
-    <row r="23" ht="73.5" customHeight="1">
+    <row r="23" ht="100.5" customHeight="1">
       <c r="A23" s="61" t="inlineStr">
         <is>
           <t>SFM-ACT-023</t>
@@ -19238,7 +19238,7 @@
       </c>
       <c r="C23" s="61" t="inlineStr">
         <is>
-          <t>Warn audibly and with a take-over request on every EPS fault while engaged, with no silent variant after a recent override (car_events.py steerTempUnavailableSilent), and act on the panda fields epsFault and requestsRejected on the host (TSR-626(d), TSR-516(b)). SFM-038.C1, C2; FTA BE-2.08</t>
+          <t>Escalate every EPS fault that lasts while engaged to the take-over request (steerTempUnavailable, SOFT_DISABLE), instead of keeping the low-priority steerTempUnavailableSilent prompt latched after a recent override or at standstill (car_events.py:162-177; behaviour change queued for the lead by the FSC session as DQ-342), and act on the panda fields epsFault and requestsRejected on the host (TSR-626(d), TSR-516(b)). SFM-038.C1, C2; FTA BE-2.08</t>
         </is>
       </c>
       <c r="D23" s="61" t="inlineStr"/>
@@ -24296,10 +24296,10 @@
       <c r="O73" s="37" t="inlineStr"/>
       <c r="P73" s="37" t="inlineStr"/>
     </row>
-    <row r="74" ht="100.5" customHeight="1">
+    <row r="74" ht="141" customHeight="1">
       <c r="A74" s="34" t="inlineStr">
         <is>
-          <t>SFM-038 · Warning of a lateral-control fault or limit late, silent or missing</t>
+          <t>SFM-038 · Warning of a lateral-control fault or limit late, not escalated or missing</t>
         </is>
       </c>
       <c r="B74" s="35" t="n">
@@ -24312,7 +24312,7 @@
       </c>
       <c r="D74" s="34" t="inlineStr">
         <is>
-          <t>After any driver steering input in the last 1.5 s, a temporary EPS fault raises only steerTempUnavailableSilent (a small WARNING with no soft disable), and the warning stays silent for as long as the fault lasts (car_events.py:162-177; T-25, GAP-03)</t>
+          <t>After any driver steering input in the last 1.5 s, or at standstill, a temporary EPS fault raises only steerTempUnavailableSilent (a LOW-priority WARNING with a prompt chime and no soft disable, events.py:516-521), and it stays latched while the fault lasts, so a long fault never escalates to the take-over request (car_events.py:162-177; T-25, GAP-03)</t>
         </is>
       </c>
       <c r="E74" s="64" t="inlineStr">
@@ -24335,7 +24335,7 @@
     <row r="75" ht="114" customHeight="1">
       <c r="A75" s="34" t="inlineStr">
         <is>
-          <t>SFM-038 · Warning of a lateral-control fault or limit late, silent or missing</t>
+          <t>SFM-038 · Warning of a lateral-control fault or limit late, not escalated or missing</t>
         </is>
       </c>
       <c r="B75" s="35" t="n">
@@ -24371,7 +24371,7 @@
     <row r="76" ht="127.5" customHeight="1">
       <c r="A76" s="34" t="inlineStr">
         <is>
-          <t>SFM-038 · Warning of a lateral-control fault or limit late, silent or missing</t>
+          <t>SFM-038 · Warning of a lateral-control fault or limit late, not escalated or missing</t>
         </is>
       </c>
       <c r="B76" s="35" t="n">

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -261,7 +261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -396,9 +396,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -823,7 +820,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.23 · draft</t>
+          <t>0.24 · draft</t>
         </is>
       </c>
     </row>
@@ -12333,7 +12330,7 @@
       <c r="R62" s="45" t="inlineStr"/>
       <c r="S62" s="45" t="inlineStr"/>
     </row>
-    <row r="63" ht="195" customHeight="1">
+    <row r="63" ht="249" customHeight="1">
       <c r="A63" s="51" t="inlineStr">
         <is>
           <r>
@@ -12605,13 +12602,13 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Decide in the FSC how the item reacts when driver awareness reaches zero (driverUnresponsive3 / driverDistracted3 have no disable reaction at BL-004 or BL-005) and implement the decision. DQ-205 (answered) makes this the safe state of SG-010 (WP-C-03 SG-08, ASIL A); the reaction itself is still to be decided. The requirement is TSR-633 (terminal reaction, ASIL A proposed) with TSR-611 (WP-S-02 §12.3a); the reaction is lead decision DQ-340. The H-09 FTTI is not yet set, so the timing rows of WP-S-04 §3.8.4 cannot be compared</t>
-          </r>
-        </is>
-      </c>
-      <c r="O63" s="57" t="inlineStr">
-        <is>
-          <t>decision pending</t>
+            <t>Implement the reaction when driver awareness reaches zero (driverUnresponsive3 / driverDistracted3 have no disable reaction at BL-004 or BL-005), the safe state of SG-010 (WP-C-03 SG-08, ASIL A; DQ-205). Decided by the lead (DQ-365, option A, 2026-10-16) and specified in TSR-633 (WP-S-02 v0.26) with TSR-611; keep the lane and decelerate in lane to a standstill with the terminal alert sounding, hold the vehicle stopped, and lock out re-engagement and resumption until the driver responds. WP-S-04 v0.12 §3.8.4 gives a preliminary time to the reaction (18 s vision, 30 s wheel-touch from loss of attention; OI-11); SFM-025.C1 is re-rated once TSR-633 is implemented and that time is confirmed</t>
+          </r>
+        </is>
+      </c>
+      <c r="O63" s="48" t="inlineStr">
+        <is>
+          <t>open</t>
         </is>
       </c>
       <c r="P63" s="40" t="inlineStr"/>
@@ -14215,7 +14212,7 @@
       <c r="L71" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="M71" s="58" t="inlineStr">
+      <c r="M71" s="57" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -17156,7 +17153,7 @@
           </r>
         </is>
       </c>
-      <c r="O86" s="59" t="inlineStr">
+      <c r="O86" s="58" t="inlineStr">
         <is>
           <t>decision pending</t>
         </is>
@@ -18404,7 +18401,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.23 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.24 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -18434,79 +18431,79 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="60" t="inlineStr">
+      <c r="A1" s="59" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B1" s="60" t="inlineStr">
+      <c r="B1" s="59" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="C1" s="60" t="inlineStr">
+      <c r="C1" s="59" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" s="60" t="inlineStr">
+      <c r="D1" s="59" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E1" s="60" t="inlineStr">
+      <c r="E1" s="59" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="60" t="inlineStr">
+      <c r="F1" s="59" t="inlineStr">
         <is>
           <t>Causes</t>
         </is>
       </c>
-      <c r="G1" s="60" t="inlineStr">
+      <c r="G1" s="59" t="inlineStr">
         <is>
           <t>Revised S/O/D</t>
         </is>
       </c>
-      <c r="H1" s="60" t="inlineStr">
+      <c r="H1" s="59" t="inlineStr">
         <is>
           <t>Revised AP</t>
         </is>
       </c>
-      <c r="I1" s="60" t="inlineStr">
+      <c r="I1" s="59" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
     </row>
     <row r="2" ht="127.5" customHeight="1">
-      <c r="A2" s="61" t="inlineStr">
+      <c r="A2" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-001</t>
         </is>
       </c>
-      <c r="B2" s="61" t="inlineStr">
+      <c r="B2" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C2" s="61" t="inlineStr">
+      <c r="C2" s="60" t="inlineStr">
         <is>
           <t>Derive steering and acceleration envelopes from measurements on the reference vehicle and set the panda limits from them, independently of the SoC limits (same as SWF-ACT-003, FSC FOI-001)</t>
         </is>
       </c>
-      <c r="D2" s="61" t="inlineStr">
+      <c r="D2" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E2" s="61" t="inlineStr">
+      <c r="E2" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F2" s="61" t="inlineStr">
+      <c r="F2" s="60" t="inlineStr">
         <is>
           <t>SFM-002.C1
 SFM-002.C2
@@ -18519,37 +18516,37 @@
 SFM-029.C2</t>
         </is>
       </c>
-      <c r="G2" s="61" t="inlineStr"/>
-      <c r="H2" s="61" t="inlineStr"/>
-      <c r="I2" s="61" t="inlineStr"/>
+      <c r="G2" s="60" t="inlineStr"/>
+      <c r="H2" s="60" t="inlineStr"/>
+      <c r="I2" s="60" t="inlineStr"/>
     </row>
     <row r="3" ht="168" customHeight="1">
-      <c r="A3" s="61" t="inlineStr">
+      <c r="A3" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-002</t>
         </is>
       </c>
-      <c r="B3" s="61" t="inlineStr">
+      <c r="B3" s="60" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C3" s="61" t="inlineStr">
+      <c r="C3" s="60" t="inlineStr">
         <is>
           <t>Requirements-based tests for the host safety-relevant functions (selfdrived, controlsd, pandad, car interface, locationd bounds, monitoring policy), proven by mutation or fault injection and run as a CI gate (see SWF host actions)</t>
         </is>
       </c>
-      <c r="D3" s="61" t="inlineStr">
+      <c r="D3" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E3" s="61" t="inlineStr">
+      <c r="E3" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F3" s="61" t="inlineStr">
+      <c r="F3" s="60" t="inlineStr">
         <is>
           <t>SFM-002.C4
 SFM-004.C3
@@ -18565,37 +18562,37 @@
 SFM-037.C3</t>
         </is>
       </c>
-      <c r="G3" s="61" t="inlineStr"/>
-      <c r="H3" s="61" t="inlineStr"/>
-      <c r="I3" s="61" t="inlineStr"/>
+      <c r="G3" s="60" t="inlineStr"/>
+      <c r="H3" s="60" t="inlineStr"/>
+      <c r="I3" s="60" t="inlineStr"/>
     </row>
     <row r="4" ht="343.5" customHeight="1">
-      <c r="A4" s="61" t="inlineStr">
+      <c r="A4" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-003</t>
         </is>
       </c>
-      <c r="B4" s="61" t="inlineStr">
+      <c r="B4" s="60" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C4" s="61" t="inlineStr">
+      <c r="C4" s="60" t="inlineStr">
         <is>
           <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
         </is>
       </c>
-      <c r="D4" s="61" t="inlineStr">
+      <c r="D4" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E4" s="61" t="inlineStr">
+      <c r="E4" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F4" s="61" t="inlineStr">
+      <c r="F4" s="60" t="inlineStr">
         <is>
           <t>SFM-003.C1
 SFM-003.C2
@@ -18624,72 +18621,72 @@
 SFM-033.C3</t>
         </is>
       </c>
-      <c r="G4" s="61" t="inlineStr"/>
-      <c r="H4" s="61" t="inlineStr"/>
-      <c r="I4" s="61" t="inlineStr"/>
+      <c r="G4" s="60" t="inlineStr"/>
+      <c r="H4" s="60" t="inlineStr"/>
+      <c r="I4" s="60" t="inlineStr"/>
     </row>
-    <row r="5" ht="114" customHeight="1">
-      <c r="A5" s="61" t="inlineStr">
+    <row r="5" ht="154.5" customHeight="1">
+      <c r="A5" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-005</t>
         </is>
       </c>
-      <c r="B5" s="61" t="inlineStr">
+      <c r="B5" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C5" s="61" t="inlineStr">
-        <is>
-          <t>Decide in the FSC how the item reacts when driver awareness reaches zero (driverUnresponsive3 / driverDistracted3 have no disable reaction at BL-004 or BL-005) and implement the decision. DQ-205 (answered) makes this the safe state of SG-010 (WP-C-03 SG-08, ASIL A); the reaction itself is still to be decided. The requirement is TSR-633 (terminal reaction, ASIL A proposed) with TSR-611 (WP-S-02 §12.3a); the reaction is lead decision DQ-340. The H-09 FTTI is not yet set, so the timing rows of WP-S-04 §3.8.4 cannot be compared</t>
-        </is>
-      </c>
-      <c r="D5" s="61" t="inlineStr">
+      <c r="C5" s="60" t="inlineStr">
+        <is>
+          <t>Implement the reaction when driver awareness reaches zero (driverUnresponsive3 / driverDistracted3 have no disable reaction at BL-004 or BL-005), the safe state of SG-010 (WP-C-03 SG-08, ASIL A; DQ-205). Decided by the lead (DQ-365, option A, 2026-10-16) and specified in TSR-633 (WP-S-02 v0.26) with TSR-611; keep the lane and decelerate in lane to a standstill with the terminal alert sounding, hold the vehicle stopped, and lock out re-engagement and resumption until the driver responds. WP-S-04 v0.12 §3.8.4 gives a preliminary time to the reaction (18 s vision, 30 s wheel-touch from loss of attention; OI-11); SFM-025.C1 is re-rated once TSR-633 is implemented and that time is confirmed</t>
+        </is>
+      </c>
+      <c r="D5" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E5" s="61" t="inlineStr">
-        <is>
-          <t>decision pending</t>
-        </is>
-      </c>
-      <c r="F5" s="61" t="inlineStr">
+      <c r="E5" s="60" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F5" s="60" t="inlineStr">
         <is>
           <t>SFM-025.C1</t>
         </is>
       </c>
-      <c r="G5" s="61" t="inlineStr"/>
-      <c r="H5" s="61" t="inlineStr"/>
-      <c r="I5" s="61" t="inlineStr"/>
+      <c r="G5" s="60" t="inlineStr"/>
+      <c r="H5" s="60" t="inlineStr"/>
+      <c r="I5" s="60" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="61" t="inlineStr">
+      <c r="A6" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-006</t>
         </is>
       </c>
-      <c r="B6" s="61" t="inlineStr">
+      <c r="B6" s="60" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C6" s="61" t="inlineStr">
+      <c r="C6" s="60" t="inlineStr">
         <is>
           <t>Establish on the reference car which stock TSS2 functions (PCS/AEB, FCW) remain available with LionDriver installed and longitudinal control enabled, and verify the stock pre-collision path after installation (PFMEA PFM-014)</t>
         </is>
       </c>
-      <c r="D6" s="61" t="inlineStr">
+      <c r="D6" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E6" s="61" t="inlineStr">
+      <c r="E6" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F6" s="61" t="inlineStr">
+      <c r="F6" s="60" t="inlineStr">
         <is>
           <t>SFM-010.C2
 SFM-033.C1
@@ -18697,37 +18694,37 @@
 SFM-036.C2</t>
         </is>
       </c>
-      <c r="G6" s="61" t="inlineStr"/>
-      <c r="H6" s="61" t="inlineStr"/>
-      <c r="I6" s="61" t="inlineStr"/>
+      <c r="G6" s="60" t="inlineStr"/>
+      <c r="H6" s="60" t="inlineStr"/>
+      <c r="I6" s="60" t="inlineStr"/>
     </row>
     <row r="7" ht="73.5" customHeight="1">
-      <c r="A7" s="61" t="inlineStr">
+      <c r="A7" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-007</t>
         </is>
       </c>
-      <c r="B7" s="61" t="inlineStr">
+      <c r="B7" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C7" s="61" t="inlineStr">
+      <c r="C7" s="60" t="inlineStr">
         <is>
           <t>Supervise the alert channels: treat loss of ui or soundd liveness, or a stale displayed state, as a fault that escalates (audible fallback, disengagement) instead of continuing silently</t>
         </is>
       </c>
-      <c r="D7" s="61" t="inlineStr">
+      <c r="D7" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E7" s="61" t="inlineStr">
+      <c r="E7" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F7" s="61" t="inlineStr">
+      <c r="F7" s="60" t="inlineStr">
         <is>
           <t>SFM-015.C1
 SFM-026.C1
@@ -18736,76 +18733,76 @@
 SFM-028.C1</t>
         </is>
       </c>
-      <c r="G7" s="61" t="inlineStr"/>
-      <c r="H7" s="61" t="inlineStr"/>
-      <c r="I7" s="61" t="inlineStr"/>
+      <c r="G7" s="60" t="inlineStr"/>
+      <c r="H7" s="60" t="inlineStr"/>
+      <c r="I7" s="60" t="inlineStr"/>
     </row>
     <row r="8" ht="73.5" customHeight="1">
-      <c r="A8" s="61" t="inlineStr">
+      <c r="A8" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-008</t>
         </is>
       </c>
-      <c r="B8" s="61" t="inlineStr">
+      <c r="B8" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C8" s="61" t="inlineStr">
+      <c r="C8" s="60" t="inlineStr">
         <is>
           <t>Allow engagement only when the fingerprint, CarParams and panda safety parameter match the reference configuration AC-001 (refuse fuzzy matches in the reference build); see PFMEA PFM-013</t>
         </is>
       </c>
-      <c r="D8" s="61" t="inlineStr">
+      <c r="D8" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E8" s="61" t="inlineStr">
+      <c r="E8" s="60" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F8" s="61" t="inlineStr">
+      <c r="F8" s="60" t="inlineStr">
         <is>
           <t>SFM-032.C1</t>
         </is>
       </c>
-      <c r="G8" s="61" t="inlineStr"/>
-      <c r="H8" s="61" t="inlineStr"/>
-      <c r="I8" s="61" t="inlineStr">
+      <c r="G8" s="60" t="inlineStr"/>
+      <c r="H8" s="60" t="inlineStr"/>
+      <c r="I8" s="60" t="inlineStr">
         <is>
           <t>BL-005: the reference build is the default (LionDriver #36), the panda accepts only TOYOTA parameter 73 (reference_lock.h) and pandad configures a car mode only on a reference panda (#41). Fuzzy fingerprint matches are still accepted on the host (SFM-032.C1)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="100.5" customHeight="1">
-      <c r="A9" s="61" t="inlineStr">
+      <c r="A9" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-009</t>
         </is>
       </c>
-      <c r="B9" s="61" t="inlineStr">
+      <c r="B9" s="60" t="inlineStr">
         <is>
           <t>prevention</t>
         </is>
       </c>
-      <c r="C9" s="61" t="inlineStr">
+      <c r="C9" s="60" t="inlineStr">
         <is>
           <t>Produce SOTIF / ISO PAS 8800 evidence for the neural-network elements (driving model, lead detection, driver monitoring model) per WP-V-02..04, including fault-induced inputs (corrupted or stale frames)</t>
         </is>
       </c>
-      <c r="D9" s="61" t="inlineStr">
+      <c r="D9" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E9" s="61" t="inlineStr">
+      <c r="E9" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F9" s="61" t="inlineStr">
+      <c r="F9" s="60" t="inlineStr">
         <is>
           <t>SFM-002.C2
 SFM-003.C3
@@ -18816,37 +18813,37 @@
 SFM-022.C2</t>
         </is>
       </c>
-      <c r="G9" s="61" t="inlineStr"/>
-      <c r="H9" s="61" t="inlineStr"/>
-      <c r="I9" s="61" t="inlineStr"/>
+      <c r="G9" s="60" t="inlineStr"/>
+      <c r="H9" s="60" t="inlineStr"/>
+      <c r="I9" s="60" t="inlineStr"/>
     </row>
     <row r="10" ht="73.5" customHeight="1">
-      <c r="A10" s="61" t="inlineStr">
+      <c r="A10" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-010</t>
         </is>
       </c>
-      <c r="B10" s="61" t="inlineStr">
+      <c r="B10" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C10" s="61" t="inlineStr">
+      <c r="C10" s="60" t="inlineStr">
         <is>
           <t>Justify every SOFT_DISABLE reaction and debounce against the FTTI (WP-S-04) and alert at once when the panda withdraws authority while engaged (controlsMismatch debounce)</t>
         </is>
       </c>
-      <c r="D10" s="61" t="inlineStr">
+      <c r="D10" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E10" s="61" t="inlineStr">
+      <c r="E10" s="60" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F10" s="61" t="inlineStr">
+      <c r="F10" s="60" t="inlineStr">
         <is>
           <t>SFM-014.C2
 SFM-015.C2
@@ -18854,408 +18851,408 @@
 SFM-016.C2</t>
         </is>
       </c>
-      <c r="G10" s="61" t="inlineStr"/>
-      <c r="H10" s="61" t="inlineStr"/>
-      <c r="I10" s="61" t="inlineStr">
+      <c r="G10" s="60" t="inlineStr"/>
+      <c r="H10" s="60" t="inlineStr"/>
+      <c r="I10" s="60" t="inlineStr">
         <is>
           <t>controlsMismatch debounce cut from 200 cumulative samples (~2 s) to 2 consecutive samples, at most 0.5 s (change-2026-10-13-host-supervision.md); credited at BL-005 (SFM-015.C2 M 6). FTTI justification of SOFT_DISABLE reactions open</t>
         </is>
       </c>
     </row>
     <row r="11" ht="33" customHeight="1">
-      <c r="A11" s="61" t="inlineStr">
+      <c r="A11" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-011</t>
         </is>
       </c>
-      <c r="B11" s="61" t="inlineStr">
+      <c r="B11" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C11" s="61" t="inlineStr">
+      <c r="C11" s="60" t="inlineStr">
         <is>
           <t>Alert the driver when stock cruise stays engaged while the item is disengaged (cruiseMismatch has no alert at BL-004)</t>
         </is>
       </c>
-      <c r="D11" s="61" t="inlineStr">
+      <c r="D11" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E11" s="62" t="inlineStr">
+      <c r="E11" s="61" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F11" s="61" t="inlineStr">
+      <c r="F11" s="60" t="inlineStr">
         <is>
           <t>SFM-021.C1
 SFM-021.C2</t>
         </is>
       </c>
-      <c r="G11" s="61" t="inlineStr"/>
-      <c r="H11" s="61" t="inlineStr"/>
-      <c r="I11" s="61" t="inlineStr">
+      <c r="G11" s="60" t="inlineStr"/>
+      <c r="H11" s="60" t="inlineStr"/>
+      <c r="I11" s="60" t="inlineStr">
         <is>
           <t>cruiseMismatch now alerts after 1 s (change-2026-10-13-host-supervision.md); see SWF-ACT-034</t>
         </is>
       </c>
     </row>
     <row r="12" ht="73.5" customHeight="1">
-      <c r="A12" s="61" t="inlineStr">
+      <c r="A12" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-012</t>
         </is>
       </c>
-      <c r="B12" s="61" t="inlineStr">
+      <c r="B12" s="60" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C12" s="61" t="inlineStr">
+      <c r="C12" s="60" t="inlineStr">
         <is>
           <t>Measure on the HIL bench and the reference car (WP-V-05) how the panda reacts to over-limit and not-engaged steering and acceleration frames and to driver brake, gas and cancel inputs, and what the EPS and PCM do when frames are refused; re-rate the MSR rows from code-derived to measured timing</t>
         </is>
       </c>
-      <c r="D12" s="61" t="inlineStr"/>
-      <c r="E12" s="61" t="inlineStr">
+      <c r="D12" s="60" t="inlineStr"/>
+      <c r="E12" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F12" s="61" t="inlineStr"/>
-      <c r="G12" s="61" t="inlineStr"/>
-      <c r="H12" s="61" t="inlineStr"/>
-      <c r="I12" s="61" t="inlineStr"/>
+      <c r="F12" s="60" t="inlineStr"/>
+      <c r="G12" s="60" t="inlineStr"/>
+      <c r="H12" s="60" t="inlineStr"/>
+      <c r="I12" s="60" t="inlineStr"/>
     </row>
     <row r="13" ht="87" customHeight="1">
-      <c r="A13" s="61" t="inlineStr">
+      <c r="A13" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-013</t>
         </is>
       </c>
-      <c r="B13" s="61" t="inlineStr">
+      <c r="B13" s="60" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C13" s="61" t="inlineStr">
+      <c r="C13" s="60" t="inlineStr">
         <is>
           <t>Check on the host, within the SG-01 FTTI, that the panda reports controls_allowed false while the item is disengaged (the reverse of the controlsMismatch check, which at BL-005 still covers only engaged with authority withdrawn), with a disable and an alert. The requirement is TSR-630, within 0.3 s (WP-S-02 §12.3a; WP-S-04 T-32, not implemented)</t>
         </is>
       </c>
-      <c r="D13" s="61" t="inlineStr"/>
-      <c r="E13" s="61" t="inlineStr">
+      <c r="D13" s="60" t="inlineStr"/>
+      <c r="E13" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F13" s="61" t="inlineStr"/>
-      <c r="G13" s="61" t="inlineStr"/>
-      <c r="H13" s="61" t="inlineStr"/>
-      <c r="I13" s="61" t="inlineStr"/>
+      <c r="F13" s="60" t="inlineStr"/>
+      <c r="G13" s="60" t="inlineStr"/>
+      <c r="H13" s="60" t="inlineStr"/>
+      <c r="I13" s="60" t="inlineStr"/>
     </row>
     <row r="14" ht="46.5" customHeight="1">
-      <c r="A14" s="61" t="inlineStr">
+      <c r="A14" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-014</t>
         </is>
       </c>
-      <c r="B14" s="61" t="inlineStr">
+      <c r="B14" s="60" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C14" s="61" t="inlineStr">
+      <c r="C14" s="60" t="inlineStr">
         <is>
           <t>Specify in the TSC a steering-direction plausibility monitor (commanded torque sign against measured yaw rate and lane-relative lateral motion), or justify its absence against HZ-003</t>
         </is>
       </c>
-      <c r="D14" s="61" t="inlineStr"/>
-      <c r="E14" s="61" t="inlineStr">
+      <c r="D14" s="60" t="inlineStr"/>
+      <c r="E14" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F14" s="61" t="inlineStr"/>
-      <c r="G14" s="61" t="inlineStr"/>
-      <c r="H14" s="61" t="inlineStr"/>
-      <c r="I14" s="61" t="inlineStr"/>
+      <c r="F14" s="60" t="inlineStr"/>
+      <c r="G14" s="60" t="inlineStr"/>
+      <c r="H14" s="60" t="inlineStr"/>
+      <c r="I14" s="60" t="inlineStr"/>
     </row>
     <row r="15" ht="100.5" customHeight="1">
-      <c r="A15" s="61" t="inlineStr">
+      <c r="A15" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-015</t>
         </is>
       </c>
-      <c r="B15" s="61" t="inlineStr">
+      <c r="B15" s="60" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C15" s="61" t="inlineStr">
+      <c r="C15" s="60" t="inlineStr">
         <is>
           <t>Detect stale commands and inputs within the SG-01 FTTI: command-frame freshness in the MCU with an active zero frame (TSR-408, TSR-109) and frozen-content and age checks on model outputs in controlsd (TSR-602, TSR-631, AIR-17)</t>
         </is>
       </c>
-      <c r="D15" s="61" t="inlineStr"/>
-      <c r="E15" s="61" t="inlineStr">
+      <c r="D15" s="60" t="inlineStr"/>
+      <c r="E15" s="60" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F15" s="61" t="inlineStr"/>
-      <c r="G15" s="61" t="inlineStr"/>
-      <c r="H15" s="61" t="inlineStr"/>
-      <c r="I15" s="61" t="inlineStr">
+      <c r="F15" s="60" t="inlineStr"/>
+      <c r="G15" s="60" t="inlineStr"/>
+      <c r="H15" s="60" t="inlineStr"/>
+      <c r="I15" s="60" t="inlineStr">
         <is>
           <t>BL-005: command-frame arrival in the MCU (TSR-408, 50 ms STEERING_LKA, reference build by default) and input age checks in controlsd (TSR-602) are in. Open: the active zero frame (TSR-109), a frozen-content check on model outputs, and stale data with fresh timestamps (SFM-006.C1 to C3). The frozen-content check is TSR-631, with the age taken from the source timestamp (WP-S-02 §12.3a)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="73.5" customHeight="1">
-      <c r="A16" s="61" t="inlineStr">
+      <c r="A16" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-016</t>
         </is>
       </c>
-      <c r="B16" s="61" t="inlineStr">
+      <c r="B16" s="60" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C16" s="61" t="inlineStr">
+      <c r="C16" s="60" t="inlineStr">
         <is>
           <t>Supervise driver override in the panda: driver steering torque above the override threshold limits or revokes lateral authority within the SG-05 0.2 s budget (TSR-304). Behaviour decided by the lead (DQ-053, option A): back off on override and show a cue. Requirements: TSR-304 (timing tied to the SG-05 budget) and TSR-628 (WP-S-02 §12.3a)</t>
         </is>
       </c>
-      <c r="D16" s="61" t="inlineStr"/>
-      <c r="E16" s="61" t="inlineStr">
+      <c r="D16" s="60" t="inlineStr"/>
+      <c r="E16" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F16" s="61" t="inlineStr"/>
-      <c r="G16" s="61" t="inlineStr"/>
-      <c r="H16" s="61" t="inlineStr"/>
-      <c r="I16" s="61" t="inlineStr"/>
+      <c r="F16" s="60" t="inlineStr"/>
+      <c r="G16" s="60" t="inlineStr"/>
+      <c r="H16" s="60" t="inlineStr"/>
+      <c r="I16" s="60" t="inlineStr"/>
     </row>
     <row r="17" ht="87" customHeight="1">
-      <c r="A17" s="61" t="inlineStr">
+      <c r="A17" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-017</t>
         </is>
       </c>
-      <c r="B17" s="61" t="inlineStr">
+      <c r="B17" s="60" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C17" s="61" t="inlineStr">
+      <c r="C17" s="60" t="inlineStr">
         <is>
           <t>Add WP-S-04 FTTI rows for the warning paths without one (insufficient lateral control, late or insufficient braking warnings, SG-008 unintended engagement, driver monitoring), so these mechanisms can be compared with a time budget</t>
         </is>
       </c>
-      <c r="D17" s="61" t="inlineStr"/>
-      <c r="E17" s="62" t="inlineStr">
+      <c r="D17" s="60" t="inlineStr"/>
+      <c r="E17" s="61" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F17" s="61" t="inlineStr"/>
-      <c r="G17" s="61" t="inlineStr"/>
-      <c r="H17" s="61" t="inlineStr"/>
-      <c r="I17" s="61" t="inlineStr">
+      <c r="F17" s="60" t="inlineStr"/>
+      <c r="G17" s="60" t="inlineStr"/>
+      <c r="H17" s="60" t="inlineStr"/>
+      <c r="I17" s="60" t="inlineStr">
         <is>
           <t>WP-S-04 v0.7 §3.7 (four rows) and §3.8, with T-30 to T-33. Rev 0.15 compares SFM-004, SFM-010.C2/C3, SFM-012.C1 and SFM-013.C1/C2 with them. Driver monitoring (SFM-022.C3, SFM-025.C1) waits for the H-09 FTTI (§3.8.4); follow-up is SFM-ACT-005. Late warnings found: SFM-ACT-021 (lateral) and SFM-ACT-022 (braking)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="100.5" customHeight="1">
-      <c r="A18" s="61" t="inlineStr">
+      <c r="A18" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-018</t>
         </is>
       </c>
-      <c r="B18" s="61" t="inlineStr">
+      <c r="B18" s="60" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C18" s="61" t="inlineStr">
+      <c r="C18" s="60" t="inlineStr">
         <is>
           <t>Detect silent loss of the actuation path: report forwarded and refused TX frames from the panda, and compare EPS and PCM acceptance (LKA_STATE, ACC status) with the commands, warning within the SG-02/06 1 s budget</t>
         </is>
       </c>
-      <c r="D18" s="61" t="inlineStr"/>
-      <c r="E18" s="61" t="inlineStr">
+      <c r="D18" s="60" t="inlineStr"/>
+      <c r="E18" s="60" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F18" s="61" t="inlineStr"/>
-      <c r="G18" s="61" t="inlineStr"/>
-      <c r="H18" s="61" t="inlineStr"/>
-      <c r="I18" s="61" t="inlineStr">
+      <c r="F18" s="60" t="inlineStr"/>
+      <c r="G18" s="60" t="inlineStr"/>
+      <c r="H18" s="60" t="inlineStr"/>
+      <c r="I18" s="60" t="inlineStr">
         <is>
           <t>BL-005: frames that stop reaching the panda are detected (TSR-408) and alerted within 0.5 s (TSR-621), credited on SFM-005.C2 and SFM-011.C2. Open: frames that reach the panda but are not accepted by the EPS or PCM (SFM-005.C1, SFM-011.C1). Requirements: TSR-632 (per-ID transmitted and refused counts), TSR-626(d)/(e) (EPS and PCM acceptance status) and TSR-615, warning within 1 s (WP-S-02 §12.3a)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="61" t="inlineStr">
+      <c r="A19" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-019</t>
         </is>
       </c>
-      <c r="B19" s="61" t="inlineStr">
+      <c r="B19" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C19" s="61" t="inlineStr">
+      <c r="C19" s="60" t="inlineStr">
         <is>
           <t>Revoke lateral authority in the panda when it rejects a steering frame while authority is granted, and keep it revoked until a new valid engagement (TSR-108; lead decision DQ-060, option A). At BL-005 the frame is dropped and only the host disengages (pandaTxBlocked)</t>
         </is>
       </c>
-      <c r="D19" s="61" t="inlineStr"/>
-      <c r="E19" s="61" t="inlineStr">
+      <c r="D19" s="60" t="inlineStr"/>
+      <c r="E19" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F19" s="61" t="inlineStr">
+      <c r="F19" s="60" t="inlineStr">
         <is>
           <t>SFM-002.C1
 SFM-002.C2
 SFM-002.C4</t>
         </is>
       </c>
-      <c r="G19" s="61" t="inlineStr"/>
-      <c r="H19" s="61" t="inlineStr"/>
-      <c r="I19" s="61" t="inlineStr"/>
+      <c r="G19" s="60" t="inlineStr"/>
+      <c r="H19" s="60" t="inlineStr"/>
+      <c r="I19" s="60" t="inlineStr"/>
     </row>
     <row r="20" ht="73.5" customHeight="1">
-      <c r="A20" s="61" t="inlineStr">
+      <c r="A20" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-020</t>
         </is>
       </c>
-      <c r="B20" s="61" t="inlineStr">
+      <c r="B20" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C20" s="61" t="inlineStr">
+      <c r="C20" s="60" t="inlineStr">
         <is>
           <t>React to a stock PCS event on the longitudinal command (for example a neutral or zero acceleration request, or a longitudinal disable, while stockAeb is set), so stock AEB does not depend on PCM arbitration alone (AOU-04R); or keep today's behaviour and rely on the AOU-04R vehicle test. Lead decision DQ-300</t>
         </is>
       </c>
-      <c r="D20" s="61" t="inlineStr"/>
-      <c r="E20" s="61" t="inlineStr">
+      <c r="D20" s="60" t="inlineStr"/>
+      <c r="E20" s="60" t="inlineStr">
         <is>
           <t>decision pending</t>
         </is>
       </c>
-      <c r="F20" s="61" t="inlineStr">
+      <c r="F20" s="60" t="inlineStr">
         <is>
           <t>SFM-036.C1</t>
         </is>
       </c>
-      <c r="G20" s="61" t="inlineStr"/>
-      <c r="H20" s="61" t="inlineStr"/>
-      <c r="I20" s="61" t="inlineStr"/>
+      <c r="G20" s="60" t="inlineStr"/>
+      <c r="H20" s="60" t="inlineStr"/>
+      <c r="I20" s="60" t="inlineStr"/>
     </row>
     <row r="21" ht="73.5" customHeight="1">
-      <c r="A21" s="61" t="inlineStr">
+      <c r="A21" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-021</t>
         </is>
       </c>
-      <c r="B21" s="61" t="inlineStr">
+      <c r="B21" s="60" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C21" s="61" t="inlineStr">
+      <c r="C21" s="60" t="inlineStr">
         <is>
           <t>Make the insufficient-lateral-control warning timely (WP-S-04 §3.8.1): warn before the deficit has lasted 0.4 s, for example from the planned curvature against the envelope, or keep the deficit at or below about 0.5 m/s² through the steering limits and the ODD curve bound (WP-S-04 OI-2). A change to the ODD bound is a lead decision</t>
         </is>
       </c>
-      <c r="D21" s="61" t="inlineStr"/>
-      <c r="E21" s="61" t="inlineStr">
+      <c r="D21" s="60" t="inlineStr"/>
+      <c r="E21" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F21" s="61" t="inlineStr">
+      <c r="F21" s="60" t="inlineStr">
         <is>
           <t>SFM-038.C3</t>
         </is>
       </c>
-      <c r="G21" s="61" t="inlineStr"/>
-      <c r="H21" s="61" t="inlineStr"/>
-      <c r="I21" s="61" t="inlineStr"/>
+      <c r="G21" s="60" t="inlineStr"/>
+      <c r="H21" s="60" t="inlineStr"/>
+      <c r="I21" s="60" t="inlineStr"/>
     </row>
     <row r="22" ht="60" customHeight="1">
-      <c r="A22" s="61" t="inlineStr">
+      <c r="A22" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-022</t>
         </is>
       </c>
-      <c r="B22" s="61" t="inlineStr">
+      <c r="B22" s="60" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C22" s="61" t="inlineStr">
+      <c r="C22" s="60" t="inlineStr">
         <is>
           <t>Measure the FCW onset after a lead brakes hard (WP-S-04 T-31, M-12) and compare it with the §3.8.2 budget (about 0.6 s at a 1.0 s gap). For pipeline lag (SFM-012.C1), detect it within that budget or show that the FCW path does not depend on the lagging process</t>
         </is>
       </c>
-      <c r="D22" s="61" t="inlineStr"/>
-      <c r="E22" s="61" t="inlineStr">
+      <c r="D22" s="60" t="inlineStr"/>
+      <c r="E22" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F22" s="61" t="inlineStr"/>
-      <c r="G22" s="61" t="inlineStr"/>
-      <c r="H22" s="61" t="inlineStr"/>
-      <c r="I22" s="61" t="inlineStr"/>
+      <c r="F22" s="60" t="inlineStr"/>
+      <c r="G22" s="60" t="inlineStr"/>
+      <c r="H22" s="60" t="inlineStr"/>
+      <c r="I22" s="60" t="inlineStr"/>
     </row>
     <row r="23" ht="100.5" customHeight="1">
-      <c r="A23" s="61" t="inlineStr">
+      <c r="A23" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-023</t>
         </is>
       </c>
-      <c r="B23" s="61" t="inlineStr">
+      <c r="B23" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C23" s="61" t="inlineStr">
+      <c r="C23" s="60" t="inlineStr">
         <is>
           <t>Escalate every EPS fault that lasts while engaged to the take-over request (steerTempUnavailable, SOFT_DISABLE), instead of keeping the low-priority steerTempUnavailableSilent prompt latched after a recent override or at standstill (car_events.py:162-177; behaviour change queued for the lead by the FSC session as DQ-342), and act on the panda fields epsFault and requestsRejected on the host (TSR-626(d), TSR-516(b)). SFM-038.C1, C2; FTA BE-2.08</t>
         </is>
       </c>
-      <c r="D23" s="61" t="inlineStr"/>
-      <c r="E23" s="61" t="inlineStr">
+      <c r="D23" s="60" t="inlineStr"/>
+      <c r="E23" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F23" s="61" t="inlineStr">
+      <c r="F23" s="60" t="inlineStr">
         <is>
           <t>SFM-038.C1
 SFM-038.C2</t>
         </is>
       </c>
-      <c r="G23" s="61" t="inlineStr"/>
-      <c r="H23" s="61" t="inlineStr"/>
-      <c r="I23" s="61" t="inlineStr"/>
+      <c r="G23" s="60" t="inlineStr"/>
+      <c r="H23" s="60" t="inlineStr"/>
+      <c r="I23" s="60" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I23"/>
@@ -19280,50 +19277,50 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="60" t="inlineStr">
+      <c r="A1" s="59" t="inlineStr">
         <is>
           <t>Element</t>
         </is>
       </c>
-      <c r="B1" s="60" t="inlineStr">
+      <c r="B1" s="59" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="60" t="inlineStr">
+      <c r="C1" s="59" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="D1" s="60" t="inlineStr">
+      <c r="D1" s="59" t="inlineStr">
         <is>
           <t>Parent</t>
         </is>
       </c>
-      <c r="E1" s="60" t="inlineStr">
+      <c r="E1" s="59" t="inlineStr">
         <is>
           <t>Functions</t>
         </is>
       </c>
     </row>
     <row r="2" ht="222" customHeight="1">
-      <c r="A2" s="61" t="inlineStr">
+      <c r="A2" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-001</t>
         </is>
       </c>
-      <c r="B2" s="61" t="inlineStr">
+      <c r="B2" s="60" t="inlineStr">
         <is>
           <t>LionDriver item (L2 ACC + ALC + driver monitoring)</t>
         </is>
       </c>
-      <c r="C2" s="61" t="inlineStr">
+      <c r="C2" s="60" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="D2" s="61" t="inlineStr"/>
-      <c r="E2" s="61" t="inlineStr">
+      <c r="D2" s="60" t="inlineStr"/>
+      <c r="E2" s="60" t="inlineStr">
         <is>
           <t>SFM-FN-001: F1 Lateral control: request steering torque from the EPS to keep the vehicle in its lane while engaged
 SFM-FN-002: F2 Longitudinal control: request acceleration/deceleration to hold set speed and follow leads while engaged
@@ -19337,398 +19334,398 @@
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="61" t="inlineStr">
+      <c r="A3" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="B3" s="61" t="inlineStr">
+      <c r="B3" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    comma 3X device</t>
         </is>
       </c>
-      <c r="C3" s="61" t="inlineStr">
+      <c r="C3" s="60" t="inlineStr">
         <is>
           <t>system</t>
         </is>
       </c>
-      <c r="D3" s="61" t="inlineStr">
+      <c r="D3" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-001</t>
         </is>
       </c>
-      <c r="E3" s="61" t="inlineStr"/>
+      <c r="E3" s="60" t="inlineStr"/>
     </row>
     <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="61" t="inlineStr">
+      <c r="A4" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-003</t>
         </is>
       </c>
-      <c r="B4" s="61" t="inlineStr">
+      <c r="B4" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Integrated panda (CAN interface and safety model)</t>
         </is>
       </c>
-      <c r="C4" s="61" t="inlineStr">
+      <c r="C4" s="60" t="inlineStr">
         <is>
           <t>subsystem</t>
         </is>
       </c>
-      <c r="D4" s="61" t="inlineStr">
+      <c r="D4" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E4" s="61" t="inlineStr"/>
+      <c r="E4" s="60" t="inlineStr"/>
     </row>
     <row r="5" ht="19.5" customHeight="1">
-      <c r="A5" s="61" t="inlineStr">
+      <c r="A5" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-004</t>
         </is>
       </c>
-      <c r="B5" s="61" t="inlineStr">
+      <c r="B5" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Harness (Toyota A connector, harness box, comma power v3)</t>
         </is>
       </c>
-      <c r="C5" s="61" t="inlineStr">
+      <c r="C5" s="60" t="inlineStr">
         <is>
           <t>component</t>
         </is>
       </c>
-      <c r="D5" s="61" t="inlineStr">
+      <c r="D5" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-001</t>
         </is>
       </c>
-      <c r="E5" s="61" t="inlineStr"/>
+      <c r="E5" s="60" t="inlineStr"/>
     </row>
     <row r="6" ht="19.5" customHeight="1">
-      <c r="A6" s="61" t="inlineStr">
+      <c r="A6" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-010</t>
         </is>
       </c>
-      <c r="B6" s="61" t="inlineStr">
+      <c r="B6" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Perception (camerad, modeld)</t>
         </is>
       </c>
-      <c r="C6" s="61" t="inlineStr">
+      <c r="C6" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D6" s="61" t="inlineStr">
+      <c r="D6" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E6" s="61" t="inlineStr"/>
+      <c r="E6" s="60" t="inlineStr"/>
     </row>
     <row r="7" ht="19.5" customHeight="1">
-      <c r="A7" s="61" t="inlineStr">
+      <c r="A7" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-011</t>
         </is>
       </c>
-      <c r="B7" s="61" t="inlineStr">
+      <c r="B7" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Localization and calibration (locationd, calibrationd, paramsd, torqued)</t>
         </is>
       </c>
-      <c r="C7" s="61" t="inlineStr">
+      <c r="C7" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D7" s="61" t="inlineStr">
+      <c r="D7" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E7" s="61" t="inlineStr"/>
+      <c r="E7" s="60" t="inlineStr"/>
     </row>
     <row r="8" ht="19.5" customHeight="1">
-      <c r="A8" s="61" t="inlineStr">
+      <c r="A8" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-012</t>
         </is>
       </c>
-      <c r="B8" s="61" t="inlineStr">
+      <c r="B8" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Planning (plannerd, radard)</t>
         </is>
       </c>
-      <c r="C8" s="61" t="inlineStr">
+      <c r="C8" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D8" s="61" t="inlineStr">
+      <c r="D8" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E8" s="61" t="inlineStr"/>
+      <c r="E8" s="60" t="inlineStr"/>
     </row>
     <row r="9" ht="19.5" customHeight="1">
-      <c r="A9" s="61" t="inlineStr">
+      <c r="A9" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-013</t>
         </is>
       </c>
-      <c r="B9" s="61" t="inlineStr">
+      <c r="B9" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Control (controlsd, lateral/longitudinal controllers)</t>
         </is>
       </c>
-      <c r="C9" s="61" t="inlineStr">
+      <c r="C9" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D9" s="61" t="inlineStr">
+      <c r="D9" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E9" s="61" t="inlineStr"/>
+      <c r="E9" s="60" t="inlineStr"/>
     </row>
     <row r="10" ht="19.5" customHeight="1">
-      <c r="A10" s="61" t="inlineStr">
+      <c r="A10" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-014</t>
         </is>
       </c>
-      <c r="B10" s="61" t="inlineStr">
+      <c r="B10" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Supervision (selfdrived state machine, events, alert manager)</t>
         </is>
       </c>
-      <c r="C10" s="61" t="inlineStr">
+      <c r="C10" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D10" s="61" t="inlineStr">
+      <c r="D10" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E10" s="61" t="inlineStr"/>
+      <c r="E10" s="60" t="inlineStr"/>
     </row>
     <row r="11" ht="19.5" customHeight="1">
-      <c r="A11" s="61" t="inlineStr">
+      <c r="A11" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-015</t>
         </is>
       </c>
-      <c r="B11" s="61" t="inlineStr">
+      <c r="B11" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Driver monitoring (dmonitoringmodeld, dmonitoringd)</t>
         </is>
       </c>
-      <c r="C11" s="61" t="inlineStr">
+      <c r="C11" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D11" s="61" t="inlineStr">
+      <c r="D11" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E11" s="61" t="inlineStr"/>
+      <c r="E11" s="60" t="inlineStr"/>
     </row>
     <row r="12" ht="19.5" customHeight="1">
-      <c r="A12" s="61" t="inlineStr">
+      <c r="A12" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-016</t>
         </is>
       </c>
-      <c r="B12" s="61" t="inlineStr">
+      <c r="B12" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Car interface (card, car_events, opendbc Toyota port)</t>
         </is>
       </c>
-      <c r="C12" s="61" t="inlineStr">
+      <c r="C12" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D12" s="61" t="inlineStr">
+      <c r="D12" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E12" s="61" t="inlineStr"/>
+      <c r="E12" s="60" t="inlineStr"/>
     </row>
     <row r="13" ht="19.5" customHeight="1">
-      <c r="A13" s="61" t="inlineStr">
+      <c r="A13" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-017</t>
         </is>
       </c>
-      <c r="B13" s="61" t="inlineStr">
+      <c r="B13" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Panda daemon (pandad)</t>
         </is>
       </c>
-      <c r="C13" s="61" t="inlineStr">
+      <c r="C13" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D13" s="61" t="inlineStr">
+      <c r="D13" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E13" s="61" t="inlineStr"/>
+      <c r="E13" s="60" t="inlineStr"/>
     </row>
     <row r="14" ht="19.5" customHeight="1">
-      <c r="A14" s="61" t="inlineStr">
+      <c r="A14" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-018</t>
         </is>
       </c>
-      <c r="B14" s="61" t="inlineStr">
+      <c r="B14" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        HMI (ui, soundd)</t>
         </is>
       </c>
-      <c r="C14" s="61" t="inlineStr">
+      <c r="C14" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D14" s="61" t="inlineStr">
+      <c r="D14" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E14" s="61" t="inlineStr"/>
+      <c r="E14" s="60" t="inlineStr"/>
     </row>
     <row r="15" ht="19.5" customHeight="1">
-      <c r="A15" s="61" t="inlineStr">
+      <c r="A15" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-019</t>
         </is>
       </c>
-      <c r="B15" s="61" t="inlineStr">
+      <c r="B15" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Platform (manager, messaging, hardwared, OS)</t>
         </is>
       </c>
-      <c r="C15" s="61" t="inlineStr">
+      <c r="C15" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D15" s="61" t="inlineStr">
+      <c r="D15" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E15" s="61" t="inlineStr"/>
+      <c r="E15" s="60" t="inlineStr"/>
     </row>
     <row r="16" ht="19.5" customHeight="1">
-      <c r="A16" s="61" t="inlineStr">
+      <c r="A16" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-030</t>
         </is>
       </c>
-      <c r="B16" s="61" t="inlineStr">
+      <c r="B16" s="60" t="inlineStr">
         <is>
           <t>Toyota EPS</t>
         </is>
       </c>
-      <c r="C16" s="61" t="inlineStr">
+      <c r="C16" s="60" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D16" s="61" t="inlineStr"/>
-      <c r="E16" s="61" t="inlineStr"/>
+      <c r="D16" s="60" t="inlineStr"/>
+      <c r="E16" s="60" t="inlineStr"/>
     </row>
     <row r="17" ht="19.5" customHeight="1">
-      <c r="A17" s="61" t="inlineStr">
+      <c r="A17" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-031</t>
         </is>
       </c>
-      <c r="B17" s="61" t="inlineStr">
+      <c r="B17" s="60" t="inlineStr">
         <is>
           <t>Toyota powertrain and brake control (receives ACC acceleration requests)</t>
         </is>
       </c>
-      <c r="C17" s="61" t="inlineStr">
+      <c r="C17" s="60" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D17" s="61" t="inlineStr"/>
-      <c r="E17" s="61" t="inlineStr"/>
+      <c r="D17" s="60" t="inlineStr"/>
+      <c r="E17" s="60" t="inlineStr"/>
     </row>
     <row r="18" ht="19.5" customHeight="1">
-      <c r="A18" s="61" t="inlineStr">
+      <c r="A18" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-032</t>
         </is>
       </c>
-      <c r="B18" s="61" t="inlineStr">
+      <c r="B18" s="60" t="inlineStr">
         <is>
           <t>Toyota stock ADAS camera (TSS2)</t>
         </is>
       </c>
-      <c r="C18" s="61" t="inlineStr">
+      <c r="C18" s="60" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D18" s="61" t="inlineStr"/>
-      <c r="E18" s="61" t="inlineStr"/>
+      <c r="D18" s="60" t="inlineStr"/>
+      <c r="E18" s="60" t="inlineStr"/>
     </row>
     <row r="19" ht="19.5" customHeight="1">
-      <c r="A19" s="61" t="inlineStr">
+      <c r="A19" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-033</t>
         </is>
       </c>
-      <c r="B19" s="61" t="inlineStr">
+      <c r="B19" s="60" t="inlineStr">
         <is>
           <t>Vehicle CAN buses and 12 V supply</t>
         </is>
       </c>
-      <c r="C19" s="61" t="inlineStr">
+      <c r="C19" s="60" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D19" s="61" t="inlineStr"/>
-      <c r="E19" s="61" t="inlineStr"/>
+      <c r="D19" s="60" t="inlineStr"/>
+      <c r="E19" s="60" t="inlineStr"/>
     </row>
     <row r="20" ht="19.5" customHeight="1">
-      <c r="A20" s="61" t="inlineStr">
+      <c r="A20" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-034</t>
         </is>
       </c>
-      <c r="B20" s="61" t="inlineStr">
+      <c r="B20" s="60" t="inlineStr">
         <is>
           <t>Driver</t>
         </is>
       </c>
-      <c r="C20" s="61" t="inlineStr">
+      <c r="C20" s="60" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D20" s="61" t="inlineStr"/>
-      <c r="E20" s="61" t="inlineStr"/>
+      <c r="D20" s="60" t="inlineStr"/>
+      <c r="E20" s="60" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E20"/>
@@ -19764,7 +19761,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="63" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>FMEA-MSR (monitoring and system response, msr-plan.md): S, F, M and MSR AP per rating-tables.md §7 (RT-2). The MSR AP table is provisional until the handbook table is transcribed (decision register DQ-207). Exempt causes are rated in the FMEA named in the reason.</t>
         </is>
@@ -22521,7 +22518,7 @@
           <t>Device power loss (12 V interruption, harness connector)</t>
         </is>
       </c>
-      <c r="E44" s="64" t="inlineStr">
+      <c r="E44" s="63" t="inlineStr">
         <is>
           <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-012.C1)</t>
         </is>
@@ -23242,7 +23239,7 @@
       </c>
       <c r="N55" s="34" t="inlineStr">
         <is>
-          <t>SFM-ACT-005 · decision pending</t>
+          <t>SFM-ACT-005 · open</t>
         </is>
       </c>
       <c r="O55" s="37" t="inlineStr"/>
@@ -23304,7 +23301,7 @@
       </c>
       <c r="N56" s="34" t="inlineStr">
         <is>
-          <t>SFM-ACT-005 · decision pending</t>
+          <t>SFM-ACT-005 · open</t>
         </is>
       </c>
       <c r="O56" s="37" t="inlineStr"/>
@@ -23643,7 +23640,7 @@
           <t>Panda MCU hardware fault (see DFMEA/FMEDA)</t>
         </is>
       </c>
-      <c r="E62" s="64" t="inlineStr">
+      <c r="E62" s="63" t="inlineStr">
         <is>
           <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-001.C1)</t>
         </is>
@@ -23803,7 +23800,7 @@
           <t>Switch U1 or U2 stuck in intercept, its IN input damaged high or driven high, its pull-down R2/R3 open, or the switches damaged by box supply transients (DG419LE, RR-2026-010)</t>
         </is>
       </c>
-      <c r="E65" s="64" t="inlineStr">
+      <c r="E65" s="63" t="inlineStr">
         <is>
           <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-010.C1)</t>
         </is>
@@ -23839,7 +23836,7 @@
           <t>Switch stuck in pass-through, or the SBU1 drive lost, held low or too low to change the switch over (5 V drive against VL = VIN)</t>
         </is>
       </c>
-      <c r="E66" s="64" t="inlineStr">
+      <c r="E66" s="63" t="inlineStr">
         <is>
           <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-011.C1)</t>
         </is>
@@ -24315,7 +24312,7 @@
           <t>After any driver steering input in the last 1.5 s, or at standstill, a temporary EPS fault raises only steerTempUnavailableSilent (a LOW-priority WARNING with a prompt chime and no soft disable, events.py:516-521), and it stays latched while the fault lasts, so a long fault never escalates to the take-over request (car_events.py:162-177; T-25, GAP-03)</t>
         </is>
       </c>
-      <c r="E74" s="64" t="inlineStr">
+      <c r="E74" s="63" t="inlineStr">
         <is>
           <t>Exempt: The cause is a defect of the warning path itself; its effect on detecting the lateral loss is rated in the MSR rows of SFM-004.C2 and SFM-005 (msr-plan §3)</t>
         </is>
@@ -24351,7 +24348,7 @@
           <t>pandad publishes the panda fields epsFault and requestsRejected (pandad.cc:137-138), but no SoC process reads them (txRateExceeded is read, TSR-615), so a panda-side EPS-fault refusal reaches the driver only through the panda siren and the stock EPS path (SW FMEA SWF-025 notes)</t>
         </is>
       </c>
-      <c r="E75" s="64" t="inlineStr">
+      <c r="E75" s="63" t="inlineStr">
         <is>
           <t>Exempt: The cause is a defect of the warning path itself; the panda siren that remains is rated on SFM-005 and in the DFMEA (msr-plan §3)</t>
         </is>
@@ -24387,7 +24384,7 @@
           <t>steerSaturated needs the controller saturated, a desired lateral acceleration above 1.0 m/s², an undershoot above 1.2x and no steering input for 2 s (selfdrived.py:465-479), and the controller reports saturation only after 0.4 s (latcontrol.py, T-30); a gradual deficit therefore warns late or not at all (WP-S-04 §3.8.1)</t>
         </is>
       </c>
-      <c r="E76" s="64" t="inlineStr">
+      <c r="E76" s="63" t="inlineStr">
         <is>
           <t>Exempt: The cause is the timing of the warning itself; it is rated as M 8 in the MSR rows of SFM-004.C1-C3 (rev 0.15, WP-S-04 §3.8.1)</t>
         </is>
@@ -24418,7 +24415,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.23 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.24 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$93</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Worksheet'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Structure'!$A$1:$E$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'MSR'!$A$2:$P$76</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'MSR'!$1:$2</definedName>
@@ -261,7 +261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -410,6 +410,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -820,7 +823,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.24 · draft</t>
+          <t>0.25 · draft</t>
         </is>
       </c>
     </row>
@@ -949,7 +952,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>22 (20)</t>
+          <t>23 (20)</t>
         </is>
       </c>
     </row>
@@ -17741,7 +17744,7 @@
       <c r="R90" s="45" t="inlineStr"/>
       <c r="S90" s="45" t="inlineStr"/>
     </row>
-    <row r="91" ht="168" customHeight="1">
+    <row r="91" ht="154.5" customHeight="1">
       <c r="A91" s="30" t="inlineStr">
         <is>
           <r>
@@ -17969,21 +17972,29 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Escalate every EPS fault that lasts while engaged to the take-over request (steerTempUnavailable, SOFT_DISABLE), instead of keeping the low-priority steerTempUnavailableSilent prompt latched after a recent override or at standstill (car_events.py:162-177; behaviour change queued for the lead by the FSC session as DQ-342), and act on the panda fields epsFault and requestsRejected on the host (TSR-626(d), TSR-516(b)). SFM-038.C1, C2; FTA BE-2.08</t>
-          </r>
-        </is>
-      </c>
-      <c r="O91" s="47" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="P91" s="33" t="inlineStr"/>
-      <c r="Q91" s="33" t="inlineStr"/>
+            <t>Escalate a temporary EPS fault that lasts while engaged to the take-over request (steerTempUnavailable, SOFT_DISABLE) instead of keeping the low-priority steerTempUnavailableSilent prompt latched after a recent override or at standstill (car_events.py; lead decision DQ-342, option A: the lighter prompt for at most 1.5 s, then the take-over request; TSR-607 (b)). SFM-038.C1; FTA BE-2.08</t>
+          </r>
+        </is>
+      </c>
+      <c r="O91" s="54" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="P91" s="33" t="inlineStr">
+        <is>
+          <t>10/5/4</t>
+        </is>
+      </c>
+      <c r="Q91" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
       <c r="R91" s="37" t="inlineStr"/>
       <c r="S91" s="37" t="inlineStr"/>
     </row>
-    <row r="92" ht="168" customHeight="1">
+    <row r="92" ht="141" customHeight="1">
       <c r="A92" s="38" t="n"/>
       <c r="B92" s="38" t="n"/>
       <c r="C92" s="38" t="n"/>
@@ -18060,16 +18071,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">SFM-ACT-023 · design change
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Escalate every EPS fault that lasts while engaged to the take-over request (steerTempUnavailable, SOFT_DISABLE), instead of keeping the low-priority steerTempUnavailableSilent prompt latched after a recent override or at standstill (car_events.py:162-177; behaviour change queued for the lead by the FSC session as DQ-342), and act on the panda fields epsFault and requestsRejected on the host (TSR-626(d), TSR-516(b)). SFM-038.C1, C2; FTA BE-2.08</t>
+            <t xml:space="preserve">SFM-ACT-024 · monitoring
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Act on the panda fields epsFault and requestsRejected on the host (TSR-626(d), TSR-516(b)): raise the take-over request when the panda reports an EPS fault or refused steering frames while lateral control is engaged, within the SG-02 1 s budget, instead of relying on the panda siren alone. Split from SFM-ACT-023 (rev 0.25). SFM-038.C2; FTA BE-2.08</t>
           </r>
         </is>
       </c>
@@ -18401,7 +18412,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.24 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.25 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -18416,7 +18427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -19222,7 +19233,7 @@
       <c r="H22" s="60" t="inlineStr"/>
       <c r="I22" s="60" t="inlineStr"/>
     </row>
-    <row r="23" ht="100.5" customHeight="1">
+    <row r="23" ht="141" customHeight="1">
       <c r="A23" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-023</t>
@@ -19235,27 +19246,69 @@
       </c>
       <c r="C23" s="60" t="inlineStr">
         <is>
-          <t>Escalate every EPS fault that lasts while engaged to the take-over request (steerTempUnavailable, SOFT_DISABLE), instead of keeping the low-priority steerTempUnavailableSilent prompt latched after a recent override or at standstill (car_events.py:162-177; behaviour change queued for the lead by the FSC session as DQ-342), and act on the panda fields epsFault and requestsRejected on the host (TSR-626(d), TSR-516(b)). SFM-038.C1, C2; FTA BE-2.08</t>
+          <t>Escalate a temporary EPS fault that lasts while engaged to the take-over request (steerTempUnavailable, SOFT_DISABLE) instead of keeping the low-priority steerTempUnavailableSilent prompt latched after a recent override or at standstill (car_events.py; lead decision DQ-342, option A: the lighter prompt for at most 1.5 s, then the take-over request; TSR-607 (b)). SFM-038.C1; FTA BE-2.08</t>
         </is>
       </c>
       <c r="D23" s="60" t="inlineStr"/>
-      <c r="E23" s="60" t="inlineStr">
+      <c r="E23" s="61" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F23" s="60" t="inlineStr">
+        <is>
+          <t>SFM-038.C1</t>
+        </is>
+      </c>
+      <c r="G23" s="60" t="inlineStr">
+        <is>
+          <t>10/5/4</t>
+        </is>
+      </c>
+      <c r="H23" s="62" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I23" s="60" t="inlineStr">
+        <is>
+          <t>Merged in jherrodthomas/LionDriver#174 (7158a9a): STEER_FAULT_SILENT_FRAMES in car_events.py limits the lighter prompt to the first 1.5 s of the fault; selfdrive/car/tests/test_steer_fault_warning.py, 6 tests run in CI, 4 of them fail on the old code. Impact record assurance/07-supporting/impact/change-2026-10-17-eps-fault-escalation.md. Unit-tested only: not verified on the vehicle (impact OI-1) and not reviewed independently. Not in BL-005, so SFM-038.C1 keeps O 8, D 10 until the next baseline; revised ratings below are a prediction (as SWF-ACT-025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="87" customHeight="1">
+      <c r="A24" s="60" t="inlineStr">
+        <is>
+          <t>SFM-ACT-024</t>
+        </is>
+      </c>
+      <c r="B24" s="60" t="inlineStr">
+        <is>
+          <t>monitoring</t>
+        </is>
+      </c>
+      <c r="C24" s="60" t="inlineStr">
+        <is>
+          <t>Act on the panda fields epsFault and requestsRejected on the host (TSR-626(d), TSR-516(b)): raise the take-over request when the panda reports an EPS fault or refused steering frames while lateral control is engaged, within the SG-02 1 s budget, instead of relying on the panda siren alone. Split from SFM-ACT-023 (rev 0.25). SFM-038.C2; FTA BE-2.08</t>
+        </is>
+      </c>
+      <c r="D24" s="60" t="inlineStr"/>
+      <c r="E24" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F23" s="60" t="inlineStr">
-        <is>
-          <t>SFM-038.C1
-SFM-038.C2</t>
-        </is>
-      </c>
-      <c r="G23" s="60" t="inlineStr"/>
-      <c r="H23" s="60" t="inlineStr"/>
-      <c r="I23" s="60" t="inlineStr"/>
+      <c r="F24" s="60" t="inlineStr">
+        <is>
+          <t>SFM-038.C2</t>
+        </is>
+      </c>
+      <c r="G24" s="60" t="inlineStr"/>
+      <c r="H24" s="60" t="inlineStr"/>
+      <c r="I24" s="60" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I23"/>
+  <autoFilter ref="A1:I24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19761,7 +19814,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="62" t="inlineStr">
+      <c r="A1" s="63" t="inlineStr">
         <is>
           <t>FMEA-MSR (monitoring and system response, msr-plan.md): S, F, M and MSR AP per rating-tables.md §7 (RT-2). The MSR AP table is provisional until the handbook table is transcribed (decision register DQ-207). Exempt causes are rated in the FMEA named in the reason.</t>
         </is>
@@ -22518,7 +22571,7 @@
           <t>Device power loss (12 V interruption, harness connector)</t>
         </is>
       </c>
-      <c r="E44" s="63" t="inlineStr">
+      <c r="E44" s="64" t="inlineStr">
         <is>
           <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-012.C1)</t>
         </is>
@@ -23640,7 +23693,7 @@
           <t>Panda MCU hardware fault (see DFMEA/FMEDA)</t>
         </is>
       </c>
-      <c r="E62" s="63" t="inlineStr">
+      <c r="E62" s="64" t="inlineStr">
         <is>
           <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-001.C1)</t>
         </is>
@@ -23800,7 +23853,7 @@
           <t>Switch U1 or U2 stuck in intercept, its IN input damaged high or driven high, its pull-down R2/R3 open, or the switches damaged by box supply transients (DG419LE, RR-2026-010)</t>
         </is>
       </c>
-      <c r="E65" s="63" t="inlineStr">
+      <c r="E65" s="64" t="inlineStr">
         <is>
           <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-010.C1)</t>
         </is>
@@ -23836,7 +23889,7 @@
           <t>Switch stuck in pass-through, or the SBU1 drive lost, held low or too low to change the switch over (5 V drive against VL = VIN)</t>
         </is>
       </c>
-      <c r="E66" s="63" t="inlineStr">
+      <c r="E66" s="64" t="inlineStr">
         <is>
           <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-011.C1)</t>
         </is>
@@ -24312,7 +24365,7 @@
           <t>After any driver steering input in the last 1.5 s, or at standstill, a temporary EPS fault raises only steerTempUnavailableSilent (a LOW-priority WARNING with a prompt chime and no soft disable, events.py:516-521), and it stays latched while the fault lasts, so a long fault never escalates to the take-over request (car_events.py:162-177; T-25, GAP-03)</t>
         </is>
       </c>
-      <c r="E74" s="63" t="inlineStr">
+      <c r="E74" s="64" t="inlineStr">
         <is>
           <t>Exempt: The cause is a defect of the warning path itself; its effect on detecting the lateral loss is rated in the MSR rows of SFM-004.C2 and SFM-005 (msr-plan §3)</t>
         </is>
@@ -24348,7 +24401,7 @@
           <t>pandad publishes the panda fields epsFault and requestsRejected (pandad.cc:137-138), but no SoC process reads them (txRateExceeded is read, TSR-615), so a panda-side EPS-fault refusal reaches the driver only through the panda siren and the stock EPS path (SW FMEA SWF-025 notes)</t>
         </is>
       </c>
-      <c r="E75" s="63" t="inlineStr">
+      <c r="E75" s="64" t="inlineStr">
         <is>
           <t>Exempt: The cause is a defect of the warning path itself; the panda siren that remains is rated on SFM-005 and in the DFMEA (msr-plan §3)</t>
         </is>
@@ -24384,7 +24437,7 @@
           <t>steerSaturated needs the controller saturated, a desired lateral acceleration above 1.0 m/s², an undershoot above 1.2x and no steering input for 2 s (selfdrived.py:465-479), and the controller reports saturation only after 0.4 s (latcontrol.py, T-30); a gradual deficit therefore warns late or not at all (WP-S-04 §3.8.1)</t>
         </is>
       </c>
-      <c r="E76" s="63" t="inlineStr">
+      <c r="E76" s="64" t="inlineStr">
         <is>
           <t>Exempt: The cause is the timing of the warning itself; it is rated as M 8 in the MSR rows of SFM-004.C1-C3 (rev 0.15, WP-S-04 §3.8.1)</t>
         </is>
@@ -24415,7 +24468,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.24 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.25 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MSR" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$94</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Worksheet'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Structure'!$A$1:$E$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'MSR'!$A$2:$P$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'MSR'!$A$2:$P$77</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'MSR'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -823,7 +823,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.25 · draft</t>
+          <t>0.26 · draft</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -964,7 +964,7 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>67 rated, 7 exempt; MSR AP H 67, M 0, L 0 (provisional table)</t>
+          <t>67 rated, 8 exempt; MSR AP H 67, M 0, L 0 (provisional table)</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S93"/>
+  <dimension ref="A1:S94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10105,18 +10105,18 @@
       <c r="S51" s="37" t="inlineStr"/>
     </row>
     <row r="52" ht="73.5" customHeight="1">
-      <c r="A52" s="39" t="n"/>
-      <c r="B52" s="39" t="n"/>
-      <c r="C52" s="39" t="n"/>
-      <c r="D52" s="39" t="n"/>
-      <c r="E52" s="39" t="n"/>
-      <c r="F52" s="39" t="n"/>
-      <c r="G52" s="40" t="inlineStr">
+      <c r="A52" s="38" t="n"/>
+      <c r="B52" s="38" t="n"/>
+      <c r="C52" s="38" t="n"/>
+      <c r="D52" s="38" t="n"/>
+      <c r="E52" s="38" t="n"/>
+      <c r="F52" s="38" t="n"/>
+      <c r="G52" s="33" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="H52" s="41" t="inlineStr">
+      <c r="H52" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10137,7 +10137,7 @@
           </r>
         </is>
       </c>
-      <c r="I52" s="41" t="inlineStr">
+      <c r="I52" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10158,10 +10158,10 @@
           </r>
         </is>
       </c>
-      <c r="J52" s="42" t="n">
+      <c r="J52" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="K52" s="41" t="inlineStr">
+      <c r="K52" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10182,15 +10182,15 @@
           </r>
         </is>
       </c>
-      <c r="L52" s="43" t="n">
+      <c r="L52" s="46" t="n">
         <v>9</v>
       </c>
-      <c r="M52" s="44" t="inlineStr">
+      <c r="M52" s="36" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N52" s="41" t="inlineStr">
+      <c r="N52" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10211,14 +10211,90 @@
           </r>
         </is>
       </c>
-      <c r="O52" s="41" t="inlineStr"/>
-      <c r="P52" s="40" t="inlineStr"/>
-      <c r="Q52" s="40" t="inlineStr"/>
-      <c r="R52" s="45" t="inlineStr"/>
-      <c r="S52" s="45" t="inlineStr"/>
+      <c r="O52" s="34" t="inlineStr"/>
+      <c r="P52" s="33" t="inlineStr"/>
+      <c r="Q52" s="33" t="inlineStr"/>
+      <c r="R52" s="37" t="inlineStr"/>
+      <c r="S52" s="37" t="inlineStr"/>
     </row>
-    <row r="53" ht="235.5" customHeight="1">
-      <c r="A53" s="51" t="inlineStr">
+    <row r="53" ht="127.5" customHeight="1">
+      <c r="A53" s="39" t="n"/>
+      <c r="B53" s="39" t="n"/>
+      <c r="C53" s="39" t="n"/>
+      <c r="D53" s="39" t="n"/>
+      <c r="E53" s="39" t="n"/>
+      <c r="F53" s="39" t="n"/>
+      <c r="G53" s="40" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="H53" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The panda envelope passes STEERING_LKA torque that opposes the driver while the driver overrides: the Toyota LKA check covers magnitude, rate and measured-torque error only, and STEER_TORQUE_DRIVER is used only on the LTA path (toyota.h:298-310, 421-424; GAP-02). TSR-304 is not implemented in either build, so only the host 500-unit cut-off (C1, C2) stops the torque</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: SWF-087</t>
+          </r>
+        </is>
+      </c>
+      <c r="I53" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream design (a bounded torque the driver can overpower); TSR-304 decided (DQ-053) but not implemented</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   opendbc_repo/opendbc/safety/modes/toyota.h</t>
+          </r>
+        </is>
+      </c>
+      <c r="J53" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="K53" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• As rated in the SW FMEA (SWF-087.C1, D 10): test_toyota.py tests the measured-torque limit, not torque opposing the driver on the LKA path</t>
+          </r>
+        </is>
+      </c>
+      <c r="L53" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="M53" s="44" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N53" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10227,269 +10303,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">SFM-SE-001
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>LionDriver item (L2 ACC + ALC + driver monitoring)</t>
-          </r>
-        </is>
-      </c>
-      <c r="B53" s="51" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SFM-FN-004
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>F4 Driver override: release control on brake or cancel; yield lateral to steering input and longitudinal to accelerator</t>
-          </r>
-        </is>
-      </c>
-      <c r="C53" s="51" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Driver must use brake to disengage</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Next higher  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Item stays engaged</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Local  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>buttonCancel not raised</t>
-          </r>
-        </is>
-      </c>
-      <c r="D53" s="52" t="inlineStr">
-        <is>
-          <t>HZ-008</t>
-        </is>
-      </c>
-      <c r="E53" s="53" t="n">
-        <v>10</v>
-      </c>
-      <c r="F53" s="51" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SFM-019 · loss
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Cancel button does not disengage</t>
-          </r>
-        </is>
-      </c>
-      <c r="G53" s="40" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="H53" s="41" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Button message parsed wrong or missing</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-linked: SWF-057</t>
-          </r>
-        </is>
-      </c>
-      <c r="I53" s="41" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• Upstream opendbc Toyota port (DBC, carstate, carcontroller) with upstream review and route-based car tests; no LionDriver requirements; no field-exposure evidence for this configuration is credited</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   opendbc_repo/opendbc/car/toyota</t>
-          </r>
-        </is>
-      </c>
-      <c r="J53" s="42" t="n">
-        <v>6</v>
-      </c>
-      <c r="K53" s="41" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• As rated in the SW FMEA (SWF-057.C1, D 9 at BL-005): process_replay (CI) replays the TOYOTA3 Corolla TSS2 segment and compares with reference logs made from the same code, so it cannot find a defect already present at the baseline; not designed for this cause</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   openpilot/selfdrive/test/process_replay/test_processes.py</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• opendbc car tests check carState against the panda safety model on recorded routes (test_models); targeted at parse and pack consistency, not proven by fault injection, and run only where the route corpus is available</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   opendbc_repo/opendbc/car/tests/test_models.py</t>
-          </r>
-        </is>
-      </c>
-      <c r="L53" s="43" t="n">
-        <v>9</v>
-      </c>
-      <c r="M53" s="44" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="N53" s="41" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SFM-ACT-003 · detection
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+            <t xml:space="preserve">SFM-ACT-016 · monitoring
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Supervise driver override in the panda: driver steering torque above the override threshold limits or revokes lateral authority within the SG-05 0.2 s budget (TSR-304). Behaviour decided by the lead (DQ-053, option A): back off on override and show a cue. Requirements: TSR-304 (timing tied to the SG-05 budget) and TSR-628 (WP-S-02 §12.3a)</t>
           </r>
         </is>
       </c>
@@ -10565,7 +10388,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Driver cannot accelerate out of a situation (e.g. merging)</t>
+            <t>Driver must use brake to disengage</t>
           </r>
           <r>
             <rPr>
@@ -10591,7 +10414,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Item keeps braking while driver accelerates</t>
+            <t>Item stays engaged</t>
           </r>
           <r>
             <rPr>
@@ -10617,13 +10440,13 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>gasPressedOverride not detected</t>
+            <t>buttonCancel not raised</t>
           </r>
         </is>
       </c>
       <c r="D54" s="52" t="inlineStr">
         <is>
-          <t>HZ-006</t>
+          <t>HZ-008</t>
         </is>
       </c>
       <c r="E54" s="53" t="n">
@@ -10638,17 +10461,17 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">SFM-020 · loss
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Accelerator override not honored</t>
+            <t xml:space="preserve">SFM-019 · loss
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Cancel button does not disengage</t>
           </r>
         </is>
       </c>
@@ -10665,7 +10488,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>gasPressed parsed wrong or missing</t>
+            <t>Button message parsed wrong or missing</t>
           </r>
           <r>
             <rPr>
@@ -10789,8 +10612,8 @@
       <c r="R54" s="45" t="inlineStr"/>
       <c r="S54" s="45" t="inlineStr"/>
     </row>
-    <row r="55" ht="100.5" customHeight="1">
-      <c r="A55" s="30" t="inlineStr">
+    <row r="55" ht="235.5" customHeight="1">
+      <c r="A55" s="51" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10812,7 +10635,7 @@
           </r>
         </is>
       </c>
-      <c r="B55" s="30" t="inlineStr">
+      <c r="B55" s="51" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10834,7 +10657,7 @@
           </r>
         </is>
       </c>
-      <c r="C55" s="30" t="inlineStr">
+      <c r="C55" s="51" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10851,6 +10674,292 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
+            <t>Driver cannot accelerate out of a situation (e.g. merging)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Item keeps braking while driver accelerates</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>gasPressedOverride not detected</t>
+          </r>
+        </is>
+      </c>
+      <c r="D55" s="52" t="inlineStr">
+        <is>
+          <t>HZ-006</t>
+        </is>
+      </c>
+      <c r="E55" s="53" t="n">
+        <v>10</v>
+      </c>
+      <c r="F55" s="51" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-020 · loss
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Accelerator override not honored</t>
+          </r>
+        </is>
+      </c>
+      <c r="G55" s="40" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H55" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>gasPressed parsed wrong or missing</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: SWF-057</t>
+          </r>
+        </is>
+      </c>
+      <c r="I55" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream opendbc Toyota port (DBC, carstate, carcontroller) with upstream review and route-based car tests; no LionDriver requirements; no field-exposure evidence for this configuration is credited</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   opendbc_repo/opendbc/car/toyota</t>
+          </r>
+        </is>
+      </c>
+      <c r="J55" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="K55" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• As rated in the SW FMEA (SWF-057.C1, D 9 at BL-005): process_replay (CI) replays the TOYOTA3 Corolla TSS2 segment and compares with reference logs made from the same code, so it cannot find a defect already present at the baseline; not designed for this cause</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/test/process_replay/test_processes.py</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• opendbc car tests check carState against the panda safety model on recorded routes (test_models); targeted at parse and pack consistency, not proven by fault injection, and run only where the route corpus is available</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   opendbc_repo/opendbc/car/tests/test_models.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L55" s="43" t="n">
+        <v>9</v>
+      </c>
+      <c r="M55" s="44" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N55" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-ACT-003 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+          </r>
+        </is>
+      </c>
+      <c r="O55" s="48" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P55" s="40" t="inlineStr"/>
+      <c r="Q55" s="40" t="inlineStr"/>
+      <c r="R55" s="45" t="inlineStr"/>
+      <c r="S55" s="45" t="inlineStr"/>
+    </row>
+    <row r="56" ht="100.5" customHeight="1">
+      <c r="A56" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-SE-001
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>LionDriver item (L2 ACC + ALC + driver monitoring)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B56" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-FN-004
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>F4 Driver override: release control on brake or cancel; yield lateral to steering input and longitudinal to accelerator</t>
+          </r>
+        </is>
+      </c>
+      <c r="C56" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
             <t>Driver believes automation is off (mode confusion)</t>
           </r>
           <r>
@@ -10933,16 +11042,16 @@
           </r>
         </is>
       </c>
-      <c r="D55" s="31" t="inlineStr">
+      <c r="D56" s="31" t="inlineStr">
         <is>
           <t>HZ-012
 HZ-008</t>
         </is>
       </c>
-      <c r="E55" s="32" t="n">
+      <c r="E56" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="F55" s="30" t="inlineStr">
+      <c r="F56" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10965,12 +11074,12 @@
           </r>
         </is>
       </c>
-      <c r="G55" s="33" t="inlineStr">
+      <c r="G56" s="33" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H55" s="34" t="inlineStr">
+      <c r="H56" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10982,7 +11091,7 @@
           </r>
         </is>
       </c>
-      <c r="I55" s="34" t="inlineStr">
+      <c r="I56" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11003,10 +11112,10 @@
           </r>
         </is>
       </c>
-      <c r="J55" s="35" t="n">
+      <c r="J56" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="K55" s="34" t="inlineStr">
+      <c r="K56" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11027,15 +11136,15 @@
           </r>
         </is>
       </c>
-      <c r="L55" s="46" t="n">
+      <c r="L56" s="46" t="n">
         <v>9</v>
       </c>
-      <c r="M55" s="36" t="inlineStr">
+      <c r="M56" s="36" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N55" s="34" t="inlineStr">
+      <c r="N56" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11057,29 +11166,29 @@
           </r>
         </is>
       </c>
-      <c r="O55" s="54" t="inlineStr">
+      <c r="O56" s="54" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="P55" s="33" t="inlineStr"/>
-      <c r="Q55" s="33" t="inlineStr"/>
-      <c r="R55" s="37" t="inlineStr"/>
-      <c r="S55" s="37" t="inlineStr"/>
+      <c r="P56" s="33" t="inlineStr"/>
+      <c r="Q56" s="33" t="inlineStr"/>
+      <c r="R56" s="37" t="inlineStr"/>
+      <c r="S56" s="37" t="inlineStr"/>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" s="39" t="n"/>
-      <c r="B56" s="39" t="n"/>
-      <c r="C56" s="39" t="n"/>
-      <c r="D56" s="39" t="n"/>
-      <c r="E56" s="39" t="n"/>
-      <c r="F56" s="39" t="n"/>
-      <c r="G56" s="40" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" s="39" t="n"/>
+      <c r="B57" s="39" t="n"/>
+      <c r="C57" s="39" t="n"/>
+      <c r="D57" s="39" t="n"/>
+      <c r="E57" s="39" t="n"/>
+      <c r="F57" s="39" t="n"/>
+      <c r="G57" s="40" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="H56" s="41" t="inlineStr">
+      <c r="H57" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11091,7 +11200,7 @@
           </r>
         </is>
       </c>
-      <c r="I56" s="41" t="inlineStr">
+      <c r="I57" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11103,10 +11212,10 @@
           </r>
         </is>
       </c>
-      <c r="J56" s="42" t="n">
+      <c r="J57" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="K56" s="41" t="inlineStr">
+      <c r="K57" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11118,15 +11227,15 @@
           </r>
         </is>
       </c>
-      <c r="L56" s="43" t="n">
+      <c r="L57" s="43" t="n">
         <v>10</v>
       </c>
-      <c r="M56" s="44" t="inlineStr">
+      <c r="M57" s="44" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N56" s="41" t="inlineStr">
+      <c r="N57" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11148,18 +11257,18 @@
           </r>
         </is>
       </c>
-      <c r="O56" s="55" t="inlineStr">
+      <c r="O57" s="55" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="P56" s="40" t="inlineStr"/>
-      <c r="Q56" s="40" t="inlineStr"/>
-      <c r="R56" s="45" t="inlineStr"/>
-      <c r="S56" s="45" t="inlineStr"/>
+      <c r="P57" s="40" t="inlineStr"/>
+      <c r="Q57" s="40" t="inlineStr"/>
+      <c r="R57" s="45" t="inlineStr"/>
+      <c r="S57" s="45" t="inlineStr"/>
     </row>
-    <row r="57" ht="87" customHeight="1">
-      <c r="A57" s="30" t="inlineStr">
+    <row r="58" ht="87" customHeight="1">
+      <c r="A58" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11181,7 +11290,7 @@
           </r>
         </is>
       </c>
-      <c r="B57" s="30" t="inlineStr">
+      <c r="B58" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11203,7 +11312,7 @@
           </r>
         </is>
       </c>
-      <c r="C57" s="30" t="inlineStr">
+      <c r="C58" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11276,15 +11385,15 @@
           </r>
         </is>
       </c>
-      <c r="D57" s="31" t="inlineStr">
+      <c r="D58" s="31" t="inlineStr">
         <is>
           <t>HZ-013</t>
         </is>
       </c>
-      <c r="E57" s="32" t="n">
+      <c r="E58" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="F57" s="30" t="inlineStr">
+      <c r="F58" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11307,12 +11416,12 @@
           </r>
         </is>
       </c>
-      <c r="G57" s="33" t="inlineStr">
+      <c r="G58" s="33" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H57" s="34" t="inlineStr">
+      <c r="H58" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11324,7 +11433,7 @@
           </r>
         </is>
       </c>
-      <c r="I57" s="34" t="inlineStr">
+      <c r="I58" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11345,10 +11454,10 @@
           </r>
         </is>
       </c>
-      <c r="J57" s="35" t="n">
+      <c r="J58" s="35" t="n">
         <v>7</v>
       </c>
-      <c r="K57" s="34" t="inlineStr">
+      <c r="K58" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11360,152 +11469,8 @@
           </r>
         </is>
       </c>
-      <c r="L57" s="46" t="n">
+      <c r="L58" s="46" t="n">
         <v>10</v>
-      </c>
-      <c r="M57" s="36" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="N57" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SFM-ACT-009 · prevention
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Produce SOTIF / ISO PAS 8800 evidence for the neural-network elements (driving model, lead detection, driver monitoring model) per WP-V-02..04, including fault-induced inputs (corrupted or stale frames)</t>
-          </r>
-        </is>
-      </c>
-      <c r="O57" s="47" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="P57" s="33" t="inlineStr"/>
-      <c r="Q57" s="33" t="inlineStr"/>
-      <c r="R57" s="37" t="inlineStr"/>
-      <c r="S57" s="37" t="inlineStr"/>
-    </row>
-    <row r="58" ht="195" customHeight="1">
-      <c r="A58" s="38" t="n"/>
-      <c r="B58" s="38" t="n"/>
-      <c r="C58" s="38" t="n"/>
-      <c r="D58" s="38" t="n"/>
-      <c r="E58" s="38" t="n"/>
-      <c r="F58" s="38" t="n"/>
-      <c r="G58" s="33" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="H58" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Pose thresholds/calibration wrong for driver or mount</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-linked: SWF-061</t>
-          </r>
-        </is>
-      </c>
-      <c r="I58" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• Upstream openpilot code with upstream review; ruff and type checks in CI (static analysis job); unit tests are not requirements-based; no field-exposure evidence for this configuration, so none is credited (RT-1 §2.2)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   scripts/lint/lint.sh</t>
-          </r>
-        </is>
-      </c>
-      <c r="J58" s="35" t="n">
-        <v>6</v>
-      </c>
-      <c r="K58" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• As rated in the SW FMEA (SWF-061.C2, D 8 at BL-005): test_monitoring.py scenarios (distracted, invisible, uncertain, last-second responder) in CI; targeted at the policy, not proven by mutation</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   openpilot/selfdrive/monitoring/test_monitoring.py</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• Driver-monitoring policy unit tests (alert timing, awareness recovery, exemptions) on synthetic inputs; targeted, not proven by fault injection; the model itself is not tested</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   openpilot/selfdrive/monitoring/test_monitoring.py</t>
-          </r>
-        </is>
-      </c>
-      <c r="L58" s="35" t="n">
-        <v>8</v>
       </c>
       <c r="M58" s="36" t="inlineStr">
         <is>
@@ -11544,19 +11509,163 @@
       <c r="R58" s="37" t="inlineStr"/>
       <c r="S58" s="37" t="inlineStr"/>
     </row>
-    <row r="59" ht="141" customHeight="1">
-      <c r="A59" s="39" t="n"/>
-      <c r="B59" s="39" t="n"/>
-      <c r="C59" s="39" t="n"/>
-      <c r="D59" s="39" t="n"/>
-      <c r="E59" s="39" t="n"/>
-      <c r="F59" s="39" t="n"/>
-      <c r="G59" s="40" t="inlineStr">
+    <row r="59" ht="195" customHeight="1">
+      <c r="A59" s="38" t="n"/>
+      <c r="B59" s="38" t="n"/>
+      <c r="C59" s="38" t="n"/>
+      <c r="D59" s="38" t="n"/>
+      <c r="E59" s="38" t="n"/>
+      <c r="F59" s="38" t="n"/>
+      <c r="G59" s="33" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H59" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Pose thresholds/calibration wrong for driver or mount</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: SWF-061</t>
+          </r>
+        </is>
+      </c>
+      <c r="I59" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream openpilot code with upstream review; ruff and type checks in CI (static analysis job); unit tests are not requirements-based; no field-exposure evidence for this configuration, so none is credited (RT-1 §2.2)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   scripts/lint/lint.sh</t>
+          </r>
+        </is>
+      </c>
+      <c r="J59" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="K59" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• As rated in the SW FMEA (SWF-061.C2, D 8 at BL-005): test_monitoring.py scenarios (distracted, invisible, uncertain, last-second responder) in CI; targeted at the policy, not proven by mutation</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/monitoring/test_monitoring.py</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Driver-monitoring policy unit tests (alert timing, awareness recovery, exemptions) on synthetic inputs; targeted, not proven by fault injection; the model itself is not tested</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/monitoring/test_monitoring.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L59" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="M59" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N59" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-ACT-009 · prevention
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Produce SOTIF / ISO PAS 8800 evidence for the neural-network elements (driving model, lead detection, driver monitoring model) per WP-V-02..04, including fault-induced inputs (corrupted or stale frames)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O59" s="47" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P59" s="33" t="inlineStr"/>
+      <c r="Q59" s="33" t="inlineStr"/>
+      <c r="R59" s="37" t="inlineStr"/>
+      <c r="S59" s="37" t="inlineStr"/>
+    </row>
+    <row r="60" ht="141" customHeight="1">
+      <c r="A60" s="39" t="n"/>
+      <c r="B60" s="39" t="n"/>
+      <c r="C60" s="39" t="n"/>
+      <c r="D60" s="39" t="n"/>
+      <c r="E60" s="39" t="n"/>
+      <c r="F60" s="39" t="n"/>
+      <c r="G60" s="40" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="H59" s="41" t="inlineStr">
+      <c r="H60" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11568,7 +11677,7 @@
           </r>
         </is>
       </c>
-      <c r="I59" s="41" t="inlineStr">
+      <c r="I60" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11615,10 +11724,10 @@
           </r>
         </is>
       </c>
-      <c r="J59" s="42" t="n">
+      <c r="J60" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="K59" s="41" t="inlineStr">
+      <c r="K60" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11630,15 +11739,15 @@
           </r>
         </is>
       </c>
-      <c r="L59" s="43" t="n">
+      <c r="L60" s="43" t="n">
         <v>10</v>
       </c>
-      <c r="M59" s="44" t="inlineStr">
+      <c r="M60" s="44" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N59" s="41" t="inlineStr">
+      <c r="N60" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11660,18 +11769,18 @@
           </r>
         </is>
       </c>
-      <c r="O59" s="48" t="inlineStr">
+      <c r="O60" s="48" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P59" s="40" t="inlineStr"/>
-      <c r="Q59" s="40" t="inlineStr"/>
-      <c r="R59" s="45" t="inlineStr"/>
-      <c r="S59" s="45" t="inlineStr"/>
+      <c r="P60" s="40" t="inlineStr"/>
+      <c r="Q60" s="40" t="inlineStr"/>
+      <c r="R60" s="45" t="inlineStr"/>
+      <c r="S60" s="45" t="inlineStr"/>
     </row>
-    <row r="60" ht="195" customHeight="1">
-      <c r="A60" s="30" t="inlineStr">
+    <row r="61" ht="195" customHeight="1">
+      <c r="A61" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11693,7 +11802,7 @@
           </r>
         </is>
       </c>
-      <c r="B60" s="30" t="inlineStr">
+      <c r="B61" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11715,7 +11824,7 @@
           </r>
         </is>
       </c>
-      <c r="C60" s="30" t="inlineStr">
+      <c r="C61" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11788,15 +11897,15 @@
           </r>
         </is>
       </c>
-      <c r="D60" s="31" t="inlineStr">
+      <c r="D61" s="31" t="inlineStr">
         <is>
           <t>HZ-013</t>
         </is>
       </c>
-      <c r="E60" s="32" t="n">
+      <c r="E61" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="F60" s="30" t="inlineStr">
+      <c r="F61" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11819,12 +11928,12 @@
           </r>
         </is>
       </c>
-      <c r="G60" s="33" t="inlineStr">
+      <c r="G61" s="33" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H60" s="34" t="inlineStr">
+      <c r="H61" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11845,7 +11954,7 @@
           </r>
         </is>
       </c>
-      <c r="I60" s="34" t="inlineStr">
+      <c r="I61" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11866,10 +11975,10 @@
           </r>
         </is>
       </c>
-      <c r="J60" s="35" t="n">
+      <c r="J61" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="K60" s="34" t="inlineStr">
+      <c r="K61" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11916,15 +12025,15 @@
           </r>
         </is>
       </c>
-      <c r="L60" s="35" t="n">
+      <c r="L61" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="M60" s="36" t="inlineStr">
+      <c r="M61" s="36" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N60" s="34" t="inlineStr">
+      <c r="N61" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11946,29 +12055,29 @@
           </r>
         </is>
       </c>
-      <c r="O60" s="47" t="inlineStr">
+      <c r="O61" s="47" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P60" s="33" t="inlineStr"/>
-      <c r="Q60" s="33" t="inlineStr"/>
-      <c r="R60" s="37" t="inlineStr"/>
-      <c r="S60" s="37" t="inlineStr"/>
+      <c r="P61" s="33" t="inlineStr"/>
+      <c r="Q61" s="33" t="inlineStr"/>
+      <c r="R61" s="37" t="inlineStr"/>
+      <c r="S61" s="37" t="inlineStr"/>
     </row>
-    <row r="61" ht="181.5" customHeight="1">
-      <c r="A61" s="39" t="n"/>
-      <c r="B61" s="39" t="n"/>
-      <c r="C61" s="39" t="n"/>
-      <c r="D61" s="39" t="n"/>
-      <c r="E61" s="39" t="n"/>
-      <c r="F61" s="39" t="n"/>
-      <c r="G61" s="40" t="inlineStr">
+    <row r="62" ht="181.5" customHeight="1">
+      <c r="A62" s="39" t="n"/>
+      <c r="B62" s="39" t="n"/>
+      <c r="C62" s="39" t="n"/>
+      <c r="D62" s="39" t="n"/>
+      <c r="E62" s="39" t="n"/>
+      <c r="F62" s="39" t="n"/>
+      <c r="G62" s="40" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="H61" s="41" t="inlineStr">
+      <c r="H62" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11989,7 +12098,7 @@
           </r>
         </is>
       </c>
-      <c r="I61" s="41" t="inlineStr">
+      <c r="I62" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12010,10 +12119,10 @@
           </r>
         </is>
       </c>
-      <c r="J61" s="42" t="n">
+      <c r="J62" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="K61" s="41" t="inlineStr">
+      <c r="K62" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12060,15 +12169,15 @@
           </r>
         </is>
       </c>
-      <c r="L61" s="43" t="n">
+      <c r="L62" s="43" t="n">
         <v>9</v>
       </c>
-      <c r="M61" s="44" t="inlineStr">
+      <c r="M62" s="44" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N61" s="41" t="inlineStr">
+      <c r="N62" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12090,250 +12199,17 @@
           </r>
         </is>
       </c>
-      <c r="O61" s="48" t="inlineStr">
+      <c r="O62" s="48" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P61" s="40" t="inlineStr"/>
-      <c r="Q61" s="40" t="inlineStr"/>
-      <c r="R61" s="45" t="inlineStr"/>
-      <c r="S61" s="45" t="inlineStr"/>
-    </row>
-    <row r="62" ht="87" customHeight="1">
-      <c r="A62" s="51" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SFM-SE-001
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>LionDriver item (L2 ACC + ALC + driver monitoring)</t>
-          </r>
-        </is>
-      </c>
-      <c r="B62" s="51" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SFM-FN-005
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>F5 Driver monitoring: detect inattention and escalate alerts; lock out engagement after repeated non-response</t>
-          </r>
-        </is>
-      </c>
-      <c r="C62" s="51" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Driver annoyance; may reduce trust or prompt disabling DM in a fork</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Next higher  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Nuisance alerts; possible lockout</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Local  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Alerts raised for an attentive driver</t>
-          </r>
-        </is>
-      </c>
-      <c r="D62" s="52" t="inlineStr"/>
-      <c r="E62" s="53" t="n">
-        <v>4</v>
-      </c>
-      <c r="F62" s="51" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SFM-024 · unintended
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>False distraction alerts</t>
-          </r>
-        </is>
-      </c>
-      <c r="G62" s="40" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="H62" s="41" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>DM model false positive (sunglasses, lighting)</t>
-          </r>
-        </is>
-      </c>
-      <c r="I62" s="41" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• Upstream neural network trained and validated by comma.ai; no development or validation evidence is available to LionDriver (SOTIF / ISO PAS 8800 scope, WP-C-06)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   openpilot/selfdrive/modeld</t>
-          </r>
-        </is>
-      </c>
-      <c r="J62" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K62" s="41" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• No pre-release test targets this cause</t>
-          </r>
-        </is>
-      </c>
-      <c r="L62" s="43" t="n">
-        <v>10</v>
-      </c>
-      <c r="M62" s="56" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N62" s="41" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Rationale  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Nuisance only (S 4); tracked through driver feedback and SOTIF validation (SFM-ACT-009); no separate action</t>
-          </r>
-        </is>
-      </c>
-      <c r="O62" s="41" t="inlineStr"/>
       <c r="P62" s="40" t="inlineStr"/>
       <c r="Q62" s="40" t="inlineStr"/>
       <c r="R62" s="45" t="inlineStr"/>
       <c r="S62" s="45" t="inlineStr"/>
     </row>
-    <row r="63" ht="249" customHeight="1">
+    <row r="63" ht="87" customHeight="1">
       <c r="A63" s="51" t="inlineStr">
         <is>
           <r>
@@ -12395,7 +12271,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>No fallback if the driver is incapacitated</t>
+            <t>Driver annoyance; may reduce trust or prompt disabling DM in a fork</t>
           </r>
           <r>
             <rPr>
@@ -12421,7 +12297,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Vehicle continues under automation with an unresponsive driver</t>
+            <t>Nuisance alerts; possible lockout</t>
           </r>
           <r>
             <rPr>
@@ -12447,144 +12323,96 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Alert level three shows "DISENGAGE IMMEDIATELY" but the item stays engaged</t>
-          </r>
-        </is>
-      </c>
-      <c r="D63" s="52" t="inlineStr">
-        <is>
-          <t>HZ-013</t>
-        </is>
-      </c>
+            <t>Alerts raised for an attentive driver</t>
+          </r>
+        </is>
+      </c>
+      <c r="D63" s="52" t="inlineStr"/>
       <c r="E63" s="53" t="n">
+        <v>4</v>
+      </c>
+      <c r="F63" s="51" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-024 · unintended
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>False distraction alerts</t>
+          </r>
+        </is>
+      </c>
+      <c r="G63" s="40" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H63" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>DM model false positive (sunglasses, lighting)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I63" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream neural network trained and validated by comma.ai; no development or validation evidence is available to LionDriver (SOTIF / ISO PAS 8800 scope, WP-C-06)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/modeld</t>
+          </r>
+        </is>
+      </c>
+      <c r="J63" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K63" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No pre-release test targets this cause</t>
+          </r>
+        </is>
+      </c>
+      <c r="L63" s="43" t="n">
         <v>10</v>
       </c>
-      <c r="F63" s="51" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SFM-025 · insufficient
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Terminal driver-unresponsive state does not bring the item to a safe state</t>
-          </r>
-        </is>
-      </c>
-      <c r="G63" s="40" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="H63" s="41" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>driverDistracted3 / driverUnresponsive3 mapped only to ET.PERMANENT (no disable reaction)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-linked: SWF-062</t>
-          </r>
-        </is>
-      </c>
-      <c r="I63" s="41" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• Upstream openpilot code with upstream review; ruff and type checks in CI (static analysis job); unit tests are not requirements-based; no field-exposure evidence for this configuration, so none is credited (RT-1 §2.2)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   scripts/lint/lint.sh</t>
-          </r>
-        </is>
-      </c>
-      <c r="J63" s="42" t="n">
-        <v>8</v>
-      </c>
-      <c r="K63" s="41" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• As rated in the SW FMEA (SWF-062.C1, D 9 at BL-005): test_longitudinal runs the force_decel maneuver in CI and test_monitoring checks the alert levels; neither checks that the reaction meets FSR-040</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   openpilot/selfdrive/test/longitudinal_maneuvers/test_longitudinal.py</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• Present by design and known; no test, because no requirement says what the reaction should be</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   openpilot/selfdrive/selfdrived/events.py</t>
-          </r>
-        </is>
-      </c>
-      <c r="L63" s="43" t="n">
-        <v>9</v>
-      </c>
-      <c r="M63" s="44" t="inlineStr">
-        <is>
-          <t>H</t>
+      <c r="M63" s="56" t="inlineStr">
+        <is>
+          <t>M</t>
         </is>
       </c>
       <c r="N63" s="41" t="inlineStr">
@@ -12593,34 +12421,29 @@
             <rPr>
               <rFont val="Calibri"/>
               <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SFM-ACT-005 · design change
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Implement the reaction when driver awareness reaches zero (driverUnresponsive3 / driverDistracted3 have no disable reaction at BL-004 or BL-005), the safe state of SG-010 (WP-C-03 SG-08, ASIL A; DQ-205). Decided by the lead (DQ-365, option A, 2026-10-16) and specified in TSR-633 (WP-S-02 v0.26) with TSR-611; keep the lane and decelerate in lane to a standstill with the terminal alert sounding, hold the vehicle stopped, and lock out re-engagement and resumption until the driver responds. WP-S-04 v0.12 §3.8.4 gives a preliminary time to the reaction (18 s vision, 30 s wheel-touch from loss of attention; OI-11); SFM-025.C1 is re-rated once TSR-633 is implemented and that time is confirmed</t>
-          </r>
-        </is>
-      </c>
-      <c r="O63" s="48" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Rationale  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Nuisance only (S 4); tracked through driver feedback and SOTIF validation (SFM-ACT-009); no separate action</t>
+          </r>
+        </is>
+      </c>
+      <c r="O63" s="41" t="inlineStr"/>
       <c r="P63" s="40" t="inlineStr"/>
       <c r="Q63" s="40" t="inlineStr"/>
       <c r="R63" s="45" t="inlineStr"/>
       <c r="S63" s="45" t="inlineStr"/>
     </row>
-    <row r="64" ht="100.5" customHeight="1">
-      <c r="A64" s="30" t="inlineStr">
+    <row r="64" ht="249" customHeight="1">
+      <c r="A64" s="51" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12642,7 +12465,7 @@
           </r>
         </is>
       </c>
-      <c r="B64" s="30" t="inlineStr">
+      <c r="B64" s="51" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12651,6 +12474,292 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
+            <t xml:space="preserve">SFM-FN-005
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>F5 Driver monitoring: detect inattention and escalate alerts; lock out engagement after repeated non-response</t>
+          </r>
+        </is>
+      </c>
+      <c r="C64" s="51" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>No fallback if the driver is incapacitated</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Vehicle continues under automation with an unresponsive driver</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Alert level three shows "DISENGAGE IMMEDIATELY" but the item stays engaged</t>
+          </r>
+        </is>
+      </c>
+      <c r="D64" s="52" t="inlineStr">
+        <is>
+          <t>HZ-013</t>
+        </is>
+      </c>
+      <c r="E64" s="53" t="n">
+        <v>10</v>
+      </c>
+      <c r="F64" s="51" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-025 · insufficient
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Terminal driver-unresponsive state does not bring the item to a safe state</t>
+          </r>
+        </is>
+      </c>
+      <c r="G64" s="40" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H64" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>driverDistracted3 / driverUnresponsive3 mapped only to ET.PERMANENT (no disable reaction)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: SWF-062</t>
+          </r>
+        </is>
+      </c>
+      <c r="I64" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream openpilot code with upstream review; ruff and type checks in CI (static analysis job); unit tests are not requirements-based; no field-exposure evidence for this configuration, so none is credited (RT-1 §2.2)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   scripts/lint/lint.sh</t>
+          </r>
+        </is>
+      </c>
+      <c r="J64" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="K64" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• As rated in the SW FMEA (SWF-062.C1, D 9 at BL-005): test_longitudinal runs the force_decel maneuver in CI and test_monitoring checks the alert levels; neither checks that the reaction meets FSR-040</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/test/longitudinal_maneuvers/test_longitudinal.py</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Present by design and known; no test, because no requirement says what the reaction should be</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/selfdrived/events.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L64" s="43" t="n">
+        <v>9</v>
+      </c>
+      <c r="M64" s="44" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N64" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-ACT-005 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Implement the reaction when driver awareness reaches zero (driverUnresponsive3 / driverDistracted3 have no disable reaction at BL-004 or BL-005), the safe state of SG-010 (WP-C-03 SG-08, ASIL A; DQ-205). Decided by the lead (DQ-365, option A, 2026-10-16) and specified in TSR-633 (WP-S-02 v0.26) with TSR-611; keep the lane and decelerate in lane to a standstill with the terminal alert sounding, hold the vehicle stopped, and lock out re-engagement and resumption until the driver responds. WP-S-04 v0.12 §3.8.4 gives a preliminary time to the reaction (18 s vision, 30 s wheel-touch from loss of attention; OI-11); SFM-025.C1 is re-rated once TSR-633 is implemented and that time is confirmed</t>
+          </r>
+        </is>
+      </c>
+      <c r="O64" s="48" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P64" s="40" t="inlineStr"/>
+      <c r="Q64" s="40" t="inlineStr"/>
+      <c r="R64" s="45" t="inlineStr"/>
+      <c r="S64" s="45" t="inlineStr"/>
+    </row>
+    <row r="65" ht="100.5" customHeight="1">
+      <c r="A65" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-SE-001
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>LionDriver item (L2 ACC + ALC + driver monitoring)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B65" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
             <t xml:space="preserve">SFM-FN-006
 </t>
           </r>
@@ -12664,7 +12773,7 @@
           </r>
         </is>
       </c>
-      <c r="C64" s="30" t="inlineStr">
+      <c r="C65" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12789,17 +12898,17 @@
           </r>
         </is>
       </c>
-      <c r="D64" s="31" t="inlineStr">
+      <c r="D65" s="31" t="inlineStr">
         <is>
           <t>HZ-012
 HZ-006
 HZ-013</t>
         </is>
       </c>
-      <c r="E64" s="32" t="n">
+      <c r="E65" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="F64" s="30" t="inlineStr">
+      <c r="F65" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12822,12 +12931,12 @@
           </r>
         </is>
       </c>
-      <c r="G64" s="33" t="inlineStr">
+      <c r="G65" s="33" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H64" s="34" t="inlineStr">
+      <c r="H65" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12839,7 +12948,7 @@
           </r>
         </is>
       </c>
-      <c r="I64" s="34" t="inlineStr">
+      <c r="I65" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12860,132 +12969,6 @@
           </r>
         </is>
       </c>
-      <c r="J64" s="35" t="n">
-        <v>6</v>
-      </c>
-      <c r="K64" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• No pre-release test targets this cause</t>
-          </r>
-        </is>
-      </c>
-      <c r="L64" s="46" t="n">
-        <v>10</v>
-      </c>
-      <c r="M64" s="36" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="N64" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SFM-ACT-007 · design change
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Supervise the alert channels: treat loss of ui or soundd liveness, or a stale displayed state, as a fault that escalates (audible fallback, disengagement) instead of continuing silently</t>
-          </r>
-        </is>
-      </c>
-      <c r="O64" s="47" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="P64" s="33" t="inlineStr"/>
-      <c r="Q64" s="33" t="inlineStr"/>
-      <c r="R64" s="37" t="inlineStr"/>
-      <c r="S64" s="37" t="inlineStr"/>
-    </row>
-    <row r="65" ht="222" customHeight="1">
-      <c r="A65" s="38" t="n"/>
-      <c r="B65" s="38" t="n"/>
-      <c r="C65" s="38" t="n"/>
-      <c r="D65" s="38" t="n"/>
-      <c r="E65" s="38" t="n"/>
-      <c r="F65" s="38" t="n"/>
-      <c r="G65" s="33" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="H65" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>soundd failure or volume too low for cabin noise</t>
-          </r>
-        </is>
-      </c>
-      <c r="I65" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• Upstream openpilot code with upstream review; ruff and type checks in CI (static analysis job); unit tests are not requirements-based; no field-exposure evidence for this configuration, so none is credited (RT-1 §2.2)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   scripts/lint/lint.sh</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• soundd scales volume with ambient noise and plays alerts at a minimum level</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   openpilot/selfdrive/ui/soundd.py</t>
-          </r>
-        </is>
-      </c>
       <c r="J65" s="35" t="n">
         <v>6</v>
       </c>
@@ -12994,24 +12977,15 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• soundd unit test (alert sound selection and volume); targeted, not proven; audibility in the cabin not tested</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   openpilot/selfdrive/ui/tests/test_soundd.py</t>
-          </r>
-        </is>
-      </c>
-      <c r="L65" s="35" t="n">
-        <v>8</v>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No pre-release test targets this cause</t>
+          </r>
+        </is>
+      </c>
+      <c r="L65" s="46" t="n">
+        <v>10</v>
       </c>
       <c r="M65" s="36" t="inlineStr">
         <is>
@@ -13038,39 +13012,11 @@
             </rPr>
             <t>Supervise the alert channels: treat loss of ui or soundd liveness, or a stale displayed state, as a fault that escalates (audible fallback, disengagement) instead of continuing silently</t>
           </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SFM-ACT-003 · detection
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
-          </r>
         </is>
       </c>
       <c r="O65" s="47" t="inlineStr">
         <is>
-          <t>open
-open</t>
+          <t>open</t>
         </is>
       </c>
       <c r="P65" s="33" t="inlineStr"/>
@@ -13078,19 +13024,182 @@
       <c r="R65" s="37" t="inlineStr"/>
       <c r="S65" s="37" t="inlineStr"/>
     </row>
-    <row r="66" ht="87" customHeight="1">
-      <c r="A66" s="39" t="n"/>
-      <c r="B66" s="39" t="n"/>
-      <c r="C66" s="39" t="n"/>
-      <c r="D66" s="39" t="n"/>
-      <c r="E66" s="39" t="n"/>
-      <c r="F66" s="39" t="n"/>
-      <c r="G66" s="40" t="inlineStr">
+    <row r="66" ht="222" customHeight="1">
+      <c r="A66" s="38" t="n"/>
+      <c r="B66" s="38" t="n"/>
+      <c r="C66" s="38" t="n"/>
+      <c r="D66" s="38" t="n"/>
+      <c r="E66" s="38" t="n"/>
+      <c r="F66" s="38" t="n"/>
+      <c r="G66" s="33" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H66" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>soundd failure or volume too low for cabin noise</t>
+          </r>
+        </is>
+      </c>
+      <c r="I66" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream openpilot code with upstream review; ruff and type checks in CI (static analysis job); unit tests are not requirements-based; no field-exposure evidence for this configuration, so none is credited (RT-1 §2.2)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   scripts/lint/lint.sh</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• soundd scales volume with ambient noise and plays alerts at a minimum level</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/ui/soundd.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="J66" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="K66" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• soundd unit test (alert sound selection and volume); targeted, not proven; audibility in the cabin not tested</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/ui/tests/test_soundd.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L66" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="M66" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N66" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-ACT-007 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Supervise the alert channels: treat loss of ui or soundd liveness, or a stale displayed state, as a fault that escalates (audible fallback, disengagement) instead of continuing silently</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-ACT-003 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+          </r>
+        </is>
+      </c>
+      <c r="O66" s="47" t="inlineStr">
+        <is>
+          <t>open
+open</t>
+        </is>
+      </c>
+      <c r="P66" s="33" t="inlineStr"/>
+      <c r="Q66" s="33" t="inlineStr"/>
+      <c r="R66" s="37" t="inlineStr"/>
+      <c r="S66" s="37" t="inlineStr"/>
+    </row>
+    <row r="67" ht="87" customHeight="1">
+      <c r="A67" s="39" t="n"/>
+      <c r="B67" s="39" t="n"/>
+      <c r="C67" s="39" t="n"/>
+      <c r="D67" s="39" t="n"/>
+      <c r="E67" s="39" t="n"/>
+      <c r="F67" s="39" t="n"/>
+      <c r="G67" s="40" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="H66" s="41" t="inlineStr">
+      <c r="H67" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13102,7 +13211,7 @@
           </r>
         </is>
       </c>
-      <c r="I66" s="41" t="inlineStr">
+      <c r="I67" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13123,10 +13232,10 @@
           </r>
         </is>
       </c>
-      <c r="J66" s="42" t="n">
+      <c r="J67" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="K66" s="41" t="inlineStr">
+      <c r="K67" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13138,15 +13247,15 @@
           </r>
         </is>
       </c>
-      <c r="L66" s="43" t="n">
+      <c r="L67" s="43" t="n">
         <v>10</v>
       </c>
-      <c r="M66" s="44" t="inlineStr">
+      <c r="M67" s="44" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N66" s="41" t="inlineStr">
+      <c r="N67" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13168,18 +13277,18 @@
           </r>
         </is>
       </c>
-      <c r="O66" s="48" t="inlineStr">
+      <c r="O67" s="48" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P66" s="40" t="inlineStr"/>
-      <c r="Q66" s="40" t="inlineStr"/>
-      <c r="R66" s="45" t="inlineStr"/>
-      <c r="S66" s="45" t="inlineStr"/>
+      <c r="P67" s="40" t="inlineStr"/>
+      <c r="Q67" s="40" t="inlineStr"/>
+      <c r="R67" s="45" t="inlineStr"/>
+      <c r="S67" s="45" t="inlineStr"/>
     </row>
-    <row r="67" ht="141" customHeight="1">
-      <c r="A67" s="30" t="inlineStr">
+    <row r="68" ht="141" customHeight="1">
+      <c r="A68" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13201,7 +13310,7 @@
           </r>
         </is>
       </c>
-      <c r="B67" s="30" t="inlineStr">
+      <c r="B68" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13223,7 +13332,7 @@
           </r>
         </is>
       </c>
-      <c r="C67" s="30" t="inlineStr">
+      <c r="C68" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13322,16 +13431,16 @@
           </r>
         </is>
       </c>
-      <c r="D67" s="31" t="inlineStr">
+      <c r="D68" s="31" t="inlineStr">
         <is>
           <t>HZ-012
 HZ-013</t>
         </is>
       </c>
-      <c r="E67" s="32" t="n">
+      <c r="E68" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="F67" s="30" t="inlineStr">
+      <c r="F68" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13354,12 +13463,12 @@
           </r>
         </is>
       </c>
-      <c r="G67" s="33" t="inlineStr">
+      <c r="G68" s="33" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H67" s="34" t="inlineStr">
+      <c r="H68" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13371,7 +13480,7 @@
           </r>
         </is>
       </c>
-      <c r="I67" s="34" t="inlineStr">
+      <c r="I68" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13392,10 +13501,10 @@
           </r>
         </is>
       </c>
-      <c r="J67" s="35" t="n">
+      <c r="J68" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="K67" s="34" t="inlineStr">
+      <c r="K68" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13407,15 +13516,15 @@
           </r>
         </is>
       </c>
-      <c r="L67" s="46" t="n">
+      <c r="L68" s="46" t="n">
         <v>10</v>
       </c>
-      <c r="M67" s="36" t="inlineStr">
+      <c r="M68" s="36" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N67" s="34" t="inlineStr">
+      <c r="N68" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13437,29 +13546,29 @@
           </r>
         </is>
       </c>
-      <c r="O67" s="47" t="inlineStr">
+      <c r="O68" s="47" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P67" s="33" t="inlineStr"/>
-      <c r="Q67" s="33" t="inlineStr"/>
-      <c r="R67" s="37" t="inlineStr"/>
-      <c r="S67" s="37" t="inlineStr"/>
+      <c r="P68" s="33" t="inlineStr"/>
+      <c r="Q68" s="33" t="inlineStr"/>
+      <c r="R68" s="37" t="inlineStr"/>
+      <c r="S68" s="37" t="inlineStr"/>
     </row>
-    <row r="68" ht="87" customHeight="1">
-      <c r="A68" s="39" t="n"/>
-      <c r="B68" s="39" t="n"/>
-      <c r="C68" s="39" t="n"/>
-      <c r="D68" s="39" t="n"/>
-      <c r="E68" s="39" t="n"/>
-      <c r="F68" s="39" t="n"/>
-      <c r="G68" s="40" t="inlineStr">
+    <row r="69" ht="87" customHeight="1">
+      <c r="A69" s="39" t="n"/>
+      <c r="B69" s="39" t="n"/>
+      <c r="C69" s="39" t="n"/>
+      <c r="D69" s="39" t="n"/>
+      <c r="E69" s="39" t="n"/>
+      <c r="F69" s="39" t="n"/>
+      <c r="G69" s="40" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="H68" s="41" t="inlineStr">
+      <c r="H69" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13480,7 +13589,7 @@
           </r>
         </is>
       </c>
-      <c r="I68" s="41" t="inlineStr">
+      <c r="I69" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13501,10 +13610,10 @@
           </r>
         </is>
       </c>
-      <c r="J68" s="42" t="n">
+      <c r="J69" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="K68" s="41" t="inlineStr">
+      <c r="K69" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13525,15 +13634,15 @@
           </r>
         </is>
       </c>
-      <c r="L68" s="43" t="n">
+      <c r="L69" s="43" t="n">
         <v>9</v>
       </c>
-      <c r="M68" s="44" t="inlineStr">
+      <c r="M69" s="44" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N68" s="41" t="inlineStr">
+      <c r="N69" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13554,14 +13663,14 @@
           </r>
         </is>
       </c>
-      <c r="O68" s="41" t="inlineStr"/>
-      <c r="P68" s="40" t="inlineStr"/>
-      <c r="Q68" s="40" t="inlineStr"/>
-      <c r="R68" s="45" t="inlineStr"/>
-      <c r="S68" s="45" t="inlineStr"/>
+      <c r="O69" s="41" t="inlineStr"/>
+      <c r="P69" s="40" t="inlineStr"/>
+      <c r="Q69" s="40" t="inlineStr"/>
+      <c r="R69" s="45" t="inlineStr"/>
+      <c r="S69" s="45" t="inlineStr"/>
     </row>
-    <row r="69" ht="100.5" customHeight="1">
-      <c r="A69" s="30" t="inlineStr">
+    <row r="70" ht="100.5" customHeight="1">
+      <c r="A70" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13583,7 +13692,7 @@
           </r>
         </is>
       </c>
-      <c r="B69" s="30" t="inlineStr">
+      <c r="B70" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13605,7 +13714,7 @@
           </r>
         </is>
       </c>
-      <c r="C69" s="30" t="inlineStr">
+      <c r="C70" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13704,16 +13813,16 @@
           </r>
         </is>
       </c>
-      <c r="D69" s="31" t="inlineStr">
+      <c r="D70" s="31" t="inlineStr">
         <is>
           <t>HZ-012
 HZ-008</t>
         </is>
       </c>
-      <c r="E69" s="32" t="n">
+      <c r="E70" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="F69" s="30" t="inlineStr">
+      <c r="F70" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13736,12 +13845,12 @@
           </r>
         </is>
       </c>
-      <c r="G69" s="33" t="inlineStr">
+      <c r="G70" s="33" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H69" s="34" t="inlineStr">
+      <c r="H70" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13753,7 +13862,7 @@
           </r>
         </is>
       </c>
-      <c r="I69" s="34" t="inlineStr">
+      <c r="I70" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13774,10 +13883,10 @@
           </r>
         </is>
       </c>
-      <c r="J69" s="35" t="n">
+      <c r="J70" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="K69" s="34" t="inlineStr">
+      <c r="K70" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13789,15 +13898,15 @@
           </r>
         </is>
       </c>
-      <c r="L69" s="46" t="n">
+      <c r="L70" s="46" t="n">
         <v>10</v>
       </c>
-      <c r="M69" s="36" t="inlineStr">
+      <c r="M70" s="36" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N69" s="34" t="inlineStr">
+      <c r="N70" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13819,29 +13928,29 @@
           </r>
         </is>
       </c>
-      <c r="O69" s="47" t="inlineStr">
+      <c r="O70" s="47" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P69" s="33" t="inlineStr"/>
-      <c r="Q69" s="33" t="inlineStr"/>
-      <c r="R69" s="37" t="inlineStr"/>
-      <c r="S69" s="37" t="inlineStr"/>
+      <c r="P70" s="33" t="inlineStr"/>
+      <c r="Q70" s="33" t="inlineStr"/>
+      <c r="R70" s="37" t="inlineStr"/>
+      <c r="S70" s="37" t="inlineStr"/>
     </row>
-    <row r="70" ht="141" customHeight="1">
-      <c r="A70" s="39" t="n"/>
-      <c r="B70" s="39" t="n"/>
-      <c r="C70" s="39" t="n"/>
-      <c r="D70" s="39" t="n"/>
-      <c r="E70" s="39" t="n"/>
-      <c r="F70" s="39" t="n"/>
-      <c r="G70" s="40" t="inlineStr">
+    <row r="71" ht="141" customHeight="1">
+      <c r="A71" s="39" t="n"/>
+      <c r="B71" s="39" t="n"/>
+      <c r="C71" s="39" t="n"/>
+      <c r="D71" s="39" t="n"/>
+      <c r="E71" s="39" t="n"/>
+      <c r="F71" s="39" t="n"/>
+      <c r="G71" s="40" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="H70" s="41" t="inlineStr">
+      <c r="H71" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13853,7 +13962,7 @@
           </r>
         </is>
       </c>
-      <c r="I70" s="41" t="inlineStr">
+      <c r="I71" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13874,10 +13983,10 @@
           </r>
         </is>
       </c>
-      <c r="J70" s="42" t="n">
+      <c r="J71" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="K70" s="41" t="inlineStr">
+      <c r="K71" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13898,15 +14007,15 @@
           </r>
         </is>
       </c>
-      <c r="L70" s="43" t="n">
+      <c r="L71" s="43" t="n">
         <v>9</v>
       </c>
-      <c r="M70" s="44" t="inlineStr">
+      <c r="M71" s="44" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N70" s="41" t="inlineStr">
+      <c r="N71" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13928,18 +14037,18 @@
           </r>
         </is>
       </c>
-      <c r="O70" s="48" t="inlineStr">
+      <c r="O71" s="48" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P70" s="40" t="inlineStr"/>
-      <c r="Q70" s="40" t="inlineStr"/>
-      <c r="R70" s="45" t="inlineStr"/>
-      <c r="S70" s="45" t="inlineStr"/>
+      <c r="P71" s="40" t="inlineStr"/>
+      <c r="Q71" s="40" t="inlineStr"/>
+      <c r="R71" s="45" t="inlineStr"/>
+      <c r="S71" s="45" t="inlineStr"/>
     </row>
-    <row r="71" ht="114" customHeight="1">
-      <c r="A71" s="30" t="inlineStr">
+    <row r="72" ht="114" customHeight="1">
+      <c r="A72" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13961,7 +14070,7 @@
           </r>
         </is>
       </c>
-      <c r="B71" s="30" t="inlineStr">
+      <c r="B72" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13983,7 +14092,7 @@
           </r>
         </is>
       </c>
-      <c r="C71" s="30" t="inlineStr">
+      <c r="C72" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14108,17 +14217,17 @@
           </r>
         </is>
       </c>
-      <c r="D71" s="31" t="inlineStr">
+      <c r="D72" s="31" t="inlineStr">
         <is>
           <t>HZ-002
 HZ-005
 HZ-006</t>
         </is>
       </c>
-      <c r="E71" s="32" t="n">
+      <c r="E72" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="F71" s="30" t="inlineStr">
+      <c r="F72" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14141,12 +14250,12 @@
           </r>
         </is>
       </c>
-      <c r="G71" s="33" t="inlineStr">
+      <c r="G72" s="33" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H71" s="34" t="inlineStr">
+      <c r="H72" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14167,7 +14276,7 @@
           </r>
         </is>
       </c>
-      <c r="I71" s="34" t="inlineStr">
+      <c r="I72" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14188,10 +14297,10 @@
           </r>
         </is>
       </c>
-      <c r="J71" s="35" t="n">
+      <c r="J72" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="K71" s="34" t="inlineStr">
+      <c r="K72" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14212,15 +14321,15 @@
           </r>
         </is>
       </c>
-      <c r="L71" s="35" t="n">
+      <c r="L72" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="M71" s="57" t="inlineStr">
+      <c r="M72" s="57" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="N71" s="34" t="inlineStr">
+      <c r="N72" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14241,157 +14350,13 @@
           </r>
         </is>
       </c>
-      <c r="O71" s="34" t="inlineStr"/>
-      <c r="P71" s="33" t="inlineStr"/>
-      <c r="Q71" s="33" t="inlineStr"/>
-      <c r="R71" s="37" t="inlineStr"/>
-      <c r="S71" s="37" t="inlineStr"/>
-    </row>
-    <row r="72" ht="168" customHeight="1">
-      <c r="A72" s="38" t="n"/>
-      <c r="B72" s="38" t="n"/>
-      <c r="C72" s="38" t="n"/>
-      <c r="D72" s="38" t="n"/>
-      <c r="E72" s="38" t="n"/>
-      <c r="F72" s="38" t="n"/>
-      <c r="G72" s="33" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="H72" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Safety model limit defect in firmware</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-linked: SWF-001</t>
-          </r>
-        </is>
-      </c>
-      <c r="I72" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• Panda limits are copied from upstream vehicle tuning (same constants as the SoC side); no independent envelope derived from vehicle measurements (FSC FOI-001)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   opendbc_repo/opendbc/safety/modes/toyota.h</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• Panda safety code: MISRA C:2012, 100% line coverage, review; rated in the SW FMEA</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   assurance/08-analyses/fmea/analyses/sw-fmea.yaml</t>
-          </r>
-        </is>
-      </c>
-      <c r="J72" s="35" t="n">
-        <v>6</v>
-      </c>
-      <c r="K72" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• opendbc safety suite with 100% line coverage and mutation tests, run by CI on every change (proven, early, test-to-fail)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   opendbc_repo/opendbc/safety/tests/test_toyota.py</t>
-          </r>
-        </is>
-      </c>
-      <c r="L72" s="46" t="n">
-        <v>9</v>
-      </c>
-      <c r="M72" s="36" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="N72" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SFM-ACT-001 · design change
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Derive steering and acceleration envelopes from measurements on the reference vehicle and set the panda limits from them, independently of the SoC limits (same as SWF-ACT-003, FSC FOI-001)</t>
-          </r>
-        </is>
-      </c>
-      <c r="O72" s="47" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
+      <c r="O72" s="34" t="inlineStr"/>
       <c r="P72" s="33" t="inlineStr"/>
       <c r="Q72" s="33" t="inlineStr"/>
       <c r="R72" s="37" t="inlineStr"/>
       <c r="S72" s="37" t="inlineStr"/>
     </row>
-    <row r="73" ht="87" customHeight="1">
+    <row r="73" ht="168" customHeight="1">
       <c r="A73" s="38" t="n"/>
       <c r="B73" s="38" t="n"/>
       <c r="C73" s="38" t="n"/>
@@ -14400,7 +14365,7 @@
       <c r="F73" s="38" t="n"/>
       <c r="G73" s="33" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="H73" s="34" t="inlineStr">
@@ -14411,7 +14376,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Panda MCU hardware fault (see DFMEA/FMEDA)</t>
+            <t>Safety model limit defect in firmware</t>
           </r>
           <r>
             <rPr>
@@ -14420,7 +14385,7 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-linked: DFM-001</t>
+linked: SWF-001</t>
           </r>
         </is>
       </c>
@@ -14432,7 +14397,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Consumer-grade device hardware (comma 3X) without automotive qualification data available to LionDriver; rated in the DFMEA where a DFM row exists</t>
+            <t>• Panda limits are copied from upstream vehicle tuning (same constants as the SoC side); no independent envelope derived from vehicle measurements (FSC FOI-001)</t>
           </r>
           <r>
             <rPr>
@@ -14441,12 +14406,38 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   assurance/08-analyses/fmea/analyses/dfmea.yaml</t>
+   opendbc_repo/opendbc/safety/modes/toyota.h</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Panda safety code: MISRA C:2012, 100% line coverage, review; rated in the SW FMEA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/08-analyses/fmea/analyses/sw-fmea.yaml</t>
           </r>
         </is>
       </c>
       <c r="J73" s="35" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K73" s="34" t="inlineStr">
         <is>
@@ -14456,7 +14447,7 @@
               <color rgb="008A5A00"/>
               <sz val="10"/>
             </rPr>
-            <t>• As rated in the DFMEA: no pre-release test of this hardware fault</t>
+            <t>• opendbc safety suite with 100% line coverage and mutation tests, run by CI on every change (proven, early, test-to-fail)</t>
           </r>
           <r>
             <rPr>
@@ -14465,12 +14456,12 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   assurance/08-analyses/fmea/analyses/dfmea.yaml</t>
+   opendbc_repo/opendbc/safety/tests/test_toyota.py</t>
           </r>
         </is>
       </c>
       <c r="L73" s="46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M73" s="36" t="inlineStr">
         <is>
@@ -14483,52 +14474,66 @@
             <rPr>
               <rFont val="Calibri"/>
               <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Rationale  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Hardware fault rated in the DFMEA (DFM-001, FMEDA SG-001); this row inherits that rating</t>
-          </r>
-        </is>
-      </c>
-      <c r="O73" s="34" t="inlineStr"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-ACT-001 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Derive steering and acceleration envelopes from measurements on the reference vehicle and set the panda limits from them, independently of the SoC limits (same as SWF-ACT-003, FSC FOI-001)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O73" s="47" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
       <c r="P73" s="33" t="inlineStr"/>
       <c r="Q73" s="33" t="inlineStr"/>
       <c r="R73" s="37" t="inlineStr"/>
       <c r="S73" s="37" t="inlineStr"/>
     </row>
-    <row r="74" ht="168" customHeight="1">
-      <c r="A74" s="39" t="n"/>
-      <c r="B74" s="39" t="n"/>
-      <c r="C74" s="39" t="n"/>
-      <c r="D74" s="39" t="n"/>
-      <c r="E74" s="39" t="n"/>
-      <c r="F74" s="39" t="n"/>
-      <c r="G74" s="40" t="inlineStr">
-        <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="H74" s="41" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Harness allows the device to reach a bus without passing the panda filter</t>
-          </r>
-        </is>
-      </c>
-      <c r="I74" s="41" t="inlineStr">
+    <row r="74" ht="87" customHeight="1">
+      <c r="A74" s="38" t="n"/>
+      <c r="B74" s="38" t="n"/>
+      <c r="C74" s="38" t="n"/>
+      <c r="D74" s="38" t="n"/>
+      <c r="E74" s="38" t="n"/>
+      <c r="F74" s="38" t="n"/>
+      <c r="G74" s="33" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="H74" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Panda MCU hardware fault (see DFMEA/FMEDA)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: DFM-001</t>
+          </r>
+        </is>
+      </c>
+      <c r="I74" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14547,6 +14552,110 @@
             <t xml:space="preserve">
    assurance/08-analyses/fmea/analyses/dfmea.yaml</t>
           </r>
+        </is>
+      </c>
+      <c r="J74" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="K74" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• As rated in the DFMEA: no pre-release test of this hardware fault</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/08-analyses/fmea/analyses/dfmea.yaml</t>
+          </r>
+        </is>
+      </c>
+      <c r="L74" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="M74" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N74" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Rationale  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Hardware fault rated in the DFMEA (DFM-001, FMEDA SG-001); this row inherits that rating</t>
+          </r>
+        </is>
+      </c>
+      <c r="O74" s="34" t="inlineStr"/>
+      <c r="P74" s="33" t="inlineStr"/>
+      <c r="Q74" s="33" t="inlineStr"/>
+      <c r="R74" s="37" t="inlineStr"/>
+      <c r="S74" s="37" t="inlineStr"/>
+    </row>
+    <row r="75" ht="168" customHeight="1">
+      <c r="A75" s="39" t="n"/>
+      <c r="B75" s="39" t="n"/>
+      <c r="C75" s="39" t="n"/>
+      <c r="D75" s="39" t="n"/>
+      <c r="E75" s="39" t="n"/>
+      <c r="F75" s="39" t="n"/>
+      <c r="G75" s="40" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="H75" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Harness allows the device to reach a bus without passing the panda filter</t>
+          </r>
+        </is>
+      </c>
+      <c r="I75" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Consumer-grade device hardware (comma 3X) without automotive qualification data available to LionDriver; rated in the DFMEA where a DFM row exists</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/08-analyses/fmea/analyses/dfmea.yaml</t>
+          </r>
           <r>
             <rPr>
               <rFont val="Calibri"/>
@@ -14566,10 +14675,10 @@
           </r>
         </is>
       </c>
-      <c r="J74" s="42" t="n">
+      <c r="J75" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="K74" s="41" t="inlineStr">
+      <c r="K75" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14581,15 +14690,15 @@
           </r>
         </is>
       </c>
-      <c r="L74" s="43" t="n">
+      <c r="L75" s="43" t="n">
         <v>10</v>
       </c>
-      <c r="M74" s="44" t="inlineStr">
+      <c r="M75" s="44" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N74" s="41" t="inlineStr">
+      <c r="N75" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14610,14 +14719,14 @@
           </r>
         </is>
       </c>
-      <c r="O74" s="41" t="inlineStr"/>
-      <c r="P74" s="40" t="inlineStr"/>
-      <c r="Q74" s="40" t="inlineStr"/>
-      <c r="R74" s="45" t="inlineStr"/>
-      <c r="S74" s="45" t="inlineStr"/>
+      <c r="O75" s="41" t="inlineStr"/>
+      <c r="P75" s="40" t="inlineStr"/>
+      <c r="Q75" s="40" t="inlineStr"/>
+      <c r="R75" s="45" t="inlineStr"/>
+      <c r="S75" s="45" t="inlineStr"/>
     </row>
-    <row r="75" ht="100.5" customHeight="1">
-      <c r="A75" s="30" t="inlineStr">
+    <row r="76" ht="100.5" customHeight="1">
+      <c r="A76" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14639,7 +14748,7 @@
           </r>
         </is>
       </c>
-      <c r="B75" s="30" t="inlineStr">
+      <c r="B76" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14661,7 +14770,7 @@
           </r>
         </is>
       </c>
-      <c r="C75" s="30" t="inlineStr">
+      <c r="C76" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14786,17 +14895,17 @@
           </r>
         </is>
       </c>
-      <c r="D75" s="31" t="inlineStr">
+      <c r="D76" s="31" t="inlineStr">
         <is>
           <t>HZ-002
 HZ-005
 HZ-006</t>
         </is>
       </c>
-      <c r="E75" s="32" t="n">
+      <c r="E76" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="F75" s="30" t="inlineStr">
+      <c r="F76" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14819,12 +14928,12 @@
           </r>
         </is>
       </c>
-      <c r="G75" s="33" t="inlineStr">
+      <c r="G76" s="33" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H75" s="34" t="inlineStr">
+      <c r="H76" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14836,7 +14945,7 @@
           </r>
         </is>
       </c>
-      <c r="I75" s="34" t="inlineStr">
+      <c r="I76" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14857,10 +14966,10 @@
           </r>
         </is>
       </c>
-      <c r="J75" s="35" t="n">
+      <c r="J76" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="K75" s="34" t="inlineStr">
+      <c r="K76" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14881,15 +14990,15 @@
           </r>
         </is>
       </c>
-      <c r="L75" s="35" t="n">
+      <c r="L76" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="M75" s="36" t="inlineStr">
+      <c r="M76" s="36" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N75" s="34" t="inlineStr">
+      <c r="N76" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14911,29 +15020,29 @@
           </r>
         </is>
       </c>
-      <c r="O75" s="47" t="inlineStr">
+      <c r="O76" s="47" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P75" s="33" t="inlineStr"/>
-      <c r="Q75" s="33" t="inlineStr"/>
-      <c r="R75" s="37" t="inlineStr"/>
-      <c r="S75" s="37" t="inlineStr"/>
+      <c r="P76" s="33" t="inlineStr"/>
+      <c r="Q76" s="33" t="inlineStr"/>
+      <c r="R76" s="37" t="inlineStr"/>
+      <c r="S76" s="37" t="inlineStr"/>
     </row>
-    <row r="76" ht="73.5" customHeight="1">
-      <c r="A76" s="39" t="n"/>
-      <c r="B76" s="39" t="n"/>
-      <c r="C76" s="39" t="n"/>
-      <c r="D76" s="39" t="n"/>
-      <c r="E76" s="39" t="n"/>
-      <c r="F76" s="39" t="n"/>
-      <c r="G76" s="40" t="inlineStr">
+    <row r="77" ht="73.5" customHeight="1">
+      <c r="A77" s="39" t="n"/>
+      <c r="B77" s="39" t="n"/>
+      <c r="C77" s="39" t="n"/>
+      <c r="D77" s="39" t="n"/>
+      <c r="E77" s="39" t="n"/>
+      <c r="F77" s="39" t="n"/>
+      <c r="G77" s="40" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="H76" s="41" t="inlineStr">
+      <c r="H77" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14954,7 +15063,7 @@
           </r>
         </is>
       </c>
-      <c r="I76" s="41" t="inlineStr">
+      <c r="I77" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14975,10 +15084,10 @@
           </r>
         </is>
       </c>
-      <c r="J76" s="42" t="n">
+      <c r="J77" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="K76" s="41" t="inlineStr">
+      <c r="K77" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14987,239 +15096,6 @@
               <sz val="10"/>
             </rPr>
             <t>• No test targets this cause</t>
-          </r>
-        </is>
-      </c>
-      <c r="L76" s="43" t="n">
-        <v>10</v>
-      </c>
-      <c r="M76" s="44" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="N76" s="41" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Rationale  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Rated, and actioned, in the SW FMEA (SWF-037.C2, SWF-ACT-038); this row inherits that rating</t>
-          </r>
-        </is>
-      </c>
-      <c r="O76" s="41" t="inlineStr"/>
-      <c r="P76" s="40" t="inlineStr"/>
-      <c r="Q76" s="40" t="inlineStr"/>
-      <c r="R76" s="45" t="inlineStr"/>
-      <c r="S76" s="45" t="inlineStr"/>
-    </row>
-    <row r="77" ht="141" customHeight="1">
-      <c r="A77" s="51" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SFM-SE-001
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>LionDriver item (L2 ACC + ALC + driver monitoring)</t>
-          </r>
-        </is>
-      </c>
-      <c r="B77" s="51" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SFM-FN-007
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>F7 Actuation limiting: bound actuator commands in magnitude and rate; detect excessive actuation</t>
-          </r>
-        </is>
-      </c>
-      <c r="C77" s="51" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Unneeded handback to the driver</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Next higher  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Soft disable with alert</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Local  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>excessiveActuation raised without excessive motion</t>
-          </r>
-        </is>
-      </c>
-      <c r="D77" s="52" t="inlineStr"/>
-      <c r="E77" s="53" t="n">
-        <v>8</v>
-      </c>
-      <c r="F77" s="51" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SFM-031 · unintended
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>False excessive-actuation detection</t>
-          </r>
-        </is>
-      </c>
-      <c r="G77" s="40" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="H77" s="41" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>IMU noise or bad mounting</t>
-          </r>
-        </is>
-      </c>
-      <c r="I77" s="41" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• Consumer-grade device hardware (comma 3X) without automotive qualification data available to LionDriver; rated in the DFMEA where a DFM row exists</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   assurance/08-analyses/fmea/analyses/dfmea.yaml</t>
-          </r>
-        </is>
-      </c>
-      <c r="J77" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="K77" s="41" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• No pre-release test targets this cause</t>
           </r>
         </is>
       </c>
@@ -15237,33 +15113,28 @@
             <rPr>
               <rFont val="Calibri"/>
               <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SFM-ACT-003 · detection
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
-          </r>
-        </is>
-      </c>
-      <c r="O77" s="48" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Rationale  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Rated, and actioned, in the SW FMEA (SWF-037.C2, SWF-ACT-038); this row inherits that rating</t>
+          </r>
+        </is>
+      </c>
+      <c r="O77" s="41" t="inlineStr"/>
       <c r="P77" s="40" t="inlineStr"/>
       <c r="Q77" s="40" t="inlineStr"/>
       <c r="R77" s="45" t="inlineStr"/>
       <c r="S77" s="45" t="inlineStr"/>
     </row>
-    <row r="78" ht="181.5" customHeight="1">
+    <row r="78" ht="141" customHeight="1">
       <c r="A78" s="51" t="inlineStr">
         <is>
           <r>
@@ -15325,7 +15196,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Any F1/F2 effect; possible message conflicts with stock ECUs</t>
+            <t>Unneeded handback to the driver</t>
           </r>
           <r>
             <rPr>
@@ -15343,15 +15214,15 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Contributes to HZ-005: Unintended acceleration</t>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Soft disable with alert</t>
           </r>
           <r>
             <rPr>
@@ -15369,58 +15240,6 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Contributes to HZ-006: Unintended or excessive deceleration</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Next higher  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Wrong limits, scaling and message layout</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
             <t xml:space="preserve">Local  </t>
           </r>
           <r>
@@ -15429,21 +15248,99 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>CarParams, safety model and DBC for a different car</t>
-          </r>
-        </is>
-      </c>
-      <c r="D78" s="52" t="inlineStr">
-        <is>
-          <t>HZ-002
-HZ-005
-HZ-006</t>
-        </is>
-      </c>
+            <t>excessiveActuation raised without excessive motion</t>
+          </r>
+        </is>
+      </c>
+      <c r="D78" s="52" t="inlineStr"/>
       <c r="E78" s="53" t="n">
+        <v>8</v>
+      </c>
+      <c r="F78" s="51" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-031 · unintended
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>False excessive-actuation detection</t>
+          </r>
+        </is>
+      </c>
+      <c r="G78" s="40" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H78" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>IMU noise or bad mounting</t>
+          </r>
+        </is>
+      </c>
+      <c r="I78" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Consumer-grade device hardware (comma 3X) without automotive qualification data available to LionDriver; rated in the DFMEA where a DFM row exists</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/08-analyses/fmea/analyses/dfmea.yaml</t>
+          </r>
+        </is>
+      </c>
+      <c r="J78" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="K78" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No pre-release test targets this cause</t>
+          </r>
+        </is>
+      </c>
+      <c r="L78" s="43" t="n">
         <v>10</v>
       </c>
-      <c r="F78" s="51" t="inlineStr">
+      <c r="M78" s="44" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N78" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15452,167 +15349,22 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">SFM-032 · unintended
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Wrong vehicle configuration active (fingerprint or car port)</t>
-          </r>
-        </is>
-      </c>
-      <c r="G78" s="40" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="H78" s="41" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Fuzzy fingerprint matches a similar platform</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-linked: SWF-058</t>
-          </r>
-        </is>
-      </c>
-      <c r="I78" s="41" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• Upstream opendbc Toyota port (DBC, carstate, carcontroller) with upstream review and route-based car tests; no LionDriver requirements; no field-exposure evidence for this configuration is credited</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   opendbc_repo/opendbc/car/toyota</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• Exact FW-version fingerprint first, fuzzy fallback; controlsMismatch if the panda safety model or parameter differ from CarParams</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   opendbc_repo/opendbc/car/fw_versions.py</t>
-          </r>
-        </is>
-      </c>
-      <c r="J78" s="42" t="n">
-        <v>4</v>
-      </c>
-      <c r="K78" s="41" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• As rated in the SW FMEA (SWF-058.C1, D 9 at BL-005): opendbc test_fw_fingerprint exists but is not run by LionDriver CI</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• Fingerprinting unit tests (FW and CAN fingerprint); targeted, not proven by fault injection</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   opendbc_repo/opendbc/car/tests/test_fw_fingerprint.py</t>
-          </r>
-        </is>
-      </c>
-      <c r="L78" s="43" t="n">
-        <v>9</v>
-      </c>
-      <c r="M78" s="44" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="N78" s="41" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SFM-ACT-008 · design change
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Allow engagement only when the fingerprint, CarParams and panda safety parameter match the reference configuration AC-001 (refuse fuzzy matches in the reference build); see PFMEA PFM-013</t>
-          </r>
-        </is>
-      </c>
-      <c r="O78" s="50" t="inlineStr">
-        <is>
-          <t>in progress</t>
+            <t xml:space="preserve">SFM-ACT-003 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
+          </r>
+        </is>
+      </c>
+      <c r="O78" s="48" t="inlineStr">
+        <is>
+          <t>open</t>
         </is>
       </c>
       <c r="P78" s="40" t="inlineStr"/>
@@ -15620,8 +15372,8 @@
       <c r="R78" s="45" t="inlineStr"/>
       <c r="S78" s="45" t="inlineStr"/>
     </row>
-    <row r="79" ht="100.5" customHeight="1">
-      <c r="A79" s="30" t="inlineStr">
+    <row r="79" ht="181.5" customHeight="1">
+      <c r="A79" s="51" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15643,7 +15395,7 @@
           </r>
         </is>
       </c>
-      <c r="B79" s="30" t="inlineStr">
+      <c r="B79" s="51" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15652,6 +15404,363 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
+            <t xml:space="preserve">SFM-FN-007
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>F7 Actuation limiting: bound actuator commands in magnitude and rate; detect excessive actuation</t>
+          </r>
+        </is>
+      </c>
+      <c r="C79" s="51" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Any F1/F2 effect; possible message conflicts with stock ECUs</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-005: Unintended acceleration</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-006: Unintended or excessive deceleration</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Wrong limits, scaling and message layout</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>CarParams, safety model and DBC for a different car</t>
+          </r>
+        </is>
+      </c>
+      <c r="D79" s="52" t="inlineStr">
+        <is>
+          <t>HZ-002
+HZ-005
+HZ-006</t>
+        </is>
+      </c>
+      <c r="E79" s="53" t="n">
+        <v>10</v>
+      </c>
+      <c r="F79" s="51" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-032 · unintended
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Wrong vehicle configuration active (fingerprint or car port)</t>
+          </r>
+        </is>
+      </c>
+      <c r="G79" s="40" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H79" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Fuzzy fingerprint matches a similar platform</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: SWF-058</t>
+          </r>
+        </is>
+      </c>
+      <c r="I79" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream opendbc Toyota port (DBC, carstate, carcontroller) with upstream review and route-based car tests; no LionDriver requirements; no field-exposure evidence for this configuration is credited</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   opendbc_repo/opendbc/car/toyota</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Exact FW-version fingerprint first, fuzzy fallback; controlsMismatch if the panda safety model or parameter differ from CarParams</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   opendbc_repo/opendbc/car/fw_versions.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="J79" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="K79" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• As rated in the SW FMEA (SWF-058.C1, D 9 at BL-005): opendbc test_fw_fingerprint exists but is not run by LionDriver CI</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Fingerprinting unit tests (FW and CAN fingerprint); targeted, not proven by fault injection</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   opendbc_repo/opendbc/car/tests/test_fw_fingerprint.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L79" s="43" t="n">
+        <v>9</v>
+      </c>
+      <c r="M79" s="44" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N79" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-ACT-008 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Allow engagement only when the fingerprint, CarParams and panda safety parameter match the reference configuration AC-001 (refuse fuzzy matches in the reference build); see PFMEA PFM-013</t>
+          </r>
+        </is>
+      </c>
+      <c r="O79" s="50" t="inlineStr">
+        <is>
+          <t>in progress</t>
+        </is>
+      </c>
+      <c r="P79" s="40" t="inlineStr"/>
+      <c r="Q79" s="40" t="inlineStr"/>
+      <c r="R79" s="45" t="inlineStr"/>
+      <c r="S79" s="45" t="inlineStr"/>
+    </row>
+    <row r="80" ht="100.5" customHeight="1">
+      <c r="A80" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-SE-001
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>LionDriver item (L2 ACC + ALC + driver monitoring)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B80" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
             <t xml:space="preserve">SFM-FN-008
 </t>
           </r>
@@ -15665,7 +15774,7 @@
           </r>
         </is>
       </c>
-      <c r="C79" s="30" t="inlineStr">
+      <c r="C80" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15738,15 +15847,15 @@
           </r>
         </is>
       </c>
-      <c r="D79" s="31" t="inlineStr">
+      <c r="D80" s="31" t="inlineStr">
         <is>
           <t>HZ-011</t>
         </is>
       </c>
-      <c r="E79" s="32" t="n">
+      <c r="E80" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="F79" s="30" t="inlineStr">
+      <c r="F80" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15769,12 +15878,12 @@
           </r>
         </is>
       </c>
-      <c r="G79" s="33" t="inlineStr">
+      <c r="G80" s="33" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H79" s="34" t="inlineStr">
+      <c r="H80" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15786,7 +15895,7 @@
           </r>
         </is>
       </c>
-      <c r="I79" s="34" t="inlineStr">
+      <c r="I80" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15807,10 +15916,10 @@
           </r>
         </is>
       </c>
-      <c r="J79" s="35" t="n">
+      <c r="J80" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="K79" s="34" t="inlineStr">
+      <c r="K80" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15822,126 +15931,8 @@
           </r>
         </is>
       </c>
-      <c r="L79" s="46" t="n">
+      <c r="L80" s="46" t="n">
         <v>10</v>
-      </c>
-      <c r="M79" s="36" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="N79" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SFM-ACT-006 · detection
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Establish on the reference car which stock TSS2 functions (PCS/AEB, FCW) remain available with LionDriver installed and longitudinal control enabled, and verify the stock pre-collision path after installation (PFMEA PFM-014)</t>
-          </r>
-        </is>
-      </c>
-      <c r="O79" s="47" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="P79" s="33" t="inlineStr"/>
-      <c r="Q79" s="33" t="inlineStr"/>
-      <c r="R79" s="37" t="inlineStr"/>
-      <c r="S79" s="37" t="inlineStr"/>
-    </row>
-    <row r="80" ht="100.5" customHeight="1">
-      <c r="A80" s="38" t="n"/>
-      <c r="B80" s="38" t="n"/>
-      <c r="C80" s="38" t="n"/>
-      <c r="D80" s="38" t="n"/>
-      <c r="E80" s="38" t="n"/>
-      <c r="F80" s="38" t="n"/>
-      <c r="G80" s="33" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="H80" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Item does not forward or reproduce stock safety messages</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-linked: SWF-011</t>
-          </r>
-        </is>
-      </c>
-      <c r="I80" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• Panda safety code: MISRA C:2012, 100% line coverage, review; rated in the SW FMEA</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   assurance/08-analyses/fmea/analyses/sw-fmea.yaml</t>
-          </r>
-        </is>
-      </c>
-      <c r="J80" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="K80" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• opendbc safety suite with 100% line coverage and mutation tests, run by CI on every change (proven, early, test-to-fail)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   opendbc_repo/opendbc/safety/tests/test_toyota.py</t>
-          </r>
-        </is>
-      </c>
-      <c r="L80" s="35" t="n">
-        <v>3</v>
       </c>
       <c r="M80" s="36" t="inlineStr">
         <is>
@@ -15980,19 +15971,137 @@
       <c r="R80" s="37" t="inlineStr"/>
       <c r="S80" s="37" t="inlineStr"/>
     </row>
-    <row r="81" ht="141" customHeight="1">
-      <c r="A81" s="39" t="n"/>
-      <c r="B81" s="39" t="n"/>
-      <c r="C81" s="39" t="n"/>
-      <c r="D81" s="39" t="n"/>
-      <c r="E81" s="39" t="n"/>
-      <c r="F81" s="39" t="n"/>
-      <c r="G81" s="40" t="inlineStr">
+    <row r="81" ht="100.5" customHeight="1">
+      <c r="A81" s="38" t="n"/>
+      <c r="B81" s="38" t="n"/>
+      <c r="C81" s="38" t="n"/>
+      <c r="D81" s="38" t="n"/>
+      <c r="E81" s="38" t="n"/>
+      <c r="F81" s="38" t="n"/>
+      <c r="G81" s="33" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H81" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Item does not forward or reproduce stock safety messages</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: SWF-011</t>
+          </r>
+        </is>
+      </c>
+      <c r="I81" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Panda safety code: MISRA C:2012, 100% line coverage, review; rated in the SW FMEA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/08-analyses/fmea/analyses/sw-fmea.yaml</t>
+          </r>
+        </is>
+      </c>
+      <c r="J81" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K81" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• opendbc safety suite with 100% line coverage and mutation tests, run by CI on every change (proven, early, test-to-fail)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   opendbc_repo/opendbc/safety/tests/test_toyota.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L81" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="M81" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N81" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-ACT-006 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Establish on the reference car which stock TSS2 functions (PCS/AEB, FCW) remain available with LionDriver installed and longitudinal control enabled, and verify the stock pre-collision path after installation (PFMEA PFM-014)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O81" s="47" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P81" s="33" t="inlineStr"/>
+      <c r="Q81" s="33" t="inlineStr"/>
+      <c r="R81" s="37" t="inlineStr"/>
+      <c r="S81" s="37" t="inlineStr"/>
+    </row>
+    <row r="82" ht="141" customHeight="1">
+      <c r="A82" s="39" t="n"/>
+      <c r="B82" s="39" t="n"/>
+      <c r="C82" s="39" t="n"/>
+      <c r="D82" s="39" t="n"/>
+      <c r="E82" s="39" t="n"/>
+      <c r="F82" s="39" t="n"/>
+      <c r="G82" s="40" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="H81" s="41" t="inlineStr">
+      <c r="H82" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16013,7 +16122,7 @@
           </r>
         </is>
       </c>
-      <c r="I81" s="41" t="inlineStr">
+      <c r="I82" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16034,10 +16143,10 @@
           </r>
         </is>
       </c>
-      <c r="J81" s="42" t="n">
+      <c r="J82" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="K81" s="41" t="inlineStr">
+      <c r="K82" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16058,15 +16167,15 @@
           </r>
         </is>
       </c>
-      <c r="L81" s="43" t="n">
+      <c r="L82" s="43" t="n">
         <v>10</v>
       </c>
-      <c r="M81" s="44" t="inlineStr">
+      <c r="M82" s="44" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N81" s="41" t="inlineStr">
+      <c r="N82" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16088,18 +16197,18 @@
           </r>
         </is>
       </c>
-      <c r="O81" s="48" t="inlineStr">
+      <c r="O82" s="48" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P81" s="40" t="inlineStr"/>
-      <c r="Q81" s="40" t="inlineStr"/>
-      <c r="R81" s="45" t="inlineStr"/>
-      <c r="S81" s="45" t="inlineStr"/>
+      <c r="P82" s="40" t="inlineStr"/>
+      <c r="Q82" s="40" t="inlineStr"/>
+      <c r="R82" s="45" t="inlineStr"/>
+      <c r="S82" s="45" t="inlineStr"/>
     </row>
-    <row r="82" ht="87" customHeight="1">
-      <c r="A82" s="30" t="inlineStr">
+    <row r="83" ht="87" customHeight="1">
+      <c r="A83" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16121,7 +16230,7 @@
           </r>
         </is>
       </c>
-      <c r="B82" s="30" t="inlineStr">
+      <c r="B83" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16143,7 +16252,7 @@
           </r>
         </is>
       </c>
-      <c r="C82" s="30" t="inlineStr">
+      <c r="C83" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16294,7 +16403,7 @@
           </r>
         </is>
       </c>
-      <c r="D82" s="31" t="inlineStr">
+      <c r="D83" s="31" t="inlineStr">
         <is>
           <t>HZ-011
 HZ-002
@@ -16302,10 +16411,10 @@
 HZ-005</t>
         </is>
       </c>
-      <c r="E82" s="32" t="n">
+      <c r="E83" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="F82" s="30" t="inlineStr">
+      <c r="F83" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16328,12 +16437,12 @@
           </r>
         </is>
       </c>
-      <c r="G82" s="33" t="inlineStr">
+      <c r="G83" s="33" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H82" s="34" t="inlineStr">
+      <c r="H83" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16354,7 +16463,7 @@
           </r>
         </is>
       </c>
-      <c r="I82" s="34" t="inlineStr">
+      <c r="I83" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16375,10 +16484,10 @@
           </r>
         </is>
       </c>
-      <c r="J82" s="35" t="n">
+      <c r="J83" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="K82" s="34" t="inlineStr">
+      <c r="K83" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16399,15 +16508,15 @@
           </r>
         </is>
       </c>
-      <c r="L82" s="46" t="n">
+      <c r="L83" s="46" t="n">
         <v>10</v>
       </c>
-      <c r="M82" s="36" t="inlineStr">
+      <c r="M83" s="36" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N82" s="34" t="inlineStr">
+      <c r="N83" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16428,25 +16537,25 @@
           </r>
         </is>
       </c>
-      <c r="O82" s="34" t="inlineStr"/>
-      <c r="P82" s="33" t="inlineStr"/>
-      <c r="Q82" s="33" t="inlineStr"/>
-      <c r="R82" s="37" t="inlineStr"/>
-      <c r="S82" s="37" t="inlineStr"/>
+      <c r="O83" s="34" t="inlineStr"/>
+      <c r="P83" s="33" t="inlineStr"/>
+      <c r="Q83" s="33" t="inlineStr"/>
+      <c r="R83" s="37" t="inlineStr"/>
+      <c r="S83" s="37" t="inlineStr"/>
     </row>
-    <row r="83" ht="142.5" customHeight="1">
-      <c r="A83" s="39" t="n"/>
-      <c r="B83" s="39" t="n"/>
-      <c r="C83" s="39" t="n"/>
-      <c r="D83" s="39" t="n"/>
-      <c r="E83" s="39" t="n"/>
-      <c r="F83" s="39" t="n"/>
-      <c r="G83" s="40" t="inlineStr">
+    <row r="84" ht="142.5" customHeight="1">
+      <c r="A84" s="39" t="n"/>
+      <c r="B84" s="39" t="n"/>
+      <c r="C84" s="39" t="n"/>
+      <c r="D84" s="39" t="n"/>
+      <c r="E84" s="39" t="n"/>
+      <c r="F84" s="39" t="n"/>
+      <c r="G84" s="40" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="H83" s="41" t="inlineStr">
+      <c r="H84" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16467,7 +16576,7 @@
           </r>
         </is>
       </c>
-      <c r="I83" s="41" t="inlineStr">
+      <c r="I84" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16488,10 +16597,10 @@
           </r>
         </is>
       </c>
-      <c r="J83" s="42" t="n">
+      <c r="J84" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="K83" s="41" t="inlineStr">
+      <c r="K84" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16512,15 +16621,15 @@
           </r>
         </is>
       </c>
-      <c r="L83" s="43" t="n">
+      <c r="L84" s="43" t="n">
         <v>9</v>
       </c>
-      <c r="M83" s="44" t="inlineStr">
+      <c r="M84" s="44" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N83" s="41" t="inlineStr">
+      <c r="N84" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16541,14 +16650,14 @@
           </r>
         </is>
       </c>
-      <c r="O83" s="41" t="inlineStr"/>
-      <c r="P83" s="40" t="inlineStr"/>
-      <c r="Q83" s="40" t="inlineStr"/>
-      <c r="R83" s="45" t="inlineStr"/>
-      <c r="S83" s="45" t="inlineStr"/>
+      <c r="O84" s="41" t="inlineStr"/>
+      <c r="P84" s="40" t="inlineStr"/>
+      <c r="Q84" s="40" t="inlineStr"/>
+      <c r="R84" s="45" t="inlineStr"/>
+      <c r="S84" s="45" t="inlineStr"/>
     </row>
-    <row r="84" ht="100.5" customHeight="1">
-      <c r="A84" s="30" t="inlineStr">
+    <row r="85" ht="100.5" customHeight="1">
+      <c r="A85" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16570,7 +16679,7 @@
           </r>
         </is>
       </c>
-      <c r="B84" s="30" t="inlineStr">
+      <c r="B85" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16592,7 +16701,7 @@
           </r>
         </is>
       </c>
-      <c r="C84" s="30" t="inlineStr">
+      <c r="C85" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16691,16 +16800,16 @@
           </r>
         </is>
       </c>
-      <c r="D84" s="31" t="inlineStr">
+      <c r="D85" s="31" t="inlineStr">
         <is>
           <t>HZ-011
 HZ-006</t>
         </is>
       </c>
-      <c r="E84" s="32" t="n">
+      <c r="E85" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="F84" s="30" t="inlineStr">
+      <c r="F85" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16723,12 +16832,12 @@
           </r>
         </is>
       </c>
-      <c r="G84" s="33" t="inlineStr">
+      <c r="G85" s="33" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H84" s="34" t="inlineStr">
+      <c r="H85" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16740,7 +16849,7 @@
           </r>
         </is>
       </c>
-      <c r="I84" s="34" t="inlineStr">
+      <c r="I85" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16761,10 +16870,10 @@
           </r>
         </is>
       </c>
-      <c r="J84" s="35" t="n">
+      <c r="J85" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="K84" s="34" t="inlineStr">
+      <c r="K85" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16785,15 +16894,15 @@
           </r>
         </is>
       </c>
-      <c r="L84" s="46" t="n">
+      <c r="L85" s="46" t="n">
         <v>9</v>
       </c>
-      <c r="M84" s="36" t="inlineStr">
+      <c r="M85" s="36" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N84" s="34" t="inlineStr">
+      <c r="N85" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16814,25 +16923,25 @@
           </r>
         </is>
       </c>
-      <c r="O84" s="34" t="inlineStr"/>
-      <c r="P84" s="33" t="inlineStr"/>
-      <c r="Q84" s="33" t="inlineStr"/>
-      <c r="R84" s="37" t="inlineStr"/>
-      <c r="S84" s="37" t="inlineStr"/>
+      <c r="O85" s="34" t="inlineStr"/>
+      <c r="P85" s="33" t="inlineStr"/>
+      <c r="Q85" s="33" t="inlineStr"/>
+      <c r="R85" s="37" t="inlineStr"/>
+      <c r="S85" s="37" t="inlineStr"/>
     </row>
-    <row r="85" ht="100.5" customHeight="1">
-      <c r="A85" s="39" t="n"/>
-      <c r="B85" s="39" t="n"/>
-      <c r="C85" s="39" t="n"/>
-      <c r="D85" s="39" t="n"/>
-      <c r="E85" s="39" t="n"/>
-      <c r="F85" s="39" t="n"/>
-      <c r="G85" s="40" t="inlineStr">
+    <row r="86" ht="100.5" customHeight="1">
+      <c r="A86" s="39" t="n"/>
+      <c r="B86" s="39" t="n"/>
+      <c r="C86" s="39" t="n"/>
+      <c r="D86" s="39" t="n"/>
+      <c r="E86" s="39" t="n"/>
+      <c r="F86" s="39" t="n"/>
+      <c r="G86" s="40" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="H85" s="41" t="inlineStr">
+      <c r="H86" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16844,7 +16953,7 @@
           </r>
         </is>
       </c>
-      <c r="I85" s="41" t="inlineStr">
+      <c r="I86" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16865,10 +16974,10 @@
           </r>
         </is>
       </c>
-      <c r="J85" s="42" t="n">
+      <c r="J86" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="K85" s="41" t="inlineStr">
+      <c r="K86" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16889,15 +16998,15 @@
           </r>
         </is>
       </c>
-      <c r="L85" s="42" t="n">
+      <c r="L86" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="M85" s="44" t="inlineStr">
+      <c r="M86" s="44" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N85" s="41" t="inlineStr">
+      <c r="N86" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16918,14 +17027,14 @@
           </r>
         </is>
       </c>
-      <c r="O85" s="41" t="inlineStr"/>
-      <c r="P85" s="40" t="inlineStr"/>
-      <c r="Q85" s="40" t="inlineStr"/>
-      <c r="R85" s="45" t="inlineStr"/>
-      <c r="S85" s="45" t="inlineStr"/>
+      <c r="O86" s="41" t="inlineStr"/>
+      <c r="P86" s="40" t="inlineStr"/>
+      <c r="Q86" s="40" t="inlineStr"/>
+      <c r="R86" s="45" t="inlineStr"/>
+      <c r="S86" s="45" t="inlineStr"/>
     </row>
-    <row r="86" ht="127.5" customHeight="1">
-      <c r="A86" s="30" t="inlineStr">
+    <row r="87" ht="127.5" customHeight="1">
+      <c r="A87" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16947,7 +17056,7 @@
           </r>
         </is>
       </c>
-      <c r="B86" s="30" t="inlineStr">
+      <c r="B87" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16969,7 +17078,7 @@
           </r>
         </is>
       </c>
-      <c r="C86" s="30" t="inlineStr">
+      <c r="C87" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17042,15 +17151,15 @@
           </r>
         </is>
       </c>
-      <c r="D86" s="31" t="inlineStr">
+      <c r="D87" s="31" t="inlineStr">
         <is>
           <t>HZ-011</t>
         </is>
       </c>
-      <c r="E86" s="32" t="n">
+      <c r="E87" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="F86" s="30" t="inlineStr">
+      <c r="F87" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17073,12 +17182,12 @@
           </r>
         </is>
       </c>
-      <c r="G86" s="33" t="inlineStr">
+      <c r="G87" s="33" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H86" s="34" t="inlineStr">
+      <c r="H87" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17090,7 +17199,7 @@
           </r>
         </is>
       </c>
-      <c r="I86" s="34" t="inlineStr">
+      <c r="I87" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17111,10 +17220,10 @@
           </r>
         </is>
       </c>
-      <c r="J86" s="35" t="n">
+      <c r="J87" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="K86" s="34" t="inlineStr">
+      <c r="K87" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17126,15 +17235,15 @@
           </r>
         </is>
       </c>
-      <c r="L86" s="46" t="n">
+      <c r="L87" s="46" t="n">
         <v>10</v>
       </c>
-      <c r="M86" s="36" t="inlineStr">
+      <c r="M87" s="36" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N86" s="34" t="inlineStr">
+      <c r="N87" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17156,109 +17265,76 @@
           </r>
         </is>
       </c>
-      <c r="O86" s="58" t="inlineStr">
+      <c r="O87" s="58" t="inlineStr">
         <is>
           <t>decision pending</t>
         </is>
       </c>
-      <c r="P86" s="33" t="inlineStr"/>
-      <c r="Q86" s="33" t="inlineStr"/>
-      <c r="R86" s="37" t="inlineStr"/>
-      <c r="S86" s="37" t="inlineStr"/>
-    </row>
-    <row r="87" ht="100.5" customHeight="1">
-      <c r="A87" s="39" t="n"/>
-      <c r="B87" s="39" t="n"/>
-      <c r="C87" s="39" t="n"/>
-      <c r="D87" s="39" t="n"/>
-      <c r="E87" s="39" t="n"/>
-      <c r="F87" s="39" t="n"/>
-      <c r="G87" s="40" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="H87" s="41" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>The PCM does not give stock PCS braking priority over the item's ACC_CONTROL request (AOU-04R not met)</t>
-          </r>
-        </is>
-      </c>
-      <c r="I87" s="41" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• Series-production Toyota ECU; PCS priority over 0x343 assumed (AOU-04R), not verified by LionDriver</t>
-          </r>
-        </is>
-      </c>
-      <c r="J87" s="42" t="n">
-        <v>3</v>
-      </c>
-      <c r="K87" s="41" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• No pre-release test targets this cause; AOU-04R needs a message review and a PCS target test (WP-C-04)</t>
-          </r>
-        </is>
-      </c>
-      <c r="L87" s="43" t="n">
-        <v>10</v>
-      </c>
-      <c r="M87" s="44" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="N87" s="41" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SFM-ACT-006 · detection
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Establish on the reference car which stock TSS2 functions (PCS/AEB, FCW) remain available with LionDriver installed and longitudinal control enabled, and verify the stock pre-collision path after installation (PFMEA PFM-014)</t>
-          </r>
-        </is>
-      </c>
-      <c r="O87" s="48" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="P87" s="40" t="inlineStr"/>
-      <c r="Q87" s="40" t="inlineStr"/>
-      <c r="R87" s="45" t="inlineStr"/>
-      <c r="S87" s="45" t="inlineStr"/>
+      <c r="P87" s="33" t="inlineStr"/>
+      <c r="Q87" s="33" t="inlineStr"/>
+      <c r="R87" s="37" t="inlineStr"/>
+      <c r="S87" s="37" t="inlineStr"/>
     </row>
     <row r="88" ht="100.5" customHeight="1">
-      <c r="A88" s="30" t="inlineStr">
+      <c r="A88" s="39" t="n"/>
+      <c r="B88" s="39" t="n"/>
+      <c r="C88" s="39" t="n"/>
+      <c r="D88" s="39" t="n"/>
+      <c r="E88" s="39" t="n"/>
+      <c r="F88" s="39" t="n"/>
+      <c r="G88" s="40" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H88" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The PCM does not give stock PCS braking priority over the item's ACC_CONTROL request (AOU-04R not met)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I88" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Series-production Toyota ECU; PCS priority over 0x343 assumed (AOU-04R), not verified by LionDriver</t>
+          </r>
+        </is>
+      </c>
+      <c r="J88" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="K88" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No pre-release test targets this cause; AOU-04R needs a message review and a PCS target test (WP-C-04)</t>
+          </r>
+        </is>
+      </c>
+      <c r="L88" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="M88" s="44" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N88" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17267,6 +17343,39 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
+            <t xml:space="preserve">SFM-ACT-006 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Establish on the reference car which stock TSS2 functions (PCS/AEB, FCW) remain available with LionDriver installed and longitudinal control enabled, and verify the stock pre-collision path after installation (PFMEA PFM-014)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O88" s="48" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P88" s="40" t="inlineStr"/>
+      <c r="Q88" s="40" t="inlineStr"/>
+      <c r="R88" s="45" t="inlineStr"/>
+      <c r="S88" s="45" t="inlineStr"/>
+    </row>
+    <row r="89" ht="100.5" customHeight="1">
+      <c r="A89" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
             <t xml:space="preserve">SFM-SE-001
 </t>
           </r>
@@ -17280,7 +17389,7 @@
           </r>
         </is>
       </c>
-      <c r="B88" s="30" t="inlineStr">
+      <c r="B89" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17302,7 +17411,7 @@
           </r>
         </is>
       </c>
-      <c r="C88" s="30" t="inlineStr">
+      <c r="C89" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17401,16 +17510,16 @@
           </r>
         </is>
       </c>
-      <c r="D88" s="31" t="inlineStr">
+      <c r="D89" s="31" t="inlineStr">
         <is>
           <t>HZ-005
 HZ-007</t>
         </is>
       </c>
-      <c r="E88" s="32" t="n">
+      <c r="E89" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="F88" s="30" t="inlineStr">
+      <c r="F89" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17433,12 +17542,12 @@
           </r>
         </is>
       </c>
-      <c r="G88" s="33" t="inlineStr">
+      <c r="G89" s="33" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H88" s="34" t="inlineStr">
+      <c r="H89" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17459,7 +17568,7 @@
           </r>
         </is>
       </c>
-      <c r="I88" s="34" t="inlineStr">
+      <c r="I89" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17480,10 +17589,10 @@
           </r>
         </is>
       </c>
-      <c r="J88" s="35" t="n">
+      <c r="J89" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="K88" s="34" t="inlineStr">
+      <c r="K89" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17495,117 +17604,8 @@
           </r>
         </is>
       </c>
-      <c r="L88" s="46" t="n">
+      <c r="L89" s="46" t="n">
         <v>10</v>
-      </c>
-      <c r="M88" s="36" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="N88" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SFM-ACT-002 · detection
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Requirements-based tests for the host safety-relevant functions (selfdrived, controlsd, pandad, car interface, locationd bounds, monitoring policy), proven by mutation or fault injection and run as a CI gate (see SWF host actions)</t>
-          </r>
-        </is>
-      </c>
-      <c r="O88" s="47" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="P88" s="33" t="inlineStr"/>
-      <c r="Q88" s="33" t="inlineStr"/>
-      <c r="R88" s="37" t="inlineStr"/>
-      <c r="S88" s="37" t="inlineStr"/>
-    </row>
-    <row r="89" ht="100.5" customHeight="1">
-      <c r="A89" s="38" t="n"/>
-      <c r="B89" s="38" t="n"/>
-      <c r="C89" s="38" t="n"/>
-      <c r="D89" s="38" t="n"/>
-      <c r="E89" s="38" t="n"/>
-      <c r="F89" s="38" t="n"/>
-      <c r="G89" s="33" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="H89" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>plannerd stops or runs late while engaged, so controlsd keeps using the last longitudinalPlan</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-linked: SWF-068</t>
-          </r>
-        </is>
-      </c>
-      <c r="I89" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• Upstream openpilot code with upstream review; rated in the SW FMEA</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   assurance/08-analyses/fmea/analyses/sw-fmea.yaml</t>
-          </r>
-        </is>
-      </c>
-      <c r="J89" s="35" t="n">
-        <v>4</v>
-      </c>
-      <c r="K89" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• As rated in the SW FMEA (SWF-068.C1, D 9 at BL-005): no test targets an exception in the planner loop</t>
-          </r>
-        </is>
-      </c>
-      <c r="L89" s="46" t="n">
-        <v>9</v>
       </c>
       <c r="M89" s="36" t="inlineStr">
         <is>
@@ -17645,18 +17645,127 @@
       <c r="S89" s="37" t="inlineStr"/>
     </row>
     <row r="90" ht="100.5" customHeight="1">
-      <c r="A90" s="39" t="n"/>
-      <c r="B90" s="39" t="n"/>
-      <c r="C90" s="39" t="n"/>
-      <c r="D90" s="39" t="n"/>
-      <c r="E90" s="39" t="n"/>
-      <c r="F90" s="39" t="n"/>
-      <c r="G90" s="40" t="inlineStr">
+      <c r="A90" s="38" t="n"/>
+      <c r="B90" s="38" t="n"/>
+      <c r="C90" s="38" t="n"/>
+      <c r="D90" s="38" t="n"/>
+      <c r="E90" s="38" t="n"/>
+      <c r="F90" s="38" t="n"/>
+      <c r="G90" s="33" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H90" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>plannerd stops or runs late while engaged, so controlsd keeps using the last longitudinalPlan</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: SWF-068</t>
+          </r>
+        </is>
+      </c>
+      <c r="I90" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Upstream openpilot code with upstream review; rated in the SW FMEA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/08-analyses/fmea/analyses/sw-fmea.yaml</t>
+          </r>
+        </is>
+      </c>
+      <c r="J90" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="K90" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• As rated in the SW FMEA (SWF-068.C1, D 9 at BL-005): no test targets an exception in the planner loop</t>
+          </r>
+        </is>
+      </c>
+      <c r="L90" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="M90" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N90" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-ACT-002 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Requirements-based tests for the host safety-relevant functions (selfdrived, controlsd, pandad, car interface, locationd bounds, monitoring policy), proven by mutation or fault injection and run as a CI gate (see SWF host actions)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O90" s="47" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P90" s="33" t="inlineStr"/>
+      <c r="Q90" s="33" t="inlineStr"/>
+      <c r="R90" s="37" t="inlineStr"/>
+      <c r="S90" s="37" t="inlineStr"/>
+    </row>
+    <row r="91" ht="100.5" customHeight="1">
+      <c r="A91" s="39" t="n"/>
+      <c r="B91" s="39" t="n"/>
+      <c r="C91" s="39" t="n"/>
+      <c r="D91" s="39" t="n"/>
+      <c r="E91" s="39" t="n"/>
+      <c r="F91" s="39" t="n"/>
+      <c r="G91" s="40" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="H90" s="41" t="inlineStr">
+      <c r="H91" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17668,7 +17777,7 @@
           </r>
         </is>
       </c>
-      <c r="I90" s="41" t="inlineStr">
+      <c r="I91" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17689,10 +17798,10 @@
           </r>
         </is>
       </c>
-      <c r="J90" s="42" t="n">
+      <c r="J91" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="K90" s="41" t="inlineStr">
+      <c r="K91" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17704,15 +17813,15 @@
           </r>
         </is>
       </c>
-      <c r="L90" s="43" t="n">
+      <c r="L91" s="43" t="n">
         <v>10</v>
       </c>
-      <c r="M90" s="44" t="inlineStr">
+      <c r="M91" s="44" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N90" s="41" t="inlineStr">
+      <c r="N91" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17734,18 +17843,18 @@
           </r>
         </is>
       </c>
-      <c r="O90" s="48" t="inlineStr">
+      <c r="O91" s="48" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P90" s="40" t="inlineStr"/>
-      <c r="Q90" s="40" t="inlineStr"/>
-      <c r="R90" s="45" t="inlineStr"/>
-      <c r="S90" s="45" t="inlineStr"/>
+      <c r="P91" s="40" t="inlineStr"/>
+      <c r="Q91" s="40" t="inlineStr"/>
+      <c r="R91" s="45" t="inlineStr"/>
+      <c r="S91" s="45" t="inlineStr"/>
     </row>
-    <row r="91" ht="154.5" customHeight="1">
-      <c r="A91" s="30" t="inlineStr">
+    <row r="92" ht="154.5" customHeight="1">
+      <c r="A92" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17767,7 +17876,7 @@
           </r>
         </is>
       </c>
-      <c r="B91" s="30" t="inlineStr">
+      <c r="B92" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17789,7 +17898,7 @@
           </r>
         </is>
       </c>
-      <c r="C91" s="30" t="inlineStr">
+      <c r="C92" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17862,15 +17971,15 @@
           </r>
         </is>
       </c>
-      <c r="D91" s="31" t="inlineStr">
+      <c r="D92" s="31" t="inlineStr">
         <is>
           <t>HZ-004</t>
         </is>
       </c>
-      <c r="E91" s="32" t="n">
+      <c r="E92" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="F91" s="30" t="inlineStr">
+      <c r="F92" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17893,12 +18002,12 @@
           </r>
         </is>
       </c>
-      <c r="G91" s="33" t="inlineStr">
+      <c r="G92" s="33" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H91" s="34" t="inlineStr">
+      <c r="H92" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17910,7 +18019,7 @@
           </r>
         </is>
       </c>
-      <c r="I91" s="34" t="inlineStr">
+      <c r="I92" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17931,114 +18040,6 @@
           </r>
         </is>
       </c>
-      <c r="J91" s="35" t="n">
-        <v>8</v>
-      </c>
-      <c r="K91" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• No LionDriver test targets this cause</t>
-          </r>
-        </is>
-      </c>
-      <c r="L91" s="46" t="n">
-        <v>10</v>
-      </c>
-      <c r="M91" s="36" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="N91" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">SFM-ACT-023 · design change
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Escalate a temporary EPS fault that lasts while engaged to the take-over request (steerTempUnavailable, SOFT_DISABLE) instead of keeping the low-priority steerTempUnavailableSilent prompt latched after a recent override or at standstill (car_events.py; lead decision DQ-342, option A: the lighter prompt for at most 1.5 s, then the take-over request; TSR-607 (b)). SFM-038.C1; FTA BE-2.08</t>
-          </r>
-        </is>
-      </c>
-      <c r="O91" s="54" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="P91" s="33" t="inlineStr">
-        <is>
-          <t>10/5/4</t>
-        </is>
-      </c>
-      <c r="Q91" s="36" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="R91" s="37" t="inlineStr"/>
-      <c r="S91" s="37" t="inlineStr"/>
-    </row>
-    <row r="92" ht="141" customHeight="1">
-      <c r="A92" s="38" t="n"/>
-      <c r="B92" s="38" t="n"/>
-      <c r="C92" s="38" t="n"/>
-      <c r="D92" s="38" t="n"/>
-      <c r="E92" s="38" t="n"/>
-      <c r="F92" s="38" t="n"/>
-      <c r="G92" s="33" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="H92" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>pandad publishes the panda fields epsFault and requestsRejected (pandad.cc:137-138), but no SoC process reads them (txRateExceeded is read, TSR-615), so a panda-side EPS-fault refusal reaches the driver only through the panda siren and the stock EPS path (SW FMEA SWF-025 notes)</t>
-          </r>
-        </is>
-      </c>
-      <c r="I92" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• None; the fields were added for the panda siren and logging</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   openpilot/selfdrive/pandad/pandad.cc</t>
-          </r>
-        </is>
-      </c>
       <c r="J92" s="35" t="n">
         <v>8</v>
       </c>
@@ -18050,7 +18051,7 @@
               <color rgb="008A5A00"/>
               <sz val="10"/>
             </rPr>
-            <t>• No test targets this cause</t>
+            <t>• No LionDriver test targets this cause</t>
           </r>
         </is>
       </c>
@@ -18071,42 +18072,150 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">SFM-ACT-024 · monitoring
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Act on the panda fields epsFault and requestsRejected on the host (TSR-626(d), TSR-516(b)): raise the take-over request when the panda reports an EPS fault or refused steering frames while lateral control is engaged, within the SG-02 1 s budget, instead of relying on the panda siren alone. Split from SFM-ACT-023 (rev 0.25). SFM-038.C2; FTA BE-2.08</t>
-          </r>
-        </is>
-      </c>
-      <c r="O92" s="47" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="P92" s="33" t="inlineStr"/>
-      <c r="Q92" s="33" t="inlineStr"/>
+            <t xml:space="preserve">SFM-ACT-023 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Escalate a temporary EPS fault that lasts while engaged to the take-over request (steerTempUnavailable, SOFT_DISABLE) instead of keeping the low-priority steerTempUnavailableSilent prompt latched after a recent override or at standstill (car_events.py; lead decision DQ-342, option A: the lighter prompt for at most 1.5 s, then the take-over request; TSR-607 (b)). SFM-038.C1; FTA BE-2.08</t>
+          </r>
+        </is>
+      </c>
+      <c r="O92" s="54" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="P92" s="33" t="inlineStr">
+        <is>
+          <t>10/5/4</t>
+        </is>
+      </c>
+      <c r="Q92" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
       <c r="R92" s="37" t="inlineStr"/>
       <c r="S92" s="37" t="inlineStr"/>
     </row>
-    <row r="93" ht="127.5" customHeight="1">
-      <c r="A93" s="39" t="n"/>
-      <c r="B93" s="39" t="n"/>
-      <c r="C93" s="39" t="n"/>
-      <c r="D93" s="39" t="n"/>
-      <c r="E93" s="39" t="n"/>
-      <c r="F93" s="39" t="n"/>
-      <c r="G93" s="40" t="inlineStr">
+    <row r="93" ht="141" customHeight="1">
+      <c r="A93" s="38" t="n"/>
+      <c r="B93" s="38" t="n"/>
+      <c r="C93" s="38" t="n"/>
+      <c r="D93" s="38" t="n"/>
+      <c r="E93" s="38" t="n"/>
+      <c r="F93" s="38" t="n"/>
+      <c r="G93" s="33" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H93" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>pandad publishes the panda fields epsFault and requestsRejected (pandad.cc:137-138), but no SoC process reads them (txRateExceeded is read, TSR-615), so a panda-side EPS-fault refusal reaches the driver only through the panda siren and the stock EPS path (SW FMEA SWF-025 notes)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I93" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• None; the fields were added for the panda siren and logging</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/pandad/pandad.cc</t>
+          </r>
+        </is>
+      </c>
+      <c r="J93" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="K93" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No test targets this cause</t>
+          </r>
+        </is>
+      </c>
+      <c r="L93" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="M93" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N93" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">SFM-ACT-024 · monitoring
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Act on the panda fields epsFault and requestsRejected on the host (TSR-626(d), TSR-516(b)): raise the take-over request when the panda reports an EPS fault or refused steering frames while lateral control is engaged, within the SG-02 1 s budget, instead of relying on the panda siren alone. Split from SFM-ACT-023 (rev 0.25). SFM-038.C2; FTA BE-2.08</t>
+          </r>
+        </is>
+      </c>
+      <c r="O93" s="47" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P93" s="33" t="inlineStr"/>
+      <c r="Q93" s="33" t="inlineStr"/>
+      <c r="R93" s="37" t="inlineStr"/>
+      <c r="S93" s="37" t="inlineStr"/>
+    </row>
+    <row r="94" ht="127.5" customHeight="1">
+      <c r="A94" s="39" t="n"/>
+      <c r="B94" s="39" t="n"/>
+      <c r="C94" s="39" t="n"/>
+      <c r="D94" s="39" t="n"/>
+      <c r="E94" s="39" t="n"/>
+      <c r="F94" s="39" t="n"/>
+      <c r="G94" s="40" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="H93" s="41" t="inlineStr">
+      <c r="H94" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18118,7 +18227,7 @@
           </r>
         </is>
       </c>
-      <c r="I93" s="41" t="inlineStr">
+      <c r="I94" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18139,10 +18248,10 @@
           </r>
         </is>
       </c>
-      <c r="J93" s="42" t="n">
+      <c r="J94" s="42" t="n">
         <v>8</v>
       </c>
-      <c r="K93" s="41" t="inlineStr">
+      <c r="K94" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18163,15 +18272,15 @@
           </r>
         </is>
       </c>
-      <c r="L93" s="42" t="n">
+      <c r="L94" s="42" t="n">
         <v>8</v>
       </c>
-      <c r="M93" s="44" t="inlineStr">
+      <c r="M94" s="44" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N93" s="41" t="inlineStr">
+      <c r="N94" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18193,35 +18302,36 @@
           </r>
         </is>
       </c>
-      <c r="O93" s="48" t="inlineStr">
+      <c r="O94" s="48" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P93" s="40" t="inlineStr"/>
-      <c r="Q93" s="40" t="inlineStr"/>
-      <c r="R93" s="45" t="inlineStr"/>
-      <c r="S93" s="45" t="inlineStr"/>
+      <c r="P94" s="40" t="inlineStr"/>
+      <c r="Q94" s="40" t="inlineStr"/>
+      <c r="R94" s="45" t="inlineStr"/>
+      <c r="S94" s="45" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S93"/>
+  <autoFilter ref="A2:S94"/>
   <mergeCells count="196">
-    <mergeCell ref="F84:F85"/>
     <mergeCell ref="F17:F19"/>
     <mergeCell ref="E39:E40"/>
-    <mergeCell ref="A57:A59"/>
+    <mergeCell ref="C51:C53"/>
     <mergeCell ref="A20:A22"/>
     <mergeCell ref="F25:F28"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="B61:B62"/>
     <mergeCell ref="A29:A31"/>
-    <mergeCell ref="D86:D87"/>
+    <mergeCell ref="D61:D62"/>
     <mergeCell ref="E23:E24"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="F86:F87"/>
     <mergeCell ref="C32:C34"/>
     <mergeCell ref="E32:E34"/>
+    <mergeCell ref="B92:B94"/>
     <mergeCell ref="B23:B24"/>
+    <mergeCell ref="D92:D94"/>
+    <mergeCell ref="F92:F94"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="A58:A60"/>
     <mergeCell ref="B20:B22"/>
     <mergeCell ref="D20:D22"/>
     <mergeCell ref="E3:E5"/>
@@ -18229,102 +18339,112 @@
     <mergeCell ref="D47:D48"/>
     <mergeCell ref="F29:F31"/>
     <mergeCell ref="F47:F48"/>
+    <mergeCell ref="D87:D88"/>
     <mergeCell ref="E49:E50"/>
-    <mergeCell ref="A71:A74"/>
+    <mergeCell ref="A85:A86"/>
     <mergeCell ref="B37:B38"/>
-    <mergeCell ref="C71:C74"/>
+    <mergeCell ref="C58:C60"/>
+    <mergeCell ref="C89:C91"/>
+    <mergeCell ref="E58:E60"/>
+    <mergeCell ref="E76:E77"/>
+    <mergeCell ref="D65:D67"/>
+    <mergeCell ref="F65:F67"/>
+    <mergeCell ref="E51:E53"/>
     <mergeCell ref="B6:B9"/>
     <mergeCell ref="F37:F38"/>
     <mergeCell ref="A41:A43"/>
+    <mergeCell ref="D80:D82"/>
     <mergeCell ref="E25:E28"/>
     <mergeCell ref="C41:C43"/>
-    <mergeCell ref="F71:F74"/>
+    <mergeCell ref="F80:F82"/>
     <mergeCell ref="A10:A13"/>
-    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="F89:F91"/>
     <mergeCell ref="C44:C46"/>
     <mergeCell ref="A35:A36"/>
     <mergeCell ref="E44:E46"/>
-    <mergeCell ref="B57:B59"/>
-    <mergeCell ref="C69:C70"/>
-    <mergeCell ref="F79:F81"/>
-    <mergeCell ref="D57:D59"/>
+    <mergeCell ref="F51:F53"/>
     <mergeCell ref="N1:Q1"/>
+    <mergeCell ref="B56:B57"/>
     <mergeCell ref="D41:D43"/>
     <mergeCell ref="F41:F43"/>
     <mergeCell ref="D10:D13"/>
     <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B88:B90"/>
+    <mergeCell ref="F68:F69"/>
     <mergeCell ref="F10:F13"/>
     <mergeCell ref="D49:D50"/>
-    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="F83:F84"/>
     <mergeCell ref="A32:A34"/>
+    <mergeCell ref="C85:C86"/>
     <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="A87:A88"/>
     <mergeCell ref="F35:F36"/>
-    <mergeCell ref="D75:D76"/>
     <mergeCell ref="C47:C48"/>
-    <mergeCell ref="F75:F76"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="C56:C57"/>
     <mergeCell ref="D44:D46"/>
-    <mergeCell ref="B60:B61"/>
     <mergeCell ref="F44:F46"/>
     <mergeCell ref="A37:A38"/>
     <mergeCell ref="E6:E9"/>
-    <mergeCell ref="B69:B70"/>
     <mergeCell ref="B3:B5"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="A88:A90"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="C64:C66"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="A51:A53"/>
+    <mergeCell ref="F61:F62"/>
     <mergeCell ref="D25:D28"/>
-    <mergeCell ref="E64:E66"/>
     <mergeCell ref="D37:D38"/>
     <mergeCell ref="A23:A24"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="C79:C81"/>
     <mergeCell ref="I1:M1"/>
-    <mergeCell ref="E79:E81"/>
-    <mergeCell ref="C88:C90"/>
-    <mergeCell ref="E88:E90"/>
+    <mergeCell ref="A68:A69"/>
     <mergeCell ref="D39:D40"/>
+    <mergeCell ref="C87:C88"/>
     <mergeCell ref="A39:A40"/>
     <mergeCell ref="A3:A5"/>
+    <mergeCell ref="C68:C69"/>
     <mergeCell ref="B14:B16"/>
     <mergeCell ref="D23:D24"/>
     <mergeCell ref="B29:B31"/>
+    <mergeCell ref="E68:E69"/>
+    <mergeCell ref="C83:C84"/>
     <mergeCell ref="A49:A50"/>
+    <mergeCell ref="E83:E84"/>
     <mergeCell ref="D32:D34"/>
     <mergeCell ref="C49:C50"/>
     <mergeCell ref="F32:F34"/>
+    <mergeCell ref="E65:E67"/>
     <mergeCell ref="R1:S1"/>
-    <mergeCell ref="E67:E68"/>
-    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="B65:B67"/>
     <mergeCell ref="A17:A19"/>
-    <mergeCell ref="E51:E52"/>
     <mergeCell ref="C17:C19"/>
-    <mergeCell ref="E82:E83"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="E69:E70"/>
     <mergeCell ref="A25:A28"/>
-    <mergeCell ref="B71:B74"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="E84:E85"/>
+    <mergeCell ref="B80:B82"/>
+    <mergeCell ref="B89:B91"/>
+    <mergeCell ref="D58:D60"/>
+    <mergeCell ref="D76:D77"/>
+    <mergeCell ref="D89:D91"/>
+    <mergeCell ref="F58:F60"/>
+    <mergeCell ref="F76:F77"/>
     <mergeCell ref="A44:A46"/>
-    <mergeCell ref="F51:F52"/>
+    <mergeCell ref="B51:B53"/>
+    <mergeCell ref="D51:D53"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="A79:A81"/>
-    <mergeCell ref="E86:E87"/>
+    <mergeCell ref="A92:A94"/>
     <mergeCell ref="B41:B43"/>
     <mergeCell ref="F23:F24"/>
+    <mergeCell ref="B68:B69"/>
     <mergeCell ref="B10:B13"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="C92:C94"/>
     <mergeCell ref="C23:C24"/>
     <mergeCell ref="B49:B50"/>
-    <mergeCell ref="B91:B93"/>
+    <mergeCell ref="E70:E71"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="E92:E94"/>
+    <mergeCell ref="D83:D84"/>
     <mergeCell ref="C20:C22"/>
     <mergeCell ref="C14:C16"/>
     <mergeCell ref="E20:E22"/>
@@ -18334,28 +18454,30 @@
     <mergeCell ref="E29:E31"/>
     <mergeCell ref="F39:F40"/>
     <mergeCell ref="C39:C40"/>
+    <mergeCell ref="A65:A67"/>
+    <mergeCell ref="A72:A75"/>
+    <mergeCell ref="C72:C75"/>
     <mergeCell ref="F49:F50"/>
+    <mergeCell ref="D85:D86"/>
     <mergeCell ref="B17:B19"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="D91:D93"/>
+    <mergeCell ref="E56:E57"/>
     <mergeCell ref="F20:F22"/>
-    <mergeCell ref="F91:F93"/>
     <mergeCell ref="B44:B46"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="E71:E74"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="F87:F88"/>
+    <mergeCell ref="E80:E82"/>
+    <mergeCell ref="E89:E91"/>
     <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C57:C59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="E57:E59"/>
-    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="D70:D71"/>
     <mergeCell ref="D6:D9"/>
-    <mergeCell ref="A91:A93"/>
+    <mergeCell ref="B72:B75"/>
+    <mergeCell ref="F70:F71"/>
     <mergeCell ref="F6:F9"/>
-    <mergeCell ref="C91:C93"/>
-    <mergeCell ref="D64:D66"/>
+    <mergeCell ref="C80:C82"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="E41:E43"/>
-    <mergeCell ref="F64:F66"/>
     <mergeCell ref="C10:C13"/>
     <mergeCell ref="D14:D16"/>
     <mergeCell ref="E10:E13"/>
@@ -18363,48 +18485,35 @@
     <mergeCell ref="F14:F16"/>
     <mergeCell ref="B39:B40"/>
     <mergeCell ref="E35:E36"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="E91:E93"/>
-    <mergeCell ref="F57:F59"/>
-    <mergeCell ref="B64:B66"/>
     <mergeCell ref="C25:C28"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="B79:B81"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="F56:F57"/>
+    <mergeCell ref="D72:D75"/>
     <mergeCell ref="B32:B34"/>
-    <mergeCell ref="D79:D81"/>
-    <mergeCell ref="D88:D90"/>
-    <mergeCell ref="F88:F90"/>
-    <mergeCell ref="C67:C68"/>
+    <mergeCell ref="F72:F75"/>
+    <mergeCell ref="C61:C62"/>
     <mergeCell ref="E17:E19"/>
-    <mergeCell ref="D71:D74"/>
-    <mergeCell ref="E75:E76"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="E61:E62"/>
     <mergeCell ref="A47:A48"/>
     <mergeCell ref="D17:D19"/>
-    <mergeCell ref="F82:F83"/>
-    <mergeCell ref="D67:D68"/>
-    <mergeCell ref="F67:F68"/>
-    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="E85:E86"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B76:B77"/>
     <mergeCell ref="E47:E48"/>
-    <mergeCell ref="D51:D52"/>
-    <mergeCell ref="D82:D83"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="F60:F61"/>
+    <mergeCell ref="C65:C67"/>
     <mergeCell ref="C37:C38"/>
-    <mergeCell ref="D69:D70"/>
+    <mergeCell ref="E72:E75"/>
     <mergeCell ref="E37:E38"/>
     <mergeCell ref="D3:D5"/>
-    <mergeCell ref="F69:F70"/>
+    <mergeCell ref="A80:A82"/>
     <mergeCell ref="B25:B28"/>
-    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="A89:A91"/>
     <mergeCell ref="D35:D36"/>
     <mergeCell ref="C6:C9"/>
-    <mergeCell ref="D84:D85"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83 R84 R85 R86 R87 R88 R89 R90 R91 R92 R93" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
+    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53 R54 R55 R56 R57 R58 R59 R60 R61 R62 R63 R64 R65 R66 R67 R68 R69 R70 R71 R72 R73 R74 R75 R76 R77 R78 R79 R80 R81 R82 R83 R84 R85 R86 R87 R88 R89 R90 R91 R92 R93 R94" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
       <formula1>"Agree,Re-rate,Reject,Question"</formula1>
     </dataValidation>
   </dataValidations>
@@ -18412,7 +18521,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.25 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.26 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -19044,7 +19153,11 @@
           <t>open</t>
         </is>
       </c>
-      <c r="F16" s="60" t="inlineStr"/>
+      <c r="F16" s="60" t="inlineStr">
+        <is>
+          <t>SFM-018.C3</t>
+        </is>
+      </c>
       <c r="G16" s="60" t="inlineStr"/>
       <c r="H16" s="60" t="inlineStr"/>
       <c r="I16" s="60" t="inlineStr"/>
@@ -19792,7 +19905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P76"/>
+  <dimension ref="A1:P77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -22846,10 +22959,10 @@
       <c r="O48" s="37" t="inlineStr"/>
       <c r="P48" s="37" t="inlineStr"/>
     </row>
-    <row r="49" ht="60" customHeight="1">
+    <row r="49" ht="154.5" customHeight="1">
       <c r="A49" s="34" t="inlineStr">
         <is>
-          <t>SFM-019 · Cancel button does not disengage</t>
+          <t>SFM-018 · Item resists driver steering input</t>
         </is>
       </c>
       <c r="B49" s="35" t="n">
@@ -22857,66 +22970,35 @@
       </c>
       <c r="C49" s="33" t="inlineStr">
         <is>
-          <t>SFM-019.C1</t>
+          <t>SFM-018.C3</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>Button message parsed wrong or missing</t>
-        </is>
-      </c>
-      <c r="E49" s="34" t="inlineStr">
-        <is>
-          <t>Cancel turns PCM cruise off; the panda reads PCM cruise from the car bus and revokes control (T-04, 30 ms), independently of the host button parse</t>
-        </is>
-      </c>
-      <c r="F49" s="34" t="inlineStr">
-        <is>
-          <t>Frames refused from the next cycle</t>
-        </is>
-      </c>
-      <c r="G49" s="34" t="inlineStr">
-        <is>
-          <t>Control released within about 40 ms</t>
-        </is>
-      </c>
-      <c r="H49" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="I49" s="35" t="n">
-        <v>6</v>
-      </c>
-      <c r="J49" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="K49" s="36" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="L49" s="34" t="inlineStr">
-        <is>
-          <t>SG-05 brake/cancel · 200 ms
-30 + 10 ms</t>
-        </is>
-      </c>
-      <c r="M49" s="33" t="inlineStr">
-        <is>
-          <t>code derived</t>
-        </is>
-      </c>
-      <c r="N49" s="34" t="inlineStr">
-        <is>
-          <t>SFM-ACT-012 · open</t>
-        </is>
-      </c>
+          <t>The panda envelope passes STEERING_LKA torque that opposes the driver while the driver overrides: the Toyota LKA check covers magnitude, rate and measured-torque error only, and STEER_TORQUE_DRIVER is used only on the LTA path (toyota.h:298-310, 421-424; GAP-02). TSR-304 is not implemented in either build, so only the host 500-unit cut-off (C1, C2) stops the torque</t>
+        </is>
+      </c>
+      <c r="E49" s="64" t="inlineStr">
+        <is>
+          <t>Exempt: The cause is the missing panda override supervision itself, which is the MSR mechanism of C1 and C2; its absence is rated there as M 10 (msr-plan §3)</t>
+        </is>
+      </c>
+      <c r="F49" s="34" t="inlineStr"/>
+      <c r="G49" s="34" t="inlineStr"/>
+      <c r="H49" s="35" t="inlineStr"/>
+      <c r="I49" s="35" t="inlineStr"/>
+      <c r="J49" s="35" t="inlineStr"/>
+      <c r="K49" s="33" t="inlineStr"/>
+      <c r="L49" s="34" t="inlineStr"/>
+      <c r="M49" s="33" t="inlineStr"/>
+      <c r="N49" s="34" t="inlineStr"/>
       <c r="O49" s="37" t="inlineStr"/>
       <c r="P49" s="37" t="inlineStr"/>
     </row>
-    <row r="50" ht="46.5" customHeight="1">
+    <row r="50" ht="60" customHeight="1">
       <c r="A50" s="34" t="inlineStr">
         <is>
-          <t>SFM-020 · Accelerator override not honored</t>
+          <t>SFM-019 · Cancel button does not disengage</t>
         </is>
       </c>
       <c r="B50" s="35" t="n">
@@ -22924,27 +23006,27 @@
       </c>
       <c r="C50" s="33" t="inlineStr">
         <is>
-          <t>SFM-020.C1</t>
+          <t>SFM-019.C1</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>gasPressed parsed wrong or missing</t>
+          <t>Button message parsed wrong or missing</t>
         </is>
       </c>
       <c r="E50" s="34" t="inlineStr">
         <is>
-          <t>Panda parses the gas pedal itself and refuses acceleration requests while it is pressed (longitudinal allowed only without gas)</t>
+          <t>Cancel turns PCM cruise off; the panda reads PCM cruise from the car bus and revokes control (T-04, 30 ms), independently of the host button parse</t>
         </is>
       </c>
       <c r="F50" s="34" t="inlineStr">
         <is>
-          <t>ACC_CONTROL frames with a request refused</t>
+          <t>Frames refused from the next cycle</t>
         </is>
       </c>
       <c r="G50" s="34" t="inlineStr">
         <is>
-          <t>No item deceleration while the driver presses the gas</t>
+          <t>Control released within about 40 ms</t>
         </is>
       </c>
       <c r="H50" s="35" t="n">
@@ -22963,8 +23045,8 @@
       </c>
       <c r="L50" s="34" t="inlineStr">
         <is>
-          <t>SG-03/04 · 1000 ms
-33 + 10 ms</t>
+          <t>SG-05 brake/cancel · 200 ms
+30 + 10 ms</t>
         </is>
       </c>
       <c r="M50" s="33" t="inlineStr">
@@ -22980,10 +23062,10 @@
       <c r="O50" s="37" t="inlineStr"/>
       <c r="P50" s="37" t="inlineStr"/>
     </row>
-    <row r="51" ht="87" customHeight="1">
+    <row r="51" ht="46.5" customHeight="1">
       <c r="A51" s="34" t="inlineStr">
         <is>
-          <t>SFM-021 · Stock cruise stays engaged after LionDriver disengages</t>
+          <t>SFM-020 · Accelerator override not honored</t>
         </is>
       </c>
       <c r="B51" s="35" t="n">
@@ -22991,37 +23073,37 @@
       </c>
       <c r="C51" s="33" t="inlineStr">
         <is>
-          <t>SFM-021.C1</t>
+          <t>SFM-020.C1</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>Cancel message not packed/sent for this car</t>
+          <t>gasPressed parsed wrong or missing</t>
         </is>
       </c>
       <c r="E51" s="34" t="inlineStr">
         <is>
-          <t>BL-005: selfdrived raises cruiseMismatch after 1 s of PCM cruise engaged while the item is not (CRUISE_MISMATCH_TIME, selfdrived.py; TSR-308). At BL-004 it was raised after 6 s with no reaction (T-19)</t>
+          <t>Panda parses the gas pedal itself and refuses acceleration requests while it is pressed (longitudinal allowed only without gas)</t>
         </is>
       </c>
       <c r="F51" s="34" t="inlineStr">
         <is>
-          <t>Repeating audible prompt to press Cancel or brake; controlsd keeps requesting the cancel</t>
+          <t>ACC_CONTROL frames with a request refused</t>
         </is>
       </c>
       <c r="G51" s="34" t="inlineStr">
         <is>
-          <t>Stock cruise keeps controlling speed until the driver acts on the prompt; the mode confusion is now announced. The driver must act, so S after the response stays 10 (msr-plan.md §4.8)</t>
+          <t>No item deceleration while the driver presses the gas</t>
         </is>
       </c>
       <c r="H51" s="35" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I51" s="35" t="n">
         <v>6</v>
       </c>
       <c r="J51" s="35" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K51" s="36" t="inlineStr">
         <is>
@@ -23030,7 +23112,8 @@
       </c>
       <c r="L51" s="34" t="inlineStr">
         <is>
-          <t>1000 + 10 ms</t>
+          <t>SG-03/04 · 1000 ms
+33 + 10 ms</t>
         </is>
       </c>
       <c r="M51" s="33" t="inlineStr">
@@ -23040,7 +23123,7 @@
       </c>
       <c r="N51" s="34" t="inlineStr">
         <is>
-          <t>SFM-ACT-011 · completed</t>
+          <t>SFM-ACT-012 · open</t>
         </is>
       </c>
       <c r="O51" s="37" t="inlineStr"/>
@@ -23057,12 +23140,12 @@
       </c>
       <c r="C52" s="33" t="inlineStr">
         <is>
-          <t>SFM-021.C2</t>
+          <t>SFM-021.C1</t>
         </is>
       </c>
       <c r="D52" s="34" t="inlineStr">
         <is>
-          <t>PCM ignores cancel request</t>
+          <t>Cancel message not packed/sent for this car</t>
         </is>
       </c>
       <c r="E52" s="34" t="inlineStr">
@@ -23084,7 +23167,7 @@
         <v>10</v>
       </c>
       <c r="I52" s="35" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J52" s="35" t="n">
         <v>7</v>
@@ -23112,10 +23195,10 @@
       <c r="O52" s="37" t="inlineStr"/>
       <c r="P52" s="37" t="inlineStr"/>
     </row>
-    <row r="53" ht="46.5" customHeight="1">
+    <row r="53" ht="87" customHeight="1">
       <c r="A53" s="34" t="inlineStr">
         <is>
-          <t>SFM-022 · Inattentive driver not detected</t>
+          <t>SFM-021 · Stock cruise stays engaged after LionDriver disengages</t>
         </is>
       </c>
       <c r="B53" s="35" t="n">
@@ -23123,52 +23206,56 @@
       </c>
       <c r="C53" s="33" t="inlineStr">
         <is>
-          <t>SFM-022.C1</t>
+          <t>SFM-021.C2</t>
         </is>
       </c>
       <c r="D53" s="34" t="inlineStr">
         <is>
-          <t>DM model false negative (eyes off road classified attentive)</t>
+          <t>PCM ignores cancel request</t>
         </is>
       </c>
       <c r="E53" s="34" t="inlineStr">
         <is>
-          <t>Fallback to the wheel-touch policy only when the model is uncertain; a confident false negative is not caught</t>
+          <t>BL-005: selfdrived raises cruiseMismatch after 1 s of PCM cruise engaged while the item is not (CRUISE_MISMATCH_TIME, selfdrived.py; TSR-308). At BL-004 it was raised after 6 s with no reaction (T-19)</t>
         </is>
       </c>
       <c r="F53" s="34" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Repeating audible prompt to press Cancel or brake; controlsd keeps requesting the cancel</t>
         </is>
       </c>
       <c r="G53" s="34" t="inlineStr">
         <is>
-          <t>Unchanged: escalation does not start</t>
+          <t>Stock cruise keeps controlling speed until the driver acts on the prompt; the mode confusion is now announced. The driver must act, so S after the response stays 10 (msr-plan.md §4.8)</t>
         </is>
       </c>
       <c r="H53" s="35" t="n">
         <v>10</v>
       </c>
       <c r="I53" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="J53" s="35" t="n">
         <v>7</v>
       </c>
-      <c r="J53" s="46" t="n">
-        <v>9</v>
-      </c>
       <c r="K53" s="36" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="L53" s="34" t="inlineStr"/>
+      <c r="L53" s="34" t="inlineStr">
+        <is>
+          <t>1000 + 10 ms</t>
+        </is>
+      </c>
       <c r="M53" s="33" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>code derived</t>
         </is>
       </c>
       <c r="N53" s="34" t="inlineStr">
         <is>
-          <t>SFM-ACT-009 · open</t>
+          <t>SFM-ACT-011 · completed</t>
         </is>
       </c>
       <c r="O53" s="37" t="inlineStr"/>
@@ -23185,17 +23272,17 @@
       </c>
       <c r="C54" s="33" t="inlineStr">
         <is>
-          <t>SFM-022.C2</t>
+          <t>SFM-022.C1</t>
         </is>
       </c>
       <c r="D54" s="34" t="inlineStr">
         <is>
-          <t>Pose thresholds/calibration wrong for driver or mount</t>
+          <t>DM model false negative (eyes off road classified attentive)</t>
         </is>
       </c>
       <c r="E54" s="34" t="inlineStr">
         <is>
-          <t>Fallback to the wheel-touch policy only when the model is uncertain; wrong thresholds give confident outputs</t>
+          <t>Fallback to the wheel-touch policy only when the model is uncertain; a confident false negative is not caught</t>
         </is>
       </c>
       <c r="F54" s="34" t="inlineStr">
@@ -23212,7 +23299,7 @@
         <v>10</v>
       </c>
       <c r="I54" s="35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J54" s="46" t="n">
         <v>9</v>
@@ -23247,37 +23334,37 @@
       </c>
       <c r="C55" s="33" t="inlineStr">
         <is>
-          <t>SFM-022.C3</t>
+          <t>SFM-022.C2</t>
         </is>
       </c>
       <c r="D55" s="34" t="inlineStr">
         <is>
-          <t>Driver camera or IR illumination degraded</t>
+          <t>Pose thresholds/calibration wrong for driver or mount</t>
         </is>
       </c>
       <c r="E55" s="34" t="inlineStr">
         <is>
-          <t>A dead camera raises cameraMalfunction; a degraded image makes the model uncertain and falls back to the wheel-touch policy after 10 s</t>
+          <t>Fallback to the wheel-touch policy only when the model is uncertain; wrong thresholds give confident outputs</t>
         </is>
       </c>
       <c r="F55" s="34" t="inlineStr">
         <is>
-          <t>SOFT_DISABLE, or wheel-touch escalation</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G55" s="34" t="inlineStr">
         <is>
-          <t>Driver monitored by wheel touch; no FTTI until the H-09 goal has one (WP-S-04 §3.8.4)</t>
+          <t>Unchanged: escalation does not start</t>
         </is>
       </c>
       <c r="H55" s="35" t="n">
         <v>10</v>
       </c>
       <c r="I55" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="J55" s="35" t="n">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="J55" s="46" t="n">
+        <v>9</v>
       </c>
       <c r="K55" s="36" t="inlineStr">
         <is>
@@ -23292,7 +23379,7 @@
       </c>
       <c r="N55" s="34" t="inlineStr">
         <is>
-          <t>SFM-ACT-005 · open</t>
+          <t>SFM-ACT-009 · open</t>
         </is>
       </c>
       <c r="O55" s="37" t="inlineStr"/>
@@ -23301,7 +23388,7 @@
     <row r="56" ht="46.5" customHeight="1">
       <c r="A56" s="34" t="inlineStr">
         <is>
-          <t>SFM-025 · Terminal driver-unresponsive state does not bring the item to a safe state</t>
+          <t>SFM-022 · Inattentive driver not detected</t>
         </is>
       </c>
       <c r="B56" s="35" t="n">
@@ -23309,37 +23396,37 @@
       </c>
       <c r="C56" s="33" t="inlineStr">
         <is>
-          <t>SFM-025.C1</t>
+          <t>SFM-022.C3</t>
         </is>
       </c>
       <c r="D56" s="34" t="inlineStr">
         <is>
-          <t>driverDistracted3 / driverUnresponsive3 mapped only to ET.PERMANENT (no disable reaction)</t>
+          <t>Driver camera or IR illumination degraded</t>
         </is>
       </c>
       <c r="E56" s="34" t="inlineStr">
         <is>
-          <t>None: the lockout acts only after disengagement; the terminal alert has no disable reaction</t>
+          <t>A dead camera raises cameraMalfunction; a degraded image makes the model uncertain and falls back to the wheel-touch policy after 10 s</t>
         </is>
       </c>
       <c r="F56" s="34" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>SOFT_DISABLE, or wheel-touch escalation</t>
         </is>
       </c>
       <c r="G56" s="34" t="inlineStr">
         <is>
-          <t>Unchanged: control continues with an unresponsive driver</t>
+          <t>Driver monitored by wheel touch; no FTTI until the H-09 goal has one (WP-S-04 §3.8.4)</t>
         </is>
       </c>
       <c r="H56" s="35" t="n">
         <v>10</v>
       </c>
       <c r="I56" s="35" t="n">
-        <v>8</v>
-      </c>
-      <c r="J56" s="46" t="n">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="J56" s="35" t="n">
+        <v>7</v>
       </c>
       <c r="K56" s="36" t="inlineStr">
         <is>
@@ -23360,10 +23447,10 @@
       <c r="O56" s="37" t="inlineStr"/>
       <c r="P56" s="37" t="inlineStr"/>
     </row>
-    <row r="57" ht="33" customHeight="1">
+    <row r="57" ht="46.5" customHeight="1">
       <c r="A57" s="34" t="inlineStr">
         <is>
-          <t>SFM-026 · Takeover or disengagement alert not presented</t>
+          <t>SFM-025 · Terminal driver-unresponsive state does not bring the item to a safe state</t>
         </is>
       </c>
       <c r="B57" s="35" t="n">
@@ -23371,17 +23458,17 @@
       </c>
       <c r="C57" s="33" t="inlineStr">
         <is>
-          <t>SFM-026.C1</t>
+          <t>SFM-025.C1</t>
         </is>
       </c>
       <c r="D57" s="34" t="inlineStr">
         <is>
-          <t>UI process hung or display off</t>
+          <t>driverDistracted3 / driverUnresponsive3 mapped only to ET.PERMANENT (no disable reaction)</t>
         </is>
       </c>
       <c r="E57" s="34" t="inlineStr">
         <is>
-          <t>None at BL-004: the audio channel masks a hung UI but nothing detects it</t>
+          <t>None: the lockout acts only after disengagement; the terminal alert has no disable reaction</t>
         </is>
       </c>
       <c r="F57" s="34" t="inlineStr">
@@ -23391,14 +23478,14 @@
       </c>
       <c r="G57" s="34" t="inlineStr">
         <is>
-          <t>Alert audible only</t>
+          <t>Unchanged: control continues with an unresponsive driver</t>
         </is>
       </c>
       <c r="H57" s="35" t="n">
         <v>10</v>
       </c>
       <c r="I57" s="35" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J57" s="46" t="n">
         <v>10</v>
@@ -23416,7 +23503,7 @@
       </c>
       <c r="N57" s="34" t="inlineStr">
         <is>
-          <t>SFM-ACT-007 · open</t>
+          <t>SFM-ACT-005 · open</t>
         </is>
       </c>
       <c r="O57" s="37" t="inlineStr"/>
@@ -23433,17 +23520,17 @@
       </c>
       <c r="C58" s="33" t="inlineStr">
         <is>
-          <t>SFM-026.C2</t>
+          <t>SFM-026.C1</t>
         </is>
       </c>
       <c r="D58" s="34" t="inlineStr">
         <is>
-          <t>soundd failure or volume too low for cabin noise</t>
+          <t>UI process hung or display off</t>
         </is>
       </c>
       <c r="E58" s="34" t="inlineStr">
         <is>
-          <t>None at BL-004: the screen masks a soundd failure but nothing detects it</t>
+          <t>None at BL-004: the audio channel masks a hung UI but nothing detects it</t>
         </is>
       </c>
       <c r="F58" s="34" t="inlineStr">
@@ -23453,7 +23540,7 @@
       </c>
       <c r="G58" s="34" t="inlineStr">
         <is>
-          <t>Alert visual only</t>
+          <t>Alert audible only</t>
         </is>
       </c>
       <c r="H58" s="35" t="n">
@@ -23495,17 +23582,17 @@
       </c>
       <c r="C59" s="33" t="inlineStr">
         <is>
-          <t>SFM-026.C3</t>
+          <t>SFM-026.C2</t>
         </is>
       </c>
       <c r="D59" s="34" t="inlineStr">
         <is>
-          <t>Speaker or display hardware failure</t>
+          <t>soundd failure or volume too low for cabin noise</t>
         </is>
       </c>
       <c r="E59" s="34" t="inlineStr">
         <is>
-          <t>None: no self-test of speaker or display</t>
+          <t>None at BL-004: the screen masks a soundd failure but nothing detects it</t>
         </is>
       </c>
       <c r="F59" s="34" t="inlineStr">
@@ -23515,14 +23602,14 @@
       </c>
       <c r="G59" s="34" t="inlineStr">
         <is>
-          <t>Alert on one channel or none</t>
+          <t>Alert visual only</t>
         </is>
       </c>
       <c r="H59" s="35" t="n">
         <v>10</v>
       </c>
       <c r="I59" s="35" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J59" s="46" t="n">
         <v>10</v>
@@ -23546,10 +23633,10 @@
       <c r="O59" s="37" t="inlineStr"/>
       <c r="P59" s="37" t="inlineStr"/>
     </row>
-    <row r="60" ht="127.5" customHeight="1">
+    <row r="60" ht="33" customHeight="1">
       <c r="A60" s="34" t="inlineStr">
         <is>
-          <t>SFM-029 · Actuator command limits not enforced</t>
+          <t>SFM-026 · Takeover or disengagement alert not presented</t>
         </is>
       </c>
       <c r="B60" s="35" t="n">
@@ -23557,62 +23644,58 @@
       </c>
       <c r="C60" s="33" t="inlineStr">
         <is>
-          <t>SFM-029.C1</t>
+          <t>SFM-026.C3</t>
         </is>
       </c>
       <c r="D60" s="34" t="inlineStr">
         <is>
-          <t>Wrong safety model or parameter set for this car</t>
+          <t>Speaker or display hardware failure</t>
         </is>
       </c>
       <c r="E60" s="34" t="inlineStr">
         <is>
-          <t>controlsMismatch compares the panda safety model and parameter with CarParams, only from 10 s after start (T-18). BL-005: the panda refuses any car mode other than TOYOTA parameter 73, so a wrong request leaves it out of the car mode and the mismatch blocks engagement; a non-reference panda is named (pandaNotReferenceBuild). Not compared with an FTTI: the fault is present from power-up</t>
+          <t>None: no self-test of speaker or display</t>
         </is>
       </c>
       <c r="F60" s="34" t="inlineStr">
         <is>
-          <t>IMMEDIATE_DISABLE with alert; engagement refused while the mismatch persists</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G60" s="34" t="inlineStr">
         <is>
-          <t>Item disengaged with an alert</t>
+          <t>Alert on one channel or none</t>
         </is>
       </c>
       <c r="H60" s="35" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I60" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="J60" s="35" t="n">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="J60" s="46" t="n">
+        <v>10</v>
       </c>
       <c r="K60" s="36" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="L60" s="34" t="inlineStr">
-        <is>
-          <t>10000 + 10 ms</t>
-        </is>
-      </c>
+      <c r="L60" s="34" t="inlineStr"/>
       <c r="M60" s="33" t="inlineStr">
         <is>
-          <t>code derived</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="N60" s="34" t="inlineStr">
         <is>
-          <t>SFM-ACT-008 · in progress</t>
+          <t>SFM-ACT-007 · open</t>
         </is>
       </c>
       <c r="O60" s="37" t="inlineStr"/>
       <c r="P60" s="37" t="inlineStr"/>
     </row>
-    <row r="61" ht="46.5" customHeight="1">
+    <row r="61" ht="127.5" customHeight="1">
       <c r="A61" s="34" t="inlineStr">
         <is>
           <t>SFM-029 · Actuator command limits not enforced</t>
@@ -23623,58 +23706,62 @@
       </c>
       <c r="C61" s="33" t="inlineStr">
         <is>
-          <t>SFM-029.C2</t>
+          <t>SFM-029.C1</t>
         </is>
       </c>
       <c r="D61" s="34" t="inlineStr">
         <is>
-          <t>Safety model limit defect in firmware</t>
+          <t>Wrong safety model or parameter set for this car</t>
         </is>
       </c>
       <c r="E61" s="34" t="inlineStr">
         <is>
-          <t>None: controlsMismatch checks which safety model is active, not its limit values; the limit code is itself the monitor that has failed</t>
+          <t>controlsMismatch compares the panda safety model and parameter with CarParams, only from 10 s after start (T-18). BL-005: the panda refuses any car mode other than TOYOTA parameter 73, so a wrong request leaves it out of the car mode and the mismatch blocks engagement; a non-reference panda is named (pandaNotReferenceBuild). Not compared with an FTTI: the fault is present from power-up</t>
         </is>
       </c>
       <c r="F61" s="34" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>IMMEDIATE_DISABLE with alert; engagement refused while the mismatch persists</t>
         </is>
       </c>
       <c r="G61" s="34" t="inlineStr">
         <is>
-          <t>Unchanged: commands beyond the intended envelope reach the EPS</t>
+          <t>Item disengaged with an alert</t>
         </is>
       </c>
       <c r="H61" s="35" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I61" s="35" t="n">
-        <v>6</v>
-      </c>
-      <c r="J61" s="46" t="n">
-        <v>10</v>
+        <v>3</v>
+      </c>
+      <c r="J61" s="35" t="n">
+        <v>7</v>
       </c>
       <c r="K61" s="36" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="L61" s="34" t="inlineStr"/>
+      <c r="L61" s="34" t="inlineStr">
+        <is>
+          <t>10000 + 10 ms</t>
+        </is>
+      </c>
       <c r="M61" s="33" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>code derived</t>
         </is>
       </c>
       <c r="N61" s="34" t="inlineStr">
         <is>
-          <t>SFM-ACT-001 · open</t>
+          <t>SFM-ACT-008 · in progress</t>
         </is>
       </c>
       <c r="O61" s="37" t="inlineStr"/>
       <c r="P61" s="37" t="inlineStr"/>
     </row>
-    <row r="62" ht="33" customHeight="1">
+    <row r="62" ht="46.5" customHeight="1">
       <c r="A62" s="34" t="inlineStr">
         <is>
           <t>SFM-029 · Actuator command limits not enforced</t>
@@ -23685,32 +23772,58 @@
       </c>
       <c r="C62" s="33" t="inlineStr">
         <is>
-          <t>SFM-029.C3</t>
+          <t>SFM-029.C2</t>
         </is>
       </c>
       <c r="D62" s="34" t="inlineStr">
         <is>
-          <t>Panda MCU hardware fault (see DFMEA/FMEDA)</t>
-        </is>
-      </c>
-      <c r="E62" s="64" t="inlineStr">
-        <is>
-          <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-001.C1)</t>
-        </is>
-      </c>
-      <c r="F62" s="34" t="inlineStr"/>
-      <c r="G62" s="34" t="inlineStr"/>
-      <c r="H62" s="35" t="inlineStr"/>
-      <c r="I62" s="35" t="inlineStr"/>
-      <c r="J62" s="35" t="inlineStr"/>
-      <c r="K62" s="33" t="inlineStr"/>
+          <t>Safety model limit defect in firmware</t>
+        </is>
+      </c>
+      <c r="E62" s="34" t="inlineStr">
+        <is>
+          <t>None: controlsMismatch checks which safety model is active, not its limit values; the limit code is itself the monitor that has failed</t>
+        </is>
+      </c>
+      <c r="F62" s="34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G62" s="34" t="inlineStr">
+        <is>
+          <t>Unchanged: commands beyond the intended envelope reach the EPS</t>
+        </is>
+      </c>
+      <c r="H62" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I62" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J62" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K62" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
       <c r="L62" s="34" t="inlineStr"/>
-      <c r="M62" s="33" t="inlineStr"/>
-      <c r="N62" s="34" t="inlineStr"/>
+      <c r="M62" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N62" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-001 · open</t>
+        </is>
+      </c>
       <c r="O62" s="37" t="inlineStr"/>
       <c r="P62" s="37" t="inlineStr"/>
     </row>
-    <row r="63" ht="46.5" customHeight="1">
+    <row r="63" ht="33" customHeight="1">
       <c r="A63" s="34" t="inlineStr">
         <is>
           <t>SFM-029 · Actuator command limits not enforced</t>
@@ -23721,57 +23834,35 @@
       </c>
       <c r="C63" s="33" t="inlineStr">
         <is>
-          <t>SFM-029.C4</t>
+          <t>SFM-029.C3</t>
         </is>
       </c>
       <c r="D63" s="34" t="inlineStr">
         <is>
-          <t>Harness allows the device to reach a bus without passing the panda filter</t>
-        </is>
-      </c>
-      <c r="E63" s="34" t="inlineStr">
-        <is>
-          <t>None: controlsMismatch cannot see a path that bypasses the panda</t>
-        </is>
-      </c>
-      <c r="F63" s="34" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G63" s="34" t="inlineStr">
-        <is>
-          <t>Unchanged</t>
-        </is>
-      </c>
-      <c r="H63" s="35" t="n">
-        <v>10</v>
-      </c>
-      <c r="I63" s="35" t="n">
-        <v>2</v>
-      </c>
-      <c r="J63" s="46" t="n">
-        <v>10</v>
-      </c>
-      <c r="K63" s="36" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
+          <t>Panda MCU hardware fault (see DFMEA/FMEDA)</t>
+        </is>
+      </c>
+      <c r="E63" s="64" t="inlineStr">
+        <is>
+          <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-001.C1)</t>
+        </is>
+      </c>
+      <c r="F63" s="34" t="inlineStr"/>
+      <c r="G63" s="34" t="inlineStr"/>
+      <c r="H63" s="35" t="inlineStr"/>
+      <c r="I63" s="35" t="inlineStr"/>
+      <c r="J63" s="35" t="inlineStr"/>
+      <c r="K63" s="33" t="inlineStr"/>
       <c r="L63" s="34" t="inlineStr"/>
-      <c r="M63" s="33" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
+      <c r="M63" s="33" t="inlineStr"/>
       <c r="N63" s="34" t="inlineStr"/>
       <c r="O63" s="37" t="inlineStr"/>
       <c r="P63" s="37" t="inlineStr"/>
     </row>
-    <row r="64" ht="114" customHeight="1">
+    <row r="64" ht="46.5" customHeight="1">
       <c r="A64" s="34" t="inlineStr">
         <is>
-          <t>SFM-032 · Wrong vehicle configuration active (fingerprint or car port)</t>
+          <t>SFM-029 · Actuator command limits not enforced</t>
         </is>
       </c>
       <c r="B64" s="35" t="n">
@@ -23779,65 +23870,57 @@
       </c>
       <c r="C64" s="33" t="inlineStr">
         <is>
-          <t>SFM-032.C1</t>
+          <t>SFM-029.C4</t>
         </is>
       </c>
       <c r="D64" s="34" t="inlineStr">
         <is>
-          <t>Fuzzy fingerprint matches a similar platform</t>
+          <t>Harness allows the device to reach a bus without passing the panda filter</t>
         </is>
       </c>
       <c r="E64" s="34" t="inlineStr">
         <is>
-          <t>BL-005: if the matched platform needs a Toyota safety parameter other than 73, the panda refuses the car mode, so controlsMismatch (from 10 s after start) blocks engagement. A similar platform with parameter 73 is not detected: controlsMismatch compares the panda with CarParams, which share the same wrong platform, and carUnrecognized does not fire on a fuzzy match</t>
+          <t>None: controlsMismatch cannot see a path that bypasses the panda</t>
         </is>
       </c>
       <c r="F64" s="34" t="inlineStr">
         <is>
-          <t>For a platform with another safety parameter, no engagement (NO_ENTRY) and an alert; otherwise none</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G64" s="34" t="inlineStr">
         <is>
-          <t>Partly mitigated: the panda envelope is that of the reference parameter, but host tuning, scaling and DBC of a similar platform with parameter 73 apply unseen</t>
+          <t>Unchanged</t>
         </is>
       </c>
       <c r="H64" s="35" t="n">
         <v>10</v>
       </c>
       <c r="I64" s="35" t="n">
-        <v>4</v>
-      </c>
-      <c r="J64" s="35" t="n">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="J64" s="46" t="n">
+        <v>10</v>
       </c>
       <c r="K64" s="36" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="L64" s="34" t="inlineStr">
-        <is>
-          <t>10000 + 10 ms</t>
-        </is>
-      </c>
+      <c r="L64" s="34" t="inlineStr"/>
       <c r="M64" s="33" t="inlineStr">
         <is>
-          <t>code derived</t>
-        </is>
-      </c>
-      <c r="N64" s="34" t="inlineStr">
-        <is>
-          <t>SFM-ACT-008 · in progress</t>
-        </is>
-      </c>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N64" s="34" t="inlineStr"/>
       <c r="O64" s="37" t="inlineStr"/>
       <c r="P64" s="37" t="inlineStr"/>
     </row>
-    <row r="65" ht="73.5" customHeight="1">
+    <row r="65" ht="114" customHeight="1">
       <c r="A65" s="34" t="inlineStr">
         <is>
-          <t>SFM-034 · Harness-box intercept switch stuck or in the wrong position</t>
+          <t>SFM-032 · Wrong vehicle configuration active (fingerprint or car port)</t>
         </is>
       </c>
       <c r="B65" s="35" t="n">
@@ -23845,32 +23928,62 @@
       </c>
       <c r="C65" s="33" t="inlineStr">
         <is>
-          <t>SFM-034.C1</t>
+          <t>SFM-032.C1</t>
         </is>
       </c>
       <c r="D65" s="34" t="inlineStr">
         <is>
-          <t>Switch U1 or U2 stuck in intercept, its IN input damaged high or driven high, its pull-down R2/R3 open, or the switches damaged by box supply transients (DG419LE, RR-2026-010)</t>
-        </is>
-      </c>
-      <c r="E65" s="64" t="inlineStr">
-        <is>
-          <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-010.C1)</t>
-        </is>
-      </c>
-      <c r="F65" s="34" t="inlineStr"/>
-      <c r="G65" s="34" t="inlineStr"/>
-      <c r="H65" s="35" t="inlineStr"/>
-      <c r="I65" s="35" t="inlineStr"/>
-      <c r="J65" s="35" t="inlineStr"/>
-      <c r="K65" s="33" t="inlineStr"/>
-      <c r="L65" s="34" t="inlineStr"/>
-      <c r="M65" s="33" t="inlineStr"/>
-      <c r="N65" s="34" t="inlineStr"/>
+          <t>Fuzzy fingerprint matches a similar platform</t>
+        </is>
+      </c>
+      <c r="E65" s="34" t="inlineStr">
+        <is>
+          <t>BL-005: if the matched platform needs a Toyota safety parameter other than 73, the panda refuses the car mode, so controlsMismatch (from 10 s after start) blocks engagement. A similar platform with parameter 73 is not detected: controlsMismatch compares the panda with CarParams, which share the same wrong platform, and carUnrecognized does not fire on a fuzzy match</t>
+        </is>
+      </c>
+      <c r="F65" s="34" t="inlineStr">
+        <is>
+          <t>For a platform with another safety parameter, no engagement (NO_ENTRY) and an alert; otherwise none</t>
+        </is>
+      </c>
+      <c r="G65" s="34" t="inlineStr">
+        <is>
+          <t>Partly mitigated: the panda envelope is that of the reference parameter, but host tuning, scaling and DBC of a similar platform with parameter 73 apply unseen</t>
+        </is>
+      </c>
+      <c r="H65" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I65" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="J65" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="K65" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L65" s="34" t="inlineStr">
+        <is>
+          <t>10000 + 10 ms</t>
+        </is>
+      </c>
+      <c r="M65" s="33" t="inlineStr">
+        <is>
+          <t>code derived</t>
+        </is>
+      </c>
+      <c r="N65" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-008 · in progress</t>
+        </is>
+      </c>
       <c r="O65" s="37" t="inlineStr"/>
       <c r="P65" s="37" t="inlineStr"/>
     </row>
-    <row r="66" ht="60" customHeight="1">
+    <row r="66" ht="73.5" customHeight="1">
       <c r="A66" s="34" t="inlineStr">
         <is>
           <t>SFM-034 · Harness-box intercept switch stuck or in the wrong position</t>
@@ -23881,17 +23994,17 @@
       </c>
       <c r="C66" s="33" t="inlineStr">
         <is>
-          <t>SFM-034.C2</t>
+          <t>SFM-034.C1</t>
         </is>
       </c>
       <c r="D66" s="34" t="inlineStr">
         <is>
-          <t>Switch stuck in pass-through, or the SBU1 drive lost, held low or too low to change the switch over (5 V drive against VL = VIN)</t>
+          <t>Switch U1 or U2 stuck in intercept, its IN input damaged high or driven high, its pull-down R2/R3 open, or the switches damaged by box supply transients (DG419LE, RR-2026-010)</t>
         </is>
       </c>
       <c r="E66" s="64" t="inlineStr">
         <is>
-          <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-011.C1)</t>
+          <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-010.C1)</t>
         </is>
       </c>
       <c r="F66" s="34" t="inlineStr"/>
@@ -23906,10 +24019,10 @@
       <c r="O66" s="37" t="inlineStr"/>
       <c r="P66" s="37" t="inlineStr"/>
     </row>
-    <row r="67" ht="73.5" customHeight="1">
+    <row r="67" ht="60" customHeight="1">
       <c r="A67" s="34" t="inlineStr">
         <is>
-          <t>SFM-035 · Item sends a frame that alters the stock pre-collision function</t>
+          <t>SFM-034 · Harness-box intercept switch stuck or in the wrong position</t>
         </is>
       </c>
       <c r="B67" s="35" t="n">
@@ -23917,54 +24030,27 @@
       </c>
       <c r="C67" s="33" t="inlineStr">
         <is>
-          <t>SFM-035.C1</t>
+          <t>SFM-034.C2</t>
         </is>
       </c>
       <c r="D67" s="34" t="inlineStr">
         <is>
-          <t>Host code (car interface, pandad) emits a PCS-relevant ID or a non-zero PRE_COLLISION payload (QM fault)</t>
-        </is>
-      </c>
-      <c r="E67" s="34" t="inlineStr">
-        <is>
-          <t>The panda checks every frame from the SoC against the TX whitelist and the 0x283 zero-payload rule before it is sent</t>
-        </is>
-      </c>
-      <c r="F67" s="34" t="inlineStr">
-        <is>
-          <t>Frame refused, the stock PCS path is untouched; while engaged the refusal also gives pandaTxBlocked, an immediate disable with a take-over alert</t>
-        </is>
-      </c>
-      <c r="G67" s="34" t="inlineStr">
-        <is>
-          <t>Stock PCS unaffected. While engaged the item disengages with an alert (controlled handback, S 8), the worst effect left after the response</t>
-        </is>
-      </c>
-      <c r="H67" s="35" t="n">
-        <v>8</v>
-      </c>
-      <c r="I67" s="35" t="n">
-        <v>6</v>
-      </c>
-      <c r="J67" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="K67" s="36" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="L67" s="34" t="inlineStr">
-        <is>
-          <t>SG-07 content (TX gate, block list) · per frame
-0 + 10 ms</t>
-        </is>
-      </c>
-      <c r="M67" s="33" t="inlineStr">
-        <is>
-          <t>code derived</t>
-        </is>
-      </c>
+          <t>Switch stuck in pass-through, or the SBU1 drive lost, held low or too low to change the switch over (5 V drive against VL = VIN)</t>
+        </is>
+      </c>
+      <c r="E67" s="64" t="inlineStr">
+        <is>
+          <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-011.C1)</t>
+        </is>
+      </c>
+      <c r="F67" s="34" t="inlineStr"/>
+      <c r="G67" s="34" t="inlineStr"/>
+      <c r="H67" s="35" t="inlineStr"/>
+      <c r="I67" s="35" t="inlineStr"/>
+      <c r="J67" s="35" t="inlineStr"/>
+      <c r="K67" s="33" t="inlineStr"/>
+      <c r="L67" s="34" t="inlineStr"/>
+      <c r="M67" s="33" t="inlineStr"/>
       <c r="N67" s="34" t="inlineStr"/>
       <c r="O67" s="37" t="inlineStr"/>
       <c r="P67" s="37" t="inlineStr"/>
@@ -23980,47 +24066,52 @@
       </c>
       <c r="C68" s="33" t="inlineStr">
         <is>
-          <t>SFM-035.C3</t>
+          <t>SFM-035.C1</t>
         </is>
       </c>
       <c r="D68" s="34" t="inlineStr">
         <is>
-          <t>The TX whitelist or the PRE_COLLISION content check lets a PCS-relevant frame through (table change, or a build that is not the reference build, where 0x411 is allowed by design)</t>
+          <t>Host code (car interface, pandad) emits a PCS-relevant ID or a non-zero PRE_COLLISION payload (QM fault)</t>
         </is>
       </c>
       <c r="E68" s="34" t="inlineStr">
         <is>
-          <t>None: the gate is itself the monitor that has failed; pandaTxBlocked counts only refused frames</t>
+          <t>The panda checks every frame from the SoC against the TX whitelist and the 0x283 zero-payload rule before it is sent</t>
         </is>
       </c>
       <c r="F68" s="34" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Frame refused, the stock PCS path is untouched; while engaged the refusal also gives pandaTxBlocked, an immediate disable with a take-over alert</t>
         </is>
       </c>
       <c r="G68" s="34" t="inlineStr">
         <is>
-          <t>Unchanged: the frame reaches the car while the SoC sends it</t>
+          <t>Stock PCS unaffected. While engaged the item disengages with an alert (controlled handback, S 8), the worst effect left after the response</t>
         </is>
       </c>
       <c r="H68" s="35" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I68" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J68" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="J68" s="46" t="n">
-        <v>10</v>
-      </c>
       <c r="K68" s="36" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="L68" s="34" t="inlineStr"/>
+      <c r="L68" s="34" t="inlineStr">
+        <is>
+          <t>SG-07 content (TX gate, block list) · per frame
+0 + 10 ms</t>
+        </is>
+      </c>
       <c r="M68" s="33" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>code derived</t>
         </is>
       </c>
       <c r="N68" s="34" t="inlineStr"/>
@@ -24030,7 +24121,7 @@
     <row r="69" ht="73.5" customHeight="1">
       <c r="A69" s="34" t="inlineStr">
         <is>
-          <t>SFM-036 · Item keeps requesting acceleration while stock PCS brakes</t>
+          <t>SFM-035 · Item sends a frame that alters the stock pre-collision function</t>
         </is>
       </c>
       <c r="B69" s="35" t="n">
@@ -24038,37 +24129,37 @@
       </c>
       <c r="C69" s="33" t="inlineStr">
         <is>
-          <t>SFM-036.C1</t>
+          <t>SFM-035.C3</t>
         </is>
       </c>
       <c r="D69" s="34" t="inlineStr">
         <is>
-          <t>The item has no reaction to a stock PCS event on its longitudinal command; controlsd keeps requesting the planner's acceleration (design gap, FTA BE-7.13)</t>
+          <t>The TX whitelist or the PRE_COLLISION content check lets a PCS-relevant frame through (table change, or a build that is not the reference build, where 0x411 is allowed by design)</t>
         </is>
       </c>
       <c r="E69" s="34" t="inlineStr">
         <is>
-          <t>stockAeb detects the PCS event from the stock camera's PRE_COLLISION frame and raises an alert</t>
+          <t>None: the gate is itself the monitor that has failed; pandaTxBlocked counts only refused frames</t>
         </is>
       </c>
       <c r="F69" s="34" t="inlineStr">
         <is>
-          <t>Alert only; the longitudinal request continues until the driver brakes (panda revokes on the brake press)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G69" s="34" t="inlineStr">
         <is>
-          <t>Unchanged unless the PCM gives PCS priority (AOU-04R): the item may still oppose stock braking</t>
+          <t>Unchanged: the frame reaches the car while the SoC sends it</t>
         </is>
       </c>
       <c r="H69" s="35" t="n">
         <v>10</v>
       </c>
       <c r="I69" s="35" t="n">
-        <v>8</v>
-      </c>
-      <c r="J69" s="35" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="J69" s="46" t="n">
+        <v>10</v>
       </c>
       <c r="K69" s="36" t="inlineStr">
         <is>
@@ -24081,15 +24172,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="N69" s="34" t="inlineStr">
-        <is>
-          <t>SFM-ACT-020 · decision pending</t>
-        </is>
-      </c>
+      <c r="N69" s="34" t="inlineStr"/>
       <c r="O69" s="37" t="inlineStr"/>
       <c r="P69" s="37" t="inlineStr"/>
     </row>
-    <row r="70" ht="46.5" customHeight="1">
+    <row r="70" ht="73.5" customHeight="1">
       <c r="A70" s="34" t="inlineStr">
         <is>
           <t>SFM-036 · Item keeps requesting acceleration while stock PCS brakes</t>
@@ -24100,37 +24187,37 @@
       </c>
       <c r="C70" s="33" t="inlineStr">
         <is>
-          <t>SFM-036.C2</t>
+          <t>SFM-036.C1</t>
         </is>
       </c>
       <c r="D70" s="34" t="inlineStr">
         <is>
-          <t>The PCM does not give stock PCS braking priority over the item's ACC_CONTROL request (AOU-04R not met)</t>
+          <t>The item has no reaction to a stock PCS event on its longitudinal command; controlsd keeps requesting the planner's acceleration (design gap, FTA BE-7.13)</t>
         </is>
       </c>
       <c r="E70" s="34" t="inlineStr">
         <is>
-          <t>None: the item cannot see how the PCM arbitrates</t>
+          <t>stockAeb detects the PCS event from the stock camera's PRE_COLLISION frame and raises an alert</t>
         </is>
       </c>
       <c r="F70" s="34" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Alert only; the longitudinal request continues until the driver brakes (panda revokes on the brake press)</t>
         </is>
       </c>
       <c r="G70" s="34" t="inlineStr">
         <is>
-          <t>Unchanged: stock braking reduced while the item requests acceleration</t>
+          <t>Unchanged unless the PCM gives PCS priority (AOU-04R): the item may still oppose stock braking</t>
         </is>
       </c>
       <c r="H70" s="35" t="n">
         <v>10</v>
       </c>
       <c r="I70" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="J70" s="46" t="n">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="J70" s="35" t="n">
+        <v>8</v>
       </c>
       <c r="K70" s="36" t="inlineStr">
         <is>
@@ -24151,10 +24238,10 @@
       <c r="O70" s="37" t="inlineStr"/>
       <c r="P70" s="37" t="inlineStr"/>
     </row>
-    <row r="71" ht="100.5" customHeight="1">
+    <row r="71" ht="46.5" customHeight="1">
       <c r="A71" s="34" t="inlineStr">
         <is>
-          <t>SFM-037 · Longitudinal command frozen at last value</t>
+          <t>SFM-036 · Item keeps requesting acceleration while stock PCS brakes</t>
         </is>
       </c>
       <c r="B71" s="35" t="n">
@@ -24162,48 +24249,44 @@
       </c>
       <c r="C71" s="33" t="inlineStr">
         <is>
-          <t>SFM-037.C1</t>
+          <t>SFM-036.C2</t>
         </is>
       </c>
       <c r="D71" s="34" t="inlineStr">
         <is>
-          <t>controlsd hangs while card keeps sending the last carControl</t>
+          <t>The PCM does not give stock PCS braking priority over the item's ACC_CONTROL request (AOU-04R not met)</t>
         </is>
       </c>
       <c r="E71" s="34" t="inlineStr">
         <is>
-          <t>card stops sending once carControl is 0.1 s old (T-13); the panda then revokes authority within 0.11 s of the last ACC_CONTROL frame (TSR-408, T-34) and selfdrived raises controlsMismatch within 0.5 s (TSR-621)</t>
+          <t>None: the item cannot see how the PCM arbitrates</t>
         </is>
       </c>
       <c r="F71" s="34" t="inlineStr">
         <is>
-          <t>controlsMismatch IMMEDIATE_DISABLE with alert; no ACC_CONTROL frame follows the stall and there is no active zero request (TSR-109), so what the PCM does with the last request after the frames stop is not known (AOU, not measured)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G71" s="34" t="inlineStr">
         <is>
-          <t>Last request held about 0.2 s, then frames stop; the PCM reaction to missing ACC_CONTROL is not established</t>
+          <t>Unchanged: stock braking reduced while the item requests acceleration</t>
         </is>
       </c>
       <c r="H71" s="35" t="n">
         <v>10</v>
       </c>
       <c r="I71" s="35" t="n">
-        <v>6</v>
-      </c>
-      <c r="J71" s="35" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="J71" s="46" t="n">
+        <v>10</v>
       </c>
       <c r="K71" s="36" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="L71" s="34" t="inlineStr">
-        <is>
-          <t>SG-03/04 · 1000 ms</t>
-        </is>
-      </c>
+      <c r="L71" s="34" t="inlineStr"/>
       <c r="M71" s="33" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -24211,13 +24294,13 @@
       </c>
       <c r="N71" s="34" t="inlineStr">
         <is>
-          <t>SFM-ACT-015 · in progress</t>
+          <t>SFM-ACT-020 · decision pending</t>
         </is>
       </c>
       <c r="O71" s="37" t="inlineStr"/>
       <c r="P71" s="37" t="inlineStr"/>
     </row>
-    <row r="72" ht="46.5" customHeight="1">
+    <row r="72" ht="100.5" customHeight="1">
       <c r="A72" s="34" t="inlineStr">
         <is>
           <t>SFM-037 · Longitudinal command frozen at last value</t>
@@ -24228,37 +24311,37 @@
       </c>
       <c r="C72" s="33" t="inlineStr">
         <is>
-          <t>SFM-037.C2</t>
+          <t>SFM-037.C1</t>
         </is>
       </c>
       <c r="D72" s="34" t="inlineStr">
         <is>
-          <t>plannerd stops or runs late while engaged, so controlsd keeps using the last longitudinalPlan</t>
+          <t>controlsd hangs while card keeps sending the last carControl</t>
         </is>
       </c>
       <c r="E72" s="34" t="inlineStr">
         <is>
-          <t>selfdrived liveness check on longitudinalPlan (10 missed periods at 20 Hz, 0.5 s, T-14)</t>
+          <t>card stops sending once carControl is 0.1 s old (T-13); the panda then revokes authority within 0.11 s of the last ACC_CONTROL frame (TSR-408, T-34) and selfdrived raises controlsMismatch within 0.5 s (TSR-621)</t>
         </is>
       </c>
       <c r="F72" s="34" t="inlineStr">
         <is>
-          <t>commIssue SOFT_DISABLE; actuation continues for the 3 s countdown (T-16) on the last plan</t>
+          <t>controlsMismatch IMMEDIATE_DISABLE with alert; no ACC_CONTROL frame follows the stall and there is no active zero request (TSR-109), so what the PCM does with the last request after the frames stop is not known (AOU, not measured)</t>
         </is>
       </c>
       <c r="G72" s="34" t="inlineStr">
         <is>
-          <t>Frozen request held up to about 3.5 s before the item disengages</t>
+          <t>Last request held about 0.2 s, then frames stop; the PCM reaction to missing ACC_CONTROL is not established</t>
         </is>
       </c>
       <c r="H72" s="35" t="n">
         <v>10</v>
       </c>
       <c r="I72" s="35" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J72" s="35" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K72" s="36" t="inlineStr">
         <is>
@@ -24267,13 +24350,12 @@
       </c>
       <c r="L72" s="34" t="inlineStr">
         <is>
-          <t>SG-03/04 · 1000 ms
-500 + 3000 ms</t>
+          <t>SG-03/04 · 1000 ms</t>
         </is>
       </c>
       <c r="M72" s="33" t="inlineStr">
         <is>
-          <t>code derived</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="N72" s="34" t="inlineStr">
@@ -24295,47 +24377,52 @@
       </c>
       <c r="C73" s="33" t="inlineStr">
         <is>
-          <t>SFM-037.C3</t>
+          <t>SFM-037.C2</t>
         </is>
       </c>
       <c r="D73" s="34" t="inlineStr">
         <is>
-          <t>Messaging delivers a stale longitudinal plan or command with fresh timestamps</t>
+          <t>plannerd stops or runs late while engaged, so controlsd keeps using the last longitudinalPlan</t>
         </is>
       </c>
       <c r="E73" s="34" t="inlineStr">
         <is>
-          <t>Liveness checks use arrival and timestamps, so stale data with fresh timestamps passes them</t>
+          <t>selfdrived liveness check on longitudinalPlan (10 missed periods at 20 Hz, 0.5 s, T-14)</t>
         </is>
       </c>
       <c r="F73" s="34" t="inlineStr">
         <is>
-          <t>None until another check trips</t>
+          <t>commIssue SOFT_DISABLE; actuation continues for the 3 s countdown (T-16) on the last plan</t>
         </is>
       </c>
       <c r="G73" s="34" t="inlineStr">
         <is>
-          <t>Unchanged: longitudinal control acts on stale data</t>
+          <t>Frozen request held up to about 3.5 s before the item disengages</t>
         </is>
       </c>
       <c r="H73" s="35" t="n">
         <v>10</v>
       </c>
       <c r="I73" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="J73" s="46" t="n">
-        <v>9</v>
+        <v>4</v>
+      </c>
+      <c r="J73" s="35" t="n">
+        <v>8</v>
       </c>
       <c r="K73" s="36" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="L73" s="34" t="inlineStr"/>
+      <c r="L73" s="34" t="inlineStr">
+        <is>
+          <t>SG-03/04 · 1000 ms
+500 + 3000 ms</t>
+        </is>
+      </c>
       <c r="M73" s="33" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>code derived</t>
         </is>
       </c>
       <c r="N73" s="34" t="inlineStr">
@@ -24346,10 +24433,10 @@
       <c r="O73" s="37" t="inlineStr"/>
       <c r="P73" s="37" t="inlineStr"/>
     </row>
-    <row r="74" ht="141" customHeight="1">
+    <row r="74" ht="46.5" customHeight="1">
       <c r="A74" s="34" t="inlineStr">
         <is>
-          <t>SFM-038 · Warning of a lateral-control fault or limit late, not escalated or missing</t>
+          <t>SFM-037 · Longitudinal command frozen at last value</t>
         </is>
       </c>
       <c r="B74" s="35" t="n">
@@ -24357,32 +24444,58 @@
       </c>
       <c r="C74" s="33" t="inlineStr">
         <is>
-          <t>SFM-038.C1</t>
+          <t>SFM-037.C3</t>
         </is>
       </c>
       <c r="D74" s="34" t="inlineStr">
         <is>
-          <t>After any driver steering input in the last 1.5 s, or at standstill, a temporary EPS fault raises only steerTempUnavailableSilent (a LOW-priority WARNING with a prompt chime and no soft disable, events.py:516-521), and it stays latched while the fault lasts, so a long fault never escalates to the take-over request (car_events.py:162-177; T-25, GAP-03)</t>
-        </is>
-      </c>
-      <c r="E74" s="64" t="inlineStr">
-        <is>
-          <t>Exempt: The cause is a defect of the warning path itself; its effect on detecting the lateral loss is rated in the MSR rows of SFM-004.C2 and SFM-005 (msr-plan §3)</t>
-        </is>
-      </c>
-      <c r="F74" s="34" t="inlineStr"/>
-      <c r="G74" s="34" t="inlineStr"/>
-      <c r="H74" s="35" t="inlineStr"/>
-      <c r="I74" s="35" t="inlineStr"/>
-      <c r="J74" s="35" t="inlineStr"/>
-      <c r="K74" s="33" t="inlineStr"/>
+          <t>Messaging delivers a stale longitudinal plan or command with fresh timestamps</t>
+        </is>
+      </c>
+      <c r="E74" s="34" t="inlineStr">
+        <is>
+          <t>Liveness checks use arrival and timestamps, so stale data with fresh timestamps passes them</t>
+        </is>
+      </c>
+      <c r="F74" s="34" t="inlineStr">
+        <is>
+          <t>None until another check trips</t>
+        </is>
+      </c>
+      <c r="G74" s="34" t="inlineStr">
+        <is>
+          <t>Unchanged: longitudinal control acts on stale data</t>
+        </is>
+      </c>
+      <c r="H74" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I74" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="J74" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="K74" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
       <c r="L74" s="34" t="inlineStr"/>
-      <c r="M74" s="33" t="inlineStr"/>
-      <c r="N74" s="34" t="inlineStr"/>
+      <c r="M74" s="33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N74" s="34" t="inlineStr">
+        <is>
+          <t>SFM-ACT-015 · in progress</t>
+        </is>
+      </c>
       <c r="O74" s="37" t="inlineStr"/>
       <c r="P74" s="37" t="inlineStr"/>
     </row>
-    <row r="75" ht="114" customHeight="1">
+    <row r="75" ht="141" customHeight="1">
       <c r="A75" s="34" t="inlineStr">
         <is>
           <t>SFM-038 · Warning of a lateral-control fault or limit late, not escalated or missing</t>
@@ -24393,17 +24506,17 @@
       </c>
       <c r="C75" s="33" t="inlineStr">
         <is>
-          <t>SFM-038.C2</t>
+          <t>SFM-038.C1</t>
         </is>
       </c>
       <c r="D75" s="34" t="inlineStr">
         <is>
-          <t>pandad publishes the panda fields epsFault and requestsRejected (pandad.cc:137-138), but no SoC process reads them (txRateExceeded is read, TSR-615), so a panda-side EPS-fault refusal reaches the driver only through the panda siren and the stock EPS path (SW FMEA SWF-025 notes)</t>
+          <t>After any driver steering input in the last 1.5 s, or at standstill, a temporary EPS fault raises only steerTempUnavailableSilent (a LOW-priority WARNING with a prompt chime and no soft disable, events.py:516-521), and it stays latched while the fault lasts, so a long fault never escalates to the take-over request (car_events.py:162-177; T-25, GAP-03)</t>
         </is>
       </c>
       <c r="E75" s="64" t="inlineStr">
         <is>
-          <t>Exempt: The cause is a defect of the warning path itself; the panda siren that remains is rated on SFM-005 and in the DFMEA (msr-plan §3)</t>
+          <t>Exempt: The cause is a defect of the warning path itself; its effect on detecting the lateral loss is rated in the MSR rows of SFM-004.C2 and SFM-005 (msr-plan §3)</t>
         </is>
       </c>
       <c r="F75" s="34" t="inlineStr"/>
@@ -24418,7 +24531,7 @@
       <c r="O75" s="37" t="inlineStr"/>
       <c r="P75" s="37" t="inlineStr"/>
     </row>
-    <row r="76" ht="127.5" customHeight="1">
+    <row r="76" ht="114" customHeight="1">
       <c r="A76" s="34" t="inlineStr">
         <is>
           <t>SFM-038 · Warning of a lateral-control fault or limit late, not escalated or missing</t>
@@ -24429,17 +24542,17 @@
       </c>
       <c r="C76" s="33" t="inlineStr">
         <is>
-          <t>SFM-038.C3</t>
+          <t>SFM-038.C2</t>
         </is>
       </c>
       <c r="D76" s="34" t="inlineStr">
         <is>
-          <t>steerSaturated needs the controller saturated, a desired lateral acceleration above 1.0 m/s², an undershoot above 1.2x and no steering input for 2 s (selfdrived.py:465-479), and the controller reports saturation only after 0.4 s (latcontrol.py, T-30); a gradual deficit therefore warns late or not at all (WP-S-04 §3.8.1)</t>
+          <t>pandad publishes the panda fields epsFault and requestsRejected (pandad.cc:137-138), but no SoC process reads them (txRateExceeded is read, TSR-615), so a panda-side EPS-fault refusal reaches the driver only through the panda siren and the stock EPS path (SW FMEA SWF-025 notes)</t>
         </is>
       </c>
       <c r="E76" s="64" t="inlineStr">
         <is>
-          <t>Exempt: The cause is the timing of the warning itself; it is rated as M 8 in the MSR rows of SFM-004.C1-C3 (rev 0.15, WP-S-04 §3.8.1)</t>
+          <t>Exempt: The cause is a defect of the warning path itself; the panda siren that remains is rated on SFM-005 and in the DFMEA (msr-plan §3)</t>
         </is>
       </c>
       <c r="F76" s="34" t="inlineStr"/>
@@ -24454,13 +24567,49 @@
       <c r="O76" s="37" t="inlineStr"/>
       <c r="P76" s="37" t="inlineStr"/>
     </row>
+    <row r="77" ht="127.5" customHeight="1">
+      <c r="A77" s="34" t="inlineStr">
+        <is>
+          <t>SFM-038 · Warning of a lateral-control fault or limit late, not escalated or missing</t>
+        </is>
+      </c>
+      <c r="B77" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C77" s="33" t="inlineStr">
+        <is>
+          <t>SFM-038.C3</t>
+        </is>
+      </c>
+      <c r="D77" s="34" t="inlineStr">
+        <is>
+          <t>steerSaturated needs the controller saturated, a desired lateral acceleration above 1.0 m/s², an undershoot above 1.2x and no steering input for 2 s (selfdrived.py:465-479), and the controller reports saturation only after 0.4 s (latcontrol.py, T-30); a gradual deficit therefore warns late or not at all (WP-S-04 §3.8.1)</t>
+        </is>
+      </c>
+      <c r="E77" s="64" t="inlineStr">
+        <is>
+          <t>Exempt: The cause is the timing of the warning itself; it is rated as M 8 in the MSR rows of SFM-004.C1-C3 (rev 0.15, WP-S-04 §3.8.1)</t>
+        </is>
+      </c>
+      <c r="F77" s="34" t="inlineStr"/>
+      <c r="G77" s="34" t="inlineStr"/>
+      <c r="H77" s="35" t="inlineStr"/>
+      <c r="I77" s="35" t="inlineStr"/>
+      <c r="J77" s="35" t="inlineStr"/>
+      <c r="K77" s="33" t="inlineStr"/>
+      <c r="L77" s="34" t="inlineStr"/>
+      <c r="M77" s="33" t="inlineStr"/>
+      <c r="N77" s="34" t="inlineStr"/>
+      <c r="O77" s="37" t="inlineStr"/>
+      <c r="P77" s="37" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:P76"/>
+  <autoFilter ref="A2:P77"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="O3 O4 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 O34 O35 O36 O37 O38 O39 O40 O41 O42 O43 O44 O45 O46 O47 O48 O49 O50 O51 O52 O53 O54 O55 O56 O57 O58 O59 O60 O61 O62 O63 O64 O65 O66 O67 O68 O69 O70 O71 O72 O73 O74 O75 O76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this MSR row" type="list">
+    <dataValidation sqref="O3 O4 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 O34 O35 O36 O37 O38 O39 O40 O41 O42 O43 O44 O45 O46 O47 O48 O49 O50 O51 O52 O53 O54 O55 O56 O57 O58 O59 O60 O61 O62 O63 O64 O65 O66 O67 O68 O69 O70 O71 O72 O73 O74 O75 O76 O77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this MSR row" type="list">
       <formula1>"Agree,Re-rate,Reject,Question"</formula1>
     </dataValidation>
   </dataValidations>
@@ -24468,7 +24617,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.25 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.26 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -823,7 +823,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.26 · draft</t>
+          <t>0.27 · draft</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>BL-005</t>
+          <t>BL-006</t>
         </is>
       </c>
     </row>
@@ -18015,7 +18015,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>After any driver steering input in the last 1.5 s, or at standstill, a temporary EPS fault raises only steerTempUnavailableSilent (a LOW-priority WARNING with a prompt chime and no soft disable, events.py:516-521), and it stays latched while the fault lasts, so a long fault never escalates to the take-over request (car_events.py:162-177; T-25, GAP-03)</t>
+            <t>The lighter EPS-fault prompt (steerTempUnavailableSilent, a LOW-priority WARNING with a chime and no soft disable, events.py:516-521) after a recent override, at standstill or while the driver steers is not limited to 1.5 s, so a long fault does not escalate to the take-over request (car_events.py:167-185, STEER_FAULT_SILENT_FRAMES; T-25, GAP-03). Until BL-005 the prompt was latched for the whole fault by design; from BL-006 the cause is a defect of the TSR-607 (b)/(c) frame counter</t>
           </r>
         </is>
       </c>
@@ -18027,7 +18027,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Upstream openpilot design choice (a softer alert after an override); no LionDriver requirement on it</t>
+            <t>• TSR-607 (b)/(c) implemented in car_events.py (#174, f350f5b; DQ-342 A, DQ-366 A): the lighter prompt is allowed for the first 150 frames of the fault only; ruff and ty in fork CI; impact record change-2026-10-17-eps-fault-escalation.md. Not reviewed independently</t>
           </r>
           <r>
             <rPr>
@@ -18041,22 +18041,31 @@
         </is>
       </c>
       <c r="J92" s="35" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K92" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• No LionDriver test targets this cause</t>
-          </r>
-        </is>
-      </c>
-      <c r="L92" s="46" t="n">
-        <v>10</v>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_steer_fault_warning.py (7 tests: silent window, no recent override, escalation after an override, at standstill, after releasing the wheel, a returning fault, a short fault while holding), run by the CI test runner; 4 of the #174 tests fail on the BL-005 code. Not proven by mutation; not verified on the vehicle (impact record OI-1)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/car/tests/test_steer_fault_warning.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L92" s="35" t="n">
+        <v>4</v>
       </c>
       <c r="M92" s="36" t="inlineStr">
         <is>
@@ -18521,7 +18530,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.26 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.27 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -19346,7 +19355,7 @@
       <c r="H22" s="60" t="inlineStr"/>
       <c r="I22" s="60" t="inlineStr"/>
     </row>
-    <row r="23" ht="141" customHeight="1">
+    <row r="23" ht="154.5" customHeight="1">
       <c r="A23" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-023</t>
@@ -19385,7 +19394,7 @@
       </c>
       <c r="I23" s="60" t="inlineStr">
         <is>
-          <t>Merged in jherrodthomas/LionDriver#174 (7158a9a): STEER_FAULT_SILENT_FRAMES in car_events.py limits the lighter prompt to the first 1.5 s of the fault; selfdrive/car/tests/test_steer_fault_warning.py, 6 tests run in CI, 4 of them fail on the old code. Impact record assurance/07-supporting/impact/change-2026-10-17-eps-fault-escalation.md. Unit-tested only: not verified on the vehicle (impact OI-1) and not reviewed independently. Not in BL-005, so SFM-038.C1 keeps O 8, D 10 until the next baseline; revised ratings below are a prediction (as SWF-ACT-025)</t>
+          <t>Merged in jherrodthomas/LionDriver#174 (7158a9a): STEER_FAULT_SILENT_FRAMES in car_events.py limits the lighter prompt to the first 1.5 s of the fault; selfdrive/car/tests/test_steer_fault_warning.py, 6 tests run in CI, 4 of them fail on the old code. Impact record assurance/07-supporting/impact/change-2026-10-17-eps-fault-escalation.md. Unit-tested only: not verified on the vehicle (impact OI-1) and not reviewed independently. Credited at BL-006 (System FMEA rev 0.27): SFM-038.C1 O 8 -&gt; 5, D 10 -&gt; 4, AP stays H (S 10); f350f5b adds TSR-607 (c) for a fault while the driver steers</t>
         </is>
       </c>
     </row>
@@ -24495,7 +24504,7 @@
       <c r="O74" s="37" t="inlineStr"/>
       <c r="P74" s="37" t="inlineStr"/>
     </row>
-    <row r="75" ht="141" customHeight="1">
+    <row r="75" ht="195" customHeight="1">
       <c r="A75" s="34" t="inlineStr">
         <is>
           <t>SFM-038 · Warning of a lateral-control fault or limit late, not escalated or missing</t>
@@ -24511,7 +24520,7 @@
       </c>
       <c r="D75" s="34" t="inlineStr">
         <is>
-          <t>After any driver steering input in the last 1.5 s, or at standstill, a temporary EPS fault raises only steerTempUnavailableSilent (a LOW-priority WARNING with a prompt chime and no soft disable, events.py:516-521), and it stays latched while the fault lasts, so a long fault never escalates to the take-over request (car_events.py:162-177; T-25, GAP-03)</t>
+          <t>The lighter EPS-fault prompt (steerTempUnavailableSilent, a LOW-priority WARNING with a chime and no soft disable, events.py:516-521) after a recent override, at standstill or while the driver steers is not limited to 1.5 s, so a long fault does not escalate to the take-over request (car_events.py:167-185, STEER_FAULT_SILENT_FRAMES; T-25, GAP-03). Until BL-005 the prompt was latched for the whole fault by design; from BL-006 the cause is a defect of the TSR-607 (b)/(c) frame counter</t>
         </is>
       </c>
       <c r="E75" s="64" t="inlineStr">
@@ -24617,7 +24626,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.26 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.27 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -823,7 +823,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.26 · draft</t>
+          <t>0.27 · draft</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>BL-005</t>
+          <t>BL-006</t>
         </is>
       </c>
     </row>
@@ -18015,7 +18015,16 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>After any driver steering input in the last 1.5 s, or at standstill, a temporary EPS fault raises only steerTempUnavailableSilent (a LOW-priority WARNING with a prompt chime and no soft disable, events.py:516-521), and it stays latched while the fault lasts, so a long fault never escalates to the take-over request (car_events.py:162-177; T-25, GAP-03)</t>
+            <t>The lighter EPS-fault prompt (steerTempUnavailableSilent, a LOW-priority WARNING with a chime and no soft disable, events.py:516-521) after a recent override, at standstill or while the driver steers is not limited to 1.5 s, so a long fault does not escalate to the take-over request (car_events.py:167-185, STEER_FAULT_SILENT_FRAMES; T-25, GAP-03). Until BL-005 the prompt was latched for the whole fault by design; from BL-006 the cause is a defect of the TSR-607 (b)/(c) frame counter</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+linked: SWF-088</t>
           </r>
         </is>
       </c>
@@ -18027,7 +18036,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Upstream openpilot design choice (a softer alert after an override); no LionDriver requirement on it</t>
+            <t>• TSR-607 (b)/(c) implemented in car_events.py (#174, f350f5b; DQ-342 A, DQ-366 A): the lighter prompt is allowed for the first 150 frames of the fault only; ruff and ty in fork CI; impact record change-2026-10-17-eps-fault-escalation.md. Not reviewed independently</t>
           </r>
           <r>
             <rPr>
@@ -18041,22 +18050,31 @@
         </is>
       </c>
       <c r="J92" s="35" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K92" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• No LionDriver test targets this cause</t>
-          </r>
-        </is>
-      </c>
-      <c r="L92" s="46" t="n">
-        <v>10</v>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_steer_fault_warning.py (7 tests: silent window, no recent override, escalation after an override, at standstill, after releasing the wheel, a returning fault, a short fault while holding), run by the CI test runner; 4 of the #174 tests fail on the BL-005 code. Not proven by mutation; not verified on the vehicle (impact record OI-1)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/car/tests/test_steer_fault_warning.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L92" s="35" t="n">
+        <v>4</v>
       </c>
       <c r="M92" s="36" t="inlineStr">
         <is>
@@ -18521,7 +18539,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.26 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.27 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -19346,7 +19364,7 @@
       <c r="H22" s="60" t="inlineStr"/>
       <c r="I22" s="60" t="inlineStr"/>
     </row>
-    <row r="23" ht="141" customHeight="1">
+    <row r="23" ht="154.5" customHeight="1">
       <c r="A23" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-023</t>
@@ -19385,7 +19403,7 @@
       </c>
       <c r="I23" s="60" t="inlineStr">
         <is>
-          <t>Merged in jherrodthomas/LionDriver#174 (7158a9a): STEER_FAULT_SILENT_FRAMES in car_events.py limits the lighter prompt to the first 1.5 s of the fault; selfdrive/car/tests/test_steer_fault_warning.py, 6 tests run in CI, 4 of them fail on the old code. Impact record assurance/07-supporting/impact/change-2026-10-17-eps-fault-escalation.md. Unit-tested only: not verified on the vehicle (impact OI-1) and not reviewed independently. Not in BL-005, so SFM-038.C1 keeps O 8, D 10 until the next baseline; revised ratings below are a prediction (as SWF-ACT-025)</t>
+          <t>Merged in jherrodthomas/LionDriver#174 (7158a9a): STEER_FAULT_SILENT_FRAMES in car_events.py limits the lighter prompt to the first 1.5 s of the fault; selfdrive/car/tests/test_steer_fault_warning.py, 6 tests run in CI, 4 of them fail on the old code. Impact record assurance/07-supporting/impact/change-2026-10-17-eps-fault-escalation.md. Unit-tested only: not verified on the vehicle (impact OI-1) and not reviewed independently. Credited at BL-006 (System FMEA rev 0.27): SFM-038.C1 O 8 -&gt; 5, D 10 -&gt; 4, AP stays H (S 10); f350f5b adds TSR-607 (c) for a fault while the driver steers</t>
         </is>
       </c>
     </row>
@@ -24495,7 +24513,7 @@
       <c r="O74" s="37" t="inlineStr"/>
       <c r="P74" s="37" t="inlineStr"/>
     </row>
-    <row r="75" ht="141" customHeight="1">
+    <row r="75" ht="195" customHeight="1">
       <c r="A75" s="34" t="inlineStr">
         <is>
           <t>SFM-038 · Warning of a lateral-control fault or limit late, not escalated or missing</t>
@@ -24511,7 +24529,7 @@
       </c>
       <c r="D75" s="34" t="inlineStr">
         <is>
-          <t>After any driver steering input in the last 1.5 s, or at standstill, a temporary EPS fault raises only steerTempUnavailableSilent (a LOW-priority WARNING with a prompt chime and no soft disable, events.py:516-521), and it stays latched while the fault lasts, so a long fault never escalates to the take-over request (car_events.py:162-177; T-25, GAP-03)</t>
+          <t>The lighter EPS-fault prompt (steerTempUnavailableSilent, a LOW-priority WARNING with a chime and no soft disable, events.py:516-521) after a recent override, at standstill or while the driver steers is not limited to 1.5 s, so a long fault does not escalate to the take-over request (car_events.py:167-185, STEER_FAULT_SILENT_FRAMES; T-25, GAP-03). Until BL-005 the prompt was latched for the whole fault by design; from BL-006 the cause is a defect of the TSR-607 (b)/(c) frame counter</t>
         </is>
       </c>
       <c r="E75" s="64" t="inlineStr">
@@ -24617,7 +24635,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.26 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.27 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -17853,7 +17853,7 @@
       <c r="R91" s="45" t="inlineStr"/>
       <c r="S91" s="45" t="inlineStr"/>
     </row>
-    <row r="92" ht="154.5" customHeight="1">
+    <row r="92" ht="168" customHeight="1">
       <c r="A92" s="30" t="inlineStr">
         <is>
           <r>
@@ -18060,7 +18060,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• test_steer_fault_warning.py (7 tests: silent window, no recent override, escalation after an override, at standstill, after releasing the wheel, a returning fault, a short fault while holding), run by the CI test runner; 4 of the #174 tests fail on the BL-005 code. Not proven by mutation; not verified on the vehicle (impact record OI-1)</t>
+            <t>• test_steer_fault_warning.py (7 tests: silent window, no recent override, escalation after an override, at standstill, after releasing the wheel, a returning fault, a short fault while holding), run by the CI test runner; 4 of the #174 tests fail on the BL-005 code. Targeted but not proven by mutation, so D 8 (RT-2); not verified on the vehicle (impact record OI-1)</t>
           </r>
           <r>
             <rPr>
@@ -18074,7 +18074,7 @@
         </is>
       </c>
       <c r="L92" s="35" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M92" s="36" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
       </c>
       <c r="P92" s="33" t="inlineStr">
         <is>
-          <t>10/5/4</t>
+          <t>10/5/8</t>
         </is>
       </c>
       <c r="Q92" s="36" t="inlineStr">
@@ -19364,7 +19364,7 @@
       <c r="H22" s="60" t="inlineStr"/>
       <c r="I22" s="60" t="inlineStr"/>
     </row>
-    <row r="23" ht="154.5" customHeight="1">
+    <row r="23" ht="195" customHeight="1">
       <c r="A23" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-023</t>
@@ -19393,7 +19393,7 @@
       </c>
       <c r="G23" s="60" t="inlineStr">
         <is>
-          <t>10/5/4</t>
+          <t>10/5/8</t>
         </is>
       </c>
       <c r="H23" s="62" t="inlineStr">
@@ -19403,7 +19403,7 @@
       </c>
       <c r="I23" s="60" t="inlineStr">
         <is>
-          <t>Merged in jherrodthomas/LionDriver#174 (7158a9a): STEER_FAULT_SILENT_FRAMES in car_events.py limits the lighter prompt to the first 1.5 s of the fault; selfdrive/car/tests/test_steer_fault_warning.py, 6 tests run in CI, 4 of them fail on the old code. Impact record assurance/07-supporting/impact/change-2026-10-17-eps-fault-escalation.md. Unit-tested only: not verified on the vehicle (impact OI-1) and not reviewed independently. Credited at BL-006 (System FMEA rev 0.27): SFM-038.C1 O 8 -&gt; 5, D 10 -&gt; 4, AP stays H (S 10); f350f5b adds TSR-607 (c) for a fault while the driver steers</t>
+          <t>Merged in jherrodthomas/LionDriver#174 (7158a9a): STEER_FAULT_SILENT_FRAMES in car_events.py limits the lighter prompt to the first 1.5 s of the fault; selfdrive/car/tests/test_steer_fault_warning.py, 6 tests run in CI, 4 of them fail on the old code. Impact record assurance/07-supporting/impact/change-2026-10-17-eps-fault-escalation.md. Unit-tested only: not verified on the vehicle (impact OI-1) and not reviewed independently. Credited at BL-006 (System FMEA rev 0.27): SFM-038.C1 O 8 -&gt; 5, D 10 -&gt; 8, AP stays H (S 10): the tests are targeted but not proven by mutation, so D 8 rather than the D 4 predicted below (rating tables D 8; a car_events.py mutation run, planned with SWF-ACT-077, would support D 4); f350f5b adds TSR-607 (c) for a fault while the driver steers</t>
         </is>
       </c>
     </row>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -823,7 +823,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.27 · draft</t>
+          <t>0.28 · draft</t>
         </is>
       </c>
     </row>
@@ -18539,7 +18539,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.27 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.28 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -24635,7 +24635,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.27 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.28 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -261,7 +261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -399,9 +399,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -823,7 +820,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.28 · draft</t>
+          <t>0.29 · draft</t>
         </is>
       </c>
     </row>
@@ -17033,7 +17030,7 @@
       <c r="R86" s="45" t="inlineStr"/>
       <c r="S86" s="45" t="inlineStr"/>
     </row>
-    <row r="87" ht="127.5" customHeight="1">
+    <row r="87" ht="141" customHeight="1">
       <c r="A87" s="30" t="inlineStr">
         <is>
           <r>
@@ -17261,13 +17258,13 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>React to a stock PCS event on the longitudinal command (for example a neutral or zero acceleration request, or a longitudinal disable, while stockAeb is set), so stock AEB does not depend on PCM arbitration alone (AOU-04R); or keep today's behaviour and rely on the AOU-04R vehicle test. Lead decision DQ-300</t>
-          </r>
-        </is>
-      </c>
-      <c r="O87" s="58" t="inlineStr">
-        <is>
-          <t>decision pending</t>
+            <t>Stand down during stock AEB: while the car reports a stock PCS/AEB event (stockAeb), LionDriver requests zero acceleration, so stock AEB does not depend on PCM arbitration alone (AOU-04R). Lead decision DQ-300, option A (2026-10-18); the AOU-04R vehicle test still runs. Code change with the implementation-spec session; not in BL-006, so SFM-036 keeps its ratings</t>
+          </r>
+        </is>
+      </c>
+      <c r="O87" s="47" t="inlineStr">
+        <is>
+          <t>open</t>
         </is>
       </c>
       <c r="P87" s="33" t="inlineStr"/>
@@ -18539,7 +18536,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.28 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.29 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -18569,79 +18566,79 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="59" t="inlineStr">
+      <c r="A1" s="58" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B1" s="59" t="inlineStr">
+      <c r="B1" s="58" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="C1" s="59" t="inlineStr">
+      <c r="C1" s="58" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" s="59" t="inlineStr">
+      <c r="D1" s="58" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E1" s="59" t="inlineStr">
+      <c r="E1" s="58" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="59" t="inlineStr">
+      <c r="F1" s="58" t="inlineStr">
         <is>
           <t>Causes</t>
         </is>
       </c>
-      <c r="G1" s="59" t="inlineStr">
+      <c r="G1" s="58" t="inlineStr">
         <is>
           <t>Revised S/O/D</t>
         </is>
       </c>
-      <c r="H1" s="59" t="inlineStr">
+      <c r="H1" s="58" t="inlineStr">
         <is>
           <t>Revised AP</t>
         </is>
       </c>
-      <c r="I1" s="59" t="inlineStr">
+      <c r="I1" s="58" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
     </row>
     <row r="2" ht="127.5" customHeight="1">
-      <c r="A2" s="60" t="inlineStr">
+      <c r="A2" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-001</t>
         </is>
       </c>
-      <c r="B2" s="60" t="inlineStr">
+      <c r="B2" s="59" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C2" s="60" t="inlineStr">
+      <c r="C2" s="59" t="inlineStr">
         <is>
           <t>Derive steering and acceleration envelopes from measurements on the reference vehicle and set the panda limits from them, independently of the SoC limits (same as SWF-ACT-003, FSC FOI-001)</t>
         </is>
       </c>
-      <c r="D2" s="60" t="inlineStr">
+      <c r="D2" s="59" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E2" s="60" t="inlineStr">
+      <c r="E2" s="59" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F2" s="60" t="inlineStr">
+      <c r="F2" s="59" t="inlineStr">
         <is>
           <t>SFM-002.C1
 SFM-002.C2
@@ -18654,37 +18651,37 @@
 SFM-029.C2</t>
         </is>
       </c>
-      <c r="G2" s="60" t="inlineStr"/>
-      <c r="H2" s="60" t="inlineStr"/>
-      <c r="I2" s="60" t="inlineStr"/>
+      <c r="G2" s="59" t="inlineStr"/>
+      <c r="H2" s="59" t="inlineStr"/>
+      <c r="I2" s="59" t="inlineStr"/>
     </row>
     <row r="3" ht="168" customHeight="1">
-      <c r="A3" s="60" t="inlineStr">
+      <c r="A3" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-002</t>
         </is>
       </c>
-      <c r="B3" s="60" t="inlineStr">
+      <c r="B3" s="59" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C3" s="60" t="inlineStr">
+      <c r="C3" s="59" t="inlineStr">
         <is>
           <t>Requirements-based tests for the host safety-relevant functions (selfdrived, controlsd, pandad, car interface, locationd bounds, monitoring policy), proven by mutation or fault injection and run as a CI gate (see SWF host actions)</t>
         </is>
       </c>
-      <c r="D3" s="60" t="inlineStr">
+      <c r="D3" s="59" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E3" s="60" t="inlineStr">
+      <c r="E3" s="59" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F3" s="60" t="inlineStr">
+      <c r="F3" s="59" t="inlineStr">
         <is>
           <t>SFM-002.C4
 SFM-004.C3
@@ -18700,37 +18697,37 @@
 SFM-037.C3</t>
         </is>
       </c>
-      <c r="G3" s="60" t="inlineStr"/>
-      <c r="H3" s="60" t="inlineStr"/>
-      <c r="I3" s="60" t="inlineStr"/>
+      <c r="G3" s="59" t="inlineStr"/>
+      <c r="H3" s="59" t="inlineStr"/>
+      <c r="I3" s="59" t="inlineStr"/>
     </row>
     <row r="4" ht="343.5" customHeight="1">
-      <c r="A4" s="60" t="inlineStr">
+      <c r="A4" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-003</t>
         </is>
       </c>
-      <c r="B4" s="60" t="inlineStr">
+      <c r="B4" s="59" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C4" s="60" t="inlineStr">
+      <c r="C4" s="59" t="inlineStr">
         <is>
           <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
         </is>
       </c>
-      <c r="D4" s="60" t="inlineStr">
+      <c r="D4" s="59" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E4" s="60" t="inlineStr">
+      <c r="E4" s="59" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F4" s="60" t="inlineStr">
+      <c r="F4" s="59" t="inlineStr">
         <is>
           <t>SFM-003.C1
 SFM-003.C2
@@ -18759,72 +18756,72 @@
 SFM-033.C3</t>
         </is>
       </c>
-      <c r="G4" s="60" t="inlineStr"/>
-      <c r="H4" s="60" t="inlineStr"/>
-      <c r="I4" s="60" t="inlineStr"/>
+      <c r="G4" s="59" t="inlineStr"/>
+      <c r="H4" s="59" t="inlineStr"/>
+      <c r="I4" s="59" t="inlineStr"/>
     </row>
     <row r="5" ht="154.5" customHeight="1">
-      <c r="A5" s="60" t="inlineStr">
+      <c r="A5" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-005</t>
         </is>
       </c>
-      <c r="B5" s="60" t="inlineStr">
+      <c r="B5" s="59" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C5" s="60" t="inlineStr">
+      <c r="C5" s="59" t="inlineStr">
         <is>
           <t>Implement the reaction when driver awareness reaches zero (driverUnresponsive3 / driverDistracted3 have no disable reaction at BL-004 or BL-005), the safe state of SG-010 (WP-C-03 SG-08, ASIL A; DQ-205). Decided by the lead (DQ-365, option A, 2026-10-16) and specified in TSR-633 (WP-S-02 v0.26) with TSR-611; keep the lane and decelerate in lane to a standstill with the terminal alert sounding, hold the vehicle stopped, and lock out re-engagement and resumption until the driver responds. WP-S-04 v0.12 §3.8.4 gives a preliminary time to the reaction (18 s vision, 30 s wheel-touch from loss of attention; OI-11); SFM-025.C1 is re-rated once TSR-633 is implemented and that time is confirmed</t>
         </is>
       </c>
-      <c r="D5" s="60" t="inlineStr">
+      <c r="D5" s="59" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E5" s="60" t="inlineStr">
+      <c r="E5" s="59" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F5" s="60" t="inlineStr">
+      <c r="F5" s="59" t="inlineStr">
         <is>
           <t>SFM-025.C1</t>
         </is>
       </c>
-      <c r="G5" s="60" t="inlineStr"/>
-      <c r="H5" s="60" t="inlineStr"/>
-      <c r="I5" s="60" t="inlineStr"/>
+      <c r="G5" s="59" t="inlineStr"/>
+      <c r="H5" s="59" t="inlineStr"/>
+      <c r="I5" s="59" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="60" t="inlineStr">
+      <c r="A6" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-006</t>
         </is>
       </c>
-      <c r="B6" s="60" t="inlineStr">
+      <c r="B6" s="59" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C6" s="60" t="inlineStr">
+      <c r="C6" s="59" t="inlineStr">
         <is>
           <t>Establish on the reference car which stock TSS2 functions (PCS/AEB, FCW) remain available with LionDriver installed and longitudinal control enabled, and verify the stock pre-collision path after installation (PFMEA PFM-014)</t>
         </is>
       </c>
-      <c r="D6" s="60" t="inlineStr">
+      <c r="D6" s="59" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E6" s="60" t="inlineStr">
+      <c r="E6" s="59" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F6" s="60" t="inlineStr">
+      <c r="F6" s="59" t="inlineStr">
         <is>
           <t>SFM-010.C2
 SFM-033.C1
@@ -18832,37 +18829,37 @@
 SFM-036.C2</t>
         </is>
       </c>
-      <c r="G6" s="60" t="inlineStr"/>
-      <c r="H6" s="60" t="inlineStr"/>
-      <c r="I6" s="60" t="inlineStr"/>
+      <c r="G6" s="59" t="inlineStr"/>
+      <c r="H6" s="59" t="inlineStr"/>
+      <c r="I6" s="59" t="inlineStr"/>
     </row>
     <row r="7" ht="73.5" customHeight="1">
-      <c r="A7" s="60" t="inlineStr">
+      <c r="A7" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-007</t>
         </is>
       </c>
-      <c r="B7" s="60" t="inlineStr">
+      <c r="B7" s="59" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C7" s="60" t="inlineStr">
+      <c r="C7" s="59" t="inlineStr">
         <is>
           <t>Supervise the alert channels: treat loss of ui or soundd liveness, or a stale displayed state, as a fault that escalates (audible fallback, disengagement) instead of continuing silently</t>
         </is>
       </c>
-      <c r="D7" s="60" t="inlineStr">
+      <c r="D7" s="59" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E7" s="60" t="inlineStr">
+      <c r="E7" s="59" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F7" s="60" t="inlineStr">
+      <c r="F7" s="59" t="inlineStr">
         <is>
           <t>SFM-015.C1
 SFM-026.C1
@@ -18871,76 +18868,76 @@
 SFM-028.C1</t>
         </is>
       </c>
-      <c r="G7" s="60" t="inlineStr"/>
-      <c r="H7" s="60" t="inlineStr"/>
-      <c r="I7" s="60" t="inlineStr"/>
+      <c r="G7" s="59" t="inlineStr"/>
+      <c r="H7" s="59" t="inlineStr"/>
+      <c r="I7" s="59" t="inlineStr"/>
     </row>
     <row r="8" ht="73.5" customHeight="1">
-      <c r="A8" s="60" t="inlineStr">
+      <c r="A8" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-008</t>
         </is>
       </c>
-      <c r="B8" s="60" t="inlineStr">
+      <c r="B8" s="59" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C8" s="60" t="inlineStr">
+      <c r="C8" s="59" t="inlineStr">
         <is>
           <t>Allow engagement only when the fingerprint, CarParams and panda safety parameter match the reference configuration AC-001 (refuse fuzzy matches in the reference build); see PFMEA PFM-013</t>
         </is>
       </c>
-      <c r="D8" s="60" t="inlineStr">
+      <c r="D8" s="59" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E8" s="60" t="inlineStr">
+      <c r="E8" s="59" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F8" s="60" t="inlineStr">
+      <c r="F8" s="59" t="inlineStr">
         <is>
           <t>SFM-032.C1</t>
         </is>
       </c>
-      <c r="G8" s="60" t="inlineStr"/>
-      <c r="H8" s="60" t="inlineStr"/>
-      <c r="I8" s="60" t="inlineStr">
+      <c r="G8" s="59" t="inlineStr"/>
+      <c r="H8" s="59" t="inlineStr"/>
+      <c r="I8" s="59" t="inlineStr">
         <is>
           <t>BL-005: the reference build is the default (LionDriver #36), the panda accepts only TOYOTA parameter 73 (reference_lock.h) and pandad configures a car mode only on a reference panda (#41). Fuzzy fingerprint matches are still accepted on the host (SFM-032.C1)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="100.5" customHeight="1">
-      <c r="A9" s="60" t="inlineStr">
+      <c r="A9" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-009</t>
         </is>
       </c>
-      <c r="B9" s="60" t="inlineStr">
+      <c r="B9" s="59" t="inlineStr">
         <is>
           <t>prevention</t>
         </is>
       </c>
-      <c r="C9" s="60" t="inlineStr">
+      <c r="C9" s="59" t="inlineStr">
         <is>
           <t>Produce SOTIF / ISO PAS 8800 evidence for the neural-network elements (driving model, lead detection, driver monitoring model) per WP-V-02..04, including fault-induced inputs (corrupted or stale frames)</t>
         </is>
       </c>
-      <c r="D9" s="60" t="inlineStr">
+      <c r="D9" s="59" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E9" s="60" t="inlineStr">
+      <c r="E9" s="59" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F9" s="60" t="inlineStr">
+      <c r="F9" s="59" t="inlineStr">
         <is>
           <t>SFM-002.C2
 SFM-003.C3
@@ -18951,37 +18948,37 @@
 SFM-022.C2</t>
         </is>
       </c>
-      <c r="G9" s="60" t="inlineStr"/>
-      <c r="H9" s="60" t="inlineStr"/>
-      <c r="I9" s="60" t="inlineStr"/>
+      <c r="G9" s="59" t="inlineStr"/>
+      <c r="H9" s="59" t="inlineStr"/>
+      <c r="I9" s="59" t="inlineStr"/>
     </row>
     <row r="10" ht="73.5" customHeight="1">
-      <c r="A10" s="60" t="inlineStr">
+      <c r="A10" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-010</t>
         </is>
       </c>
-      <c r="B10" s="60" t="inlineStr">
+      <c r="B10" s="59" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C10" s="60" t="inlineStr">
+      <c r="C10" s="59" t="inlineStr">
         <is>
           <t>Justify every SOFT_DISABLE reaction and debounce against the FTTI (WP-S-04) and alert at once when the panda withdraws authority while engaged (controlsMismatch debounce)</t>
         </is>
       </c>
-      <c r="D10" s="60" t="inlineStr">
+      <c r="D10" s="59" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E10" s="60" t="inlineStr">
+      <c r="E10" s="59" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F10" s="60" t="inlineStr">
+      <c r="F10" s="59" t="inlineStr">
         <is>
           <t>SFM-014.C2
 SFM-015.C2
@@ -18989,454 +18986,454 @@
 SFM-016.C2</t>
         </is>
       </c>
-      <c r="G10" s="60" t="inlineStr"/>
-      <c r="H10" s="60" t="inlineStr"/>
-      <c r="I10" s="60" t="inlineStr">
+      <c r="G10" s="59" t="inlineStr"/>
+      <c r="H10" s="59" t="inlineStr"/>
+      <c r="I10" s="59" t="inlineStr">
         <is>
           <t>controlsMismatch debounce cut from 200 cumulative samples (~2 s) to 2 consecutive samples, at most 0.5 s (change-2026-10-13-host-supervision.md); credited at BL-005 (SFM-015.C2 M 6). FTTI justification of SOFT_DISABLE reactions open</t>
         </is>
       </c>
     </row>
     <row r="11" ht="33" customHeight="1">
-      <c r="A11" s="60" t="inlineStr">
+      <c r="A11" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-011</t>
         </is>
       </c>
-      <c r="B11" s="60" t="inlineStr">
+      <c r="B11" s="59" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C11" s="60" t="inlineStr">
+      <c r="C11" s="59" t="inlineStr">
         <is>
           <t>Alert the driver when stock cruise stays engaged while the item is disengaged (cruiseMismatch has no alert at BL-004)</t>
         </is>
       </c>
-      <c r="D11" s="60" t="inlineStr">
+      <c r="D11" s="59" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E11" s="61" t="inlineStr">
+      <c r="E11" s="60" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F11" s="60" t="inlineStr">
+      <c r="F11" s="59" t="inlineStr">
         <is>
           <t>SFM-021.C1
 SFM-021.C2</t>
         </is>
       </c>
-      <c r="G11" s="60" t="inlineStr"/>
-      <c r="H11" s="60" t="inlineStr"/>
-      <c r="I11" s="60" t="inlineStr">
+      <c r="G11" s="59" t="inlineStr"/>
+      <c r="H11" s="59" t="inlineStr"/>
+      <c r="I11" s="59" t="inlineStr">
         <is>
           <t>cruiseMismatch now alerts after 1 s (change-2026-10-13-host-supervision.md); see SWF-ACT-034</t>
         </is>
       </c>
     </row>
     <row r="12" ht="73.5" customHeight="1">
-      <c r="A12" s="60" t="inlineStr">
+      <c r="A12" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-012</t>
         </is>
       </c>
-      <c r="B12" s="60" t="inlineStr">
+      <c r="B12" s="59" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C12" s="60" t="inlineStr">
+      <c r="C12" s="59" t="inlineStr">
         <is>
           <t>Measure on the HIL bench and the reference car (WP-V-05) how the panda reacts to over-limit and not-engaged steering and acceleration frames and to driver brake, gas and cancel inputs, and what the EPS and PCM do when frames are refused; re-rate the MSR rows from code-derived to measured timing</t>
         </is>
       </c>
-      <c r="D12" s="60" t="inlineStr"/>
-      <c r="E12" s="60" t="inlineStr">
+      <c r="D12" s="59" t="inlineStr"/>
+      <c r="E12" s="59" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F12" s="60" t="inlineStr"/>
-      <c r="G12" s="60" t="inlineStr"/>
-      <c r="H12" s="60" t="inlineStr"/>
-      <c r="I12" s="60" t="inlineStr"/>
+      <c r="F12" s="59" t="inlineStr"/>
+      <c r="G12" s="59" t="inlineStr"/>
+      <c r="H12" s="59" t="inlineStr"/>
+      <c r="I12" s="59" t="inlineStr"/>
     </row>
     <row r="13" ht="87" customHeight="1">
-      <c r="A13" s="60" t="inlineStr">
+      <c r="A13" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-013</t>
         </is>
       </c>
-      <c r="B13" s="60" t="inlineStr">
+      <c r="B13" s="59" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C13" s="60" t="inlineStr">
+      <c r="C13" s="59" t="inlineStr">
         <is>
           <t>Check on the host, within the SG-01 FTTI, that the panda reports controls_allowed false while the item is disengaged (the reverse of the controlsMismatch check, which at BL-005 still covers only engaged with authority withdrawn), with a disable and an alert. The requirement is TSR-630, within 0.3 s (WP-S-02 §12.3a; WP-S-04 T-32, not implemented)</t>
         </is>
       </c>
-      <c r="D13" s="60" t="inlineStr"/>
-      <c r="E13" s="60" t="inlineStr">
+      <c r="D13" s="59" t="inlineStr"/>
+      <c r="E13" s="59" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F13" s="60" t="inlineStr"/>
-      <c r="G13" s="60" t="inlineStr"/>
-      <c r="H13" s="60" t="inlineStr"/>
-      <c r="I13" s="60" t="inlineStr"/>
+      <c r="F13" s="59" t="inlineStr"/>
+      <c r="G13" s="59" t="inlineStr"/>
+      <c r="H13" s="59" t="inlineStr"/>
+      <c r="I13" s="59" t="inlineStr"/>
     </row>
     <row r="14" ht="46.5" customHeight="1">
-      <c r="A14" s="60" t="inlineStr">
+      <c r="A14" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-014</t>
         </is>
       </c>
-      <c r="B14" s="60" t="inlineStr">
+      <c r="B14" s="59" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C14" s="60" t="inlineStr">
+      <c r="C14" s="59" t="inlineStr">
         <is>
           <t>Specify in the TSC a steering-direction plausibility monitor (commanded torque sign against measured yaw rate and lane-relative lateral motion), or justify its absence against HZ-003</t>
         </is>
       </c>
-      <c r="D14" s="60" t="inlineStr"/>
-      <c r="E14" s="60" t="inlineStr">
+      <c r="D14" s="59" t="inlineStr"/>
+      <c r="E14" s="59" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F14" s="60" t="inlineStr"/>
-      <c r="G14" s="60" t="inlineStr"/>
-      <c r="H14" s="60" t="inlineStr"/>
-      <c r="I14" s="60" t="inlineStr"/>
+      <c r="F14" s="59" t="inlineStr"/>
+      <c r="G14" s="59" t="inlineStr"/>
+      <c r="H14" s="59" t="inlineStr"/>
+      <c r="I14" s="59" t="inlineStr"/>
     </row>
     <row r="15" ht="100.5" customHeight="1">
-      <c r="A15" s="60" t="inlineStr">
+      <c r="A15" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-015</t>
         </is>
       </c>
-      <c r="B15" s="60" t="inlineStr">
+      <c r="B15" s="59" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C15" s="60" t="inlineStr">
+      <c r="C15" s="59" t="inlineStr">
         <is>
           <t>Detect stale commands and inputs within the SG-01 FTTI: command-frame freshness in the MCU with an active zero frame (TSR-408, TSR-109) and frozen-content and age checks on model outputs in controlsd (TSR-602, TSR-631, AIR-17)</t>
         </is>
       </c>
-      <c r="D15" s="60" t="inlineStr"/>
-      <c r="E15" s="60" t="inlineStr">
+      <c r="D15" s="59" t="inlineStr"/>
+      <c r="E15" s="59" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F15" s="60" t="inlineStr"/>
-      <c r="G15" s="60" t="inlineStr"/>
-      <c r="H15" s="60" t="inlineStr"/>
-      <c r="I15" s="60" t="inlineStr">
+      <c r="F15" s="59" t="inlineStr"/>
+      <c r="G15" s="59" t="inlineStr"/>
+      <c r="H15" s="59" t="inlineStr"/>
+      <c r="I15" s="59" t="inlineStr">
         <is>
           <t>BL-005: command-frame arrival in the MCU (TSR-408, 50 ms STEERING_LKA, reference build by default) and input age checks in controlsd (TSR-602) are in. Open: the active zero frame (TSR-109), a frozen-content check on model outputs, and stale data with fresh timestamps (SFM-006.C1 to C3). The frozen-content check is TSR-631, with the age taken from the source timestamp (WP-S-02 §12.3a)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="73.5" customHeight="1">
-      <c r="A16" s="60" t="inlineStr">
+      <c r="A16" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-016</t>
         </is>
       </c>
-      <c r="B16" s="60" t="inlineStr">
+      <c r="B16" s="59" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C16" s="60" t="inlineStr">
+      <c r="C16" s="59" t="inlineStr">
         <is>
           <t>Supervise driver override in the panda: driver steering torque above the override threshold limits or revokes lateral authority within the SG-05 0.2 s budget (TSR-304). Behaviour decided by the lead (DQ-053, option A): back off on override and show a cue. Requirements: TSR-304 (timing tied to the SG-05 budget) and TSR-628 (WP-S-02 §12.3a)</t>
         </is>
       </c>
-      <c r="D16" s="60" t="inlineStr"/>
-      <c r="E16" s="60" t="inlineStr">
+      <c r="D16" s="59" t="inlineStr"/>
+      <c r="E16" s="59" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F16" s="60" t="inlineStr">
+      <c r="F16" s="59" t="inlineStr">
         <is>
           <t>SFM-018.C3</t>
         </is>
       </c>
-      <c r="G16" s="60" t="inlineStr"/>
-      <c r="H16" s="60" t="inlineStr"/>
-      <c r="I16" s="60" t="inlineStr"/>
+      <c r="G16" s="59" t="inlineStr"/>
+      <c r="H16" s="59" t="inlineStr"/>
+      <c r="I16" s="59" t="inlineStr"/>
     </row>
     <row r="17" ht="87" customHeight="1">
-      <c r="A17" s="60" t="inlineStr">
+      <c r="A17" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-017</t>
         </is>
       </c>
-      <c r="B17" s="60" t="inlineStr">
+      <c r="B17" s="59" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C17" s="60" t="inlineStr">
+      <c r="C17" s="59" t="inlineStr">
         <is>
           <t>Add WP-S-04 FTTI rows for the warning paths without one (insufficient lateral control, late or insufficient braking warnings, SG-008 unintended engagement, driver monitoring), so these mechanisms can be compared with a time budget</t>
         </is>
       </c>
-      <c r="D17" s="60" t="inlineStr"/>
-      <c r="E17" s="61" t="inlineStr">
+      <c r="D17" s="59" t="inlineStr"/>
+      <c r="E17" s="60" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F17" s="60" t="inlineStr"/>
-      <c r="G17" s="60" t="inlineStr"/>
-      <c r="H17" s="60" t="inlineStr"/>
-      <c r="I17" s="60" t="inlineStr">
+      <c r="F17" s="59" t="inlineStr"/>
+      <c r="G17" s="59" t="inlineStr"/>
+      <c r="H17" s="59" t="inlineStr"/>
+      <c r="I17" s="59" t="inlineStr">
         <is>
           <t>WP-S-04 v0.7 §3.7 (four rows) and §3.8, with T-30 to T-33. Rev 0.15 compares SFM-004, SFM-010.C2/C3, SFM-012.C1 and SFM-013.C1/C2 with them. Driver monitoring (SFM-022.C3, SFM-025.C1) waits for the H-09 FTTI (§3.8.4); follow-up is SFM-ACT-005. Late warnings found: SFM-ACT-021 (lateral) and SFM-ACT-022 (braking)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="100.5" customHeight="1">
-      <c r="A18" s="60" t="inlineStr">
+      <c r="A18" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-018</t>
         </is>
       </c>
-      <c r="B18" s="60" t="inlineStr">
+      <c r="B18" s="59" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C18" s="60" t="inlineStr">
+      <c r="C18" s="59" t="inlineStr">
         <is>
           <t>Detect silent loss of the actuation path: report forwarded and refused TX frames from the panda, and compare EPS and PCM acceptance (LKA_STATE, ACC status) with the commands, warning within the SG-02/06 1 s budget</t>
         </is>
       </c>
-      <c r="D18" s="60" t="inlineStr"/>
-      <c r="E18" s="60" t="inlineStr">
+      <c r="D18" s="59" t="inlineStr"/>
+      <c r="E18" s="59" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F18" s="60" t="inlineStr"/>
-      <c r="G18" s="60" t="inlineStr"/>
-      <c r="H18" s="60" t="inlineStr"/>
-      <c r="I18" s="60" t="inlineStr">
+      <c r="F18" s="59" t="inlineStr"/>
+      <c r="G18" s="59" t="inlineStr"/>
+      <c r="H18" s="59" t="inlineStr"/>
+      <c r="I18" s="59" t="inlineStr">
         <is>
           <t>BL-005: frames that stop reaching the panda are detected (TSR-408) and alerted within 0.5 s (TSR-621), credited on SFM-005.C2 and SFM-011.C2. Open: frames that reach the panda but are not accepted by the EPS or PCM (SFM-005.C1, SFM-011.C1). Requirements: TSR-632 (per-ID transmitted and refused counts), TSR-626(d)/(e) (EPS and PCM acceptance status) and TSR-615, warning within 1 s (WP-S-02 §12.3a)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="60" t="inlineStr">
+      <c r="A19" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-019</t>
         </is>
       </c>
-      <c r="B19" s="60" t="inlineStr">
+      <c r="B19" s="59" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C19" s="60" t="inlineStr">
+      <c r="C19" s="59" t="inlineStr">
         <is>
           <t>Revoke lateral authority in the panda when it rejects a steering frame while authority is granted, and keep it revoked until a new valid engagement (TSR-108; lead decision DQ-060, option A). At BL-005 the frame is dropped and only the host disengages (pandaTxBlocked)</t>
         </is>
       </c>
-      <c r="D19" s="60" t="inlineStr"/>
-      <c r="E19" s="60" t="inlineStr">
+      <c r="D19" s="59" t="inlineStr"/>
+      <c r="E19" s="59" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F19" s="60" t="inlineStr">
+      <c r="F19" s="59" t="inlineStr">
         <is>
           <t>SFM-002.C1
 SFM-002.C2
 SFM-002.C4</t>
         </is>
       </c>
-      <c r="G19" s="60" t="inlineStr"/>
-      <c r="H19" s="60" t="inlineStr"/>
-      <c r="I19" s="60" t="inlineStr"/>
+      <c r="G19" s="59" t="inlineStr"/>
+      <c r="H19" s="59" t="inlineStr"/>
+      <c r="I19" s="59" t="inlineStr"/>
     </row>
-    <row r="20" ht="73.5" customHeight="1">
-      <c r="A20" s="60" t="inlineStr">
+    <row r="20" ht="87" customHeight="1">
+      <c r="A20" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-020</t>
         </is>
       </c>
-      <c r="B20" s="60" t="inlineStr">
+      <c r="B20" s="59" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C20" s="60" t="inlineStr">
-        <is>
-          <t>React to a stock PCS event on the longitudinal command (for example a neutral or zero acceleration request, or a longitudinal disable, while stockAeb is set), so stock AEB does not depend on PCM arbitration alone (AOU-04R); or keep today's behaviour and rely on the AOU-04R vehicle test. Lead decision DQ-300</t>
-        </is>
-      </c>
-      <c r="D20" s="60" t="inlineStr"/>
-      <c r="E20" s="60" t="inlineStr">
-        <is>
-          <t>decision pending</t>
-        </is>
-      </c>
-      <c r="F20" s="60" t="inlineStr">
+      <c r="C20" s="59" t="inlineStr">
+        <is>
+          <t>Stand down during stock AEB: while the car reports a stock PCS/AEB event (stockAeb), LionDriver requests zero acceleration, so stock AEB does not depend on PCM arbitration alone (AOU-04R). Lead decision DQ-300, option A (2026-10-18); the AOU-04R vehicle test still runs. Code change with the implementation-spec session; not in BL-006, so SFM-036 keeps its ratings</t>
+        </is>
+      </c>
+      <c r="D20" s="59" t="inlineStr"/>
+      <c r="E20" s="59" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F20" s="59" t="inlineStr">
         <is>
           <t>SFM-036.C1</t>
         </is>
       </c>
-      <c r="G20" s="60" t="inlineStr"/>
-      <c r="H20" s="60" t="inlineStr"/>
-      <c r="I20" s="60" t="inlineStr"/>
+      <c r="G20" s="59" t="inlineStr"/>
+      <c r="H20" s="59" t="inlineStr"/>
+      <c r="I20" s="59" t="inlineStr"/>
     </row>
     <row r="21" ht="73.5" customHeight="1">
-      <c r="A21" s="60" t="inlineStr">
+      <c r="A21" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-021</t>
         </is>
       </c>
-      <c r="B21" s="60" t="inlineStr">
+      <c r="B21" s="59" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C21" s="60" t="inlineStr">
+      <c r="C21" s="59" t="inlineStr">
         <is>
           <t>Make the insufficient-lateral-control warning timely (WP-S-04 §3.8.1): warn before the deficit has lasted 0.4 s, for example from the planned curvature against the envelope, or keep the deficit at or below about 0.5 m/s² through the steering limits and the ODD curve bound (WP-S-04 OI-2). A change to the ODD bound is a lead decision</t>
         </is>
       </c>
-      <c r="D21" s="60" t="inlineStr"/>
-      <c r="E21" s="60" t="inlineStr">
+      <c r="D21" s="59" t="inlineStr"/>
+      <c r="E21" s="59" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F21" s="60" t="inlineStr">
+      <c r="F21" s="59" t="inlineStr">
         <is>
           <t>SFM-038.C3</t>
         </is>
       </c>
-      <c r="G21" s="60" t="inlineStr"/>
-      <c r="H21" s="60" t="inlineStr"/>
-      <c r="I21" s="60" t="inlineStr"/>
+      <c r="G21" s="59" t="inlineStr"/>
+      <c r="H21" s="59" t="inlineStr"/>
+      <c r="I21" s="59" t="inlineStr"/>
     </row>
     <row r="22" ht="60" customHeight="1">
-      <c r="A22" s="60" t="inlineStr">
+      <c r="A22" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-022</t>
         </is>
       </c>
-      <c r="B22" s="60" t="inlineStr">
+      <c r="B22" s="59" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C22" s="60" t="inlineStr">
+      <c r="C22" s="59" t="inlineStr">
         <is>
           <t>Measure the FCW onset after a lead brakes hard (WP-S-04 T-31, M-12) and compare it with the §3.8.2 budget (about 0.6 s at a 1.0 s gap). For pipeline lag (SFM-012.C1), detect it within that budget or show that the FCW path does not depend on the lagging process</t>
         </is>
       </c>
-      <c r="D22" s="60" t="inlineStr"/>
-      <c r="E22" s="60" t="inlineStr">
+      <c r="D22" s="59" t="inlineStr"/>
+      <c r="E22" s="59" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F22" s="60" t="inlineStr"/>
-      <c r="G22" s="60" t="inlineStr"/>
-      <c r="H22" s="60" t="inlineStr"/>
-      <c r="I22" s="60" t="inlineStr"/>
+      <c r="F22" s="59" t="inlineStr"/>
+      <c r="G22" s="59" t="inlineStr"/>
+      <c r="H22" s="59" t="inlineStr"/>
+      <c r="I22" s="59" t="inlineStr"/>
     </row>
     <row r="23" ht="195" customHeight="1">
-      <c r="A23" s="60" t="inlineStr">
+      <c r="A23" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-023</t>
         </is>
       </c>
-      <c r="B23" s="60" t="inlineStr">
+      <c r="B23" s="59" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C23" s="60" t="inlineStr">
+      <c r="C23" s="59" t="inlineStr">
         <is>
           <t>Escalate a temporary EPS fault that lasts while engaged to the take-over request (steerTempUnavailable, SOFT_DISABLE) instead of keeping the low-priority steerTempUnavailableSilent prompt latched after a recent override or at standstill (car_events.py; lead decision DQ-342, option A: the lighter prompt for at most 1.5 s, then the take-over request; TSR-607 (b)). SFM-038.C1; FTA BE-2.08</t>
         </is>
       </c>
-      <c r="D23" s="60" t="inlineStr"/>
-      <c r="E23" s="61" t="inlineStr">
+      <c r="D23" s="59" t="inlineStr"/>
+      <c r="E23" s="60" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F23" s="60" t="inlineStr">
+      <c r="F23" s="59" t="inlineStr">
         <is>
           <t>SFM-038.C1</t>
         </is>
       </c>
-      <c r="G23" s="60" t="inlineStr">
+      <c r="G23" s="59" t="inlineStr">
         <is>
           <t>10/5/8</t>
         </is>
       </c>
-      <c r="H23" s="62" t="inlineStr">
+      <c r="H23" s="61" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="I23" s="60" t="inlineStr">
+      <c r="I23" s="59" t="inlineStr">
         <is>
           <t>Merged in jherrodthomas/LionDriver#174 (7158a9a): STEER_FAULT_SILENT_FRAMES in car_events.py limits the lighter prompt to the first 1.5 s of the fault; selfdrive/car/tests/test_steer_fault_warning.py, 6 tests run in CI, 4 of them fail on the old code. Impact record assurance/07-supporting/impact/change-2026-10-17-eps-fault-escalation.md. Unit-tested only: not verified on the vehicle (impact OI-1) and not reviewed independently. Credited at BL-006 (System FMEA rev 0.27): SFM-038.C1 O 8 -&gt; 5, D 10 -&gt; 8, AP stays H (S 10): the tests are targeted but not proven by mutation, so D 8 rather than the D 4 predicted below (rating tables D 8; a car_events.py mutation run, planned with SWF-ACT-077, would support D 4); f350f5b adds TSR-607 (c) for a fault while the driver steers</t>
         </is>
       </c>
     </row>
     <row r="24" ht="87" customHeight="1">
-      <c r="A24" s="60" t="inlineStr">
+      <c r="A24" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-024</t>
         </is>
       </c>
-      <c r="B24" s="60" t="inlineStr">
+      <c r="B24" s="59" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C24" s="60" t="inlineStr">
+      <c r="C24" s="59" t="inlineStr">
         <is>
           <t>Act on the panda fields epsFault and requestsRejected on the host (TSR-626(d), TSR-516(b)): raise the take-over request when the panda reports an EPS fault or refused steering frames while lateral control is engaged, within the SG-02 1 s budget, instead of relying on the panda siren alone. Split from SFM-ACT-023 (rev 0.25). SFM-038.C2; FTA BE-2.08</t>
         </is>
       </c>
-      <c r="D24" s="60" t="inlineStr"/>
-      <c r="E24" s="60" t="inlineStr">
+      <c r="D24" s="59" t="inlineStr"/>
+      <c r="E24" s="59" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F24" s="60" t="inlineStr">
+      <c r="F24" s="59" t="inlineStr">
         <is>
           <t>SFM-038.C2</t>
         </is>
       </c>
-      <c r="G24" s="60" t="inlineStr"/>
-      <c r="H24" s="60" t="inlineStr"/>
-      <c r="I24" s="60" t="inlineStr"/>
+      <c r="G24" s="59" t="inlineStr"/>
+      <c r="H24" s="59" t="inlineStr"/>
+      <c r="I24" s="59" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I24"/>
@@ -19461,50 +19458,50 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="59" t="inlineStr">
+      <c r="A1" s="58" t="inlineStr">
         <is>
           <t>Element</t>
         </is>
       </c>
-      <c r="B1" s="59" t="inlineStr">
+      <c r="B1" s="58" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="59" t="inlineStr">
+      <c r="C1" s="58" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="D1" s="59" t="inlineStr">
+      <c r="D1" s="58" t="inlineStr">
         <is>
           <t>Parent</t>
         </is>
       </c>
-      <c r="E1" s="59" t="inlineStr">
+      <c r="E1" s="58" t="inlineStr">
         <is>
           <t>Functions</t>
         </is>
       </c>
     </row>
     <row r="2" ht="222" customHeight="1">
-      <c r="A2" s="60" t="inlineStr">
+      <c r="A2" s="59" t="inlineStr">
         <is>
           <t>SFM-SE-001</t>
         </is>
       </c>
-      <c r="B2" s="60" t="inlineStr">
+      <c r="B2" s="59" t="inlineStr">
         <is>
           <t>LionDriver item (L2 ACC + ALC + driver monitoring)</t>
         </is>
       </c>
-      <c r="C2" s="60" t="inlineStr">
+      <c r="C2" s="59" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="D2" s="60" t="inlineStr"/>
-      <c r="E2" s="60" t="inlineStr">
+      <c r="D2" s="59" t="inlineStr"/>
+      <c r="E2" s="59" t="inlineStr">
         <is>
           <t>SFM-FN-001: F1 Lateral control: request steering torque from the EPS to keep the vehicle in its lane while engaged
 SFM-FN-002: F2 Longitudinal control: request acceleration/deceleration to hold set speed and follow leads while engaged
@@ -19518,398 +19515,398 @@
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="60" t="inlineStr">
+      <c r="A3" s="59" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="B3" s="60" t="inlineStr">
+      <c r="B3" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">    comma 3X device</t>
         </is>
       </c>
-      <c r="C3" s="60" t="inlineStr">
+      <c r="C3" s="59" t="inlineStr">
         <is>
           <t>system</t>
         </is>
       </c>
-      <c r="D3" s="60" t="inlineStr">
+      <c r="D3" s="59" t="inlineStr">
         <is>
           <t>SFM-SE-001</t>
         </is>
       </c>
-      <c r="E3" s="60" t="inlineStr"/>
+      <c r="E3" s="59" t="inlineStr"/>
     </row>
     <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="60" t="inlineStr">
+      <c r="A4" s="59" t="inlineStr">
         <is>
           <t>SFM-SE-003</t>
         </is>
       </c>
-      <c r="B4" s="60" t="inlineStr">
+      <c r="B4" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">        Integrated panda (CAN interface and safety model)</t>
         </is>
       </c>
-      <c r="C4" s="60" t="inlineStr">
+      <c r="C4" s="59" t="inlineStr">
         <is>
           <t>subsystem</t>
         </is>
       </c>
-      <c r="D4" s="60" t="inlineStr">
+      <c r="D4" s="59" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E4" s="60" t="inlineStr"/>
+      <c r="E4" s="59" t="inlineStr"/>
     </row>
     <row r="5" ht="19.5" customHeight="1">
-      <c r="A5" s="60" t="inlineStr">
+      <c r="A5" s="59" t="inlineStr">
         <is>
           <t>SFM-SE-004</t>
         </is>
       </c>
-      <c r="B5" s="60" t="inlineStr">
+      <c r="B5" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">    Harness (Toyota A connector, harness box, comma power v3)</t>
         </is>
       </c>
-      <c r="C5" s="60" t="inlineStr">
+      <c r="C5" s="59" t="inlineStr">
         <is>
           <t>component</t>
         </is>
       </c>
-      <c r="D5" s="60" t="inlineStr">
+      <c r="D5" s="59" t="inlineStr">
         <is>
           <t>SFM-SE-001</t>
         </is>
       </c>
-      <c r="E5" s="60" t="inlineStr"/>
+      <c r="E5" s="59" t="inlineStr"/>
     </row>
     <row r="6" ht="19.5" customHeight="1">
-      <c r="A6" s="60" t="inlineStr">
+      <c r="A6" s="59" t="inlineStr">
         <is>
           <t>SFM-SE-010</t>
         </is>
       </c>
-      <c r="B6" s="60" t="inlineStr">
+      <c r="B6" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">        Perception (camerad, modeld)</t>
         </is>
       </c>
-      <c r="C6" s="60" t="inlineStr">
+      <c r="C6" s="59" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D6" s="60" t="inlineStr">
+      <c r="D6" s="59" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E6" s="60" t="inlineStr"/>
+      <c r="E6" s="59" t="inlineStr"/>
     </row>
     <row r="7" ht="19.5" customHeight="1">
-      <c r="A7" s="60" t="inlineStr">
+      <c r="A7" s="59" t="inlineStr">
         <is>
           <t>SFM-SE-011</t>
         </is>
       </c>
-      <c r="B7" s="60" t="inlineStr">
+      <c r="B7" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">        Localization and calibration (locationd, calibrationd, paramsd, torqued)</t>
         </is>
       </c>
-      <c r="C7" s="60" t="inlineStr">
+      <c r="C7" s="59" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D7" s="60" t="inlineStr">
+      <c r="D7" s="59" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E7" s="60" t="inlineStr"/>
+      <c r="E7" s="59" t="inlineStr"/>
     </row>
     <row r="8" ht="19.5" customHeight="1">
-      <c r="A8" s="60" t="inlineStr">
+      <c r="A8" s="59" t="inlineStr">
         <is>
           <t>SFM-SE-012</t>
         </is>
       </c>
-      <c r="B8" s="60" t="inlineStr">
+      <c r="B8" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">        Planning (plannerd, radard)</t>
         </is>
       </c>
-      <c r="C8" s="60" t="inlineStr">
+      <c r="C8" s="59" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D8" s="60" t="inlineStr">
+      <c r="D8" s="59" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E8" s="60" t="inlineStr"/>
+      <c r="E8" s="59" t="inlineStr"/>
     </row>
     <row r="9" ht="19.5" customHeight="1">
-      <c r="A9" s="60" t="inlineStr">
+      <c r="A9" s="59" t="inlineStr">
         <is>
           <t>SFM-SE-013</t>
         </is>
       </c>
-      <c r="B9" s="60" t="inlineStr">
+      <c r="B9" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">        Control (controlsd, lateral/longitudinal controllers)</t>
         </is>
       </c>
-      <c r="C9" s="60" t="inlineStr">
+      <c r="C9" s="59" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D9" s="60" t="inlineStr">
+      <c r="D9" s="59" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E9" s="60" t="inlineStr"/>
+      <c r="E9" s="59" t="inlineStr"/>
     </row>
     <row r="10" ht="19.5" customHeight="1">
-      <c r="A10" s="60" t="inlineStr">
+      <c r="A10" s="59" t="inlineStr">
         <is>
           <t>SFM-SE-014</t>
         </is>
       </c>
-      <c r="B10" s="60" t="inlineStr">
+      <c r="B10" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">        Supervision (selfdrived state machine, events, alert manager)</t>
         </is>
       </c>
-      <c r="C10" s="60" t="inlineStr">
+      <c r="C10" s="59" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D10" s="60" t="inlineStr">
+      <c r="D10" s="59" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E10" s="60" t="inlineStr"/>
+      <c r="E10" s="59" t="inlineStr"/>
     </row>
     <row r="11" ht="19.5" customHeight="1">
-      <c r="A11" s="60" t="inlineStr">
+      <c r="A11" s="59" t="inlineStr">
         <is>
           <t>SFM-SE-015</t>
         </is>
       </c>
-      <c r="B11" s="60" t="inlineStr">
+      <c r="B11" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">        Driver monitoring (dmonitoringmodeld, dmonitoringd)</t>
         </is>
       </c>
-      <c r="C11" s="60" t="inlineStr">
+      <c r="C11" s="59" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D11" s="60" t="inlineStr">
+      <c r="D11" s="59" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E11" s="60" t="inlineStr"/>
+      <c r="E11" s="59" t="inlineStr"/>
     </row>
     <row r="12" ht="19.5" customHeight="1">
-      <c r="A12" s="60" t="inlineStr">
+      <c r="A12" s="59" t="inlineStr">
         <is>
           <t>SFM-SE-016</t>
         </is>
       </c>
-      <c r="B12" s="60" t="inlineStr">
+      <c r="B12" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">        Car interface (card, car_events, opendbc Toyota port)</t>
         </is>
       </c>
-      <c r="C12" s="60" t="inlineStr">
+      <c r="C12" s="59" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D12" s="60" t="inlineStr">
+      <c r="D12" s="59" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E12" s="60" t="inlineStr"/>
+      <c r="E12" s="59" t="inlineStr"/>
     </row>
     <row r="13" ht="19.5" customHeight="1">
-      <c r="A13" s="60" t="inlineStr">
+      <c r="A13" s="59" t="inlineStr">
         <is>
           <t>SFM-SE-017</t>
         </is>
       </c>
-      <c r="B13" s="60" t="inlineStr">
+      <c r="B13" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">        Panda daemon (pandad)</t>
         </is>
       </c>
-      <c r="C13" s="60" t="inlineStr">
+      <c r="C13" s="59" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D13" s="60" t="inlineStr">
+      <c r="D13" s="59" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E13" s="60" t="inlineStr"/>
+      <c r="E13" s="59" t="inlineStr"/>
     </row>
     <row r="14" ht="19.5" customHeight="1">
-      <c r="A14" s="60" t="inlineStr">
+      <c r="A14" s="59" t="inlineStr">
         <is>
           <t>SFM-SE-018</t>
         </is>
       </c>
-      <c r="B14" s="60" t="inlineStr">
+      <c r="B14" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">        HMI (ui, soundd)</t>
         </is>
       </c>
-      <c r="C14" s="60" t="inlineStr">
+      <c r="C14" s="59" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D14" s="60" t="inlineStr">
+      <c r="D14" s="59" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E14" s="60" t="inlineStr"/>
+      <c r="E14" s="59" t="inlineStr"/>
     </row>
     <row r="15" ht="19.5" customHeight="1">
-      <c r="A15" s="60" t="inlineStr">
+      <c r="A15" s="59" t="inlineStr">
         <is>
           <t>SFM-SE-019</t>
         </is>
       </c>
-      <c r="B15" s="60" t="inlineStr">
+      <c r="B15" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve">        Platform (manager, messaging, hardwared, OS)</t>
         </is>
       </c>
-      <c r="C15" s="60" t="inlineStr">
+      <c r="C15" s="59" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D15" s="60" t="inlineStr">
+      <c r="D15" s="59" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E15" s="60" t="inlineStr"/>
+      <c r="E15" s="59" t="inlineStr"/>
     </row>
     <row r="16" ht="19.5" customHeight="1">
-      <c r="A16" s="60" t="inlineStr">
+      <c r="A16" s="59" t="inlineStr">
         <is>
           <t>SFM-SE-030</t>
         </is>
       </c>
-      <c r="B16" s="60" t="inlineStr">
+      <c r="B16" s="59" t="inlineStr">
         <is>
           <t>Toyota EPS</t>
         </is>
       </c>
-      <c r="C16" s="60" t="inlineStr">
+      <c r="C16" s="59" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D16" s="60" t="inlineStr"/>
-      <c r="E16" s="60" t="inlineStr"/>
+      <c r="D16" s="59" t="inlineStr"/>
+      <c r="E16" s="59" t="inlineStr"/>
     </row>
     <row r="17" ht="19.5" customHeight="1">
-      <c r="A17" s="60" t="inlineStr">
+      <c r="A17" s="59" t="inlineStr">
         <is>
           <t>SFM-SE-031</t>
         </is>
       </c>
-      <c r="B17" s="60" t="inlineStr">
+      <c r="B17" s="59" t="inlineStr">
         <is>
           <t>Toyota powertrain and brake control (receives ACC acceleration requests)</t>
         </is>
       </c>
-      <c r="C17" s="60" t="inlineStr">
+      <c r="C17" s="59" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D17" s="60" t="inlineStr"/>
-      <c r="E17" s="60" t="inlineStr"/>
+      <c r="D17" s="59" t="inlineStr"/>
+      <c r="E17" s="59" t="inlineStr"/>
     </row>
     <row r="18" ht="19.5" customHeight="1">
-      <c r="A18" s="60" t="inlineStr">
+      <c r="A18" s="59" t="inlineStr">
         <is>
           <t>SFM-SE-032</t>
         </is>
       </c>
-      <c r="B18" s="60" t="inlineStr">
+      <c r="B18" s="59" t="inlineStr">
         <is>
           <t>Toyota stock ADAS camera (TSS2)</t>
         </is>
       </c>
-      <c r="C18" s="60" t="inlineStr">
+      <c r="C18" s="59" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D18" s="60" t="inlineStr"/>
-      <c r="E18" s="60" t="inlineStr"/>
+      <c r="D18" s="59" t="inlineStr"/>
+      <c r="E18" s="59" t="inlineStr"/>
     </row>
     <row r="19" ht="19.5" customHeight="1">
-      <c r="A19" s="60" t="inlineStr">
+      <c r="A19" s="59" t="inlineStr">
         <is>
           <t>SFM-SE-033</t>
         </is>
       </c>
-      <c r="B19" s="60" t="inlineStr">
+      <c r="B19" s="59" t="inlineStr">
         <is>
           <t>Vehicle CAN buses and 12 V supply</t>
         </is>
       </c>
-      <c r="C19" s="60" t="inlineStr">
+      <c r="C19" s="59" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D19" s="60" t="inlineStr"/>
-      <c r="E19" s="60" t="inlineStr"/>
+      <c r="D19" s="59" t="inlineStr"/>
+      <c r="E19" s="59" t="inlineStr"/>
     </row>
     <row r="20" ht="19.5" customHeight="1">
-      <c r="A20" s="60" t="inlineStr">
+      <c r="A20" s="59" t="inlineStr">
         <is>
           <t>SFM-SE-034</t>
         </is>
       </c>
-      <c r="B20" s="60" t="inlineStr">
+      <c r="B20" s="59" t="inlineStr">
         <is>
           <t>Driver</t>
         </is>
       </c>
-      <c r="C20" s="60" t="inlineStr">
+      <c r="C20" s="59" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D20" s="60" t="inlineStr"/>
-      <c r="E20" s="60" t="inlineStr"/>
+      <c r="D20" s="59" t="inlineStr"/>
+      <c r="E20" s="59" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E20"/>
@@ -19945,7 +19942,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="63" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>FMEA-MSR (monitoring and system response, msr-plan.md): S, F, M and MSR AP per rating-tables.md §7 (RT-2). The MSR AP table is provisional until the handbook table is transcribed (decision register DQ-207). Exempt causes are rated in the FMEA named in the reason.</t>
         </is>
@@ -22702,7 +22699,7 @@
           <t>Device power loss (12 V interruption, harness connector)</t>
         </is>
       </c>
-      <c r="E44" s="64" t="inlineStr">
+      <c r="E44" s="63" t="inlineStr">
         <is>
           <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-012.C1)</t>
         </is>
@@ -22996,7 +22993,7 @@
           <t>The panda envelope passes STEERING_LKA torque that opposes the driver while the driver overrides: the Toyota LKA check covers magnitude, rate and measured-torque error only, and STEER_TORQUE_DRIVER is used only on the LTA path (toyota.h:298-310, 421-424; GAP-02). TSR-304 is not implemented in either build, so only the host 500-unit cut-off (C1, C2) stops the torque</t>
         </is>
       </c>
-      <c r="E49" s="64" t="inlineStr">
+      <c r="E49" s="63" t="inlineStr">
         <is>
           <t>Exempt: The cause is the missing panda override supervision itself, which is the MSR mechanism of C1 and C2; its absence is rated there as M 10 (msr-plan §3)</t>
         </is>
@@ -23860,7 +23857,7 @@
           <t>Panda MCU hardware fault (see DFMEA/FMEDA)</t>
         </is>
       </c>
-      <c r="E63" s="64" t="inlineStr">
+      <c r="E63" s="63" t="inlineStr">
         <is>
           <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-001.C1)</t>
         </is>
@@ -24020,7 +24017,7 @@
           <t>Switch U1 or U2 stuck in intercept, its IN input damaged high or driven high, its pull-down R2/R3 open, or the switches damaged by box supply transients (DG419LE, RR-2026-010)</t>
         </is>
       </c>
-      <c r="E66" s="64" t="inlineStr">
+      <c r="E66" s="63" t="inlineStr">
         <is>
           <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-010.C1)</t>
         </is>
@@ -24056,7 +24053,7 @@
           <t>Switch stuck in pass-through, or the SBU1 drive lost, held low or too low to change the switch over (5 V drive against VL = VIN)</t>
         </is>
       </c>
-      <c r="E67" s="64" t="inlineStr">
+      <c r="E67" s="63" t="inlineStr">
         <is>
           <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-011.C1)</t>
         </is>
@@ -24250,7 +24247,7 @@
       </c>
       <c r="N70" s="34" t="inlineStr">
         <is>
-          <t>SFM-ACT-020 · decision pending</t>
+          <t>SFM-ACT-020 · open</t>
         </is>
       </c>
       <c r="O70" s="37" t="inlineStr"/>
@@ -24312,7 +24309,7 @@
       </c>
       <c r="N71" s="34" t="inlineStr">
         <is>
-          <t>SFM-ACT-020 · decision pending</t>
+          <t>SFM-ACT-020 · open</t>
         </is>
       </c>
       <c r="O71" s="37" t="inlineStr"/>
@@ -24532,7 +24529,7 @@
           <t>The lighter EPS-fault prompt (steerTempUnavailableSilent, a LOW-priority WARNING with a chime and no soft disable, events.py:516-521) after a recent override, at standstill or while the driver steers is not limited to 1.5 s, so a long fault does not escalate to the take-over request (car_events.py:167-185, STEER_FAULT_SILENT_FRAMES; T-25, GAP-03). Until BL-005 the prompt was latched for the whole fault by design; from BL-006 the cause is a defect of the TSR-607 (b)/(c) frame counter</t>
         </is>
       </c>
-      <c r="E75" s="64" t="inlineStr">
+      <c r="E75" s="63" t="inlineStr">
         <is>
           <t>Exempt: The cause is a defect of the warning path itself; its effect on detecting the lateral loss is rated in the MSR rows of SFM-004.C2 and SFM-005 (msr-plan §3)</t>
         </is>
@@ -24568,7 +24565,7 @@
           <t>pandad publishes the panda fields epsFault and requestsRejected (pandad.cc:137-138), but no SoC process reads them (txRateExceeded is read, TSR-615), so a panda-side EPS-fault refusal reaches the driver only through the panda siren and the stock EPS path (SW FMEA SWF-025 notes)</t>
         </is>
       </c>
-      <c r="E76" s="64" t="inlineStr">
+      <c r="E76" s="63" t="inlineStr">
         <is>
           <t>Exempt: The cause is a defect of the warning path itself; the panda siren that remains is rated on SFM-005 and in the DFMEA (msr-plan §3)</t>
         </is>
@@ -24604,7 +24601,7 @@
           <t>steerSaturated needs the controller saturated, a desired lateral acceleration above 1.0 m/s², an undershoot above 1.2x and no steering input for 2 s (selfdrived.py:465-479), and the controller reports saturation only after 0.4 s (latcontrol.py, T-30); a gradual deficit therefore warns late or not at all (WP-S-04 §3.8.1)</t>
         </is>
       </c>
-      <c r="E77" s="64" t="inlineStr">
+      <c r="E77" s="63" t="inlineStr">
         <is>
           <t>Exempt: The cause is the timing of the warning itself; it is rated as M 8 in the MSR rows of SFM-004.C1-C3 (rev 0.15, WP-S-04 §3.8.1)</t>
         </is>
@@ -24635,7 +24632,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.28 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.29 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -261,7 +261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -414,6 +414,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -820,7 +823,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.29 · draft</t>
+          <t>0.30 · draft</t>
         </is>
       </c>
     </row>
@@ -844,7 +847,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>RT-2</t>
+          <t>RT-3</t>
         </is>
       </c>
     </row>
@@ -961,7 +964,7 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>67 rated, 8 exempt; MSR AP H 67, M 0, L 0 (provisional table)</t>
+          <t>67 rated, 8 exempt; MSR AP H 65, M 2, L 0</t>
         </is>
       </c>
     </row>
@@ -18536,7 +18539,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.29 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.30 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -19944,7 +19947,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="62" t="inlineStr">
         <is>
-          <t>FMEA-MSR (monitoring and system response, msr-plan.md): S, F, M and MSR AP per rating-tables.md §7 (RT-2). The MSR AP table is provisional until the handbook table is transcribed (decision register DQ-207). Exempt causes are rated in the FMEA named in the reason.</t>
+          <t>FMEA-MSR (monitoring and system response, msr-plan.md): S, F, M and MSR AP per rating-tables.md §7 (RT-3, handbook MSR AP table for S 9–10). Exempt causes are rated in the FMEA named in the reason.</t>
         </is>
       </c>
     </row>
@@ -22535,9 +22538,9 @@
       <c r="J41" s="46" t="n">
         <v>10</v>
       </c>
-      <c r="K41" s="36" t="inlineStr">
-        <is>
-          <t>H</t>
+      <c r="K41" s="63" t="inlineStr">
+        <is>
+          <t>M</t>
         </is>
       </c>
       <c r="L41" s="34" t="inlineStr"/>
@@ -22699,7 +22702,7 @@
           <t>Device power loss (12 V interruption, harness connector)</t>
         </is>
       </c>
-      <c r="E44" s="63" t="inlineStr">
+      <c r="E44" s="64" t="inlineStr">
         <is>
           <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-012.C1)</t>
         </is>
@@ -22993,7 +22996,7 @@
           <t>The panda envelope passes STEERING_LKA torque that opposes the driver while the driver overrides: the Toyota LKA check covers magnitude, rate and measured-torque error only, and STEER_TORQUE_DRIVER is used only on the LTA path (toyota.h:298-310, 421-424; GAP-02). TSR-304 is not implemented in either build, so only the host 500-unit cut-off (C1, C2) stops the torque</t>
         </is>
       </c>
-      <c r="E49" s="63" t="inlineStr">
+      <c r="E49" s="64" t="inlineStr">
         <is>
           <t>Exempt: The cause is the missing panda override supervision itself, which is the MSR mechanism of C1 and C2; its absence is rated there as M 10 (msr-plan §3)</t>
         </is>
@@ -23857,7 +23860,7 @@
           <t>Panda MCU hardware fault (see DFMEA/FMEDA)</t>
         </is>
       </c>
-      <c r="E63" s="63" t="inlineStr">
+      <c r="E63" s="64" t="inlineStr">
         <is>
           <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-001.C1)</t>
         </is>
@@ -23917,9 +23920,9 @@
       <c r="J64" s="46" t="n">
         <v>10</v>
       </c>
-      <c r="K64" s="36" t="inlineStr">
-        <is>
-          <t>H</t>
+      <c r="K64" s="63" t="inlineStr">
+        <is>
+          <t>M</t>
         </is>
       </c>
       <c r="L64" s="34" t="inlineStr"/>
@@ -24017,7 +24020,7 @@
           <t>Switch U1 or U2 stuck in intercept, its IN input damaged high or driven high, its pull-down R2/R3 open, or the switches damaged by box supply transients (DG419LE, RR-2026-010)</t>
         </is>
       </c>
-      <c r="E66" s="63" t="inlineStr">
+      <c r="E66" s="64" t="inlineStr">
         <is>
           <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-010.C1)</t>
         </is>
@@ -24053,7 +24056,7 @@
           <t>Switch stuck in pass-through, or the SBU1 drive lost, held low or too low to change the switch over (5 V drive against VL = VIN)</t>
         </is>
       </c>
-      <c r="E67" s="63" t="inlineStr">
+      <c r="E67" s="64" t="inlineStr">
         <is>
           <t>Exempt: Hardware cause; rated once in the DFMEA (DFM-011.C1)</t>
         </is>
@@ -24529,7 +24532,7 @@
           <t>The lighter EPS-fault prompt (steerTempUnavailableSilent, a LOW-priority WARNING with a chime and no soft disable, events.py:516-521) after a recent override, at standstill or while the driver steers is not limited to 1.5 s, so a long fault does not escalate to the take-over request (car_events.py:167-185, STEER_FAULT_SILENT_FRAMES; T-25, GAP-03). Until BL-005 the prompt was latched for the whole fault by design; from BL-006 the cause is a defect of the TSR-607 (b)/(c) frame counter</t>
         </is>
       </c>
-      <c r="E75" s="63" t="inlineStr">
+      <c r="E75" s="64" t="inlineStr">
         <is>
           <t>Exempt: The cause is a defect of the warning path itself; its effect on detecting the lateral loss is rated in the MSR rows of SFM-004.C2 and SFM-005 (msr-plan §3)</t>
         </is>
@@ -24565,7 +24568,7 @@
           <t>pandad publishes the panda fields epsFault and requestsRejected (pandad.cc:137-138), but no SoC process reads them (txRateExceeded is read, TSR-615), so a panda-side EPS-fault refusal reaches the driver only through the panda siren and the stock EPS path (SW FMEA SWF-025 notes)</t>
         </is>
       </c>
-      <c r="E76" s="63" t="inlineStr">
+      <c r="E76" s="64" t="inlineStr">
         <is>
           <t>Exempt: The cause is a defect of the warning path itself; the panda siren that remains is rated on SFM-005 and in the DFMEA (msr-plan §3)</t>
         </is>
@@ -24601,7 +24604,7 @@
           <t>steerSaturated needs the controller saturated, a desired lateral acceleration above 1.0 m/s², an undershoot above 1.2x and no steering input for 2 s (selfdrived.py:465-479), and the controller reports saturation only after 0.4 s (latcontrol.py, T-30); a gradual deficit therefore warns late or not at all (WP-S-04 §3.8.1)</t>
         </is>
       </c>
-      <c r="E77" s="63" t="inlineStr">
+      <c r="E77" s="64" t="inlineStr">
         <is>
           <t>Exempt: The cause is the timing of the warning itself; it is rated as M 8 in the MSR rows of SFM-004.C1-C3 (rev 0.15, WP-S-04 §3.8.1)</t>
         </is>
@@ -24632,7 +24635,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.29 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.30 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -8181,7 +8181,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Only relayMalfunction, safety model/param and controlsAllowed are checked (selfdrived.py:328-346)</t>
+            <t>• Only relayMalfunction, safety model/param and controlsAllowed are checked (selfdrived.py:330-348)</t>
           </r>
           <r>
             <rPr>
@@ -8190,7 +8190,7 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   openpilot/selfdrive/selfdrived/selfdrived.py:328-346</t>
+   openpilot/selfdrive/selfdrived/selfdrived.py:330-348</t>
           </r>
         </is>
       </c>
@@ -8429,7 +8429,7 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   openpilot/selfdrive/selfdrived/selfdrived.py:384-388</t>
+   openpilot/selfdrive/selfdrived/selfdrived.py:386-390</t>
           </r>
         </is>
       </c>
@@ -8473,7 +8473,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Code review at BL-004 (selfdrived.py:384-388) shows the suppression cannot remove the disable reaction, so the cause does not lead to the failure mode; no action. The big-model suppression of commIssue is a different cause (SWF-032.C2)</t>
+            <t>Code review at BL-004 (selfdrived.py:386-390) shows the suppression cannot remove the disable reaction, so the cause does not lead to the failure mode; no action. The big-model suppression of commIssue is a different cause (SWF-032.C2)</t>
           </r>
         </is>
       </c>
@@ -18241,7 +18241,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>steerSaturated needs the controller saturated, a desired lateral acceleration above 1.0 m/s², an undershoot above 1.2x and no steering input for 2 s (selfdrived.py:465-479), and the controller reports saturation only after 0.4 s (latcontrol.py, T-30); a gradual deficit therefore warns late or not at all (WP-S-04 §3.8.1)</t>
+            <t>steerSaturated needs the controller saturated, a desired lateral acceleration above 1.0 m/s², an undershoot above 1.2x and no steering input for 2 s (selfdrived.py:467-481), and the controller reports saturation only after 0.4 s (latcontrol.py, T-30); a gradual deficit therefore warns late or not at all (WP-S-04 §3.8.1)</t>
           </r>
         </is>
       </c>
@@ -24601,7 +24601,7 @@
       </c>
       <c r="D77" s="34" t="inlineStr">
         <is>
-          <t>steerSaturated needs the controller saturated, a desired lateral acceleration above 1.0 m/s², an undershoot above 1.2x and no steering input for 2 s (selfdrived.py:465-479), and the controller reports saturation only after 0.4 s (latcontrol.py, T-30); a gradual deficit therefore warns late or not at all (WP-S-04 §3.8.1)</t>
+          <t>steerSaturated needs the controller saturated, a desired lateral acceleration above 1.0 m/s², an undershoot above 1.2x and no steering input for 2 s (selfdrived.py:467-481), and the controller reports saturation only after 0.4 s (latcontrol.py, T-30); a gradual deficit therefore warns late or not at all (WP-S-04 §3.8.1)</t>
         </is>
       </c>
       <c r="E77" s="64" t="inlineStr">

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -5028,7 +5028,7 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   openpilot/selfdrive/controls/controlsd.py:237</t>
+   openpilot/selfdrive/controls/controlsd.py:238</t>
           </r>
         </is>
       </c>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -823,7 +823,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.30 · draft</t>
+          <t>0.31 · draft</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>23 (20)</t>
+          <t>23 (19)</t>
         </is>
       </c>
     </row>
@@ -17033,7 +17033,7 @@
       <c r="R86" s="45" t="inlineStr"/>
       <c r="S86" s="45" t="inlineStr"/>
     </row>
-    <row r="87" ht="141" customHeight="1">
+    <row r="87" ht="114" customHeight="1">
       <c r="A87" s="30" t="inlineStr">
         <is>
           <r>
@@ -17261,17 +17261,25 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Stand down during stock AEB: while the car reports a stock PCS/AEB event (stockAeb), LionDriver requests zero acceleration, so stock AEB does not depend on PCM arbitration alone (AOU-04R). Lead decision DQ-300, option A (2026-10-18); the AOU-04R vehicle test still runs. Code change with the implementation-spec session; not in BL-006, so SFM-036 keeps its ratings</t>
-          </r>
-        </is>
-      </c>
-      <c r="O87" s="47" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="P87" s="33" t="inlineStr"/>
-      <c r="Q87" s="33" t="inlineStr"/>
+            <t>Stand down during stock AEB: while the car reports a stock PCS/AEB event (stockAeb), LionDriver requests zero acceleration, so stock AEB does not depend on PCM arbitration alone (AOU-04R). Lead decision DQ-300, option A (2026-10-18); the AOU-04R vehicle test still runs. SFM-036.C1; FTA BE-7.13</t>
+          </r>
+        </is>
+      </c>
+      <c r="O87" s="54" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="P87" s="33" t="inlineStr">
+        <is>
+          <t>10/5/8</t>
+        </is>
+      </c>
+      <c r="Q87" s="36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
       <c r="R87" s="37" t="inlineStr"/>
       <c r="S87" s="37" t="inlineStr"/>
     </row>
@@ -18539,7 +18547,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.30 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.31 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -19275,7 +19283,7 @@
       <c r="H19" s="59" t="inlineStr"/>
       <c r="I19" s="59" t="inlineStr"/>
     </row>
-    <row r="20" ht="87" customHeight="1">
+    <row r="20" ht="235.5" customHeight="1">
       <c r="A20" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-020</t>
@@ -19288,13 +19296,13 @@
       </c>
       <c r="C20" s="59" t="inlineStr">
         <is>
-          <t>Stand down during stock AEB: while the car reports a stock PCS/AEB event (stockAeb), LionDriver requests zero acceleration, so stock AEB does not depend on PCM arbitration alone (AOU-04R). Lead decision DQ-300, option A (2026-10-18); the AOU-04R vehicle test still runs. Code change with the implementation-spec session; not in BL-006, so SFM-036 keeps its ratings</t>
+          <t>Stand down during stock AEB: while the car reports a stock PCS/AEB event (stockAeb), LionDriver requests zero acceleration, so stock AEB does not depend on PCM arbitration alone (AOU-04R). Lead decision DQ-300, option A (2026-10-18); the AOU-04R vehicle test still runs. SFM-036.C1; FTA BE-7.13</t>
         </is>
       </c>
       <c r="D20" s="59" t="inlineStr"/>
-      <c r="E20" s="59" t="inlineStr">
-        <is>
-          <t>open</t>
+      <c r="E20" s="60" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="F20" s="59" t="inlineStr">
@@ -19302,9 +19310,21 @@
           <t>SFM-036.C1</t>
         </is>
       </c>
-      <c r="G20" s="59" t="inlineStr"/>
-      <c r="H20" s="59" t="inlineStr"/>
-      <c r="I20" s="59" t="inlineStr"/>
+      <c r="G20" s="59" t="inlineStr">
+        <is>
+          <t>10/5/8</t>
+        </is>
+      </c>
+      <c r="H20" s="61" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I20" s="59" t="inlineStr">
+        <is>
+          <t>Merged in jherrodthomas/LionDriver#292 (c045874): stock_aeb_stand_down in longcontrol.py, called from controlsd.py, caps the acceleration target and the upper PID limit at 0 m/s² while stockAeb is set and keeps any braking request; selfdrive/controls/tests/test_stock_aeb.py, 4 tests, run locally only (CI scons is blocked by the LFS 404, DQ-401; cite the CI run once it re-runs). Impact record assurance/07-supporting/impact/change-2026-10-19-stock-aeb-stand-down.md. Host code only: the opendbc Toyota controller still applies its rate limit and positive terms, so the command reaches 0 about 0.4 s after +1.5 m/s² (impact OI-2); the parent TSR/SWSR are open (OI-1); not verified on the vehicle (OI-3, the AOU-04R test, also checks that stockAeb is reported during a PCS event) and not reviewed independently. Not in BL-006, so SFM-036.C1 keeps O 8 D 10 until the next baseline; the prediction below assumes targeted tests, not mutation-proven (rating tables D 8)</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="73.5" customHeight="1">
       <c r="A21" s="59" t="inlineStr">
@@ -24250,7 +24270,7 @@
       </c>
       <c r="N70" s="34" t="inlineStr">
         <is>
-          <t>SFM-ACT-020 · open</t>
+          <t>SFM-ACT-020 · completed</t>
         </is>
       </c>
       <c r="O70" s="37" t="inlineStr"/>
@@ -24312,7 +24332,7 @@
       </c>
       <c r="N71" s="34" t="inlineStr">
         <is>
-          <t>SFM-ACT-020 · open</t>
+          <t>SFM-ACT-020 · completed</t>
         </is>
       </c>
       <c r="O71" s="37" t="inlineStr"/>
@@ -24635,7 +24655,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.30 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.31 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -823,7 +823,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.31 · draft</t>
+          <t>0.32 · draft</t>
         </is>
       </c>
     </row>
@@ -18547,7 +18547,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.31 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.32 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -19283,7 +19283,7 @@
       <c r="H19" s="59" t="inlineStr"/>
       <c r="I19" s="59" t="inlineStr"/>
     </row>
-    <row r="20" ht="235.5" customHeight="1">
+    <row r="20" ht="343.5" customHeight="1">
       <c r="A20" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-020</t>
@@ -19322,7 +19322,7 @@
       </c>
       <c r="I20" s="59" t="inlineStr">
         <is>
-          <t>Merged in jherrodthomas/LionDriver#292 (c045874): stock_aeb_stand_down in longcontrol.py, called from controlsd.py, caps the acceleration target and the upper PID limit at 0 m/s² while stockAeb is set and keeps any braking request; selfdrive/controls/tests/test_stock_aeb.py, 4 tests, run locally only (CI scons is blocked by the LFS 404, DQ-401; cite the CI run once it re-runs). Impact record assurance/07-supporting/impact/change-2026-10-19-stock-aeb-stand-down.md. Host code only: the opendbc Toyota controller still applies its rate limit and positive terms, so the command reaches 0 about 0.4 s after +1.5 m/s² (impact OI-2); the parent TSR/SWSR are open (OI-1); not verified on the vehicle (OI-3, the AOU-04R test, also checks that stockAeb is reported during a PCS event) and not reviewed independently. Not in BL-006, so SFM-036.C1 keeps O 8 D 10 until the next baseline; the prediction below assumes targeted tests, not mutation-proven (rating tables D 8)</t>
+          <t>Merged in jherrodthomas/LionDriver#292 (c045874): stock_aeb_stand_down in longcontrol.py, called from controlsd.py, caps the acceleration target and the upper PID limit at 0 m/s² while stockAeb is set and keeps any braking request; selfdrive/controls/tests/test_stock_aeb.py, 4 tests. CI: tests run 39296172878 on liondriver-dev 6126485 (2026-10-19), unit tests job 1578 passed, 42 skipped, 3 xfailed, no failures or collection errors; process replay passed. The runner collects every openpilot/**/test_*.py and prints no test names, so the four tests are shown to have run by collection, not by name; the file has no skip. Second layer, opendbc e233362 (#311, SWSR-713h): the Toyota controller caps the 0x343 command at 0 from the first frame of the event, after its rate limit, PID and pitch compensation (impact OI-2 done); its 6 test_carcontroller.py cases ran locally only (opendbc_repo tests are not in the openpilot runner). Impact records assurance/07-supporting/impact/change-2026-10-19-stock-aeb-stand-down.md and change-2026-10-19-pin-e233362.md. TSR-713 and FSR-07.07 implemented (#313). Not verified on the vehicle (OI-3, the AOU-04R test, also checks that stockAeb is reported during a PCS event) and not reviewed independently. Not in BL-006, so SFM-036.C1 keeps O 8 D 10 until the next baseline; the prediction below assumes targeted tests, not mutation-proven (rating tables D 8)</t>
         </is>
       </c>
     </row>
@@ -24655,7 +24655,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.31 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.32 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -19283,7 +19283,7 @@
       <c r="H19" s="59" t="inlineStr"/>
       <c r="I19" s="59" t="inlineStr"/>
     </row>
-    <row r="20" ht="343.5" customHeight="1">
+    <row r="20" ht="384" customHeight="1">
       <c r="A20" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-020</t>
@@ -19322,7 +19322,7 @@
       </c>
       <c r="I20" s="59" t="inlineStr">
         <is>
-          <t>Merged in jherrodthomas/LionDriver#292 (c045874): stock_aeb_stand_down in longcontrol.py, called from controlsd.py, caps the acceleration target and the upper PID limit at 0 m/s² while stockAeb is set and keeps any braking request; selfdrive/controls/tests/test_stock_aeb.py, 4 tests. CI: tests run 39296172878 on liondriver-dev 6126485 (2026-10-19), unit tests job 1578 passed, 42 skipped, 3 xfailed, no failures or collection errors; process replay passed. The runner collects every openpilot/**/test_*.py and prints no test names, so the four tests are shown to have run by collection, not by name; the file has no skip. Second layer, opendbc e233362 (#311, SWSR-713h): the Toyota controller caps the 0x343 command at 0 from the first frame of the event, after its rate limit, PID and pitch compensation (impact OI-2 done); its 6 test_carcontroller.py cases ran locally only (opendbc_repo tests are not in the openpilot runner). Impact records assurance/07-supporting/impact/change-2026-10-19-stock-aeb-stand-down.md and change-2026-10-19-pin-e233362.md. TSR-713 and FSR-07.07 implemented (#313). Not verified on the vehicle (OI-3, the AOU-04R test, also checks that stockAeb is reported during a PCS event) and not reviewed independently. Not in BL-006, so SFM-036.C1 keeps O 8 D 10 until the next baseline; the prediction below assumes targeted tests, not mutation-proven (rating tables D 8)</t>
+          <t>Merged in jherrodthomas/LionDriver#292 (c045874): stock_aeb_stand_down in longcontrol.py, called from controlsd.py, caps the acceleration target and the upper PID limit at 0 m/s² while stockAeb is set and keeps any braking request; selfdrive/controls/tests/test_stock_aeb.py, 4 tests. CI: tests run 39296172878 on liondriver-dev 6126485 (2026-10-19), unit tests job 1578 passed, 42 skipped, 3 xfailed, no failures or collection errors; process replay passed. The runner collects every openpilot/**/test_*.py and prints no test names, so the four tests are shown to have run by collection, not by name; the file has no skip. Second layer, opendbc e233362 (#311, SWSR-713h): the Toyota controller caps the 0x343 command at 0 from the first frame of the event, after its rate limit, PID and pitch compensation (impact OI-2 done); its 6 test_carcontroller.py cases ran locally (pin record). The openpilot runner does not run opendbc_repo tests; tests.yml in the opendbc fork triggers on pull requests, but a CI run on jherrodthomas/opendbc#20 is not confirmed here (the pin record says none). Impact records assurance/07-supporting/impact/change-2026-10-19-stock-aeb-stand-down.md and change-2026-10-19-pin-e233362.md. TSR-713 and FSR-07.07 implemented (#313). Not verified on the vehicle (OI-3, the AOU-04R test, also checks that stockAeb is reported during a PCS event) and not reviewed independently. Not in BL-006, so SFM-036.C1 keeps O 8 D 10 until the next baseline; the prediction below assumes targeted tests, not mutation-proven (rating tables D 8)</t>
         </is>
       </c>
     </row>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -8181,7 +8181,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Only relayMalfunction, safety model/param and controlsAllowed are checked (selfdrived.py:330-348)</t>
+            <t>• Only relayMalfunction, safety model/param and controlsAllowed are checked (selfdrived.py:333-351)</t>
           </r>
           <r>
             <rPr>
@@ -8190,7 +8190,7 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   openpilot/selfdrive/selfdrived/selfdrived.py:330-348</t>
+   openpilot/selfdrive/selfdrived/selfdrived.py:333-351</t>
           </r>
         </is>
       </c>
@@ -8429,7 +8429,7 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   openpilot/selfdrive/selfdrived/selfdrived.py:386-390</t>
+   openpilot/selfdrive/selfdrived/selfdrived.py:389-393</t>
           </r>
         </is>
       </c>
@@ -8473,7 +8473,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Code review at BL-004 (selfdrived.py:386-390) shows the suppression cannot remove the disable reaction, so the cause does not lead to the failure mode; no action. The big-model suppression of commIssue is a different cause (SWF-032.C2)</t>
+            <t>Code review at BL-004 (selfdrived.py:389-393) shows the suppression cannot remove the disable reaction, so the cause does not lead to the failure mode; no action. The big-model suppression of commIssue is a different cause (SWF-032.C2)</t>
           </r>
         </is>
       </c>
@@ -18249,7 +18249,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>steerSaturated needs the controller saturated, a desired lateral acceleration above 1.0 m/s², an undershoot above 1.2x and no steering input for 2 s (selfdrived.py:467-481), and the controller reports saturation only after 0.4 s (latcontrol.py, T-30); a gradual deficit therefore warns late or not at all (WP-S-04 §3.8.1)</t>
+            <t>steerSaturated needs the controller saturated, a desired lateral acceleration above 1.0 m/s², an undershoot above 1.2x and no steering input for 2 s (selfdrived.py:470-484), and the controller reports saturation only after 0.4 s (latcontrol.py, T-30); a gradual deficit therefore warns late or not at all (WP-S-04 §3.8.1)</t>
           </r>
         </is>
       </c>
@@ -24621,7 +24621,7 @@
       </c>
       <c r="D77" s="34" t="inlineStr">
         <is>
-          <t>steerSaturated needs the controller saturated, a desired lateral acceleration above 1.0 m/s², an undershoot above 1.2x and no steering input for 2 s (selfdrived.py:467-481), and the controller reports saturation only after 0.4 s (latcontrol.py, T-30); a gradual deficit therefore warns late or not at all (WP-S-04 §3.8.1)</t>
+          <t>steerSaturated needs the controller saturated, a desired lateral acceleration above 1.0 m/s², an undershoot above 1.2x and no steering input for 2 s (selfdrived.py:470-484), and the controller reports saturation only after 0.4 s (latcontrol.py, T-30); a gradual deficit therefore warns late or not at all (WP-S-04 §3.8.1)</t>
         </is>
       </c>
       <c r="E77" s="64" t="inlineStr">

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -823,7 +823,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.32 · draft</t>
+          <t>0.33 · draft</t>
         </is>
       </c>
     </row>
@@ -18547,7 +18547,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.32 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.33 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -21030,7 +21030,7 @@
       <c r="O17" s="37" t="inlineStr"/>
       <c r="P17" s="37" t="inlineStr"/>
     </row>
-    <row r="18" ht="141" customHeight="1">
+    <row r="18" ht="195" customHeight="1">
       <c r="A18" s="34" t="inlineStr">
         <is>
           <t>SFM-005 · Loss of lateral control without driver alert</t>
@@ -21051,7 +21051,7 @@
       </c>
       <c r="E18" s="34" t="inlineStr">
         <is>
-          <t>BL-005: when no STEERING_LKA frame reaches the panda for 50 ms while authority is granted, the 100 Hz safety task clears controls_allowed (tx_arrival_ok, safety.h; TSR-408). pandad keeps publishing pandaStates, so selfdrived sees controlsAllowed false on the next sample and raises controlsMismatch after 2 consecutive samples, at most 0.5 s after the first mismatched frame (TSR-621). At BL-004 only the EPS drop-out path existed (about 3.5 s)</t>
+          <t>BL-005: when no STEERING_LKA frame reaches the panda for 50 ms while authority is granted, the 100 Hz safety task clears controls_allowed (tx_arrival_ok, safety.h; TSR-408). pandad keeps publishing pandaStates, so selfdrived sees controlsAllowed false on the next sample and raises controlsMismatch after 2 consecutive samples, at most 0.5 s after the first mismatched frame (TSR-621). At BL-004 only the EPS drop-out path existed (about 3.5 s). After BL-006 (panda 8a69ccf, DQ-404 A; kept in f4803c5) the panda also sounds its own siren on this revocation, independent of the SoC (TSR-516(b)); not in BL-006, so the rating below does not credit it</t>
         </is>
       </c>
       <c r="F18" s="34" t="inlineStr">
@@ -21160,7 +21160,7 @@
       <c r="O19" s="37" t="inlineStr"/>
       <c r="P19" s="37" t="inlineStr"/>
     </row>
-    <row r="20" ht="100.5" customHeight="1">
+    <row r="20" ht="127.5" customHeight="1">
       <c r="A20" s="34" t="inlineStr">
         <is>
           <t>SFM-006 · Lateral command frozen at last value</t>
@@ -21191,7 +21191,7 @@
       </c>
       <c r="G20" s="34" t="inlineStr">
         <is>
-          <t>Last torque command held about 0.1 s, then LKA frames stop and assist decays over about 2 s. The driver is now warned within about 0.66 s, but the actuation reaction is still beyond the 0.5 s FTTI</t>
+          <t>Last torque command held about 0.1 s, then LKA frames stop and assist decays over about 2 s. The driver is now warned within about 0.66 s (after BL-006 the panda siren comes first, about 0.25 s after the last frame, DQ-404), but the actuation reaction is still beyond the 0.5 s FTTI</t>
         </is>
       </c>
       <c r="H20" s="35" t="n">
@@ -24655,7 +24655,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.32 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.33 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -823,7 +823,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.34 · draft</t>
+          <t>0.35 · draft</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>BL-006</t>
+          <t>BL-007</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>LionDriver as installed on the reference configuration CFG-001 (Corolla E210 · ZRE212 · US, US sedan MY2020-2022) with comma 3X and integrated panda, software BL-005 (structure and failure analysis written at BL-001, risk analysis at BL-004, MSR re-rated at BL-005), while the vehicle is driven by a licensed driver inside the ODD: limited-access highways only since WP-C-02 / WP-C-03 v0.4 (DQ-023), up to 110 km/h (DQ-260). Functions F1-F7 per fmea-plan.md section 3.1, plus F8 (stock vehicle safety functions are preserved), added because the harness intercepts the stock ADAS camera.</t>
+          <t>LionDriver as installed on the reference configuration CFG-001 (Corolla E210 · ZRE212 · US, US sedan MY2020-2022) with comma 3X and integrated panda, software BL-005 (structure and failure analysis written at BL-001, risk analysis at BL-004, MSR re-rated at BL-005; re-checked at BL-006 and BL-007), while the vehicle is driven by a licensed driver inside the ODD: limited-access highways only since WP-C-02 / WP-C-03 v0.4 (DQ-023), up to 110 km/h (DQ-260). Functions F1-F7 per fmea-plan.md section 3.1, plus F8 (stock vehicle safety functions are preserved), added because the harness intercepts the stock ADAS camera.</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>1–4: 0 · 5–6: 18 · 7–8: 17 · 9–10: 40 (see sheet MSR)</t>
+          <t>1–4: 0 · 5–6: 18 · 7–8: 19 · 9–10: 38 (see sheet MSR)</t>
         </is>
       </c>
     </row>
@@ -6549,7 +6549,7 @@
       <c r="R33" s="37" t="inlineStr"/>
       <c r="S33" s="37" t="inlineStr"/>
     </row>
-    <row r="34" ht="114" customHeight="1">
+    <row r="34" ht="154.5" customHeight="1">
       <c r="A34" s="39" t="n"/>
       <c r="B34" s="39" t="n"/>
       <c r="C34" s="39" t="n"/>
@@ -6569,7 +6569,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>The item starts a soft-disable or no-response deceleration with no lead time: a fault soft-disable deceleration is announced only at its start, which TSR-624 accepts for that mild slow-down (DQ-407 A); its jerk is not bounded (TSR-205, GAP-04)</t>
+            <t>Defect in the announcement of the driver-monitoring no-response stop (TSR-624, #374, BL-007): noResponseDecelIn or the countdown alert ("Car Stops in N s", then "Car Is Stopping") wrong or missing, so the stop starts without the at-least-1 s announcement. Up to BL-006 the cause was by design (no lead time). The fault soft-disable deceleration is announced only at its start, which TSR-624 accepts for that mild slow-down (DQ-407 A); its jerk is not bounded in the envelope (TSR-205, GAP-04)</t>
           </r>
           <r>
             <rPr>
@@ -6590,7 +6590,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• DM escalation alerts precede the no-response deceleration; the fault soft-disable alert sounds from the first frame, and the slow-down is bounded by A_CRUISE_MIN (-1.2 m/s²) for 3 s; rated in the SW FMEA</t>
+            <t>• TSR-624 implemented for the no-response stop (#374, 59e22e0): the DM policy publishes the time left and the terminal alert counts down to it; new LionDriver code reviewed in the PR only, ruff and ty in CI; rated in the SW FMEA (SWF-050.C1)</t>
           </r>
           <r>
             <rPr>
@@ -6599,27 +6599,36 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   openpilot/selfdrive/selfdrived/state.py</t>
+   openpilot/selfdrive/monitoring/policy.py</t>
           </r>
         </is>
       </c>
       <c r="J34" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="K34" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_monitoring.py (the countdown runs 5 s to 0 and the stop starts at least 1 s after the first countdown frame) and the alert and event tests, in the CI unit_tests job; targeted, not proven by mutation, so D 8 (SW FMEA SWF-050.C1)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/monitoring/test_monitoring.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L34" s="42" t="n">
         <v>8</v>
-      </c>
-      <c r="K34" s="41" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• No test targets this cause</t>
-          </r>
-        </is>
-      </c>
-      <c r="L34" s="43" t="n">
-        <v>10</v>
       </c>
       <c r="M34" s="44" t="inlineStr">
         <is>
@@ -13342,7 +13351,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>driverDistracted3 / driverUnresponsive3 mapped only to ET.PERMANENT (no disable reaction)</t>
+            <t>Defect in the minimum-risk manoeuvre of TSR-633 (#372): the latch in minimum_risk.py not set or cleared while the item is still engaged, controlsd not keeping forceDecel on while selfdriveState.minimumRiskManeuver is set, or the terminal alert not re-raised, so the car resumes or keeps driving with an unresponsive driver. Up to BL-006 the cause was by design: the terminal alerts were ET.PERMANENT only and the forced deceleration was recomputed every DM frame, so a dmonitoringd restart or an awareness reset dropped it</t>
           </r>
           <r>
             <rPr>
@@ -13363,7 +13372,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Upstream openpilot code with upstream review; ruff and type checks in CI (static analysis job); unit tests are not requirements-based; no field-exposure evidence for this configuration, so none is credited (RT-1 §2.2)</t>
+            <t>• Lead decision DQ-365 A implemented as TSR-633 (#372, dacd8f7; #374, 59e22e0 for the announcement); new LionDriver code on upstream openpilot, reviewed in the PR only, ruff and ty in CI; O 5 as the other new host code with targeted tests (SW FMEA SWF-062.C1)</t>
           </r>
           <r>
             <rPr>
@@ -13372,63 +13381,37 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   scripts/lint/lint.sh</t>
+   openpilot/selfdrive/selfdrived/minimum_risk.py</t>
           </r>
         </is>
       </c>
       <c r="J71" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="K71" s="41" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_minimum_risk.py (the latch), test_monitoring.py (lockout from the takeover) and a test_longitudinal maneuver that stays stopped under forced deceleration while the lead drives off, run by the CI unit_tests job; targeted, not proven by mutation, so D 8. The PCM standstill hold over time (AOU-16) and the stop time are not verified on the vehicle</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/selfdrived/tests/test_minimum_risk.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L71" s="42" t="n">
         <v>8</v>
       </c>
-      <c r="K71" s="41" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• As rated in the SW FMEA (SWF-062.C1, D 9 at BL-005): test_longitudinal runs the force_decel maneuver in CI and test_monitoring checks the alert levels; neither checks that the reaction meets FSR-040</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   openpilot/selfdrive/test/longitudinal_maneuvers/test_longitudinal.py</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• Present by design and known; no test, because no requirement says what the reaction should be</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   openpilot/selfdrive/selfdrived/events.py</t>
-          </r>
-        </is>
-      </c>
-      <c r="L71" s="43" t="n">
-        <v>9</v>
-      </c>
       <c r="M71" s="44" t="inlineStr">
         <is>
           <t>H</t>
@@ -13456,9 +13439,9 @@
           </r>
         </is>
       </c>
-      <c r="O71" s="48" t="inlineStr">
-        <is>
-          <t>open</t>
+      <c r="O71" s="50" t="inlineStr">
+        <is>
+          <t>in progress</t>
         </is>
       </c>
       <c r="P71" s="40" t="inlineStr"/>
@@ -18898,7 +18881,7 @@
       <c r="R103" s="45" t="inlineStr"/>
       <c r="S103" s="45" t="inlineStr"/>
     </row>
-    <row r="104" ht="114" customHeight="1">
+    <row r="104" ht="154.5" customHeight="1">
       <c r="A104" s="30" t="inlineStr">
         <is>
           <r>
@@ -19060,7 +19043,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>The item has no reaction to a stock PCS event on its longitudinal command; controlsd keeps requesting the planner's acceleration (design gap, FTA BE-7.13)</t>
+            <t>Defect in the stand-down of DQ-300 A (#292): stock_aeb_stand_down not called or not capping the target and the upper PID limit while stockAeb is set, or the opendbc 0x343 cap not applied, so the item keeps requesting the planner's acceleration during a stock PCS event (FTA BE-7.13). Up to BL-006 the cause was a design gap: the item had no reaction to a stock PCS event on its longitudinal command</t>
           </r>
         </is>
       </c>
@@ -19072,7 +19055,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• None in the item: FSR-07.04 places PCS priority in the PCM as an external measure (AOU-04R)</t>
+            <t>• Lead decision DQ-300 A implemented in #292 (c045874) and opendbc e233362 (#311); new LionDriver code reviewed in the PR only, ruff and ty in CI; O 5 as the other new host code with targeted tests. FSR-07.04 keeps PCS priority in the PCM as the external measure (AOU-04R)</t>
           </r>
           <r>
             <rPr>
@@ -19081,27 +19064,36 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   assurance/02-concept/WP-C-04-functional-safety-concept.md</t>
+   assurance/07-supporting/impact/change-2026-10-19-stock-aeb-stand-down.md</t>
           </r>
         </is>
       </c>
       <c r="J104" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K104" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_stock_aeb.py (4 tests) in the CI unit_tests job (tests run 39296172878); targeted, not proven by mutation, so D 8. The opendbc test_carcontroller.py cases ran locally only (LionDriver CI does not run opendbc car tests). Not verified on the vehicle (the AOU-04R test also checks that stockAeb is reported during a PCS event)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/controls/tests/test_stock_aeb.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L104" s="35" t="n">
         <v>8</v>
-      </c>
-      <c r="K104" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• No pre-release test targets this cause</t>
-          </r>
-        </is>
-      </c>
-      <c r="L104" s="46" t="n">
-        <v>10</v>
       </c>
       <c r="M104" s="36" t="inlineStr">
         <is>
@@ -20412,7 +20404,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.34 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.35 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -20641,7 +20633,7 @@
       <c r="H4" s="59" t="inlineStr"/>
       <c r="I4" s="59" t="inlineStr"/>
     </row>
-    <row r="5" ht="154.5" customHeight="1">
+    <row r="5" ht="168" customHeight="1">
       <c r="A5" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-005</t>
@@ -20664,7 +20656,7 @@
       </c>
       <c r="E5" s="59" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>in progress</t>
         </is>
       </c>
       <c r="F5" s="59" t="inlineStr">
@@ -20674,7 +20666,11 @@
       </c>
       <c r="G5" s="59" t="inlineStr"/>
       <c r="H5" s="59" t="inlineStr"/>
-      <c r="I5" s="59" t="inlineStr"/>
+      <c r="I5" s="59" t="inlineStr">
+        <is>
+          <t>Code done in BL-007: the manoeuvre is latched until the driver takes over, held at standstill and the alert re-raised (#372, dacd8f7, minimum_risk.py, test_minimum_risk.py), the lockout runs from the takeover (test_monitoring.py), a longitudinal maneuver stays stopped under forced deceleration (test_longitudinal.py), and the stop is announced by a countdown (#374, 59e22e0, TSR-624); all in the CI unit_tests job. SFM-025.C1 re-rated at BL-007 to a defect of that code (O 5 D 8). Open: the PCM standstill hold over time (AOU-16 vehicle test), the measured deceleration and stop time, and the time to the reaction (WP-S-04 OI-11)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="59" t="inlineStr">
@@ -21153,7 +21149,7 @@
       <c r="H19" s="59" t="inlineStr"/>
       <c r="I19" s="59" t="inlineStr"/>
     </row>
-    <row r="20" ht="384" customHeight="1">
+    <row r="20" ht="370.5" customHeight="1">
       <c r="A20" s="59" t="inlineStr">
         <is>
           <t>SFM-ACT-020</t>
@@ -21192,7 +21188,7 @@
       </c>
       <c r="I20" s="59" t="inlineStr">
         <is>
-          <t>Merged in jherrodthomas/LionDriver#292 (c045874): stock_aeb_stand_down in longcontrol.py, called from controlsd.py, caps the acceleration target and the upper PID limit at 0 m/s² while stockAeb is set and keeps any braking request; selfdrive/controls/tests/test_stock_aeb.py, 4 tests. CI: tests run 39296172878 on liondriver-dev 6126485 (2026-10-19), unit tests job 1578 passed, 42 skipped, 3 xfailed, no failures or collection errors; process replay passed. The runner collects every openpilot/**/test_*.py and prints no test names, so the four tests are shown to have run by collection, not by name; the file has no skip. Second layer, opendbc e233362 (#311, SWSR-713h): the Toyota controller caps the 0x343 command at 0 from the first frame of the event, after its rate limit, PID and pitch compensation (impact OI-2 done); its 6 test_carcontroller.py cases ran locally (pin record). The openpilot runner does not run opendbc_repo tests; tests.yml in the opendbc fork triggers on pull requests, but a CI run on jherrodthomas/opendbc#20 is not confirmed here (the pin record says none). Impact records assurance/07-supporting/impact/change-2026-10-19-stock-aeb-stand-down.md and change-2026-10-19-pin-e233362.md. TSR-713 and FSR-07.07 implemented (#313). Not verified on the vehicle (OI-3, the AOU-04R test, also checks that stockAeb is reported during a PCS event) and not reviewed independently. Not in BL-006, so SFM-036.C1 keeps O 8 D 10 until the next baseline; the prediction below assumes targeted tests, not mutation-proven (rating tables D 8)</t>
+          <t>Merged in jherrodthomas/LionDriver#292 (c045874): stock_aeb_stand_down in longcontrol.py, called from controlsd.py, caps the acceleration target and the upper PID limit at 0 m/s² while stockAeb is set and keeps any braking request; selfdrive/controls/tests/test_stock_aeb.py, 4 tests. CI: tests run 39296172878 on liondriver-dev 6126485 (2026-10-19), unit tests job 1578 passed, 42 skipped, 3 xfailed, no failures or collection errors; process replay passed. The runner collects every openpilot/**/test_*.py and prints no test names, so the four tests are shown to have run by collection, not by name; the file has no skip. Second layer, opendbc e233362 (#311, SWSR-713h): the Toyota controller caps the 0x343 command at 0 from the first frame of the event, after its rate limit, PID and pitch compensation (impact OI-2 done); its 6 test_carcontroller.py cases ran locally (pin record). The openpilot runner does not run opendbc_repo tests; tests.yml in the opendbc fork triggers on pull requests, but a CI run on jherrodthomas/opendbc#20 is not confirmed here (the pin record says none). Impact records assurance/07-supporting/impact/change-2026-10-19-stock-aeb-stand-down.md and change-2026-10-19-pin-e233362.md. TSR-713 and FSR-07.07 implemented (#313). Not verified on the vehicle (OI-3, the AOU-04R test, also checks that stockAeb is reported during a PCS event) and not reviewed independently. In BL-007, where SFM-036.C1 is re-rated O 8 D 10 -&gt; O 5 D 8 as predicted below (targeted tests, not mutation-proven: rating tables D 8)</t>
         </is>
       </c>
     </row>
@@ -22962,7 +22958,7 @@
       <c r="O18" s="37" t="inlineStr"/>
       <c r="P18" s="37" t="inlineStr"/>
     </row>
-    <row r="19" ht="195" customHeight="1">
+    <row r="19" ht="222" customHeight="1">
       <c r="A19" s="34" t="inlineStr">
         <is>
           <t>SFM-005 · Loss of lateral control without driver alert</t>
@@ -22983,7 +22979,7 @@
       </c>
       <c r="E19" s="34" t="inlineStr">
         <is>
-          <t>BL-005: when no STEERING_LKA frame reaches the panda for 50 ms while authority is granted, the 100 Hz safety task clears controls_allowed (tx_arrival_ok, safety.h; TSR-408). pandad keeps publishing pandaStates, so selfdrived sees controlsAllowed false on the next sample and raises controlsMismatch after 2 consecutive samples, at most 0.5 s after the first mismatched frame (TSR-621). At BL-004 only the EPS drop-out path existed (about 3.5 s). After BL-006 (panda 8a69ccf, DQ-404 A; kept in f4803c5) the panda also sounds its own siren on this revocation, independent of the SoC (TSR-516(b)); not in BL-006, so the rating below does not credit it</t>
+          <t>BL-005: when no STEERING_LKA frame reaches the panda for 50 ms while authority is granted, the 100 Hz safety task clears controls_allowed (tx_arrival_ok, safety.h; TSR-408). pandad keeps publishing pandaStates, so selfdrived sees controlsAllowed false on the next sample and raises controlsMismatch after 2 consecutive samples, at most 0.5 s after the first mismatched frame (TSR-621). At BL-004 only the EPS drop-out path existed (about 3.5 s). In BL-007 (panda 8a69ccf, DQ-404 A; kept in f4803c5) the panda also sounds its own siren on this revocation, independent of the SoC (TSR-516(b)), credited below as the second warning path; M stays 6 because neither path is proven (the siren tests are host unit tests, the alert path unit tests) and nothing is measured</t>
         </is>
       </c>
       <c r="F19" s="34" t="inlineStr">
@@ -23185,7 +23181,7 @@
       </c>
       <c r="G22" s="34" t="inlineStr">
         <is>
-          <t>Last torque command held about 0.1 s, then LKA frames stop and assist decays over about 2 s. The driver is now warned within about 0.66 s (after BL-006 the panda siren comes first, about 0.25 s after the last frame, DQ-404), but the actuation reaction is still beyond the 0.5 s FTTI</t>
+          <t>Last torque command held about 0.1 s, then LKA frames stop and assist decays over about 2 s. The driver is now warned within about 0.66 s (in BL-007 the panda siren comes first, about 0.25 s after the last frame, DQ-404), but the actuation reaction is still beyond the 0.5 s FTTI</t>
         </is>
       </c>
       <c r="H22" s="35" t="n">
@@ -23800,7 +23796,7 @@
       <c r="O31" s="37" t="inlineStr"/>
       <c r="P31" s="37" t="inlineStr"/>
     </row>
-    <row r="32" ht="100.5" customHeight="1">
+    <row r="32" ht="195" customHeight="1">
       <c r="A32" s="34" t="inlineStr">
         <is>
           <t>SFM-009 · Unintended or excessive deceleration (phantom braking)</t>
@@ -23816,7 +23812,7 @@
       </c>
       <c r="D32" s="34" t="inlineStr">
         <is>
-          <t>The item starts a soft-disable or no-response deceleration with no lead time: a fault soft-disable deceleration is announced only at its start, which TSR-624 accepts for that mild slow-down (DQ-407 A); its jerk is not bounded (TSR-205, GAP-04)</t>
+          <t>Defect in the announcement of the driver-monitoring no-response stop (TSR-624, #374, BL-007): noResponseDecelIn or the countdown alert ("Car Stops in N s", then "Car Is Stopping") wrong or missing, so the stop starts without the at-least-1 s announcement. Up to BL-006 the cause was by design (no lead time). The fault soft-disable deceleration is announced only at its start, which TSR-624 accepts for that mild slow-down (DQ-407 A); its jerk is not bounded in the envelope (TSR-205, GAP-04)</t>
         </is>
       </c>
       <c r="E32" s="34" t="inlineStr">
@@ -23831,14 +23827,14 @@
       </c>
       <c r="G32" s="34" t="inlineStr">
         <is>
-          <t>Unchanged: a deceleration of at most -1.2 m/s², announced from its first frame</t>
+          <t>Unchanged: a deceleration of at most -1.2 m/s², without its announcement</t>
         </is>
       </c>
       <c r="H32" s="35" t="n">
         <v>10</v>
       </c>
       <c r="I32" s="35" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J32" s="46" t="n">
         <v>10</v>
@@ -25687,7 +25683,7 @@
       </c>
       <c r="N62" s="34" t="inlineStr">
         <is>
-          <t>SFM-ACT-005 · open</t>
+          <t>SFM-ACT-005 · in progress</t>
         </is>
       </c>
       <c r="O62" s="37" t="inlineStr"/>
@@ -25751,7 +25747,7 @@
       <c r="O63" s="37" t="inlineStr"/>
       <c r="P63" s="37" t="inlineStr"/>
     </row>
-    <row r="64" ht="46.5" customHeight="1">
+    <row r="64" ht="208.5" customHeight="1">
       <c r="A64" s="34" t="inlineStr">
         <is>
           <t>SFM-025 · Terminal driver-unresponsive state does not bring the item to a safe state</t>
@@ -25767,32 +25763,32 @@
       </c>
       <c r="D64" s="34" t="inlineStr">
         <is>
-          <t>driverDistracted3 / driverUnresponsive3 mapped only to ET.PERMANENT (no disable reaction)</t>
+          <t>Defect in the minimum-risk manoeuvre of TSR-633 (#372): the latch in minimum_risk.py not set or cleared while the item is still engaged, controlsd not keeping forceDecel on while selfdriveState.minimumRiskManeuver is set, or the terminal alert not re-raised, so the car resumes or keeps driving with an unresponsive driver. Up to BL-006 the cause was by design: the terminal alerts were ET.PERMANENT only and the forced deceleration was recomputed every DM frame, so a dmonitoringd restart or an awareness reset dropped it</t>
         </is>
       </c>
       <c r="E64" s="34" t="inlineStr">
         <is>
-          <t>None: the lockout acts only after disengagement; the terminal alert has no disable reaction</t>
+          <t>The DM policy keeps requesting the forced deceleration while the driver stays unresponsive (noResponseForceDecel), so a defective latch still leaves the unlatched stop request, which a dmonitoringd restart or awareness reset can drop; nothing checks the latch itself</t>
         </is>
       </c>
       <c r="F64" s="34" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Forced deceleration toward standstill at A_CRUISE_MIN while the DM request holds; lockout after the takeover</t>
         </is>
       </c>
       <c r="G64" s="34" t="inlineStr">
         <is>
-          <t>Unchanged: control continues with an unresponsive driver</t>
+          <t>Mostly unchanged: the car slows while the request holds but may resume after it drops; the 25 s stop from 110 km/h is not compared with an FTTI (WP-S-04 §3.8.4 preliminary)</t>
         </is>
       </c>
       <c r="H64" s="35" t="n">
         <v>10</v>
       </c>
       <c r="I64" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="J64" s="35" t="n">
         <v>8</v>
-      </c>
-      <c r="J64" s="46" t="n">
-        <v>10</v>
       </c>
       <c r="K64" s="36" t="inlineStr">
         <is>
@@ -25807,7 +25803,7 @@
       </c>
       <c r="N64" s="34" t="inlineStr">
         <is>
-          <t>SFM-ACT-005 · open</t>
+          <t>SFM-ACT-005 · in progress</t>
         </is>
       </c>
       <c r="O64" s="37" t="inlineStr"/>
@@ -26776,7 +26772,7 @@
       <c r="O83" s="37" t="inlineStr"/>
       <c r="P83" s="37" t="inlineStr"/>
     </row>
-    <row r="84" ht="73.5" customHeight="1">
+    <row r="84" ht="168" customHeight="1">
       <c r="A84" s="34" t="inlineStr">
         <is>
           <t>SFM-036 · Item keeps requesting acceleration while stock PCS brakes</t>
@@ -26792,17 +26788,17 @@
       </c>
       <c r="D84" s="34" t="inlineStr">
         <is>
-          <t>The item has no reaction to a stock PCS event on its longitudinal command; controlsd keeps requesting the planner's acceleration (design gap, FTA BE-7.13)</t>
+          <t>Defect in the stand-down of DQ-300 A (#292): stock_aeb_stand_down not called or not capping the target and the upper PID limit while stockAeb is set, or the opendbc 0x343 cap not applied, so the item keeps requesting the planner's acceleration during a stock PCS event (FTA BE-7.13). Up to BL-006 the cause was a design gap: the item had no reaction to a stock PCS event on its longitudinal command</t>
         </is>
       </c>
       <c r="E84" s="34" t="inlineStr">
         <is>
-          <t>stockAeb detects the PCS event from the stock camera's PRE_COLLISION frame and raises an alert</t>
+          <t>stockAeb detects the PCS event from the stock camera's PRE_COLLISION frame and raises an alert; nothing checks that the stand-down acted</t>
         </is>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
-          <t>Alert only; the longitudinal request continues until the driver brakes (panda revokes on the brake press)</t>
+          <t>Alert only when the stand-down is defective; the longitudinal request continues until the driver brakes (panda revokes on the brake press)</t>
         </is>
       </c>
       <c r="G84" s="34" t="inlineStr">
@@ -26814,7 +26810,7 @@
         <v>10</v>
       </c>
       <c r="I84" s="35" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J84" s="35" t="n">
         <v>8</v>
@@ -26838,7 +26834,7 @@
       <c r="O84" s="37" t="inlineStr"/>
       <c r="P84" s="37" t="inlineStr"/>
     </row>
-    <row r="85" ht="46.5" customHeight="1">
+    <row r="85" ht="73.5" customHeight="1">
       <c r="A85" s="34" t="inlineStr">
         <is>
           <t>SFM-036 · Item keeps requesting acceleration while stock PCS brakes</t>
@@ -26859,17 +26855,17 @@
       </c>
       <c r="E85" s="34" t="inlineStr">
         <is>
-          <t>None: the item cannot see how the PCM arbitrates</t>
+          <t>The item cannot see how the PCM arbitrates. BL-007: on the stockAeb flag it stops requesting acceleration (mechanism 3), so what the PCM arbitrates against is a zero request, not the planner's acceleration</t>
         </is>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Zero acceleration request while stockAeb is set (#292, opendbc e233362)</t>
         </is>
       </c>
       <c r="G85" s="34" t="inlineStr">
         <is>
-          <t>Unchanged: stock braking reduced while the item requests acceleration</t>
+          <t>Stock braking no longer opposed by an item acceleration request, provided stockAeb is reported during the event; not verified on the vehicle (AOU-04R test)</t>
         </is>
       </c>
       <c r="H85" s="35" t="n">
@@ -26878,8 +26874,8 @@
       <c r="I85" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="J85" s="46" t="n">
-        <v>10</v>
+      <c r="J85" s="35" t="n">
+        <v>7</v>
       </c>
       <c r="K85" s="36" t="inlineStr">
         <is>
@@ -27217,7 +27213,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.34 · BL-006&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.35 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -823,7 +823,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.35 · draft</t>
+          <t>0.36 · draft</t>
         </is>
       </c>
     </row>
@@ -6549,7 +6549,7 @@
       <c r="R33" s="37" t="inlineStr"/>
       <c r="S33" s="37" t="inlineStr"/>
     </row>
-    <row r="34" ht="154.5" customHeight="1">
+    <row r="34" ht="181.5" customHeight="1">
       <c r="A34" s="39" t="n"/>
       <c r="B34" s="39" t="n"/>
       <c r="C34" s="39" t="n"/>
@@ -6614,6 +6614,32 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
+            <t>• Proven by mutation in CI after BL-007 (AN-1, AN-2, tools/ci/host_mutation.py), as SWF-050.C1; D 8 -&gt; 4 (System FMEA rev 0.36)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   tools/ci/host_mutants.toml</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
             <t>• test_monitoring.py (the countdown runs 5 s to 0 and the stop starts at least 1 s after the first countdown frame) and the alert and event tests, in the CI unit_tests job; targeted, not proven by mutation, so D 8 (SW FMEA SWF-050.C1)</t>
           </r>
           <r>
@@ -6628,7 +6654,7 @@
         </is>
       </c>
       <c r="L34" s="42" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M34" s="44" t="inlineStr">
         <is>
@@ -19718,7 +19744,7 @@
       <c r="R108" s="45" t="inlineStr"/>
       <c r="S108" s="45" t="inlineStr"/>
     </row>
-    <row r="109" ht="168" customHeight="1">
+    <row r="109" ht="235.5" customHeight="1">
       <c r="A109" s="30" t="inlineStr">
         <is>
           <r>
@@ -19925,6 +19951,32 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
+            <t>• Proven by mutation in CI after BL-007 (CE-1..CE-3, tools/ci/host_mutation.py), as SWF-088.C1/C2; D 8 -&gt; 4 (System FMEA rev 0.36)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   tools/ci/host_mutants.toml</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
             <t>• test_steer_fault_warning.py (7 tests: silent window, no recent override, escalation after an override, at standstill, after releasing the wheel, a returning fault, a short fault while holding), run by the CI test runner; 4 of the #174 tests fail on the BL-005 code. Targeted but not proven by mutation, so D 8 (RT-2); not verified on the vehicle (impact record OI-1)</t>
           </r>
           <r>
@@ -19939,7 +19991,7 @@
         </is>
       </c>
       <c r="L109" s="35" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M109" s="36" t="inlineStr">
         <is>
@@ -20404,7 +20456,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.35 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.36 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -27213,7 +27265,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.35 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.36 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -823,7 +823,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.36 · draft</t>
+          <t>0.37 · draft</t>
         </is>
       </c>
     </row>
@@ -13422,6 +13422,32 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
+            <t>• Proven by mutation in CI after BL-007 (MR-1..MR-7, tools/ci/host_mutation.py), as SWF-062.C1; D 8 -&gt; 4 (System FMEA rev 0.37)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   tools/ci/host_mutants.toml</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
             <t>• test_minimum_risk.py (the latch), test_monitoring.py (lockout from the takeover) and a test_longitudinal maneuver that stays stopped under forced deceleration while the lead drives off, run by the CI unit_tests job; targeted, not proven by mutation, so D 8. The PCM standstill hold over time (AOU-16) and the stop time are not verified on the vehicle</t>
           </r>
           <r>
@@ -13436,7 +13462,7 @@
         </is>
       </c>
       <c r="L71" s="42" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M71" s="44" t="inlineStr">
         <is>
@@ -20456,7 +20482,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.36 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.37 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -27265,7 +27291,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.36 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.37 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -364,14 +364,17 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -414,9 +417,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -823,7 +823,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.37 · draft</t>
+          <t>0.38 · draft</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1950,7 +1950,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Upstream review and lint; LatControlCurvature does reset its PID (latcontrol_curvature.py:28-31), so the omission may be an oversight or deliberate upstream; no requirement states either</t>
+            <t>• LionDriver change: LatControlTorque and LatControlPID reset their PID in reset(), as LatControlCurvature does (DQ-426 A); targeted unit tests; no requirement yet; O 5</t>
           </r>
           <r>
             <rPr>
@@ -1959,27 +1959,36 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   openpilot/selfdrive/controls/lib/latcontrol_curvature.py</t>
+   assurance/07-supporting/impact/change-2026-10-29-lateral-integrator-reset.md</t>
           </r>
         </is>
       </c>
       <c r="J6" s="35" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K6" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• test_latcontrol.py covers saturation only; test_latcontrol_torque_buffer.py covers the request buffer only; nothing checks controller state across disengagement</t>
-          </r>
-        </is>
-      </c>
-      <c r="L6" s="46" t="n">
-        <v>10</v>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_latcontrol.py and test_controlsd_call_sites.py, proven by mutants LR-1..LR-3 in CI (tools/ci/host_mutation.py); D 4, from D 10 (SW FMEA rev 1.13)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/controls/tests/test_latcontrol.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L6" s="35" t="n">
+        <v>4</v>
       </c>
       <c r="M6" s="36" t="inlineStr">
         <is>
@@ -2035,7 +2044,7 @@
           </r>
         </is>
       </c>
-      <c r="O6" s="47" t="inlineStr">
+      <c r="O6" s="46" t="inlineStr">
         <is>
           <t>open
 open</t>
@@ -2106,7 +2115,7 @@
           </r>
         </is>
       </c>
-      <c r="L7" s="46" t="n">
+      <c r="L7" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M7" s="36" t="inlineStr">
@@ -2190,7 +2199,7 @@
           </r>
         </is>
       </c>
-      <c r="O7" s="47" t="inlineStr">
+      <c r="O7" s="46" t="inlineStr">
         <is>
           <t>open
 open
@@ -2306,7 +2315,7 @@
           </r>
         </is>
       </c>
-      <c r="L8" s="46" t="n">
+      <c r="L8" s="47" t="n">
         <v>9</v>
       </c>
       <c r="M8" s="36" t="inlineStr">
@@ -2336,7 +2345,7 @@
           </r>
         </is>
       </c>
-      <c r="O8" s="47" t="inlineStr">
+      <c r="O8" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -2476,7 +2485,7 @@
           </r>
         </is>
       </c>
-      <c r="L9" s="46" t="n">
+      <c r="L9" s="47" t="n">
         <v>9</v>
       </c>
       <c r="M9" s="36" t="inlineStr">
@@ -2560,7 +2569,7 @@
           </r>
         </is>
       </c>
-      <c r="O9" s="47" t="inlineStr">
+      <c r="O9" s="46" t="inlineStr">
         <is>
           <t>open
 open
@@ -2965,7 +2974,7 @@
           </r>
         </is>
       </c>
-      <c r="O11" s="47" t="inlineStr">
+      <c r="O11" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -3079,7 +3088,7 @@
           </r>
         </is>
       </c>
-      <c r="L12" s="46" t="n">
+      <c r="L12" s="47" t="n">
         <v>9</v>
       </c>
       <c r="M12" s="36" t="inlineStr">
@@ -3109,7 +3118,7 @@
           </r>
         </is>
       </c>
-      <c r="O12" s="47" t="inlineStr">
+      <c r="O12" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -3205,7 +3214,7 @@
           </r>
         </is>
       </c>
-      <c r="L13" s="46" t="n">
+      <c r="L13" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M13" s="36" t="inlineStr">
@@ -3235,7 +3244,7 @@
           </r>
         </is>
       </c>
-      <c r="O13" s="47" t="inlineStr">
+      <c r="O13" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -3573,7 +3582,7 @@
           </r>
         </is>
       </c>
-      <c r="L15" s="46" t="n">
+      <c r="L15" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M15" s="36" t="inlineStr">
@@ -3603,7 +3612,7 @@
           </r>
         </is>
       </c>
-      <c r="O15" s="47" t="inlineStr">
+      <c r="O15" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -3664,7 +3673,7 @@
           </r>
         </is>
       </c>
-      <c r="L16" s="46" t="n">
+      <c r="L16" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M16" s="36" t="inlineStr">
@@ -3694,7 +3703,7 @@
           </r>
         </is>
       </c>
-      <c r="O16" s="47" t="inlineStr">
+      <c r="O16" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -4034,7 +4043,7 @@
           </r>
         </is>
       </c>
-      <c r="L18" s="46" t="n">
+      <c r="L18" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M18" s="36" t="inlineStr">
@@ -4064,7 +4073,7 @@
           </r>
         </is>
       </c>
-      <c r="O18" s="47" t="inlineStr">
+      <c r="O18" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -4134,7 +4143,7 @@
           </r>
         </is>
       </c>
-      <c r="L19" s="46" t="n">
+      <c r="L19" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M19" s="36" t="inlineStr">
@@ -4255,7 +4264,7 @@
           </r>
         </is>
       </c>
-      <c r="L20" s="46" t="n">
+      <c r="L20" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M20" s="36" t="inlineStr">
@@ -4285,7 +4294,7 @@
           </r>
         </is>
       </c>
-      <c r="O20" s="47" t="inlineStr">
+      <c r="O20" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -4610,7 +4619,7 @@
           </r>
         </is>
       </c>
-      <c r="L22" s="46" t="n">
+      <c r="L22" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M22" s="36" t="inlineStr">
@@ -4757,7 +4766,7 @@
           </r>
         </is>
       </c>
-      <c r="L23" s="46" t="n">
+      <c r="L23" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M23" s="36" t="inlineStr">
@@ -4787,7 +4796,7 @@
           </r>
         </is>
       </c>
-      <c r="O23" s="47" t="inlineStr">
+      <c r="O23" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -4923,7 +4932,7 @@
       <c r="R24" s="45" t="inlineStr"/>
       <c r="S24" s="45" t="inlineStr"/>
     </row>
-    <row r="25" ht="100.5" customHeight="1">
+    <row r="25" ht="114" customHeight="1">
       <c r="A25" s="30" t="inlineStr">
         <is>
           <r>
@@ -5102,7 +5111,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Upstream review and lint; LatControlCurvature does reset its PID (latcontrol_curvature.py:28-31), so the omission may be an oversight or deliberate upstream; no requirement states either</t>
+            <t>• LionDriver change: LatControlTorque and LatControlPID reset their PID in reset(), as LatControlCurvature does (DQ-426 A); targeted unit tests; no requirement yet; O 5</t>
           </r>
           <r>
             <rPr>
@@ -5111,31 +5120,40 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   openpilot/selfdrive/controls/lib/latcontrol_curvature.py</t>
+   assurance/07-supporting/impact/change-2026-10-29-lateral-integrator-reset.md</t>
           </r>
         </is>
       </c>
       <c r="J25" s="35" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K25" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• test_latcontrol.py covers saturation only; test_latcontrol_torque_buffer.py covers the request buffer only; nothing checks controller state across disengagement</t>
-          </r>
-        </is>
-      </c>
-      <c r="L25" s="46" t="n">
-        <v>10</v>
-      </c>
-      <c r="M25" s="36" t="inlineStr">
-        <is>
-          <t>H</t>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_latcontrol.py and test_controlsd_call_sites.py, proven by mutants LR-1..LR-3 in CI (tools/ci/host_mutation.py); D 4, from D 10 (SW FMEA rev 1.13)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/controls/tests/test_latcontrol.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L25" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="M25" s="49" t="inlineStr">
+        <is>
+          <t>M</t>
         </is>
       </c>
       <c r="N25" s="34" t="inlineStr">
@@ -5563,7 +5581,7 @@
           </r>
         </is>
       </c>
-      <c r="L27" s="46" t="n">
+      <c r="L27" s="47" t="n">
         <v>9</v>
       </c>
       <c r="M27" s="36" t="inlineStr">
@@ -5620,7 +5638,7 @@
           </r>
         </is>
       </c>
-      <c r="O27" s="47" t="inlineStr">
+      <c r="O27" s="46" t="inlineStr">
         <is>
           <t>open
 open</t>
@@ -5709,7 +5727,7 @@
           </r>
         </is>
       </c>
-      <c r="L28" s="46" t="n">
+      <c r="L28" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M28" s="36" t="inlineStr">
@@ -5739,7 +5757,7 @@
           </r>
         </is>
       </c>
-      <c r="O28" s="47" t="inlineStr">
+      <c r="O28" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -5879,7 +5897,7 @@
           </r>
         </is>
       </c>
-      <c r="L29" s="46" t="n">
+      <c r="L29" s="47" t="n">
         <v>9</v>
       </c>
       <c r="M29" s="36" t="inlineStr">
@@ -5909,7 +5927,7 @@
           </r>
         </is>
       </c>
-      <c r="O29" s="47" t="inlineStr">
+      <c r="O29" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -6277,7 +6295,7 @@
           </r>
         </is>
       </c>
-      <c r="O31" s="47" t="inlineStr">
+      <c r="O31" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -6365,7 +6383,7 @@
           </r>
         </is>
       </c>
-      <c r="L32" s="46" t="n">
+      <c r="L32" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M32" s="36" t="inlineStr">
@@ -6395,7 +6413,7 @@
           </r>
         </is>
       </c>
-      <c r="O32" s="47" t="inlineStr">
+      <c r="O32" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -6509,7 +6527,7 @@
           </r>
         </is>
       </c>
-      <c r="L33" s="46" t="n">
+      <c r="L33" s="47" t="n">
         <v>9</v>
       </c>
       <c r="M33" s="36" t="inlineStr">
@@ -6539,7 +6557,7 @@
           </r>
         </is>
       </c>
-      <c r="O33" s="47" t="inlineStr">
+      <c r="O33" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -6990,7 +7008,7 @@
           </r>
         </is>
       </c>
-      <c r="O35" s="47" t="inlineStr">
+      <c r="O35" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -7060,7 +7078,7 @@
           </r>
         </is>
       </c>
-      <c r="L36" s="46" t="n">
+      <c r="L36" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M36" s="36" t="inlineStr">
@@ -7090,7 +7108,7 @@
           </r>
         </is>
       </c>
-      <c r="O36" s="47" t="inlineStr">
+      <c r="O36" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -7384,7 +7402,7 @@
           </r>
         </is>
       </c>
-      <c r="L38" s="46" t="n">
+      <c r="L38" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M38" s="36" t="inlineStr">
@@ -7414,7 +7432,7 @@
           </r>
         </is>
       </c>
-      <c r="O38" s="47" t="inlineStr">
+      <c r="O38" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -7484,7 +7502,7 @@
           </r>
         </is>
       </c>
-      <c r="L39" s="46" t="n">
+      <c r="L39" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M39" s="36" t="inlineStr">
@@ -7860,7 +7878,7 @@
           </r>
         </is>
       </c>
-      <c r="L41" s="46" t="n">
+      <c r="L41" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M41" s="36" t="inlineStr">
@@ -7890,7 +7908,7 @@
           </r>
         </is>
       </c>
-      <c r="O41" s="47" t="inlineStr">
+      <c r="O41" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -8665,7 +8683,7 @@
           </r>
         </is>
       </c>
-      <c r="L45" s="46" t="n">
+      <c r="L45" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M45" s="36" t="inlineStr">
@@ -8778,7 +8796,7 @@
           </r>
         </is>
       </c>
-      <c r="L46" s="46" t="n">
+      <c r="L46" s="47" t="n">
         <v>9</v>
       </c>
       <c r="M46" s="36" t="inlineStr">
@@ -8808,7 +8826,7 @@
           </r>
         </is>
       </c>
-      <c r="O46" s="49" t="inlineStr">
+      <c r="O46" s="50" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
@@ -9180,7 +9198,7 @@
           </r>
         </is>
       </c>
-      <c r="O48" s="47" t="inlineStr">
+      <c r="O48" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -9315,7 +9333,7 @@
           </r>
         </is>
       </c>
-      <c r="O49" s="49" t="inlineStr">
+      <c r="O49" s="50" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
@@ -9403,7 +9421,7 @@
           </r>
         </is>
       </c>
-      <c r="L50" s="46" t="n">
+      <c r="L50" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M50" s="36" t="inlineStr">
@@ -9433,7 +9451,7 @@
           </r>
         </is>
       </c>
-      <c r="O50" s="47" t="inlineStr">
+      <c r="O50" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -9808,7 +9826,7 @@
           </r>
         </is>
       </c>
-      <c r="L52" s="46" t="n">
+      <c r="L52" s="47" t="n">
         <v>9</v>
       </c>
       <c r="M52" s="36" t="inlineStr">
@@ -9838,7 +9856,7 @@
           </r>
         </is>
       </c>
-      <c r="O52" s="49" t="inlineStr">
+      <c r="O52" s="50" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
@@ -9956,7 +9974,7 @@
           </r>
         </is>
       </c>
-      <c r="O53" s="50" t="inlineStr">
+      <c r="O53" s="51" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
@@ -10239,7 +10257,7 @@
           </r>
         </is>
       </c>
-      <c r="L54" s="46" t="n">
+      <c r="L54" s="47" t="n">
         <v>9</v>
       </c>
       <c r="M54" s="36" t="inlineStr">
@@ -10269,7 +10287,7 @@
           </r>
         </is>
       </c>
-      <c r="O54" s="47" t="inlineStr">
+      <c r="O54" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -10733,7 +10751,7 @@
           </r>
         </is>
       </c>
-      <c r="L57" s="46" t="n">
+      <c r="L57" s="47" t="n">
         <v>9</v>
       </c>
       <c r="M57" s="36" t="inlineStr">
@@ -10763,7 +10781,7 @@
           </r>
         </is>
       </c>
-      <c r="O57" s="47" t="inlineStr">
+      <c r="O57" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -10851,7 +10869,7 @@
           </r>
         </is>
       </c>
-      <c r="L58" s="46" t="n">
+      <c r="L58" s="47" t="n">
         <v>9</v>
       </c>
       <c r="M58" s="36" t="inlineStr">
@@ -10996,7 +11014,7 @@
       <c r="S59" s="45" t="inlineStr"/>
     </row>
     <row r="60" ht="235.5" customHeight="1">
-      <c r="A60" s="51" t="inlineStr">
+      <c r="A60" s="52" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11018,7 +11036,7 @@
           </r>
         </is>
       </c>
-      <c r="B60" s="51" t="inlineStr">
+      <c r="B60" s="52" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11040,7 +11058,7 @@
           </r>
         </is>
       </c>
-      <c r="C60" s="51" t="inlineStr">
+      <c r="C60" s="52" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11113,15 +11131,15 @@
           </r>
         </is>
       </c>
-      <c r="D60" s="52" t="inlineStr">
+      <c r="D60" s="53" t="inlineStr">
         <is>
           <t>HZ-008</t>
         </is>
       </c>
-      <c r="E60" s="53" t="n">
+      <c r="E60" s="54" t="n">
         <v>10</v>
       </c>
-      <c r="F60" s="51" t="inlineStr">
+      <c r="F60" s="52" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11282,7 +11300,7 @@
       <c r="S60" s="45" t="inlineStr"/>
     </row>
     <row r="61" ht="235.5" customHeight="1">
-      <c r="A61" s="51" t="inlineStr">
+      <c r="A61" s="52" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11304,7 +11322,7 @@
           </r>
         </is>
       </c>
-      <c r="B61" s="51" t="inlineStr">
+      <c r="B61" s="52" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11326,7 +11344,7 @@
           </r>
         </is>
       </c>
-      <c r="C61" s="51" t="inlineStr">
+      <c r="C61" s="52" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11399,15 +11417,15 @@
           </r>
         </is>
       </c>
-      <c r="D61" s="52" t="inlineStr">
+      <c r="D61" s="53" t="inlineStr">
         <is>
           <t>HZ-006</t>
         </is>
       </c>
-      <c r="E61" s="53" t="n">
+      <c r="E61" s="54" t="n">
         <v>10</v>
       </c>
-      <c r="F61" s="51" t="inlineStr">
+      <c r="F61" s="52" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11805,7 +11823,7 @@
           </r>
         </is>
       </c>
-      <c r="L62" s="46" t="n">
+      <c r="L62" s="47" t="n">
         <v>9</v>
       </c>
       <c r="M62" s="36" t="inlineStr">
@@ -11835,7 +11853,7 @@
           </r>
         </is>
       </c>
-      <c r="O62" s="54" t="inlineStr">
+      <c r="O62" s="55" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
@@ -11926,7 +11944,7 @@
           </r>
         </is>
       </c>
-      <c r="O63" s="55" t="inlineStr">
+      <c r="O63" s="56" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
@@ -12138,7 +12156,7 @@
           </r>
         </is>
       </c>
-      <c r="L64" s="46" t="n">
+      <c r="L64" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M64" s="36" t="inlineStr">
@@ -12168,7 +12186,7 @@
           </r>
         </is>
       </c>
-      <c r="O64" s="47" t="inlineStr">
+      <c r="O64" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -12312,7 +12330,7 @@
           </r>
         </is>
       </c>
-      <c r="O65" s="47" t="inlineStr">
+      <c r="O65" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -12408,7 +12426,7 @@
           </r>
         </is>
       </c>
-      <c r="L66" s="46" t="n">
+      <c r="L66" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M66" s="36" t="inlineStr">
@@ -12438,7 +12456,7 @@
           </r>
         </is>
       </c>
-      <c r="O66" s="47" t="inlineStr">
+      <c r="O66" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -12828,7 +12846,7 @@
           </r>
         </is>
       </c>
-      <c r="O68" s="47" t="inlineStr">
+      <c r="O68" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -12983,7 +13001,7 @@
       <c r="S69" s="45" t="inlineStr"/>
     </row>
     <row r="70" ht="87" customHeight="1">
-      <c r="A70" s="51" t="inlineStr">
+      <c r="A70" s="52" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13005,7 +13023,7 @@
           </r>
         </is>
       </c>
-      <c r="B70" s="51" t="inlineStr">
+      <c r="B70" s="52" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13027,7 +13045,7 @@
           </r>
         </is>
       </c>
-      <c r="C70" s="51" t="inlineStr">
+      <c r="C70" s="52" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13100,11 +13118,11 @@
           </r>
         </is>
       </c>
-      <c r="D70" s="52" t="inlineStr"/>
-      <c r="E70" s="53" t="n">
+      <c r="D70" s="53" t="inlineStr"/>
+      <c r="E70" s="54" t="n">
         <v>4</v>
       </c>
-      <c r="F70" s="51" t="inlineStr">
+      <c r="F70" s="52" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13183,7 +13201,7 @@
       <c r="L70" s="43" t="n">
         <v>10</v>
       </c>
-      <c r="M70" s="56" t="inlineStr">
+      <c r="M70" s="57" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -13216,7 +13234,7 @@
       <c r="S70" s="45" t="inlineStr"/>
     </row>
     <row r="71" ht="249" customHeight="1">
-      <c r="A71" s="51" t="inlineStr">
+      <c r="A71" s="52" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13238,7 +13256,7 @@
           </r>
         </is>
       </c>
-      <c r="B71" s="51" t="inlineStr">
+      <c r="B71" s="52" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13260,7 +13278,7 @@
           </r>
         </is>
       </c>
-      <c r="C71" s="51" t="inlineStr">
+      <c r="C71" s="52" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13333,15 +13351,15 @@
           </r>
         </is>
       </c>
-      <c r="D71" s="52" t="inlineStr">
+      <c r="D71" s="53" t="inlineStr">
         <is>
           <t>HZ-013</t>
         </is>
       </c>
-      <c r="E71" s="53" t="n">
+      <c r="E71" s="54" t="n">
         <v>10</v>
       </c>
-      <c r="F71" s="51" t="inlineStr">
+      <c r="F71" s="52" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13491,7 +13509,7 @@
           </r>
         </is>
       </c>
-      <c r="O71" s="50" t="inlineStr">
+      <c r="O71" s="51" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
@@ -13757,7 +13775,7 @@
           </r>
         </is>
       </c>
-      <c r="L72" s="46" t="n">
+      <c r="L72" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M72" s="36" t="inlineStr">
@@ -13787,7 +13805,7 @@
           </r>
         </is>
       </c>
-      <c r="O72" s="47" t="inlineStr">
+      <c r="O72" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -13949,7 +13967,7 @@
           </r>
         </is>
       </c>
-      <c r="O73" s="47" t="inlineStr">
+      <c r="O73" s="46" t="inlineStr">
         <is>
           <t>open
 open</t>
@@ -14289,7 +14307,7 @@
           </r>
         </is>
       </c>
-      <c r="L75" s="46" t="n">
+      <c r="L75" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M75" s="36" t="inlineStr">
@@ -14319,7 +14337,7 @@
           </r>
         </is>
       </c>
-      <c r="O75" s="47" t="inlineStr">
+      <c r="O75" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -14671,7 +14689,7 @@
           </r>
         </is>
       </c>
-      <c r="L77" s="46" t="n">
+      <c r="L77" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M77" s="36" t="inlineStr">
@@ -14701,7 +14719,7 @@
           </r>
         </is>
       </c>
-      <c r="O77" s="47" t="inlineStr">
+      <c r="O77" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -15097,7 +15115,7 @@
       <c r="L79" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="M79" s="57" t="inlineStr">
+      <c r="M79" s="58" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -15233,7 +15251,7 @@
           </r>
         </is>
       </c>
-      <c r="L80" s="46" t="n">
+      <c r="L80" s="47" t="n">
         <v>9</v>
       </c>
       <c r="M80" s="36" t="inlineStr">
@@ -15263,7 +15281,7 @@
           </r>
         </is>
       </c>
-      <c r="O80" s="47" t="inlineStr">
+      <c r="O80" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -15351,7 +15369,7 @@
           </r>
         </is>
       </c>
-      <c r="L81" s="46" t="n">
+      <c r="L81" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M81" s="36" t="inlineStr">
@@ -15463,7 +15481,7 @@
           </r>
         </is>
       </c>
-      <c r="L82" s="46" t="n">
+      <c r="L82" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M82" s="36" t="inlineStr">
@@ -15680,7 +15698,7 @@
           </r>
         </is>
       </c>
-      <c r="L84" s="46" t="n">
+      <c r="L84" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M84" s="36" t="inlineStr">
@@ -15793,7 +15811,7 @@
           </r>
         </is>
       </c>
-      <c r="L85" s="46" t="n">
+      <c r="L85" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M85" s="36" t="inlineStr">
@@ -15906,7 +15924,7 @@
           </r>
         </is>
       </c>
-      <c r="L86" s="46" t="n">
+      <c r="L86" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M86" s="36" t="inlineStr">
@@ -16019,7 +16037,7 @@
           </r>
         </is>
       </c>
-      <c r="L87" s="46" t="n">
+      <c r="L87" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M87" s="36" t="inlineStr">
@@ -16132,7 +16150,7 @@
           </r>
         </is>
       </c>
-      <c r="L88" s="46" t="n">
+      <c r="L88" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M88" s="36" t="inlineStr">
@@ -16575,7 +16593,7 @@
           </r>
         </is>
       </c>
-      <c r="O90" s="47" t="inlineStr">
+      <c r="O90" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -16690,7 +16708,7 @@
       <c r="S91" s="45" t="inlineStr"/>
     </row>
     <row r="92" ht="141" customHeight="1">
-      <c r="A92" s="51" t="inlineStr">
+      <c r="A92" s="52" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16712,7 +16730,7 @@
           </r>
         </is>
       </c>
-      <c r="B92" s="51" t="inlineStr">
+      <c r="B92" s="52" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16734,7 +16752,7 @@
           </r>
         </is>
       </c>
-      <c r="C92" s="51" t="inlineStr">
+      <c r="C92" s="52" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16807,11 +16825,11 @@
           </r>
         </is>
       </c>
-      <c r="D92" s="52" t="inlineStr"/>
-      <c r="E92" s="53" t="n">
+      <c r="D92" s="53" t="inlineStr"/>
+      <c r="E92" s="54" t="n">
         <v>8</v>
       </c>
-      <c r="F92" s="51" t="inlineStr">
+      <c r="F92" s="52" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16928,7 +16946,7 @@
       <c r="S92" s="45" t="inlineStr"/>
     </row>
     <row r="93" ht="181.5" customHeight="1">
-      <c r="A93" s="51" t="inlineStr">
+      <c r="A93" s="52" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16950,7 +16968,7 @@
           </r>
         </is>
       </c>
-      <c r="B93" s="51" t="inlineStr">
+      <c r="B93" s="52" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16972,7 +16990,7 @@
           </r>
         </is>
       </c>
-      <c r="C93" s="51" t="inlineStr">
+      <c r="C93" s="52" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17097,17 +17115,17 @@
           </r>
         </is>
       </c>
-      <c r="D93" s="52" t="inlineStr">
+      <c r="D93" s="53" t="inlineStr">
         <is>
           <t>HZ-002
 HZ-005
 HZ-006</t>
         </is>
       </c>
-      <c r="E93" s="53" t="n">
+      <c r="E93" s="54" t="n">
         <v>10</v>
       </c>
-      <c r="F93" s="51" t="inlineStr">
+      <c r="F93" s="52" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17274,7 +17292,7 @@
           </r>
         </is>
       </c>
-      <c r="O93" s="50" t="inlineStr">
+      <c r="O93" s="51" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
@@ -17486,7 +17504,7 @@
           </r>
         </is>
       </c>
-      <c r="L94" s="46" t="n">
+      <c r="L94" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M94" s="36" t="inlineStr">
@@ -17516,7 +17534,7 @@
           </r>
         </is>
       </c>
-      <c r="O94" s="47" t="inlineStr">
+      <c r="O94" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -17634,7 +17652,7 @@
           </r>
         </is>
       </c>
-      <c r="O95" s="47" t="inlineStr">
+      <c r="O95" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -17722,7 +17740,7 @@
           </r>
         </is>
       </c>
-      <c r="L96" s="46" t="n">
+      <c r="L96" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M96" s="36" t="inlineStr">
@@ -17752,7 +17770,7 @@
           </r>
         </is>
       </c>
-      <c r="O96" s="47" t="inlineStr">
+      <c r="O96" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -17870,7 +17888,7 @@
           </r>
         </is>
       </c>
-      <c r="O97" s="47" t="inlineStr">
+      <c r="O97" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -17958,7 +17976,7 @@
           </r>
         </is>
       </c>
-      <c r="L98" s="46" t="n">
+      <c r="L98" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M98" s="36" t="inlineStr">
@@ -17988,7 +18006,7 @@
           </r>
         </is>
       </c>
-      <c r="O98" s="47" t="inlineStr">
+      <c r="O98" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -18408,7 +18426,7 @@
           </r>
         </is>
       </c>
-      <c r="L100" s="46" t="n">
+      <c r="L100" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M100" s="36" t="inlineStr">
@@ -18794,7 +18812,7 @@
           </r>
         </is>
       </c>
-      <c r="L102" s="46" t="n">
+      <c r="L102" s="47" t="n">
         <v>9</v>
       </c>
       <c r="M102" s="36" t="inlineStr">
@@ -19174,7 +19192,7 @@
           </r>
         </is>
       </c>
-      <c r="O104" s="54" t="inlineStr">
+      <c r="O104" s="55" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
@@ -19521,7 +19539,7 @@
           </r>
         </is>
       </c>
-      <c r="L106" s="46" t="n">
+      <c r="L106" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M106" s="36" t="inlineStr">
@@ -19551,7 +19569,7 @@
           </r>
         </is>
       </c>
-      <c r="O106" s="47" t="inlineStr">
+      <c r="O106" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -19630,7 +19648,7 @@
           </r>
         </is>
       </c>
-      <c r="L107" s="46" t="n">
+      <c r="L107" s="47" t="n">
         <v>9</v>
       </c>
       <c r="M107" s="36" t="inlineStr">
@@ -19660,7 +19678,7 @@
           </r>
         </is>
       </c>
-      <c r="O107" s="47" t="inlineStr">
+      <c r="O107" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -20046,7 +20064,7 @@
           </r>
         </is>
       </c>
-      <c r="O109" s="54" t="inlineStr">
+      <c r="O109" s="55" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
@@ -20124,7 +20142,7 @@
           </r>
         </is>
       </c>
-      <c r="L110" s="46" t="n">
+      <c r="L110" s="47" t="n">
         <v>10</v>
       </c>
       <c r="M110" s="36" t="inlineStr">
@@ -20154,7 +20172,7 @@
           </r>
         </is>
       </c>
-      <c r="O110" s="47" t="inlineStr">
+      <c r="O110" s="46" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -20482,7 +20500,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.37 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.38 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -20512,79 +20530,79 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="58" t="inlineStr">
+      <c r="A1" s="59" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B1" s="58" t="inlineStr">
+      <c r="B1" s="59" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="C1" s="58" t="inlineStr">
+      <c r="C1" s="59" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" s="58" t="inlineStr">
+      <c r="D1" s="59" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E1" s="58" t="inlineStr">
+      <c r="E1" s="59" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="58" t="inlineStr">
+      <c r="F1" s="59" t="inlineStr">
         <is>
           <t>Causes</t>
         </is>
       </c>
-      <c r="G1" s="58" t="inlineStr">
+      <c r="G1" s="59" t="inlineStr">
         <is>
           <t>Revised S/O/D</t>
         </is>
       </c>
-      <c r="H1" s="58" t="inlineStr">
+      <c r="H1" s="59" t="inlineStr">
         <is>
           <t>Revised AP</t>
         </is>
       </c>
-      <c r="I1" s="58" t="inlineStr">
+      <c r="I1" s="59" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
     </row>
     <row r="2" ht="127.5" customHeight="1">
-      <c r="A2" s="59" t="inlineStr">
+      <c r="A2" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-001</t>
         </is>
       </c>
-      <c r="B2" s="59" t="inlineStr">
+      <c r="B2" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C2" s="59" t="inlineStr">
+      <c r="C2" s="60" t="inlineStr">
         <is>
           <t>Derive steering and acceleration envelopes from measurements on the reference vehicle and set the panda limits from them, independently of the SoC limits (same as SWF-ACT-003, FSC FOI-001)</t>
         </is>
       </c>
-      <c r="D2" s="59" t="inlineStr">
+      <c r="D2" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E2" s="59" t="inlineStr">
+      <c r="E2" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F2" s="59" t="inlineStr">
+      <c r="F2" s="60" t="inlineStr">
         <is>
           <t>SFM-002.C1
 SFM-002.C2
@@ -20597,37 +20615,37 @@
 SFM-029.C2</t>
         </is>
       </c>
-      <c r="G2" s="59" t="inlineStr"/>
-      <c r="H2" s="59" t="inlineStr"/>
-      <c r="I2" s="59" t="inlineStr"/>
+      <c r="G2" s="60" t="inlineStr"/>
+      <c r="H2" s="60" t="inlineStr"/>
+      <c r="I2" s="60" t="inlineStr"/>
     </row>
     <row r="3" ht="168" customHeight="1">
-      <c r="A3" s="59" t="inlineStr">
+      <c r="A3" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-002</t>
         </is>
       </c>
-      <c r="B3" s="59" t="inlineStr">
+      <c r="B3" s="60" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C3" s="59" t="inlineStr">
+      <c r="C3" s="60" t="inlineStr">
         <is>
           <t>Requirements-based tests for the host safety-relevant functions (selfdrived, controlsd, pandad, car interface, locationd bounds, monitoring policy), proven by mutation or fault injection and run as a CI gate (see SWF host actions)</t>
         </is>
       </c>
-      <c r="D3" s="59" t="inlineStr">
+      <c r="D3" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E3" s="59" t="inlineStr">
+      <c r="E3" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F3" s="59" t="inlineStr">
+      <c r="F3" s="60" t="inlineStr">
         <is>
           <t>SFM-002.C4
 SFM-004.C3
@@ -20643,37 +20661,37 @@
 SFM-037.C3</t>
         </is>
       </c>
-      <c r="G3" s="59" t="inlineStr"/>
-      <c r="H3" s="59" t="inlineStr"/>
-      <c r="I3" s="59" t="inlineStr"/>
+      <c r="G3" s="60" t="inlineStr"/>
+      <c r="H3" s="60" t="inlineStr"/>
+      <c r="I3" s="60" t="inlineStr"/>
     </row>
     <row r="4" ht="409" customHeight="1">
-      <c r="A4" s="59" t="inlineStr">
+      <c r="A4" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-003</t>
         </is>
       </c>
-      <c r="B4" s="59" t="inlineStr">
+      <c r="B4" s="60" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C4" s="59" t="inlineStr">
+      <c r="C4" s="60" t="inlineStr">
         <is>
           <t>Execute system integration and vehicle verification on the reference car (WP-S-08, WP-S-09) and the HIL bench (D-04): steering sign and torque response, EPS and powertrain interface behaviour (lockouts, ignored requests), brake, accelerator and cancel paths, intercept-switch and harness faults, 12 V interruptions, alert latency and audibility, CPU-load soak</t>
         </is>
       </c>
-      <c r="D4" s="59" t="inlineStr">
+      <c r="D4" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E4" s="59" t="inlineStr">
+      <c r="E4" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F4" s="59" t="inlineStr">
+      <c r="F4" s="60" t="inlineStr">
         <is>
           <t>SFM-002.C5
 SFM-003.C1
@@ -20707,76 +20725,76 @@
 SFM-033.C6</t>
         </is>
       </c>
-      <c r="G4" s="59" t="inlineStr"/>
-      <c r="H4" s="59" t="inlineStr"/>
-      <c r="I4" s="59" t="inlineStr"/>
+      <c r="G4" s="60" t="inlineStr"/>
+      <c r="H4" s="60" t="inlineStr"/>
+      <c r="I4" s="60" t="inlineStr"/>
     </row>
     <row r="5" ht="168" customHeight="1">
-      <c r="A5" s="59" t="inlineStr">
+      <c r="A5" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-005</t>
         </is>
       </c>
-      <c r="B5" s="59" t="inlineStr">
+      <c r="B5" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C5" s="59" t="inlineStr">
+      <c r="C5" s="60" t="inlineStr">
         <is>
           <t>Implement the reaction when driver awareness reaches zero (driverUnresponsive3 / driverDistracted3 have no disable reaction at BL-004 or BL-005), the safe state of SG-010 (WP-C-03 SG-08, ASIL A; DQ-205). Decided by the lead (DQ-365, option A, 2026-10-16) and specified in TSR-633 (WP-S-02 v0.26) with TSR-611; keep the lane and decelerate in lane to a standstill with the terminal alert sounding, hold the vehicle stopped, and lock out re-engagement and resumption until the driver responds. WP-S-04 v0.12 §3.8.4 gives a preliminary time to the reaction (18 s vision, 30 s wheel-touch from loss of attention; OI-11); SFM-025.C1 is re-rated once TSR-633 is implemented and that time is confirmed</t>
         </is>
       </c>
-      <c r="D5" s="59" t="inlineStr">
+      <c r="D5" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E5" s="59" t="inlineStr">
+      <c r="E5" s="60" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F5" s="59" t="inlineStr">
+      <c r="F5" s="60" t="inlineStr">
         <is>
           <t>SFM-025.C1</t>
         </is>
       </c>
-      <c r="G5" s="59" t="inlineStr"/>
-      <c r="H5" s="59" t="inlineStr"/>
-      <c r="I5" s="59" t="inlineStr">
+      <c r="G5" s="60" t="inlineStr"/>
+      <c r="H5" s="60" t="inlineStr"/>
+      <c r="I5" s="60" t="inlineStr">
         <is>
           <t>Code done in BL-007: the manoeuvre is latched until the driver takes over, held at standstill and the alert re-raised (#372, dacd8f7, minimum_risk.py, test_minimum_risk.py), the lockout runs from the takeover (test_monitoring.py), a longitudinal maneuver stays stopped under forced deceleration (test_longitudinal.py), and the stop is announced by a countdown (#374, 59e22e0, TSR-624); all in the CI unit_tests job. SFM-025.C1 re-rated at BL-007 to a defect of that code (O 5 D 8). Open: the PCM standstill hold over time (AOU-16 vehicle test), the measured deceleration and stop time, and the time to the reaction (WP-S-04 OI-11)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="59" t="inlineStr">
+      <c r="A6" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-006</t>
         </is>
       </c>
-      <c r="B6" s="59" t="inlineStr">
+      <c r="B6" s="60" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C6" s="59" t="inlineStr">
+      <c r="C6" s="60" t="inlineStr">
         <is>
           <t>Establish on the reference car which stock TSS2 functions (PCS/AEB, FCW) remain available with LionDriver installed and longitudinal control enabled, and verify the stock pre-collision path after installation (PFMEA PFM-014)</t>
         </is>
       </c>
-      <c r="D6" s="59" t="inlineStr">
+      <c r="D6" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E6" s="59" t="inlineStr">
+      <c r="E6" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F6" s="59" t="inlineStr">
+      <c r="F6" s="60" t="inlineStr">
         <is>
           <t>SFM-010.C2
 SFM-033.C1
@@ -20784,37 +20802,37 @@
 SFM-036.C2</t>
         </is>
       </c>
-      <c r="G6" s="59" t="inlineStr"/>
-      <c r="H6" s="59" t="inlineStr"/>
-      <c r="I6" s="59" t="inlineStr"/>
+      <c r="G6" s="60" t="inlineStr"/>
+      <c r="H6" s="60" t="inlineStr"/>
+      <c r="I6" s="60" t="inlineStr"/>
     </row>
     <row r="7" ht="73.5" customHeight="1">
-      <c r="A7" s="59" t="inlineStr">
+      <c r="A7" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-007</t>
         </is>
       </c>
-      <c r="B7" s="59" t="inlineStr">
+      <c r="B7" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C7" s="59" t="inlineStr">
+      <c r="C7" s="60" t="inlineStr">
         <is>
           <t>Supervise the alert channels: treat loss of ui or soundd liveness, or a stale displayed state, as a fault that escalates (audible fallback, disengagement) instead of continuing silently</t>
         </is>
       </c>
-      <c r="D7" s="59" t="inlineStr">
+      <c r="D7" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E7" s="59" t="inlineStr">
+      <c r="E7" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F7" s="59" t="inlineStr">
+      <c r="F7" s="60" t="inlineStr">
         <is>
           <t>SFM-015.C1
 SFM-026.C1
@@ -20823,76 +20841,76 @@
 SFM-028.C1</t>
         </is>
       </c>
-      <c r="G7" s="59" t="inlineStr"/>
-      <c r="H7" s="59" t="inlineStr"/>
-      <c r="I7" s="59" t="inlineStr"/>
+      <c r="G7" s="60" t="inlineStr"/>
+      <c r="H7" s="60" t="inlineStr"/>
+      <c r="I7" s="60" t="inlineStr"/>
     </row>
     <row r="8" ht="73.5" customHeight="1">
-      <c r="A8" s="59" t="inlineStr">
+      <c r="A8" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-008</t>
         </is>
       </c>
-      <c r="B8" s="59" t="inlineStr">
+      <c r="B8" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C8" s="59" t="inlineStr">
+      <c r="C8" s="60" t="inlineStr">
         <is>
           <t>Allow engagement only when the fingerprint, CarParams and panda safety parameter match the reference configuration AC-001 (refuse fuzzy matches in the reference build); see PFMEA PFM-013</t>
         </is>
       </c>
-      <c r="D8" s="59" t="inlineStr">
+      <c r="D8" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E8" s="59" t="inlineStr">
+      <c r="E8" s="60" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F8" s="59" t="inlineStr">
+      <c r="F8" s="60" t="inlineStr">
         <is>
           <t>SFM-032.C1</t>
         </is>
       </c>
-      <c r="G8" s="59" t="inlineStr"/>
-      <c r="H8" s="59" t="inlineStr"/>
-      <c r="I8" s="59" t="inlineStr">
+      <c r="G8" s="60" t="inlineStr"/>
+      <c r="H8" s="60" t="inlineStr"/>
+      <c r="I8" s="60" t="inlineStr">
         <is>
           <t>BL-005: the reference build is the default (LionDriver #36), the panda accepts only TOYOTA parameter 73 (reference_lock.h) and pandad configures a car mode only on a reference panda (#41). Fuzzy fingerprint matches are still accepted on the host (SFM-032.C1)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="100.5" customHeight="1">
-      <c r="A9" s="59" t="inlineStr">
+      <c r="A9" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-009</t>
         </is>
       </c>
-      <c r="B9" s="59" t="inlineStr">
+      <c r="B9" s="60" t="inlineStr">
         <is>
           <t>prevention</t>
         </is>
       </c>
-      <c r="C9" s="59" t="inlineStr">
+      <c r="C9" s="60" t="inlineStr">
         <is>
           <t>Produce SOTIF / ISO PAS 8800 evidence for the neural-network elements (driving model, lead detection, driver monitoring model) per WP-V-02..04, including fault-induced inputs (corrupted or stale frames)</t>
         </is>
       </c>
-      <c r="D9" s="59" t="inlineStr">
+      <c r="D9" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E9" s="59" t="inlineStr">
+      <c r="E9" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F9" s="59" t="inlineStr">
+      <c r="F9" s="60" t="inlineStr">
         <is>
           <t>SFM-002.C2
 SFM-003.C3
@@ -20903,37 +20921,37 @@
 SFM-022.C2</t>
         </is>
       </c>
-      <c r="G9" s="59" t="inlineStr"/>
-      <c r="H9" s="59" t="inlineStr"/>
-      <c r="I9" s="59" t="inlineStr"/>
+      <c r="G9" s="60" t="inlineStr"/>
+      <c r="H9" s="60" t="inlineStr"/>
+      <c r="I9" s="60" t="inlineStr"/>
     </row>
     <row r="10" ht="73.5" customHeight="1">
-      <c r="A10" s="59" t="inlineStr">
+      <c r="A10" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-010</t>
         </is>
       </c>
-      <c r="B10" s="59" t="inlineStr">
+      <c r="B10" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C10" s="59" t="inlineStr">
+      <c r="C10" s="60" t="inlineStr">
         <is>
           <t>Justify every SOFT_DISABLE reaction and debounce against the FTTI (WP-S-04) and alert at once when the panda withdraws authority while engaged (controlsMismatch debounce)</t>
         </is>
       </c>
-      <c r="D10" s="59" t="inlineStr">
+      <c r="D10" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E10" s="59" t="inlineStr">
+      <c r="E10" s="60" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F10" s="59" t="inlineStr">
+      <c r="F10" s="60" t="inlineStr">
         <is>
           <t>SFM-014.C2
 SFM-015.C2
@@ -20941,466 +20959,466 @@
 SFM-016.C2</t>
         </is>
       </c>
-      <c r="G10" s="59" t="inlineStr"/>
-      <c r="H10" s="59" t="inlineStr"/>
-      <c r="I10" s="59" t="inlineStr">
+      <c r="G10" s="60" t="inlineStr"/>
+      <c r="H10" s="60" t="inlineStr"/>
+      <c r="I10" s="60" t="inlineStr">
         <is>
           <t>controlsMismatch debounce cut from 200 cumulative samples (~2 s) to 2 consecutive samples, at most 0.5 s (change-2026-10-13-host-supervision.md); credited at BL-005 (SFM-015.C2 M 6). FTTI justification of SOFT_DISABLE reactions open</t>
         </is>
       </c>
     </row>
     <row r="11" ht="33" customHeight="1">
-      <c r="A11" s="59" t="inlineStr">
+      <c r="A11" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-011</t>
         </is>
       </c>
-      <c r="B11" s="59" t="inlineStr">
+      <c r="B11" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C11" s="59" t="inlineStr">
+      <c r="C11" s="60" t="inlineStr">
         <is>
           <t>Alert the driver when stock cruise stays engaged while the item is disengaged (cruiseMismatch has no alert at BL-004)</t>
         </is>
       </c>
-      <c r="D11" s="59" t="inlineStr">
+      <c r="D11" s="60" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E11" s="60" t="inlineStr">
+      <c r="E11" s="61" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F11" s="59" t="inlineStr">
+      <c r="F11" s="60" t="inlineStr">
         <is>
           <t>SFM-021.C1
 SFM-021.C2</t>
         </is>
       </c>
-      <c r="G11" s="59" t="inlineStr"/>
-      <c r="H11" s="59" t="inlineStr"/>
-      <c r="I11" s="59" t="inlineStr">
+      <c r="G11" s="60" t="inlineStr"/>
+      <c r="H11" s="60" t="inlineStr"/>
+      <c r="I11" s="60" t="inlineStr">
         <is>
           <t>cruiseMismatch now alerts after 1 s (change-2026-10-13-host-supervision.md); see SWF-ACT-034</t>
         </is>
       </c>
     </row>
     <row r="12" ht="73.5" customHeight="1">
-      <c r="A12" s="59" t="inlineStr">
+      <c r="A12" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-012</t>
         </is>
       </c>
-      <c r="B12" s="59" t="inlineStr">
+      <c r="B12" s="60" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C12" s="59" t="inlineStr">
+      <c r="C12" s="60" t="inlineStr">
         <is>
           <t>Measure on the HIL bench and the reference car (WP-V-05) how the panda reacts to over-limit and not-engaged steering and acceleration frames and to driver brake, gas and cancel inputs, and what the EPS and PCM do when frames are refused; re-rate the MSR rows from code-derived to measured timing</t>
         </is>
       </c>
-      <c r="D12" s="59" t="inlineStr"/>
-      <c r="E12" s="59" t="inlineStr">
+      <c r="D12" s="60" t="inlineStr"/>
+      <c r="E12" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F12" s="59" t="inlineStr"/>
-      <c r="G12" s="59" t="inlineStr"/>
-      <c r="H12" s="59" t="inlineStr"/>
-      <c r="I12" s="59" t="inlineStr"/>
+      <c r="F12" s="60" t="inlineStr"/>
+      <c r="G12" s="60" t="inlineStr"/>
+      <c r="H12" s="60" t="inlineStr"/>
+      <c r="I12" s="60" t="inlineStr"/>
     </row>
     <row r="13" ht="87" customHeight="1">
-      <c r="A13" s="59" t="inlineStr">
+      <c r="A13" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-013</t>
         </is>
       </c>
-      <c r="B13" s="59" t="inlineStr">
+      <c r="B13" s="60" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C13" s="59" t="inlineStr">
+      <c r="C13" s="60" t="inlineStr">
         <is>
           <t>Check on the host, within the SG-01 FTTI, that the panda reports controls_allowed false while the item is disengaged (the reverse of the controlsMismatch check, which at BL-005 still covers only engaged with authority withdrawn), with a disable and an alert. The requirement is TSR-630, within 0.3 s (WP-S-02 §12.3a; WP-S-04 T-32, not implemented)</t>
         </is>
       </c>
-      <c r="D13" s="59" t="inlineStr"/>
-      <c r="E13" s="59" t="inlineStr">
+      <c r="D13" s="60" t="inlineStr"/>
+      <c r="E13" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F13" s="59" t="inlineStr"/>
-      <c r="G13" s="59" t="inlineStr"/>
-      <c r="H13" s="59" t="inlineStr"/>
-      <c r="I13" s="59" t="inlineStr"/>
+      <c r="F13" s="60" t="inlineStr"/>
+      <c r="G13" s="60" t="inlineStr"/>
+      <c r="H13" s="60" t="inlineStr"/>
+      <c r="I13" s="60" t="inlineStr"/>
     </row>
     <row r="14" ht="46.5" customHeight="1">
-      <c r="A14" s="59" t="inlineStr">
+      <c r="A14" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-014</t>
         </is>
       </c>
-      <c r="B14" s="59" t="inlineStr">
+      <c r="B14" s="60" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C14" s="59" t="inlineStr">
+      <c r="C14" s="60" t="inlineStr">
         <is>
           <t>Specify in the TSC a steering-direction plausibility monitor (commanded torque sign against measured yaw rate and lane-relative lateral motion), or justify its absence against HZ-003</t>
         </is>
       </c>
-      <c r="D14" s="59" t="inlineStr"/>
-      <c r="E14" s="59" t="inlineStr">
+      <c r="D14" s="60" t="inlineStr"/>
+      <c r="E14" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F14" s="59" t="inlineStr"/>
-      <c r="G14" s="59" t="inlineStr"/>
-      <c r="H14" s="59" t="inlineStr"/>
-      <c r="I14" s="59" t="inlineStr"/>
+      <c r="F14" s="60" t="inlineStr"/>
+      <c r="G14" s="60" t="inlineStr"/>
+      <c r="H14" s="60" t="inlineStr"/>
+      <c r="I14" s="60" t="inlineStr"/>
     </row>
     <row r="15" ht="100.5" customHeight="1">
-      <c r="A15" s="59" t="inlineStr">
+      <c r="A15" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-015</t>
         </is>
       </c>
-      <c r="B15" s="59" t="inlineStr">
+      <c r="B15" s="60" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C15" s="59" t="inlineStr">
+      <c r="C15" s="60" t="inlineStr">
         <is>
           <t>Detect stale commands and inputs within the SG-01 FTTI: command-frame freshness in the MCU with an active zero frame (TSR-408, TSR-109) and frozen-content and age checks on model outputs in controlsd (TSR-602, TSR-631, AIR-17)</t>
         </is>
       </c>
-      <c r="D15" s="59" t="inlineStr"/>
-      <c r="E15" s="59" t="inlineStr">
+      <c r="D15" s="60" t="inlineStr"/>
+      <c r="E15" s="60" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F15" s="59" t="inlineStr"/>
-      <c r="G15" s="59" t="inlineStr"/>
-      <c r="H15" s="59" t="inlineStr"/>
-      <c r="I15" s="59" t="inlineStr">
+      <c r="F15" s="60" t="inlineStr"/>
+      <c r="G15" s="60" t="inlineStr"/>
+      <c r="H15" s="60" t="inlineStr"/>
+      <c r="I15" s="60" t="inlineStr">
         <is>
           <t>BL-005: command-frame arrival in the MCU (TSR-408, 50 ms STEERING_LKA, reference build by default) and input age checks in controlsd (TSR-602) are in. Open: the active zero frame (TSR-109), a frozen-content check on model outputs, and stale data with fresh timestamps (SFM-006.C1 to C3). The frozen-content check is TSR-631, with the age taken from the source timestamp (WP-S-02 §12.3a)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="73.5" customHeight="1">
-      <c r="A16" s="59" t="inlineStr">
+      <c r="A16" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-016</t>
         </is>
       </c>
-      <c r="B16" s="59" t="inlineStr">
+      <c r="B16" s="60" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C16" s="59" t="inlineStr">
+      <c r="C16" s="60" t="inlineStr">
         <is>
           <t>Supervise driver override in the panda: driver steering torque above the override threshold limits or revokes lateral authority within the SG-05 0.2 s budget (TSR-304). Behaviour decided by the lead (DQ-053, option A): back off on override and show a cue. Requirements: TSR-304 (timing tied to the SG-05 budget) and TSR-628 (WP-S-02 §12.3a)</t>
         </is>
       </c>
-      <c r="D16" s="59" t="inlineStr"/>
-      <c r="E16" s="59" t="inlineStr">
+      <c r="D16" s="60" t="inlineStr"/>
+      <c r="E16" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F16" s="59" t="inlineStr">
+      <c r="F16" s="60" t="inlineStr">
         <is>
           <t>SFM-018.C3</t>
         </is>
       </c>
-      <c r="G16" s="59" t="inlineStr"/>
-      <c r="H16" s="59" t="inlineStr"/>
-      <c r="I16" s="59" t="inlineStr"/>
+      <c r="G16" s="60" t="inlineStr"/>
+      <c r="H16" s="60" t="inlineStr"/>
+      <c r="I16" s="60" t="inlineStr"/>
     </row>
     <row r="17" ht="87" customHeight="1">
-      <c r="A17" s="59" t="inlineStr">
+      <c r="A17" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-017</t>
         </is>
       </c>
-      <c r="B17" s="59" t="inlineStr">
+      <c r="B17" s="60" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C17" s="59" t="inlineStr">
+      <c r="C17" s="60" t="inlineStr">
         <is>
           <t>Add WP-S-04 FTTI rows for the warning paths without one (insufficient lateral control, late or insufficient braking warnings, SG-008 unintended engagement, driver monitoring), so these mechanisms can be compared with a time budget</t>
         </is>
       </c>
-      <c r="D17" s="59" t="inlineStr"/>
-      <c r="E17" s="60" t="inlineStr">
+      <c r="D17" s="60" t="inlineStr"/>
+      <c r="E17" s="61" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F17" s="59" t="inlineStr"/>
-      <c r="G17" s="59" t="inlineStr"/>
-      <c r="H17" s="59" t="inlineStr"/>
-      <c r="I17" s="59" t="inlineStr">
+      <c r="F17" s="60" t="inlineStr"/>
+      <c r="G17" s="60" t="inlineStr"/>
+      <c r="H17" s="60" t="inlineStr"/>
+      <c r="I17" s="60" t="inlineStr">
         <is>
           <t>WP-S-04 v0.7 §3.7 (four rows) and §3.8, with T-30 to T-33. Rev 0.15 compares SFM-004, SFM-010.C2/C3, SFM-012.C1 and SFM-013.C1/C2 with them. Driver monitoring (SFM-022.C3, SFM-025.C1) waits for the H-09 FTTI (§3.8.4); follow-up is SFM-ACT-005. Late warnings found: SFM-ACT-021 (lateral) and SFM-ACT-022 (braking)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="100.5" customHeight="1">
-      <c r="A18" s="59" t="inlineStr">
+      <c r="A18" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-018</t>
         </is>
       </c>
-      <c r="B18" s="59" t="inlineStr">
+      <c r="B18" s="60" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C18" s="59" t="inlineStr">
+      <c r="C18" s="60" t="inlineStr">
         <is>
           <t>Detect silent loss of the actuation path: report forwarded and refused TX frames from the panda, and compare EPS and PCM acceptance (LKA_STATE, ACC status) with the commands, warning within the SG-02/06 1 s budget</t>
         </is>
       </c>
-      <c r="D18" s="59" t="inlineStr"/>
-      <c r="E18" s="59" t="inlineStr">
+      <c r="D18" s="60" t="inlineStr"/>
+      <c r="E18" s="60" t="inlineStr">
         <is>
           <t>in progress</t>
         </is>
       </c>
-      <c r="F18" s="59" t="inlineStr"/>
-      <c r="G18" s="59" t="inlineStr"/>
-      <c r="H18" s="59" t="inlineStr"/>
-      <c r="I18" s="59" t="inlineStr">
+      <c r="F18" s="60" t="inlineStr"/>
+      <c r="G18" s="60" t="inlineStr"/>
+      <c r="H18" s="60" t="inlineStr"/>
+      <c r="I18" s="60" t="inlineStr">
         <is>
           <t>BL-005: frames that stop reaching the panda are detected (TSR-408) and alerted within 0.5 s (TSR-621), credited on SFM-005.C2 and SFM-011.C2. Open: frames that reach the panda but are not accepted by the EPS or PCM (SFM-005.C1, SFM-011.C1). Requirements: TSR-632 (per-ID transmitted and refused counts), TSR-626(d)/(e) (EPS and PCM acceptance status) and TSR-615, warning within 1 s (WP-S-02 §12.3a)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="59" t="inlineStr">
+      <c r="A19" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-019</t>
         </is>
       </c>
-      <c r="B19" s="59" t="inlineStr">
+      <c r="B19" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C19" s="59" t="inlineStr">
+      <c r="C19" s="60" t="inlineStr">
         <is>
           <t>Revoke lateral authority in the panda when it rejects a steering frame while authority is granted, and keep it revoked until a new valid engagement (TSR-108; lead decision DQ-060, option A). At BL-005 the frame is dropped and only the host disengages (pandaTxBlocked)</t>
         </is>
       </c>
-      <c r="D19" s="59" t="inlineStr"/>
-      <c r="E19" s="59" t="inlineStr">
+      <c r="D19" s="60" t="inlineStr"/>
+      <c r="E19" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F19" s="59" t="inlineStr">
+      <c r="F19" s="60" t="inlineStr">
         <is>
           <t>SFM-002.C1
 SFM-002.C2
 SFM-002.C4</t>
         </is>
       </c>
-      <c r="G19" s="59" t="inlineStr"/>
-      <c r="H19" s="59" t="inlineStr"/>
-      <c r="I19" s="59" t="inlineStr"/>
+      <c r="G19" s="60" t="inlineStr"/>
+      <c r="H19" s="60" t="inlineStr"/>
+      <c r="I19" s="60" t="inlineStr"/>
     </row>
     <row r="20" ht="370.5" customHeight="1">
-      <c r="A20" s="59" t="inlineStr">
+      <c r="A20" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-020</t>
         </is>
       </c>
-      <c r="B20" s="59" t="inlineStr">
+      <c r="B20" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C20" s="59" t="inlineStr">
+      <c r="C20" s="60" t="inlineStr">
         <is>
           <t>Stand down during stock AEB: while the car reports a stock PCS/AEB event (stockAeb), LionDriver requests zero acceleration, so stock AEB does not depend on PCM arbitration alone (AOU-04R). Lead decision DQ-300, option A (2026-10-18); the AOU-04R vehicle test still runs. SFM-036.C1; FTA BE-7.13</t>
         </is>
       </c>
-      <c r="D20" s="59" t="inlineStr"/>
-      <c r="E20" s="60" t="inlineStr">
+      <c r="D20" s="60" t="inlineStr"/>
+      <c r="E20" s="61" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F20" s="59" t="inlineStr">
+      <c r="F20" s="60" t="inlineStr">
         <is>
           <t>SFM-036.C1</t>
         </is>
       </c>
-      <c r="G20" s="59" t="inlineStr">
+      <c r="G20" s="60" t="inlineStr">
         <is>
           <t>10/5/8</t>
         </is>
       </c>
-      <c r="H20" s="61" t="inlineStr">
+      <c r="H20" s="62" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="I20" s="59" t="inlineStr">
+      <c r="I20" s="60" t="inlineStr">
         <is>
           <t>Merged in jherrodthomas/LionDriver#292 (c045874): stock_aeb_stand_down in longcontrol.py, called from controlsd.py, caps the acceleration target and the upper PID limit at 0 m/s² while stockAeb is set and keeps any braking request; selfdrive/controls/tests/test_stock_aeb.py, 4 tests. CI: tests run 39296172878 on liondriver-dev 6126485 (2026-10-19), unit tests job 1578 passed, 42 skipped, 3 xfailed, no failures or collection errors; process replay passed. The runner collects every openpilot/**/test_*.py and prints no test names, so the four tests are shown to have run by collection, not by name; the file has no skip. Second layer, opendbc e233362 (#311, SWSR-713h): the Toyota controller caps the 0x343 command at 0 from the first frame of the event, after its rate limit, PID and pitch compensation (impact OI-2 done); its 6 test_carcontroller.py cases ran locally (pin record). The openpilot runner does not run opendbc_repo tests; tests.yml in the opendbc fork triggers on pull requests, but a CI run on jherrodthomas/opendbc#20 is not confirmed here (the pin record says none). Impact records assurance/07-supporting/impact/change-2026-10-19-stock-aeb-stand-down.md and change-2026-10-19-pin-e233362.md. TSR-713 and FSR-07.07 implemented (#313). Not verified on the vehicle (OI-3, the AOU-04R test, also checks that stockAeb is reported during a PCS event) and not reviewed independently. In BL-007, where SFM-036.C1 is re-rated O 8 D 10 -&gt; O 5 D 8 as predicted below (targeted tests, not mutation-proven: rating tables D 8)</t>
         </is>
       </c>
     </row>
     <row r="21" ht="73.5" customHeight="1">
-      <c r="A21" s="59" t="inlineStr">
+      <c r="A21" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-021</t>
         </is>
       </c>
-      <c r="B21" s="59" t="inlineStr">
+      <c r="B21" s="60" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C21" s="59" t="inlineStr">
+      <c r="C21" s="60" t="inlineStr">
         <is>
           <t>Make the insufficient-lateral-control warning timely (WP-S-04 §3.8.1): warn before the deficit has lasted 0.4 s, for example from the planned curvature against the envelope, or keep the deficit at or below about 0.5 m/s² through the steering limits and the ODD curve bound (WP-S-04 OI-2). A change to the ODD bound is a lead decision</t>
         </is>
       </c>
-      <c r="D21" s="59" t="inlineStr"/>
-      <c r="E21" s="59" t="inlineStr">
+      <c r="D21" s="60" t="inlineStr"/>
+      <c r="E21" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F21" s="59" t="inlineStr">
+      <c r="F21" s="60" t="inlineStr">
         <is>
           <t>SFM-038.C3</t>
         </is>
       </c>
-      <c r="G21" s="59" t="inlineStr"/>
-      <c r="H21" s="59" t="inlineStr"/>
-      <c r="I21" s="59" t="inlineStr"/>
+      <c r="G21" s="60" t="inlineStr"/>
+      <c r="H21" s="60" t="inlineStr"/>
+      <c r="I21" s="60" t="inlineStr"/>
     </row>
     <row r="22" ht="60" customHeight="1">
-      <c r="A22" s="59" t="inlineStr">
+      <c r="A22" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-022</t>
         </is>
       </c>
-      <c r="B22" s="59" t="inlineStr">
+      <c r="B22" s="60" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C22" s="59" t="inlineStr">
+      <c r="C22" s="60" t="inlineStr">
         <is>
           <t>Measure the FCW onset after a lead brakes hard (WP-S-04 T-31, M-12) and compare it with the §3.8.2 budget (about 0.6 s at a 1.0 s gap). For pipeline lag (SFM-012.C1), detect it within that budget or show that the FCW path does not depend on the lagging process</t>
         </is>
       </c>
-      <c r="D22" s="59" t="inlineStr"/>
-      <c r="E22" s="59" t="inlineStr">
+      <c r="D22" s="60" t="inlineStr"/>
+      <c r="E22" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F22" s="59" t="inlineStr"/>
-      <c r="G22" s="59" t="inlineStr"/>
-      <c r="H22" s="59" t="inlineStr"/>
-      <c r="I22" s="59" t="inlineStr"/>
+      <c r="F22" s="60" t="inlineStr"/>
+      <c r="G22" s="60" t="inlineStr"/>
+      <c r="H22" s="60" t="inlineStr"/>
+      <c r="I22" s="60" t="inlineStr"/>
     </row>
     <row r="23" ht="195" customHeight="1">
-      <c r="A23" s="59" t="inlineStr">
+      <c r="A23" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-023</t>
         </is>
       </c>
-      <c r="B23" s="59" t="inlineStr">
+      <c r="B23" s="60" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C23" s="59" t="inlineStr">
+      <c r="C23" s="60" t="inlineStr">
         <is>
           <t>Escalate a temporary EPS fault that lasts while engaged to the take-over request (steerTempUnavailable, SOFT_DISABLE) instead of keeping the low-priority steerTempUnavailableSilent prompt latched after a recent override or at standstill (car_events.py; lead decision DQ-342, option A: the lighter prompt for at most 1.5 s, then the take-over request; TSR-607 (b)). SFM-038.C1; FTA BE-2.08</t>
         </is>
       </c>
-      <c r="D23" s="59" t="inlineStr"/>
-      <c r="E23" s="60" t="inlineStr">
+      <c r="D23" s="60" t="inlineStr"/>
+      <c r="E23" s="61" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="F23" s="59" t="inlineStr">
+      <c r="F23" s="60" t="inlineStr">
         <is>
           <t>SFM-038.C1</t>
         </is>
       </c>
-      <c r="G23" s="59" t="inlineStr">
+      <c r="G23" s="60" t="inlineStr">
         <is>
           <t>10/5/8</t>
         </is>
       </c>
-      <c r="H23" s="61" t="inlineStr">
+      <c r="H23" s="62" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="I23" s="59" t="inlineStr">
+      <c r="I23" s="60" t="inlineStr">
         <is>
           <t>Merged in jherrodthomas/LionDriver#174 (7158a9a): STEER_FAULT_SILENT_FRAMES in car_events.py limits the lighter prompt to the first 1.5 s of the fault; selfdrive/car/tests/test_steer_fault_warning.py, 6 tests run in CI, 4 of them fail on the old code. Impact record assurance/07-supporting/impact/change-2026-10-17-eps-fault-escalation.md. Unit-tested only: not verified on the vehicle (impact OI-1) and not reviewed independently. Credited at BL-006 (System FMEA rev 0.27): SFM-038.C1 O 8 -&gt; 5, D 10 -&gt; 8, AP stays H (S 10): the tests are targeted but not proven by mutation, so D 8 rather than the D 4 predicted below (rating tables D 8; a car_events.py mutation run, planned with SWF-ACT-077, would support D 4); f350f5b adds TSR-607 (c) for a fault while the driver steers</t>
         </is>
       </c>
     </row>
     <row r="24" ht="87" customHeight="1">
-      <c r="A24" s="59" t="inlineStr">
+      <c r="A24" s="60" t="inlineStr">
         <is>
           <t>SFM-ACT-024</t>
         </is>
       </c>
-      <c r="B24" s="59" t="inlineStr">
+      <c r="B24" s="60" t="inlineStr">
         <is>
           <t>monitoring</t>
         </is>
       </c>
-      <c r="C24" s="59" t="inlineStr">
+      <c r="C24" s="60" t="inlineStr">
         <is>
           <t>Act on the panda fields epsFault and requestsRejected on the host (TSR-626(d), TSR-516(b)): raise the take-over request when the panda reports an EPS fault or refused steering frames while lateral control is engaged, within the SG-02 1 s budget, instead of relying on the panda siren alone. Split from SFM-ACT-023 (rev 0.25). SFM-038.C2; FTA BE-2.08</t>
         </is>
       </c>
-      <c r="D24" s="59" t="inlineStr"/>
-      <c r="E24" s="59" t="inlineStr">
+      <c r="D24" s="60" t="inlineStr"/>
+      <c r="E24" s="60" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F24" s="59" t="inlineStr">
+      <c r="F24" s="60" t="inlineStr">
         <is>
           <t>SFM-038.C2</t>
         </is>
       </c>
-      <c r="G24" s="59" t="inlineStr"/>
-      <c r="H24" s="59" t="inlineStr"/>
-      <c r="I24" s="59" t="inlineStr"/>
+      <c r="G24" s="60" t="inlineStr"/>
+      <c r="H24" s="60" t="inlineStr"/>
+      <c r="I24" s="60" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I24"/>
@@ -21425,50 +21443,50 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="58" t="inlineStr">
+      <c r="A1" s="59" t="inlineStr">
         <is>
           <t>Element</t>
         </is>
       </c>
-      <c r="B1" s="58" t="inlineStr">
+      <c r="B1" s="59" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="58" t="inlineStr">
+      <c r="C1" s="59" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="D1" s="58" t="inlineStr">
+      <c r="D1" s="59" t="inlineStr">
         <is>
           <t>Parent</t>
         </is>
       </c>
-      <c r="E1" s="58" t="inlineStr">
+      <c r="E1" s="59" t="inlineStr">
         <is>
           <t>Functions</t>
         </is>
       </c>
     </row>
     <row r="2" ht="222" customHeight="1">
-      <c r="A2" s="59" t="inlineStr">
+      <c r="A2" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-001</t>
         </is>
       </c>
-      <c r="B2" s="59" t="inlineStr">
+      <c r="B2" s="60" t="inlineStr">
         <is>
           <t>LionDriver item (L2 ACC + ALC + driver monitoring)</t>
         </is>
       </c>
-      <c r="C2" s="59" t="inlineStr">
+      <c r="C2" s="60" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="D2" s="59" t="inlineStr"/>
-      <c r="E2" s="59" t="inlineStr">
+      <c r="D2" s="60" t="inlineStr"/>
+      <c r="E2" s="60" t="inlineStr">
         <is>
           <t>SFM-FN-001: F1 Lateral control: request steering torque from the EPS to keep the vehicle in its lane while engaged
 SFM-FN-002: F2 Longitudinal control: request acceleration/deceleration to hold set speed and follow leads while engaged
@@ -21482,398 +21500,398 @@
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="59" t="inlineStr">
+      <c r="A3" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="B3" s="59" t="inlineStr">
+      <c r="B3" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    comma 3X device</t>
         </is>
       </c>
-      <c r="C3" s="59" t="inlineStr">
+      <c r="C3" s="60" t="inlineStr">
         <is>
           <t>system</t>
         </is>
       </c>
-      <c r="D3" s="59" t="inlineStr">
+      <c r="D3" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-001</t>
         </is>
       </c>
-      <c r="E3" s="59" t="inlineStr"/>
+      <c r="E3" s="60" t="inlineStr"/>
     </row>
     <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="59" t="inlineStr">
+      <c r="A4" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-003</t>
         </is>
       </c>
-      <c r="B4" s="59" t="inlineStr">
+      <c r="B4" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Integrated panda (CAN interface and safety model)</t>
         </is>
       </c>
-      <c r="C4" s="59" t="inlineStr">
+      <c r="C4" s="60" t="inlineStr">
         <is>
           <t>subsystem</t>
         </is>
       </c>
-      <c r="D4" s="59" t="inlineStr">
+      <c r="D4" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E4" s="59" t="inlineStr"/>
+      <c r="E4" s="60" t="inlineStr"/>
     </row>
     <row r="5" ht="19.5" customHeight="1">
-      <c r="A5" s="59" t="inlineStr">
+      <c r="A5" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-004</t>
         </is>
       </c>
-      <c r="B5" s="59" t="inlineStr">
+      <c r="B5" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">    Harness (Toyota A connector, harness box, comma power v3)</t>
         </is>
       </c>
-      <c r="C5" s="59" t="inlineStr">
+      <c r="C5" s="60" t="inlineStr">
         <is>
           <t>component</t>
         </is>
       </c>
-      <c r="D5" s="59" t="inlineStr">
+      <c r="D5" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-001</t>
         </is>
       </c>
-      <c r="E5" s="59" t="inlineStr"/>
+      <c r="E5" s="60" t="inlineStr"/>
     </row>
     <row r="6" ht="19.5" customHeight="1">
-      <c r="A6" s="59" t="inlineStr">
+      <c r="A6" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-010</t>
         </is>
       </c>
-      <c r="B6" s="59" t="inlineStr">
+      <c r="B6" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Perception (camerad, modeld)</t>
         </is>
       </c>
-      <c r="C6" s="59" t="inlineStr">
+      <c r="C6" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D6" s="59" t="inlineStr">
+      <c r="D6" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E6" s="59" t="inlineStr"/>
+      <c r="E6" s="60" t="inlineStr"/>
     </row>
     <row r="7" ht="19.5" customHeight="1">
-      <c r="A7" s="59" t="inlineStr">
+      <c r="A7" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-011</t>
         </is>
       </c>
-      <c r="B7" s="59" t="inlineStr">
+      <c r="B7" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Localization and calibration (locationd, calibrationd, paramsd, torqued)</t>
         </is>
       </c>
-      <c r="C7" s="59" t="inlineStr">
+      <c r="C7" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D7" s="59" t="inlineStr">
+      <c r="D7" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E7" s="59" t="inlineStr"/>
+      <c r="E7" s="60" t="inlineStr"/>
     </row>
     <row r="8" ht="19.5" customHeight="1">
-      <c r="A8" s="59" t="inlineStr">
+      <c r="A8" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-012</t>
         </is>
       </c>
-      <c r="B8" s="59" t="inlineStr">
+      <c r="B8" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Planning (plannerd, radard)</t>
         </is>
       </c>
-      <c r="C8" s="59" t="inlineStr">
+      <c r="C8" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D8" s="59" t="inlineStr">
+      <c r="D8" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E8" s="59" t="inlineStr"/>
+      <c r="E8" s="60" t="inlineStr"/>
     </row>
     <row r="9" ht="19.5" customHeight="1">
-      <c r="A9" s="59" t="inlineStr">
+      <c r="A9" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-013</t>
         </is>
       </c>
-      <c r="B9" s="59" t="inlineStr">
+      <c r="B9" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Control (controlsd, lateral/longitudinal controllers)</t>
         </is>
       </c>
-      <c r="C9" s="59" t="inlineStr">
+      <c r="C9" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D9" s="59" t="inlineStr">
+      <c r="D9" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E9" s="59" t="inlineStr"/>
+      <c r="E9" s="60" t="inlineStr"/>
     </row>
     <row r="10" ht="19.5" customHeight="1">
-      <c r="A10" s="59" t="inlineStr">
+      <c r="A10" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-014</t>
         </is>
       </c>
-      <c r="B10" s="59" t="inlineStr">
+      <c r="B10" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Supervision (selfdrived state machine, events, alert manager)</t>
         </is>
       </c>
-      <c r="C10" s="59" t="inlineStr">
+      <c r="C10" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D10" s="59" t="inlineStr">
+      <c r="D10" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E10" s="59" t="inlineStr"/>
+      <c r="E10" s="60" t="inlineStr"/>
     </row>
     <row r="11" ht="19.5" customHeight="1">
-      <c r="A11" s="59" t="inlineStr">
+      <c r="A11" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-015</t>
         </is>
       </c>
-      <c r="B11" s="59" t="inlineStr">
+      <c r="B11" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Driver monitoring (dmonitoringmodeld, dmonitoringd)</t>
         </is>
       </c>
-      <c r="C11" s="59" t="inlineStr">
+      <c r="C11" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D11" s="59" t="inlineStr">
+      <c r="D11" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E11" s="59" t="inlineStr"/>
+      <c r="E11" s="60" t="inlineStr"/>
     </row>
     <row r="12" ht="19.5" customHeight="1">
-      <c r="A12" s="59" t="inlineStr">
+      <c r="A12" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-016</t>
         </is>
       </c>
-      <c r="B12" s="59" t="inlineStr">
+      <c r="B12" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Car interface (card, car_events, opendbc Toyota port)</t>
         </is>
       </c>
-      <c r="C12" s="59" t="inlineStr">
+      <c r="C12" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D12" s="59" t="inlineStr">
+      <c r="D12" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E12" s="59" t="inlineStr"/>
+      <c r="E12" s="60" t="inlineStr"/>
     </row>
     <row r="13" ht="19.5" customHeight="1">
-      <c r="A13" s="59" t="inlineStr">
+      <c r="A13" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-017</t>
         </is>
       </c>
-      <c r="B13" s="59" t="inlineStr">
+      <c r="B13" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Panda daemon (pandad)</t>
         </is>
       </c>
-      <c r="C13" s="59" t="inlineStr">
+      <c r="C13" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D13" s="59" t="inlineStr">
+      <c r="D13" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E13" s="59" t="inlineStr"/>
+      <c r="E13" s="60" t="inlineStr"/>
     </row>
     <row r="14" ht="19.5" customHeight="1">
-      <c r="A14" s="59" t="inlineStr">
+      <c r="A14" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-018</t>
         </is>
       </c>
-      <c r="B14" s="59" t="inlineStr">
+      <c r="B14" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        HMI (ui, soundd)</t>
         </is>
       </c>
-      <c r="C14" s="59" t="inlineStr">
+      <c r="C14" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D14" s="59" t="inlineStr">
+      <c r="D14" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E14" s="59" t="inlineStr"/>
+      <c r="E14" s="60" t="inlineStr"/>
     </row>
     <row r="15" ht="19.5" customHeight="1">
-      <c r="A15" s="59" t="inlineStr">
+      <c r="A15" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-019</t>
         </is>
       </c>
-      <c r="B15" s="59" t="inlineStr">
+      <c r="B15" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">        Platform (manager, messaging, hardwared, OS)</t>
         </is>
       </c>
-      <c r="C15" s="59" t="inlineStr">
+      <c r="C15" s="60" t="inlineStr">
         <is>
           <t>sw_element</t>
         </is>
       </c>
-      <c r="D15" s="59" t="inlineStr">
+      <c r="D15" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-002</t>
         </is>
       </c>
-      <c r="E15" s="59" t="inlineStr"/>
+      <c r="E15" s="60" t="inlineStr"/>
     </row>
     <row r="16" ht="19.5" customHeight="1">
-      <c r="A16" s="59" t="inlineStr">
+      <c r="A16" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-030</t>
         </is>
       </c>
-      <c r="B16" s="59" t="inlineStr">
+      <c r="B16" s="60" t="inlineStr">
         <is>
           <t>Toyota EPS</t>
         </is>
       </c>
-      <c r="C16" s="59" t="inlineStr">
+      <c r="C16" s="60" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D16" s="59" t="inlineStr"/>
-      <c r="E16" s="59" t="inlineStr"/>
+      <c r="D16" s="60" t="inlineStr"/>
+      <c r="E16" s="60" t="inlineStr"/>
     </row>
     <row r="17" ht="19.5" customHeight="1">
-      <c r="A17" s="59" t="inlineStr">
+      <c r="A17" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-031</t>
         </is>
       </c>
-      <c r="B17" s="59" t="inlineStr">
+      <c r="B17" s="60" t="inlineStr">
         <is>
           <t>Toyota powertrain and brake control (receives ACC acceleration requests)</t>
         </is>
       </c>
-      <c r="C17" s="59" t="inlineStr">
+      <c r="C17" s="60" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D17" s="59" t="inlineStr"/>
-      <c r="E17" s="59" t="inlineStr"/>
+      <c r="D17" s="60" t="inlineStr"/>
+      <c r="E17" s="60" t="inlineStr"/>
     </row>
     <row r="18" ht="19.5" customHeight="1">
-      <c r="A18" s="59" t="inlineStr">
+      <c r="A18" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-032</t>
         </is>
       </c>
-      <c r="B18" s="59" t="inlineStr">
+      <c r="B18" s="60" t="inlineStr">
         <is>
           <t>Toyota stock ADAS camera (TSS2)</t>
         </is>
       </c>
-      <c r="C18" s="59" t="inlineStr">
+      <c r="C18" s="60" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D18" s="59" t="inlineStr"/>
-      <c r="E18" s="59" t="inlineStr"/>
+      <c r="D18" s="60" t="inlineStr"/>
+      <c r="E18" s="60" t="inlineStr"/>
     </row>
     <row r="19" ht="19.5" customHeight="1">
-      <c r="A19" s="59" t="inlineStr">
+      <c r="A19" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-033</t>
         </is>
       </c>
-      <c r="B19" s="59" t="inlineStr">
+      <c r="B19" s="60" t="inlineStr">
         <is>
           <t>Vehicle CAN buses and 12 V supply</t>
         </is>
       </c>
-      <c r="C19" s="59" t="inlineStr">
+      <c r="C19" s="60" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D19" s="59" t="inlineStr"/>
-      <c r="E19" s="59" t="inlineStr"/>
+      <c r="D19" s="60" t="inlineStr"/>
+      <c r="E19" s="60" t="inlineStr"/>
     </row>
     <row r="20" ht="19.5" customHeight="1">
-      <c r="A20" s="59" t="inlineStr">
+      <c r="A20" s="60" t="inlineStr">
         <is>
           <t>SFM-SE-034</t>
         </is>
       </c>
-      <c r="B20" s="59" t="inlineStr">
+      <c r="B20" s="60" t="inlineStr">
         <is>
           <t>Driver</t>
         </is>
       </c>
-      <c r="C20" s="59" t="inlineStr">
+      <c r="C20" s="60" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D20" s="59" t="inlineStr"/>
-      <c r="E20" s="59" t="inlineStr"/>
+      <c r="D20" s="60" t="inlineStr"/>
+      <c r="E20" s="60" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E20"/>
@@ -21909,7 +21927,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="62" t="inlineStr">
+      <c r="A1" s="63" t="inlineStr">
         <is>
           <t>FMEA-MSR (monitoring and system response, msr-plan.md): S, F, M and MSR AP per rating-tables.md §7 (RT-3, handbook MSR AP table for S 9–10). Exempt causes are rated in the FMEA named in the reason.</t>
         </is>
@@ -22104,7 +22122,7 @@
       <c r="I4" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="J4" s="46" t="n">
+      <c r="J4" s="47" t="n">
         <v>10</v>
       </c>
       <c r="K4" s="36" t="inlineStr">
@@ -22500,7 +22518,7 @@
       <c r="I10" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="J10" s="46" t="n">
+      <c r="J10" s="47" t="n">
         <v>10</v>
       </c>
       <c r="K10" s="36" t="inlineStr">
@@ -22562,7 +22580,7 @@
       <c r="I11" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="J11" s="46" t="n">
+      <c r="J11" s="47" t="n">
         <v>10</v>
       </c>
       <c r="K11" s="36" t="inlineStr">
@@ -22624,7 +22642,7 @@
       <c r="I12" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="J12" s="46" t="n">
+      <c r="J12" s="47" t="n">
         <v>10</v>
       </c>
       <c r="K12" s="36" t="inlineStr">
@@ -22686,7 +22704,7 @@
       <c r="I13" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="J13" s="46" t="n">
+      <c r="J13" s="47" t="n">
         <v>10</v>
       </c>
       <c r="K13" s="36" t="inlineStr">
@@ -22748,7 +22766,7 @@
       <c r="I14" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="J14" s="46" t="n">
+      <c r="J14" s="47" t="n">
         <v>10</v>
       </c>
       <c r="K14" s="36" t="inlineStr">
@@ -23014,7 +23032,7 @@
       <c r="I18" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="J18" s="46" t="n">
+      <c r="J18" s="47" t="n">
         <v>10</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
@@ -23144,7 +23162,7 @@
       <c r="I20" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="J20" s="46" t="n">
+      <c r="J20" s="47" t="n">
         <v>10</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
@@ -23206,7 +23224,7 @@
       <c r="I21" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="J21" s="46" t="n">
+      <c r="J21" s="47" t="n">
         <v>10</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
@@ -23335,7 +23353,7 @@
       <c r="I23" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="J23" s="46" t="n">
+      <c r="J23" s="47" t="n">
         <v>9</v>
       </c>
       <c r="K23" s="36" t="inlineStr">
@@ -23397,7 +23415,7 @@
       <c r="I24" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="J24" s="46" t="n">
+      <c r="J24" s="47" t="n">
         <v>9</v>
       </c>
       <c r="K24" s="36" t="inlineStr">
@@ -23459,7 +23477,7 @@
       <c r="I25" s="35" t="n">
         <v>7</v>
       </c>
-      <c r="J25" s="46" t="n">
+      <c r="J25" s="47" t="n">
         <v>9</v>
       </c>
       <c r="K25" s="36" t="inlineStr">
@@ -23723,7 +23741,7 @@
       <c r="I29" s="35" t="n">
         <v>7</v>
       </c>
-      <c r="J29" s="46" t="n">
+      <c r="J29" s="47" t="n">
         <v>9</v>
       </c>
       <c r="K29" s="36" t="inlineStr">
@@ -23852,7 +23870,7 @@
       <c r="I31" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="J31" s="46" t="n">
+      <c r="J31" s="47" t="n">
         <v>9</v>
       </c>
       <c r="K31" s="36" t="inlineStr">
@@ -23914,7 +23932,7 @@
       <c r="I32" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="J32" s="46" t="n">
+      <c r="J32" s="47" t="n">
         <v>10</v>
       </c>
       <c r="K32" s="36" t="inlineStr">
@@ -23972,7 +23990,7 @@
       <c r="I33" s="35" t="n">
         <v>7</v>
       </c>
-      <c r="J33" s="46" t="n">
+      <c r="J33" s="47" t="n">
         <v>9</v>
       </c>
       <c r="K33" s="36" t="inlineStr">
@@ -24168,7 +24186,7 @@
       <c r="I36" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="J36" s="46" t="n">
+      <c r="J36" s="47" t="n">
         <v>10</v>
       </c>
       <c r="K36" s="36" t="inlineStr">
@@ -24298,7 +24316,7 @@
       <c r="I38" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="J38" s="46" t="n">
+      <c r="J38" s="47" t="n">
         <v>10</v>
       </c>
       <c r="K38" s="36" t="inlineStr">
@@ -24427,7 +24445,7 @@
       <c r="I40" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="J40" s="46" t="n">
+      <c r="J40" s="47" t="n">
         <v>10</v>
       </c>
       <c r="K40" s="36" t="inlineStr">
@@ -24623,7 +24641,7 @@
       <c r="I43" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="J43" s="46" t="n">
+      <c r="J43" s="47" t="n">
         <v>10</v>
       </c>
       <c r="K43" s="36" t="inlineStr">
@@ -24681,7 +24699,7 @@
       <c r="I44" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="J44" s="46" t="n">
+      <c r="J44" s="47" t="n">
         <v>10</v>
       </c>
       <c r="K44" s="36" t="inlineStr">
@@ -24743,10 +24761,10 @@
       <c r="I45" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="J45" s="46" t="n">
+      <c r="J45" s="47" t="n">
         <v>10</v>
       </c>
-      <c r="K45" s="63" t="inlineStr">
+      <c r="K45" s="49" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -24801,7 +24819,7 @@
       <c r="I46" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="J46" s="46" t="n">
+      <c r="J46" s="47" t="n">
         <v>10</v>
       </c>
       <c r="K46" s="36" t="inlineStr">
@@ -25137,7 +25155,7 @@
       <c r="I52" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="J52" s="46" t="n">
+      <c r="J52" s="47" t="n">
         <v>10</v>
       </c>
       <c r="K52" s="36" t="inlineStr">
@@ -25195,7 +25213,7 @@
       <c r="I53" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="J53" s="46" t="n">
+      <c r="J53" s="47" t="n">
         <v>10</v>
       </c>
       <c r="K53" s="36" t="inlineStr">
@@ -25257,7 +25275,7 @@
       <c r="I54" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="J54" s="46" t="n">
+      <c r="J54" s="47" t="n">
         <v>10</v>
       </c>
       <c r="K54" s="36" t="inlineStr">
@@ -25621,7 +25639,7 @@
       <c r="I60" s="35" t="n">
         <v>7</v>
       </c>
-      <c r="J60" s="46" t="n">
+      <c r="J60" s="47" t="n">
         <v>9</v>
       </c>
       <c r="K60" s="36" t="inlineStr">
@@ -25683,7 +25701,7 @@
       <c r="I61" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="J61" s="46" t="n">
+      <c r="J61" s="47" t="n">
         <v>9</v>
       </c>
       <c r="K61" s="36" t="inlineStr">
@@ -25807,7 +25825,7 @@
       <c r="I63" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="J63" s="46" t="n">
+      <c r="J63" s="47" t="n">
         <v>10</v>
       </c>
       <c r="K63" s="36" t="inlineStr">
@@ -25927,7 +25945,7 @@
       <c r="I65" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="J65" s="46" t="n">
+      <c r="J65" s="47" t="n">
         <v>10</v>
       </c>
       <c r="K65" s="36" t="inlineStr">
@@ -25989,7 +26007,7 @@
       <c r="I66" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="J66" s="46" t="n">
+      <c r="J66" s="47" t="n">
         <v>10</v>
       </c>
       <c r="K66" s="36" t="inlineStr">
@@ -26051,7 +26069,7 @@
       <c r="I67" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="J67" s="46" t="n">
+      <c r="J67" s="47" t="n">
         <v>10</v>
       </c>
       <c r="K67" s="36" t="inlineStr">
@@ -26179,7 +26197,7 @@
       <c r="I69" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="J69" s="46" t="n">
+      <c r="J69" s="47" t="n">
         <v>10</v>
       </c>
       <c r="K69" s="36" t="inlineStr">
@@ -26277,10 +26295,10 @@
       <c r="I71" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="J71" s="46" t="n">
+      <c r="J71" s="47" t="n">
         <v>10</v>
       </c>
-      <c r="K71" s="63" t="inlineStr">
+      <c r="K71" s="49" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -26335,7 +26353,7 @@
       <c r="I72" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="J72" s="46" t="n">
+      <c r="J72" s="47" t="n">
         <v>10</v>
       </c>
       <c r="K72" s="36" t="inlineStr">
@@ -26393,7 +26411,7 @@
       <c r="I73" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="J73" s="46" t="n">
+      <c r="J73" s="47" t="n">
         <v>10</v>
       </c>
       <c r="K73" s="36" t="inlineStr">
@@ -26832,7 +26850,7 @@
       <c r="I83" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="J83" s="46" t="n">
+      <c r="J83" s="47" t="n">
         <v>10</v>
       </c>
       <c r="K83" s="36" t="inlineStr">
@@ -27147,7 +27165,7 @@
       <c r="I88" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="J88" s="46" t="n">
+      <c r="J88" s="47" t="n">
         <v>9</v>
       </c>
       <c r="K88" s="36" t="inlineStr">
@@ -27291,7 +27309,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.37 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.38 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -823,7 +823,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.38 · draft</t>
+          <t>0.39 · draft</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>1–4: 0 · 5–6: 18 · 7–8: 19 · 9–10: 38 (see sheet MSR)</t>
+          <t>1–4: 0 · 5–6: 18 · 7–8: 20 · 9–10: 37 (see sheet MSR)</t>
         </is>
       </c>
     </row>
@@ -12466,7 +12466,7 @@
       <c r="R66" s="37" t="inlineStr"/>
       <c r="S66" s="37" t="inlineStr"/>
     </row>
-    <row r="67" ht="87" customHeight="1">
+    <row r="67" ht="141" customHeight="1">
       <c r="A67" s="39" t="n"/>
       <c r="B67" s="39" t="n"/>
       <c r="C67" s="39" t="n"/>
@@ -12486,7 +12486,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Driver monitoring runs in demo mode while the item is engaged (IsDriverViewEnabled left set): the policy uses a synthetic vehicle state and the monitored seat can switch, so the actual driver may not be watched (GAP-20, TSR-610 not met)</t>
+            <t>Driver monitoring runs in demo mode while the item is engaged (IsDriverViewEnabled left set): the policy uses a synthetic vehicle state and the monitored seat can switch, so the actual driver may not be watched. Since SW FMEA rev 1.14 (TSR-610, DQ-427) dmonitoringd ignores demo mode while started and selfdrived refuses engagement and soft-disables while the parameter is set; the remaining cause is a defect in those checks</t>
           </r>
           <r>
             <rPr>
@@ -12507,7 +12507,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• The cabin camera dialog opens only offroad and its buttons are disabled onroad; no engagement interlock; rated in the SW FMEA</t>
+            <t>• LionDriver change with a requirement (TSR-610, SWSR-610): demo mode only offroad, engagement interlock in selfdrived; O 5, as rated in the SW FMEA</t>
           </r>
           <r>
             <rPr>
@@ -12516,27 +12516,36 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   openpilot/selfdrive/monitoring/dmonitoringd.py</t>
+   assurance/07-supporting/impact/change-2026-10-29-driver-view-interlock.md</t>
           </r>
         </is>
       </c>
       <c r="J67" s="42" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K67" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• As rated in the SW FMEA (SWF-085, D 10): no test covers demo mode with the item started</t>
-          </r>
-        </is>
-      </c>
-      <c r="L67" s="43" t="n">
-        <v>10</v>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• test_driver_view.py with the item started, proven by mutants DV-1..DV-6 in CI; D 4, from D 10 (SW FMEA rev 1.14)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   openpilot/selfdrive/selfdrived/tests/test_driver_view.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L67" s="42" t="n">
+        <v>4</v>
       </c>
       <c r="M67" s="44" t="inlineStr">
         <is>
@@ -20500,7 +20509,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.38 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.39 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -25785,7 +25794,7 @@
       <c r="O62" s="37" t="inlineStr"/>
       <c r="P62" s="37" t="inlineStr"/>
     </row>
-    <row r="63" ht="100.5" customHeight="1">
+    <row r="63" ht="168" customHeight="1">
       <c r="A63" s="34" t="inlineStr">
         <is>
           <t>SFM-022 · Inattentive driver not detected</t>
@@ -25801,32 +25810,32 @@
       </c>
       <c r="D63" s="34" t="inlineStr">
         <is>
-          <t>Driver monitoring runs in demo mode while the item is engaged (IsDriverViewEnabled left set): the policy uses a synthetic vehicle state and the monitored seat can switch, so the actual driver may not be watched (GAP-20, TSR-610 not met)</t>
+          <t>Driver monitoring runs in demo mode while the item is engaged (IsDriverViewEnabled left set): the policy uses a synthetic vehicle state and the monitored seat can switch, so the actual driver may not be watched. Since SW FMEA rev 1.14 (TSR-610, DQ-427) dmonitoringd ignores demo mode while started and selfdrived refuses engagement and soft-disables while the parameter is set; the remaining cause is a defect in those checks</t>
         </is>
       </c>
       <c r="E63" s="34" t="inlineStr">
         <is>
-          <t>None: the camera is alive and the model can be confident, so neither the wheel-touch fallback nor cameraMalfunction acts</t>
+          <t>selfdrived reads IsDriverViewEnabled at start and every 0.1 s and raises driverViewActive (TSR-610)</t>
         </is>
       </c>
       <c r="F63" s="34" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>NO_ENTRY while set; SOFT_DISABLE with a take-over alert if set while engaged. dmonitoringd keeps monitoring the real driver while started</t>
         </is>
       </c>
       <c r="G63" s="34" t="inlineStr">
         <is>
-          <t>Unchanged: alerts still escalate on the camera input, possibly for the wrong seat</t>
+          <t>Not engaged with demo mode; if set while engaged, the driver takes over within the soft-disable time</t>
         </is>
       </c>
       <c r="H63" s="35" t="n">
         <v>10</v>
       </c>
       <c r="I63" s="35" t="n">
-        <v>8</v>
-      </c>
-      <c r="J63" s="47" t="n">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="J63" s="35" t="n">
+        <v>7</v>
       </c>
       <c r="K63" s="36" t="inlineStr">
         <is>
@@ -27309,7 +27318,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.38 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.39 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/system-fmea-review.xlsx
@@ -823,7 +823,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.39 · draft</t>
+          <t>0.40 · draft</t>
         </is>
       </c>
     </row>
@@ -18960,7 +18960,7 @@
       <c r="R103" s="45" t="inlineStr"/>
       <c r="S103" s="45" t="inlineStr"/>
     </row>
-    <row r="104" ht="154.5" customHeight="1">
+    <row r="104" ht="168" customHeight="1">
       <c r="A104" s="30" t="inlineStr">
         <is>
           <r>
@@ -19158,7 +19158,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• test_stock_aeb.py (4 tests) in the CI unit_tests job (tests run 39296172878); targeted, not proven by mutation, so D 8. The opendbc test_carcontroller.py cases ran locally only (LionDriver CI does not run opendbc car tests). Not verified on the vehicle (the AOU-04R test also checks that stockAeb is reported during a PCS event)</t>
+            <t>• Proven by mutation in CI (System FMEA rev 0.40): test_stock_aeb.py and test_controlsd_call_sites.py on the host stand-down (AE-1..AE-3) and opendbc test_carcontroller.py on the 0x343 cap (AE-5, AE-6), all in the unit_tests job, as SWF-093.C1/C2; D 4, from D 8. Not verified on the vehicle (the AOU-04R test also checks that stockAeb is reported during a PCS event)</t>
           </r>
           <r>
             <rPr>
@@ -19172,7 +19172,7 @@
         </is>
       </c>
       <c r="L104" s="35" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M104" s="36" t="inlineStr">
         <is>
@@ -20509,7 +20509,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.39 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · rev 0.40 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -27318,7 +27318,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.39 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LSystem FMEA — LionDriver L2 ACC/ALC item · FMEA-MSR · rev 0.40 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
